--- a/Info/Additional_information.xlsx
+++ b/Info/Additional_information.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FB770B6-8FF7-4B6A-A0A4-C1329223206A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{053A286D-8064-46E8-A879-D96F00A4EBE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Colours_specifications" sheetId="1" r:id="rId1"/>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="373">
   <si>
     <t>good quality (UNC for UNC collection; UNC and XF for XF collection)</t>
   </si>
@@ -342,9 +342,6 @@
     <t>San_Marino</t>
   </si>
   <si>
-    <t>1 - 5</t>
-  </si>
-  <si>
     <t>1# - 6#</t>
   </si>
   <si>
@@ -352,9 +349,6 @@
   </si>
   <si>
     <t>2*- 4*</t>
-  </si>
-  <si>
-    <t>6 - 7</t>
   </si>
   <si>
     <t>1# - 2#</t>
@@ -1172,6 +1166,33 @@
   </si>
   <si>
     <t>ЕМ</t>
+  </si>
+  <si>
+    <t>1 - 6</t>
+  </si>
+  <si>
+    <t>7 - 8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>#Coin_denomination</t>
+  </si>
+  <si>
+    <t>Bulgarian Mint</t>
+  </si>
+  <si>
+    <t>Българският монетен двор</t>
+  </si>
+  <si>
+    <t>Bulgaria</t>
+  </si>
+  <si>
+    <t>Sofia</t>
+  </si>
+  <si>
+    <t>BNB</t>
   </si>
 </sst>
 </file>
@@ -1723,7 +1744,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1966,6 +1987,9 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -2523,8 +2547,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{973D7237-72C7-453E-A0E1-526C93326B28}" name="Таблица3" displayName="Таблица3" ref="A1:F50" totalsRowShown="0" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
-  <autoFilter ref="A1:F50" xr:uid="{A2D8FA3D-4024-4365-BE1D-F93D0AF2D426}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{973D7237-72C7-453E-A0E1-526C93326B28}" name="Таблица3" displayName="Таблица3" ref="A1:F51" totalsRowShown="0" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
+  <autoFilter ref="A1:F51" xr:uid="{A2D8FA3D-4024-4365-BE1D-F93D0AF2D426}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{12C2DF0B-47FA-46A4-8424-55A1488EF88B}" name="ID" dataDxfId="22"/>
     <tableColumn id="2" xr3:uid="{EB0B36CE-168D-429E-896D-DBA54794224F}" name="Name_Eng" dataDxfId="21"/>
@@ -2538,8 +2562,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9D0F8E3D-96B1-4DB8-B1A6-8DD6B84F3693}" name="Таблица35" displayName="Таблица35" ref="A1:D51" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13" totalsRowBorderDxfId="12">
-  <autoFilter ref="A1:D51" xr:uid="{A2D8FA3D-4024-4365-BE1D-F93D0AF2D426}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9D0F8E3D-96B1-4DB8-B1A6-8DD6B84F3693}" name="Таблица35" displayName="Таблица35" ref="A1:D52" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13" totalsRowBorderDxfId="12">
+  <autoFilter ref="A1:D52" xr:uid="{A2D8FA3D-4024-4365-BE1D-F93D0AF2D426}"/>
   <tableColumns count="4">
     <tableColumn id="4" xr3:uid="{74AFB32D-7AAA-46BE-8174-ED698BB4613E}" name="Mint_id" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{523D65CD-0F56-441F-90B5-E46A9B14F0D0}" name="Ekaterinburg Mint" dataDxfId="10"/>
@@ -3163,7 +3187,7 @@
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="78"/>
       <c r="B7" s="16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>69</v>
@@ -3222,7 +3246,7 @@
     <row r="14" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="80"/>
       <c r="B14" s="26" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C14" s="13" t="s">
         <v>65</v>
@@ -3233,7 +3257,7 @@
         <v>2</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>89</v>
+        <v>364</v>
       </c>
       <c r="C15" s="14" t="s">
         <v>84</v>
@@ -3242,7 +3266,7 @@
     <row r="16" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="82"/>
       <c r="B16" s="20" t="s">
-        <v>93</v>
+        <v>365</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>85</v>
@@ -3250,8 +3274,8 @@
     </row>
     <row r="17" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="82"/>
-      <c r="B17" s="21">
-        <v>8</v>
+      <c r="B17" s="21" t="s">
+        <v>366</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>86</v>
@@ -3260,7 +3284,7 @@
     <row r="18" spans="1:3" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="83"/>
       <c r="B18" s="22" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C18" s="13" t="s">
         <v>86</v>
@@ -3271,7 +3295,7 @@
         <v>3</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C19" s="14" t="s">
         <v>87</v>
@@ -3280,7 +3304,7 @@
     <row r="20" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="71"/>
       <c r="B20" s="27" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>88</v>
@@ -3289,10 +3313,10 @@
     <row r="21" spans="1:3" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="72"/>
       <c r="B21" s="28" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="14.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
@@ -3300,55 +3324,55 @@
         <v>4</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="74"/>
       <c r="B23" s="20" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="74"/>
       <c r="B24" s="21" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="74"/>
       <c r="B25" s="16" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="74"/>
       <c r="B26" s="29" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="74"/>
       <c r="B27" s="30" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
@@ -3357,7 +3381,7 @@
         <v>8</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3366,7 +3390,7 @@
         <v>78</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
@@ -3391,7 +3415,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4C14141-45DA-4C30-845C-3E630B347F10}">
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.54296875" style="41" customWidth="1"/>
@@ -3406,19 +3430,19 @@
         <v>7</v>
       </c>
       <c r="B1" s="33" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C1" s="33" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D1" s="33" t="s">
         <v>21</v>
       </c>
       <c r="E1" s="33" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F1" s="34" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -3426,19 +3450,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="36" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D2" s="36" t="s">
         <v>64</v>
       </c>
       <c r="E2" s="36" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F2" s="37" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -3446,19 +3470,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C3" s="36" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D3" s="36" t="s">
         <v>84</v>
       </c>
       <c r="E3" s="36" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F3" s="39" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -3466,19 +3490,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="36" t="s">
+        <v>119</v>
+      </c>
+      <c r="C4" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="D4" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="E4" s="36" t="s">
         <v>121</v>
       </c>
-      <c r="C4" s="36" t="s">
+      <c r="F4" s="37" t="s">
         <v>122</v>
-      </c>
-      <c r="D4" s="36" t="s">
-        <v>101</v>
-      </c>
-      <c r="E4" s="36" t="s">
-        <v>123</v>
-      </c>
-      <c r="F4" s="37" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -3486,19 +3510,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C5" s="40" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D5" s="40" t="s">
         <v>68</v>
       </c>
       <c r="E5" s="36" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F5" s="37" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -3506,19 +3530,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D6" s="36" t="s">
         <v>65</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F6" s="37" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -3526,19 +3550,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D7" s="36" t="s">
         <v>73</v>
       </c>
       <c r="E7" s="36" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F7" s="37" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -3546,19 +3570,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="36" t="s">
+        <v>135</v>
+      </c>
+      <c r="C8" s="36" t="s">
+        <v>136</v>
+      </c>
+      <c r="D8" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="E8" s="36" t="s">
         <v>137</v>
       </c>
-      <c r="C8" s="36" t="s">
+      <c r="F8" s="37" t="s">
         <v>138</v>
-      </c>
-      <c r="D8" s="36" t="s">
-        <v>107</v>
-      </c>
-      <c r="E8" s="36" t="s">
-        <v>139</v>
-      </c>
-      <c r="F8" s="37" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -3566,19 +3590,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="36" t="s">
+        <v>139</v>
+      </c>
+      <c r="C9" s="36" t="s">
+        <v>140</v>
+      </c>
+      <c r="D9" s="36" t="s">
+        <v>107</v>
+      </c>
+      <c r="E9" s="36" t="s">
         <v>141</v>
       </c>
-      <c r="C9" s="36" t="s">
+      <c r="F9" s="36" t="s">
         <v>142</v>
-      </c>
-      <c r="D9" s="36" t="s">
-        <v>109</v>
-      </c>
-      <c r="E9" s="36" t="s">
-        <v>143</v>
-      </c>
-      <c r="F9" s="36" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -3586,19 +3610,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="36" t="s">
+        <v>143</v>
+      </c>
+      <c r="C10" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="D10" s="36" t="s">
+        <v>97</v>
+      </c>
+      <c r="E10" s="36" t="s">
         <v>145</v>
       </c>
-      <c r="C10" s="36" t="s">
+      <c r="F10" s="36" t="s">
         <v>146</v>
-      </c>
-      <c r="D10" s="36" t="s">
-        <v>99</v>
-      </c>
-      <c r="E10" s="36" t="s">
-        <v>147</v>
-      </c>
-      <c r="F10" s="36" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -3606,19 +3630,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D11" s="36" t="s">
         <v>84</v>
       </c>
       <c r="E11" s="36" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F11" s="36" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
@@ -3626,19 +3650,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C12" s="39" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D12" s="36" t="s">
         <v>84</v>
       </c>
       <c r="E12" s="39" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F12" s="39" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
@@ -3646,19 +3670,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C13" s="39" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D13" s="36" t="s">
         <v>84</v>
       </c>
       <c r="E13" s="39" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F13" s="39" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
@@ -3666,19 +3690,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C14" s="39" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D14" s="36" t="s">
         <v>84</v>
       </c>
       <c r="E14" s="39" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F14" s="39" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
@@ -3686,19 +3710,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="39" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C15" s="39" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D15" s="36" t="s">
         <v>84</v>
       </c>
       <c r="E15" s="39" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F15" s="39" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
@@ -3706,19 +3730,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C16" s="39" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D16" s="36" t="s">
         <v>84</v>
       </c>
       <c r="E16" s="39" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F16" s="39" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
@@ -3726,19 +3750,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="39" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C17" s="39" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D17" s="36" t="s">
         <v>84</v>
       </c>
       <c r="E17" s="39" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F17" s="39" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
@@ -3746,19 +3770,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="39" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C18" s="39" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D18" s="36" t="s">
         <v>84</v>
       </c>
       <c r="E18" s="39" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F18" s="39" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
@@ -3766,19 +3790,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="39" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C19" s="39" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D19" s="36" t="s">
         <v>84</v>
       </c>
       <c r="E19" s="39" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F19" s="39" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
@@ -3786,19 +3810,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="36" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C20" s="36" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D20" s="36" t="s">
         <v>84</v>
       </c>
       <c r="E20" s="36" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F20" s="36" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
@@ -3806,19 +3830,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="39" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C21" s="39" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D21" s="39" t="s">
         <v>72</v>
       </c>
       <c r="E21" s="39" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F21" s="39" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
@@ -3826,19 +3850,19 @@
         <v>21</v>
       </c>
       <c r="B22" s="36" t="s">
+        <v>189</v>
+      </c>
+      <c r="C22" s="36" t="s">
+        <v>190</v>
+      </c>
+      <c r="D22" s="36" t="s">
+        <v>103</v>
+      </c>
+      <c r="E22" s="36" t="s">
         <v>191</v>
       </c>
-      <c r="C22" s="36" t="s">
+      <c r="F22" s="36" t="s">
         <v>192</v>
-      </c>
-      <c r="D22" s="36" t="s">
-        <v>105</v>
-      </c>
-      <c r="E22" s="36" t="s">
-        <v>193</v>
-      </c>
-      <c r="F22" s="36" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
@@ -3846,19 +3870,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="36" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C23" s="36" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D23" s="36" t="s">
         <v>71</v>
       </c>
       <c r="E23" s="36" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F23" s="36" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
@@ -3866,19 +3890,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="36" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C24" s="36" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D24" s="36" t="s">
         <v>69</v>
       </c>
       <c r="E24" s="36" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F24" s="36" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
@@ -3886,19 +3910,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="36" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C25" s="36" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D25" s="36" t="s">
         <v>83</v>
       </c>
       <c r="E25" s="36" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F25" s="36" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
@@ -3906,19 +3930,19 @@
         <v>25</v>
       </c>
       <c r="B26" s="39" t="s">
+        <v>205</v>
+      </c>
+      <c r="C26" s="39" t="s">
+        <v>206</v>
+      </c>
+      <c r="D26" s="39" t="s">
         <v>207</v>
       </c>
-      <c r="C26" s="39" t="s">
+      <c r="E26" s="39" t="s">
         <v>208</v>
       </c>
-      <c r="D26" s="39" t="s">
+      <c r="F26" s="39" t="s">
         <v>209</v>
-      </c>
-      <c r="E26" s="39" t="s">
-        <v>210</v>
-      </c>
-      <c r="F26" s="39" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
@@ -3926,19 +3950,19 @@
         <v>26</v>
       </c>
       <c r="B27" s="36" t="s">
+        <v>210</v>
+      </c>
+      <c r="C27" s="36" t="s">
+        <v>211</v>
+      </c>
+      <c r="D27" s="39" t="s">
+        <v>207</v>
+      </c>
+      <c r="E27" s="36" t="s">
         <v>212</v>
       </c>
-      <c r="C27" s="36" t="s">
+      <c r="F27" s="36" t="s">
         <v>213</v>
-      </c>
-      <c r="D27" s="39" t="s">
-        <v>209</v>
-      </c>
-      <c r="E27" s="36" t="s">
-        <v>214</v>
-      </c>
-      <c r="F27" s="36" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
@@ -3946,19 +3970,19 @@
         <v>27</v>
       </c>
       <c r="B28" s="39" t="s">
+        <v>214</v>
+      </c>
+      <c r="C28" s="39" t="s">
+        <v>215</v>
+      </c>
+      <c r="D28" s="39" t="s">
         <v>216</v>
       </c>
-      <c r="C28" s="39" t="s">
+      <c r="E28" s="39" t="s">
         <v>217</v>
       </c>
-      <c r="D28" s="39" t="s">
+      <c r="F28" s="39" t="s">
         <v>218</v>
-      </c>
-      <c r="E28" s="39" t="s">
-        <v>219</v>
-      </c>
-      <c r="F28" s="39" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
@@ -3966,19 +3990,19 @@
         <v>28</v>
       </c>
       <c r="B29" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="C29" s="36" t="s">
+        <v>220</v>
+      </c>
+      <c r="D29" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="E29" s="36" t="s">
         <v>221</v>
       </c>
-      <c r="C29" s="36" t="s">
+      <c r="F29" s="36" t="s">
         <v>222</v>
-      </c>
-      <c r="D29" s="36" t="s">
-        <v>218</v>
-      </c>
-      <c r="E29" s="36" t="s">
-        <v>223</v>
-      </c>
-      <c r="F29" s="36" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
@@ -3986,19 +4010,19 @@
         <v>29</v>
       </c>
       <c r="B30" s="36" t="s">
+        <v>223</v>
+      </c>
+      <c r="C30" s="36" t="s">
+        <v>223</v>
+      </c>
+      <c r="D30" s="36" t="s">
+        <v>224</v>
+      </c>
+      <c r="E30" s="36" t="s">
         <v>225</v>
       </c>
-      <c r="C30" s="36" t="s">
-        <v>225</v>
-      </c>
-      <c r="D30" s="36" t="s">
+      <c r="F30" s="36" t="s">
         <v>226</v>
-      </c>
-      <c r="E30" s="36" t="s">
-        <v>227</v>
-      </c>
-      <c r="F30" s="36" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
@@ -4006,19 +4030,19 @@
         <v>30</v>
       </c>
       <c r="B31" s="39" t="s">
+        <v>227</v>
+      </c>
+      <c r="C31" s="39" t="s">
+        <v>227</v>
+      </c>
+      <c r="D31" s="39" t="s">
+        <v>228</v>
+      </c>
+      <c r="E31" s="39" t="s">
         <v>229</v>
       </c>
-      <c r="C31" s="39" t="s">
-        <v>229</v>
-      </c>
-      <c r="D31" s="39" t="s">
+      <c r="F31" s="39" t="s">
         <v>230</v>
-      </c>
-      <c r="E31" s="39" t="s">
-        <v>231</v>
-      </c>
-      <c r="F31" s="39" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
@@ -4026,19 +4050,19 @@
         <v>31</v>
       </c>
       <c r="B32" s="36" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C32" s="36" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D32" s="39" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E32" s="39" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F32" s="39" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
@@ -4046,19 +4070,19 @@
         <v>32</v>
       </c>
       <c r="B33" s="36" t="s">
+        <v>233</v>
+      </c>
+      <c r="C33" s="36" t="s">
+        <v>233</v>
+      </c>
+      <c r="D33" s="39" t="s">
+        <v>228</v>
+      </c>
+      <c r="E33" s="36" t="s">
+        <v>234</v>
+      </c>
+      <c r="F33" s="39" t="s">
         <v>235</v>
-      </c>
-      <c r="C33" s="36" t="s">
-        <v>235</v>
-      </c>
-      <c r="D33" s="39" t="s">
-        <v>230</v>
-      </c>
-      <c r="E33" s="36" t="s">
-        <v>236</v>
-      </c>
-      <c r="F33" s="39" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
@@ -4066,19 +4090,19 @@
         <v>33</v>
       </c>
       <c r="B34" s="39" t="s">
+        <v>236</v>
+      </c>
+      <c r="C34" s="39" t="s">
+        <v>236</v>
+      </c>
+      <c r="D34" s="39" t="s">
+        <v>228</v>
+      </c>
+      <c r="E34" s="39" t="s">
+        <v>237</v>
+      </c>
+      <c r="F34" s="39" t="s">
         <v>238</v>
-      </c>
-      <c r="C34" s="39" t="s">
-        <v>238</v>
-      </c>
-      <c r="D34" s="39" t="s">
-        <v>230</v>
-      </c>
-      <c r="E34" s="39" t="s">
-        <v>239</v>
-      </c>
-      <c r="F34" s="39" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
@@ -4086,19 +4110,19 @@
         <v>34</v>
       </c>
       <c r="B35" s="39" t="s">
+        <v>239</v>
+      </c>
+      <c r="C35" s="39" t="s">
+        <v>239</v>
+      </c>
+      <c r="D35" s="39" t="s">
+        <v>228</v>
+      </c>
+      <c r="E35" s="39" t="s">
+        <v>240</v>
+      </c>
+      <c r="F35" s="39" t="s">
         <v>241</v>
-      </c>
-      <c r="C35" s="39" t="s">
-        <v>241</v>
-      </c>
-      <c r="D35" s="39" t="s">
-        <v>230</v>
-      </c>
-      <c r="E35" s="39" t="s">
-        <v>242</v>
-      </c>
-      <c r="F35" s="39" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
@@ -4106,19 +4130,19 @@
         <v>35</v>
       </c>
       <c r="B36" s="36" t="s">
+        <v>242</v>
+      </c>
+      <c r="C36" s="36" t="s">
+        <v>242</v>
+      </c>
+      <c r="D36" s="36" t="s">
+        <v>243</v>
+      </c>
+      <c r="E36" s="36" t="s">
         <v>244</v>
       </c>
-      <c r="C36" s="36" t="s">
-        <v>244</v>
-      </c>
-      <c r="D36" s="36" t="s">
-        <v>245</v>
-      </c>
-      <c r="E36" s="36" t="s">
-        <v>246</v>
-      </c>
       <c r="F36" s="36" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
@@ -4126,19 +4150,19 @@
         <v>36</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C37" s="36" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D37" s="36" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E37" s="36" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F37" s="36" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
@@ -4146,19 +4170,19 @@
         <v>37</v>
       </c>
       <c r="B38" s="39" t="s">
+        <v>247</v>
+      </c>
+      <c r="C38" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="D38" s="39" t="s">
         <v>249</v>
       </c>
-      <c r="C38" s="39" t="s">
+      <c r="E38" s="39" t="s">
         <v>250</v>
       </c>
-      <c r="D38" s="39" t="s">
+      <c r="F38" s="39" t="s">
         <v>251</v>
-      </c>
-      <c r="E38" s="39" t="s">
-        <v>252</v>
-      </c>
-      <c r="F38" s="39" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
@@ -4166,19 +4190,19 @@
         <v>38</v>
       </c>
       <c r="B39" s="39" t="s">
+        <v>252</v>
+      </c>
+      <c r="C39" s="39" t="s">
+        <v>253</v>
+      </c>
+      <c r="D39" s="39" t="s">
+        <v>249</v>
+      </c>
+      <c r="E39" s="39" t="s">
         <v>254</v>
       </c>
-      <c r="C39" s="39" t="s">
+      <c r="F39" s="39" t="s">
         <v>255</v>
-      </c>
-      <c r="D39" s="39" t="s">
-        <v>251</v>
-      </c>
-      <c r="E39" s="39" t="s">
-        <v>256</v>
-      </c>
-      <c r="F39" s="39" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
@@ -4186,19 +4210,19 @@
         <v>39</v>
       </c>
       <c r="B40" s="36" t="s">
+        <v>256</v>
+      </c>
+      <c r="C40" s="36" t="s">
+        <v>257</v>
+      </c>
+      <c r="D40" s="39" t="s">
+        <v>249</v>
+      </c>
+      <c r="E40" s="36" t="s">
         <v>258</v>
       </c>
-      <c r="C40" s="36" t="s">
+      <c r="F40" s="36" t="s">
         <v>259</v>
-      </c>
-      <c r="D40" s="39" t="s">
-        <v>251</v>
-      </c>
-      <c r="E40" s="36" t="s">
-        <v>260</v>
-      </c>
-      <c r="F40" s="36" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
@@ -4206,19 +4230,19 @@
         <v>40</v>
       </c>
       <c r="B41" s="36" t="s">
+        <v>260</v>
+      </c>
+      <c r="C41" s="36" t="s">
+        <v>260</v>
+      </c>
+      <c r="D41" s="39" t="s">
+        <v>249</v>
+      </c>
+      <c r="E41" s="36" t="s">
+        <v>261</v>
+      </c>
+      <c r="F41" s="36" t="s">
         <v>262</v>
-      </c>
-      <c r="C41" s="36" t="s">
-        <v>262</v>
-      </c>
-      <c r="D41" s="39" t="s">
-        <v>251</v>
-      </c>
-      <c r="E41" s="36" t="s">
-        <v>263</v>
-      </c>
-      <c r="F41" s="36" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
@@ -4226,19 +4250,19 @@
         <v>41</v>
       </c>
       <c r="B42" s="36" t="s">
+        <v>263</v>
+      </c>
+      <c r="C42" s="36" t="s">
+        <v>264</v>
+      </c>
+      <c r="D42" s="36" t="s">
         <v>265</v>
       </c>
-      <c r="C42" s="36" t="s">
+      <c r="E42" s="36" t="s">
         <v>266</v>
       </c>
-      <c r="D42" s="36" t="s">
+      <c r="F42" s="36" t="s">
         <v>267</v>
-      </c>
-      <c r="E42" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="F42" s="36" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
@@ -4246,19 +4270,19 @@
         <v>42</v>
       </c>
       <c r="B43" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="C43" s="36" t="s">
+        <v>269</v>
+      </c>
+      <c r="D43" s="36" t="s">
+        <v>224</v>
+      </c>
+      <c r="E43" s="36" t="s">
         <v>270</v>
       </c>
-      <c r="C43" s="36" t="s">
+      <c r="F43" s="36" t="s">
         <v>271</v>
-      </c>
-      <c r="D43" s="36" t="s">
-        <v>226</v>
-      </c>
-      <c r="E43" s="36" t="s">
-        <v>272</v>
-      </c>
-      <c r="F43" s="36" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
@@ -4266,19 +4290,19 @@
         <v>43</v>
       </c>
       <c r="B44" s="39" t="s">
+        <v>272</v>
+      </c>
+      <c r="C44" s="39" t="s">
+        <v>272</v>
+      </c>
+      <c r="D44" s="36" t="s">
+        <v>224</v>
+      </c>
+      <c r="E44" s="39" t="s">
+        <v>273</v>
+      </c>
+      <c r="F44" s="39" t="s">
         <v>274</v>
-      </c>
-      <c r="C44" s="39" t="s">
-        <v>274</v>
-      </c>
-      <c r="D44" s="36" t="s">
-        <v>226</v>
-      </c>
-      <c r="E44" s="39" t="s">
-        <v>275</v>
-      </c>
-      <c r="F44" s="39" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
@@ -4286,19 +4310,19 @@
         <v>44</v>
       </c>
       <c r="B45" s="39" t="s">
+        <v>275</v>
+      </c>
+      <c r="C45" s="39" t="s">
+        <v>276</v>
+      </c>
+      <c r="D45" s="39" t="s">
         <v>277</v>
       </c>
-      <c r="C45" s="39" t="s">
+      <c r="E45" s="39" t="s">
         <v>278</v>
       </c>
-      <c r="D45" s="39" t="s">
+      <c r="F45" s="39" t="s">
         <v>279</v>
-      </c>
-      <c r="E45" s="39" t="s">
-        <v>280</v>
-      </c>
-      <c r="F45" s="39" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
@@ -4306,19 +4330,19 @@
         <v>45</v>
       </c>
       <c r="B46" s="36" t="s">
+        <v>280</v>
+      </c>
+      <c r="C46" s="36" t="s">
+        <v>281</v>
+      </c>
+      <c r="D46" s="36" t="s">
         <v>282</v>
       </c>
-      <c r="C46" s="36" t="s">
+      <c r="E46" s="36" t="s">
         <v>283</v>
       </c>
-      <c r="D46" s="36" t="s">
+      <c r="F46" s="36" t="s">
         <v>284</v>
-      </c>
-      <c r="E46" s="36" t="s">
-        <v>285</v>
-      </c>
-      <c r="F46" s="36" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
@@ -4326,19 +4350,19 @@
         <v>46</v>
       </c>
       <c r="B47" s="36" t="s">
+        <v>285</v>
+      </c>
+      <c r="C47" s="36" t="s">
+        <v>286</v>
+      </c>
+      <c r="D47" s="39" t="s">
+        <v>249</v>
+      </c>
+      <c r="E47" s="36" t="s">
         <v>287</v>
       </c>
-      <c r="C47" s="36" t="s">
+      <c r="F47" s="36" t="s">
         <v>288</v>
-      </c>
-      <c r="D47" s="39" t="s">
-        <v>251</v>
-      </c>
-      <c r="E47" s="36" t="s">
-        <v>289</v>
-      </c>
-      <c r="F47" s="36" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
@@ -4346,19 +4370,19 @@
         <v>47</v>
       </c>
       <c r="B48" s="36" t="s">
+        <v>289</v>
+      </c>
+      <c r="C48" s="36" t="s">
+        <v>290</v>
+      </c>
+      <c r="D48" s="36" t="s">
         <v>291</v>
       </c>
-      <c r="C48" s="36" t="s">
+      <c r="E48" s="36" t="s">
         <v>292</v>
       </c>
-      <c r="D48" s="36" t="s">
+      <c r="F48" s="36" t="s">
         <v>293</v>
-      </c>
-      <c r="E48" s="36" t="s">
-        <v>294</v>
-      </c>
-      <c r="F48" s="36" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
@@ -4366,19 +4390,19 @@
         <v>48</v>
       </c>
       <c r="B49" s="36" t="s">
+        <v>294</v>
+      </c>
+      <c r="C49" s="36" t="s">
+        <v>295</v>
+      </c>
+      <c r="D49" s="36" t="s">
         <v>296</v>
       </c>
-      <c r="C49" s="36" t="s">
+      <c r="E49" s="36" t="s">
         <v>297</v>
       </c>
-      <c r="D49" s="36" t="s">
+      <c r="F49" s="36" t="s">
         <v>298</v>
-      </c>
-      <c r="E49" s="36" t="s">
-        <v>299</v>
-      </c>
-      <c r="F49" s="36" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
@@ -4386,19 +4410,39 @@
         <v>49</v>
       </c>
       <c r="B50" s="68" t="s">
+        <v>360</v>
+      </c>
+      <c r="C50" s="68" t="s">
+        <v>361</v>
+      </c>
+      <c r="D50" s="39" t="s">
+        <v>207</v>
+      </c>
+      <c r="E50" s="68" t="s">
         <v>362</v>
       </c>
-      <c r="C50" s="68" t="s">
+      <c r="F50" s="68" t="s">
         <v>363</v>
       </c>
-      <c r="D50" s="39" t="s">
-        <v>209</v>
-      </c>
-      <c r="E50" s="68" t="s">
-        <v>364</v>
-      </c>
-      <c r="F50" s="68" t="s">
-        <v>365</v>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A51" s="88">
+        <v>50</v>
+      </c>
+      <c r="B51" s="68" t="s">
+        <v>368</v>
+      </c>
+      <c r="C51" s="68" t="s">
+        <v>369</v>
+      </c>
+      <c r="D51" s="68" t="s">
+        <v>370</v>
+      </c>
+      <c r="E51" s="68" t="s">
+        <v>371</v>
+      </c>
+      <c r="F51" s="68" t="s">
+        <v>372</v>
       </c>
     </row>
   </sheetData>
@@ -4411,7 +4455,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF1BA8E2-9FD2-4C47-B5D3-EF9907B8F692}">
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.54296875" style="41" customWidth="1"/>
@@ -4422,16 +4466,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="32" t="s">
+        <v>299</v>
+      </c>
+      <c r="B1" s="68" t="s">
+        <v>360</v>
+      </c>
+      <c r="C1" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="D1" s="33" t="s">
         <v>301</v>
-      </c>
-      <c r="B1" s="68" t="s">
-        <v>362</v>
-      </c>
-      <c r="C1" s="34" t="s">
-        <v>302</v>
-      </c>
-      <c r="D1" s="33" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
@@ -4439,7 +4483,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="36" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C2" s="42">
         <v>1194</v>
@@ -4451,7 +4495,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C3" s="43">
         <v>1938</v>
@@ -4465,7 +4509,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="36" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C4" s="42">
         <v>1591</v>
@@ -4477,7 +4521,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C5" s="42">
         <v>1973</v>
@@ -4489,7 +4533,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C6" s="42">
         <v>989</v>
@@ -4503,7 +4547,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C7" s="42">
         <v>1010</v>
@@ -4515,7 +4559,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C8" s="42">
         <v>1994</v>
@@ -4527,7 +4571,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C9" s="43">
         <v>1972</v>
@@ -4539,7 +4583,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C10" s="43">
         <v>1988</v>
@@ -4553,7 +4597,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C11" s="43">
         <v>1280</v>
@@ -4565,7 +4609,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C12" s="43">
         <v>1872</v>
@@ -4579,7 +4623,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C13" s="43">
         <v>1872</v>
@@ -4593,7 +4637,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C14" s="43">
         <v>1871</v>
@@ -4605,7 +4649,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="39" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C15" s="43">
         <v>1872</v>
@@ -4619,7 +4663,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C16" s="43">
         <v>1888</v>
@@ -4633,7 +4677,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="39" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C17" s="43">
         <v>1374</v>
@@ -4645,7 +4689,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="39" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C18" s="43">
         <v>1827</v>
@@ -4657,7 +4701,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="39" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C19" s="43">
         <v>1872</v>
@@ -4671,7 +4715,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="36" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C20" s="43">
         <v>801</v>
@@ -4683,7 +4727,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="39" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C21" s="43">
         <v>1990</v>
@@ -4695,7 +4739,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C22" s="43">
         <v>1328</v>
@@ -4707,7 +4751,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="36" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C23" s="43">
         <v>1976</v>
@@ -4719,7 +4763,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="36" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C24" s="43">
         <v>1928</v>
@@ -4731,7 +4775,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="36" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C25" s="43">
         <v>1972</v>
@@ -4743,7 +4787,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="39" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C26" s="43">
         <v>1942</v>
@@ -4755,7 +4799,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="36" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C27" s="43">
         <v>1724</v>
@@ -4767,7 +4811,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C28" s="43">
         <v>1992</v>
@@ -4781,7 +4825,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="36" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C29" s="43">
         <v>1998</v>
@@ -4793,7 +4837,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C30" s="43">
         <v>1968</v>
@@ -4805,7 +4849,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="39" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C31" s="43">
         <v>1792</v>
@@ -4817,7 +4861,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="36" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C32" s="43">
         <v>1906</v>
@@ -4829,7 +4873,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="36" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C33" s="43">
         <v>1854</v>
@@ -4841,7 +4885,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="39" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C34" s="43">
         <v>1835</v>
@@ -4855,7 +4899,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="39" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C35" s="43">
         <v>1973</v>
@@ -4867,7 +4911,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="36" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C36" s="43">
         <v>1908</v>
@@ -4879,7 +4923,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="36" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C37" s="43">
         <v>1976</v>
@@ -4891,7 +4935,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="39" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C38" s="43">
         <v>1803</v>
@@ -4903,7 +4947,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="39" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C39" s="43">
         <v>1829</v>
@@ -4915,7 +4959,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="36" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C40" s="43">
         <v>1757</v>
@@ -4927,7 +4971,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C41" s="43">
         <v>1640</v>
@@ -4941,7 +4985,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C42" s="43">
         <v>1992</v>
@@ -4953,7 +4997,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="36" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C43" s="43">
         <v>1850</v>
@@ -4967,7 +5011,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="39" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C44" s="43">
         <v>1860</v>
@@ -4981,7 +5025,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="39" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C45" s="43">
         <v>1890</v>
@@ -4995,7 +5039,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="39" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C46" s="43">
         <v>1923</v>
@@ -5007,7 +5051,7 @@
         <v>45</v>
       </c>
       <c r="B47" s="36" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C47" s="43">
         <v>1943</v>
@@ -5019,7 +5063,7 @@
         <v>46</v>
       </c>
       <c r="B48" s="36" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C48" s="43">
         <v>1988</v>
@@ -5031,7 +5075,7 @@
         <v>47</v>
       </c>
       <c r="B49" s="36" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C49" s="43">
         <v>1951</v>
@@ -5043,7 +5087,7 @@
         <v>48</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C50" s="43">
         <v>1535</v>
@@ -5055,7 +5099,7 @@
         <v>49</v>
       </c>
       <c r="B51" s="68" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C51" s="69">
         <v>1725</v>
@@ -5064,10 +5108,23 @@
         <v>1876</v>
       </c>
     </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" s="38">
+        <v>50</v>
+      </c>
+      <c r="B52" s="68" t="s">
+        <v>368</v>
+      </c>
+      <c r="C52" s="69">
+        <v>1952</v>
+      </c>
+      <c r="D52" s="69"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -5188,7 +5245,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8265AFD9-D9EB-4B75-B60D-6B7F7204230D}">
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.36328125" customWidth="1"/>
@@ -5364,6 +5421,12 @@
         <v>61</v>
       </c>
       <c r="B28" s="4"/>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="B29" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5383,13 +5446,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B1" s="45" t="s">
+        <v>304</v>
+      </c>
+      <c r="C1" t="s">
         <v>305</v>
-      </c>
-      <c r="B1" s="45" t="s">
-        <v>306</v>
-      </c>
-      <c r="C1" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
@@ -5397,10 +5460,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="46" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C2" s="47" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -5408,10 +5471,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="46" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C3" s="47" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -5419,10 +5482,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="46" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C4" s="47" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -5430,10 +5493,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="46" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C5" s="47" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -5441,10 +5504,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="46" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C6" s="47" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
@@ -5452,10 +5515,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="46" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C7" s="47" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="29" x14ac:dyDescent="0.35">
@@ -5463,10 +5526,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="46" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C8" s="47" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
@@ -5474,10 +5537,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="46" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C9" s="47" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="29" x14ac:dyDescent="0.35">
@@ -5485,10 +5548,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="46" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C10" s="47" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
@@ -5496,10 +5559,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="46" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C11" s="47" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
@@ -5507,10 +5570,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="46" t="s">
+        <v>324</v>
+      </c>
+      <c r="C12" s="47" t="s">
         <v>326</v>
-      </c>
-      <c r="C12" s="47" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
@@ -5518,10 +5581,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="46" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C13" s="47" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
@@ -5529,10 +5592,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="48" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C14" s="49" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
@@ -5540,10 +5603,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="48" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C15" s="49" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
@@ -5551,10 +5614,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="48" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C16" s="49" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
   </sheetData>
@@ -5596,13 +5659,13 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="51" t="s">
+        <v>303</v>
+      </c>
+      <c r="B1" s="53" t="s">
+        <v>304</v>
+      </c>
+      <c r="C1" s="52" t="s">
         <v>305</v>
-      </c>
-      <c r="B1" s="53" t="s">
-        <v>306</v>
-      </c>
-      <c r="C1" s="52" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.35">
@@ -5610,10 +5673,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="55" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C2" s="56" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -5621,10 +5684,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="55" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C3" s="57" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -5632,10 +5695,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="59" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C4" s="49" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -5643,10 +5706,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="59" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C5" s="49" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -5654,10 +5717,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C6" s="49" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
@@ -5665,10 +5728,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="59" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C7" s="49" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
@@ -5676,10 +5739,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C8" s="49" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
@@ -5687,10 +5750,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="59" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C9" s="49" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
@@ -5698,10 +5761,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="59" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C10" s="49" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="29" x14ac:dyDescent="0.35">
@@ -5709,10 +5772,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="59" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
@@ -5720,10 +5783,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="60" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C12" s="61" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
@@ -5731,10 +5794,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="60" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C13" s="49" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
@@ -5742,10 +5805,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="60" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C14" s="49" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">

--- a/Info/Additional_information.xlsx
+++ b/Info/Additional_information.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{053A286D-8064-46E8-A879-D96F00A4EBE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB1AE7AD-E559-4AF8-8FA7-E78742B96477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Colours_specifications" sheetId="1" r:id="rId1"/>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="375">
   <si>
     <t>good quality (UNC for UNC collection; UNC and XF for XF collection)</t>
   </si>
@@ -1193,13 +1193,19 @@
   </si>
   <si>
     <t>BNB</t>
+  </si>
+  <si>
+    <t>Orange</t>
+  </si>
+  <si>
+    <t>Annual Sets</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1312,6 +1318,13 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="5" tint="0.39997558519241921"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
     </font>
@@ -1744,7 +1757,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1939,6 +1952,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="20" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1987,9 +2006,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -2869,7 +2885,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.08984375" customWidth="1"/>
@@ -2975,8 +2991,22 @@
         <v>15</v>
       </c>
     </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="4">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="C8" s="71">
+        <v>1</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>374</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="C7">
+  <conditionalFormatting sqref="C7:C8">
     <cfRule type="containsText" dxfId="33" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C7))))</formula>
     </cfRule>
@@ -3064,7 +3094,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C7">
+  <conditionalFormatting sqref="C7:C8">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3115,10 +3145,10 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" s="76">
+      <c r="A2" s="78">
         <v>1</v>
       </c>
-      <c r="B2" s="84">
+      <c r="B2" s="86">
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
@@ -3135,8 +3165,8 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" s="77"/>
-      <c r="B3" s="84"/>
+      <c r="A3" s="79"/>
+      <c r="B3" s="86"/>
       <c r="C3" s="4" t="s">
         <v>65</v>
       </c>
@@ -3151,8 +3181,8 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" s="78"/>
-      <c r="B4" s="85">
+      <c r="A4" s="80"/>
+      <c r="B4" s="87">
         <v>2</v>
       </c>
       <c r="C4" s="4" t="s">
@@ -3169,14 +3199,14 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" s="78"/>
-      <c r="B5" s="85"/>
+      <c r="A5" s="80"/>
+      <c r="B5" s="87"/>
       <c r="C5" s="4" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6" s="78"/>
+      <c r="A6" s="80"/>
       <c r="B6" s="15">
         <v>3</v>
       </c>
@@ -3185,7 +3215,7 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" s="78"/>
+      <c r="A7" s="80"/>
       <c r="B7" s="16" t="s">
         <v>90</v>
       </c>
@@ -3194,8 +3224,8 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" s="78"/>
-      <c r="B8" s="86">
+      <c r="A8" s="80"/>
+      <c r="B8" s="88">
         <v>6</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -3203,14 +3233,14 @@
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="78"/>
-      <c r="B9" s="87"/>
+      <c r="A9" s="80"/>
+      <c r="B9" s="89"/>
       <c r="C9" s="4" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A10" s="78"/>
+      <c r="A10" s="80"/>
       <c r="B10" s="17">
         <v>7</v>
       </c>
@@ -3219,14 +3249,14 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="78"/>
+      <c r="A11" s="80"/>
       <c r="B11" s="24"/>
       <c r="C11" s="4" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="78"/>
+      <c r="A12" s="80"/>
       <c r="B12" s="18">
         <v>8</v>
       </c>
@@ -3235,7 +3265,7 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" s="79"/>
+      <c r="A13" s="81"/>
       <c r="B13" s="25" t="s">
         <v>78</v>
       </c>
@@ -3244,7 +3274,7 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="80"/>
+      <c r="A14" s="82"/>
       <c r="B14" s="26" t="s">
         <v>91</v>
       </c>
@@ -3253,7 +3283,7 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="14.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="81">
+      <c r="A15" s="83">
         <v>2</v>
       </c>
       <c r="B15" s="19" t="s">
@@ -3264,7 +3294,7 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="82"/>
+      <c r="A16" s="84"/>
       <c r="B16" s="20" t="s">
         <v>365</v>
       </c>
@@ -3273,7 +3303,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="82"/>
+      <c r="A17" s="84"/>
       <c r="B17" s="21" t="s">
         <v>366</v>
       </c>
@@ -3282,7 +3312,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="83"/>
+      <c r="A18" s="85"/>
       <c r="B18" s="22" t="s">
         <v>92</v>
       </c>
@@ -3291,7 +3321,7 @@
       </c>
     </row>
     <row r="19" spans="1:3" ht="14.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="70">
+      <c r="A19" s="72">
         <v>3</v>
       </c>
       <c r="B19" s="23" t="s">
@@ -3302,7 +3332,7 @@
       </c>
     </row>
     <row r="20" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="71"/>
+      <c r="A20" s="73"/>
       <c r="B20" s="27" t="s">
         <v>93</v>
       </c>
@@ -3311,7 +3341,7 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="72"/>
+      <c r="A21" s="74"/>
       <c r="B21" s="28" t="s">
         <v>95</v>
       </c>
@@ -3320,7 +3350,7 @@
       </c>
     </row>
     <row r="22" spans="1:3" ht="14.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="73">
+      <c r="A22" s="75">
         <v>4</v>
       </c>
       <c r="B22" s="19" t="s">
@@ -3331,7 +3361,7 @@
       </c>
     </row>
     <row r="23" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="74"/>
+      <c r="A23" s="76"/>
       <c r="B23" s="20" t="s">
         <v>98</v>
       </c>
@@ -3340,7 +3370,7 @@
       </c>
     </row>
     <row r="24" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="74"/>
+      <c r="A24" s="76"/>
       <c r="B24" s="21" t="s">
         <v>100</v>
       </c>
@@ -3349,7 +3379,7 @@
       </c>
     </row>
     <row r="25" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="74"/>
+      <c r="A25" s="76"/>
       <c r="B25" s="16" t="s">
         <v>102</v>
       </c>
@@ -3358,7 +3388,7 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" s="74"/>
+      <c r="A26" s="76"/>
       <c r="B26" s="29" t="s">
         <v>104</v>
       </c>
@@ -3367,7 +3397,7 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" s="74"/>
+      <c r="A27" s="76"/>
       <c r="B27" s="30" t="s">
         <v>106</v>
       </c>
@@ -3376,7 +3406,7 @@
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" s="74"/>
+      <c r="A28" s="76"/>
       <c r="B28" s="18">
         <v>8</v>
       </c>
@@ -3385,7 +3415,7 @@
       </c>
     </row>
     <row r="29" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="75"/>
+      <c r="A29" s="77"/>
       <c r="B29" s="31" t="s">
         <v>78</v>
       </c>
@@ -4426,7 +4456,7 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A51" s="88">
+      <c r="A51" s="70">
         <v>50</v>
       </c>
       <c r="B51" s="68" t="s">

--- a/Info/Additional_information.xlsx
+++ b/Info/Additional_information.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB1AE7AD-E559-4AF8-8FA7-E78742B96477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC2FEB27-7281-49CC-9204-B32339E6B645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Colours_specifications" sheetId="1" r:id="rId1"/>
     <sheet name="EURO albums content" sheetId="4" r:id="rId2"/>
-    <sheet name="Mint_Alias" sheetId="5" r:id="rId3"/>
-    <sheet name="Mint_work_years" sheetId="6" r:id="rId4"/>
-    <sheet name="File_Naming" sheetId="2" r:id="rId5"/>
-    <sheet name="Existing_subtypes" sheetId="3" r:id="rId6"/>
-    <sheet name="Links_to_Data" sheetId="7" r:id="rId7"/>
-    <sheet name="Coin_Shops" sheetId="8" r:id="rId8"/>
+    <sheet name="albums ID naming" sheetId="9" r:id="rId3"/>
+    <sheet name="Mint_Alias" sheetId="5" r:id="rId4"/>
+    <sheet name="Mint_work_years" sheetId="6" r:id="rId5"/>
+    <sheet name="File_Naming" sheetId="2" r:id="rId6"/>
+    <sheet name="Existing_subtypes" sheetId="3" r:id="rId7"/>
+    <sheet name="Links_to_Data" sheetId="7" r:id="rId8"/>
+    <sheet name="Coin_Shops" sheetId="8" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Colours_specifications!$A$1:$D$1</definedName>
@@ -73,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="403">
   <si>
     <t>good quality (UNC for UNC collection; UNC and XF for XF collection)</t>
   </si>
@@ -1199,6 +1200,90 @@
   </si>
   <si>
     <t>Annual Sets</t>
+  </si>
+  <si>
+    <t>BK</t>
+  </si>
+  <si>
+    <t>WH</t>
+  </si>
+  <si>
+    <t>RD</t>
+  </si>
+  <si>
+    <t>YL</t>
+  </si>
+  <si>
+    <t>BN</t>
+  </si>
+  <si>
+    <t>GY</t>
+  </si>
+  <si>
+    <t>BL</t>
+  </si>
+  <si>
+    <t>LB</t>
+  </si>
+  <si>
+    <t>DB</t>
+  </si>
+  <si>
+    <t>GD</t>
+  </si>
+  <si>
+    <t>SL</t>
+  </si>
+  <si>
+    <t>VT</t>
+  </si>
+  <si>
+    <t>OR</t>
+  </si>
+  <si>
+    <t>Black</t>
+  </si>
+  <si>
+    <t>White</t>
+  </si>
+  <si>
+    <t>Brown</t>
+  </si>
+  <si>
+    <t>Grey</t>
+  </si>
+  <si>
+    <t>Light Blue</t>
+  </si>
+  <si>
+    <t>Dark Blue</t>
+  </si>
+  <si>
+    <t>Gold</t>
+  </si>
+  <si>
+    <t>Silver</t>
+  </si>
+  <si>
+    <t>Violet</t>
+  </si>
+  <si>
+    <t>Optima</t>
+  </si>
+  <si>
+    <t>Grand</t>
+  </si>
+  <si>
+    <t>List format</t>
+  </si>
+  <si>
+    <t>Full List format</t>
+  </si>
+  <si>
+    <t>Album Clolour</t>
+  </si>
+  <si>
+    <t>Full Album name</t>
   </si>
 </sst>
 </file>
@@ -1457,7 +1542,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -1752,12 +1837,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2006,12 +2100,72 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="34">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2496,54 +2650,6 @@
         </horizontal>
       </border>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -2562,29 +2668,78 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>336550</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>298450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>232866</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>83201</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Рисунок 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A868196E-1DF9-449B-9D2C-1C8DABFA701C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4654550" y="298450"/>
+          <a:ext cx="7821116" cy="4667901"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{973D7237-72C7-453E-A0E1-526C93326B28}" name="Таблица3" displayName="Таблица3" ref="A1:F51" totalsRowShown="0" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{973D7237-72C7-453E-A0E1-526C93326B28}" name="Таблица3" displayName="Таблица3" ref="A1:F51" totalsRowShown="0" headerRowDxfId="33" dataDxfId="31" headerRowBorderDxfId="32" tableBorderDxfId="30" totalsRowBorderDxfId="29">
   <autoFilter ref="A1:F51" xr:uid="{A2D8FA3D-4024-4365-BE1D-F93D0AF2D426}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{12C2DF0B-47FA-46A4-8424-55A1488EF88B}" name="ID" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{EB0B36CE-168D-429E-896D-DBA54794224F}" name="Name_Eng" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{6C3A2CE8-252E-4C52-985B-8CDDFD9FA0C7}" name="OfficialMintName_Native" dataDxfId="20"/>
-    <tableColumn id="8" xr3:uid="{DA5871DC-2EDB-49C0-953E-EC0F70288E21}" name="Country" dataDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{FCD85F85-A94E-4BBE-9D3B-2B7494638375}" name="Mint_City" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{E5141978-CA91-4DE9-86F1-8A8AFA716534}" name="Alias" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{12C2DF0B-47FA-46A4-8424-55A1488EF88B}" name="ID" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{EB0B36CE-168D-429E-896D-DBA54794224F}" name="Name_Eng" dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{6C3A2CE8-252E-4C52-985B-8CDDFD9FA0C7}" name="OfficialMintName_Native" dataDxfId="26"/>
+    <tableColumn id="8" xr3:uid="{DA5871DC-2EDB-49C0-953E-EC0F70288E21}" name="Country" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{FCD85F85-A94E-4BBE-9D3B-2B7494638375}" name="Mint_City" dataDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{E5141978-CA91-4DE9-86F1-8A8AFA716534}" name="Alias" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9D0F8E3D-96B1-4DB8-B1A6-8DD6B84F3693}" name="Таблица35" displayName="Таблица35" ref="A1:D52" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13" totalsRowBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9D0F8E3D-96B1-4DB8-B1A6-8DD6B84F3693}" name="Таблица35" displayName="Таблица35" ref="A1:D52" totalsRowShown="0" headerRowDxfId="22" dataDxfId="20" headerRowBorderDxfId="21" tableBorderDxfId="19" totalsRowBorderDxfId="18">
   <autoFilter ref="A1:D52" xr:uid="{A2D8FA3D-4024-4365-BE1D-F93D0AF2D426}"/>
   <tableColumns count="4">
-    <tableColumn id="4" xr3:uid="{74AFB32D-7AAA-46BE-8174-ED698BB4613E}" name="Mint_id" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{523D65CD-0F56-441F-90B5-E46A9B14F0D0}" name="Ekaterinburg Mint" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{1AAB7352-E935-4EC6-A0D1-3EDC5D0BC93C}" name="Year_of_start" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{5FF15381-476A-4F88-B93A-6452F2830A0A}" name="Year_of_end" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{74AFB32D-7AAA-46BE-8174-ED698BB4613E}" name="Mint_id" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{523D65CD-0F56-441F-90B5-E46A9B14F0D0}" name="Ekaterinburg Mint" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{1AAB7352-E935-4EC6-A0D1-3EDC5D0BC93C}" name="Year_of_start" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{5FF15381-476A-4F88-B93A-6452F2830A0A}" name="Year_of_end" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2598,25 +2753,25 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{8354E581-3B48-4762-81A7-EA76E36C4BB5}" name="№" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{1F45DC85-8ECA-45FE-BF45-E528619CEE0E}" name="Links:" dataDxfId="6" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{3FAE616B-3296-4770-9E56-8A824991EECA}" name="Description:" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{8354E581-3B48-4762-81A7-EA76E36C4BB5}" name="№" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{1F45DC85-8ECA-45FE-BF45-E528619CEE0E}" name="Links:" dataDxfId="12" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{3FAE616B-3296-4770-9E56-8A824991EECA}" name="Description:" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D0DCC88A-2D36-4004-A694-FC0C0F0C3396}" name="Таблица2" displayName="Таблица2" ref="A1:C16" totalsRowShown="0" headerRowBorderDxfId="4" tableBorderDxfId="3" totalsRowBorderDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D0DCC88A-2D36-4004-A694-FC0C0F0C3396}" name="Таблица2" displayName="Таблица2" ref="A1:C16" totalsRowShown="0" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
   <autoFilter ref="A1:C16" xr:uid="{00000000-0009-0000-0100-000002000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{28358E6A-6F3A-468C-9E1C-880A34D9BECE}" name="№" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{28358E6A-6F3A-468C-9E1C-880A34D9BECE}" name="№" dataDxfId="7"/>
     <tableColumn id="2" xr3:uid="{DD0AD5C8-324B-4DA7-B39F-B2DB3EF91222}" name="Links:"/>
-    <tableColumn id="3" xr3:uid="{FC8A6018-CA7E-4C73-9B21-B272B55FA8C1}" name="Description:" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{FC8A6018-CA7E-4C73-9B21-B272B55FA8C1}" name="Description:" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -3007,12 +3162,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C7:C8">
-    <cfRule type="containsText" dxfId="33" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C7))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6">
-    <cfRule type="containsText" dxfId="32" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="4" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C6))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3029,7 +3184,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2">
-    <cfRule type="containsText" dxfId="31" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="3" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C2))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3046,7 +3201,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4">
-    <cfRule type="containsText" dxfId="30" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="2" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C4))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3063,7 +3218,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C5">
-    <cfRule type="containsText" dxfId="29" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="1" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C5))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3080,7 +3235,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3">
-    <cfRule type="containsText" dxfId="28" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C3))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -3444,6 +3599,162 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{866E9A5E-386D-439E-AA25-CB46A31C625C}">
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="15.453125" style="95" customWidth="1"/>
+    <col min="2" max="2" width="15.453125" customWidth="1"/>
+    <col min="3" max="3" width="15.453125" style="95" customWidth="1"/>
+    <col min="4" max="4" width="15.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="36.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="94" t="s">
+        <v>399</v>
+      </c>
+      <c r="B1" s="94" t="s">
+        <v>400</v>
+      </c>
+      <c r="C1" s="92" t="s">
+        <v>401</v>
+      </c>
+      <c r="D1" s="90" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="95" t="s">
+        <v>238</v>
+      </c>
+      <c r="B2" s="93" t="s">
+        <v>397</v>
+      </c>
+      <c r="C2" s="91" t="s">
+        <v>375</v>
+      </c>
+      <c r="D2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="95" t="s">
+        <v>176</v>
+      </c>
+      <c r="B3" s="93" t="s">
+        <v>398</v>
+      </c>
+      <c r="C3" s="91" t="s">
+        <v>376</v>
+      </c>
+      <c r="D3" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C4" s="91" t="s">
+        <v>377</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C5" s="91" t="s">
+        <v>142</v>
+      </c>
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C6" s="91" t="s">
+        <v>378</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C7" s="91" t="s">
+        <v>379</v>
+      </c>
+      <c r="D7" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C8" s="91" t="s">
+        <v>380</v>
+      </c>
+      <c r="D8" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C9" s="91" t="s">
+        <v>381</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C10" s="91" t="s">
+        <v>382</v>
+      </c>
+      <c r="D10" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C11" s="91" t="s">
+        <v>383</v>
+      </c>
+      <c r="D11" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C12" s="91" t="s">
+        <v>384</v>
+      </c>
+      <c r="D12" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C13" s="91" t="s">
+        <v>385</v>
+      </c>
+      <c r="D13" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C14" s="91" t="s">
+        <v>386</v>
+      </c>
+      <c r="D14" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C15" s="91" t="s">
+        <v>387</v>
+      </c>
+      <c r="D15" t="s">
+        <v>373</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4C14141-45DA-4C30-845C-3E630B347F10}">
   <dimension ref="A1:F51"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -4483,7 +4794,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF1BA8E2-9FD2-4C47-B5D3-EF9907B8F692}">
   <dimension ref="A1:D52"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -5159,7 +5470,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0041FEF0-BF6F-4667-AFBD-1C23A1866795}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -5273,7 +5584,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8265AFD9-D9EB-4B75-B60D-6B7F7204230D}">
   <dimension ref="A1:B29"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -5463,7 +5774,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{729F7C06-1AE8-4162-8F40-6E9A64E311D7}">
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -5677,7 +5988,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8049D8E-7482-48AF-95C9-7F1B728B0DDE}">
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/Info/Additional_information.xlsx
+++ b/Info/Additional_information.xlsx
@@ -8,20 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC2FEB27-7281-49CC-9204-B32339E6B645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA4E6752-4C0F-4F21-9A2C-B49E2BCDB4F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Colours_specifications" sheetId="1" r:id="rId1"/>
     <sheet name="EURO albums content" sheetId="4" r:id="rId2"/>
-    <sheet name="albums ID naming" sheetId="9" r:id="rId3"/>
-    <sheet name="Mint_Alias" sheetId="5" r:id="rId4"/>
-    <sheet name="Mint_work_years" sheetId="6" r:id="rId5"/>
-    <sheet name="File_Naming" sheetId="2" r:id="rId6"/>
-    <sheet name="Existing_subtypes" sheetId="3" r:id="rId7"/>
-    <sheet name="Links_to_Data" sheetId="7" r:id="rId8"/>
-    <sheet name="Coin_Shops" sheetId="8" r:id="rId9"/>
+    <sheet name="albums ID" sheetId="11" r:id="rId3"/>
+    <sheet name="albums ID naming" sheetId="9" r:id="rId4"/>
+    <sheet name="Лист1" sheetId="10" r:id="rId5"/>
+    <sheet name="Mint_Alias" sheetId="5" r:id="rId6"/>
+    <sheet name="Mint_work_years" sheetId="6" r:id="rId7"/>
+    <sheet name="File_Naming" sheetId="2" r:id="rId8"/>
+    <sheet name="Existing_subtypes" sheetId="3" r:id="rId9"/>
+    <sheet name="Links_to_Data" sheetId="7" r:id="rId10"/>
+    <sheet name="Coin_Shops" sheetId="8" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Colours_specifications!$A$1:$D$1</definedName>
@@ -74,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="409">
   <si>
     <t>good quality (UNC for UNC collection; UNC and XF for XF collection)</t>
   </si>
@@ -1284,6 +1286,24 @@
   </si>
   <si>
     <t>Full Album name</t>
+  </si>
+  <si>
+    <t>Album ID</t>
+  </si>
+  <si>
+    <t>Album hardcoded link</t>
+  </si>
+  <si>
+    <t>OP</t>
+  </si>
+  <si>
+    <t>FB</t>
+  </si>
+  <si>
+    <t>Fufalco Bogdan list format</t>
+  </si>
+  <si>
+    <t>A0001-GR-BL</t>
   </si>
 </sst>
 </file>
@@ -1851,7 +1871,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2052,6 +2072,18 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="20" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2100,72 +2132,13 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="34">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2650,6 +2623,54 @@
         </horizontal>
       </border>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -2672,23 +2693,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>336550</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>298450</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>82550</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>232866</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>83201</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>488950</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>45570</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Рисунок 2">
+        <xdr:cNvPr id="2" name="Рисунок 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A868196E-1DF9-449B-9D2C-1C8DABFA701C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{416ACAFA-E733-4429-ADBA-6168899E9B07}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2704,8 +2725,57 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4654550" y="298450"/>
-          <a:ext cx="7821116" cy="4667901"/>
+          <a:off x="7048500" y="635000"/>
+          <a:ext cx="8375650" cy="4566770"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>431800</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>147170</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Рисунок 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC090D59-0D82-45A0-BE1D-FAFACCD1761B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6775450" y="463550"/>
+          <a:ext cx="8375650" cy="4566770"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2718,28 +2788,28 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{973D7237-72C7-453E-A0E1-526C93326B28}" name="Таблица3" displayName="Таблица3" ref="A1:F51" totalsRowShown="0" headerRowDxfId="33" dataDxfId="31" headerRowBorderDxfId="32" tableBorderDxfId="30" totalsRowBorderDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{973D7237-72C7-453E-A0E1-526C93326B28}" name="Таблица3" displayName="Таблица3" ref="A1:F51" totalsRowShown="0" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
   <autoFilter ref="A1:F51" xr:uid="{A2D8FA3D-4024-4365-BE1D-F93D0AF2D426}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{12C2DF0B-47FA-46A4-8424-55A1488EF88B}" name="ID" dataDxfId="28"/>
-    <tableColumn id="2" xr3:uid="{EB0B36CE-168D-429E-896D-DBA54794224F}" name="Name_Eng" dataDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{6C3A2CE8-252E-4C52-985B-8CDDFD9FA0C7}" name="OfficialMintName_Native" dataDxfId="26"/>
-    <tableColumn id="8" xr3:uid="{DA5871DC-2EDB-49C0-953E-EC0F70288E21}" name="Country" dataDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{FCD85F85-A94E-4BBE-9D3B-2B7494638375}" name="Mint_City" dataDxfId="24"/>
-    <tableColumn id="6" xr3:uid="{E5141978-CA91-4DE9-86F1-8A8AFA716534}" name="Alias" dataDxfId="23"/>
+    <tableColumn id="1" xr3:uid="{12C2DF0B-47FA-46A4-8424-55A1488EF88B}" name="ID" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{EB0B36CE-168D-429E-896D-DBA54794224F}" name="Name_Eng" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{6C3A2CE8-252E-4C52-985B-8CDDFD9FA0C7}" name="OfficialMintName_Native" dataDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{DA5871DC-2EDB-49C0-953E-EC0F70288E21}" name="Country" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{FCD85F85-A94E-4BBE-9D3B-2B7494638375}" name="Mint_City" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{E5141978-CA91-4DE9-86F1-8A8AFA716534}" name="Alias" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9D0F8E3D-96B1-4DB8-B1A6-8DD6B84F3693}" name="Таблица35" displayName="Таблица35" ref="A1:D52" totalsRowShown="0" headerRowDxfId="22" dataDxfId="20" headerRowBorderDxfId="21" tableBorderDxfId="19" totalsRowBorderDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9D0F8E3D-96B1-4DB8-B1A6-8DD6B84F3693}" name="Таблица35" displayName="Таблица35" ref="A1:D52" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13" totalsRowBorderDxfId="12">
   <autoFilter ref="A1:D52" xr:uid="{A2D8FA3D-4024-4365-BE1D-F93D0AF2D426}"/>
   <tableColumns count="4">
-    <tableColumn id="4" xr3:uid="{74AFB32D-7AAA-46BE-8174-ED698BB4613E}" name="Mint_id" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{523D65CD-0F56-441F-90B5-E46A9B14F0D0}" name="Ekaterinburg Mint" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{1AAB7352-E935-4EC6-A0D1-3EDC5D0BC93C}" name="Year_of_start" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{5FF15381-476A-4F88-B93A-6452F2830A0A}" name="Year_of_end" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{74AFB32D-7AAA-46BE-8174-ED698BB4613E}" name="Mint_id" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{523D65CD-0F56-441F-90B5-E46A9B14F0D0}" name="Ekaterinburg Mint" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{1AAB7352-E935-4EC6-A0D1-3EDC5D0BC93C}" name="Year_of_start" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{5FF15381-476A-4F88-B93A-6452F2830A0A}" name="Year_of_end" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2753,25 +2823,25 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{8354E581-3B48-4762-81A7-EA76E36C4BB5}" name="№" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{1F45DC85-8ECA-45FE-BF45-E528619CEE0E}" name="Links:" dataDxfId="12" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{3FAE616B-3296-4770-9E56-8A824991EECA}" name="Description:" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{8354E581-3B48-4762-81A7-EA76E36C4BB5}" name="№" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{1F45DC85-8ECA-45FE-BF45-E528619CEE0E}" name="Links:" dataDxfId="6" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{3FAE616B-3296-4770-9E56-8A824991EECA}" name="Description:" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D0DCC88A-2D36-4004-A694-FC0C0F0C3396}" name="Таблица2" displayName="Таблица2" ref="A1:C16" totalsRowShown="0" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D0DCC88A-2D36-4004-A694-FC0C0F0C3396}" name="Таблица2" displayName="Таблица2" ref="A1:C16" totalsRowShown="0" headerRowBorderDxfId="4" tableBorderDxfId="3" totalsRowBorderDxfId="2">
   <autoFilter ref="A1:C16" xr:uid="{00000000-0009-0000-0100-000002000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{28358E6A-6F3A-468C-9E1C-880A34D9BECE}" name="№" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{28358E6A-6F3A-468C-9E1C-880A34D9BECE}" name="№" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{DD0AD5C8-324B-4DA7-B39F-B2DB3EF91222}" name="Links:"/>
-    <tableColumn id="3" xr3:uid="{FC8A6018-CA7E-4C73-9B21-B272B55FA8C1}" name="Description:" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{FC8A6018-CA7E-4C73-9B21-B272B55FA8C1}" name="Description:" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -3162,12 +3232,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C7:C8">
-    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="33" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C7))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6">
-    <cfRule type="containsText" dxfId="4" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="32" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C6))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3184,7 +3254,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2">
-    <cfRule type="containsText" dxfId="3" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="31" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C2))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3201,7 +3271,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4">
-    <cfRule type="containsText" dxfId="2" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="30" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C4))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3218,7 +3288,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C5">
-    <cfRule type="containsText" dxfId="1" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="29" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C5))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3235,7 +3305,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3">
-    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="28" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C3))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -3266,2515 +3336,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57D9DE6C-583F-4F0B-9E0F-CDE5965E194A}">
-  <dimension ref="A1:I30"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="9.90625" customWidth="1"/>
-    <col min="2" max="2" width="18.7265625" customWidth="1"/>
-    <col min="3" max="3" width="19.54296875" customWidth="1"/>
-    <col min="7" max="7" width="14.08984375" customWidth="1"/>
-    <col min="8" max="8" width="11.90625" customWidth="1"/>
-    <col min="9" max="9" width="26.08984375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="66" t="s">
-        <v>62</v>
-      </c>
-      <c r="B1" s="66" t="s">
-        <v>63</v>
-      </c>
-      <c r="C1" s="67" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="64" t="s">
-        <v>63</v>
-      </c>
-      <c r="H1" s="64" t="s">
-        <v>74</v>
-      </c>
-      <c r="I1" s="64" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" s="78">
-        <v>1</v>
-      </c>
-      <c r="B2" s="86">
-        <v>1</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="H2" s="10">
-        <v>1</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" s="79"/>
-      <c r="B3" s="86"/>
-      <c r="C3" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" s="80"/>
-      <c r="B4" s="87">
-        <v>2</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" s="80"/>
-      <c r="B5" s="87"/>
-      <c r="C5" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6" s="80"/>
-      <c r="B6" s="15">
-        <v>3</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" s="80"/>
-      <c r="B7" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" s="80"/>
-      <c r="B8" s="88">
-        <v>6</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="80"/>
-      <c r="B9" s="89"/>
-      <c r="C9" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A10" s="80"/>
-      <c r="B10" s="17">
-        <v>7</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="80"/>
-      <c r="B11" s="24"/>
-      <c r="C11" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="80"/>
-      <c r="B12" s="18">
-        <v>8</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" s="81"/>
-      <c r="B13" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="82"/>
-      <c r="B14" s="26" t="s">
-        <v>91</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="14.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="83">
-        <v>2</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>364</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="84"/>
-      <c r="B16" s="20" t="s">
-        <v>365</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="84"/>
-      <c r="B17" s="21" t="s">
-        <v>366</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="85"/>
-      <c r="B18" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="14.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="72">
-        <v>3</v>
-      </c>
-      <c r="B19" s="23" t="s">
-        <v>89</v>
-      </c>
-      <c r="C19" s="14" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="73"/>
-      <c r="B20" s="27" t="s">
-        <v>93</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="74"/>
-      <c r="B21" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="14.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="75">
-        <v>4</v>
-      </c>
-      <c r="B22" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="76"/>
-      <c r="B23" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="76"/>
-      <c r="B24" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="76"/>
-      <c r="B25" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" s="76"/>
-      <c r="B26" s="29" t="s">
-        <v>104</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" s="76"/>
-      <c r="B27" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" s="76"/>
-      <c r="B28" s="18">
-        <v>8</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="77"/>
-      <c r="B29" s="31" t="s">
-        <v>78</v>
-      </c>
-      <c r="C29" s="13" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
-  </sheetData>
-  <autoFilter ref="A1:C15" xr:uid="{57D9DE6C-583F-4F0B-9E0F-CDE5965E194A}"/>
-  <mergeCells count="7">
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="A22:A29"/>
-    <mergeCell ref="A2:A14"/>
-    <mergeCell ref="A15:A18"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="B8:B9"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <ignoredErrors>
-    <ignoredError sqref="B23:B27" numberStoredAsText="1"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{866E9A5E-386D-439E-AA25-CB46A31C625C}">
-  <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="15.453125" style="95" customWidth="1"/>
-    <col min="2" max="2" width="15.453125" customWidth="1"/>
-    <col min="3" max="3" width="15.453125" style="95" customWidth="1"/>
-    <col min="4" max="4" width="15.453125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="36.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="94" t="s">
-        <v>399</v>
-      </c>
-      <c r="B1" s="94" t="s">
-        <v>400</v>
-      </c>
-      <c r="C1" s="92" t="s">
-        <v>401</v>
-      </c>
-      <c r="D1" s="90" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="95" t="s">
-        <v>238</v>
-      </c>
-      <c r="B2" s="93" t="s">
-        <v>397</v>
-      </c>
-      <c r="C2" s="91" t="s">
-        <v>375</v>
-      </c>
-      <c r="D2" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="95" t="s">
-        <v>176</v>
-      </c>
-      <c r="B3" s="93" t="s">
-        <v>398</v>
-      </c>
-      <c r="C3" s="91" t="s">
-        <v>376</v>
-      </c>
-      <c r="D3" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C4" s="91" t="s">
-        <v>377</v>
-      </c>
-      <c r="D4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C5" s="91" t="s">
-        <v>142</v>
-      </c>
-      <c r="D5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C6" s="91" t="s">
-        <v>378</v>
-      </c>
-      <c r="D6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C7" s="91" t="s">
-        <v>379</v>
-      </c>
-      <c r="D7" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C8" s="91" t="s">
-        <v>380</v>
-      </c>
-      <c r="D8" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C9" s="91" t="s">
-        <v>381</v>
-      </c>
-      <c r="D9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C10" s="91" t="s">
-        <v>382</v>
-      </c>
-      <c r="D10" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C11" s="91" t="s">
-        <v>383</v>
-      </c>
-      <c r="D11" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C12" s="91" t="s">
-        <v>384</v>
-      </c>
-      <c r="D12" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C13" s="91" t="s">
-        <v>385</v>
-      </c>
-      <c r="D13" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C14" s="91" t="s">
-        <v>386</v>
-      </c>
-      <c r="D14" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C15" s="91" t="s">
-        <v>387</v>
-      </c>
-      <c r="D15" t="s">
-        <v>373</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4C14141-45DA-4C30-845C-3E630B347F10}">
-  <dimension ref="A1:F51"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="6.54296875" style="41" customWidth="1"/>
-    <col min="2" max="2" width="38.26953125" customWidth="1"/>
-    <col min="3" max="3" width="65.36328125" customWidth="1"/>
-    <col min="4" max="5" width="16.81640625" customWidth="1"/>
-    <col min="6" max="6" width="6.7265625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="32" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" s="33" t="s">
-        <v>109</v>
-      </c>
-      <c r="C1" s="33" t="s">
-        <v>110</v>
-      </c>
-      <c r="D1" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" s="33" t="s">
-        <v>111</v>
-      </c>
-      <c r="F1" s="34" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="35">
-        <v>1</v>
-      </c>
-      <c r="B2" s="36" t="s">
-        <v>113</v>
-      </c>
-      <c r="C2" s="36" t="s">
-        <v>114</v>
-      </c>
-      <c r="D2" s="36" t="s">
-        <v>64</v>
-      </c>
-      <c r="E2" s="36" t="s">
-        <v>115</v>
-      </c>
-      <c r="F2" s="37" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="38">
-        <v>2</v>
-      </c>
-      <c r="B3" s="39" t="s">
-        <v>117</v>
-      </c>
-      <c r="C3" s="36" t="s">
-        <v>114</v>
-      </c>
-      <c r="D3" s="36" t="s">
-        <v>84</v>
-      </c>
-      <c r="E3" s="36" t="s">
-        <v>115</v>
-      </c>
-      <c r="F3" s="39" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="35">
-        <v>3</v>
-      </c>
-      <c r="B4" s="36" t="s">
-        <v>119</v>
-      </c>
-      <c r="C4" s="36" t="s">
-        <v>120</v>
-      </c>
-      <c r="D4" s="36" t="s">
-        <v>99</v>
-      </c>
-      <c r="E4" s="36" t="s">
-        <v>121</v>
-      </c>
-      <c r="F4" s="37" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="38">
-        <v>4</v>
-      </c>
-      <c r="B5" s="36" t="s">
-        <v>123</v>
-      </c>
-      <c r="C5" s="40" t="s">
-        <v>124</v>
-      </c>
-      <c r="D5" s="40" t="s">
-        <v>68</v>
-      </c>
-      <c r="E5" s="36" t="s">
-        <v>125</v>
-      </c>
-      <c r="F5" s="37" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="35">
-        <v>5</v>
-      </c>
-      <c r="B6" s="36" t="s">
-        <v>127</v>
-      </c>
-      <c r="C6" s="36" t="s">
-        <v>128</v>
-      </c>
-      <c r="D6" s="36" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="36" t="s">
-        <v>129</v>
-      </c>
-      <c r="F6" s="37" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="38">
-        <v>6</v>
-      </c>
-      <c r="B7" s="36" t="s">
-        <v>131</v>
-      </c>
-      <c r="C7" s="36" t="s">
-        <v>132</v>
-      </c>
-      <c r="D7" s="36" t="s">
-        <v>73</v>
-      </c>
-      <c r="E7" s="36" t="s">
-        <v>133</v>
-      </c>
-      <c r="F7" s="37" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="35">
-        <v>7</v>
-      </c>
-      <c r="B8" s="36" t="s">
-        <v>135</v>
-      </c>
-      <c r="C8" s="36" t="s">
-        <v>136</v>
-      </c>
-      <c r="D8" s="36" t="s">
-        <v>105</v>
-      </c>
-      <c r="E8" s="36" t="s">
-        <v>137</v>
-      </c>
-      <c r="F8" s="37" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="38">
-        <v>8</v>
-      </c>
-      <c r="B9" s="36" t="s">
-        <v>139</v>
-      </c>
-      <c r="C9" s="36" t="s">
-        <v>140</v>
-      </c>
-      <c r="D9" s="36" t="s">
-        <v>107</v>
-      </c>
-      <c r="E9" s="36" t="s">
-        <v>141</v>
-      </c>
-      <c r="F9" s="36" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="35">
-        <v>9</v>
-      </c>
-      <c r="B10" s="36" t="s">
-        <v>143</v>
-      </c>
-      <c r="C10" s="36" t="s">
-        <v>144</v>
-      </c>
-      <c r="D10" s="36" t="s">
-        <v>97</v>
-      </c>
-      <c r="E10" s="36" t="s">
-        <v>145</v>
-      </c>
-      <c r="F10" s="36" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="38">
-        <v>10</v>
-      </c>
-      <c r="B11" s="36" t="s">
-        <v>147</v>
-      </c>
-      <c r="C11" s="36" t="s">
-        <v>148</v>
-      </c>
-      <c r="D11" s="36" t="s">
-        <v>84</v>
-      </c>
-      <c r="E11" s="36" t="s">
-        <v>149</v>
-      </c>
-      <c r="F11" s="36" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="35">
-        <v>11</v>
-      </c>
-      <c r="B12" s="39" t="s">
-        <v>151</v>
-      </c>
-      <c r="C12" s="39" t="s">
-        <v>152</v>
-      </c>
-      <c r="D12" s="36" t="s">
-        <v>84</v>
-      </c>
-      <c r="E12" s="39" t="s">
-        <v>153</v>
-      </c>
-      <c r="F12" s="39" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="38">
-        <v>12</v>
-      </c>
-      <c r="B13" s="39" t="s">
-        <v>154</v>
-      </c>
-      <c r="C13" s="39" t="s">
-        <v>155</v>
-      </c>
-      <c r="D13" s="36" t="s">
-        <v>84</v>
-      </c>
-      <c r="E13" s="39" t="s">
-        <v>156</v>
-      </c>
-      <c r="F13" s="39" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="35">
-        <v>13</v>
-      </c>
-      <c r="B14" s="39" t="s">
-        <v>158</v>
-      </c>
-      <c r="C14" s="39" t="s">
-        <v>159</v>
-      </c>
-      <c r="D14" s="36" t="s">
-        <v>84</v>
-      </c>
-      <c r="E14" s="39" t="s">
-        <v>160</v>
-      </c>
-      <c r="F14" s="39" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="38">
-        <v>14</v>
-      </c>
-      <c r="B15" s="39" t="s">
-        <v>162</v>
-      </c>
-      <c r="C15" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="D15" s="36" t="s">
-        <v>84</v>
-      </c>
-      <c r="E15" s="39" t="s">
-        <v>164</v>
-      </c>
-      <c r="F15" s="39" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="35">
-        <v>15</v>
-      </c>
-      <c r="B16" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="C16" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="D16" s="36" t="s">
-        <v>84</v>
-      </c>
-      <c r="E16" s="39" t="s">
-        <v>168</v>
-      </c>
-      <c r="F16" s="39" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="38">
-        <v>16</v>
-      </c>
-      <c r="B17" s="39" t="s">
-        <v>169</v>
-      </c>
-      <c r="C17" s="39" t="s">
-        <v>170</v>
-      </c>
-      <c r="D17" s="36" t="s">
-        <v>84</v>
-      </c>
-      <c r="E17" s="39" t="s">
-        <v>171</v>
-      </c>
-      <c r="F17" s="39" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="35">
-        <v>17</v>
-      </c>
-      <c r="B18" s="39" t="s">
-        <v>173</v>
-      </c>
-      <c r="C18" s="39" t="s">
-        <v>174</v>
-      </c>
-      <c r="D18" s="36" t="s">
-        <v>84</v>
-      </c>
-      <c r="E18" s="39" t="s">
-        <v>175</v>
-      </c>
-      <c r="F18" s="39" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="38">
-        <v>18</v>
-      </c>
-      <c r="B19" s="39" t="s">
-        <v>177</v>
-      </c>
-      <c r="C19" s="39" t="s">
-        <v>178</v>
-      </c>
-      <c r="D19" s="36" t="s">
-        <v>84</v>
-      </c>
-      <c r="E19" s="39" t="s">
-        <v>179</v>
-      </c>
-      <c r="F19" s="39" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="35">
-        <v>19</v>
-      </c>
-      <c r="B20" s="36" t="s">
-        <v>181</v>
-      </c>
-      <c r="C20" s="36" t="s">
-        <v>182</v>
-      </c>
-      <c r="D20" s="36" t="s">
-        <v>84</v>
-      </c>
-      <c r="E20" s="36" t="s">
-        <v>183</v>
-      </c>
-      <c r="F20" s="36" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="38">
-        <v>20</v>
-      </c>
-      <c r="B21" s="39" t="s">
-        <v>185</v>
-      </c>
-      <c r="C21" s="39" t="s">
-        <v>186</v>
-      </c>
-      <c r="D21" s="39" t="s">
-        <v>72</v>
-      </c>
-      <c r="E21" s="39" t="s">
-        <v>187</v>
-      </c>
-      <c r="F21" s="39" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="35">
-        <v>21</v>
-      </c>
-      <c r="B22" s="36" t="s">
-        <v>189</v>
-      </c>
-      <c r="C22" s="36" t="s">
-        <v>190</v>
-      </c>
-      <c r="D22" s="36" t="s">
-        <v>103</v>
-      </c>
-      <c r="E22" s="36" t="s">
-        <v>191</v>
-      </c>
-      <c r="F22" s="36" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="38">
-        <v>22</v>
-      </c>
-      <c r="B23" s="36" t="s">
-        <v>193</v>
-      </c>
-      <c r="C23" s="36" t="s">
-        <v>194</v>
-      </c>
-      <c r="D23" s="36" t="s">
-        <v>71</v>
-      </c>
-      <c r="E23" s="36" t="s">
-        <v>195</v>
-      </c>
-      <c r="F23" s="36" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="35">
-        <v>23</v>
-      </c>
-      <c r="B24" s="36" t="s">
-        <v>197</v>
-      </c>
-      <c r="C24" s="36" t="s">
-        <v>198</v>
-      </c>
-      <c r="D24" s="36" t="s">
-        <v>69</v>
-      </c>
-      <c r="E24" s="36" t="s">
-        <v>199</v>
-      </c>
-      <c r="F24" s="36" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="38">
-        <v>24</v>
-      </c>
-      <c r="B25" s="36" t="s">
-        <v>201</v>
-      </c>
-      <c r="C25" s="36" t="s">
-        <v>202</v>
-      </c>
-      <c r="D25" s="36" t="s">
-        <v>83</v>
-      </c>
-      <c r="E25" s="36" t="s">
-        <v>203</v>
-      </c>
-      <c r="F25" s="36" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="35">
-        <v>25</v>
-      </c>
-      <c r="B26" s="39" t="s">
-        <v>205</v>
-      </c>
-      <c r="C26" s="39" t="s">
-        <v>206</v>
-      </c>
-      <c r="D26" s="39" t="s">
-        <v>207</v>
-      </c>
-      <c r="E26" s="39" t="s">
-        <v>208</v>
-      </c>
-      <c r="F26" s="39" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="38">
-        <v>26</v>
-      </c>
-      <c r="B27" s="36" t="s">
-        <v>210</v>
-      </c>
-      <c r="C27" s="36" t="s">
-        <v>211</v>
-      </c>
-      <c r="D27" s="39" t="s">
-        <v>207</v>
-      </c>
-      <c r="E27" s="36" t="s">
-        <v>212</v>
-      </c>
-      <c r="F27" s="36" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" s="35">
-        <v>27</v>
-      </c>
-      <c r="B28" s="39" t="s">
-        <v>214</v>
-      </c>
-      <c r="C28" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="D28" s="39" t="s">
-        <v>216</v>
-      </c>
-      <c r="E28" s="39" t="s">
-        <v>217</v>
-      </c>
-      <c r="F28" s="39" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" s="38">
-        <v>28</v>
-      </c>
-      <c r="B29" s="36" t="s">
-        <v>219</v>
-      </c>
-      <c r="C29" s="36" t="s">
-        <v>220</v>
-      </c>
-      <c r="D29" s="36" t="s">
-        <v>216</v>
-      </c>
-      <c r="E29" s="36" t="s">
-        <v>221</v>
-      </c>
-      <c r="F29" s="36" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" s="35">
-        <v>29</v>
-      </c>
-      <c r="B30" s="36" t="s">
-        <v>223</v>
-      </c>
-      <c r="C30" s="36" t="s">
-        <v>223</v>
-      </c>
-      <c r="D30" s="36" t="s">
-        <v>224</v>
-      </c>
-      <c r="E30" s="36" t="s">
-        <v>225</v>
-      </c>
-      <c r="F30" s="36" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31" s="38">
-        <v>30</v>
-      </c>
-      <c r="B31" s="39" t="s">
-        <v>227</v>
-      </c>
-      <c r="C31" s="39" t="s">
-        <v>227</v>
-      </c>
-      <c r="D31" s="39" t="s">
-        <v>228</v>
-      </c>
-      <c r="E31" s="39" t="s">
-        <v>229</v>
-      </c>
-      <c r="F31" s="39" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" s="35">
-        <v>31</v>
-      </c>
-      <c r="B32" s="36" t="s">
-        <v>231</v>
-      </c>
-      <c r="C32" s="36" t="s">
-        <v>231</v>
-      </c>
-      <c r="D32" s="39" t="s">
-        <v>228</v>
-      </c>
-      <c r="E32" s="39" t="s">
-        <v>232</v>
-      </c>
-      <c r="F32" s="39" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" s="38">
-        <v>32</v>
-      </c>
-      <c r="B33" s="36" t="s">
-        <v>233</v>
-      </c>
-      <c r="C33" s="36" t="s">
-        <v>233</v>
-      </c>
-      <c r="D33" s="39" t="s">
-        <v>228</v>
-      </c>
-      <c r="E33" s="36" t="s">
-        <v>234</v>
-      </c>
-      <c r="F33" s="39" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A34" s="38">
-        <v>33</v>
-      </c>
-      <c r="B34" s="39" t="s">
-        <v>236</v>
-      </c>
-      <c r="C34" s="39" t="s">
-        <v>236</v>
-      </c>
-      <c r="D34" s="39" t="s">
-        <v>228</v>
-      </c>
-      <c r="E34" s="39" t="s">
-        <v>237</v>
-      </c>
-      <c r="F34" s="39" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A35" s="35">
-        <v>34</v>
-      </c>
-      <c r="B35" s="39" t="s">
-        <v>239</v>
-      </c>
-      <c r="C35" s="39" t="s">
-        <v>239</v>
-      </c>
-      <c r="D35" s="39" t="s">
-        <v>228</v>
-      </c>
-      <c r="E35" s="39" t="s">
-        <v>240</v>
-      </c>
-      <c r="F35" s="39" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A36" s="35">
-        <v>35</v>
-      </c>
-      <c r="B36" s="36" t="s">
-        <v>242</v>
-      </c>
-      <c r="C36" s="36" t="s">
-        <v>242</v>
-      </c>
-      <c r="D36" s="36" t="s">
-        <v>243</v>
-      </c>
-      <c r="E36" s="36" t="s">
-        <v>244</v>
-      </c>
-      <c r="F36" s="36" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A37" s="35">
-        <v>36</v>
-      </c>
-      <c r="B37" s="36" t="s">
-        <v>245</v>
-      </c>
-      <c r="C37" s="36" t="s">
-        <v>245</v>
-      </c>
-      <c r="D37" s="36" t="s">
-        <v>243</v>
-      </c>
-      <c r="E37" s="36" t="s">
-        <v>246</v>
-      </c>
-      <c r="F37" s="36" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38" s="35">
-        <v>37</v>
-      </c>
-      <c r="B38" s="39" t="s">
-        <v>247</v>
-      </c>
-      <c r="C38" s="39" t="s">
-        <v>248</v>
-      </c>
-      <c r="D38" s="39" t="s">
-        <v>249</v>
-      </c>
-      <c r="E38" s="39" t="s">
-        <v>250</v>
-      </c>
-      <c r="F38" s="39" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A39" s="35">
-        <v>38</v>
-      </c>
-      <c r="B39" s="39" t="s">
-        <v>252</v>
-      </c>
-      <c r="C39" s="39" t="s">
-        <v>253</v>
-      </c>
-      <c r="D39" s="39" t="s">
-        <v>249</v>
-      </c>
-      <c r="E39" s="39" t="s">
-        <v>254</v>
-      </c>
-      <c r="F39" s="39" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A40" s="35">
-        <v>39</v>
-      </c>
-      <c r="B40" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="C40" s="36" t="s">
-        <v>257</v>
-      </c>
-      <c r="D40" s="39" t="s">
-        <v>249</v>
-      </c>
-      <c r="E40" s="36" t="s">
-        <v>258</v>
-      </c>
-      <c r="F40" s="36" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A41" s="35">
-        <v>40</v>
-      </c>
-      <c r="B41" s="36" t="s">
-        <v>260</v>
-      </c>
-      <c r="C41" s="36" t="s">
-        <v>260</v>
-      </c>
-      <c r="D41" s="39" t="s">
-        <v>249</v>
-      </c>
-      <c r="E41" s="36" t="s">
-        <v>261</v>
-      </c>
-      <c r="F41" s="36" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A42" s="35">
-        <v>41</v>
-      </c>
-      <c r="B42" s="36" t="s">
-        <v>263</v>
-      </c>
-      <c r="C42" s="36" t="s">
-        <v>264</v>
-      </c>
-      <c r="D42" s="36" t="s">
-        <v>265</v>
-      </c>
-      <c r="E42" s="36" t="s">
-        <v>266</v>
-      </c>
-      <c r="F42" s="36" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A43" s="35">
-        <v>42</v>
-      </c>
-      <c r="B43" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="C43" s="36" t="s">
-        <v>269</v>
-      </c>
-      <c r="D43" s="36" t="s">
-        <v>224</v>
-      </c>
-      <c r="E43" s="36" t="s">
-        <v>270</v>
-      </c>
-      <c r="F43" s="36" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A44" s="38">
-        <v>43</v>
-      </c>
-      <c r="B44" s="39" t="s">
-        <v>272</v>
-      </c>
-      <c r="C44" s="39" t="s">
-        <v>272</v>
-      </c>
-      <c r="D44" s="36" t="s">
-        <v>224</v>
-      </c>
-      <c r="E44" s="39" t="s">
-        <v>273</v>
-      </c>
-      <c r="F44" s="39" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A45" s="38">
-        <v>44</v>
-      </c>
-      <c r="B45" s="39" t="s">
-        <v>275</v>
-      </c>
-      <c r="C45" s="39" t="s">
-        <v>276</v>
-      </c>
-      <c r="D45" s="39" t="s">
-        <v>277</v>
-      </c>
-      <c r="E45" s="39" t="s">
-        <v>278</v>
-      </c>
-      <c r="F45" s="39" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A46" s="35">
-        <v>45</v>
-      </c>
-      <c r="B46" s="36" t="s">
-        <v>280</v>
-      </c>
-      <c r="C46" s="36" t="s">
-        <v>281</v>
-      </c>
-      <c r="D46" s="36" t="s">
-        <v>282</v>
-      </c>
-      <c r="E46" s="36" t="s">
-        <v>283</v>
-      </c>
-      <c r="F46" s="36" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A47" s="35">
-        <v>46</v>
-      </c>
-      <c r="B47" s="36" t="s">
-        <v>285</v>
-      </c>
-      <c r="C47" s="36" t="s">
-        <v>286</v>
-      </c>
-      <c r="D47" s="39" t="s">
-        <v>249</v>
-      </c>
-      <c r="E47" s="36" t="s">
-        <v>287</v>
-      </c>
-      <c r="F47" s="36" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A48" s="35">
-        <v>47</v>
-      </c>
-      <c r="B48" s="36" t="s">
-        <v>289</v>
-      </c>
-      <c r="C48" s="36" t="s">
-        <v>290</v>
-      </c>
-      <c r="D48" s="36" t="s">
-        <v>291</v>
-      </c>
-      <c r="E48" s="36" t="s">
-        <v>292</v>
-      </c>
-      <c r="F48" s="36" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A49" s="35">
-        <v>48</v>
-      </c>
-      <c r="B49" s="36" t="s">
-        <v>294</v>
-      </c>
-      <c r="C49" s="36" t="s">
-        <v>295</v>
-      </c>
-      <c r="D49" s="36" t="s">
-        <v>296</v>
-      </c>
-      <c r="E49" s="36" t="s">
-        <v>297</v>
-      </c>
-      <c r="F49" s="36" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A50" s="35">
-        <v>49</v>
-      </c>
-      <c r="B50" s="68" t="s">
-        <v>360</v>
-      </c>
-      <c r="C50" s="68" t="s">
-        <v>361</v>
-      </c>
-      <c r="D50" s="39" t="s">
-        <v>207</v>
-      </c>
-      <c r="E50" s="68" t="s">
-        <v>362</v>
-      </c>
-      <c r="F50" s="68" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A51" s="70">
-        <v>50</v>
-      </c>
-      <c r="B51" s="68" t="s">
-        <v>368</v>
-      </c>
-      <c r="C51" s="68" t="s">
-        <v>369</v>
-      </c>
-      <c r="D51" s="68" t="s">
-        <v>370</v>
-      </c>
-      <c r="E51" s="68" t="s">
-        <v>371</v>
-      </c>
-      <c r="F51" s="68" t="s">
-        <v>372</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF1BA8E2-9FD2-4C47-B5D3-EF9907B8F692}">
-  <dimension ref="A1:D52"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="10.54296875" style="41" customWidth="1"/>
-    <col min="2" max="2" width="38.26953125" customWidth="1"/>
-    <col min="3" max="3" width="14.6328125" customWidth="1"/>
-    <col min="4" max="4" width="13.36328125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="32" t="s">
-        <v>299</v>
-      </c>
-      <c r="B1" s="68" t="s">
-        <v>360</v>
-      </c>
-      <c r="C1" s="34" t="s">
-        <v>300</v>
-      </c>
-      <c r="D1" s="33" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="35">
-        <v>1</v>
-      </c>
-      <c r="B2" s="36" t="s">
-        <v>113</v>
-      </c>
-      <c r="C2" s="42">
-        <v>1194</v>
-      </c>
-      <c r="D2" s="43"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="38">
-        <v>2</v>
-      </c>
-      <c r="B3" s="39" t="s">
-        <v>117</v>
-      </c>
-      <c r="C3" s="43">
-        <v>1938</v>
-      </c>
-      <c r="D3" s="44">
-        <v>1944</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="35">
-        <v>3</v>
-      </c>
-      <c r="B4" s="36" t="s">
-        <v>119</v>
-      </c>
-      <c r="C4" s="42">
-        <v>1591</v>
-      </c>
-      <c r="D4" s="43"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="38">
-        <v>4</v>
-      </c>
-      <c r="B5" s="36" t="s">
-        <v>123</v>
-      </c>
-      <c r="C5" s="42">
-        <v>1973</v>
-      </c>
-      <c r="D5" s="43"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="35">
-        <v>5</v>
-      </c>
-      <c r="B6" s="36" t="s">
-        <v>127</v>
-      </c>
-      <c r="C6" s="42">
-        <v>989</v>
-      </c>
-      <c r="D6" s="43">
-        <v>2017</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="38">
-        <v>6</v>
-      </c>
-      <c r="B7" s="36" t="s">
-        <v>131</v>
-      </c>
-      <c r="C7" s="42">
-        <v>1010</v>
-      </c>
-      <c r="D7" s="43"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="35">
-        <v>7</v>
-      </c>
-      <c r="B8" s="36" t="s">
-        <v>135</v>
-      </c>
-      <c r="C8" s="42">
-        <v>1994</v>
-      </c>
-      <c r="D8" s="43"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="38">
-        <v>8</v>
-      </c>
-      <c r="B9" s="36" t="s">
-        <v>139</v>
-      </c>
-      <c r="C9" s="43">
-        <v>1972</v>
-      </c>
-      <c r="D9" s="43"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="35">
-        <v>9</v>
-      </c>
-      <c r="B10" s="36" t="s">
-        <v>143</v>
-      </c>
-      <c r="C10" s="43">
-        <v>1988</v>
-      </c>
-      <c r="D10" s="43">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="38">
-        <v>10</v>
-      </c>
-      <c r="B11" s="36" t="s">
-        <v>147</v>
-      </c>
-      <c r="C11" s="43">
-        <v>1280</v>
-      </c>
-      <c r="D11" s="43"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="35">
-        <v>11</v>
-      </c>
-      <c r="B12" s="39" t="s">
-        <v>151</v>
-      </c>
-      <c r="C12" s="43">
-        <v>1872</v>
-      </c>
-      <c r="D12" s="44">
-        <v>1878</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="38">
-        <v>12</v>
-      </c>
-      <c r="B13" s="39" t="s">
-        <v>154</v>
-      </c>
-      <c r="C13" s="43">
-        <v>1872</v>
-      </c>
-      <c r="D13" s="44">
-        <v>1879</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="35">
-        <v>13</v>
-      </c>
-      <c r="B14" s="39" t="s">
-        <v>158</v>
-      </c>
-      <c r="C14" s="43">
-        <v>1871</v>
-      </c>
-      <c r="D14" s="44"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="38">
-        <v>14</v>
-      </c>
-      <c r="B15" s="39" t="s">
-        <v>162</v>
-      </c>
-      <c r="C15" s="43">
-        <v>1872</v>
-      </c>
-      <c r="D15" s="44">
-        <v>1887</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="35">
-        <v>15</v>
-      </c>
-      <c r="B16" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="C16" s="43">
-        <v>1888</v>
-      </c>
-      <c r="D16" s="44">
-        <v>1953</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="38">
-        <v>16</v>
-      </c>
-      <c r="B17" s="39" t="s">
-        <v>169</v>
-      </c>
-      <c r="C17" s="43">
-        <v>1374</v>
-      </c>
-      <c r="D17" s="44"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="35">
-        <v>17</v>
-      </c>
-      <c r="B18" s="39" t="s">
-        <v>173</v>
-      </c>
-      <c r="C18" s="43">
-        <v>1827</v>
-      </c>
-      <c r="D18" s="44"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="38">
-        <v>18</v>
-      </c>
-      <c r="B19" s="39" t="s">
-        <v>177</v>
-      </c>
-      <c r="C19" s="43">
-        <v>1872</v>
-      </c>
-      <c r="D19" s="44">
-        <v>1882</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="35">
-        <v>19</v>
-      </c>
-      <c r="B20" s="36" t="s">
-        <v>181</v>
-      </c>
-      <c r="C20" s="43">
-        <v>801</v>
-      </c>
-      <c r="D20" s="43"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="38">
-        <v>20</v>
-      </c>
-      <c r="B21" s="39" t="s">
-        <v>185</v>
-      </c>
-      <c r="C21" s="43">
-        <v>1990</v>
-      </c>
-      <c r="D21" s="43"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="35">
-        <v>21</v>
-      </c>
-      <c r="B22" s="36" t="s">
-        <v>189</v>
-      </c>
-      <c r="C22" s="43">
-        <v>1328</v>
-      </c>
-      <c r="D22" s="43"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="38">
-        <v>22</v>
-      </c>
-      <c r="B23" s="36" t="s">
-        <v>193</v>
-      </c>
-      <c r="C23" s="43">
-        <v>1976</v>
-      </c>
-      <c r="D23" s="43"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="35">
-        <v>23</v>
-      </c>
-      <c r="B24" s="36" t="s">
-        <v>197</v>
-      </c>
-      <c r="C24" s="43">
-        <v>1928</v>
-      </c>
-      <c r="D24" s="43"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="38">
-        <v>24</v>
-      </c>
-      <c r="B25" s="36" t="s">
-        <v>201</v>
-      </c>
-      <c r="C25" s="43">
-        <v>1972</v>
-      </c>
-      <c r="D25" s="43"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="35">
-        <v>25</v>
-      </c>
-      <c r="B26" s="39" t="s">
-        <v>205</v>
-      </c>
-      <c r="C26" s="43">
-        <v>1942</v>
-      </c>
-      <c r="D26" s="44"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="38">
-        <v>26</v>
-      </c>
-      <c r="B27" s="36" t="s">
-        <v>210</v>
-      </c>
-      <c r="C27" s="43">
-        <v>1724</v>
-      </c>
-      <c r="D27" s="43"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" s="35">
-        <v>27</v>
-      </c>
-      <c r="B28" s="39" t="s">
-        <v>214</v>
-      </c>
-      <c r="C28" s="43">
-        <v>1992</v>
-      </c>
-      <c r="D28" s="44">
-        <v>1996</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="38">
-        <v>28</v>
-      </c>
-      <c r="B29" s="36" t="s">
-        <v>219</v>
-      </c>
-      <c r="C29" s="43">
-        <v>1998</v>
-      </c>
-      <c r="D29" s="43"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="35">
-        <v>29</v>
-      </c>
-      <c r="B30" s="36" t="s">
-        <v>223</v>
-      </c>
-      <c r="C30" s="43">
-        <v>1968</v>
-      </c>
-      <c r="D30" s="43"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" s="38">
-        <v>30</v>
-      </c>
-      <c r="B31" s="39" t="s">
-        <v>227</v>
-      </c>
-      <c r="C31" s="43">
-        <v>1792</v>
-      </c>
-      <c r="D31" s="44"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" s="35">
-        <v>31</v>
-      </c>
-      <c r="B32" s="36" t="s">
-        <v>231</v>
-      </c>
-      <c r="C32" s="43">
-        <v>1906</v>
-      </c>
-      <c r="D32" s="44"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="38">
-        <v>32</v>
-      </c>
-      <c r="B33" s="36" t="s">
-        <v>233</v>
-      </c>
-      <c r="C33" s="43">
-        <v>1854</v>
-      </c>
-      <c r="D33" s="43"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" s="38">
-        <v>33</v>
-      </c>
-      <c r="B34" s="39" t="s">
-        <v>236</v>
-      </c>
-      <c r="C34" s="43">
-        <v>1835</v>
-      </c>
-      <c r="D34" s="44">
-        <v>1942</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" s="35">
-        <v>34</v>
-      </c>
-      <c r="B35" s="39" t="s">
-        <v>239</v>
-      </c>
-      <c r="C35" s="43">
-        <v>1973</v>
-      </c>
-      <c r="D35" s="44"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" s="35">
-        <v>35</v>
-      </c>
-      <c r="B36" s="36" t="s">
-        <v>242</v>
-      </c>
-      <c r="C36" s="43">
-        <v>1908</v>
-      </c>
-      <c r="D36" s="43"/>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" s="35">
-        <v>36</v>
-      </c>
-      <c r="B37" s="36" t="s">
-        <v>245</v>
-      </c>
-      <c r="C37" s="43">
-        <v>1976</v>
-      </c>
-      <c r="D37" s="43"/>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" s="35">
-        <v>37</v>
-      </c>
-      <c r="B38" s="39" t="s">
-        <v>247</v>
-      </c>
-      <c r="C38" s="43">
-        <v>1803</v>
-      </c>
-      <c r="D38" s="44"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" s="35">
-        <v>38</v>
-      </c>
-      <c r="B39" s="39" t="s">
-        <v>252</v>
-      </c>
-      <c r="C39" s="43">
-        <v>1829</v>
-      </c>
-      <c r="D39" s="44"/>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" s="35">
-        <v>39</v>
-      </c>
-      <c r="B40" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="C40" s="43">
-        <v>1757</v>
-      </c>
-      <c r="D40" s="43"/>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="35">
-        <v>40</v>
-      </c>
-      <c r="B41" s="36" t="s">
-        <v>260</v>
-      </c>
-      <c r="C41" s="43">
-        <v>1640</v>
-      </c>
-      <c r="D41" s="43">
-        <v>1869</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" s="35">
-        <v>41</v>
-      </c>
-      <c r="B42" s="36" t="s">
-        <v>263</v>
-      </c>
-      <c r="C42" s="43">
-        <v>1992</v>
-      </c>
-      <c r="D42" s="43"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" s="35">
-        <v>42</v>
-      </c>
-      <c r="B43" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="C43" s="43">
-        <v>1850</v>
-      </c>
-      <c r="D43" s="43">
-        <v>2003</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" s="38">
-        <v>43</v>
-      </c>
-      <c r="B44" s="39" t="s">
-        <v>272</v>
-      </c>
-      <c r="C44" s="43">
-        <v>1860</v>
-      </c>
-      <c r="D44" s="43">
-        <v>1895</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" s="38">
-        <v>44</v>
-      </c>
-      <c r="B45" s="39" t="s">
-        <v>275</v>
-      </c>
-      <c r="C45" s="43">
-        <v>1890</v>
-      </c>
-      <c r="D45" s="44">
-        <v>1902</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" s="38">
-        <v>44</v>
-      </c>
-      <c r="B46" s="39" t="s">
-        <v>275</v>
-      </c>
-      <c r="C46" s="43">
-        <v>1923</v>
-      </c>
-      <c r="D46" s="43"/>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" s="35">
-        <v>45</v>
-      </c>
-      <c r="B47" s="36" t="s">
-        <v>280</v>
-      </c>
-      <c r="C47" s="43">
-        <v>1943</v>
-      </c>
-      <c r="D47" s="43"/>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" s="35">
-        <v>46</v>
-      </c>
-      <c r="B48" s="36" t="s">
-        <v>302</v>
-      </c>
-      <c r="C48" s="43">
-        <v>1988</v>
-      </c>
-      <c r="D48" s="43"/>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" s="35">
-        <v>47</v>
-      </c>
-      <c r="B49" s="36" t="s">
-        <v>289</v>
-      </c>
-      <c r="C49" s="43">
-        <v>1951</v>
-      </c>
-      <c r="D49" s="43"/>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" s="38">
-        <v>48</v>
-      </c>
-      <c r="B50" s="36" t="s">
-        <v>294</v>
-      </c>
-      <c r="C50" s="43">
-        <v>1535</v>
-      </c>
-      <c r="D50" s="43"/>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" s="35">
-        <v>49</v>
-      </c>
-      <c r="B51" s="68" t="s">
-        <v>360</v>
-      </c>
-      <c r="C51" s="69">
-        <v>1725</v>
-      </c>
-      <c r="D51" s="69">
-        <v>1876</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" s="38">
-        <v>50</v>
-      </c>
-      <c r="B52" s="68" t="s">
-        <v>368</v>
-      </c>
-      <c r="C52" s="69">
-        <v>1952</v>
-      </c>
-      <c r="D52" s="69"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId2"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0041FEF0-BF6F-4667-AFBD-1C23A1866795}">
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="10.7265625" customWidth="1"/>
-    <col min="2" max="2" width="17.453125" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="37.90625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="9">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="9">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="9">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="9">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="9">
-        <v>5</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="9">
-        <v>6</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8265AFD9-D9EB-4B75-B60D-6B7F7204230D}">
-  <dimension ref="A1:B29"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="26.36328125" customWidth="1"/>
-    <col min="2" max="2" width="31.36328125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" s="4"/>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" s="4"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="4"/>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" s="4"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="4"/>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="4"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="4"/>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" s="4"/>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="4"/>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" s="4"/>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B12" s="4"/>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B13" s="4"/>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" s="4"/>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B15" s="4"/>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B16" s="4"/>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B17" s="4"/>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B18" s="4"/>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B19" s="4"/>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B20" s="4"/>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B21" s="4"/>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B22" s="4"/>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B23" s="4"/>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A24" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B24" s="4"/>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B25" s="4"/>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A26" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B26" s="4"/>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A27" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B27" s="4"/>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A28" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B28" s="4"/>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A29" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="B29" s="4"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{729F7C06-1AE8-4162-8F40-6E9A64E311D7}">
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -5988,7 +3550,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8049D8E-7482-48AF-95C9-7F1B728B0DDE}">
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -6184,4 +3746,2556 @@
     <tablePart r:id="rId15"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57D9DE6C-583F-4F0B-9E0F-CDE5965E194A}">
+  <dimension ref="A1:I30"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="9.90625" customWidth="1"/>
+    <col min="2" max="2" width="18.7265625" customWidth="1"/>
+    <col min="3" max="3" width="19.54296875" customWidth="1"/>
+    <col min="7" max="7" width="14.08984375" customWidth="1"/>
+    <col min="8" max="8" width="11.90625" customWidth="1"/>
+    <col min="9" max="9" width="26.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A1" s="66" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="66" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="67" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="64" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" s="64" t="s">
+        <v>74</v>
+      </c>
+      <c r="I1" s="64" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" s="84">
+        <v>1</v>
+      </c>
+      <c r="B2" s="92">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="H2" s="10">
+        <v>1</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" s="85"/>
+      <c r="B3" s="92"/>
+      <c r="C3" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="86"/>
+      <c r="B4" s="93">
+        <v>2</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="86"/>
+      <c r="B5" s="93"/>
+      <c r="C5" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" s="86"/>
+      <c r="B6" s="15">
+        <v>3</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" s="86"/>
+      <c r="B7" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" s="86"/>
+      <c r="B8" s="94">
+        <v>6</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" s="86"/>
+      <c r="B9" s="95"/>
+      <c r="C9" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" s="86"/>
+      <c r="B10" s="17">
+        <v>7</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" s="86"/>
+      <c r="B11" s="24"/>
+      <c r="C11" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12" s="86"/>
+      <c r="B12" s="18">
+        <v>8</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13" s="87"/>
+      <c r="B13" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="88"/>
+      <c r="B14" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="14.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="89">
+        <v>2</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>364</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="90"/>
+      <c r="B16" s="20" t="s">
+        <v>365</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="90"/>
+      <c r="B17" s="21" t="s">
+        <v>366</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="91"/>
+      <c r="B18" s="22" t="s">
+        <v>92</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="14.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="78">
+        <v>3</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="79"/>
+      <c r="B20" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="80"/>
+      <c r="B21" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="14.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="81">
+        <v>4</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="82"/>
+      <c r="B23" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="82"/>
+      <c r="B24" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="82"/>
+      <c r="B25" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="82"/>
+      <c r="B26" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="82"/>
+      <c r="B27" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" s="82"/>
+      <c r="B28" s="18">
+        <v>8</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="83"/>
+      <c r="B29" s="31" t="s">
+        <v>78</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
+  </sheetData>
+  <autoFilter ref="A1:C15" xr:uid="{57D9DE6C-583F-4F0B-9E0F-CDE5965E194A}"/>
+  <mergeCells count="7">
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A22:A29"/>
+    <mergeCell ref="A2:A14"/>
+    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B8:B9"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="B23:B27" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DC835FD-69FE-4DBC-957F-9A46CA05517E}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="13.26953125" customWidth="1"/>
+    <col min="2" max="2" width="30.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A1" s="96" t="s">
+        <v>403</v>
+      </c>
+      <c r="B1" s="96" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{866E9A5E-386D-439E-AA25-CB46A31C625C}">
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="15.453125" style="77" customWidth="1"/>
+    <col min="2" max="2" width="24.7265625" customWidth="1"/>
+    <col min="3" max="3" width="15.453125" style="77" customWidth="1"/>
+    <col min="4" max="4" width="15.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="36.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="76" t="s">
+        <v>399</v>
+      </c>
+      <c r="B1" s="76" t="s">
+        <v>400</v>
+      </c>
+      <c r="C1" s="74" t="s">
+        <v>401</v>
+      </c>
+      <c r="D1" s="72" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="77" t="s">
+        <v>405</v>
+      </c>
+      <c r="B2" s="75" t="s">
+        <v>397</v>
+      </c>
+      <c r="C2" s="73" t="s">
+        <v>375</v>
+      </c>
+      <c r="D2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="77" t="s">
+        <v>142</v>
+      </c>
+      <c r="B3" s="75" t="s">
+        <v>398</v>
+      </c>
+      <c r="C3" s="73" t="s">
+        <v>376</v>
+      </c>
+      <c r="D3" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="77" t="s">
+        <v>406</v>
+      </c>
+      <c r="B4" t="s">
+        <v>407</v>
+      </c>
+      <c r="C4" s="73" t="s">
+        <v>377</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C5" s="73" t="s">
+        <v>142</v>
+      </c>
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C6" s="73" t="s">
+        <v>378</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C7" s="73" t="s">
+        <v>379</v>
+      </c>
+      <c r="D7" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C8" s="73" t="s">
+        <v>380</v>
+      </c>
+      <c r="D8" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C9" s="73" t="s">
+        <v>381</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C10" s="73" t="s">
+        <v>382</v>
+      </c>
+      <c r="D10" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C11" s="73" t="s">
+        <v>383</v>
+      </c>
+      <c r="D11" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C12" s="73" t="s">
+        <v>384</v>
+      </c>
+      <c r="D12" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C13" s="73" t="s">
+        <v>385</v>
+      </c>
+      <c r="D13" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C14" s="73" t="s">
+        <v>386</v>
+      </c>
+      <c r="D14" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C15" s="73" t="s">
+        <v>387</v>
+      </c>
+      <c r="D15" t="s">
+        <v>373</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1D965D1-2F9C-4783-AB93-708A62EBAC76}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4C14141-45DA-4C30-845C-3E630B347F10}">
+  <dimension ref="A1:F51"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="6.54296875" style="41" customWidth="1"/>
+    <col min="2" max="2" width="38.26953125" customWidth="1"/>
+    <col min="3" max="3" width="65.36328125" customWidth="1"/>
+    <col min="4" max="5" width="16.81640625" customWidth="1"/>
+    <col min="6" max="6" width="6.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1" s="33" t="s">
+        <v>110</v>
+      </c>
+      <c r="D1" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="33" t="s">
+        <v>111</v>
+      </c>
+      <c r="F1" s="34" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="35">
+        <v>1</v>
+      </c>
+      <c r="B2" s="36" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2" s="36" t="s">
+        <v>114</v>
+      </c>
+      <c r="D2" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="36" t="s">
+        <v>115</v>
+      </c>
+      <c r="F2" s="37" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="38">
+        <v>2</v>
+      </c>
+      <c r="B3" s="39" t="s">
+        <v>117</v>
+      </c>
+      <c r="C3" s="36" t="s">
+        <v>114</v>
+      </c>
+      <c r="D3" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="E3" s="36" t="s">
+        <v>115</v>
+      </c>
+      <c r="F3" s="39" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="35">
+        <v>3</v>
+      </c>
+      <c r="B4" s="36" t="s">
+        <v>119</v>
+      </c>
+      <c r="C4" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="D4" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="E4" s="36" t="s">
+        <v>121</v>
+      </c>
+      <c r="F4" s="37" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" s="38">
+        <v>4</v>
+      </c>
+      <c r="B5" s="36" t="s">
+        <v>123</v>
+      </c>
+      <c r="C5" s="40" t="s">
+        <v>124</v>
+      </c>
+      <c r="D5" s="40" t="s">
+        <v>68</v>
+      </c>
+      <c r="E5" s="36" t="s">
+        <v>125</v>
+      </c>
+      <c r="F5" s="37" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="35">
+        <v>5</v>
+      </c>
+      <c r="B6" s="36" t="s">
+        <v>127</v>
+      </c>
+      <c r="C6" s="36" t="s">
+        <v>128</v>
+      </c>
+      <c r="D6" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="36" t="s">
+        <v>129</v>
+      </c>
+      <c r="F6" s="37" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="38">
+        <v>6</v>
+      </c>
+      <c r="B7" s="36" t="s">
+        <v>131</v>
+      </c>
+      <c r="C7" s="36" t="s">
+        <v>132</v>
+      </c>
+      <c r="D7" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="E7" s="36" t="s">
+        <v>133</v>
+      </c>
+      <c r="F7" s="37" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="35">
+        <v>7</v>
+      </c>
+      <c r="B8" s="36" t="s">
+        <v>135</v>
+      </c>
+      <c r="C8" s="36" t="s">
+        <v>136</v>
+      </c>
+      <c r="D8" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="E8" s="36" t="s">
+        <v>137</v>
+      </c>
+      <c r="F8" s="37" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="38">
+        <v>8</v>
+      </c>
+      <c r="B9" s="36" t="s">
+        <v>139</v>
+      </c>
+      <c r="C9" s="36" t="s">
+        <v>140</v>
+      </c>
+      <c r="D9" s="36" t="s">
+        <v>107</v>
+      </c>
+      <c r="E9" s="36" t="s">
+        <v>141</v>
+      </c>
+      <c r="F9" s="36" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="35">
+        <v>9</v>
+      </c>
+      <c r="B10" s="36" t="s">
+        <v>143</v>
+      </c>
+      <c r="C10" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="D10" s="36" t="s">
+        <v>97</v>
+      </c>
+      <c r="E10" s="36" t="s">
+        <v>145</v>
+      </c>
+      <c r="F10" s="36" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="38">
+        <v>10</v>
+      </c>
+      <c r="B11" s="36" t="s">
+        <v>147</v>
+      </c>
+      <c r="C11" s="36" t="s">
+        <v>148</v>
+      </c>
+      <c r="D11" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="E11" s="36" t="s">
+        <v>149</v>
+      </c>
+      <c r="F11" s="36" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="35">
+        <v>11</v>
+      </c>
+      <c r="B12" s="39" t="s">
+        <v>151</v>
+      </c>
+      <c r="C12" s="39" t="s">
+        <v>152</v>
+      </c>
+      <c r="D12" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="E12" s="39" t="s">
+        <v>153</v>
+      </c>
+      <c r="F12" s="39" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="38">
+        <v>12</v>
+      </c>
+      <c r="B13" s="39" t="s">
+        <v>154</v>
+      </c>
+      <c r="C13" s="39" t="s">
+        <v>155</v>
+      </c>
+      <c r="D13" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="E13" s="39" t="s">
+        <v>156</v>
+      </c>
+      <c r="F13" s="39" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="35">
+        <v>13</v>
+      </c>
+      <c r="B14" s="39" t="s">
+        <v>158</v>
+      </c>
+      <c r="C14" s="39" t="s">
+        <v>159</v>
+      </c>
+      <c r="D14" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="E14" s="39" t="s">
+        <v>160</v>
+      </c>
+      <c r="F14" s="39" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="38">
+        <v>14</v>
+      </c>
+      <c r="B15" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="C15" s="39" t="s">
+        <v>163</v>
+      </c>
+      <c r="D15" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="E15" s="39" t="s">
+        <v>164</v>
+      </c>
+      <c r="F15" s="39" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="35">
+        <v>15</v>
+      </c>
+      <c r="B16" s="39" t="s">
+        <v>166</v>
+      </c>
+      <c r="C16" s="39" t="s">
+        <v>167</v>
+      </c>
+      <c r="D16" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="E16" s="39" t="s">
+        <v>168</v>
+      </c>
+      <c r="F16" s="39" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" s="38">
+        <v>16</v>
+      </c>
+      <c r="B17" s="39" t="s">
+        <v>169</v>
+      </c>
+      <c r="C17" s="39" t="s">
+        <v>170</v>
+      </c>
+      <c r="D17" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="E17" s="39" t="s">
+        <v>171</v>
+      </c>
+      <c r="F17" s="39" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" s="35">
+        <v>17</v>
+      </c>
+      <c r="B18" s="39" t="s">
+        <v>173</v>
+      </c>
+      <c r="C18" s="39" t="s">
+        <v>174</v>
+      </c>
+      <c r="D18" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="E18" s="39" t="s">
+        <v>175</v>
+      </c>
+      <c r="F18" s="39" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="38">
+        <v>18</v>
+      </c>
+      <c r="B19" s="39" t="s">
+        <v>177</v>
+      </c>
+      <c r="C19" s="39" t="s">
+        <v>178</v>
+      </c>
+      <c r="D19" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="E19" s="39" t="s">
+        <v>179</v>
+      </c>
+      <c r="F19" s="39" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" s="35">
+        <v>19</v>
+      </c>
+      <c r="B20" s="36" t="s">
+        <v>181</v>
+      </c>
+      <c r="C20" s="36" t="s">
+        <v>182</v>
+      </c>
+      <c r="D20" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F20" s="36" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="38">
+        <v>20</v>
+      </c>
+      <c r="B21" s="39" t="s">
+        <v>185</v>
+      </c>
+      <c r="C21" s="39" t="s">
+        <v>186</v>
+      </c>
+      <c r="D21" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="E21" s="39" t="s">
+        <v>187</v>
+      </c>
+      <c r="F21" s="39" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="35">
+        <v>21</v>
+      </c>
+      <c r="B22" s="36" t="s">
+        <v>189</v>
+      </c>
+      <c r="C22" s="36" t="s">
+        <v>190</v>
+      </c>
+      <c r="D22" s="36" t="s">
+        <v>103</v>
+      </c>
+      <c r="E22" s="36" t="s">
+        <v>191</v>
+      </c>
+      <c r="F22" s="36" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" s="38">
+        <v>22</v>
+      </c>
+      <c r="B23" s="36" t="s">
+        <v>193</v>
+      </c>
+      <c r="C23" s="36" t="s">
+        <v>194</v>
+      </c>
+      <c r="D23" s="36" t="s">
+        <v>71</v>
+      </c>
+      <c r="E23" s="36" t="s">
+        <v>195</v>
+      </c>
+      <c r="F23" s="36" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" s="35">
+        <v>23</v>
+      </c>
+      <c r="B24" s="36" t="s">
+        <v>197</v>
+      </c>
+      <c r="C24" s="36" t="s">
+        <v>198</v>
+      </c>
+      <c r="D24" s="36" t="s">
+        <v>69</v>
+      </c>
+      <c r="E24" s="36" t="s">
+        <v>199</v>
+      </c>
+      <c r="F24" s="36" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" s="38">
+        <v>24</v>
+      </c>
+      <c r="B25" s="36" t="s">
+        <v>201</v>
+      </c>
+      <c r="C25" s="36" t="s">
+        <v>202</v>
+      </c>
+      <c r="D25" s="36" t="s">
+        <v>83</v>
+      </c>
+      <c r="E25" s="36" t="s">
+        <v>203</v>
+      </c>
+      <c r="F25" s="36" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" s="35">
+        <v>25</v>
+      </c>
+      <c r="B26" s="39" t="s">
+        <v>205</v>
+      </c>
+      <c r="C26" s="39" t="s">
+        <v>206</v>
+      </c>
+      <c r="D26" s="39" t="s">
+        <v>207</v>
+      </c>
+      <c r="E26" s="39" t="s">
+        <v>208</v>
+      </c>
+      <c r="F26" s="39" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" s="38">
+        <v>26</v>
+      </c>
+      <c r="B27" s="36" t="s">
+        <v>210</v>
+      </c>
+      <c r="C27" s="36" t="s">
+        <v>211</v>
+      </c>
+      <c r="D27" s="39" t="s">
+        <v>207</v>
+      </c>
+      <c r="E27" s="36" t="s">
+        <v>212</v>
+      </c>
+      <c r="F27" s="36" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" s="35">
+        <v>27</v>
+      </c>
+      <c r="B28" s="39" t="s">
+        <v>214</v>
+      </c>
+      <c r="C28" s="39" t="s">
+        <v>215</v>
+      </c>
+      <c r="D28" s="39" t="s">
+        <v>216</v>
+      </c>
+      <c r="E28" s="39" t="s">
+        <v>217</v>
+      </c>
+      <c r="F28" s="39" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" s="38">
+        <v>28</v>
+      </c>
+      <c r="B29" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="C29" s="36" t="s">
+        <v>220</v>
+      </c>
+      <c r="D29" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="E29" s="36" t="s">
+        <v>221</v>
+      </c>
+      <c r="F29" s="36" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" s="35">
+        <v>29</v>
+      </c>
+      <c r="B30" s="36" t="s">
+        <v>223</v>
+      </c>
+      <c r="C30" s="36" t="s">
+        <v>223</v>
+      </c>
+      <c r="D30" s="36" t="s">
+        <v>224</v>
+      </c>
+      <c r="E30" s="36" t="s">
+        <v>225</v>
+      </c>
+      <c r="F30" s="36" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" s="38">
+        <v>30</v>
+      </c>
+      <c r="B31" s="39" t="s">
+        <v>227</v>
+      </c>
+      <c r="C31" s="39" t="s">
+        <v>227</v>
+      </c>
+      <c r="D31" s="39" t="s">
+        <v>228</v>
+      </c>
+      <c r="E31" s="39" t="s">
+        <v>229</v>
+      </c>
+      <c r="F31" s="39" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" s="35">
+        <v>31</v>
+      </c>
+      <c r="B32" s="36" t="s">
+        <v>231</v>
+      </c>
+      <c r="C32" s="36" t="s">
+        <v>231</v>
+      </c>
+      <c r="D32" s="39" t="s">
+        <v>228</v>
+      </c>
+      <c r="E32" s="39" t="s">
+        <v>232</v>
+      </c>
+      <c r="F32" s="39" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" s="38">
+        <v>32</v>
+      </c>
+      <c r="B33" s="36" t="s">
+        <v>233</v>
+      </c>
+      <c r="C33" s="36" t="s">
+        <v>233</v>
+      </c>
+      <c r="D33" s="39" t="s">
+        <v>228</v>
+      </c>
+      <c r="E33" s="36" t="s">
+        <v>234</v>
+      </c>
+      <c r="F33" s="39" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34" s="38">
+        <v>33</v>
+      </c>
+      <c r="B34" s="39" t="s">
+        <v>236</v>
+      </c>
+      <c r="C34" s="39" t="s">
+        <v>236</v>
+      </c>
+      <c r="D34" s="39" t="s">
+        <v>228</v>
+      </c>
+      <c r="E34" s="39" t="s">
+        <v>237</v>
+      </c>
+      <c r="F34" s="39" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35" s="35">
+        <v>34</v>
+      </c>
+      <c r="B35" s="39" t="s">
+        <v>239</v>
+      </c>
+      <c r="C35" s="39" t="s">
+        <v>239</v>
+      </c>
+      <c r="D35" s="39" t="s">
+        <v>228</v>
+      </c>
+      <c r="E35" s="39" t="s">
+        <v>240</v>
+      </c>
+      <c r="F35" s="39" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36" s="35">
+        <v>35</v>
+      </c>
+      <c r="B36" s="36" t="s">
+        <v>242</v>
+      </c>
+      <c r="C36" s="36" t="s">
+        <v>242</v>
+      </c>
+      <c r="D36" s="36" t="s">
+        <v>243</v>
+      </c>
+      <c r="E36" s="36" t="s">
+        <v>244</v>
+      </c>
+      <c r="F36" s="36" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37" s="35">
+        <v>36</v>
+      </c>
+      <c r="B37" s="36" t="s">
+        <v>245</v>
+      </c>
+      <c r="C37" s="36" t="s">
+        <v>245</v>
+      </c>
+      <c r="D37" s="36" t="s">
+        <v>243</v>
+      </c>
+      <c r="E37" s="36" t="s">
+        <v>246</v>
+      </c>
+      <c r="F37" s="36" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38" s="35">
+        <v>37</v>
+      </c>
+      <c r="B38" s="39" t="s">
+        <v>247</v>
+      </c>
+      <c r="C38" s="39" t="s">
+        <v>248</v>
+      </c>
+      <c r="D38" s="39" t="s">
+        <v>249</v>
+      </c>
+      <c r="E38" s="39" t="s">
+        <v>250</v>
+      </c>
+      <c r="F38" s="39" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A39" s="35">
+        <v>38</v>
+      </c>
+      <c r="B39" s="39" t="s">
+        <v>252</v>
+      </c>
+      <c r="C39" s="39" t="s">
+        <v>253</v>
+      </c>
+      <c r="D39" s="39" t="s">
+        <v>249</v>
+      </c>
+      <c r="E39" s="39" t="s">
+        <v>254</v>
+      </c>
+      <c r="F39" s="39" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A40" s="35">
+        <v>39</v>
+      </c>
+      <c r="B40" s="36" t="s">
+        <v>256</v>
+      </c>
+      <c r="C40" s="36" t="s">
+        <v>257</v>
+      </c>
+      <c r="D40" s="39" t="s">
+        <v>249</v>
+      </c>
+      <c r="E40" s="36" t="s">
+        <v>258</v>
+      </c>
+      <c r="F40" s="36" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A41" s="35">
+        <v>40</v>
+      </c>
+      <c r="B41" s="36" t="s">
+        <v>260</v>
+      </c>
+      <c r="C41" s="36" t="s">
+        <v>260</v>
+      </c>
+      <c r="D41" s="39" t="s">
+        <v>249</v>
+      </c>
+      <c r="E41" s="36" t="s">
+        <v>261</v>
+      </c>
+      <c r="F41" s="36" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A42" s="35">
+        <v>41</v>
+      </c>
+      <c r="B42" s="36" t="s">
+        <v>263</v>
+      </c>
+      <c r="C42" s="36" t="s">
+        <v>264</v>
+      </c>
+      <c r="D42" s="36" t="s">
+        <v>265</v>
+      </c>
+      <c r="E42" s="36" t="s">
+        <v>266</v>
+      </c>
+      <c r="F42" s="36" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A43" s="35">
+        <v>42</v>
+      </c>
+      <c r="B43" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="C43" s="36" t="s">
+        <v>269</v>
+      </c>
+      <c r="D43" s="36" t="s">
+        <v>224</v>
+      </c>
+      <c r="E43" s="36" t="s">
+        <v>270</v>
+      </c>
+      <c r="F43" s="36" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A44" s="38">
+        <v>43</v>
+      </c>
+      <c r="B44" s="39" t="s">
+        <v>272</v>
+      </c>
+      <c r="C44" s="39" t="s">
+        <v>272</v>
+      </c>
+      <c r="D44" s="36" t="s">
+        <v>224</v>
+      </c>
+      <c r="E44" s="39" t="s">
+        <v>273</v>
+      </c>
+      <c r="F44" s="39" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A45" s="38">
+        <v>44</v>
+      </c>
+      <c r="B45" s="39" t="s">
+        <v>275</v>
+      </c>
+      <c r="C45" s="39" t="s">
+        <v>276</v>
+      </c>
+      <c r="D45" s="39" t="s">
+        <v>277</v>
+      </c>
+      <c r="E45" s="39" t="s">
+        <v>278</v>
+      </c>
+      <c r="F45" s="39" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A46" s="35">
+        <v>45</v>
+      </c>
+      <c r="B46" s="36" t="s">
+        <v>280</v>
+      </c>
+      <c r="C46" s="36" t="s">
+        <v>281</v>
+      </c>
+      <c r="D46" s="36" t="s">
+        <v>282</v>
+      </c>
+      <c r="E46" s="36" t="s">
+        <v>283</v>
+      </c>
+      <c r="F46" s="36" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A47" s="35">
+        <v>46</v>
+      </c>
+      <c r="B47" s="36" t="s">
+        <v>285</v>
+      </c>
+      <c r="C47" s="36" t="s">
+        <v>286</v>
+      </c>
+      <c r="D47" s="39" t="s">
+        <v>249</v>
+      </c>
+      <c r="E47" s="36" t="s">
+        <v>287</v>
+      </c>
+      <c r="F47" s="36" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A48" s="35">
+        <v>47</v>
+      </c>
+      <c r="B48" s="36" t="s">
+        <v>289</v>
+      </c>
+      <c r="C48" s="36" t="s">
+        <v>290</v>
+      </c>
+      <c r="D48" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="E48" s="36" t="s">
+        <v>292</v>
+      </c>
+      <c r="F48" s="36" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A49" s="35">
+        <v>48</v>
+      </c>
+      <c r="B49" s="36" t="s">
+        <v>294</v>
+      </c>
+      <c r="C49" s="36" t="s">
+        <v>295</v>
+      </c>
+      <c r="D49" s="36" t="s">
+        <v>296</v>
+      </c>
+      <c r="E49" s="36" t="s">
+        <v>297</v>
+      </c>
+      <c r="F49" s="36" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A50" s="35">
+        <v>49</v>
+      </c>
+      <c r="B50" s="68" t="s">
+        <v>360</v>
+      </c>
+      <c r="C50" s="68" t="s">
+        <v>361</v>
+      </c>
+      <c r="D50" s="39" t="s">
+        <v>207</v>
+      </c>
+      <c r="E50" s="68" t="s">
+        <v>362</v>
+      </c>
+      <c r="F50" s="68" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A51" s="70">
+        <v>50</v>
+      </c>
+      <c r="B51" s="68" t="s">
+        <v>368</v>
+      </c>
+      <c r="C51" s="68" t="s">
+        <v>369</v>
+      </c>
+      <c r="D51" s="68" t="s">
+        <v>370</v>
+      </c>
+      <c r="E51" s="68" t="s">
+        <v>371</v>
+      </c>
+      <c r="F51" s="68" t="s">
+        <v>372</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF1BA8E2-9FD2-4C47-B5D3-EF9907B8F692}">
+  <dimension ref="A1:D52"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.54296875" style="41" customWidth="1"/>
+    <col min="2" max="2" width="38.26953125" customWidth="1"/>
+    <col min="3" max="3" width="14.6328125" customWidth="1"/>
+    <col min="4" max="4" width="13.36328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="32" t="s">
+        <v>299</v>
+      </c>
+      <c r="B1" s="68" t="s">
+        <v>360</v>
+      </c>
+      <c r="C1" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="D1" s="33" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="35">
+        <v>1</v>
+      </c>
+      <c r="B2" s="36" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2" s="42">
+        <v>1194</v>
+      </c>
+      <c r="D2" s="43"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="38">
+        <v>2</v>
+      </c>
+      <c r="B3" s="39" t="s">
+        <v>117</v>
+      </c>
+      <c r="C3" s="43">
+        <v>1938</v>
+      </c>
+      <c r="D3" s="44">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="35">
+        <v>3</v>
+      </c>
+      <c r="B4" s="36" t="s">
+        <v>119</v>
+      </c>
+      <c r="C4" s="42">
+        <v>1591</v>
+      </c>
+      <c r="D4" s="43"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="38">
+        <v>4</v>
+      </c>
+      <c r="B5" s="36" t="s">
+        <v>123</v>
+      </c>
+      <c r="C5" s="42">
+        <v>1973</v>
+      </c>
+      <c r="D5" s="43"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="35">
+        <v>5</v>
+      </c>
+      <c r="B6" s="36" t="s">
+        <v>127</v>
+      </c>
+      <c r="C6" s="42">
+        <v>989</v>
+      </c>
+      <c r="D6" s="43">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="38">
+        <v>6</v>
+      </c>
+      <c r="B7" s="36" t="s">
+        <v>131</v>
+      </c>
+      <c r="C7" s="42">
+        <v>1010</v>
+      </c>
+      <c r="D7" s="43"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="35">
+        <v>7</v>
+      </c>
+      <c r="B8" s="36" t="s">
+        <v>135</v>
+      </c>
+      <c r="C8" s="42">
+        <v>1994</v>
+      </c>
+      <c r="D8" s="43"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="38">
+        <v>8</v>
+      </c>
+      <c r="B9" s="36" t="s">
+        <v>139</v>
+      </c>
+      <c r="C9" s="43">
+        <v>1972</v>
+      </c>
+      <c r="D9" s="43"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="35">
+        <v>9</v>
+      </c>
+      <c r="B10" s="36" t="s">
+        <v>143</v>
+      </c>
+      <c r="C10" s="43">
+        <v>1988</v>
+      </c>
+      <c r="D10" s="43">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="38">
+        <v>10</v>
+      </c>
+      <c r="B11" s="36" t="s">
+        <v>147</v>
+      </c>
+      <c r="C11" s="43">
+        <v>1280</v>
+      </c>
+      <c r="D11" s="43"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="35">
+        <v>11</v>
+      </c>
+      <c r="B12" s="39" t="s">
+        <v>151</v>
+      </c>
+      <c r="C12" s="43">
+        <v>1872</v>
+      </c>
+      <c r="D12" s="44">
+        <v>1878</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="38">
+        <v>12</v>
+      </c>
+      <c r="B13" s="39" t="s">
+        <v>154</v>
+      </c>
+      <c r="C13" s="43">
+        <v>1872</v>
+      </c>
+      <c r="D13" s="44">
+        <v>1879</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="35">
+        <v>13</v>
+      </c>
+      <c r="B14" s="39" t="s">
+        <v>158</v>
+      </c>
+      <c r="C14" s="43">
+        <v>1871</v>
+      </c>
+      <c r="D14" s="44"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="38">
+        <v>14</v>
+      </c>
+      <c r="B15" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="C15" s="43">
+        <v>1872</v>
+      </c>
+      <c r="D15" s="44">
+        <v>1887</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="35">
+        <v>15</v>
+      </c>
+      <c r="B16" s="39" t="s">
+        <v>166</v>
+      </c>
+      <c r="C16" s="43">
+        <v>1888</v>
+      </c>
+      <c r="D16" s="44">
+        <v>1953</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="38">
+        <v>16</v>
+      </c>
+      <c r="B17" s="39" t="s">
+        <v>169</v>
+      </c>
+      <c r="C17" s="43">
+        <v>1374</v>
+      </c>
+      <c r="D17" s="44"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="35">
+        <v>17</v>
+      </c>
+      <c r="B18" s="39" t="s">
+        <v>173</v>
+      </c>
+      <c r="C18" s="43">
+        <v>1827</v>
+      </c>
+      <c r="D18" s="44"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="38">
+        <v>18</v>
+      </c>
+      <c r="B19" s="39" t="s">
+        <v>177</v>
+      </c>
+      <c r="C19" s="43">
+        <v>1872</v>
+      </c>
+      <c r="D19" s="44">
+        <v>1882</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="35">
+        <v>19</v>
+      </c>
+      <c r="B20" s="36" t="s">
+        <v>181</v>
+      </c>
+      <c r="C20" s="43">
+        <v>801</v>
+      </c>
+      <c r="D20" s="43"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="38">
+        <v>20</v>
+      </c>
+      <c r="B21" s="39" t="s">
+        <v>185</v>
+      </c>
+      <c r="C21" s="43">
+        <v>1990</v>
+      </c>
+      <c r="D21" s="43"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="35">
+        <v>21</v>
+      </c>
+      <c r="B22" s="36" t="s">
+        <v>189</v>
+      </c>
+      <c r="C22" s="43">
+        <v>1328</v>
+      </c>
+      <c r="D22" s="43"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="38">
+        <v>22</v>
+      </c>
+      <c r="B23" s="36" t="s">
+        <v>193</v>
+      </c>
+      <c r="C23" s="43">
+        <v>1976</v>
+      </c>
+      <c r="D23" s="43"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="35">
+        <v>23</v>
+      </c>
+      <c r="B24" s="36" t="s">
+        <v>197</v>
+      </c>
+      <c r="C24" s="43">
+        <v>1928</v>
+      </c>
+      <c r="D24" s="43"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="38">
+        <v>24</v>
+      </c>
+      <c r="B25" s="36" t="s">
+        <v>201</v>
+      </c>
+      <c r="C25" s="43">
+        <v>1972</v>
+      </c>
+      <c r="D25" s="43"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" s="35">
+        <v>25</v>
+      </c>
+      <c r="B26" s="39" t="s">
+        <v>205</v>
+      </c>
+      <c r="C26" s="43">
+        <v>1942</v>
+      </c>
+      <c r="D26" s="44"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" s="38">
+        <v>26</v>
+      </c>
+      <c r="B27" s="36" t="s">
+        <v>210</v>
+      </c>
+      <c r="C27" s="43">
+        <v>1724</v>
+      </c>
+      <c r="D27" s="43"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" s="35">
+        <v>27</v>
+      </c>
+      <c r="B28" s="39" t="s">
+        <v>214</v>
+      </c>
+      <c r="C28" s="43">
+        <v>1992</v>
+      </c>
+      <c r="D28" s="44">
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" s="38">
+        <v>28</v>
+      </c>
+      <c r="B29" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="C29" s="43">
+        <v>1998</v>
+      </c>
+      <c r="D29" s="43"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" s="35">
+        <v>29</v>
+      </c>
+      <c r="B30" s="36" t="s">
+        <v>223</v>
+      </c>
+      <c r="C30" s="43">
+        <v>1968</v>
+      </c>
+      <c r="D30" s="43"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" s="38">
+        <v>30</v>
+      </c>
+      <c r="B31" s="39" t="s">
+        <v>227</v>
+      </c>
+      <c r="C31" s="43">
+        <v>1792</v>
+      </c>
+      <c r="D31" s="44"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" s="35">
+        <v>31</v>
+      </c>
+      <c r="B32" s="36" t="s">
+        <v>231</v>
+      </c>
+      <c r="C32" s="43">
+        <v>1906</v>
+      </c>
+      <c r="D32" s="44"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" s="38">
+        <v>32</v>
+      </c>
+      <c r="B33" s="36" t="s">
+        <v>233</v>
+      </c>
+      <c r="C33" s="43">
+        <v>1854</v>
+      </c>
+      <c r="D33" s="43"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" s="38">
+        <v>33</v>
+      </c>
+      <c r="B34" s="39" t="s">
+        <v>236</v>
+      </c>
+      <c r="C34" s="43">
+        <v>1835</v>
+      </c>
+      <c r="D34" s="44">
+        <v>1942</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" s="35">
+        <v>34</v>
+      </c>
+      <c r="B35" s="39" t="s">
+        <v>239</v>
+      </c>
+      <c r="C35" s="43">
+        <v>1973</v>
+      </c>
+      <c r="D35" s="44"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" s="35">
+        <v>35</v>
+      </c>
+      <c r="B36" s="36" t="s">
+        <v>242</v>
+      </c>
+      <c r="C36" s="43">
+        <v>1908</v>
+      </c>
+      <c r="D36" s="43"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" s="35">
+        <v>36</v>
+      </c>
+      <c r="B37" s="36" t="s">
+        <v>245</v>
+      </c>
+      <c r="C37" s="43">
+        <v>1976</v>
+      </c>
+      <c r="D37" s="43"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" s="35">
+        <v>37</v>
+      </c>
+      <c r="B38" s="39" t="s">
+        <v>247</v>
+      </c>
+      <c r="C38" s="43">
+        <v>1803</v>
+      </c>
+      <c r="D38" s="44"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" s="35">
+        <v>38</v>
+      </c>
+      <c r="B39" s="39" t="s">
+        <v>252</v>
+      </c>
+      <c r="C39" s="43">
+        <v>1829</v>
+      </c>
+      <c r="D39" s="44"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" s="35">
+        <v>39</v>
+      </c>
+      <c r="B40" s="36" t="s">
+        <v>256</v>
+      </c>
+      <c r="C40" s="43">
+        <v>1757</v>
+      </c>
+      <c r="D40" s="43"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" s="35">
+        <v>40</v>
+      </c>
+      <c r="B41" s="36" t="s">
+        <v>260</v>
+      </c>
+      <c r="C41" s="43">
+        <v>1640</v>
+      </c>
+      <c r="D41" s="43">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" s="35">
+        <v>41</v>
+      </c>
+      <c r="B42" s="36" t="s">
+        <v>263</v>
+      </c>
+      <c r="C42" s="43">
+        <v>1992</v>
+      </c>
+      <c r="D42" s="43"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" s="35">
+        <v>42</v>
+      </c>
+      <c r="B43" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="C43" s="43">
+        <v>1850</v>
+      </c>
+      <c r="D43" s="43">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" s="38">
+        <v>43</v>
+      </c>
+      <c r="B44" s="39" t="s">
+        <v>272</v>
+      </c>
+      <c r="C44" s="43">
+        <v>1860</v>
+      </c>
+      <c r="D44" s="43">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" s="38">
+        <v>44</v>
+      </c>
+      <c r="B45" s="39" t="s">
+        <v>275</v>
+      </c>
+      <c r="C45" s="43">
+        <v>1890</v>
+      </c>
+      <c r="D45" s="44">
+        <v>1902</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" s="38">
+        <v>44</v>
+      </c>
+      <c r="B46" s="39" t="s">
+        <v>275</v>
+      </c>
+      <c r="C46" s="43">
+        <v>1923</v>
+      </c>
+      <c r="D46" s="43"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" s="35">
+        <v>45</v>
+      </c>
+      <c r="B47" s="36" t="s">
+        <v>280</v>
+      </c>
+      <c r="C47" s="43">
+        <v>1943</v>
+      </c>
+      <c r="D47" s="43"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48" s="35">
+        <v>46</v>
+      </c>
+      <c r="B48" s="36" t="s">
+        <v>302</v>
+      </c>
+      <c r="C48" s="43">
+        <v>1988</v>
+      </c>
+      <c r="D48" s="43"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" s="35">
+        <v>47</v>
+      </c>
+      <c r="B49" s="36" t="s">
+        <v>289</v>
+      </c>
+      <c r="C49" s="43">
+        <v>1951</v>
+      </c>
+      <c r="D49" s="43"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" s="38">
+        <v>48</v>
+      </c>
+      <c r="B50" s="36" t="s">
+        <v>294</v>
+      </c>
+      <c r="C50" s="43">
+        <v>1535</v>
+      </c>
+      <c r="D50" s="43"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" s="35">
+        <v>49</v>
+      </c>
+      <c r="B51" s="68" t="s">
+        <v>360</v>
+      </c>
+      <c r="C51" s="69">
+        <v>1725</v>
+      </c>
+      <c r="D51" s="69">
+        <v>1876</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" s="38">
+        <v>50</v>
+      </c>
+      <c r="B52" s="68" t="s">
+        <v>368</v>
+      </c>
+      <c r="C52" s="69">
+        <v>1952</v>
+      </c>
+      <c r="D52" s="69"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0041FEF0-BF6F-4667-AFBD-1C23A1866795}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.7265625" customWidth="1"/>
+    <col min="2" max="2" width="17.453125" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="37.90625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="9">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="9">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="9">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="9">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="9">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="9">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8265AFD9-D9EB-4B75-B60D-6B7F7204230D}">
+  <dimension ref="A1:B29"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="26.36328125" customWidth="1"/>
+    <col min="2" max="2" width="31.36328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="4"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="4"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="4"/>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="4"/>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="4"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="4"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="4"/>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="4"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="4"/>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="4"/>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="4"/>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="4"/>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="4"/>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="4"/>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" s="4"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" s="4"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="4"/>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="4"/>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" s="4"/>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" s="4"/>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="4"/>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="4"/>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24" s="4"/>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" s="4"/>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" s="4"/>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" s="4"/>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B28" s="4"/>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="B29" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Info/Additional_information.xlsx
+++ b/Info/Additional_information.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA4E6752-4C0F-4F21-9A2C-B49E2BCDB4F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05FFB623-752F-4C88-AA5E-51EE9830B29B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="495">
   <si>
     <t>good quality (UNC for UNC collection; UNC and XF for XF collection)</t>
   </si>
@@ -1294,23 +1294,281 @@
     <t>Album hardcoded link</t>
   </si>
   <si>
-    <t>OP</t>
-  </si>
-  <si>
     <t>FB</t>
   </si>
   <si>
     <t>Fufalco Bogdan list format</t>
   </si>
   <si>
-    <t>A0001-GR-BL</t>
+    <t>СНГ и Бывший СССР</t>
+  </si>
+  <si>
+    <t>Америка и Океания</t>
+  </si>
+  <si>
+    <t>Азия и Восток</t>
+  </si>
+  <si>
+    <t>Album Content</t>
+  </si>
+  <si>
+    <t>OA</t>
+  </si>
+  <si>
+    <t>A0001-GD-BK</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A0001-GD-BK.html</t>
+  </si>
+  <si>
+    <t>Flags (for links)</t>
+  </si>
+  <si>
+    <t>🇷🇺</t>
+  </si>
+  <si>
+    <t>🇧🇾</t>
+  </si>
+  <si>
+    <t>🇺🇦</t>
+  </si>
+  <si>
+    <t>🇰🇿</t>
+  </si>
+  <si>
+    <t>🇺🇿</t>
+  </si>
+  <si>
+    <t>🇦🇲</t>
+  </si>
+  <si>
+    <t>🇬🇪</t>
+  </si>
+  <si>
+    <t>🇦🇹</t>
+  </si>
+  <si>
+    <t>🇧🇪</t>
+  </si>
+  <si>
+    <t>🇩🇪</t>
+  </si>
+  <si>
+    <t>🇬🇷</t>
+  </si>
+  <si>
+    <t>🇮🇪</t>
+  </si>
+  <si>
+    <t>🇪🇸</t>
+  </si>
+  <si>
+    <t>🇮🇹</t>
+  </si>
+  <si>
+    <t>🇨🇾</t>
+  </si>
+  <si>
+    <t>🇱🇻</t>
+  </si>
+  <si>
+    <t>🇱🇹</t>
+  </si>
+  <si>
+    <t>🇱🇺</t>
+  </si>
+  <si>
+    <t>🇲🇹</t>
+  </si>
+  <si>
+    <t>🇳🇱</t>
+  </si>
+  <si>
+    <t>🇵🇹</t>
+  </si>
+  <si>
+    <t>🇸🇰</t>
+  </si>
+  <si>
+    <t>🇸🇮</t>
+  </si>
+  <si>
+    <t>🇫🇮</t>
+  </si>
+  <si>
+    <t>🇫🇷</t>
+  </si>
+  <si>
+    <t>🇭🇷</t>
+  </si>
+  <si>
+    <t>🇪🇪</t>
+  </si>
+  <si>
+    <t>🇪🇺</t>
+  </si>
+  <si>
+    <t>🇺🇸</t>
+  </si>
+  <si>
+    <t>🇨🇦</t>
+  </si>
+  <si>
+    <t>🇲🇽</t>
+  </si>
+  <si>
+    <t>🇧🇷</t>
+  </si>
+  <si>
+    <t>🇦🇺</t>
+  </si>
+  <si>
+    <t>🇨🇳</t>
+  </si>
+  <si>
+    <t>🇯🇵</t>
+  </si>
+  <si>
+    <t>🇮🇳</t>
+  </si>
+  <si>
+    <t>🇹🇷</t>
+  </si>
+  <si>
+    <t>🇮🇱</t>
+  </si>
+  <si>
+    <t>Россия / СССР</t>
+  </si>
+  <si>
+    <t>Беларусь</t>
+  </si>
+  <si>
+    <t>Украина</t>
+  </si>
+  <si>
+    <t>Казахстан</t>
+  </si>
+  <si>
+    <t>Узбекистан</t>
+  </si>
+  <si>
+    <t>Армения</t>
+  </si>
+  <si>
+    <t>Грузия</t>
+  </si>
+  <si>
+    <t>Австрия (Austria)</t>
+  </si>
+  <si>
+    <t>Бельгия (Belgium)</t>
+  </si>
+  <si>
+    <t>Германия (Germany)</t>
+  </si>
+  <si>
+    <t>Греция (Greece)</t>
+  </si>
+  <si>
+    <t>Ирландия (Ireland)</t>
+  </si>
+  <si>
+    <t>Испания (Spain)</t>
+  </si>
+  <si>
+    <t>Италия (Italy)</t>
+  </si>
+  <si>
+    <t>Кипр (Cyprus)</t>
+  </si>
+  <si>
+    <t>Латвия (Latvia)</t>
+  </si>
+  <si>
+    <t>Литва (Lithuania)</t>
+  </si>
+  <si>
+    <t>Люксембург (Luxembourg)</t>
+  </si>
+  <si>
+    <t>Мальта (Malta)</t>
+  </si>
+  <si>
+    <t>Нидерланды (Netherlands)</t>
+  </si>
+  <si>
+    <t>Португалия (Portugal)</t>
+  </si>
+  <si>
+    <t>Словакия (Slovakia)</t>
+  </si>
+  <si>
+    <t>Словения (Slovenia)</t>
+  </si>
+  <si>
+    <t>Финляндия (Finland)</t>
+  </si>
+  <si>
+    <t>Франция (France)</t>
+  </si>
+  <si>
+    <t>Хорватия (Croatia)</t>
+  </si>
+  <si>
+    <t>Эстония (Estonia)</t>
+  </si>
+  <si>
+    <t>Евросоюз (Общий раздел)</t>
+  </si>
+  <si>
+    <t>США</t>
+  </si>
+  <si>
+    <t>Канада</t>
+  </si>
+  <si>
+    <t>Мексика</t>
+  </si>
+  <si>
+    <t>Бразилия</t>
+  </si>
+  <si>
+    <t>Австралия</t>
+  </si>
+  <si>
+    <t>Китай</t>
+  </si>
+  <si>
+    <t>Япония</t>
+  </si>
+  <si>
+    <t>Индия</t>
+  </si>
+  <si>
+    <t>Турция</t>
+  </si>
+  <si>
+    <t>Израиль</t>
+  </si>
+  <si>
+    <t>Европа</t>
+  </si>
+  <si>
+    <t>2 Euro album (part 1)</t>
+  </si>
+  <si>
+    <t>Album Content (ru)</t>
+  </si>
+  <si>
+    <t>Альбом юбилейных 2 евро (часть 1)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1432,6 +1690,24 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="22">
@@ -1871,7 +2147,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2084,6 +2360,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="20" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2132,13 +2409,74 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="34">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2623,54 +2961,6 @@
         </horizontal>
       </border>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -2693,23 +2983,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>539750</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>82550</xdr:rowOff>
+      <xdr:rowOff>139700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>488950</xdr:colOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>45570</xdr:rowOff>
+      <xdr:rowOff>102720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Рисунок 1">
+        <xdr:cNvPr id="3" name="Рисунок 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{416ACAFA-E733-4429-ADBA-6168899E9B07}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{320DA919-34E4-48A1-9AE7-B1B277A4600E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2725,7 +3015,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7048500" y="635000"/>
+          <a:off x="10172700" y="742950"/>
           <a:ext cx="8375650" cy="4566770"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2751,7 +3041,7 @@
       <xdr:col>20</xdr:col>
       <xdr:colOff>431800</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>147170</xdr:rowOff>
+      <xdr:rowOff>121770</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2788,28 +3078,28 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{973D7237-72C7-453E-A0E1-526C93326B28}" name="Таблица3" displayName="Таблица3" ref="A1:F51" totalsRowShown="0" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{973D7237-72C7-453E-A0E1-526C93326B28}" name="Таблица3" displayName="Таблица3" ref="A1:F51" totalsRowShown="0" headerRowDxfId="33" dataDxfId="31" headerRowBorderDxfId="32" tableBorderDxfId="30" totalsRowBorderDxfId="29">
   <autoFilter ref="A1:F51" xr:uid="{A2D8FA3D-4024-4365-BE1D-F93D0AF2D426}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{12C2DF0B-47FA-46A4-8424-55A1488EF88B}" name="ID" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{EB0B36CE-168D-429E-896D-DBA54794224F}" name="Name_Eng" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{6C3A2CE8-252E-4C52-985B-8CDDFD9FA0C7}" name="OfficialMintName_Native" dataDxfId="20"/>
-    <tableColumn id="8" xr3:uid="{DA5871DC-2EDB-49C0-953E-EC0F70288E21}" name="Country" dataDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{FCD85F85-A94E-4BBE-9D3B-2B7494638375}" name="Mint_City" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{E5141978-CA91-4DE9-86F1-8A8AFA716534}" name="Alias" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{12C2DF0B-47FA-46A4-8424-55A1488EF88B}" name="ID" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{EB0B36CE-168D-429E-896D-DBA54794224F}" name="Name_Eng" dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{6C3A2CE8-252E-4C52-985B-8CDDFD9FA0C7}" name="OfficialMintName_Native" dataDxfId="26"/>
+    <tableColumn id="8" xr3:uid="{DA5871DC-2EDB-49C0-953E-EC0F70288E21}" name="Country" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{FCD85F85-A94E-4BBE-9D3B-2B7494638375}" name="Mint_City" dataDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{E5141978-CA91-4DE9-86F1-8A8AFA716534}" name="Alias" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9D0F8E3D-96B1-4DB8-B1A6-8DD6B84F3693}" name="Таблица35" displayName="Таблица35" ref="A1:D52" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13" totalsRowBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9D0F8E3D-96B1-4DB8-B1A6-8DD6B84F3693}" name="Таблица35" displayName="Таблица35" ref="A1:D52" totalsRowShown="0" headerRowDxfId="22" dataDxfId="20" headerRowBorderDxfId="21" tableBorderDxfId="19" totalsRowBorderDxfId="18">
   <autoFilter ref="A1:D52" xr:uid="{A2D8FA3D-4024-4365-BE1D-F93D0AF2D426}"/>
   <tableColumns count="4">
-    <tableColumn id="4" xr3:uid="{74AFB32D-7AAA-46BE-8174-ED698BB4613E}" name="Mint_id" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{523D65CD-0F56-441F-90B5-E46A9B14F0D0}" name="Ekaterinburg Mint" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{1AAB7352-E935-4EC6-A0D1-3EDC5D0BC93C}" name="Year_of_start" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{5FF15381-476A-4F88-B93A-6452F2830A0A}" name="Year_of_end" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{74AFB32D-7AAA-46BE-8174-ED698BB4613E}" name="Mint_id" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{523D65CD-0F56-441F-90B5-E46A9B14F0D0}" name="Ekaterinburg Mint" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{1AAB7352-E935-4EC6-A0D1-3EDC5D0BC93C}" name="Year_of_start" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{5FF15381-476A-4F88-B93A-6452F2830A0A}" name="Year_of_end" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2823,25 +3113,25 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{8354E581-3B48-4762-81A7-EA76E36C4BB5}" name="№" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{1F45DC85-8ECA-45FE-BF45-E528619CEE0E}" name="Links:" dataDxfId="6" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{3FAE616B-3296-4770-9E56-8A824991EECA}" name="Description:" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{8354E581-3B48-4762-81A7-EA76E36C4BB5}" name="№" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{1F45DC85-8ECA-45FE-BF45-E528619CEE0E}" name="Links:" dataDxfId="12" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{3FAE616B-3296-4770-9E56-8A824991EECA}" name="Description:" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D0DCC88A-2D36-4004-A694-FC0C0F0C3396}" name="Таблица2" displayName="Таблица2" ref="A1:C16" totalsRowShown="0" headerRowBorderDxfId="4" tableBorderDxfId="3" totalsRowBorderDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D0DCC88A-2D36-4004-A694-FC0C0F0C3396}" name="Таблица2" displayName="Таблица2" ref="A1:C16" totalsRowShown="0" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
   <autoFilter ref="A1:C16" xr:uid="{00000000-0009-0000-0100-000002000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{28358E6A-6F3A-468C-9E1C-880A34D9BECE}" name="№" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{28358E6A-6F3A-468C-9E1C-880A34D9BECE}" name="№" dataDxfId="7"/>
     <tableColumn id="2" xr3:uid="{DD0AD5C8-324B-4DA7-B39F-B2DB3EF91222}" name="Links:"/>
-    <tableColumn id="3" xr3:uid="{FC8A6018-CA7E-4C73-9B21-B272B55FA8C1}" name="Description:" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{FC8A6018-CA7E-4C73-9B21-B272B55FA8C1}" name="Description:" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -3232,12 +3522,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C7:C8">
-    <cfRule type="containsText" dxfId="33" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C7))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6">
-    <cfRule type="containsText" dxfId="32" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="4" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C6))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3254,7 +3544,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2">
-    <cfRule type="containsText" dxfId="31" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="3" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C2))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3271,7 +3561,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4">
-    <cfRule type="containsText" dxfId="30" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="2" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C4))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3288,7 +3578,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C5">
-    <cfRule type="containsText" dxfId="29" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="1" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C5))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3305,7 +3595,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3">
-    <cfRule type="containsText" dxfId="28" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C3))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -3782,10 +4072,10 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" s="84">
+      <c r="A2" s="85">
         <v>1</v>
       </c>
-      <c r="B2" s="92">
+      <c r="B2" s="93">
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
@@ -3802,8 +4092,8 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" s="85"/>
-      <c r="B3" s="92"/>
+      <c r="A3" s="86"/>
+      <c r="B3" s="93"/>
       <c r="C3" s="4" t="s">
         <v>65</v>
       </c>
@@ -3818,8 +4108,8 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" s="86"/>
-      <c r="B4" s="93">
+      <c r="A4" s="87"/>
+      <c r="B4" s="94">
         <v>2</v>
       </c>
       <c r="C4" s="4" t="s">
@@ -3836,14 +4126,14 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" s="86"/>
-      <c r="B5" s="93"/>
+      <c r="A5" s="87"/>
+      <c r="B5" s="94"/>
       <c r="C5" s="4" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6" s="86"/>
+      <c r="A6" s="87"/>
       <c r="B6" s="15">
         <v>3</v>
       </c>
@@ -3852,7 +4142,7 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" s="86"/>
+      <c r="A7" s="87"/>
       <c r="B7" s="16" t="s">
         <v>90</v>
       </c>
@@ -3861,8 +4151,8 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" s="86"/>
-      <c r="B8" s="94">
+      <c r="A8" s="87"/>
+      <c r="B8" s="95">
         <v>6</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -3870,14 +4160,14 @@
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="86"/>
-      <c r="B9" s="95"/>
+      <c r="A9" s="87"/>
+      <c r="B9" s="96"/>
       <c r="C9" s="4" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A10" s="86"/>
+      <c r="A10" s="87"/>
       <c r="B10" s="17">
         <v>7</v>
       </c>
@@ -3886,14 +4176,14 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="86"/>
+      <c r="A11" s="87"/>
       <c r="B11" s="24"/>
       <c r="C11" s="4" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="86"/>
+      <c r="A12" s="87"/>
       <c r="B12" s="18">
         <v>8</v>
       </c>
@@ -3902,7 +4192,7 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" s="87"/>
+      <c r="A13" s="88"/>
       <c r="B13" s="25" t="s">
         <v>78</v>
       </c>
@@ -3911,7 +4201,7 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="88"/>
+      <c r="A14" s="89"/>
       <c r="B14" s="26" t="s">
         <v>91</v>
       </c>
@@ -3920,7 +4210,7 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="14.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="89">
+      <c r="A15" s="90">
         <v>2</v>
       </c>
       <c r="B15" s="19" t="s">
@@ -3931,7 +4221,7 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="90"/>
+      <c r="A16" s="91"/>
       <c r="B16" s="20" t="s">
         <v>365</v>
       </c>
@@ -3940,7 +4230,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="90"/>
+      <c r="A17" s="91"/>
       <c r="B17" s="21" t="s">
         <v>366</v>
       </c>
@@ -3949,7 +4239,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="91"/>
+      <c r="A18" s="92"/>
       <c r="B18" s="22" t="s">
         <v>92</v>
       </c>
@@ -3958,7 +4248,7 @@
       </c>
     </row>
     <row r="19" spans="1:3" ht="14.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="78">
+      <c r="A19" s="79">
         <v>3</v>
       </c>
       <c r="B19" s="23" t="s">
@@ -3969,7 +4259,7 @@
       </c>
     </row>
     <row r="20" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="79"/>
+      <c r="A20" s="80"/>
       <c r="B20" s="27" t="s">
         <v>93</v>
       </c>
@@ -3978,7 +4268,7 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="80"/>
+      <c r="A21" s="81"/>
       <c r="B21" s="28" t="s">
         <v>95</v>
       </c>
@@ -3987,7 +4277,7 @@
       </c>
     </row>
     <row r="22" spans="1:3" ht="14.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="81">
+      <c r="A22" s="82">
         <v>4</v>
       </c>
       <c r="B22" s="19" t="s">
@@ -3998,7 +4288,7 @@
       </c>
     </row>
     <row r="23" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="82"/>
+      <c r="A23" s="83"/>
       <c r="B23" s="20" t="s">
         <v>98</v>
       </c>
@@ -4007,7 +4297,7 @@
       </c>
     </row>
     <row r="24" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="82"/>
+      <c r="A24" s="83"/>
       <c r="B24" s="21" t="s">
         <v>100</v>
       </c>
@@ -4016,7 +4306,7 @@
       </c>
     </row>
     <row r="25" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="82"/>
+      <c r="A25" s="83"/>
       <c r="B25" s="16" t="s">
         <v>102</v>
       </c>
@@ -4025,7 +4315,7 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" s="82"/>
+      <c r="A26" s="83"/>
       <c r="B26" s="29" t="s">
         <v>104</v>
       </c>
@@ -4034,7 +4324,7 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" s="82"/>
+      <c r="A27" s="83"/>
       <c r="B27" s="30" t="s">
         <v>106</v>
       </c>
@@ -4043,7 +4333,7 @@
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" s="82"/>
+      <c r="A28" s="83"/>
       <c r="B28" s="18">
         <v>8</v>
       </c>
@@ -4052,7 +4342,7 @@
       </c>
     </row>
     <row r="29" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="83"/>
+      <c r="A29" s="84"/>
       <c r="B29" s="31" t="s">
         <v>78</v>
       </c>
@@ -4082,45 +4372,69 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DC835FD-69FE-4DBC-957F-9A46CA05517E}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.26953125" customWidth="1"/>
-    <col min="2" max="2" width="30.81640625" customWidth="1"/>
+    <col min="2" max="2" width="22.7265625" customWidth="1"/>
+    <col min="3" max="3" width="33.54296875" customWidth="1"/>
+    <col min="4" max="4" width="84.6328125" customWidth="1"/>
+    <col min="5" max="5" width="8.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="96" t="s">
+    <row r="1" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A1" s="78" t="s">
         <v>403</v>
       </c>
-      <c r="B1" s="96" t="s">
+      <c r="B1" s="78" t="s">
+        <v>410</v>
+      </c>
+      <c r="C1" s="78" t="s">
+        <v>493</v>
+      </c>
+      <c r="D1" s="78" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>408</v>
+        <v>412</v>
+      </c>
+      <c r="B2" t="s">
+        <v>492</v>
+      </c>
+      <c r="C2" t="s">
+        <v>494</v>
+      </c>
+      <c r="D2" s="98" t="s">
+        <v>413</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{D827BEB2-1C88-4D17-BA13-D6C7BE5F2B8D}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{866E9A5E-386D-439E-AA25-CB46A31C625C}">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:Y45"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.453125" style="77" customWidth="1"/>
     <col min="2" max="2" width="24.7265625" customWidth="1"/>
     <col min="3" max="3" width="15.453125" style="77" customWidth="1"/>
     <col min="4" max="4" width="15.453125" customWidth="1"/>
+    <col min="23" max="23" width="20.36328125" customWidth="1"/>
+    <col min="24" max="24" width="6.7265625" customWidth="1"/>
+    <col min="25" max="25" width="26.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="36.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:25" ht="36.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="76" t="s">
         <v>399</v>
       </c>
@@ -4133,10 +4447,15 @@
       <c r="D1" s="72" t="s">
         <v>402</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="W1" s="102" t="s">
+        <v>414</v>
+      </c>
+      <c r="X1" s="102"/>
+      <c r="Y1" s="102"/>
+    </row>
+    <row r="2" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="77" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="B2" s="75" t="s">
         <v>397</v>
@@ -4147,10 +4466,13 @@
       <c r="D2" t="s">
         <v>388</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="W2" s="101" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3" s="77" t="s">
-        <v>142</v>
+        <v>384</v>
       </c>
       <c r="B3" s="75" t="s">
         <v>398</v>
@@ -4161,13 +4483,19 @@
       <c r="D3" t="s">
         <v>389</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="X3" s="97" t="s">
+        <v>415</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4" s="77" t="s">
+        <v>405</v>
+      </c>
+      <c r="B4" t="s">
         <v>406</v>
-      </c>
-      <c r="B4" t="s">
-        <v>407</v>
       </c>
       <c r="C4" s="73" t="s">
         <v>377</v>
@@ -4175,96 +4503,391 @@
       <c r="D4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="X4" s="97" t="s">
+        <v>416</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="C5" s="73" t="s">
         <v>142</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="X5" s="97" t="s">
+        <v>417</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
       <c r="C6" s="73" t="s">
         <v>378</v>
       </c>
       <c r="D6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="X6" s="97" t="s">
+        <v>418</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
       <c r="C7" s="73" t="s">
         <v>379</v>
       </c>
       <c r="D7" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="X7" s="97" t="s">
+        <v>419</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
       <c r="C8" s="73" t="s">
         <v>380</v>
       </c>
       <c r="D8" t="s">
         <v>391</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="X8" s="97" t="s">
+        <v>420</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
       <c r="C9" s="73" t="s">
         <v>381</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="X9" s="97" t="s">
+        <v>421</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C10" s="73" t="s">
         <v>382</v>
       </c>
       <c r="D10" t="s">
         <v>392</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="W10" s="100" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
       <c r="C11" s="73" t="s">
         <v>383</v>
       </c>
       <c r="D11" t="s">
         <v>393</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="X11" s="97" t="s">
+        <v>422</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
       <c r="C12" s="73" t="s">
         <v>384</v>
       </c>
       <c r="D12" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="X12" s="97" t="s">
+        <v>423</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
       <c r="C13" s="73" t="s">
         <v>385</v>
       </c>
       <c r="D13" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="X13" s="97" t="s">
+        <v>424</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
       <c r="C14" s="73" t="s">
         <v>386</v>
       </c>
       <c r="D14" t="s">
         <v>396</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="X14" s="97" t="s">
+        <v>425</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
       <c r="C15" s="73" t="s">
         <v>387</v>
       </c>
       <c r="D15" t="s">
         <v>373</v>
       </c>
+      <c r="X15" s="97" t="s">
+        <v>426</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="X16" s="97" t="s">
+        <v>427</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="17" spans="23:25" x14ac:dyDescent="0.35">
+      <c r="X17" s="97" t="s">
+        <v>428</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="18" spans="23:25" x14ac:dyDescent="0.35">
+      <c r="X18" s="97" t="s">
+        <v>429</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="19" spans="23:25" x14ac:dyDescent="0.35">
+      <c r="X19" s="97" t="s">
+        <v>430</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="20" spans="23:25" x14ac:dyDescent="0.35">
+      <c r="X20" s="97" t="s">
+        <v>431</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="21" spans="23:25" x14ac:dyDescent="0.35">
+      <c r="X21" s="97" t="s">
+        <v>432</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="22" spans="23:25" x14ac:dyDescent="0.35">
+      <c r="X22" s="97" t="s">
+        <v>433</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="23" spans="23:25" x14ac:dyDescent="0.35">
+      <c r="X23" s="97" t="s">
+        <v>434</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="24" spans="23:25" x14ac:dyDescent="0.35">
+      <c r="X24" s="97" t="s">
+        <v>435</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="25" spans="23:25" x14ac:dyDescent="0.35">
+      <c r="X25" s="97" t="s">
+        <v>436</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="26" spans="23:25" x14ac:dyDescent="0.35">
+      <c r="X26" s="97" t="s">
+        <v>437</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="27" spans="23:25" x14ac:dyDescent="0.35">
+      <c r="X27" s="97" t="s">
+        <v>438</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="28" spans="23:25" x14ac:dyDescent="0.35">
+      <c r="X28" s="97" t="s">
+        <v>439</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="29" spans="23:25" x14ac:dyDescent="0.35">
+      <c r="X29" s="97" t="s">
+        <v>440</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="30" spans="23:25" x14ac:dyDescent="0.35">
+      <c r="X30" s="97" t="s">
+        <v>441</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="31" spans="23:25" x14ac:dyDescent="0.35">
+      <c r="X31" s="97" t="s">
+        <v>442</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="32" spans="23:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="W32" s="100" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="33" spans="14:25" x14ac:dyDescent="0.35">
+      <c r="X33" s="97" t="s">
+        <v>443</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="34" spans="14:25" x14ac:dyDescent="0.35">
+      <c r="X34" s="97" t="s">
+        <v>444</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="35" spans="14:25" x14ac:dyDescent="0.35">
+      <c r="X35" s="97" t="s">
+        <v>445</v>
+      </c>
+      <c r="Y35" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="36" spans="14:25" x14ac:dyDescent="0.35">
+      <c r="X36" s="97" t="s">
+        <v>446</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="37" spans="14:25" x14ac:dyDescent="0.35">
+      <c r="X37" s="97" t="s">
+        <v>447</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="38" spans="14:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="W38" s="100" t="s">
+        <v>409</v>
+      </c>
+      <c r="X38" s="99"/>
+    </row>
+    <row r="39" spans="14:25" x14ac:dyDescent="0.35">
+      <c r="N39" s="97"/>
+      <c r="X39" s="97" t="s">
+        <v>448</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="40" spans="14:25" x14ac:dyDescent="0.35">
+      <c r="X40" s="97" t="s">
+        <v>449</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="41" spans="14:25" x14ac:dyDescent="0.35">
+      <c r="X41" s="97" t="s">
+        <v>450</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="42" spans="14:25" x14ac:dyDescent="0.35">
+      <c r="X42" s="97" t="s">
+        <v>451</v>
+      </c>
+      <c r="Y42" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="43" spans="14:25" x14ac:dyDescent="0.35">
+      <c r="X43" s="97" t="s">
+        <v>452</v>
+      </c>
+      <c r="Y43" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="45" spans="14:25" x14ac:dyDescent="0.35">
+      <c r="N45" s="97"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="W1:Y1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>

--- a/Info/Additional_information.xlsx
+++ b/Info/Additional_information.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05FFB623-752F-4C88-AA5E-51EE9830B29B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{720DBF33-0378-4F90-B838-837903359CB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2361,6 +2361,17 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="20" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2409,17 +2420,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2429,54 +2429,6 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="34">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2961,6 +2913,54 @@
         </horizontal>
       </border>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -3078,28 +3078,28 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{973D7237-72C7-453E-A0E1-526C93326B28}" name="Таблица3" displayName="Таблица3" ref="A1:F51" totalsRowShown="0" headerRowDxfId="33" dataDxfId="31" headerRowBorderDxfId="32" tableBorderDxfId="30" totalsRowBorderDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{973D7237-72C7-453E-A0E1-526C93326B28}" name="Таблица3" displayName="Таблица3" ref="A1:F51" totalsRowShown="0" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
   <autoFilter ref="A1:F51" xr:uid="{A2D8FA3D-4024-4365-BE1D-F93D0AF2D426}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{12C2DF0B-47FA-46A4-8424-55A1488EF88B}" name="ID" dataDxfId="28"/>
-    <tableColumn id="2" xr3:uid="{EB0B36CE-168D-429E-896D-DBA54794224F}" name="Name_Eng" dataDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{6C3A2CE8-252E-4C52-985B-8CDDFD9FA0C7}" name="OfficialMintName_Native" dataDxfId="26"/>
-    <tableColumn id="8" xr3:uid="{DA5871DC-2EDB-49C0-953E-EC0F70288E21}" name="Country" dataDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{FCD85F85-A94E-4BBE-9D3B-2B7494638375}" name="Mint_City" dataDxfId="24"/>
-    <tableColumn id="6" xr3:uid="{E5141978-CA91-4DE9-86F1-8A8AFA716534}" name="Alias" dataDxfId="23"/>
+    <tableColumn id="1" xr3:uid="{12C2DF0B-47FA-46A4-8424-55A1488EF88B}" name="ID" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{EB0B36CE-168D-429E-896D-DBA54794224F}" name="Name_Eng" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{6C3A2CE8-252E-4C52-985B-8CDDFD9FA0C7}" name="OfficialMintName_Native" dataDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{DA5871DC-2EDB-49C0-953E-EC0F70288E21}" name="Country" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{FCD85F85-A94E-4BBE-9D3B-2B7494638375}" name="Mint_City" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{E5141978-CA91-4DE9-86F1-8A8AFA716534}" name="Alias" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9D0F8E3D-96B1-4DB8-B1A6-8DD6B84F3693}" name="Таблица35" displayName="Таблица35" ref="A1:D52" totalsRowShown="0" headerRowDxfId="22" dataDxfId="20" headerRowBorderDxfId="21" tableBorderDxfId="19" totalsRowBorderDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9D0F8E3D-96B1-4DB8-B1A6-8DD6B84F3693}" name="Таблица35" displayName="Таблица35" ref="A1:D52" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13" totalsRowBorderDxfId="12">
   <autoFilter ref="A1:D52" xr:uid="{A2D8FA3D-4024-4365-BE1D-F93D0AF2D426}"/>
   <tableColumns count="4">
-    <tableColumn id="4" xr3:uid="{74AFB32D-7AAA-46BE-8174-ED698BB4613E}" name="Mint_id" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{523D65CD-0F56-441F-90B5-E46A9B14F0D0}" name="Ekaterinburg Mint" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{1AAB7352-E935-4EC6-A0D1-3EDC5D0BC93C}" name="Year_of_start" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{5FF15381-476A-4F88-B93A-6452F2830A0A}" name="Year_of_end" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{74AFB32D-7AAA-46BE-8174-ED698BB4613E}" name="Mint_id" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{523D65CD-0F56-441F-90B5-E46A9B14F0D0}" name="Ekaterinburg Mint" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{1AAB7352-E935-4EC6-A0D1-3EDC5D0BC93C}" name="Year_of_start" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{5FF15381-476A-4F88-B93A-6452F2830A0A}" name="Year_of_end" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3113,25 +3113,25 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{8354E581-3B48-4762-81A7-EA76E36C4BB5}" name="№" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{1F45DC85-8ECA-45FE-BF45-E528619CEE0E}" name="Links:" dataDxfId="12" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{3FAE616B-3296-4770-9E56-8A824991EECA}" name="Description:" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{8354E581-3B48-4762-81A7-EA76E36C4BB5}" name="№" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{1F45DC85-8ECA-45FE-BF45-E528619CEE0E}" name="Links:" dataDxfId="6" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{3FAE616B-3296-4770-9E56-8A824991EECA}" name="Description:" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D0DCC88A-2D36-4004-A694-FC0C0F0C3396}" name="Таблица2" displayName="Таблица2" ref="A1:C16" totalsRowShown="0" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D0DCC88A-2D36-4004-A694-FC0C0F0C3396}" name="Таблица2" displayName="Таблица2" ref="A1:C16" totalsRowShown="0" headerRowBorderDxfId="4" tableBorderDxfId="3" totalsRowBorderDxfId="2">
   <autoFilter ref="A1:C16" xr:uid="{00000000-0009-0000-0100-000002000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{28358E6A-6F3A-468C-9E1C-880A34D9BECE}" name="№" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{28358E6A-6F3A-468C-9E1C-880A34D9BECE}" name="№" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{DD0AD5C8-324B-4DA7-B39F-B2DB3EF91222}" name="Links:"/>
-    <tableColumn id="3" xr3:uid="{FC8A6018-CA7E-4C73-9B21-B272B55FA8C1}" name="Description:" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{FC8A6018-CA7E-4C73-9B21-B272B55FA8C1}" name="Description:" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -3522,12 +3522,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C7:C8">
-    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="33" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C7))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6">
-    <cfRule type="containsText" dxfId="4" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="32" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C6))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3544,7 +3544,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2">
-    <cfRule type="containsText" dxfId="3" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="31" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C2))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3561,7 +3561,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4">
-    <cfRule type="containsText" dxfId="2" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="30" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C4))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3578,7 +3578,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C5">
-    <cfRule type="containsText" dxfId="1" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="29" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C5))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3595,7 +3595,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3">
-    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="28" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C3))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -4072,10 +4072,10 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" s="85">
+      <c r="A2" s="90">
         <v>1</v>
       </c>
-      <c r="B2" s="93">
+      <c r="B2" s="98">
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
@@ -4092,8 +4092,8 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" s="86"/>
-      <c r="B3" s="93"/>
+      <c r="A3" s="91"/>
+      <c r="B3" s="98"/>
       <c r="C3" s="4" t="s">
         <v>65</v>
       </c>
@@ -4108,8 +4108,8 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" s="87"/>
-      <c r="B4" s="94">
+      <c r="A4" s="92"/>
+      <c r="B4" s="99">
         <v>2</v>
       </c>
       <c r="C4" s="4" t="s">
@@ -4126,14 +4126,14 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" s="87"/>
-      <c r="B5" s="94"/>
+      <c r="A5" s="92"/>
+      <c r="B5" s="99"/>
       <c r="C5" s="4" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6" s="87"/>
+      <c r="A6" s="92"/>
       <c r="B6" s="15">
         <v>3</v>
       </c>
@@ -4142,7 +4142,7 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" s="87"/>
+      <c r="A7" s="92"/>
       <c r="B7" s="16" t="s">
         <v>90</v>
       </c>
@@ -4151,8 +4151,8 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" s="87"/>
-      <c r="B8" s="95">
+      <c r="A8" s="92"/>
+      <c r="B8" s="100">
         <v>6</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -4160,14 +4160,14 @@
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="87"/>
-      <c r="B9" s="96"/>
+      <c r="A9" s="92"/>
+      <c r="B9" s="101"/>
       <c r="C9" s="4" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A10" s="87"/>
+      <c r="A10" s="92"/>
       <c r="B10" s="17">
         <v>7</v>
       </c>
@@ -4176,14 +4176,14 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="87"/>
+      <c r="A11" s="92"/>
       <c r="B11" s="24"/>
       <c r="C11" s="4" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="87"/>
+      <c r="A12" s="92"/>
       <c r="B12" s="18">
         <v>8</v>
       </c>
@@ -4192,7 +4192,7 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" s="88"/>
+      <c r="A13" s="93"/>
       <c r="B13" s="25" t="s">
         <v>78</v>
       </c>
@@ -4201,7 +4201,7 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="89"/>
+      <c r="A14" s="94"/>
       <c r="B14" s="26" t="s">
         <v>91</v>
       </c>
@@ -4210,7 +4210,7 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="14.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="90">
+      <c r="A15" s="95">
         <v>2</v>
       </c>
       <c r="B15" s="19" t="s">
@@ -4221,7 +4221,7 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="91"/>
+      <c r="A16" s="96"/>
       <c r="B16" s="20" t="s">
         <v>365</v>
       </c>
@@ -4230,7 +4230,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="91"/>
+      <c r="A17" s="96"/>
       <c r="B17" s="21" t="s">
         <v>366</v>
       </c>
@@ -4239,7 +4239,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="92"/>
+      <c r="A18" s="97"/>
       <c r="B18" s="22" t="s">
         <v>92</v>
       </c>
@@ -4248,7 +4248,7 @@
       </c>
     </row>
     <row r="19" spans="1:3" ht="14.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="79">
+      <c r="A19" s="84">
         <v>3</v>
       </c>
       <c r="B19" s="23" t="s">
@@ -4259,7 +4259,7 @@
       </c>
     </row>
     <row r="20" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="80"/>
+      <c r="A20" s="85"/>
       <c r="B20" s="27" t="s">
         <v>93</v>
       </c>
@@ -4268,7 +4268,7 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="81"/>
+      <c r="A21" s="86"/>
       <c r="B21" s="28" t="s">
         <v>95</v>
       </c>
@@ -4277,7 +4277,7 @@
       </c>
     </row>
     <row r="22" spans="1:3" ht="14.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="82">
+      <c r="A22" s="87">
         <v>4</v>
       </c>
       <c r="B22" s="19" t="s">
@@ -4288,7 +4288,7 @@
       </c>
     </row>
     <row r="23" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="83"/>
+      <c r="A23" s="88"/>
       <c r="B23" s="20" t="s">
         <v>98</v>
       </c>
@@ -4297,7 +4297,7 @@
       </c>
     </row>
     <row r="24" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="83"/>
+      <c r="A24" s="88"/>
       <c r="B24" s="21" t="s">
         <v>100</v>
       </c>
@@ -4306,7 +4306,7 @@
       </c>
     </row>
     <row r="25" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="83"/>
+      <c r="A25" s="88"/>
       <c r="B25" s="16" t="s">
         <v>102</v>
       </c>
@@ -4315,7 +4315,7 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" s="83"/>
+      <c r="A26" s="88"/>
       <c r="B26" s="29" t="s">
         <v>104</v>
       </c>
@@ -4324,7 +4324,7 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" s="83"/>
+      <c r="A27" s="88"/>
       <c r="B27" s="30" t="s">
         <v>106</v>
       </c>
@@ -4333,7 +4333,7 @@
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" s="83"/>
+      <c r="A28" s="88"/>
       <c r="B28" s="18">
         <v>8</v>
       </c>
@@ -4342,7 +4342,7 @@
       </c>
     </row>
     <row r="29" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="84"/>
+      <c r="A29" s="89"/>
       <c r="B29" s="31" t="s">
         <v>78</v>
       </c>
@@ -4379,7 +4379,7 @@
     <col min="2" max="2" width="22.7265625" customWidth="1"/>
     <col min="3" max="3" width="33.54296875" customWidth="1"/>
     <col min="4" max="4" width="84.6328125" customWidth="1"/>
-    <col min="5" max="5" width="8.54296875" customWidth="1"/>
+    <col min="5" max="5" width="8.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
@@ -4406,7 +4406,7 @@
       <c r="C2" t="s">
         <v>494</v>
       </c>
-      <c r="D2" s="98" t="s">
+      <c r="D2" s="80" t="s">
         <v>413</v>
       </c>
     </row>
@@ -4466,7 +4466,7 @@
       <c r="D2" t="s">
         <v>388</v>
       </c>
-      <c r="W2" s="101" t="s">
+      <c r="W2" s="83" t="s">
         <v>407</v>
       </c>
     </row>
@@ -4483,7 +4483,7 @@
       <c r="D3" t="s">
         <v>389</v>
       </c>
-      <c r="X3" s="97" t="s">
+      <c r="X3" s="79" t="s">
         <v>415</v>
       </c>
       <c r="Y3" t="s">
@@ -4503,7 +4503,7 @@
       <c r="D4" t="s">
         <v>9</v>
       </c>
-      <c r="X4" s="97" t="s">
+      <c r="X4" s="79" t="s">
         <v>416</v>
       </c>
       <c r="Y4" t="s">
@@ -4517,7 +4517,7 @@
       <c r="D5" t="s">
         <v>10</v>
       </c>
-      <c r="X5" s="97" t="s">
+      <c r="X5" s="79" t="s">
         <v>417</v>
       </c>
       <c r="Y5" t="s">
@@ -4531,7 +4531,7 @@
       <c r="D6" t="s">
         <v>13</v>
       </c>
-      <c r="X6" s="97" t="s">
+      <c r="X6" s="79" t="s">
         <v>418</v>
       </c>
       <c r="Y6" t="s">
@@ -4545,7 +4545,7 @@
       <c r="D7" t="s">
         <v>390</v>
       </c>
-      <c r="X7" s="97" t="s">
+      <c r="X7" s="79" t="s">
         <v>419</v>
       </c>
       <c r="Y7" t="s">
@@ -4559,7 +4559,7 @@
       <c r="D8" t="s">
         <v>391</v>
       </c>
-      <c r="X8" s="97" t="s">
+      <c r="X8" s="79" t="s">
         <v>420</v>
       </c>
       <c r="Y8" t="s">
@@ -4573,7 +4573,7 @@
       <c r="D9" t="s">
         <v>11</v>
       </c>
-      <c r="X9" s="97" t="s">
+      <c r="X9" s="79" t="s">
         <v>421</v>
       </c>
       <c r="Y9" t="s">
@@ -4587,7 +4587,7 @@
       <c r="D10" t="s">
         <v>392</v>
       </c>
-      <c r="W10" s="100" t="s">
+      <c r="W10" s="82" t="s">
         <v>491</v>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       <c r="D11" t="s">
         <v>393</v>
       </c>
-      <c r="X11" s="97" t="s">
+      <c r="X11" s="79" t="s">
         <v>422</v>
       </c>
       <c r="Y11" t="s">
@@ -4612,7 +4612,7 @@
       <c r="D12" t="s">
         <v>394</v>
       </c>
-      <c r="X12" s="97" t="s">
+      <c r="X12" s="79" t="s">
         <v>423</v>
       </c>
       <c r="Y12" t="s">
@@ -4626,7 +4626,7 @@
       <c r="D13" t="s">
         <v>395</v>
       </c>
-      <c r="X13" s="97" t="s">
+      <c r="X13" s="79" t="s">
         <v>424</v>
       </c>
       <c r="Y13" t="s">
@@ -4640,7 +4640,7 @@
       <c r="D14" t="s">
         <v>396</v>
       </c>
-      <c r="X14" s="97" t="s">
+      <c r="X14" s="79" t="s">
         <v>425</v>
       </c>
       <c r="Y14" t="s">
@@ -4654,7 +4654,7 @@
       <c r="D15" t="s">
         <v>373</v>
       </c>
-      <c r="X15" s="97" t="s">
+      <c r="X15" s="79" t="s">
         <v>426</v>
       </c>
       <c r="Y15" t="s">
@@ -4662,7 +4662,7 @@
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="X16" s="97" t="s">
+      <c r="X16" s="79" t="s">
         <v>427</v>
       </c>
       <c r="Y16" t="s">
@@ -4670,7 +4670,7 @@
       </c>
     </row>
     <row r="17" spans="23:25" x14ac:dyDescent="0.35">
-      <c r="X17" s="97" t="s">
+      <c r="X17" s="79" t="s">
         <v>428</v>
       </c>
       <c r="Y17" t="s">
@@ -4678,7 +4678,7 @@
       </c>
     </row>
     <row r="18" spans="23:25" x14ac:dyDescent="0.35">
-      <c r="X18" s="97" t="s">
+      <c r="X18" s="79" t="s">
         <v>429</v>
       </c>
       <c r="Y18" t="s">
@@ -4686,7 +4686,7 @@
       </c>
     </row>
     <row r="19" spans="23:25" x14ac:dyDescent="0.35">
-      <c r="X19" s="97" t="s">
+      <c r="X19" s="79" t="s">
         <v>430</v>
       </c>
       <c r="Y19" t="s">
@@ -4694,7 +4694,7 @@
       </c>
     </row>
     <row r="20" spans="23:25" x14ac:dyDescent="0.35">
-      <c r="X20" s="97" t="s">
+      <c r="X20" s="79" t="s">
         <v>431</v>
       </c>
       <c r="Y20" t="s">
@@ -4702,7 +4702,7 @@
       </c>
     </row>
     <row r="21" spans="23:25" x14ac:dyDescent="0.35">
-      <c r="X21" s="97" t="s">
+      <c r="X21" s="79" t="s">
         <v>432</v>
       </c>
       <c r="Y21" t="s">
@@ -4710,7 +4710,7 @@
       </c>
     </row>
     <row r="22" spans="23:25" x14ac:dyDescent="0.35">
-      <c r="X22" s="97" t="s">
+      <c r="X22" s="79" t="s">
         <v>433</v>
       </c>
       <c r="Y22" t="s">
@@ -4718,7 +4718,7 @@
       </c>
     </row>
     <row r="23" spans="23:25" x14ac:dyDescent="0.35">
-      <c r="X23" s="97" t="s">
+      <c r="X23" s="79" t="s">
         <v>434</v>
       </c>
       <c r="Y23" t="s">
@@ -4726,7 +4726,7 @@
       </c>
     </row>
     <row r="24" spans="23:25" x14ac:dyDescent="0.35">
-      <c r="X24" s="97" t="s">
+      <c r="X24" s="79" t="s">
         <v>435</v>
       </c>
       <c r="Y24" t="s">
@@ -4734,7 +4734,7 @@
       </c>
     </row>
     <row r="25" spans="23:25" x14ac:dyDescent="0.35">
-      <c r="X25" s="97" t="s">
+      <c r="X25" s="79" t="s">
         <v>436</v>
       </c>
       <c r="Y25" t="s">
@@ -4742,7 +4742,7 @@
       </c>
     </row>
     <row r="26" spans="23:25" x14ac:dyDescent="0.35">
-      <c r="X26" s="97" t="s">
+      <c r="X26" s="79" t="s">
         <v>437</v>
       </c>
       <c r="Y26" t="s">
@@ -4750,7 +4750,7 @@
       </c>
     </row>
     <row r="27" spans="23:25" x14ac:dyDescent="0.35">
-      <c r="X27" s="97" t="s">
+      <c r="X27" s="79" t="s">
         <v>438</v>
       </c>
       <c r="Y27" t="s">
@@ -4758,7 +4758,7 @@
       </c>
     </row>
     <row r="28" spans="23:25" x14ac:dyDescent="0.35">
-      <c r="X28" s="97" t="s">
+      <c r="X28" s="79" t="s">
         <v>439</v>
       </c>
       <c r="Y28" t="s">
@@ -4766,7 +4766,7 @@
       </c>
     </row>
     <row r="29" spans="23:25" x14ac:dyDescent="0.35">
-      <c r="X29" s="97" t="s">
+      <c r="X29" s="79" t="s">
         <v>440</v>
       </c>
       <c r="Y29" t="s">
@@ -4774,7 +4774,7 @@
       </c>
     </row>
     <row r="30" spans="23:25" x14ac:dyDescent="0.35">
-      <c r="X30" s="97" t="s">
+      <c r="X30" s="79" t="s">
         <v>441</v>
       </c>
       <c r="Y30" t="s">
@@ -4782,7 +4782,7 @@
       </c>
     </row>
     <row r="31" spans="23:25" x14ac:dyDescent="0.35">
-      <c r="X31" s="97" t="s">
+      <c r="X31" s="79" t="s">
         <v>442</v>
       </c>
       <c r="Y31" t="s">
@@ -4790,12 +4790,12 @@
       </c>
     </row>
     <row r="32" spans="23:25" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="W32" s="100" t="s">
+      <c r="W32" s="82" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="33" spans="14:25" x14ac:dyDescent="0.35">
-      <c r="X33" s="97" t="s">
+      <c r="X33" s="79" t="s">
         <v>443</v>
       </c>
       <c r="Y33" t="s">
@@ -4803,7 +4803,7 @@
       </c>
     </row>
     <row r="34" spans="14:25" x14ac:dyDescent="0.35">
-      <c r="X34" s="97" t="s">
+      <c r="X34" s="79" t="s">
         <v>444</v>
       </c>
       <c r="Y34" t="s">
@@ -4811,7 +4811,7 @@
       </c>
     </row>
     <row r="35" spans="14:25" x14ac:dyDescent="0.35">
-      <c r="X35" s="97" t="s">
+      <c r="X35" s="79" t="s">
         <v>445</v>
       </c>
       <c r="Y35" t="s">
@@ -4819,7 +4819,7 @@
       </c>
     </row>
     <row r="36" spans="14:25" x14ac:dyDescent="0.35">
-      <c r="X36" s="97" t="s">
+      <c r="X36" s="79" t="s">
         <v>446</v>
       </c>
       <c r="Y36" t="s">
@@ -4827,7 +4827,7 @@
       </c>
     </row>
     <row r="37" spans="14:25" x14ac:dyDescent="0.35">
-      <c r="X37" s="97" t="s">
+      <c r="X37" s="79" t="s">
         <v>447</v>
       </c>
       <c r="Y37" t="s">
@@ -4835,14 +4835,14 @@
       </c>
     </row>
     <row r="38" spans="14:25" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="W38" s="100" t="s">
+      <c r="W38" s="82" t="s">
         <v>409</v>
       </c>
-      <c r="X38" s="99"/>
+      <c r="X38" s="81"/>
     </row>
     <row r="39" spans="14:25" x14ac:dyDescent="0.35">
-      <c r="N39" s="97"/>
-      <c r="X39" s="97" t="s">
+      <c r="N39" s="79"/>
+      <c r="X39" s="79" t="s">
         <v>448</v>
       </c>
       <c r="Y39" t="s">
@@ -4850,7 +4850,7 @@
       </c>
     </row>
     <row r="40" spans="14:25" x14ac:dyDescent="0.35">
-      <c r="X40" s="97" t="s">
+      <c r="X40" s="79" t="s">
         <v>449</v>
       </c>
       <c r="Y40" t="s">
@@ -4858,7 +4858,7 @@
       </c>
     </row>
     <row r="41" spans="14:25" x14ac:dyDescent="0.35">
-      <c r="X41" s="97" t="s">
+      <c r="X41" s="79" t="s">
         <v>450</v>
       </c>
       <c r="Y41" t="s">
@@ -4866,7 +4866,7 @@
       </c>
     </row>
     <row r="42" spans="14:25" x14ac:dyDescent="0.35">
-      <c r="X42" s="97" t="s">
+      <c r="X42" s="79" t="s">
         <v>451</v>
       </c>
       <c r="Y42" t="s">
@@ -4874,7 +4874,7 @@
       </c>
     </row>
     <row r="43" spans="14:25" x14ac:dyDescent="0.35">
-      <c r="X43" s="97" t="s">
+      <c r="X43" s="79" t="s">
         <v>452</v>
       </c>
       <c r="Y43" t="s">
@@ -4882,7 +4882,7 @@
       </c>
     </row>
     <row r="45" spans="14:25" x14ac:dyDescent="0.35">
-      <c r="N45" s="97"/>
+      <c r="N45" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Info/Additional_information.xlsx
+++ b/Info/Additional_information.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{720DBF33-0378-4F90-B838-837903359CB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F457B47-424A-47F2-8BD5-0BB106C7D780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,15 +17,15 @@
     <sheet name="EURO albums content" sheetId="4" r:id="rId2"/>
     <sheet name="albums ID" sheetId="11" r:id="rId3"/>
     <sheet name="albums ID naming" sheetId="9" r:id="rId4"/>
-    <sheet name="Лист1" sheetId="10" r:id="rId5"/>
-    <sheet name="Mint_Alias" sheetId="5" r:id="rId6"/>
-    <sheet name="Mint_work_years" sheetId="6" r:id="rId7"/>
-    <sheet name="File_Naming" sheetId="2" r:id="rId8"/>
-    <sheet name="Existing_subtypes" sheetId="3" r:id="rId9"/>
-    <sheet name="Links_to_Data" sheetId="7" r:id="rId10"/>
-    <sheet name="Coin_Shops" sheetId="8" r:id="rId11"/>
+    <sheet name="Mint_Alias" sheetId="5" r:id="rId5"/>
+    <sheet name="Mint_work_years" sheetId="6" r:id="rId6"/>
+    <sheet name="File_Naming" sheetId="2" r:id="rId7"/>
+    <sheet name="Existing_subtypes" sheetId="3" r:id="rId8"/>
+    <sheet name="Links_to_Data" sheetId="7" r:id="rId9"/>
+    <sheet name="Coin_Shops" sheetId="8" r:id="rId10"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'albums ID'!$A$1:$D$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Colours_specifications!$A$1:$D$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'EURO albums content'!$A$1:$C$15</definedName>
   </definedNames>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="521">
   <si>
     <t>good quality (UNC for UNC collection; UNC and XF for XF collection)</t>
   </si>
@@ -1318,9 +1318,6 @@
     <t>A0001-GD-BK</t>
   </si>
   <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A0001-GD-BK.html</t>
-  </si>
-  <si>
     <t>Flags (for links)</t>
   </si>
   <si>
@@ -1562,13 +1559,94 @@
   </si>
   <si>
     <t>Альбом юбилейных 2 евро (часть 1)</t>
+  </si>
+  <si>
+    <t>A0002-GD-BK</t>
+  </si>
+  <si>
+    <t>A0003-GD-BK</t>
+  </si>
+  <si>
+    <t>A0004-GD-BK</t>
+  </si>
+  <si>
+    <t>A0005-GD-BK</t>
+  </si>
+  <si>
+    <t>A0006-GD-BK</t>
+  </si>
+  <si>
+    <t>2 Euro album (part 2)</t>
+  </si>
+  <si>
+    <t>Альбом юбилейных 2 евро (часть 2)</t>
+  </si>
+  <si>
+    <t>2 Euro album (part 3)</t>
+  </si>
+  <si>
+    <t>Альбом юбилейных 2 евро (часть 3)</t>
+  </si>
+  <si>
+    <t>2 Euro album (part 4)</t>
+  </si>
+  <si>
+    <t>Альбом юбилейных 2 евро (часть 4)</t>
+  </si>
+  <si>
+    <t>Альбом юбилейных 2 евро (часть 5)</t>
+  </si>
+  <si>
+    <t>2 Euro album (part 5)</t>
+  </si>
+  <si>
+    <t>2 Euro album (part 6)</t>
+  </si>
+  <si>
+    <t>Альбом юбилейных 2 евро (часть 6)</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A0001-GR-BK.html</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A0004-GR-BK.html</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A0002-GR-BK.html</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A0003-GR-BK.html</t>
+  </si>
+  <si>
+    <t>🇻🇦</t>
+  </si>
+  <si>
+    <t>🇦🇩</t>
+  </si>
+  <si>
+    <t>🇲🇨</t>
+  </si>
+  <si>
+    <t>🇸🇲</t>
+  </si>
+  <si>
+    <t>Ватикан (Vatican City)</t>
+  </si>
+  <si>
+    <t>Андорра (Andorra)</t>
+  </si>
+  <si>
+    <t>Монако (Monaco)</t>
+  </si>
+  <si>
+    <t>Сан-Марино (San Marino)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1707,6 +1785,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2362,7 +2446,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2423,12 +2506,61 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="34">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2913,54 +3045,6 @@
         </horizontal>
       </border>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -3078,28 +3162,28 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{973D7237-72C7-453E-A0E1-526C93326B28}" name="Таблица3" displayName="Таблица3" ref="A1:F51" totalsRowShown="0" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{973D7237-72C7-453E-A0E1-526C93326B28}" name="Таблица3" displayName="Таблица3" ref="A1:F51" totalsRowShown="0" headerRowDxfId="33" dataDxfId="31" headerRowBorderDxfId="32" tableBorderDxfId="30" totalsRowBorderDxfId="29">
   <autoFilter ref="A1:F51" xr:uid="{A2D8FA3D-4024-4365-BE1D-F93D0AF2D426}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{12C2DF0B-47FA-46A4-8424-55A1488EF88B}" name="ID" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{EB0B36CE-168D-429E-896D-DBA54794224F}" name="Name_Eng" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{6C3A2CE8-252E-4C52-985B-8CDDFD9FA0C7}" name="OfficialMintName_Native" dataDxfId="20"/>
-    <tableColumn id="8" xr3:uid="{DA5871DC-2EDB-49C0-953E-EC0F70288E21}" name="Country" dataDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{FCD85F85-A94E-4BBE-9D3B-2B7494638375}" name="Mint_City" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{E5141978-CA91-4DE9-86F1-8A8AFA716534}" name="Alias" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{12C2DF0B-47FA-46A4-8424-55A1488EF88B}" name="ID" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{EB0B36CE-168D-429E-896D-DBA54794224F}" name="Name_Eng" dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{6C3A2CE8-252E-4C52-985B-8CDDFD9FA0C7}" name="OfficialMintName_Native" dataDxfId="26"/>
+    <tableColumn id="8" xr3:uid="{DA5871DC-2EDB-49C0-953E-EC0F70288E21}" name="Country" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{FCD85F85-A94E-4BBE-9D3B-2B7494638375}" name="Mint_City" dataDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{E5141978-CA91-4DE9-86F1-8A8AFA716534}" name="Alias" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9D0F8E3D-96B1-4DB8-B1A6-8DD6B84F3693}" name="Таблица35" displayName="Таблица35" ref="A1:D52" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13" totalsRowBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9D0F8E3D-96B1-4DB8-B1A6-8DD6B84F3693}" name="Таблица35" displayName="Таблица35" ref="A1:D52" totalsRowShown="0" headerRowDxfId="22" dataDxfId="20" headerRowBorderDxfId="21" tableBorderDxfId="19" totalsRowBorderDxfId="18">
   <autoFilter ref="A1:D52" xr:uid="{A2D8FA3D-4024-4365-BE1D-F93D0AF2D426}"/>
   <tableColumns count="4">
-    <tableColumn id="4" xr3:uid="{74AFB32D-7AAA-46BE-8174-ED698BB4613E}" name="Mint_id" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{523D65CD-0F56-441F-90B5-E46A9B14F0D0}" name="Ekaterinburg Mint" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{1AAB7352-E935-4EC6-A0D1-3EDC5D0BC93C}" name="Year_of_start" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{5FF15381-476A-4F88-B93A-6452F2830A0A}" name="Year_of_end" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{74AFB32D-7AAA-46BE-8174-ED698BB4613E}" name="Mint_id" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{523D65CD-0F56-441F-90B5-E46A9B14F0D0}" name="Ekaterinburg Mint" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{1AAB7352-E935-4EC6-A0D1-3EDC5D0BC93C}" name="Year_of_start" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{5FF15381-476A-4F88-B93A-6452F2830A0A}" name="Year_of_end" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3113,25 +3197,25 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{8354E581-3B48-4762-81A7-EA76E36C4BB5}" name="№" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{1F45DC85-8ECA-45FE-BF45-E528619CEE0E}" name="Links:" dataDxfId="6" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{3FAE616B-3296-4770-9E56-8A824991EECA}" name="Description:" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{8354E581-3B48-4762-81A7-EA76E36C4BB5}" name="№" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{1F45DC85-8ECA-45FE-BF45-E528619CEE0E}" name="Links:" dataDxfId="12" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{3FAE616B-3296-4770-9E56-8A824991EECA}" name="Description:" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D0DCC88A-2D36-4004-A694-FC0C0F0C3396}" name="Таблица2" displayName="Таблица2" ref="A1:C16" totalsRowShown="0" headerRowBorderDxfId="4" tableBorderDxfId="3" totalsRowBorderDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D0DCC88A-2D36-4004-A694-FC0C0F0C3396}" name="Таблица2" displayName="Таблица2" ref="A1:C16" totalsRowShown="0" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
   <autoFilter ref="A1:C16" xr:uid="{00000000-0009-0000-0100-000002000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{28358E6A-6F3A-468C-9E1C-880A34D9BECE}" name="№" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{28358E6A-6F3A-468C-9E1C-880A34D9BECE}" name="№" dataDxfId="7"/>
     <tableColumn id="2" xr3:uid="{DD0AD5C8-324B-4DA7-B39F-B2DB3EF91222}" name="Links:"/>
-    <tableColumn id="3" xr3:uid="{FC8A6018-CA7E-4C73-9B21-B272B55FA8C1}" name="Description:" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{FC8A6018-CA7E-4C73-9B21-B272B55FA8C1}" name="Description:" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -3522,12 +3606,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C7:C8">
-    <cfRule type="containsText" dxfId="33" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C7))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6">
-    <cfRule type="containsText" dxfId="32" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="4" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C6))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3544,7 +3628,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2">
-    <cfRule type="containsText" dxfId="31" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="3" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C2))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3561,7 +3645,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4">
-    <cfRule type="containsText" dxfId="30" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="2" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C4))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3578,7 +3662,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C5">
-    <cfRule type="containsText" dxfId="29" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="1" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C5))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3595,7 +3679,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3">
-    <cfRule type="containsText" dxfId="28" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C3))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -3627,220 +3711,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{729F7C06-1AE8-4162-8F40-6E9A64E311D7}">
-  <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="4.81640625" customWidth="1"/>
-    <col min="2" max="2" width="57.1796875" customWidth="1"/>
-    <col min="3" max="3" width="104.453125" customWidth="1"/>
-    <col min="4" max="4" width="15.453125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>303</v>
-      </c>
-      <c r="B1" s="45" t="s">
-        <v>304</v>
-      </c>
-      <c r="C1" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="41">
-        <v>1</v>
-      </c>
-      <c r="B2" s="46" t="s">
-        <v>306</v>
-      </c>
-      <c r="C2" s="47" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="41">
-        <v>2</v>
-      </c>
-      <c r="B3" s="46" t="s">
-        <v>308</v>
-      </c>
-      <c r="C3" s="47" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="41">
-        <v>3</v>
-      </c>
-      <c r="B4" s="46" t="s">
-        <v>310</v>
-      </c>
-      <c r="C4" s="47" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="41">
-        <v>4</v>
-      </c>
-      <c r="B5" s="46" t="s">
-        <v>312</v>
-      </c>
-      <c r="C5" s="47" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="41">
-        <v>5</v>
-      </c>
-      <c r="B6" s="46" t="s">
-        <v>314</v>
-      </c>
-      <c r="C6" s="47" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="41">
-        <v>6</v>
-      </c>
-      <c r="B7" s="46" t="s">
-        <v>316</v>
-      </c>
-      <c r="C7" s="47" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A8" s="41">
-        <v>7</v>
-      </c>
-      <c r="B8" s="46" t="s">
-        <v>318</v>
-      </c>
-      <c r="C8" s="47" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="41">
-        <v>8</v>
-      </c>
-      <c r="B9" s="46" t="s">
-        <v>320</v>
-      </c>
-      <c r="C9" s="47" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A10" s="41">
-        <v>9</v>
-      </c>
-      <c r="B10" s="46" t="s">
-        <v>322</v>
-      </c>
-      <c r="C10" s="47" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="41">
-        <v>10</v>
-      </c>
-      <c r="B11" s="46" t="s">
-        <v>324</v>
-      </c>
-      <c r="C11" s="47" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="41">
-        <v>11</v>
-      </c>
-      <c r="B12" s="46" t="s">
-        <v>324</v>
-      </c>
-      <c r="C12" s="47" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" s="41">
-        <v>12</v>
-      </c>
-      <c r="B13" s="46" t="s">
-        <v>327</v>
-      </c>
-      <c r="C13" s="47" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" s="41">
-        <v>13</v>
-      </c>
-      <c r="B14" s="48" t="s">
-        <v>329</v>
-      </c>
-      <c r="C14" s="49" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" s="50">
-        <v>14</v>
-      </c>
-      <c r="B15" s="48" t="s">
-        <v>331</v>
-      </c>
-      <c r="C15" s="49" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" s="50">
-        <v>15</v>
-      </c>
-      <c r="B16" s="48" t="s">
-        <v>333</v>
-      </c>
-      <c r="C16" s="49" t="s">
-        <v>332</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" location="p75892" xr:uid="{2004A8F5-EEA3-401A-8147-DCBE2B32B8A8}"/>
-    <hyperlink ref="B9" r:id="rId2" xr:uid="{3753811B-46E0-40E4-A28F-CA6D25194D0F}"/>
-    <hyperlink ref="B3" r:id="rId3" xr:uid="{ABC31D49-3E50-4123-A5E8-5A9AD3B5E23A}"/>
-    <hyperlink ref="B4" r:id="rId4" xr:uid="{9BB030EB-2475-45E8-8729-CB926565C2F2}"/>
-    <hyperlink ref="B5" r:id="rId5" xr:uid="{7321AD3B-4F9A-4715-8E78-C68C70C3ED3B}"/>
-    <hyperlink ref="B6" r:id="rId6" xr:uid="{548D83D1-6D3D-4818-ADA3-FE0E9231956A}"/>
-    <hyperlink ref="B7" r:id="rId7" xr:uid="{472B0F29-A646-4E1D-889A-066C1E7B1A15}"/>
-    <hyperlink ref="B8" r:id="rId8" xr:uid="{AC393C1F-E1F7-4A34-BAB9-9A5547AA9097}"/>
-    <hyperlink ref="B10" r:id="rId9" xr:uid="{03660F06-E14B-4321-BA0A-8107D65FCB9A}"/>
-    <hyperlink ref="B11" r:id="rId10" xr:uid="{4C30CEFE-89AC-45A8-B194-BA95B0264245}"/>
-    <hyperlink ref="B12" r:id="rId11" xr:uid="{6B68188A-ED23-4BA9-84BA-0548CD8D3167}"/>
-    <hyperlink ref="B13" r:id="rId12" xr:uid="{3F6B392C-913E-4879-8C3F-C8EDE5C0C628}"/>
-    <hyperlink ref="B14" r:id="rId13" xr:uid="{C5D03E4D-384E-4F2E-B584-EB754AA1EC51}"/>
-    <hyperlink ref="B15" r:id="rId14" xr:uid="{4438EF86-C632-4762-BA87-39D3DF57E123}"/>
-    <hyperlink ref="B16" r:id="rId15" xr:uid="{953D4D13-1E13-4CD6-AAB4-804DCEA3E92F}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId16"/>
-  <legacyDrawing r:id="rId17"/>
-  <tableParts count="1">
-    <tablePart r:id="rId18"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8049D8E-7482-48AF-95C9-7F1B728B0DDE}">
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -4072,10 +3942,10 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" s="90">
+      <c r="A2" s="89">
         <v>1</v>
       </c>
-      <c r="B2" s="98">
+      <c r="B2" s="97">
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
@@ -4092,8 +3962,8 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" s="91"/>
-      <c r="B3" s="98"/>
+      <c r="A3" s="90"/>
+      <c r="B3" s="97"/>
       <c r="C3" s="4" t="s">
         <v>65</v>
       </c>
@@ -4108,8 +3978,8 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" s="92"/>
-      <c r="B4" s="99">
+      <c r="A4" s="91"/>
+      <c r="B4" s="98">
         <v>2</v>
       </c>
       <c r="C4" s="4" t="s">
@@ -4126,14 +3996,14 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" s="92"/>
-      <c r="B5" s="99"/>
+      <c r="A5" s="91"/>
+      <c r="B5" s="98"/>
       <c r="C5" s="4" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6" s="92"/>
+      <c r="A6" s="91"/>
       <c r="B6" s="15">
         <v>3</v>
       </c>
@@ -4142,7 +4012,7 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" s="92"/>
+      <c r="A7" s="91"/>
       <c r="B7" s="16" t="s">
         <v>90</v>
       </c>
@@ -4151,8 +4021,8 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" s="92"/>
-      <c r="B8" s="100">
+      <c r="A8" s="91"/>
+      <c r="B8" s="99">
         <v>6</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -4160,14 +4030,14 @@
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="92"/>
-      <c r="B9" s="101"/>
+      <c r="A9" s="91"/>
+      <c r="B9" s="100"/>
       <c r="C9" s="4" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A10" s="92"/>
+      <c r="A10" s="91"/>
       <c r="B10" s="17">
         <v>7</v>
       </c>
@@ -4176,14 +4046,14 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="92"/>
+      <c r="A11" s="91"/>
       <c r="B11" s="24"/>
       <c r="C11" s="4" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="92"/>
+      <c r="A12" s="91"/>
       <c r="B12" s="18">
         <v>8</v>
       </c>
@@ -4192,7 +4062,7 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" s="93"/>
+      <c r="A13" s="92"/>
       <c r="B13" s="25" t="s">
         <v>78</v>
       </c>
@@ -4201,7 +4071,7 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="94"/>
+      <c r="A14" s="93"/>
       <c r="B14" s="26" t="s">
         <v>91</v>
       </c>
@@ -4210,7 +4080,7 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="14.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="95">
+      <c r="A15" s="94">
         <v>2</v>
       </c>
       <c r="B15" s="19" t="s">
@@ -4221,7 +4091,7 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="96"/>
+      <c r="A16" s="95"/>
       <c r="B16" s="20" t="s">
         <v>365</v>
       </c>
@@ -4230,7 +4100,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="96"/>
+      <c r="A17" s="95"/>
       <c r="B17" s="21" t="s">
         <v>366</v>
       </c>
@@ -4239,7 +4109,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="97"/>
+      <c r="A18" s="96"/>
       <c r="B18" s="22" t="s">
         <v>92</v>
       </c>
@@ -4248,7 +4118,7 @@
       </c>
     </row>
     <row r="19" spans="1:3" ht="14.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="84">
+      <c r="A19" s="83">
         <v>3</v>
       </c>
       <c r="B19" s="23" t="s">
@@ -4259,7 +4129,7 @@
       </c>
     </row>
     <row r="20" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="85"/>
+      <c r="A20" s="84"/>
       <c r="B20" s="27" t="s">
         <v>93</v>
       </c>
@@ -4268,7 +4138,7 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="86"/>
+      <c r="A21" s="85"/>
       <c r="B21" s="28" t="s">
         <v>95</v>
       </c>
@@ -4277,7 +4147,7 @@
       </c>
     </row>
     <row r="22" spans="1:3" ht="14.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="87">
+      <c r="A22" s="86">
         <v>4</v>
       </c>
       <c r="B22" s="19" t="s">
@@ -4288,7 +4158,7 @@
       </c>
     </row>
     <row r="23" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="88"/>
+      <c r="A23" s="87"/>
       <c r="B23" s="20" t="s">
         <v>98</v>
       </c>
@@ -4297,7 +4167,7 @@
       </c>
     </row>
     <row r="24" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="88"/>
+      <c r="A24" s="87"/>
       <c r="B24" s="21" t="s">
         <v>100</v>
       </c>
@@ -4306,7 +4176,7 @@
       </c>
     </row>
     <row r="25" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="88"/>
+      <c r="A25" s="87"/>
       <c r="B25" s="16" t="s">
         <v>102</v>
       </c>
@@ -4315,7 +4185,7 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" s="88"/>
+      <c r="A26" s="87"/>
       <c r="B26" s="29" t="s">
         <v>104</v>
       </c>
@@ -4324,7 +4194,7 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" s="88"/>
+      <c r="A27" s="87"/>
       <c r="B27" s="30" t="s">
         <v>106</v>
       </c>
@@ -4333,7 +4203,7 @@
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" s="88"/>
+      <c r="A28" s="87"/>
       <c r="B28" s="18">
         <v>8</v>
       </c>
@@ -4342,7 +4212,7 @@
       </c>
     </row>
     <row r="29" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="89"/>
+      <c r="A29" s="88"/>
       <c r="B29" s="31" t="s">
         <v>78</v>
       </c>
@@ -4372,7 +4242,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DC835FD-69FE-4DBC-957F-9A46CA05517E}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.26953125" customWidth="1"/>
@@ -4390,7 +4260,7 @@
         <v>410</v>
       </c>
       <c r="C1" s="78" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D1" s="78" t="s">
         <v>404</v>
@@ -4401,28 +4271,103 @@
         <v>412</v>
       </c>
       <c r="B2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C2" t="s">
+        <v>493</v>
+      </c>
+      <c r="D2" s="102" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>494</v>
       </c>
-      <c r="D2" s="80" t="s">
-        <v>413</v>
+      <c r="B3" t="s">
+        <v>499</v>
+      </c>
+      <c r="C3" t="s">
+        <v>500</v>
+      </c>
+      <c r="D3" s="102" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>495</v>
+      </c>
+      <c r="B4" t="s">
+        <v>501</v>
+      </c>
+      <c r="C4" t="s">
+        <v>502</v>
+      </c>
+      <c r="D4" s="102" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>496</v>
+      </c>
+      <c r="B5" t="s">
+        <v>503</v>
+      </c>
+      <c r="C5" t="s">
+        <v>504</v>
+      </c>
+      <c r="D5" s="102" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>497</v>
+      </c>
+      <c r="B6" t="s">
+        <v>506</v>
+      </c>
+      <c r="C6" t="s">
+        <v>505</v>
+      </c>
+      <c r="D6" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>498</v>
+      </c>
+      <c r="B7" t="s">
+        <v>507</v>
+      </c>
+      <c r="C7" t="s">
+        <v>508</v>
+      </c>
+      <c r="D7" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D1" xr:uid="{1DC835FD-69FE-4DBC-957F-9A46CA05517E}"/>
+  <phoneticPr fontId="18" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{D827BEB2-1C88-4D17-BA13-D6C7BE5F2B8D}"/>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{202A29D0-9EE0-4193-BB2A-5199720DC977}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{CF441EF5-F4BD-438B-8859-6D3EFE142B71}"/>
+    <hyperlink ref="D4" r:id="rId3" xr:uid="{FCDDF3A3-0B92-4B7E-84DE-1369DD81862B}"/>
+    <hyperlink ref="D5" r:id="rId4" xr:uid="{0D149830-0064-4F8C-AEB1-2BE082CF8F84}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
-  <drawing r:id="rId3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
+  <drawing r:id="rId6"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{866E9A5E-386D-439E-AA25-CB46A31C625C}">
-  <dimension ref="A1:Y45"/>
+  <dimension ref="A1:Y50"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.453125" style="77" customWidth="1"/>
@@ -4447,11 +4392,11 @@
       <c r="D1" s="72" t="s">
         <v>402</v>
       </c>
-      <c r="W1" s="102" t="s">
-        <v>414</v>
-      </c>
-      <c r="X1" s="102"/>
-      <c r="Y1" s="102"/>
+      <c r="W1" s="101" t="s">
+        <v>413</v>
+      </c>
+      <c r="X1" s="101"/>
+      <c r="Y1" s="101"/>
     </row>
     <row r="2" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="77" t="s">
@@ -4466,7 +4411,7 @@
       <c r="D2" t="s">
         <v>388</v>
       </c>
-      <c r="W2" s="83" t="s">
+      <c r="W2" s="82" t="s">
         <v>407</v>
       </c>
     </row>
@@ -4484,10 +4429,10 @@
         <v>389</v>
       </c>
       <c r="X3" s="79" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="Y3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.35">
@@ -4504,10 +4449,10 @@
         <v>9</v>
       </c>
       <c r="X4" s="79" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Y4" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.35">
@@ -4518,10 +4463,10 @@
         <v>10</v>
       </c>
       <c r="X5" s="79" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="Y5" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.35">
@@ -4532,10 +4477,10 @@
         <v>13</v>
       </c>
       <c r="X6" s="79" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="Y6" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.35">
@@ -4546,10 +4491,10 @@
         <v>390</v>
       </c>
       <c r="X7" s="79" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="Y7" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.35">
@@ -4560,10 +4505,10 @@
         <v>391</v>
       </c>
       <c r="X8" s="79" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="Y8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.35">
@@ -4574,10 +4519,10 @@
         <v>11</v>
       </c>
       <c r="X9" s="79" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="Y9" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="10" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
@@ -4587,8 +4532,8 @@
       <c r="D10" t="s">
         <v>392</v>
       </c>
-      <c r="W10" s="82" t="s">
-        <v>491</v>
+      <c r="W10" s="81" t="s">
+        <v>490</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.35">
@@ -4599,10 +4544,10 @@
         <v>393</v>
       </c>
       <c r="X11" s="79" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="Y11" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.35">
@@ -4613,10 +4558,10 @@
         <v>394</v>
       </c>
       <c r="X12" s="79" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="Y12" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.35">
@@ -4627,10 +4572,10 @@
         <v>395</v>
       </c>
       <c r="X13" s="79" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="Y13" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.35">
@@ -4641,10 +4586,10 @@
         <v>396</v>
       </c>
       <c r="X14" s="79" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="Y14" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.35">
@@ -4655,234 +4600,281 @@
         <v>373</v>
       </c>
       <c r="X15" s="79" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="Y15" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.35">
       <c r="X16" s="79" t="s">
+        <v>426</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="17" spans="24:25" x14ac:dyDescent="0.35">
+      <c r="X17" s="79" t="s">
         <v>427</v>
       </c>
-      <c r="Y16" t="s">
+      <c r="Y17" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="17" spans="23:25" x14ac:dyDescent="0.35">
-      <c r="X17" s="79" t="s">
+    <row r="18" spans="24:25" x14ac:dyDescent="0.35">
+      <c r="X18" s="79" t="s">
         <v>428</v>
       </c>
-      <c r="Y17" t="s">
+      <c r="Y18" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="18" spans="23:25" x14ac:dyDescent="0.35">
-      <c r="X18" s="79" t="s">
+    <row r="19" spans="24:25" x14ac:dyDescent="0.35">
+      <c r="X19" s="79" t="s">
         <v>429</v>
       </c>
-      <c r="Y18" t="s">
+      <c r="Y19" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="19" spans="23:25" x14ac:dyDescent="0.35">
-      <c r="X19" s="79" t="s">
+    <row r="20" spans="24:25" x14ac:dyDescent="0.35">
+      <c r="X20" s="79" t="s">
         <v>430</v>
       </c>
-      <c r="Y19" t="s">
+      <c r="Y20" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="20" spans="23:25" x14ac:dyDescent="0.35">
-      <c r="X20" s="79" t="s">
+    <row r="21" spans="24:25" x14ac:dyDescent="0.35">
+      <c r="X21" s="79" t="s">
         <v>431</v>
       </c>
-      <c r="Y20" t="s">
+      <c r="Y21" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="21" spans="23:25" x14ac:dyDescent="0.35">
-      <c r="X21" s="79" t="s">
+    <row r="22" spans="24:25" x14ac:dyDescent="0.35">
+      <c r="X22" s="79" t="s">
         <v>432</v>
       </c>
-      <c r="Y21" t="s">
+      <c r="Y22" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="22" spans="23:25" x14ac:dyDescent="0.35">
-      <c r="X22" s="79" t="s">
+    <row r="23" spans="24:25" x14ac:dyDescent="0.35">
+      <c r="X23" s="79" t="s">
         <v>433</v>
       </c>
-      <c r="Y22" t="s">
+      <c r="Y23" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="23" spans="23:25" x14ac:dyDescent="0.35">
-      <c r="X23" s="79" t="s">
+    <row r="24" spans="24:25" x14ac:dyDescent="0.35">
+      <c r="X24" s="79" t="s">
         <v>434</v>
       </c>
-      <c r="Y23" t="s">
+      <c r="Y24" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="24" spans="23:25" x14ac:dyDescent="0.35">
-      <c r="X24" s="79" t="s">
+    <row r="25" spans="24:25" x14ac:dyDescent="0.35">
+      <c r="X25" s="79" t="s">
         <v>435</v>
       </c>
-      <c r="Y24" t="s">
+      <c r="Y25" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="25" spans="23:25" x14ac:dyDescent="0.35">
-      <c r="X25" s="79" t="s">
+    <row r="26" spans="24:25" x14ac:dyDescent="0.35">
+      <c r="X26" s="79" t="s">
         <v>436</v>
       </c>
-      <c r="Y25" t="s">
+      <c r="Y26" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="26" spans="23:25" x14ac:dyDescent="0.35">
-      <c r="X26" s="79" t="s">
+    <row r="27" spans="24:25" x14ac:dyDescent="0.35">
+      <c r="X27" s="79" t="s">
         <v>437</v>
       </c>
-      <c r="Y26" t="s">
+      <c r="Y27" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="27" spans="23:25" x14ac:dyDescent="0.35">
-      <c r="X27" s="79" t="s">
+    <row r="28" spans="24:25" x14ac:dyDescent="0.35">
+      <c r="X28" s="79" t="s">
         <v>438</v>
       </c>
-      <c r="Y27" t="s">
+      <c r="Y28" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="28" spans="23:25" x14ac:dyDescent="0.35">
-      <c r="X28" s="79" t="s">
+    <row r="29" spans="24:25" x14ac:dyDescent="0.35">
+      <c r="X29" s="79" t="s">
         <v>439</v>
       </c>
-      <c r="Y28" t="s">
+      <c r="Y29" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="29" spans="23:25" x14ac:dyDescent="0.35">
-      <c r="X29" s="79" t="s">
+    <row r="30" spans="24:25" x14ac:dyDescent="0.35">
+      <c r="X30" s="79" t="s">
         <v>440</v>
       </c>
-      <c r="Y29" t="s">
+      <c r="Y30" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="30" spans="23:25" x14ac:dyDescent="0.35">
-      <c r="X30" s="79" t="s">
+    <row r="31" spans="24:25" x14ac:dyDescent="0.35">
+      <c r="X31" s="79" t="s">
         <v>441</v>
       </c>
-      <c r="Y30" t="s">
+      <c r="Y31" t="s">
         <v>479</v>
       </c>
     </row>
-    <row r="31" spans="23:25" x14ac:dyDescent="0.35">
-      <c r="X31" s="79" t="s">
-        <v>442</v>
-      </c>
-      <c r="Y31" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="32" spans="23:25" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="W32" s="82" t="s">
-        <v>408</v>
+    <row r="32" spans="24:25" x14ac:dyDescent="0.35">
+      <c r="X32" s="79" t="s">
+        <v>513</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>517</v>
       </c>
     </row>
     <row r="33" spans="14:25" x14ac:dyDescent="0.35">
       <c r="X33" s="79" t="s">
-        <v>443</v>
+        <v>514</v>
       </c>
       <c r="Y33" t="s">
-        <v>481</v>
+        <v>518</v>
       </c>
     </row>
     <row r="34" spans="14:25" x14ac:dyDescent="0.35">
       <c r="X34" s="79" t="s">
-        <v>444</v>
+        <v>515</v>
       </c>
       <c r="Y34" t="s">
-        <v>482</v>
+        <v>519</v>
       </c>
     </row>
     <row r="35" spans="14:25" x14ac:dyDescent="0.35">
       <c r="X35" s="79" t="s">
-        <v>445</v>
+        <v>516</v>
       </c>
       <c r="Y35" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="36" spans="14:25" x14ac:dyDescent="0.35">
-      <c r="X36" s="79" t="s">
-        <v>446</v>
-      </c>
-      <c r="Y36" t="s">
-        <v>484</v>
+        <v>520</v>
+      </c>
+    </row>
+    <row r="36" spans="14:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="W36" s="81" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="37" spans="14:25" x14ac:dyDescent="0.35">
       <c r="X37" s="79" t="s">
+        <v>442</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="38" spans="14:25" x14ac:dyDescent="0.35">
+      <c r="X38" s="79" t="s">
+        <v>443</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="39" spans="14:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="N39" s="81"/>
+      <c r="X39" s="79" t="s">
+        <v>444</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="40" spans="14:25" x14ac:dyDescent="0.35">
+      <c r="O40" s="79"/>
+      <c r="X40" s="79" t="s">
+        <v>445</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="41" spans="14:25" x14ac:dyDescent="0.35">
+      <c r="O41" s="79"/>
+      <c r="X41" s="79" t="s">
+        <v>446</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="42" spans="14:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="O42" s="79"/>
+      <c r="W42" s="81" t="s">
+        <v>409</v>
+      </c>
+      <c r="X42" s="80"/>
+    </row>
+    <row r="43" spans="14:25" x14ac:dyDescent="0.35">
+      <c r="O43" s="79"/>
+      <c r="X43" s="79" t="s">
         <v>447</v>
       </c>
-      <c r="Y37" t="s">
+      <c r="Y43" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="38" spans="14:25" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="W38" s="82" t="s">
-        <v>409</v>
-      </c>
-      <c r="X38" s="81"/>
-    </row>
-    <row r="39" spans="14:25" x14ac:dyDescent="0.35">
-      <c r="N39" s="79"/>
-      <c r="X39" s="79" t="s">
+    <row r="44" spans="14:25" x14ac:dyDescent="0.35">
+      <c r="O44" s="79"/>
+      <c r="X44" s="79" t="s">
         <v>448</v>
       </c>
-      <c r="Y39" t="s">
+      <c r="Y44" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="40" spans="14:25" x14ac:dyDescent="0.35">
-      <c r="X40" s="79" t="s">
+    <row r="45" spans="14:25" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="N45" s="81"/>
+      <c r="O45" s="80"/>
+      <c r="X45" s="79" t="s">
         <v>449</v>
       </c>
-      <c r="Y40" t="s">
+      <c r="Y45" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="41" spans="14:25" x14ac:dyDescent="0.35">
-      <c r="X41" s="79" t="s">
+    <row r="46" spans="14:25" x14ac:dyDescent="0.35">
+      <c r="O46" s="79"/>
+      <c r="X46" s="79" t="s">
         <v>450</v>
       </c>
-      <c r="Y41" t="s">
+      <c r="Y46" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="42" spans="14:25" x14ac:dyDescent="0.35">
-      <c r="X42" s="79" t="s">
+    <row r="47" spans="14:25" x14ac:dyDescent="0.35">
+      <c r="O47" s="79"/>
+      <c r="X47" s="79" t="s">
         <v>451</v>
       </c>
-      <c r="Y42" t="s">
+      <c r="Y47" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="43" spans="14:25" x14ac:dyDescent="0.35">
-      <c r="X43" s="79" t="s">
-        <v>452</v>
-      </c>
-      <c r="Y43" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="45" spans="14:25" x14ac:dyDescent="0.35">
-      <c r="N45" s="79"/>
+    <row r="48" spans="14:25" x14ac:dyDescent="0.35">
+      <c r="O48" s="79"/>
+    </row>
+    <row r="49" spans="15:15" x14ac:dyDescent="0.35">
+      <c r="O49" s="79"/>
+    </row>
+    <row r="50" spans="15:15" x14ac:dyDescent="0.35">
+      <c r="O50" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4895,15 +4887,6 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1D965D1-2F9C-4783-AB93-708A62EBAC76}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4C14141-45DA-4C30-845C-3E630B347F10}">
   <dimension ref="A1:F51"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -5943,7 +5926,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF1BA8E2-9FD2-4C47-B5D3-EF9907B8F692}">
   <dimension ref="A1:D52"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -6619,7 +6602,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0041FEF0-BF6F-4667-AFBD-1C23A1866795}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -6733,7 +6716,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8265AFD9-D9EB-4B75-B60D-6B7F7204230D}">
   <dimension ref="A1:B29"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -6921,4 +6904,218 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{729F7C06-1AE8-4162-8F40-6E9A64E311D7}">
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="4.81640625" customWidth="1"/>
+    <col min="2" max="2" width="57.1796875" customWidth="1"/>
+    <col min="3" max="3" width="104.453125" customWidth="1"/>
+    <col min="4" max="4" width="15.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B1" s="45" t="s">
+        <v>304</v>
+      </c>
+      <c r="C1" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="41">
+        <v>1</v>
+      </c>
+      <c r="B2" s="46" t="s">
+        <v>306</v>
+      </c>
+      <c r="C2" s="47" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="41">
+        <v>2</v>
+      </c>
+      <c r="B3" s="46" t="s">
+        <v>308</v>
+      </c>
+      <c r="C3" s="47" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="41">
+        <v>3</v>
+      </c>
+      <c r="B4" s="46" t="s">
+        <v>310</v>
+      </c>
+      <c r="C4" s="47" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="41">
+        <v>4</v>
+      </c>
+      <c r="B5" s="46" t="s">
+        <v>312</v>
+      </c>
+      <c r="C5" s="47" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="41">
+        <v>5</v>
+      </c>
+      <c r="B6" s="46" t="s">
+        <v>314</v>
+      </c>
+      <c r="C6" s="47" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="41">
+        <v>6</v>
+      </c>
+      <c r="B7" s="46" t="s">
+        <v>316</v>
+      </c>
+      <c r="C7" s="47" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A8" s="41">
+        <v>7</v>
+      </c>
+      <c r="B8" s="46" t="s">
+        <v>318</v>
+      </c>
+      <c r="C8" s="47" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="41">
+        <v>8</v>
+      </c>
+      <c r="B9" s="46" t="s">
+        <v>320</v>
+      </c>
+      <c r="C9" s="47" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A10" s="41">
+        <v>9</v>
+      </c>
+      <c r="B10" s="46" t="s">
+        <v>322</v>
+      </c>
+      <c r="C10" s="47" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="41">
+        <v>10</v>
+      </c>
+      <c r="B11" s="46" t="s">
+        <v>324</v>
+      </c>
+      <c r="C11" s="47" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="41">
+        <v>11</v>
+      </c>
+      <c r="B12" s="46" t="s">
+        <v>324</v>
+      </c>
+      <c r="C12" s="47" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="41">
+        <v>12</v>
+      </c>
+      <c r="B13" s="46" t="s">
+        <v>327</v>
+      </c>
+      <c r="C13" s="47" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="41">
+        <v>13</v>
+      </c>
+      <c r="B14" s="48" t="s">
+        <v>329</v>
+      </c>
+      <c r="C14" s="49" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="50">
+        <v>14</v>
+      </c>
+      <c r="B15" s="48" t="s">
+        <v>331</v>
+      </c>
+      <c r="C15" s="49" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="50">
+        <v>15</v>
+      </c>
+      <c r="B16" s="48" t="s">
+        <v>333</v>
+      </c>
+      <c r="C16" s="49" t="s">
+        <v>332</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" location="p75892" xr:uid="{2004A8F5-EEA3-401A-8147-DCBE2B32B8A8}"/>
+    <hyperlink ref="B9" r:id="rId2" xr:uid="{3753811B-46E0-40E4-A28F-CA6D25194D0F}"/>
+    <hyperlink ref="B3" r:id="rId3" xr:uid="{ABC31D49-3E50-4123-A5E8-5A9AD3B5E23A}"/>
+    <hyperlink ref="B4" r:id="rId4" xr:uid="{9BB030EB-2475-45E8-8729-CB926565C2F2}"/>
+    <hyperlink ref="B5" r:id="rId5" xr:uid="{7321AD3B-4F9A-4715-8E78-C68C70C3ED3B}"/>
+    <hyperlink ref="B6" r:id="rId6" xr:uid="{548D83D1-6D3D-4818-ADA3-FE0E9231956A}"/>
+    <hyperlink ref="B7" r:id="rId7" xr:uid="{472B0F29-A646-4E1D-889A-066C1E7B1A15}"/>
+    <hyperlink ref="B8" r:id="rId8" xr:uid="{AC393C1F-E1F7-4A34-BAB9-9A5547AA9097}"/>
+    <hyperlink ref="B10" r:id="rId9" xr:uid="{03660F06-E14B-4321-BA0A-8107D65FCB9A}"/>
+    <hyperlink ref="B11" r:id="rId10" xr:uid="{4C30CEFE-89AC-45A8-B194-BA95B0264245}"/>
+    <hyperlink ref="B12" r:id="rId11" xr:uid="{6B68188A-ED23-4BA9-84BA-0548CD8D3167}"/>
+    <hyperlink ref="B13" r:id="rId12" xr:uid="{3F6B392C-913E-4879-8C3F-C8EDE5C0C628}"/>
+    <hyperlink ref="B14" r:id="rId13" xr:uid="{C5D03E4D-384E-4F2E-B584-EB754AA1EC51}"/>
+    <hyperlink ref="B15" r:id="rId14" xr:uid="{4438EF86-C632-4762-BA87-39D3DF57E123}"/>
+    <hyperlink ref="B16" r:id="rId15" xr:uid="{953D4D13-1E13-4CD6-AAB4-804DCEA3E92F}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId16"/>
+  <legacyDrawing r:id="rId17"/>
+  <tableParts count="1">
+    <tablePart r:id="rId18"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/Info/Additional_information.xlsx
+++ b/Info/Additional_information.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F457B47-424A-47F2-8BD5-0BB106C7D780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44BF6265-42CE-4E72-862E-FAB0DA48F4F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="529">
   <si>
     <t>good quality (UNC for UNC collection; UNC and XF for XF collection)</t>
   </si>
@@ -1552,15 +1552,9 @@
     <t>Европа</t>
   </si>
   <si>
-    <t>2 Euro album (part 1)</t>
-  </si>
-  <si>
     <t>Album Content (ru)</t>
   </si>
   <si>
-    <t>Альбом юбилейных 2 евро (часть 1)</t>
-  </si>
-  <si>
     <t>A0002-GD-BK</t>
   </si>
   <si>
@@ -1576,36 +1570,6 @@
     <t>A0006-GD-BK</t>
   </si>
   <si>
-    <t>2 Euro album (part 2)</t>
-  </si>
-  <si>
-    <t>Альбом юбилейных 2 евро (часть 2)</t>
-  </si>
-  <si>
-    <t>2 Euro album (part 3)</t>
-  </si>
-  <si>
-    <t>Альбом юбилейных 2 евро (часть 3)</t>
-  </si>
-  <si>
-    <t>2 Euro album (part 4)</t>
-  </si>
-  <si>
-    <t>Альбом юбилейных 2 евро (часть 4)</t>
-  </si>
-  <si>
-    <t>Альбом юбилейных 2 евро (часть 5)</t>
-  </si>
-  <si>
-    <t>2 Euro album (part 5)</t>
-  </si>
-  <si>
-    <t>2 Euro album (part 6)</t>
-  </si>
-  <si>
-    <t>Альбом юбилейных 2 евро (часть 6)</t>
-  </si>
-  <si>
     <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A0001-GR-BK.html</t>
   </si>
   <si>
@@ -1640,6 +1604,66 @@
   </si>
   <si>
     <t>Сан-Марино (San Marino)</t>
+  </si>
+  <si>
+    <t>A0007-OA-BK</t>
+  </si>
+  <si>
+    <t>A0008-OA-BK</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A0007-OA-BK.html</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A0008-OA-BK.html</t>
+  </si>
+  <si>
+    <t>2 Euro (part 1)</t>
+  </si>
+  <si>
+    <t>2 Euro (part 2)</t>
+  </si>
+  <si>
+    <t>2 Euro (part 3)</t>
+  </si>
+  <si>
+    <t>2 Euro (part 4)</t>
+  </si>
+  <si>
+    <t>2 Euro (part 5)</t>
+  </si>
+  <si>
+    <t>2 Euro (part 6)</t>
+  </si>
+  <si>
+    <t>Юбилейные 2 евро (часть 6)</t>
+  </si>
+  <si>
+    <t>Юбилейные 2 евро (часть 5)</t>
+  </si>
+  <si>
+    <t>Юбилейные 2 евро (часть 4)</t>
+  </si>
+  <si>
+    <t>Юбилейные Монеты США (Двор D)</t>
+  </si>
+  <si>
+    <t>Юбилейные Монеты США (Дворы P и S)</t>
+  </si>
+  <si>
+    <t>Commemorative USA coins (Mints P and S)</t>
+  </si>
+  <si>
+    <t>Commemorative USA coins (Mint D)</t>
+  </si>
+  <si>
+    <t>Юбилейные 2 евро (часть 1)</t>
+  </si>
+  <si>
+    <t>Юбилейные 2 евро (часть 2)</t>
+  </si>
+  <si>
+    <t>Юбилейные 2 евро (часть 3)</t>
   </si>
 </sst>
 </file>
@@ -4242,12 +4266,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DC835FD-69FE-4DBC-957F-9A46CA05517E}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.26953125" customWidth="1"/>
-    <col min="2" max="2" width="22.7265625" customWidth="1"/>
-    <col min="3" max="3" width="33.54296875" customWidth="1"/>
+    <col min="2" max="2" width="38.36328125" customWidth="1"/>
+    <col min="3" max="3" width="41.81640625" customWidth="1"/>
     <col min="4" max="4" width="84.6328125" customWidth="1"/>
     <col min="5" max="5" width="8.453125" customWidth="1"/>
   </cols>
@@ -4260,7 +4284,7 @@
         <v>410</v>
       </c>
       <c r="C1" s="78" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D1" s="78" t="s">
         <v>404</v>
@@ -4271,66 +4295,66 @@
         <v>412</v>
       </c>
       <c r="B2" t="s">
-        <v>491</v>
+        <v>513</v>
       </c>
       <c r="C2" t="s">
-        <v>493</v>
+        <v>526</v>
       </c>
       <c r="D2" s="102" t="s">
-        <v>509</v>
+        <v>497</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B3" t="s">
+        <v>514</v>
+      </c>
+      <c r="C3" t="s">
+        <v>527</v>
+      </c>
+      <c r="D3" s="102" t="s">
         <v>499</v>
-      </c>
-      <c r="C3" t="s">
-        <v>500</v>
-      </c>
-      <c r="D3" s="102" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B4" t="s">
-        <v>501</v>
+        <v>515</v>
       </c>
       <c r="C4" t="s">
-        <v>502</v>
+        <v>528</v>
       </c>
       <c r="D4" s="102" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B5" t="s">
-        <v>503</v>
+        <v>516</v>
       </c>
       <c r="C5" t="s">
-        <v>504</v>
+        <v>521</v>
       </c>
       <c r="D5" s="102" t="s">
-        <v>510</v>
+        <v>498</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B6" t="s">
-        <v>506</v>
+        <v>517</v>
       </c>
       <c r="C6" t="s">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="D6" t="s">
         <v>108</v>
@@ -4338,16 +4362,44 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B7" t="s">
-        <v>507</v>
+        <v>518</v>
       </c>
       <c r="C7" t="s">
-        <v>508</v>
+        <v>519</v>
       </c>
       <c r="D7" t="s">
         <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>509</v>
+      </c>
+      <c r="B8" t="s">
+        <v>524</v>
+      </c>
+      <c r="C8" t="s">
+        <v>523</v>
+      </c>
+      <c r="D8" s="102" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>510</v>
+      </c>
+      <c r="B9" t="s">
+        <v>525</v>
+      </c>
+      <c r="C9" t="s">
+        <v>522</v>
+      </c>
+      <c r="D9" s="102" t="s">
+        <v>512</v>
       </c>
     </row>
   </sheetData>
@@ -4358,10 +4410,12 @@
     <hyperlink ref="D3" r:id="rId2" xr:uid="{CF441EF5-F4BD-438B-8859-6D3EFE142B71}"/>
     <hyperlink ref="D4" r:id="rId3" xr:uid="{FCDDF3A3-0B92-4B7E-84DE-1369DD81862B}"/>
     <hyperlink ref="D5" r:id="rId4" xr:uid="{0D149830-0064-4F8C-AEB1-2BE082CF8F84}"/>
+    <hyperlink ref="D8" r:id="rId5" xr:uid="{890CA23B-C010-4A65-868C-79309E78EA56}"/>
+    <hyperlink ref="D9" r:id="rId6" xr:uid="{E0018DB5-8E36-48D7-AE39-2F84BF07DB13}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
-  <drawing r:id="rId6"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
+  <drawing r:id="rId8"/>
 </worksheet>
 </file>
 
@@ -4736,34 +4790,34 @@
     </row>
     <row r="32" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X32" s="79" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="Y32" t="s">
-        <v>517</v>
+        <v>505</v>
       </c>
     </row>
     <row r="33" spans="14:25" x14ac:dyDescent="0.35">
       <c r="X33" s="79" t="s">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="Y33" t="s">
-        <v>518</v>
+        <v>506</v>
       </c>
     </row>
     <row r="34" spans="14:25" x14ac:dyDescent="0.35">
       <c r="X34" s="79" t="s">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="Y34" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
     </row>
     <row r="35" spans="14:25" x14ac:dyDescent="0.35">
       <c r="X35" s="79" t="s">
-        <v>516</v>
+        <v>504</v>
       </c>
       <c r="Y35" t="s">
-        <v>520</v>
+        <v>508</v>
       </c>
     </row>
     <row r="36" spans="14:25" ht="15.5" x14ac:dyDescent="0.35">

--- a/Info/Additional_information.xlsx
+++ b/Info/Additional_information.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44BF6265-42CE-4E72-862E-FAB0DA48F4F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC1AF2CC-4579-428C-85B9-747526C50181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
     <sheet name="Coin_Shops" sheetId="8" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'albums ID'!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'albums ID'!$B$1:$E$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Colours_specifications!$A$1:$D$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'EURO albums content'!$A$1:$C$15</definedName>
   </definedNames>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="561">
   <si>
     <t>good quality (UNC for UNC collection; UNC and XF for XF collection)</t>
   </si>
@@ -1315,9 +1315,6 @@
     <t>OA</t>
   </si>
   <si>
-    <t>A0001-GD-BK</t>
-  </si>
-  <si>
     <t>Flags (for links)</t>
   </si>
   <si>
@@ -1555,33 +1552,6 @@
     <t>Album Content (ru)</t>
   </si>
   <si>
-    <t>A0002-GD-BK</t>
-  </si>
-  <si>
-    <t>A0003-GD-BK</t>
-  </si>
-  <si>
-    <t>A0004-GD-BK</t>
-  </si>
-  <si>
-    <t>A0005-GD-BK</t>
-  </si>
-  <si>
-    <t>A0006-GD-BK</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A0001-GR-BK.html</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A0004-GR-BK.html</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A0002-GR-BK.html</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A0003-GR-BK.html</t>
-  </si>
-  <si>
     <t>🇻🇦</t>
   </si>
   <si>
@@ -1606,18 +1576,6 @@
     <t>Сан-Марино (San Marino)</t>
   </si>
   <si>
-    <t>A0007-OA-BK</t>
-  </si>
-  <si>
-    <t>A0008-OA-BK</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A0007-OA-BK.html</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A0008-OA-BK.html</t>
-  </si>
-  <si>
     <t>2 Euro (part 1)</t>
   </si>
   <si>
@@ -1645,12 +1603,6 @@
     <t>Юбилейные 2 евро (часть 4)</t>
   </si>
   <si>
-    <t>Юбилейные Монеты США (Двор D)</t>
-  </si>
-  <si>
-    <t>Юбилейные Монеты США (Дворы P и S)</t>
-  </si>
-  <si>
     <t>Commemorative USA coins (Mints P and S)</t>
   </si>
   <si>
@@ -1664,6 +1616,150 @@
   </si>
   <si>
     <t>Юбилейные 2 евро (часть 3)</t>
+  </si>
+  <si>
+    <t>Commemorative Russian Federasion coins (part 1)</t>
+  </si>
+  <si>
+    <t>Commemorative Russian Federasion coins (part 2)</t>
+  </si>
+  <si>
+    <t>Юбилейные монеты США (Двор D)</t>
+  </si>
+  <si>
+    <t>Юбилейные монеты США (Дворы P и S)</t>
+  </si>
+  <si>
+    <t>Юбилейные монеты РФ (часть 1)</t>
+  </si>
+  <si>
+    <t>Юбилейные монеты РФ (часть 2)</t>
+  </si>
+  <si>
+    <t>Регулярные монеты евро (часть 1)</t>
+  </si>
+  <si>
+    <t>Регулярные монеты евро (часть 2)</t>
+  </si>
+  <si>
+    <t>Regular euro coins (part 1)</t>
+  </si>
+  <si>
+    <t>Regular euro coins (part 2)</t>
+  </si>
+  <si>
+    <t>🇧🇬</t>
+  </si>
+  <si>
+    <t>Болгария (Bulgaria)</t>
+  </si>
+  <si>
+    <t>Regular USA coins (Mints P and S)</t>
+  </si>
+  <si>
+    <t>Regular USA coins (Mint D)</t>
+  </si>
+  <si>
+    <t>Регулярные монеты США (Дворы P и S)</t>
+  </si>
+  <si>
+    <t>Регулярные монеты США (Двор D)</t>
+  </si>
+  <si>
+    <t>A001-03-GD-BK</t>
+  </si>
+  <si>
+    <t>Виртуальный альбом</t>
+  </si>
+  <si>
+    <t>Virtual album</t>
+  </si>
+  <si>
+    <t>A001-01-GD-BK</t>
+  </si>
+  <si>
+    <t>A000-00-00-00</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A000-00-00-00.html</t>
+  </si>
+  <si>
+    <t>A001-06-GD-BK</t>
+  </si>
+  <si>
+    <t>A001-05-GD-BK</t>
+  </si>
+  <si>
+    <t>A001-04-GD-BK</t>
+  </si>
+  <si>
+    <t>A001-02-GD-BK</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A001-01-GD-BK.html</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A001-02-GD-BK.html</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A001-03-GD-BK.html</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A001-04-GD-BK.html</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>A002-02-OA-BK</t>
+  </si>
+  <si>
+    <t>A002-01-OA-BK</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A002-01-OA-BK.html</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A002-02-OA-BK.html</t>
+  </si>
+  <si>
+    <t>A003-01-OA-DB</t>
+  </si>
+  <si>
+    <t>A003-02-OA-DB</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A003-01-OA-DB.html</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A003-02-OA-DB.html</t>
+  </si>
+  <si>
+    <t>A004-01-OA-BK</t>
+  </si>
+  <si>
+    <t>A004-02-OA-BK</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A004-01-OA-BK.html</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A004-02-OA-BK.html</t>
+  </si>
+  <si>
+    <t>A005-01-OA-BK</t>
+  </si>
+  <si>
+    <t>A005-02-OA-BK</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A005-01-OA-BK.html</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A005-02-OA-BK.html</t>
+  </si>
+  <si>
+    <t>A006-01-OA-BK</t>
   </si>
 </sst>
 </file>
@@ -3092,22 +3188,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>539750</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>139700</xdr:rowOff>
+      <xdr:colOff>223008</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>102720</xdr:rowOff>
+      <xdr:colOff>15841</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Рисунок 2">
+        <xdr:cNvPr id="2" name="Рисунок 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{320DA919-34E4-48A1-9AE7-B1B277A4600E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D5C5BC0-A332-43E9-8ADB-26F86382A1D1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3123,8 +3219,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10172700" y="742950"/>
-          <a:ext cx="8375650" cy="4566770"/>
+          <a:off x="14345408" y="0"/>
+          <a:ext cx="8327233" cy="4502150"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3140,23 +3236,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>590550</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>146050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>431800</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>121770</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>364333</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Рисунок 1">
+        <xdr:cNvPr id="3" name="Рисунок 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC090D59-0D82-45A0-BE1D-FAFACCD1761B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C4A6C6F-3CC8-4756-B3D9-1E17A62D8C4C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3172,8 +3268,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6775450" y="463550"/>
-          <a:ext cx="8375650" cy="4566770"/>
+          <a:off x="6146800" y="609600"/>
+          <a:ext cx="8327233" cy="4502150"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4266,162 +4362,324 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DC835FD-69FE-4DBC-957F-9A46CA05517E}">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.26953125" customWidth="1"/>
-    <col min="2" max="2" width="38.36328125" customWidth="1"/>
-    <col min="3" max="3" width="41.81640625" customWidth="1"/>
-    <col min="4" max="4" width="84.6328125" customWidth="1"/>
-    <col min="5" max="5" width="8.453125" customWidth="1"/>
+    <col min="1" max="1" width="3.453125" customWidth="1"/>
+    <col min="2" max="2" width="15.54296875" customWidth="1"/>
+    <col min="3" max="3" width="49.54296875" customWidth="1"/>
+    <col min="4" max="4" width="41.81640625" customWidth="1"/>
+    <col min="5" max="5" width="84.6328125" customWidth="1"/>
+    <col min="6" max="6" width="8.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="78" t="s">
+        <v>543</v>
+      </c>
+      <c r="B1" s="78" t="s">
         <v>403</v>
       </c>
-      <c r="B1" s="78" t="s">
+      <c r="C1" s="78" t="s">
         <v>410</v>
       </c>
-      <c r="C1" s="78" t="s">
-        <v>491</v>
-      </c>
       <c r="D1" s="78" t="s">
+        <v>490</v>
+      </c>
+      <c r="E1" s="78" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>412</v>
+    <row r="2" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>533</v>
+      </c>
+      <c r="C2" t="s">
+        <v>531</v>
+      </c>
+      <c r="D2" t="s">
+        <v>530</v>
+      </c>
+      <c r="E2" s="102" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>532</v>
+      </c>
+      <c r="C3" t="s">
+        <v>499</v>
+      </c>
+      <c r="D3" t="s">
+        <v>510</v>
+      </c>
+      <c r="E3" s="102" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>538</v>
+      </c>
+      <c r="C4" t="s">
+        <v>500</v>
+      </c>
+      <c r="D4" t="s">
+        <v>511</v>
+      </c>
+      <c r="E4" s="102" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>529</v>
+      </c>
+      <c r="C5" t="s">
+        <v>501</v>
+      </c>
+      <c r="D5" t="s">
+        <v>512</v>
+      </c>
+      <c r="E5" s="102" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>537</v>
+      </c>
+      <c r="C6" t="s">
+        <v>502</v>
+      </c>
+      <c r="D6" t="s">
+        <v>507</v>
+      </c>
+      <c r="E6" s="102" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>536</v>
+      </c>
+      <c r="C7" t="s">
+        <v>503</v>
+      </c>
+      <c r="D7" t="s">
+        <v>506</v>
+      </c>
+      <c r="E7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>535</v>
+      </c>
+      <c r="C8" t="s">
+        <v>504</v>
+      </c>
+      <c r="D8" t="s">
+        <v>505</v>
+      </c>
+      <c r="E8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>545</v>
+      </c>
+      <c r="C9" t="s">
+        <v>508</v>
+      </c>
+      <c r="D9" t="s">
+        <v>516</v>
+      </c>
+      <c r="E9" s="102" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>544</v>
+      </c>
+      <c r="C10" t="s">
+        <v>509</v>
+      </c>
+      <c r="D10" t="s">
+        <v>515</v>
+      </c>
+      <c r="E10" s="102" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>548</v>
+      </c>
+      <c r="C11" t="s">
         <v>513</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D11" t="s">
+        <v>517</v>
+      </c>
+      <c r="E11" s="102" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>549</v>
+      </c>
+      <c r="C12" t="s">
+        <v>514</v>
+      </c>
+      <c r="D12" t="s">
+        <v>518</v>
+      </c>
+      <c r="E12" s="102" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>552</v>
+      </c>
+      <c r="C13" t="s">
+        <v>521</v>
+      </c>
+      <c r="D13" t="s">
+        <v>519</v>
+      </c>
+      <c r="E13" s="102" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>553</v>
+      </c>
+      <c r="C14" t="s">
+        <v>522</v>
+      </c>
+      <c r="D14" t="s">
+        <v>520</v>
+      </c>
+      <c r="E14" s="102" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>556</v>
+      </c>
+      <c r="C15" t="s">
+        <v>525</v>
+      </c>
+      <c r="D15" t="s">
+        <v>527</v>
+      </c>
+      <c r="E15" s="102" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>557</v>
+      </c>
+      <c r="C16" t="s">
         <v>526</v>
       </c>
-      <c r="D2" s="102" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>492</v>
-      </c>
-      <c r="B3" t="s">
-        <v>514</v>
-      </c>
-      <c r="C3" t="s">
-        <v>527</v>
-      </c>
-      <c r="D3" s="102" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>493</v>
-      </c>
-      <c r="B4" t="s">
-        <v>515</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="D16" t="s">
         <v>528</v>
       </c>
-      <c r="D4" s="102" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>494</v>
-      </c>
-      <c r="B5" t="s">
-        <v>516</v>
-      </c>
-      <c r="C5" t="s">
-        <v>521</v>
-      </c>
-      <c r="D5" s="102" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>495</v>
-      </c>
-      <c r="B6" t="s">
-        <v>517</v>
-      </c>
-      <c r="C6" t="s">
-        <v>520</v>
-      </c>
-      <c r="D6" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>496</v>
-      </c>
-      <c r="B7" t="s">
-        <v>518</v>
-      </c>
-      <c r="C7" t="s">
-        <v>519</v>
-      </c>
-      <c r="D7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>509</v>
-      </c>
-      <c r="B8" t="s">
-        <v>524</v>
-      </c>
-      <c r="C8" t="s">
-        <v>523</v>
-      </c>
-      <c r="D8" s="102" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>510</v>
-      </c>
-      <c r="B9" t="s">
-        <v>525</v>
-      </c>
-      <c r="C9" t="s">
-        <v>522</v>
-      </c>
-      <c r="D9" s="102" t="s">
-        <v>512</v>
+      <c r="E16" s="102" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>560</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D1" xr:uid="{1DC835FD-69FE-4DBC-957F-9A46CA05517E}"/>
+  <autoFilter ref="B1:E1" xr:uid="{1DC835FD-69FE-4DBC-957F-9A46CA05517E}"/>
   <phoneticPr fontId="18" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{202A29D0-9EE0-4193-BB2A-5199720DC977}"/>
-    <hyperlink ref="D3" r:id="rId2" xr:uid="{CF441EF5-F4BD-438B-8859-6D3EFE142B71}"/>
-    <hyperlink ref="D4" r:id="rId3" xr:uid="{FCDDF3A3-0B92-4B7E-84DE-1369DD81862B}"/>
-    <hyperlink ref="D5" r:id="rId4" xr:uid="{0D149830-0064-4F8C-AEB1-2BE082CF8F84}"/>
-    <hyperlink ref="D8" r:id="rId5" xr:uid="{890CA23B-C010-4A65-868C-79309E78EA56}"/>
-    <hyperlink ref="D9" r:id="rId6" xr:uid="{E0018DB5-8E36-48D7-AE39-2F84BF07DB13}"/>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{A9DAC5E2-B569-49C7-B7C7-5FB2F0F45121}"/>
+    <hyperlink ref="E3" r:id="rId2" xr:uid="{33229A5C-B9EF-446E-B26C-5E9B3367FC6A}"/>
+    <hyperlink ref="E4" r:id="rId3" xr:uid="{E92AA73C-477D-491C-B552-06044006752C}"/>
+    <hyperlink ref="E5" r:id="rId4" xr:uid="{46F4B82E-CA81-4179-8D28-AC8C124F710A}"/>
+    <hyperlink ref="E6" r:id="rId5" xr:uid="{C6A03004-EF3C-49D6-8ACE-BE0675BA0CCC}"/>
+    <hyperlink ref="E9" r:id="rId6" xr:uid="{6FD5A6C1-19A0-4B26-8171-7C4526375D06}"/>
+    <hyperlink ref="E10" r:id="rId7" xr:uid="{055F54FF-C230-49E3-8AD3-39B18FF220A9}"/>
+    <hyperlink ref="E11" r:id="rId8" xr:uid="{9F0940F2-1A8A-4E23-95C1-A7D4AE8ED2FC}"/>
+    <hyperlink ref="E12" r:id="rId9" xr:uid="{5E911F10-CBF5-4238-ADB1-11E959F15120}"/>
+    <hyperlink ref="E13" r:id="rId10" xr:uid="{8862EA93-397B-43EB-950D-E7CA51E64B3F}"/>
+    <hyperlink ref="E14" r:id="rId11" xr:uid="{8200010C-9C93-4E8D-8296-12B7EC7B60F9}"/>
+    <hyperlink ref="E15" r:id="rId12" xr:uid="{37ED73B8-7E15-4DEB-825D-F64E0DFBF76A}"/>
+    <hyperlink ref="E16" r:id="rId13" xr:uid="{5232A4EB-1465-4673-AA0F-DE4AFAAFFFF6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
-  <drawing r:id="rId8"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId14"/>
+  <drawing r:id="rId15"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{866E9A5E-386D-439E-AA25-CB46A31C625C}">
-  <dimension ref="A1:Y50"/>
+  <dimension ref="A1:Z50"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.453125" style="77" customWidth="1"/>
@@ -4447,7 +4705,7 @@
         <v>402</v>
       </c>
       <c r="W1" s="101" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="X1" s="101"/>
       <c r="Y1" s="101"/>
@@ -4483,10 +4741,10 @@
         <v>389</v>
       </c>
       <c r="X3" s="79" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="Y3" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.35">
@@ -4503,10 +4761,10 @@
         <v>9</v>
       </c>
       <c r="X4" s="79" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="Y4" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.35">
@@ -4517,10 +4775,10 @@
         <v>10</v>
       </c>
       <c r="X5" s="79" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Y5" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.35">
@@ -4531,10 +4789,10 @@
         <v>13</v>
       </c>
       <c r="X6" s="79" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="Y6" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.35">
@@ -4545,10 +4803,10 @@
         <v>390</v>
       </c>
       <c r="X7" s="79" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="Y7" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.35">
@@ -4559,10 +4817,10 @@
         <v>391</v>
       </c>
       <c r="X8" s="79" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="Y8" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.35">
@@ -4573,10 +4831,10 @@
         <v>11</v>
       </c>
       <c r="X9" s="79" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="Y9" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="10" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
@@ -4587,7 +4845,7 @@
         <v>392</v>
       </c>
       <c r="W10" s="81" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.35">
@@ -4598,10 +4856,10 @@
         <v>393</v>
       </c>
       <c r="X11" s="79" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="Y11" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.35">
@@ -4612,10 +4870,10 @@
         <v>394</v>
       </c>
       <c r="X12" s="79" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="Y12" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.35">
@@ -4626,10 +4884,10 @@
         <v>395</v>
       </c>
       <c r="X13" s="79" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="Y13" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.35">
@@ -4640,10 +4898,10 @@
         <v>396</v>
       </c>
       <c r="X14" s="79" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="Y14" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.35">
@@ -4654,275 +4912,279 @@
         <v>373</v>
       </c>
       <c r="X15" s="79" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="Y15" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.35">
       <c r="X16" s="79" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="Y16" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="17" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X17" s="79" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="Y17" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="18" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X18" s="79" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="Y18" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="19" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X19" s="79" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="Y19" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="20" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X20" s="79" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="Y20" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="21" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X21" s="79" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="Y21" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="22" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X22" s="79" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="Y22" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="23" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X23" s="79" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="Y23" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="24" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X24" s="79" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="Y24" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="25" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X25" s="79" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Y25" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="26" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X26" s="79" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="Y26" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="27" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X27" s="79" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="Y27" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="28" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X28" s="79" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="Y28" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="29" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X29" s="79" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Y29" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="30" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X30" s="79" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="Y30" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="31" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X31" s="79" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Y31" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="32" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X32" s="79" t="s">
-        <v>501</v>
+        <v>491</v>
       </c>
       <c r="Y32" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="33" spans="14:25" x14ac:dyDescent="0.35">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="33" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X33" s="79" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="Y33" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="34" spans="14:25" x14ac:dyDescent="0.35">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="34" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X34" s="79" t="s">
-        <v>503</v>
+        <v>493</v>
       </c>
       <c r="Y34" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="35" spans="14:25" x14ac:dyDescent="0.35">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="35" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X35" s="79" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="Y35" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="36" spans="14:25" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="W36" s="81" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="36" spans="23:26" x14ac:dyDescent="0.35">
+      <c r="X36" s="79" t="s">
+        <v>523</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="37" spans="23:26" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="W37" s="81" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="37" spans="14:25" x14ac:dyDescent="0.35">
-      <c r="X37" s="79" t="s">
+    <row r="38" spans="23:26" x14ac:dyDescent="0.35">
+      <c r="X38" s="79" t="s">
+        <v>441</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="39" spans="23:26" x14ac:dyDescent="0.35">
+      <c r="X39" s="79" t="s">
         <v>442</v>
       </c>
-      <c r="Y37" t="s">
+      <c r="Y39" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="38" spans="14:25" x14ac:dyDescent="0.35">
-      <c r="X38" s="79" t="s">
+    <row r="40" spans="23:26" x14ac:dyDescent="0.35">
+      <c r="X40" s="79" t="s">
         <v>443</v>
       </c>
-      <c r="Y38" t="s">
+      <c r="Y40" t="s">
         <v>481</v>
       </c>
-    </row>
-    <row r="39" spans="14:25" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="N39" s="81"/>
-      <c r="X39" s="79" t="s">
+      <c r="Z40" s="79"/>
+    </row>
+    <row r="41" spans="23:26" x14ac:dyDescent="0.35">
+      <c r="X41" s="79" t="s">
         <v>444</v>
       </c>
-      <c r="Y39" t="s">
+      <c r="Y41" t="s">
         <v>482</v>
       </c>
-    </row>
-    <row r="40" spans="14:25" x14ac:dyDescent="0.35">
-      <c r="O40" s="79"/>
-      <c r="X40" s="79" t="s">
+      <c r="Z41" s="79"/>
+    </row>
+    <row r="42" spans="23:26" x14ac:dyDescent="0.35">
+      <c r="X42" s="79" t="s">
         <v>445</v>
       </c>
-      <c r="Y40" t="s">
+      <c r="Y42" t="s">
         <v>483</v>
       </c>
-    </row>
-    <row r="41" spans="14:25" x14ac:dyDescent="0.35">
-      <c r="O41" s="79"/>
-      <c r="X41" s="79" t="s">
+      <c r="Z42" s="79"/>
+    </row>
+    <row r="43" spans="23:26" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="W43" s="81" t="s">
+        <v>409</v>
+      </c>
+      <c r="X43" s="80"/>
+      <c r="Z43" s="79"/>
+    </row>
+    <row r="44" spans="23:26" x14ac:dyDescent="0.35">
+      <c r="X44" s="79" t="s">
         <v>446</v>
       </c>
-      <c r="Y41" t="s">
+      <c r="Y44" t="s">
         <v>484</v>
       </c>
-    </row>
-    <row r="42" spans="14:25" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="O42" s="79"/>
-      <c r="W42" s="81" t="s">
-        <v>409</v>
-      </c>
-      <c r="X42" s="80"/>
-    </row>
-    <row r="43" spans="14:25" x14ac:dyDescent="0.35">
-      <c r="O43" s="79"/>
-      <c r="X43" s="79" t="s">
+      <c r="Z44" s="79"/>
+    </row>
+    <row r="45" spans="23:26" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="X45" s="79" t="s">
         <v>447</v>
       </c>
-      <c r="Y43" t="s">
+      <c r="Y45" t="s">
         <v>485</v>
       </c>
-    </row>
-    <row r="44" spans="14:25" x14ac:dyDescent="0.35">
-      <c r="O44" s="79"/>
-      <c r="X44" s="79" t="s">
+      <c r="Z45" s="80"/>
+    </row>
+    <row r="46" spans="23:26" x14ac:dyDescent="0.35">
+      <c r="X46" s="79" t="s">
         <v>448</v>
       </c>
-      <c r="Y44" t="s">
+      <c r="Y46" t="s">
         <v>486</v>
       </c>
-    </row>
-    <row r="45" spans="14:25" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="N45" s="81"/>
-      <c r="O45" s="80"/>
-      <c r="X45" s="79" t="s">
+      <c r="Z46" s="79"/>
+    </row>
+    <row r="47" spans="23:26" x14ac:dyDescent="0.35">
+      <c r="X47" s="79" t="s">
         <v>449</v>
       </c>
-      <c r="Y45" t="s">
+      <c r="Y47" t="s">
         <v>487</v>
       </c>
-    </row>
-    <row r="46" spans="14:25" x14ac:dyDescent="0.35">
-      <c r="O46" s="79"/>
-      <c r="X46" s="79" t="s">
+      <c r="Z47" s="79"/>
+    </row>
+    <row r="48" spans="23:26" x14ac:dyDescent="0.35">
+      <c r="X48" s="79" t="s">
         <v>450</v>
       </c>
-      <c r="Y46" t="s">
+      <c r="Y48" t="s">
         <v>488</v>
       </c>
-    </row>
-    <row r="47" spans="14:25" x14ac:dyDescent="0.35">
-      <c r="O47" s="79"/>
-      <c r="X47" s="79" t="s">
-        <v>451</v>
-      </c>
-      <c r="Y47" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="48" spans="14:25" x14ac:dyDescent="0.35">
-      <c r="O48" s="79"/>
+      <c r="Z48" s="79"/>
     </row>
     <row r="49" spans="15:15" x14ac:dyDescent="0.35">
       <c r="O49" s="79"/>

--- a/Info/Additional_information.xlsx
+++ b/Info/Additional_information.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC1AF2CC-4579-428C-85B9-747526C50181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DEE3F75-7B12-4D2C-9DE3-A0CADF339F85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="614">
   <si>
     <t>good quality (UNC for UNC collection; UNC and XF for XF collection)</t>
   </si>
@@ -1759,7 +1759,166 @@
     <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A005-02-OA-BK.html</t>
   </si>
   <si>
-    <t>A006-01-OA-BK</t>
+    <t xml:space="preserve">Регулярные монеты РФ </t>
+  </si>
+  <si>
+    <t>Regular Russian Federasion coins</t>
+  </si>
+  <si>
+    <t>BU</t>
+  </si>
+  <si>
+    <t>Burgundy</t>
+  </si>
+  <si>
+    <t>A006-01-OA-BU</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A006-01-OA-BU.html</t>
+  </si>
+  <si>
+    <t>USSR commemorative and regular coins</t>
+  </si>
+  <si>
+    <t>Советские юбилейные и регулярные монеты</t>
+  </si>
+  <si>
+    <t>A007-01-OA-BK</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A007-01-OA-BK.html</t>
+  </si>
+  <si>
+    <t>A008-01-OA-BK</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A008-01-OA-BK.html</t>
+  </si>
+  <si>
+    <t>DN</t>
+  </si>
+  <si>
+    <t>Dark Brown</t>
+  </si>
+  <si>
+    <t>A009-01-FB-BN</t>
+  </si>
+  <si>
+    <t>A009-02-FB-BN</t>
+  </si>
+  <si>
+    <t>LN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Light Brown</t>
+  </si>
+  <si>
+    <t>Kazachstan, Indian, Russian Empire coins</t>
+  </si>
+  <si>
+    <t>Монеты Казахстана, Индии, Российской империи</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A009-01-FB-BN.html</t>
+  </si>
+  <si>
+    <t>Great Britain, Ukrainian and German coins</t>
+  </si>
+  <si>
+    <t>Монеты Великобритании, Украины и Германии</t>
+  </si>
+  <si>
+    <t>Spain and Canada regular and commemorative coins</t>
+  </si>
+  <si>
+    <t>Регулярные и юбилейныеонеты Испании и Канады</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A009-02-FB-BN.html</t>
+  </si>
+  <si>
+    <t>A009-03-FB-BN</t>
+  </si>
+  <si>
+    <t>A009-04-FB-DN</t>
+  </si>
+  <si>
+    <t>Монеты мира (Азия)</t>
+  </si>
+  <si>
+    <t>Монеты мира (Европа, Америка, Африка, Австралия и Океания)</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A009-03-FB-BN.html</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A009-04-FB-DN.html</t>
+  </si>
+  <si>
+    <t>Банкноты мира</t>
+  </si>
+  <si>
+    <t>World banknotes</t>
+  </si>
+  <si>
+    <t>World coins (Asia)</t>
+  </si>
+  <si>
+    <t>World coins (Europe, America, Africa, Australia and Oceania)</t>
+  </si>
+  <si>
+    <t>A010-01-OA-DB</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A010-01-OA-DB.html</t>
+  </si>
+  <si>
+    <t>A011-01-OA-GR</t>
+  </si>
+  <si>
+    <t>Tickets (part 1) to the theater, museums, concerts and performances</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A011-01-OA-GR.html</t>
+  </si>
+  <si>
+    <t>A011-02-OA-GR</t>
+  </si>
+  <si>
+    <t>Билеты (часть 1) в театры, музеи, на концерты и спектакли</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A011-02-OA-GR.html</t>
+  </si>
+  <si>
+    <t>Билеты (часть 2) в паркии, кино, на особые события, на поезда, на самолёты. Различные жетоны</t>
+  </si>
+  <si>
+    <t>Tickets (part 2) for parks, cinemas, special events, trains, and planes. Various tokens</t>
+  </si>
+  <si>
+    <t>Билеты на метро, проездные трамвайные билеты. Жетоны метро</t>
+  </si>
+  <si>
+    <t>A012-01-OA-BU</t>
+  </si>
+  <si>
+    <t>Tickets for metro, tram passes. Metro tokens</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A012-01-OA-BU.html</t>
+  </si>
+  <si>
+    <t>A013-01-OA-LN</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A013-01-OA-LN.html</t>
+  </si>
+  <si>
+    <t>Пластиковые карты</t>
+  </si>
+  <si>
+    <t>Plastic cards</t>
   </si>
 </sst>
 </file>
@@ -2351,7 +2510,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2575,6 +2734,8 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="20" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2626,7 +2787,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -3187,55 +3347,6 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>223008</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>15841</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>31750</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Рисунок 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D5C5BC0-A332-43E9-8ADB-26F86382A1D1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14345408" y="0"/>
-          <a:ext cx="8327233" cy="4502150"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>571500</xdr:colOff>
       <xdr:row>1</xdr:row>
@@ -4062,10 +4173,10 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" s="89">
+      <c r="A2" s="91">
         <v>1</v>
       </c>
-      <c r="B2" s="97">
+      <c r="B2" s="99">
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
@@ -4082,8 +4193,8 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" s="90"/>
-      <c r="B3" s="97"/>
+      <c r="A3" s="92"/>
+      <c r="B3" s="99"/>
       <c r="C3" s="4" t="s">
         <v>65</v>
       </c>
@@ -4098,8 +4209,8 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" s="91"/>
-      <c r="B4" s="98">
+      <c r="A4" s="93"/>
+      <c r="B4" s="100">
         <v>2</v>
       </c>
       <c r="C4" s="4" t="s">
@@ -4116,14 +4227,14 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" s="91"/>
-      <c r="B5" s="98"/>
+      <c r="A5" s="93"/>
+      <c r="B5" s="100"/>
       <c r="C5" s="4" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6" s="91"/>
+      <c r="A6" s="93"/>
       <c r="B6" s="15">
         <v>3</v>
       </c>
@@ -4132,7 +4243,7 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" s="91"/>
+      <c r="A7" s="93"/>
       <c r="B7" s="16" t="s">
         <v>90</v>
       </c>
@@ -4141,8 +4252,8 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" s="91"/>
-      <c r="B8" s="99">
+      <c r="A8" s="93"/>
+      <c r="B8" s="101">
         <v>6</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -4150,14 +4261,14 @@
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="91"/>
-      <c r="B9" s="100"/>
+      <c r="A9" s="93"/>
+      <c r="B9" s="102"/>
       <c r="C9" s="4" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A10" s="91"/>
+      <c r="A10" s="93"/>
       <c r="B10" s="17">
         <v>7</v>
       </c>
@@ -4166,14 +4277,14 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="91"/>
+      <c r="A11" s="93"/>
       <c r="B11" s="24"/>
       <c r="C11" s="4" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="91"/>
+      <c r="A12" s="93"/>
       <c r="B12" s="18">
         <v>8</v>
       </c>
@@ -4182,7 +4293,7 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" s="92"/>
+      <c r="A13" s="94"/>
       <c r="B13" s="25" t="s">
         <v>78</v>
       </c>
@@ -4191,7 +4302,7 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="93"/>
+      <c r="A14" s="95"/>
       <c r="B14" s="26" t="s">
         <v>91</v>
       </c>
@@ -4200,7 +4311,7 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="14.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="94">
+      <c r="A15" s="96">
         <v>2</v>
       </c>
       <c r="B15" s="19" t="s">
@@ -4211,7 +4322,7 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="95"/>
+      <c r="A16" s="97"/>
       <c r="B16" s="20" t="s">
         <v>365</v>
       </c>
@@ -4220,7 +4331,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="95"/>
+      <c r="A17" s="97"/>
       <c r="B17" s="21" t="s">
         <v>366</v>
       </c>
@@ -4229,7 +4340,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="96"/>
+      <c r="A18" s="98"/>
       <c r="B18" s="22" t="s">
         <v>92</v>
       </c>
@@ -4238,7 +4349,7 @@
       </c>
     </row>
     <row r="19" spans="1:3" ht="14.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="83">
+      <c r="A19" s="85">
         <v>3</v>
       </c>
       <c r="B19" s="23" t="s">
@@ -4249,7 +4360,7 @@
       </c>
     </row>
     <row r="20" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="84"/>
+      <c r="A20" s="86"/>
       <c r="B20" s="27" t="s">
         <v>93</v>
       </c>
@@ -4258,7 +4369,7 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="85"/>
+      <c r="A21" s="87"/>
       <c r="B21" s="28" t="s">
         <v>95</v>
       </c>
@@ -4267,7 +4378,7 @@
       </c>
     </row>
     <row r="22" spans="1:3" ht="14.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="86">
+      <c r="A22" s="88">
         <v>4</v>
       </c>
       <c r="B22" s="19" t="s">
@@ -4278,7 +4389,7 @@
       </c>
     </row>
     <row r="23" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="87"/>
+      <c r="A23" s="89"/>
       <c r="B23" s="20" t="s">
         <v>98</v>
       </c>
@@ -4287,7 +4398,7 @@
       </c>
     </row>
     <row r="24" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="87"/>
+      <c r="A24" s="89"/>
       <c r="B24" s="21" t="s">
         <v>100</v>
       </c>
@@ -4296,7 +4407,7 @@
       </c>
     </row>
     <row r="25" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="87"/>
+      <c r="A25" s="89"/>
       <c r="B25" s="16" t="s">
         <v>102</v>
       </c>
@@ -4305,7 +4416,7 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" s="87"/>
+      <c r="A26" s="89"/>
       <c r="B26" s="29" t="s">
         <v>104</v>
       </c>
@@ -4314,7 +4425,7 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" s="87"/>
+      <c r="A27" s="89"/>
       <c r="B27" s="30" t="s">
         <v>106</v>
       </c>
@@ -4323,7 +4434,7 @@
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" s="87"/>
+      <c r="A28" s="89"/>
       <c r="B28" s="18">
         <v>8</v>
       </c>
@@ -4332,7 +4443,7 @@
       </c>
     </row>
     <row r="29" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="88"/>
+      <c r="A29" s="90"/>
       <c r="B29" s="31" t="s">
         <v>78</v>
       </c>
@@ -4362,13 +4473,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DC835FD-69FE-4DBC-957F-9A46CA05517E}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.453125" customWidth="1"/>
     <col min="2" max="2" width="15.54296875" customWidth="1"/>
-    <col min="3" max="3" width="49.54296875" customWidth="1"/>
-    <col min="4" max="4" width="41.81640625" customWidth="1"/>
+    <col min="3" max="3" width="70" customWidth="1"/>
+    <col min="4" max="4" width="89.08984375" customWidth="1"/>
     <col min="5" max="5" width="84.6328125" customWidth="1"/>
     <col min="6" max="6" width="8.453125" customWidth="1"/>
   </cols>
@@ -4403,7 +4514,7 @@
       <c r="D2" t="s">
         <v>530</v>
       </c>
-      <c r="E2" s="102" t="s">
+      <c r="E2" s="83" t="s">
         <v>534</v>
       </c>
     </row>
@@ -4420,7 +4531,7 @@
       <c r="D3" t="s">
         <v>510</v>
       </c>
-      <c r="E3" s="102" t="s">
+      <c r="E3" s="83" t="s">
         <v>539</v>
       </c>
     </row>
@@ -4437,7 +4548,7 @@
       <c r="D4" t="s">
         <v>511</v>
       </c>
-      <c r="E4" s="102" t="s">
+      <c r="E4" s="83" t="s">
         <v>540</v>
       </c>
     </row>
@@ -4454,7 +4565,7 @@
       <c r="D5" t="s">
         <v>512</v>
       </c>
-      <c r="E5" s="102" t="s">
+      <c r="E5" s="83" t="s">
         <v>541</v>
       </c>
     </row>
@@ -4471,7 +4582,7 @@
       <c r="D6" t="s">
         <v>507</v>
       </c>
-      <c r="E6" s="102" t="s">
+      <c r="E6" s="83" t="s">
         <v>542</v>
       </c>
     </row>
@@ -4522,7 +4633,7 @@
       <c r="D9" t="s">
         <v>516</v>
       </c>
-      <c r="E9" s="102" t="s">
+      <c r="E9" s="83" t="s">
         <v>546</v>
       </c>
     </row>
@@ -4539,7 +4650,7 @@
       <c r="D10" t="s">
         <v>515</v>
       </c>
-      <c r="E10" s="102" t="s">
+      <c r="E10" s="83" t="s">
         <v>547</v>
       </c>
     </row>
@@ -4556,7 +4667,7 @@
       <c r="D11" t="s">
         <v>517</v>
       </c>
-      <c r="E11" s="102" t="s">
+      <c r="E11" s="83" t="s">
         <v>550</v>
       </c>
     </row>
@@ -4573,7 +4684,7 @@
       <c r="D12" t="s">
         <v>518</v>
       </c>
-      <c r="E12" s="102" t="s">
+      <c r="E12" s="83" t="s">
         <v>551</v>
       </c>
     </row>
@@ -4590,7 +4701,7 @@
       <c r="D13" t="s">
         <v>519</v>
       </c>
-      <c r="E13" s="102" t="s">
+      <c r="E13" s="83" t="s">
         <v>554</v>
       </c>
     </row>
@@ -4607,7 +4718,7 @@
       <c r="D14" t="s">
         <v>520</v>
       </c>
-      <c r="E14" s="102" t="s">
+      <c r="E14" s="83" t="s">
         <v>555</v>
       </c>
     </row>
@@ -4624,7 +4735,7 @@
       <c r="D15" t="s">
         <v>527</v>
       </c>
-      <c r="E15" s="102" t="s">
+      <c r="E15" s="83" t="s">
         <v>558</v>
       </c>
     </row>
@@ -4641,16 +4752,212 @@
       <c r="D16" t="s">
         <v>528</v>
       </c>
-      <c r="E16" s="102" t="s">
+      <c r="E16" s="83" t="s">
         <v>559</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>15</v>
       </c>
       <c r="B17" t="s">
+        <v>564</v>
+      </c>
+      <c r="C17" t="s">
+        <v>561</v>
+      </c>
+      <c r="D17" t="s">
         <v>560</v>
+      </c>
+      <c r="E17" s="83" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>568</v>
+      </c>
+      <c r="C18" t="s">
+        <v>566</v>
+      </c>
+      <c r="D18" t="s">
+        <v>567</v>
+      </c>
+      <c r="E18" s="83" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>570</v>
+      </c>
+      <c r="C19" t="s">
+        <v>583</v>
+      </c>
+      <c r="D19" t="s">
+        <v>584</v>
+      </c>
+      <c r="E19" s="83" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>574</v>
+      </c>
+      <c r="C20" t="s">
+        <v>578</v>
+      </c>
+      <c r="D20" t="s">
+        <v>579</v>
+      </c>
+      <c r="E20" s="83" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
+        <v>575</v>
+      </c>
+      <c r="C21" t="s">
+        <v>581</v>
+      </c>
+      <c r="D21" t="s">
+        <v>582</v>
+      </c>
+      <c r="E21" s="83" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>586</v>
+      </c>
+      <c r="C22" t="s">
+        <v>595</v>
+      </c>
+      <c r="D22" t="s">
+        <v>589</v>
+      </c>
+      <c r="E22" s="83" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>587</v>
+      </c>
+      <c r="C23" t="s">
+        <v>594</v>
+      </c>
+      <c r="D23" t="s">
+        <v>588</v>
+      </c>
+      <c r="E23" s="83" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>596</v>
+      </c>
+      <c r="C24" t="s">
+        <v>593</v>
+      </c>
+      <c r="D24" t="s">
+        <v>592</v>
+      </c>
+      <c r="E24" s="83" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s">
+        <v>598</v>
+      </c>
+      <c r="C25" t="s">
+        <v>599</v>
+      </c>
+      <c r="D25" t="s">
+        <v>602</v>
+      </c>
+      <c r="E25" s="83" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26" t="s">
+        <v>601</v>
+      </c>
+      <c r="C26" t="s">
+        <v>605</v>
+      </c>
+      <c r="D26" t="s">
+        <v>604</v>
+      </c>
+      <c r="E26" s="83" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>607</v>
+      </c>
+      <c r="C27" t="s">
+        <v>608</v>
+      </c>
+      <c r="D27" t="s">
+        <v>606</v>
+      </c>
+      <c r="E27" s="83" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s">
+        <v>610</v>
+      </c>
+      <c r="C28" t="s">
+        <v>613</v>
+      </c>
+      <c r="D28" t="s">
+        <v>612</v>
+      </c>
+      <c r="E28" s="83" t="s">
+        <v>611</v>
       </c>
     </row>
   </sheetData>
@@ -4670,10 +4977,21 @@
     <hyperlink ref="E14" r:id="rId11" xr:uid="{8200010C-9C93-4E8D-8296-12B7EC7B60F9}"/>
     <hyperlink ref="E15" r:id="rId12" xr:uid="{37ED73B8-7E15-4DEB-825D-F64E0DFBF76A}"/>
     <hyperlink ref="E16" r:id="rId13" xr:uid="{5232A4EB-1465-4673-AA0F-DE4AFAAFFFF6}"/>
+    <hyperlink ref="E17" r:id="rId14" xr:uid="{BB9C39F4-10B9-4609-B013-760BBB7F8EFB}"/>
+    <hyperlink ref="E18" r:id="rId15" xr:uid="{D6DAB22F-8554-40C2-BC8F-DB4FE657DEE9}"/>
+    <hyperlink ref="E19" r:id="rId16" xr:uid="{64EBF9BB-DC33-40A2-9BE8-3F6E300B72B4}"/>
+    <hyperlink ref="E20" r:id="rId17" xr:uid="{D5AC7FB8-8438-4C97-A0DD-85AEE0D9D86C}"/>
+    <hyperlink ref="E21" r:id="rId18" xr:uid="{EC2C4800-EA3C-4E26-8261-C6A03A377983}"/>
+    <hyperlink ref="E22" r:id="rId19" xr:uid="{84B2B169-2119-45C3-BD04-4482D7704951}"/>
+    <hyperlink ref="E23" r:id="rId20" xr:uid="{50B15920-8FF5-4A31-A3B6-630BFE6B7256}"/>
+    <hyperlink ref="E24" r:id="rId21" xr:uid="{CEF53131-34F9-40EB-8CC6-385E2C745B2A}"/>
+    <hyperlink ref="E25" r:id="rId22" xr:uid="{59E99A6F-25C8-4D24-898D-69FF859E9ADC}"/>
+    <hyperlink ref="E26" r:id="rId23" xr:uid="{99417517-FEFC-4B15-8968-043D037E8B12}"/>
+    <hyperlink ref="E27" r:id="rId24" xr:uid="{26F0F77D-076A-435A-A497-02AC8B18D716}"/>
+    <hyperlink ref="E28" r:id="rId25" xr:uid="{4275CB21-59E8-4194-8A88-6E70460DDA71}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId14"/>
-  <drawing r:id="rId15"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId26"/>
 </worksheet>
 </file>
 
@@ -4704,11 +5022,11 @@
       <c r="D1" s="72" t="s">
         <v>402</v>
       </c>
-      <c r="W1" s="101" t="s">
+      <c r="W1" s="103" t="s">
         <v>412</v>
       </c>
-      <c r="X1" s="101"/>
-      <c r="Y1" s="101"/>
+      <c r="X1" s="103"/>
+      <c r="Y1" s="103"/>
     </row>
     <row r="2" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="77" t="s">
@@ -4797,10 +5115,10 @@
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.35">
       <c r="C7" s="73" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D7" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="X7" s="79" t="s">
         <v>417</v>
@@ -4811,10 +5129,10 @@
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.35">
       <c r="C8" s="73" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D8" t="s">
-        <v>391</v>
+        <v>11</v>
       </c>
       <c r="X8" s="79" t="s">
         <v>418</v>
@@ -4825,10 +5143,10 @@
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.35">
       <c r="C9" s="73" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D9" t="s">
-        <v>11</v>
+        <v>392</v>
       </c>
       <c r="X9" s="79" t="s">
         <v>419</v>
@@ -4839,10 +5157,10 @@
     </row>
     <row r="10" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C10" s="73" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D10" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="W10" s="81" t="s">
         <v>489</v>
@@ -4850,10 +5168,10 @@
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.35">
       <c r="C11" s="73" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D11" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="X11" s="79" t="s">
         <v>420</v>
@@ -4864,10 +5182,10 @@
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.35">
       <c r="C12" s="73" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D12" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="X12" s="79" t="s">
         <v>421</v>
@@ -4878,10 +5196,10 @@
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.35">
       <c r="C13" s="73" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D13" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="X13" s="79" t="s">
         <v>422</v>
@@ -4892,10 +5210,10 @@
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.35">
       <c r="C14" s="73" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D14" t="s">
-        <v>396</v>
+        <v>373</v>
       </c>
       <c r="X14" s="79" t="s">
         <v>423</v>
@@ -4905,11 +5223,11 @@
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="C15" s="73" t="s">
-        <v>387</v>
+      <c r="C15" s="84" t="s">
+        <v>562</v>
       </c>
       <c r="D15" t="s">
-        <v>373</v>
+        <v>563</v>
       </c>
       <c r="X15" s="79" t="s">
         <v>424</v>
@@ -4919,6 +5237,12 @@
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="C16" s="73" t="s">
+        <v>379</v>
+      </c>
+      <c r="D16" t="s">
+        <v>390</v>
+      </c>
       <c r="X16" s="79" t="s">
         <v>425</v>
       </c>
@@ -4926,7 +5250,13 @@
         <v>463</v>
       </c>
     </row>
-    <row r="17" spans="24:25" x14ac:dyDescent="0.35">
+    <row r="17" spans="3:25" x14ac:dyDescent="0.35">
+      <c r="C17" s="73" t="s">
+        <v>572</v>
+      </c>
+      <c r="D17" t="s">
+        <v>573</v>
+      </c>
       <c r="X17" s="79" t="s">
         <v>426</v>
       </c>
@@ -4934,7 +5264,13 @@
         <v>464</v>
       </c>
     </row>
-    <row r="18" spans="24:25" x14ac:dyDescent="0.35">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.35">
+      <c r="C18" s="84" t="s">
+        <v>576</v>
+      </c>
+      <c r="D18" t="s">
+        <v>577</v>
+      </c>
       <c r="X18" s="79" t="s">
         <v>427</v>
       </c>
@@ -4942,7 +5278,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="19" spans="24:25" x14ac:dyDescent="0.35">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.35">
       <c r="X19" s="79" t="s">
         <v>428</v>
       </c>
@@ -4950,7 +5286,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="20" spans="24:25" x14ac:dyDescent="0.35">
+    <row r="20" spans="3:25" x14ac:dyDescent="0.35">
       <c r="X20" s="79" t="s">
         <v>429</v>
       </c>
@@ -4958,7 +5294,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="21" spans="24:25" x14ac:dyDescent="0.35">
+    <row r="21" spans="3:25" x14ac:dyDescent="0.35">
       <c r="X21" s="79" t="s">
         <v>430</v>
       </c>
@@ -4966,7 +5302,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="22" spans="24:25" x14ac:dyDescent="0.35">
+    <row r="22" spans="3:25" x14ac:dyDescent="0.35">
       <c r="X22" s="79" t="s">
         <v>431</v>
       </c>
@@ -4974,7 +5310,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="23" spans="24:25" x14ac:dyDescent="0.35">
+    <row r="23" spans="3:25" x14ac:dyDescent="0.35">
       <c r="X23" s="79" t="s">
         <v>432</v>
       </c>
@@ -4982,7 +5318,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="24" spans="24:25" x14ac:dyDescent="0.35">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.35">
       <c r="X24" s="79" t="s">
         <v>433</v>
       </c>
@@ -4990,7 +5326,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="25" spans="24:25" x14ac:dyDescent="0.35">
+    <row r="25" spans="3:25" x14ac:dyDescent="0.35">
       <c r="X25" s="79" t="s">
         <v>434</v>
       </c>
@@ -4998,7 +5334,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="26" spans="24:25" x14ac:dyDescent="0.35">
+    <row r="26" spans="3:25" x14ac:dyDescent="0.35">
       <c r="X26" s="79" t="s">
         <v>435</v>
       </c>
@@ -5006,7 +5342,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="27" spans="24:25" x14ac:dyDescent="0.35">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.35">
       <c r="X27" s="79" t="s">
         <v>436</v>
       </c>
@@ -5014,7 +5350,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="28" spans="24:25" x14ac:dyDescent="0.35">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.35">
       <c r="X28" s="79" t="s">
         <v>437</v>
       </c>
@@ -5022,7 +5358,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="29" spans="24:25" x14ac:dyDescent="0.35">
+    <row r="29" spans="3:25" x14ac:dyDescent="0.35">
       <c r="X29" s="79" t="s">
         <v>438</v>
       </c>
@@ -5030,7 +5366,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="30" spans="24:25" x14ac:dyDescent="0.35">
+    <row r="30" spans="3:25" x14ac:dyDescent="0.35">
       <c r="X30" s="79" t="s">
         <v>439</v>
       </c>
@@ -5038,7 +5374,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="31" spans="24:25" x14ac:dyDescent="0.35">
+    <row r="31" spans="3:25" x14ac:dyDescent="0.35">
       <c r="X31" s="79" t="s">
         <v>440</v>
       </c>
@@ -5046,7 +5382,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="32" spans="24:25" x14ac:dyDescent="0.35">
+    <row r="32" spans="3:25" x14ac:dyDescent="0.35">
       <c r="X32" s="79" t="s">
         <v>491</v>
       </c>
@@ -5086,111 +5422,115 @@
         <v>524</v>
       </c>
     </row>
-    <row r="37" spans="23:26" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="W37" s="81" t="s">
+    <row r="38" spans="23:26" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="W38" s="81" t="s">
         <v>408</v>
-      </c>
-    </row>
-    <row r="38" spans="23:26" x14ac:dyDescent="0.35">
-      <c r="X38" s="79" t="s">
-        <v>441</v>
-      </c>
-      <c r="Y38" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="39" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X39" s="79" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Y39" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="40" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X40" s="79" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="Y40" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="Z40" s="79"/>
     </row>
     <row r="41" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X41" s="79" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="Y41" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="Z41" s="79"/>
     </row>
     <row r="42" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X42" s="79" t="s">
+        <v>444</v>
+      </c>
+      <c r="Y42" t="s">
+        <v>482</v>
+      </c>
+      <c r="Z42" s="79"/>
+    </row>
+    <row r="43" spans="23:26" x14ac:dyDescent="0.35">
+      <c r="X43" s="79" t="s">
         <v>445</v>
       </c>
-      <c r="Y42" t="s">
+      <c r="Y43" t="s">
         <v>483</v>
       </c>
-      <c r="Z42" s="79"/>
-    </row>
-    <row r="43" spans="23:26" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="W43" s="81" t="s">
+      <c r="Z43" s="79"/>
+    </row>
+    <row r="44" spans="23:26" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="W44" s="81" t="s">
         <v>409</v>
       </c>
-      <c r="X43" s="80"/>
-      <c r="Z43" s="79"/>
-    </row>
-    <row r="44" spans="23:26" x14ac:dyDescent="0.35">
-      <c r="X44" s="79" t="s">
-        <v>446</v>
-      </c>
-      <c r="Y44" t="s">
-        <v>484</v>
-      </c>
+      <c r="X44" s="80"/>
       <c r="Z44" s="79"/>
     </row>
     <row r="45" spans="23:26" ht="15.5" x14ac:dyDescent="0.35">
       <c r="X45" s="79" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="Y45" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Z45" s="80"/>
     </row>
     <row r="46" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X46" s="79" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="Y46" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="Z46" s="79"/>
     </row>
     <row r="47" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X47" s="79" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="Y47" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="Z47" s="79"/>
     </row>
     <row r="48" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X48" s="79" t="s">
+        <v>449</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>487</v>
+      </c>
+      <c r="Z48" s="79"/>
+    </row>
+    <row r="49" spans="15:25" x14ac:dyDescent="0.35">
+      <c r="O49" s="79"/>
+      <c r="X49" s="79" t="s">
         <v>450</v>
       </c>
-      <c r="Y48" t="s">
+      <c r="Y49" t="s">
         <v>488</v>
       </c>
-      <c r="Z48" s="79"/>
-    </row>
-    <row r="49" spans="15:15" x14ac:dyDescent="0.35">
-      <c r="O49" s="79"/>
-    </row>
-    <row r="50" spans="15:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="50" spans="15:25" x14ac:dyDescent="0.35">
       <c r="O50" s="79"/>
+      <c r="X50" s="79" t="s">
+        <v>448</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>486</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Info/Additional_information.xlsx
+++ b/Info/Additional_information.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DEE3F75-7B12-4D2C-9DE3-A0CADF339F85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55754215-FBF9-4410-8845-3AA5EB81FFB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="614">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="614">
   <si>
     <t>good quality (UNC for UNC collection; UNC and XF for XF collection)</t>
   </si>
@@ -2794,54 +2794,6 @@
   </cellStyles>
   <dxfs count="34">
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -3325,6 +3277,54 @@
         </horizontal>
       </border>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -3393,28 +3393,28 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{973D7237-72C7-453E-A0E1-526C93326B28}" name="Таблица3" displayName="Таблица3" ref="A1:F51" totalsRowShown="0" headerRowDxfId="33" dataDxfId="31" headerRowBorderDxfId="32" tableBorderDxfId="30" totalsRowBorderDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{973D7237-72C7-453E-A0E1-526C93326B28}" name="Таблица3" displayName="Таблица3" ref="A1:F51" totalsRowShown="0" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
   <autoFilter ref="A1:F51" xr:uid="{A2D8FA3D-4024-4365-BE1D-F93D0AF2D426}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{12C2DF0B-47FA-46A4-8424-55A1488EF88B}" name="ID" dataDxfId="28"/>
-    <tableColumn id="2" xr3:uid="{EB0B36CE-168D-429E-896D-DBA54794224F}" name="Name_Eng" dataDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{6C3A2CE8-252E-4C52-985B-8CDDFD9FA0C7}" name="OfficialMintName_Native" dataDxfId="26"/>
-    <tableColumn id="8" xr3:uid="{DA5871DC-2EDB-49C0-953E-EC0F70288E21}" name="Country" dataDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{FCD85F85-A94E-4BBE-9D3B-2B7494638375}" name="Mint_City" dataDxfId="24"/>
-    <tableColumn id="6" xr3:uid="{E5141978-CA91-4DE9-86F1-8A8AFA716534}" name="Alias" dataDxfId="23"/>
+    <tableColumn id="1" xr3:uid="{12C2DF0B-47FA-46A4-8424-55A1488EF88B}" name="ID" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{EB0B36CE-168D-429E-896D-DBA54794224F}" name="Name_Eng" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{6C3A2CE8-252E-4C52-985B-8CDDFD9FA0C7}" name="OfficialMintName_Native" dataDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{DA5871DC-2EDB-49C0-953E-EC0F70288E21}" name="Country" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{FCD85F85-A94E-4BBE-9D3B-2B7494638375}" name="Mint_City" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{E5141978-CA91-4DE9-86F1-8A8AFA716534}" name="Alias" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9D0F8E3D-96B1-4DB8-B1A6-8DD6B84F3693}" name="Таблица35" displayName="Таблица35" ref="A1:D52" totalsRowShown="0" headerRowDxfId="22" dataDxfId="20" headerRowBorderDxfId="21" tableBorderDxfId="19" totalsRowBorderDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9D0F8E3D-96B1-4DB8-B1A6-8DD6B84F3693}" name="Таблица35" displayName="Таблица35" ref="A1:D52" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13" totalsRowBorderDxfId="12">
   <autoFilter ref="A1:D52" xr:uid="{A2D8FA3D-4024-4365-BE1D-F93D0AF2D426}"/>
   <tableColumns count="4">
-    <tableColumn id="4" xr3:uid="{74AFB32D-7AAA-46BE-8174-ED698BB4613E}" name="Mint_id" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{523D65CD-0F56-441F-90B5-E46A9B14F0D0}" name="Ekaterinburg Mint" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{1AAB7352-E935-4EC6-A0D1-3EDC5D0BC93C}" name="Year_of_start" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{5FF15381-476A-4F88-B93A-6452F2830A0A}" name="Year_of_end" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{74AFB32D-7AAA-46BE-8174-ED698BB4613E}" name="Mint_id" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{523D65CD-0F56-441F-90B5-E46A9B14F0D0}" name="Ekaterinburg Mint" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{1AAB7352-E935-4EC6-A0D1-3EDC5D0BC93C}" name="Year_of_start" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{5FF15381-476A-4F88-B93A-6452F2830A0A}" name="Year_of_end" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3428,25 +3428,25 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{8354E581-3B48-4762-81A7-EA76E36C4BB5}" name="№" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{1F45DC85-8ECA-45FE-BF45-E528619CEE0E}" name="Links:" dataDxfId="12" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{3FAE616B-3296-4770-9E56-8A824991EECA}" name="Description:" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{8354E581-3B48-4762-81A7-EA76E36C4BB5}" name="№" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{1F45DC85-8ECA-45FE-BF45-E528619CEE0E}" name="Links:" dataDxfId="6" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{3FAE616B-3296-4770-9E56-8A824991EECA}" name="Description:" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D0DCC88A-2D36-4004-A694-FC0C0F0C3396}" name="Таблица2" displayName="Таблица2" ref="A1:C16" totalsRowShown="0" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D0DCC88A-2D36-4004-A694-FC0C0F0C3396}" name="Таблица2" displayName="Таблица2" ref="A1:C16" totalsRowShown="0" headerRowBorderDxfId="4" tableBorderDxfId="3" totalsRowBorderDxfId="2">
   <autoFilter ref="A1:C16" xr:uid="{00000000-0009-0000-0100-000002000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{28358E6A-6F3A-468C-9E1C-880A34D9BECE}" name="№" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{28358E6A-6F3A-468C-9E1C-880A34D9BECE}" name="№" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{DD0AD5C8-324B-4DA7-B39F-B2DB3EF91222}" name="Links:"/>
-    <tableColumn id="3" xr3:uid="{FC8A6018-CA7E-4C73-9B21-B272B55FA8C1}" name="Description:" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{FC8A6018-CA7E-4C73-9B21-B272B55FA8C1}" name="Description:" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -3837,12 +3837,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C7:C8">
-    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="33" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C7))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6">
-    <cfRule type="containsText" dxfId="4" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="32" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C6))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3859,7 +3859,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2">
-    <cfRule type="containsText" dxfId="3" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="31" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C2))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3876,7 +3876,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4">
-    <cfRule type="containsText" dxfId="2" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="30" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C4))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3893,7 +3893,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C5">
-    <cfRule type="containsText" dxfId="1" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="29" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C5))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3910,7 +3910,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3">
-    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="28" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C3))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -4599,9 +4599,6 @@
       <c r="D7" t="s">
         <v>506</v>
       </c>
-      <c r="E7" t="s">
-        <v>108</v>
-      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8">
@@ -4615,9 +4612,6 @@
       </c>
       <c r="D8" t="s">
         <v>505</v>
-      </c>
-      <c r="E8" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">

--- a/Info/Additional_information.xlsx
+++ b/Info/Additional_information.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55754215-FBF9-4410-8845-3AA5EB81FFB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79D0317F-0C39-4BE8-B844-DC86B2BB6F3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Colours_specifications" sheetId="1" r:id="rId1"/>
     <sheet name="EURO albums content" sheetId="4" r:id="rId2"/>
-    <sheet name="albums ID" sheetId="11" r:id="rId3"/>
+    <sheet name="albums_ID" sheetId="11" r:id="rId3"/>
     <sheet name="albums ID naming" sheetId="9" r:id="rId4"/>
     <sheet name="Mint_Alias" sheetId="5" r:id="rId5"/>
     <sheet name="Mint_work_years" sheetId="6" r:id="rId6"/>
@@ -25,7 +25,7 @@
     <sheet name="Coin_Shops" sheetId="8" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'albums ID'!$B$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">albums_ID!$B$1:$E$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Colours_specifications!$A$1:$D$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'EURO albums content'!$A$1:$C$15</definedName>
   </definedNames>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="614">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="609">
   <si>
     <t>good quality (UNC for UNC collection; UNC and XF for XF collection)</t>
   </si>
@@ -1213,9 +1213,6 @@
     <t>RD</t>
   </si>
   <si>
-    <t>YL</t>
-  </si>
-  <si>
     <t>BN</t>
   </si>
   <si>
@@ -1234,15 +1231,6 @@
     <t>GD</t>
   </si>
   <si>
-    <t>SL</t>
-  </si>
-  <si>
-    <t>VT</t>
-  </si>
-  <si>
-    <t>OR</t>
-  </si>
-  <si>
     <t>Black</t>
   </si>
   <si>
@@ -1261,15 +1249,6 @@
     <t>Dark Blue</t>
   </si>
   <si>
-    <t>Gold</t>
-  </si>
-  <si>
-    <t>Silver</t>
-  </si>
-  <si>
-    <t>Violet</t>
-  </si>
-  <si>
     <t>Optima</t>
   </si>
   <si>
@@ -1801,12 +1780,6 @@
     <t>Dark Brown</t>
   </si>
   <si>
-    <t>A009-01-FB-BN</t>
-  </si>
-  <si>
-    <t>A009-02-FB-BN</t>
-  </si>
-  <si>
     <t>LN</t>
   </si>
   <si>
@@ -1819,9 +1792,6 @@
     <t>Монеты Казахстана, Индии, Российской империи</t>
   </si>
   <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A009-01-FB-BN.html</t>
-  </si>
-  <si>
     <t>Great Britain, Ukrainian and German coins</t>
   </si>
   <si>
@@ -1834,9 +1804,6 @@
     <t>Регулярные и юбилейныеонеты Испании и Канады</t>
   </si>
   <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A009-02-FB-BN.html</t>
-  </si>
-  <si>
     <t>A009-03-FB-BN</t>
   </si>
   <si>
@@ -1919,6 +1886,24 @@
   </si>
   <si>
     <t>Plastic cards</t>
+  </si>
+  <si>
+    <t>A009-01-FB-LN</t>
+  </si>
+  <si>
+    <t>A009-02-FB-LN</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A009-01-FB-LN.html</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A009-02-FB-LN.html</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A001-05-GD-BK.html</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A001-06-GD-BK.html</t>
   </si>
 </sst>
 </file>
@@ -2794,6 +2779,54 @@
   </cellStyles>
   <dxfs count="34">
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -3277,54 +3310,6 @@
         </horizontal>
       </border>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -3393,28 +3378,28 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{973D7237-72C7-453E-A0E1-526C93326B28}" name="Таблица3" displayName="Таблица3" ref="A1:F51" totalsRowShown="0" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{973D7237-72C7-453E-A0E1-526C93326B28}" name="Таблица3" displayName="Таблица3" ref="A1:F51" totalsRowShown="0" headerRowDxfId="33" dataDxfId="31" headerRowBorderDxfId="32" tableBorderDxfId="30" totalsRowBorderDxfId="29">
   <autoFilter ref="A1:F51" xr:uid="{A2D8FA3D-4024-4365-BE1D-F93D0AF2D426}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{12C2DF0B-47FA-46A4-8424-55A1488EF88B}" name="ID" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{EB0B36CE-168D-429E-896D-DBA54794224F}" name="Name_Eng" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{6C3A2CE8-252E-4C52-985B-8CDDFD9FA0C7}" name="OfficialMintName_Native" dataDxfId="20"/>
-    <tableColumn id="8" xr3:uid="{DA5871DC-2EDB-49C0-953E-EC0F70288E21}" name="Country" dataDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{FCD85F85-A94E-4BBE-9D3B-2B7494638375}" name="Mint_City" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{E5141978-CA91-4DE9-86F1-8A8AFA716534}" name="Alias" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{12C2DF0B-47FA-46A4-8424-55A1488EF88B}" name="ID" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{EB0B36CE-168D-429E-896D-DBA54794224F}" name="Name_Eng" dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{6C3A2CE8-252E-4C52-985B-8CDDFD9FA0C7}" name="OfficialMintName_Native" dataDxfId="26"/>
+    <tableColumn id="8" xr3:uid="{DA5871DC-2EDB-49C0-953E-EC0F70288E21}" name="Country" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{FCD85F85-A94E-4BBE-9D3B-2B7494638375}" name="Mint_City" dataDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{E5141978-CA91-4DE9-86F1-8A8AFA716534}" name="Alias" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9D0F8E3D-96B1-4DB8-B1A6-8DD6B84F3693}" name="Таблица35" displayName="Таблица35" ref="A1:D52" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13" totalsRowBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9D0F8E3D-96B1-4DB8-B1A6-8DD6B84F3693}" name="Таблица35" displayName="Таблица35" ref="A1:D52" totalsRowShown="0" headerRowDxfId="22" dataDxfId="20" headerRowBorderDxfId="21" tableBorderDxfId="19" totalsRowBorderDxfId="18">
   <autoFilter ref="A1:D52" xr:uid="{A2D8FA3D-4024-4365-BE1D-F93D0AF2D426}"/>
   <tableColumns count="4">
-    <tableColumn id="4" xr3:uid="{74AFB32D-7AAA-46BE-8174-ED698BB4613E}" name="Mint_id" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{523D65CD-0F56-441F-90B5-E46A9B14F0D0}" name="Ekaterinburg Mint" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{1AAB7352-E935-4EC6-A0D1-3EDC5D0BC93C}" name="Year_of_start" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{5FF15381-476A-4F88-B93A-6452F2830A0A}" name="Year_of_end" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{74AFB32D-7AAA-46BE-8174-ED698BB4613E}" name="Mint_id" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{523D65CD-0F56-441F-90B5-E46A9B14F0D0}" name="Ekaterinburg Mint" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{1AAB7352-E935-4EC6-A0D1-3EDC5D0BC93C}" name="Year_of_start" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{5FF15381-476A-4F88-B93A-6452F2830A0A}" name="Year_of_end" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3428,25 +3413,25 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{8354E581-3B48-4762-81A7-EA76E36C4BB5}" name="№" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{1F45DC85-8ECA-45FE-BF45-E528619CEE0E}" name="Links:" dataDxfId="6" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{3FAE616B-3296-4770-9E56-8A824991EECA}" name="Description:" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{8354E581-3B48-4762-81A7-EA76E36C4BB5}" name="№" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{1F45DC85-8ECA-45FE-BF45-E528619CEE0E}" name="Links:" dataDxfId="12" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{3FAE616B-3296-4770-9E56-8A824991EECA}" name="Description:" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D0DCC88A-2D36-4004-A694-FC0C0F0C3396}" name="Таблица2" displayName="Таблица2" ref="A1:C16" totalsRowShown="0" headerRowBorderDxfId="4" tableBorderDxfId="3" totalsRowBorderDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D0DCC88A-2D36-4004-A694-FC0C0F0C3396}" name="Таблица2" displayName="Таблица2" ref="A1:C16" totalsRowShown="0" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
   <autoFilter ref="A1:C16" xr:uid="{00000000-0009-0000-0100-000002000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{28358E6A-6F3A-468C-9E1C-880A34D9BECE}" name="№" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{28358E6A-6F3A-468C-9E1C-880A34D9BECE}" name="№" dataDxfId="7"/>
     <tableColumn id="2" xr3:uid="{DD0AD5C8-324B-4DA7-B39F-B2DB3EF91222}" name="Links:"/>
-    <tableColumn id="3" xr3:uid="{FC8A6018-CA7E-4C73-9B21-B272B55FA8C1}" name="Description:" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{FC8A6018-CA7E-4C73-9B21-B272B55FA8C1}" name="Description:" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -3837,12 +3822,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C7:C8">
-    <cfRule type="containsText" dxfId="33" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C7))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6">
-    <cfRule type="containsText" dxfId="32" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="4" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C6))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3859,7 +3844,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2">
-    <cfRule type="containsText" dxfId="31" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="3" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C2))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3876,7 +3861,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4">
-    <cfRule type="containsText" dxfId="30" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="2" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C4))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3893,7 +3878,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C5">
-    <cfRule type="containsText" dxfId="29" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="1" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C5))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3910,7 +3895,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3">
-    <cfRule type="containsText" dxfId="28" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C3))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -4486,19 +4471,19 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="78" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="B1" s="78" t="s">
+        <v>396</v>
+      </c>
+      <c r="C1" s="78" t="s">
         <v>403</v>
       </c>
-      <c r="C1" s="78" t="s">
-        <v>410</v>
-      </c>
       <c r="D1" s="78" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="E1" s="78" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -4506,16 +4491,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="C2" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="D2" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="E2" s="83" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -4523,16 +4508,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>525</v>
+      </c>
+      <c r="C3" t="s">
+        <v>492</v>
+      </c>
+      <c r="D3" t="s">
+        <v>503</v>
+      </c>
+      <c r="E3" s="83" t="s">
         <v>532</v>
-      </c>
-      <c r="C3" t="s">
-        <v>499</v>
-      </c>
-      <c r="D3" t="s">
-        <v>510</v>
-      </c>
-      <c r="E3" s="83" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -4540,16 +4525,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="C4" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="D4" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="E4" s="83" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -4557,16 +4542,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="C5" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
       <c r="D5" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="E5" s="83" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -4574,16 +4559,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="C6" t="s">
-        <v>502</v>
+        <v>495</v>
       </c>
       <c r="D6" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="E6" s="83" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -4591,13 +4576,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="C7" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="D7" t="s">
-        <v>506</v>
+        <v>499</v>
+      </c>
+      <c r="E7" s="83" t="s">
+        <v>607</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -4605,13 +4593,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="C8" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="D8" t="s">
-        <v>505</v>
+        <v>498</v>
+      </c>
+      <c r="E8" s="83" t="s">
+        <v>608</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -4619,16 +4610,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="C9" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="D9" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="E9" s="83" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -4636,16 +4627,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="C10" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="D10" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="E10" s="83" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -4653,16 +4644,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="C11" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="D11" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="E11" s="83" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -4670,16 +4661,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="C12" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="D12" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="E12" s="83" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -4687,16 +4678,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="C13" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="D13" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="E13" s="83" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
@@ -4704,16 +4695,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="C14" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="D14" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="E14" s="83" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
@@ -4721,16 +4712,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="C15" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="D15" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="E15" s="83" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
@@ -4738,16 +4729,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="C16" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="D16" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="E16" s="83" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
@@ -4755,16 +4746,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="C17" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
       <c r="D17" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="E17" s="83" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
@@ -4772,16 +4763,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="C18" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="D18" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="E18" s="83" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
@@ -4789,16 +4780,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
       <c r="C19" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="D19" t="s">
-        <v>584</v>
+        <v>574</v>
       </c>
       <c r="E19" s="83" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
@@ -4806,16 +4797,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>574</v>
+        <v>603</v>
       </c>
       <c r="C20" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="D20" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="E20" s="83" t="s">
-        <v>580</v>
+        <v>605</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
@@ -4823,16 +4814,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>575</v>
+        <v>604</v>
       </c>
       <c r="C21" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="D21" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="E21" s="83" t="s">
-        <v>585</v>
+        <v>606</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
@@ -4840,16 +4831,16 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>586</v>
+        <v>575</v>
       </c>
       <c r="C22" t="s">
-        <v>595</v>
+        <v>584</v>
       </c>
       <c r="D22" t="s">
-        <v>589</v>
+        <v>578</v>
       </c>
       <c r="E22" s="83" t="s">
-        <v>590</v>
+        <v>579</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
@@ -4857,16 +4848,16 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>587</v>
+        <v>576</v>
       </c>
       <c r="C23" t="s">
-        <v>594</v>
+        <v>583</v>
       </c>
       <c r="D23" t="s">
-        <v>588</v>
+        <v>577</v>
       </c>
       <c r="E23" s="83" t="s">
-        <v>591</v>
+        <v>580</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
@@ -4874,16 +4865,16 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="C24" t="s">
-        <v>593</v>
+        <v>582</v>
       </c>
       <c r="D24" t="s">
-        <v>592</v>
+        <v>581</v>
       </c>
       <c r="E24" s="83" t="s">
-        <v>597</v>
+        <v>586</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
@@ -4891,16 +4882,16 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="C25" t="s">
-        <v>599</v>
+        <v>588</v>
       </c>
       <c r="D25" t="s">
-        <v>602</v>
+        <v>591</v>
       </c>
       <c r="E25" s="83" t="s">
-        <v>600</v>
+        <v>589</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
@@ -4908,16 +4899,16 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>601</v>
+        <v>590</v>
       </c>
       <c r="C26" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="D26" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="E26" s="83" t="s">
-        <v>603</v>
+        <v>592</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
@@ -4925,16 +4916,16 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="C27" t="s">
-        <v>608</v>
+        <v>597</v>
       </c>
       <c r="D27" t="s">
-        <v>606</v>
+        <v>595</v>
       </c>
       <c r="E27" s="83" t="s">
-        <v>609</v>
+        <v>598</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
@@ -4942,16 +4933,16 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>610</v>
+        <v>599</v>
       </c>
       <c r="C28" t="s">
-        <v>613</v>
+        <v>602</v>
       </c>
       <c r="D28" t="s">
-        <v>612</v>
+        <v>601</v>
       </c>
       <c r="E28" s="83" t="s">
-        <v>611</v>
+        <v>600</v>
       </c>
     </row>
   </sheetData>
@@ -4974,18 +4965,20 @@
     <hyperlink ref="E17" r:id="rId14" xr:uid="{BB9C39F4-10B9-4609-B013-760BBB7F8EFB}"/>
     <hyperlink ref="E18" r:id="rId15" xr:uid="{D6DAB22F-8554-40C2-BC8F-DB4FE657DEE9}"/>
     <hyperlink ref="E19" r:id="rId16" xr:uid="{64EBF9BB-DC33-40A2-9BE8-3F6E300B72B4}"/>
-    <hyperlink ref="E20" r:id="rId17" xr:uid="{D5AC7FB8-8438-4C97-A0DD-85AEE0D9D86C}"/>
-    <hyperlink ref="E21" r:id="rId18" xr:uid="{EC2C4800-EA3C-4E26-8261-C6A03A377983}"/>
-    <hyperlink ref="E22" r:id="rId19" xr:uid="{84B2B169-2119-45C3-BD04-4482D7704951}"/>
-    <hyperlink ref="E23" r:id="rId20" xr:uid="{50B15920-8FF5-4A31-A3B6-630BFE6B7256}"/>
-    <hyperlink ref="E24" r:id="rId21" xr:uid="{CEF53131-34F9-40EB-8CC6-385E2C745B2A}"/>
-    <hyperlink ref="E25" r:id="rId22" xr:uid="{59E99A6F-25C8-4D24-898D-69FF859E9ADC}"/>
-    <hyperlink ref="E26" r:id="rId23" xr:uid="{99417517-FEFC-4B15-8968-043D037E8B12}"/>
-    <hyperlink ref="E27" r:id="rId24" xr:uid="{26F0F77D-076A-435A-A497-02AC8B18D716}"/>
-    <hyperlink ref="E28" r:id="rId25" xr:uid="{4275CB21-59E8-4194-8A88-6E70460DDA71}"/>
+    <hyperlink ref="E22" r:id="rId17" xr:uid="{84B2B169-2119-45C3-BD04-4482D7704951}"/>
+    <hyperlink ref="E23" r:id="rId18" xr:uid="{50B15920-8FF5-4A31-A3B6-630BFE6B7256}"/>
+    <hyperlink ref="E24" r:id="rId19" xr:uid="{CEF53131-34F9-40EB-8CC6-385E2C745B2A}"/>
+    <hyperlink ref="E25" r:id="rId20" xr:uid="{59E99A6F-25C8-4D24-898D-69FF859E9ADC}"/>
+    <hyperlink ref="E26" r:id="rId21" xr:uid="{99417517-FEFC-4B15-8968-043D037E8B12}"/>
+    <hyperlink ref="E27" r:id="rId22" xr:uid="{26F0F77D-076A-435A-A497-02AC8B18D716}"/>
+    <hyperlink ref="E28" r:id="rId23" xr:uid="{4275CB21-59E8-4194-8A88-6E70460DDA71}"/>
+    <hyperlink ref="E20" r:id="rId24" xr:uid="{A654E291-8976-4CCF-906F-52619F8C1947}"/>
+    <hyperlink ref="E21" r:id="rId25" xr:uid="{E871A1FA-77B9-4C91-B5CC-BBA3F76C259E}"/>
+    <hyperlink ref="E7" r:id="rId26" xr:uid="{E1253D1D-3D30-4B68-939D-54031E7A4705}"/>
+    <hyperlink ref="E8" r:id="rId27" xr:uid="{72D72E9D-ABBE-43E4-8111-C052FCD7B2CF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId26"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId28"/>
 </worksheet>
 </file>
 
@@ -5005,66 +4998,66 @@
   <sheetData>
     <row r="1" spans="1:25" ht="36.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="76" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="B1" s="76" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="C1" s="74" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="D1" s="72" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="W1" s="103" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="X1" s="103"/>
       <c r="Y1" s="103"/>
     </row>
     <row r="2" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="77" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="B2" s="75" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="C2" s="73" t="s">
         <v>375</v>
       </c>
       <c r="D2" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="W2" s="82" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3" s="77" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B3" s="75" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="C3" s="73" t="s">
         <v>376</v>
       </c>
       <c r="D3" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="X3" s="79" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="Y3" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4" s="77" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="B4" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="C4" s="73" t="s">
         <v>377</v>
@@ -5073,10 +5066,10 @@
         <v>9</v>
       </c>
       <c r="X4" s="79" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="Y4" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.35">
@@ -5087,24 +5080,24 @@
         <v>10</v>
       </c>
       <c r="X5" s="79" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="Y5" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.35">
       <c r="C6" s="73" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>387</v>
       </c>
       <c r="X6" s="79" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="Y6" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.35">
@@ -5112,13 +5105,13 @@
         <v>380</v>
       </c>
       <c r="D7" t="s">
-        <v>391</v>
+        <v>11</v>
       </c>
       <c r="X7" s="79" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="Y7" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.35">
@@ -5126,13 +5119,13 @@
         <v>381</v>
       </c>
       <c r="D8" t="s">
-        <v>11</v>
+        <v>388</v>
       </c>
       <c r="X8" s="79" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="Y8" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.35">
@@ -5140,390 +5133,360 @@
         <v>382</v>
       </c>
       <c r="D9" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="X9" s="79" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="Y9" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
     </row>
     <row r="10" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="C10" s="73" t="s">
-        <v>383</v>
+      <c r="C10" s="84" t="s">
+        <v>555</v>
       </c>
       <c r="D10" t="s">
-        <v>393</v>
+        <v>556</v>
       </c>
       <c r="W10" s="81" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.35">
       <c r="C11" s="73" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="D11" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="X11" s="79" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="Y11" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.35">
       <c r="C12" s="73" t="s">
-        <v>385</v>
+        <v>565</v>
       </c>
       <c r="D12" t="s">
-        <v>395</v>
+        <v>566</v>
       </c>
       <c r="X12" s="79" t="s">
+        <v>414</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="C13" s="84" t="s">
+        <v>567</v>
+      </c>
+      <c r="D13" t="s">
+        <v>568</v>
+      </c>
+      <c r="X13" s="79" t="s">
+        <v>415</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="X14" s="79" t="s">
+        <v>416</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="X15" s="79" t="s">
+        <v>417</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="X16" s="79" t="s">
+        <v>418</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="17" spans="24:25" x14ac:dyDescent="0.35">
+      <c r="X17" s="79" t="s">
+        <v>419</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="18" spans="24:25" x14ac:dyDescent="0.35">
+      <c r="X18" s="79" t="s">
+        <v>420</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="19" spans="24:25" x14ac:dyDescent="0.35">
+      <c r="X19" s="79" t="s">
         <v>421</v>
       </c>
-      <c r="Y12" t="s">
+      <c r="Y19" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="C13" s="73" t="s">
-        <v>386</v>
-      </c>
-      <c r="D13" t="s">
-        <v>396</v>
-      </c>
-      <c r="X13" s="79" t="s">
+    <row r="20" spans="24:25" x14ac:dyDescent="0.35">
+      <c r="X20" s="79" t="s">
         <v>422</v>
       </c>
-      <c r="Y13" t="s">
+      <c r="Y20" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="C14" s="73" t="s">
-        <v>387</v>
-      </c>
-      <c r="D14" t="s">
-        <v>373</v>
-      </c>
-      <c r="X14" s="79" t="s">
+    <row r="21" spans="24:25" x14ac:dyDescent="0.35">
+      <c r="X21" s="79" t="s">
         <v>423</v>
       </c>
-      <c r="Y14" t="s">
+      <c r="Y21" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="C15" s="84" t="s">
-        <v>562</v>
-      </c>
-      <c r="D15" t="s">
-        <v>563</v>
-      </c>
-      <c r="X15" s="79" t="s">
+    <row r="22" spans="24:25" x14ac:dyDescent="0.35">
+      <c r="X22" s="79" t="s">
         <v>424</v>
       </c>
-      <c r="Y15" t="s">
+      <c r="Y22" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="C16" s="73" t="s">
-        <v>379</v>
-      </c>
-      <c r="D16" t="s">
-        <v>390</v>
-      </c>
-      <c r="X16" s="79" t="s">
+    <row r="23" spans="24:25" x14ac:dyDescent="0.35">
+      <c r="X23" s="79" t="s">
         <v>425</v>
       </c>
-      <c r="Y16" t="s">
+      <c r="Y23" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.35">
-      <c r="C17" s="73" t="s">
-        <v>572</v>
-      </c>
-      <c r="D17" t="s">
-        <v>573</v>
-      </c>
-      <c r="X17" s="79" t="s">
+    <row r="24" spans="24:25" x14ac:dyDescent="0.35">
+      <c r="X24" s="79" t="s">
         <v>426</v>
       </c>
-      <c r="Y17" t="s">
+      <c r="Y24" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.35">
-      <c r="C18" s="84" t="s">
-        <v>576</v>
-      </c>
-      <c r="D18" t="s">
-        <v>577</v>
-      </c>
-      <c r="X18" s="79" t="s">
+    <row r="25" spans="24:25" x14ac:dyDescent="0.35">
+      <c r="X25" s="79" t="s">
         <v>427</v>
       </c>
-      <c r="Y18" t="s">
+      <c r="Y25" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.35">
-      <c r="X19" s="79" t="s">
+    <row r="26" spans="24:25" x14ac:dyDescent="0.35">
+      <c r="X26" s="79" t="s">
         <v>428</v>
       </c>
-      <c r="Y19" t="s">
+      <c r="Y26" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.35">
-      <c r="X20" s="79" t="s">
+    <row r="27" spans="24:25" x14ac:dyDescent="0.35">
+      <c r="X27" s="79" t="s">
         <v>429</v>
       </c>
-      <c r="Y20" t="s">
+      <c r="Y27" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.35">
-      <c r="X21" s="79" t="s">
+    <row r="28" spans="24:25" x14ac:dyDescent="0.35">
+      <c r="X28" s="79" t="s">
         <v>430</v>
       </c>
-      <c r="Y21" t="s">
+      <c r="Y28" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.35">
-      <c r="X22" s="79" t="s">
+    <row r="29" spans="24:25" x14ac:dyDescent="0.35">
+      <c r="X29" s="79" t="s">
         <v>431</v>
       </c>
-      <c r="Y22" t="s">
+      <c r="Y29" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.35">
-      <c r="X23" s="79" t="s">
+    <row r="30" spans="24:25" x14ac:dyDescent="0.35">
+      <c r="X30" s="79" t="s">
         <v>432</v>
       </c>
-      <c r="Y23" t="s">
+      <c r="Y30" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.35">
-      <c r="X24" s="79" t="s">
+    <row r="31" spans="24:25" x14ac:dyDescent="0.35">
+      <c r="X31" s="79" t="s">
         <v>433</v>
       </c>
-      <c r="Y24" t="s">
+      <c r="Y31" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.35">
-      <c r="X25" s="79" t="s">
-        <v>434</v>
-      </c>
-      <c r="Y25" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.35">
-      <c r="X26" s="79" t="s">
-        <v>435</v>
-      </c>
-      <c r="Y26" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.35">
-      <c r="X27" s="79" t="s">
-        <v>436</v>
-      </c>
-      <c r="Y27" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.35">
-      <c r="X28" s="79" t="s">
-        <v>437</v>
-      </c>
-      <c r="Y28" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.35">
-      <c r="X29" s="79" t="s">
-        <v>438</v>
-      </c>
-      <c r="Y29" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.35">
-      <c r="X30" s="79" t="s">
-        <v>439</v>
-      </c>
-      <c r="Y30" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.35">
-      <c r="X31" s="79" t="s">
-        <v>440</v>
-      </c>
-      <c r="Y31" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.35">
+    <row r="32" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X32" s="79" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="Y32" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
     </row>
     <row r="33" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X33" s="79" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="Y33" t="s">
-        <v>496</v>
+        <v>489</v>
       </c>
     </row>
     <row r="34" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X34" s="79" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="Y34" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
     </row>
     <row r="35" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X35" s="79" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="Y35" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
     </row>
     <row r="36" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X36" s="79" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="Y36" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
     </row>
     <row r="38" spans="23:26" ht="15.5" x14ac:dyDescent="0.35">
       <c r="W38" s="81" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
     </row>
     <row r="39" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X39" s="79" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="Y39" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
     </row>
     <row r="40" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X40" s="79" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="Y40" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="Z40" s="79"/>
     </row>
     <row r="41" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X41" s="79" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="Y41" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
       <c r="Z41" s="79"/>
     </row>
     <row r="42" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X42" s="79" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="Y42" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="Z42" s="79"/>
     </row>
     <row r="43" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X43" s="79" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="Y43" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="Z43" s="79"/>
     </row>
     <row r="44" spans="23:26" ht="15.5" x14ac:dyDescent="0.35">
       <c r="W44" s="81" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="X44" s="80"/>
       <c r="Z44" s="79"/>
     </row>
     <row r="45" spans="23:26" ht="15.5" x14ac:dyDescent="0.35">
       <c r="X45" s="79" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="Y45" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="Z45" s="80"/>
     </row>
     <row r="46" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X46" s="79" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="Y46" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="Z46" s="79"/>
     </row>
     <row r="47" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X47" s="79" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="Y47" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="Z47" s="79"/>
     </row>
     <row r="48" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X48" s="79" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="Y48" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="Z48" s="79"/>
     </row>
     <row r="49" spans="15:25" x14ac:dyDescent="0.35">
       <c r="O49" s="79"/>
       <c r="X49" s="79" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="Y49" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
     </row>
     <row r="50" spans="15:25" x14ac:dyDescent="0.35">
       <c r="O50" s="79"/>
       <c r="X50" s="79" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="Y50" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
     </row>
   </sheetData>

--- a/Info/Additional_information.xlsx
+++ b/Info/Additional_information.xlsx
@@ -8,26 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79D0317F-0C39-4BE8-B844-DC86B2BB6F3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54EE9027-584F-4453-92D4-EEC7B28BE9B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Colours_specifications" sheetId="1" r:id="rId1"/>
-    <sheet name="EURO albums content" sheetId="4" r:id="rId2"/>
-    <sheet name="albums_ID" sheetId="11" r:id="rId3"/>
-    <sheet name="albums ID naming" sheetId="9" r:id="rId4"/>
-    <sheet name="Mint_Alias" sheetId="5" r:id="rId5"/>
-    <sheet name="Mint_work_years" sheetId="6" r:id="rId6"/>
-    <sheet name="File_Naming" sheetId="2" r:id="rId7"/>
-    <sheet name="Existing_subtypes" sheetId="3" r:id="rId8"/>
-    <sheet name="Links_to_Data" sheetId="7" r:id="rId9"/>
-    <sheet name="Coin_Shops" sheetId="8" r:id="rId10"/>
+    <sheet name="Library_Link" sheetId="13" r:id="rId1"/>
+    <sheet name="Colours_specifications" sheetId="1" r:id="rId2"/>
+    <sheet name="EURO albums content" sheetId="4" r:id="rId3"/>
+    <sheet name="albums_ID" sheetId="11" r:id="rId4"/>
+    <sheet name="albums ID naming" sheetId="9" r:id="rId5"/>
+    <sheet name="Лист1" sheetId="12" r:id="rId6"/>
+    <sheet name="Mint_Alias" sheetId="5" r:id="rId7"/>
+    <sheet name="Coin_Shops" sheetId="8" r:id="rId8"/>
+    <sheet name="Mint_work_years" sheetId="6" r:id="rId9"/>
+    <sheet name="File_Naming" sheetId="2" r:id="rId10"/>
+    <sheet name="Existing_subtypes" sheetId="3" r:id="rId11"/>
+    <sheet name="Links_to_Data" sheetId="7" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">albums_ID!$B$1:$E$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Colours_specifications!$A$1:$D$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'EURO albums content'!$A$1:$C$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">albums_ID!$B$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Colours_specifications!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'EURO albums content'!$A$1:$C$15</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -76,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="609">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="610">
   <si>
     <t>good quality (UNC for UNC collection; UNC and XF for XF collection)</t>
   </si>
@@ -1904,13 +1906,16 @@
   </si>
   <si>
     <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A001-06-GD-BK.html</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/index.html</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2055,6 +2060,16 @@
       <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="48"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2495,7 +2510,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2772,6 +2787,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -3393,6 +3410,22 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D0DCC88A-2D36-4004-A694-FC0C0F0C3396}" name="Таблица2" displayName="Таблица2" ref="A1:C16" totalsRowShown="0" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="A1:C16" xr:uid="{00000000-0009-0000-0100-000002000000}">
+    <filterColumn colId="0" hiddenButton="1"/>
+    <filterColumn colId="1" hiddenButton="1"/>
+    <filterColumn colId="2" hiddenButton="1"/>
+  </autoFilter>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{28358E6A-6F3A-468C-9E1C-880A34D9BECE}" name="№" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{DD0AD5C8-324B-4DA7-B39F-B2DB3EF91222}" name="Links:"/>
+    <tableColumn id="3" xr3:uid="{FC8A6018-CA7E-4C73-9B21-B272B55FA8C1}" name="Description:" dataDxfId="6"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9D0F8E3D-96B1-4DB8-B1A6-8DD6B84F3693}" name="Таблица35" displayName="Таблица35" ref="A1:D52" totalsRowShown="0" headerRowDxfId="22" dataDxfId="20" headerRowBorderDxfId="21" tableBorderDxfId="19" totalsRowBorderDxfId="18">
   <autoFilter ref="A1:D52" xr:uid="{A2D8FA3D-4024-4365-BE1D-F93D0AF2D426}"/>
   <tableColumns count="4">
@@ -3405,7 +3438,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FDD79E09-67C5-4100-A809-2C00194D1D97}" name="Таблица4" displayName="Таблица4" ref="A1:C16" totalsRowShown="0">
   <autoFilter ref="A1:C16" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -3418,22 +3451,6 @@
     <tableColumn id="3" xr3:uid="{3FAE616B-3296-4770-9E56-8A824991EECA}" name="Description:" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D0DCC88A-2D36-4004-A694-FC0C0F0C3396}" name="Таблица2" displayName="Таблица2" ref="A1:C16" totalsRowShown="0" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
-  <autoFilter ref="A1:C16" xr:uid="{00000000-0009-0000-0100-000002000000}">
-    <filterColumn colId="0" hiddenButton="1"/>
-    <filterColumn colId="1" hiddenButton="1"/>
-    <filterColumn colId="2" hiddenButton="1"/>
-  </autoFilter>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{28358E6A-6F3A-468C-9E1C-880A34D9BECE}" name="№" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{DD0AD5C8-324B-4DA7-B39F-B2DB3EF91222}" name="Links:"/>
-    <tableColumn id="3" xr3:uid="{FC8A6018-CA7E-4C73-9B21-B272B55FA8C1}" name="Description:" dataDxfId="6"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -3699,6 +3716,572 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D5AF97D-14BA-4E23-B5FF-856D52BDA29A}">
+  <dimension ref="B7:Z7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="9.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="7" spans="2:26" ht="61.5" x14ac:dyDescent="1.35">
+      <c r="B7" s="105" t="s">
+        <v>609</v>
+      </c>
+      <c r="C7" s="104"/>
+      <c r="D7" s="104"/>
+      <c r="E7" s="104"/>
+      <c r="F7" s="104"/>
+      <c r="G7" s="104"/>
+      <c r="H7" s="104"/>
+      <c r="I7" s="104"/>
+      <c r="J7" s="104"/>
+      <c r="K7" s="104"/>
+      <c r="L7" s="104"/>
+      <c r="M7" s="104"/>
+      <c r="N7" s="104"/>
+      <c r="O7" s="104"/>
+      <c r="P7" s="104"/>
+      <c r="Q7" s="104"/>
+      <c r="R7" s="104"/>
+      <c r="S7" s="104"/>
+      <c r="T7" s="104"/>
+      <c r="U7" s="104"/>
+      <c r="V7" s="104"/>
+      <c r="W7" s="104"/>
+      <c r="X7" s="104"/>
+      <c r="Y7" s="104"/>
+      <c r="Z7" s="104"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B7:Z7"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="B7" r:id="rId1" xr:uid="{1B51AF5A-9579-4E45-802C-86E0D9768BAB}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0041FEF0-BF6F-4667-AFBD-1C23A1866795}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.7265625" customWidth="1"/>
+    <col min="2" max="2" width="17.453125" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="37.90625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="9">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="9">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="9">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="9">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="9">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="9">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8265AFD9-D9EB-4B75-B60D-6B7F7204230D}">
+  <dimension ref="A1:B29"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="26.36328125" customWidth="1"/>
+    <col min="2" max="2" width="31.36328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="4"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="4"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="4"/>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="4"/>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="4"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="4"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="4"/>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="4"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="4"/>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="4"/>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="4"/>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="4"/>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="4"/>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="4"/>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" s="4"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" s="4"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="4"/>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="4"/>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" s="4"/>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" s="4"/>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="4"/>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="4"/>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24" s="4"/>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" s="4"/>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" s="4"/>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" s="4"/>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B28" s="4"/>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="B29" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{729F7C06-1AE8-4162-8F40-6E9A64E311D7}">
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="4.81640625" customWidth="1"/>
+    <col min="2" max="2" width="57.1796875" customWidth="1"/>
+    <col min="3" max="3" width="104.453125" customWidth="1"/>
+    <col min="4" max="4" width="15.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B1" s="45" t="s">
+        <v>304</v>
+      </c>
+      <c r="C1" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="41">
+        <v>1</v>
+      </c>
+      <c r="B2" s="46" t="s">
+        <v>306</v>
+      </c>
+      <c r="C2" s="47" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="41">
+        <v>2</v>
+      </c>
+      <c r="B3" s="46" t="s">
+        <v>308</v>
+      </c>
+      <c r="C3" s="47" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="41">
+        <v>3</v>
+      </c>
+      <c r="B4" s="46" t="s">
+        <v>310</v>
+      </c>
+      <c r="C4" s="47" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="41">
+        <v>4</v>
+      </c>
+      <c r="B5" s="46" t="s">
+        <v>312</v>
+      </c>
+      <c r="C5" s="47" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="41">
+        <v>5</v>
+      </c>
+      <c r="B6" s="46" t="s">
+        <v>314</v>
+      </c>
+      <c r="C6" s="47" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="41">
+        <v>6</v>
+      </c>
+      <c r="B7" s="46" t="s">
+        <v>316</v>
+      </c>
+      <c r="C7" s="47" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A8" s="41">
+        <v>7</v>
+      </c>
+      <c r="B8" s="46" t="s">
+        <v>318</v>
+      </c>
+      <c r="C8" s="47" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="41">
+        <v>8</v>
+      </c>
+      <c r="B9" s="46" t="s">
+        <v>320</v>
+      </c>
+      <c r="C9" s="47" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A10" s="41">
+        <v>9</v>
+      </c>
+      <c r="B10" s="46" t="s">
+        <v>322</v>
+      </c>
+      <c r="C10" s="47" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="41">
+        <v>10</v>
+      </c>
+      <c r="B11" s="46" t="s">
+        <v>324</v>
+      </c>
+      <c r="C11" s="47" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="41">
+        <v>11</v>
+      </c>
+      <c r="B12" s="46" t="s">
+        <v>324</v>
+      </c>
+      <c r="C12" s="47" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="41">
+        <v>12</v>
+      </c>
+      <c r="B13" s="46" t="s">
+        <v>327</v>
+      </c>
+      <c r="C13" s="47" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="41">
+        <v>13</v>
+      </c>
+      <c r="B14" s="48" t="s">
+        <v>329</v>
+      </c>
+      <c r="C14" s="49" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="50">
+        <v>14</v>
+      </c>
+      <c r="B15" s="48" t="s">
+        <v>331</v>
+      </c>
+      <c r="C15" s="49" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="50">
+        <v>15</v>
+      </c>
+      <c r="B16" s="48" t="s">
+        <v>333</v>
+      </c>
+      <c r="C16" s="49" t="s">
+        <v>332</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" location="p75892" xr:uid="{2004A8F5-EEA3-401A-8147-DCBE2B32B8A8}"/>
+    <hyperlink ref="B9" r:id="rId2" xr:uid="{3753811B-46E0-40E4-A28F-CA6D25194D0F}"/>
+    <hyperlink ref="B3" r:id="rId3" xr:uid="{ABC31D49-3E50-4123-A5E8-5A9AD3B5E23A}"/>
+    <hyperlink ref="B4" r:id="rId4" xr:uid="{9BB030EB-2475-45E8-8729-CB926565C2F2}"/>
+    <hyperlink ref="B5" r:id="rId5" xr:uid="{7321AD3B-4F9A-4715-8E78-C68C70C3ED3B}"/>
+    <hyperlink ref="B6" r:id="rId6" xr:uid="{548D83D1-6D3D-4818-ADA3-FE0E9231956A}"/>
+    <hyperlink ref="B7" r:id="rId7" xr:uid="{472B0F29-A646-4E1D-889A-066C1E7B1A15}"/>
+    <hyperlink ref="B8" r:id="rId8" xr:uid="{AC393C1F-E1F7-4A34-BAB9-9A5547AA9097}"/>
+    <hyperlink ref="B10" r:id="rId9" xr:uid="{03660F06-E14B-4321-BA0A-8107D65FCB9A}"/>
+    <hyperlink ref="B11" r:id="rId10" xr:uid="{4C30CEFE-89AC-45A8-B194-BA95B0264245}"/>
+    <hyperlink ref="B12" r:id="rId11" xr:uid="{6B68188A-ED23-4BA9-84BA-0548CD8D3167}"/>
+    <hyperlink ref="B13" r:id="rId12" xr:uid="{3F6B392C-913E-4879-8C3F-C8EDE5C0C628}"/>
+    <hyperlink ref="B14" r:id="rId13" xr:uid="{C5D03E4D-384E-4F2E-B584-EB754AA1EC51}"/>
+    <hyperlink ref="B15" r:id="rId14" xr:uid="{4438EF86-C632-4762-BA87-39D3DF57E123}"/>
+    <hyperlink ref="B16" r:id="rId15" xr:uid="{953D4D13-1E13-4CD6-AAB4-804DCEA3E92F}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId16"/>
+  <legacyDrawing r:id="rId17"/>
+  <tableParts count="1">
+    <tablePart r:id="rId18"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3926,205 +4509,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8049D8E-7482-48AF-95C9-7F1B728B0DDE}">
-  <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="4.90625" customWidth="1"/>
-    <col min="2" max="2" width="57.1796875" customWidth="1"/>
-    <col min="3" max="3" width="60.54296875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="51" t="s">
-        <v>303</v>
-      </c>
-      <c r="B1" s="53" t="s">
-        <v>304</v>
-      </c>
-      <c r="C1" s="52" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="54">
-        <v>1</v>
-      </c>
-      <c r="B2" s="55" t="s">
-        <v>334</v>
-      </c>
-      <c r="C2" s="56" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="54">
-        <v>2</v>
-      </c>
-      <c r="B3" s="55" t="s">
-        <v>336</v>
-      </c>
-      <c r="C3" s="57" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="58">
-        <v>3</v>
-      </c>
-      <c r="B4" s="59" t="s">
-        <v>338</v>
-      </c>
-      <c r="C4" s="49" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="58">
-        <v>4</v>
-      </c>
-      <c r="B5" s="59" t="s">
-        <v>340</v>
-      </c>
-      <c r="C5" s="49" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="58">
-        <v>5</v>
-      </c>
-      <c r="B6" s="59" t="s">
-        <v>342</v>
-      </c>
-      <c r="C6" s="49" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="58">
-        <v>6</v>
-      </c>
-      <c r="B7" s="59" t="s">
-        <v>344</v>
-      </c>
-      <c r="C7" s="49" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="58">
-        <v>7</v>
-      </c>
-      <c r="B8" s="59" t="s">
-        <v>346</v>
-      </c>
-      <c r="C8" s="49" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="58">
-        <v>8</v>
-      </c>
-      <c r="B9" s="59" t="s">
-        <v>348</v>
-      </c>
-      <c r="C9" s="49" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="58">
-        <v>9</v>
-      </c>
-      <c r="B10" s="59" t="s">
-        <v>350</v>
-      </c>
-      <c r="C10" s="49" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A11" s="58">
-        <v>10</v>
-      </c>
-      <c r="B11" s="59" t="s">
-        <v>352</v>
-      </c>
-      <c r="C11" s="49" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="50">
-        <v>11</v>
-      </c>
-      <c r="B12" s="60" t="s">
-        <v>354</v>
-      </c>
-      <c r="C12" s="61" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" s="58">
-        <v>12</v>
-      </c>
-      <c r="B13" s="60" t="s">
-        <v>356</v>
-      </c>
-      <c r="C13" s="49" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" s="50">
-        <v>13</v>
-      </c>
-      <c r="B14" s="60" t="s">
-        <v>358</v>
-      </c>
-      <c r="C14" s="49" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" s="50"/>
-      <c r="B15" s="62"/>
-      <c r="C15" s="61"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" s="50"/>
-      <c r="B16" s="63"/>
-      <c r="C16" s="61"/>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B3" r:id="rId1" xr:uid="{13FF5B38-979E-4B2F-BAB5-6B958AFA6F63}"/>
-    <hyperlink ref="B2" r:id="rId2" xr:uid="{8CDE9249-5025-4C73-997F-4F9D70D202AC}"/>
-    <hyperlink ref="B5" r:id="rId3" xr:uid="{374ED2AF-B73D-4278-920D-1946204108B5}"/>
-    <hyperlink ref="B4" r:id="rId4" xr:uid="{2C3B89D8-9E7D-4442-80BB-FFF5536235E3}"/>
-    <hyperlink ref="B6" r:id="rId5" xr:uid="{818E9F59-13C4-4C99-87C6-FFFA7F900180}"/>
-    <hyperlink ref="B7" r:id="rId6" xr:uid="{6B707731-DB96-4AC5-95AE-2AB9C0AF043C}"/>
-    <hyperlink ref="B8" r:id="rId7" xr:uid="{C211FF41-9BDA-4A20-A485-2BC2B9F9533D}"/>
-    <hyperlink ref="B10" r:id="rId8" xr:uid="{41F4CF19-2961-4EE0-9555-ADF4FC54618B}"/>
-    <hyperlink ref="B11" r:id="rId9" xr:uid="{EEF40FFE-3C23-4FDA-A25E-76458788FA14}"/>
-    <hyperlink ref="B12" r:id="rId10" xr:uid="{19110E30-81F7-4A3F-A6B3-82184B9E2901}"/>
-    <hyperlink ref="B13" r:id="rId11" xr:uid="{5FF590CD-8D8C-47B8-946F-E06A667638A0}"/>
-    <hyperlink ref="B9" r:id="rId12" xr:uid="{29C5CF24-D4B6-4B52-986C-B80123955B99}"/>
-    <hyperlink ref="B14" r:id="rId13" xr:uid="{9012315C-5439-4976-B191-F4B5EC25A99D}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId14"/>
-  <tableParts count="1">
-    <tablePart r:id="rId15"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57D9DE6C-583F-4F0B-9E0F-CDE5965E194A}">
   <dimension ref="A1:I30"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -4456,7 +4841,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DC835FD-69FE-4DBC-957F-9A46CA05517E}">
   <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -4982,7 +5367,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{866E9A5E-386D-439E-AA25-CB46A31C625C}">
   <dimension ref="A1:Z50"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -5499,7 +5884,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7B3F3C9-87AF-45FC-9E9F-2A256D1F4917}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4C14141-45DA-4C30-845C-3E630B347F10}">
   <dimension ref="A1:F51"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -6539,7 +6933,205 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8049D8E-7482-48AF-95C9-7F1B728B0DDE}">
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="4.90625" customWidth="1"/>
+    <col min="2" max="2" width="57.1796875" customWidth="1"/>
+    <col min="3" max="3" width="60.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="51" t="s">
+        <v>303</v>
+      </c>
+      <c r="B1" s="53" t="s">
+        <v>304</v>
+      </c>
+      <c r="C1" s="52" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="54">
+        <v>1</v>
+      </c>
+      <c r="B2" s="55" t="s">
+        <v>334</v>
+      </c>
+      <c r="C2" s="56" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="54">
+        <v>2</v>
+      </c>
+      <c r="B3" s="55" t="s">
+        <v>336</v>
+      </c>
+      <c r="C3" s="57" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="58">
+        <v>3</v>
+      </c>
+      <c r="B4" s="59" t="s">
+        <v>338</v>
+      </c>
+      <c r="C4" s="49" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="58">
+        <v>4</v>
+      </c>
+      <c r="B5" s="59" t="s">
+        <v>340</v>
+      </c>
+      <c r="C5" s="49" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="58">
+        <v>5</v>
+      </c>
+      <c r="B6" s="59" t="s">
+        <v>342</v>
+      </c>
+      <c r="C6" s="49" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="58">
+        <v>6</v>
+      </c>
+      <c r="B7" s="59" t="s">
+        <v>344</v>
+      </c>
+      <c r="C7" s="49" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="58">
+        <v>7</v>
+      </c>
+      <c r="B8" s="59" t="s">
+        <v>346</v>
+      </c>
+      <c r="C8" s="49" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="58">
+        <v>8</v>
+      </c>
+      <c r="B9" s="59" t="s">
+        <v>348</v>
+      </c>
+      <c r="C9" s="49" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="58">
+        <v>9</v>
+      </c>
+      <c r="B10" s="59" t="s">
+        <v>350</v>
+      </c>
+      <c r="C10" s="49" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A11" s="58">
+        <v>10</v>
+      </c>
+      <c r="B11" s="59" t="s">
+        <v>352</v>
+      </c>
+      <c r="C11" s="49" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="50">
+        <v>11</v>
+      </c>
+      <c r="B12" s="60" t="s">
+        <v>354</v>
+      </c>
+      <c r="C12" s="61" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="58">
+        <v>12</v>
+      </c>
+      <c r="B13" s="60" t="s">
+        <v>356</v>
+      </c>
+      <c r="C13" s="49" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="50">
+        <v>13</v>
+      </c>
+      <c r="B14" s="60" t="s">
+        <v>358</v>
+      </c>
+      <c r="C14" s="49" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="50"/>
+      <c r="B15" s="62"/>
+      <c r="C15" s="61"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="50"/>
+      <c r="B16" s="63"/>
+      <c r="C16" s="61"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B3" r:id="rId1" xr:uid="{13FF5B38-979E-4B2F-BAB5-6B958AFA6F63}"/>
+    <hyperlink ref="B2" r:id="rId2" xr:uid="{8CDE9249-5025-4C73-997F-4F9D70D202AC}"/>
+    <hyperlink ref="B5" r:id="rId3" xr:uid="{374ED2AF-B73D-4278-920D-1946204108B5}"/>
+    <hyperlink ref="B4" r:id="rId4" xr:uid="{2C3B89D8-9E7D-4442-80BB-FFF5536235E3}"/>
+    <hyperlink ref="B6" r:id="rId5" xr:uid="{818E9F59-13C4-4C99-87C6-FFFA7F900180}"/>
+    <hyperlink ref="B7" r:id="rId6" xr:uid="{6B707731-DB96-4AC5-95AE-2AB9C0AF043C}"/>
+    <hyperlink ref="B8" r:id="rId7" xr:uid="{C211FF41-9BDA-4A20-A485-2BC2B9F9533D}"/>
+    <hyperlink ref="B10" r:id="rId8" xr:uid="{41F4CF19-2961-4EE0-9555-ADF4FC54618B}"/>
+    <hyperlink ref="B11" r:id="rId9" xr:uid="{EEF40FFE-3C23-4FDA-A25E-76458788FA14}"/>
+    <hyperlink ref="B12" r:id="rId10" xr:uid="{19110E30-81F7-4A3F-A6B3-82184B9E2901}"/>
+    <hyperlink ref="B13" r:id="rId11" xr:uid="{5FF590CD-8D8C-47B8-946F-E06A667638A0}"/>
+    <hyperlink ref="B9" r:id="rId12" xr:uid="{29C5CF24-D4B6-4B52-986C-B80123955B99}"/>
+    <hyperlink ref="B14" r:id="rId13" xr:uid="{9012315C-5439-4976-B191-F4B5EC25A99D}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId14"/>
+  <tableParts count="1">
+    <tablePart r:id="rId15"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF1BA8E2-9FD2-4C47-B5D3-EF9907B8F692}">
   <dimension ref="A1:D52"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -7213,522 +7805,4 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0041FEF0-BF6F-4667-AFBD-1C23A1866795}">
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="10.7265625" customWidth="1"/>
-    <col min="2" max="2" width="17.453125" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="37.90625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="9">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="9">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="9">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="9">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="9">
-        <v>5</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="9">
-        <v>6</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8265AFD9-D9EB-4B75-B60D-6B7F7204230D}">
-  <dimension ref="A1:B29"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="26.36328125" customWidth="1"/>
-    <col min="2" max="2" width="31.36328125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" s="4"/>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" s="4"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="4"/>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" s="4"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="4"/>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="4"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="4"/>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" s="4"/>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="4"/>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" s="4"/>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B12" s="4"/>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B13" s="4"/>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" s="4"/>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B15" s="4"/>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B16" s="4"/>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B17" s="4"/>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B18" s="4"/>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B19" s="4"/>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B20" s="4"/>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B21" s="4"/>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B22" s="4"/>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B23" s="4"/>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A24" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B24" s="4"/>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B25" s="4"/>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A26" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B26" s="4"/>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A27" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B27" s="4"/>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A28" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B28" s="4"/>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A29" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="B29" s="4"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{729F7C06-1AE8-4162-8F40-6E9A64E311D7}">
-  <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="4.81640625" customWidth="1"/>
-    <col min="2" max="2" width="57.1796875" customWidth="1"/>
-    <col min="3" max="3" width="104.453125" customWidth="1"/>
-    <col min="4" max="4" width="15.453125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>303</v>
-      </c>
-      <c r="B1" s="45" t="s">
-        <v>304</v>
-      </c>
-      <c r="C1" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="41">
-        <v>1</v>
-      </c>
-      <c r="B2" s="46" t="s">
-        <v>306</v>
-      </c>
-      <c r="C2" s="47" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="41">
-        <v>2</v>
-      </c>
-      <c r="B3" s="46" t="s">
-        <v>308</v>
-      </c>
-      <c r="C3" s="47" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="41">
-        <v>3</v>
-      </c>
-      <c r="B4" s="46" t="s">
-        <v>310</v>
-      </c>
-      <c r="C4" s="47" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="41">
-        <v>4</v>
-      </c>
-      <c r="B5" s="46" t="s">
-        <v>312</v>
-      </c>
-      <c r="C5" s="47" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="41">
-        <v>5</v>
-      </c>
-      <c r="B6" s="46" t="s">
-        <v>314</v>
-      </c>
-      <c r="C6" s="47" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="41">
-        <v>6</v>
-      </c>
-      <c r="B7" s="46" t="s">
-        <v>316</v>
-      </c>
-      <c r="C7" s="47" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A8" s="41">
-        <v>7</v>
-      </c>
-      <c r="B8" s="46" t="s">
-        <v>318</v>
-      </c>
-      <c r="C8" s="47" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="41">
-        <v>8</v>
-      </c>
-      <c r="B9" s="46" t="s">
-        <v>320</v>
-      </c>
-      <c r="C9" s="47" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A10" s="41">
-        <v>9</v>
-      </c>
-      <c r="B10" s="46" t="s">
-        <v>322</v>
-      </c>
-      <c r="C10" s="47" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="41">
-        <v>10</v>
-      </c>
-      <c r="B11" s="46" t="s">
-        <v>324</v>
-      </c>
-      <c r="C11" s="47" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="41">
-        <v>11</v>
-      </c>
-      <c r="B12" s="46" t="s">
-        <v>324</v>
-      </c>
-      <c r="C12" s="47" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" s="41">
-        <v>12</v>
-      </c>
-      <c r="B13" s="46" t="s">
-        <v>327</v>
-      </c>
-      <c r="C13" s="47" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" s="41">
-        <v>13</v>
-      </c>
-      <c r="B14" s="48" t="s">
-        <v>329</v>
-      </c>
-      <c r="C14" s="49" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" s="50">
-        <v>14</v>
-      </c>
-      <c r="B15" s="48" t="s">
-        <v>331</v>
-      </c>
-      <c r="C15" s="49" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" s="50">
-        <v>15</v>
-      </c>
-      <c r="B16" s="48" t="s">
-        <v>333</v>
-      </c>
-      <c r="C16" s="49" t="s">
-        <v>332</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" location="p75892" xr:uid="{2004A8F5-EEA3-401A-8147-DCBE2B32B8A8}"/>
-    <hyperlink ref="B9" r:id="rId2" xr:uid="{3753811B-46E0-40E4-A28F-CA6D25194D0F}"/>
-    <hyperlink ref="B3" r:id="rId3" xr:uid="{ABC31D49-3E50-4123-A5E8-5A9AD3B5E23A}"/>
-    <hyperlink ref="B4" r:id="rId4" xr:uid="{9BB030EB-2475-45E8-8729-CB926565C2F2}"/>
-    <hyperlink ref="B5" r:id="rId5" xr:uid="{7321AD3B-4F9A-4715-8E78-C68C70C3ED3B}"/>
-    <hyperlink ref="B6" r:id="rId6" xr:uid="{548D83D1-6D3D-4818-ADA3-FE0E9231956A}"/>
-    <hyperlink ref="B7" r:id="rId7" xr:uid="{472B0F29-A646-4E1D-889A-066C1E7B1A15}"/>
-    <hyperlink ref="B8" r:id="rId8" xr:uid="{AC393C1F-E1F7-4A34-BAB9-9A5547AA9097}"/>
-    <hyperlink ref="B10" r:id="rId9" xr:uid="{03660F06-E14B-4321-BA0A-8107D65FCB9A}"/>
-    <hyperlink ref="B11" r:id="rId10" xr:uid="{4C30CEFE-89AC-45A8-B194-BA95B0264245}"/>
-    <hyperlink ref="B12" r:id="rId11" xr:uid="{6B68188A-ED23-4BA9-84BA-0548CD8D3167}"/>
-    <hyperlink ref="B13" r:id="rId12" xr:uid="{3F6B392C-913E-4879-8C3F-C8EDE5C0C628}"/>
-    <hyperlink ref="B14" r:id="rId13" xr:uid="{C5D03E4D-384E-4F2E-B584-EB754AA1EC51}"/>
-    <hyperlink ref="B15" r:id="rId14" xr:uid="{4438EF86-C632-4762-BA87-39D3DF57E123}"/>
-    <hyperlink ref="B16" r:id="rId15" xr:uid="{953D4D13-1E13-4CD6-AAB4-804DCEA3E92F}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId16"/>
-  <legacyDrawing r:id="rId17"/>
-  <tableParts count="1">
-    <tablePart r:id="rId18"/>
-  </tableParts>
-</worksheet>
 </file>
--- a/Info/Additional_information.xlsx
+++ b/Info/Additional_information.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54EE9027-584F-4453-92D4-EEC7B28BE9B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D32B09DE-0775-4C6B-968A-C2F38F7561FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library_Link" sheetId="13" r:id="rId1"/>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="612">
   <si>
     <t>good quality (UNC for UNC collection; UNC and XF for XF collection)</t>
   </si>
@@ -1909,6 +1909,12 @@
   </si>
   <si>
     <t>https://dartalexator.github.io/CoinCollection/index.html</t>
+  </si>
+  <si>
+    <t>Virtual</t>
+  </si>
+  <si>
+    <t>00'</t>
   </si>
 </sst>
 </file>
@@ -2510,7 +2516,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2736,6 +2742,8 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="12" fillId="20" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2787,159 +2795,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="34">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color theme="0"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color theme="0"/>
-        </right>
-        <top style="thin">
-          <color theme="0"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="0"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thick">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -3100,6 +2964,103 @@
         <horizontal style="thin">
           <color auto="1"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="0"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color theme="0"/>
+        </right>
+        <top style="thin">
+          <color theme="0"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="0"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thick">
+          <color theme="0"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -3327,6 +3288,54 @@
         </horizontal>
       </border>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -3395,44 +3404,44 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{973D7237-72C7-453E-A0E1-526C93326B28}" name="Таблица3" displayName="Таблица3" ref="A1:F51" totalsRowShown="0" headerRowDxfId="33" dataDxfId="31" headerRowBorderDxfId="32" tableBorderDxfId="30" totalsRowBorderDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{973D7237-72C7-453E-A0E1-526C93326B28}" name="Таблица3" displayName="Таблица3" ref="A1:F51" totalsRowShown="0" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
   <autoFilter ref="A1:F51" xr:uid="{A2D8FA3D-4024-4365-BE1D-F93D0AF2D426}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{12C2DF0B-47FA-46A4-8424-55A1488EF88B}" name="ID" dataDxfId="28"/>
-    <tableColumn id="2" xr3:uid="{EB0B36CE-168D-429E-896D-DBA54794224F}" name="Name_Eng" dataDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{6C3A2CE8-252E-4C52-985B-8CDDFD9FA0C7}" name="OfficialMintName_Native" dataDxfId="26"/>
-    <tableColumn id="8" xr3:uid="{DA5871DC-2EDB-49C0-953E-EC0F70288E21}" name="Country" dataDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{FCD85F85-A94E-4BBE-9D3B-2B7494638375}" name="Mint_City" dataDxfId="24"/>
-    <tableColumn id="6" xr3:uid="{E5141978-CA91-4DE9-86F1-8A8AFA716534}" name="Alias" dataDxfId="23"/>
+    <tableColumn id="1" xr3:uid="{12C2DF0B-47FA-46A4-8424-55A1488EF88B}" name="ID" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{EB0B36CE-168D-429E-896D-DBA54794224F}" name="Name_Eng" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{6C3A2CE8-252E-4C52-985B-8CDDFD9FA0C7}" name="OfficialMintName_Native" dataDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{DA5871DC-2EDB-49C0-953E-EC0F70288E21}" name="Country" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{FCD85F85-A94E-4BBE-9D3B-2B7494638375}" name="Mint_City" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{E5141978-CA91-4DE9-86F1-8A8AFA716534}" name="Alias" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D0DCC88A-2D36-4004-A694-FC0C0F0C3396}" name="Таблица2" displayName="Таблица2" ref="A1:C16" totalsRowShown="0" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D0DCC88A-2D36-4004-A694-FC0C0F0C3396}" name="Таблица2" displayName="Таблица2" ref="A1:C16" totalsRowShown="0" headerRowBorderDxfId="16" tableBorderDxfId="15" totalsRowBorderDxfId="14">
   <autoFilter ref="A1:C16" xr:uid="{00000000-0009-0000-0100-000002000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{28358E6A-6F3A-468C-9E1C-880A34D9BECE}" name="№" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{28358E6A-6F3A-468C-9E1C-880A34D9BECE}" name="№" dataDxfId="13"/>
     <tableColumn id="2" xr3:uid="{DD0AD5C8-324B-4DA7-B39F-B2DB3EF91222}" name="Links:"/>
-    <tableColumn id="3" xr3:uid="{FC8A6018-CA7E-4C73-9B21-B272B55FA8C1}" name="Description:" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{FC8A6018-CA7E-4C73-9B21-B272B55FA8C1}" name="Description:" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9D0F8E3D-96B1-4DB8-B1A6-8DD6B84F3693}" name="Таблица35" displayName="Таблица35" ref="A1:D52" totalsRowShown="0" headerRowDxfId="22" dataDxfId="20" headerRowBorderDxfId="21" tableBorderDxfId="19" totalsRowBorderDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9D0F8E3D-96B1-4DB8-B1A6-8DD6B84F3693}" name="Таблица35" displayName="Таблица35" ref="A1:D52" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10" tableBorderDxfId="8" totalsRowBorderDxfId="7">
   <autoFilter ref="A1:D52" xr:uid="{A2D8FA3D-4024-4365-BE1D-F93D0AF2D426}"/>
   <tableColumns count="4">
-    <tableColumn id="4" xr3:uid="{74AFB32D-7AAA-46BE-8174-ED698BB4613E}" name="Mint_id" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{523D65CD-0F56-441F-90B5-E46A9B14F0D0}" name="Ekaterinburg Mint" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{1AAB7352-E935-4EC6-A0D1-3EDC5D0BC93C}" name="Year_of_start" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{5FF15381-476A-4F88-B93A-6452F2830A0A}" name="Year_of_end" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{74AFB32D-7AAA-46BE-8174-ED698BB4613E}" name="Mint_id" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{523D65CD-0F56-441F-90B5-E46A9B14F0D0}" name="Ekaterinburg Mint" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{1AAB7352-E935-4EC6-A0D1-3EDC5D0BC93C}" name="Year_of_start" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{5FF15381-476A-4F88-B93A-6452F2830A0A}" name="Year_of_end" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3446,9 +3455,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{8354E581-3B48-4762-81A7-EA76E36C4BB5}" name="№" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{1F45DC85-8ECA-45FE-BF45-E528619CEE0E}" name="Links:" dataDxfId="12" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{3FAE616B-3296-4770-9E56-8A824991EECA}" name="Description:" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{8354E581-3B48-4762-81A7-EA76E36C4BB5}" name="№" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{1F45DC85-8ECA-45FE-BF45-E528619CEE0E}" name="Links:" dataDxfId="1" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{3FAE616B-3296-4770-9E56-8A824991EECA}" name="Description:" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -3724,33 +3733,33 @@
   </cols>
   <sheetData>
     <row r="7" spans="2:26" ht="61.5" x14ac:dyDescent="1.35">
-      <c r="B7" s="105" t="s">
+      <c r="B7" s="85" t="s">
         <v>609</v>
       </c>
-      <c r="C7" s="104"/>
-      <c r="D7" s="104"/>
-      <c r="E7" s="104"/>
-      <c r="F7" s="104"/>
-      <c r="G7" s="104"/>
-      <c r="H7" s="104"/>
-      <c r="I7" s="104"/>
-      <c r="J7" s="104"/>
-      <c r="K7" s="104"/>
-      <c r="L7" s="104"/>
-      <c r="M7" s="104"/>
-      <c r="N7" s="104"/>
-      <c r="O7" s="104"/>
-      <c r="P7" s="104"/>
-      <c r="Q7" s="104"/>
-      <c r="R7" s="104"/>
-      <c r="S7" s="104"/>
-      <c r="T7" s="104"/>
-      <c r="U7" s="104"/>
-      <c r="V7" s="104"/>
-      <c r="W7" s="104"/>
-      <c r="X7" s="104"/>
-      <c r="Y7" s="104"/>
-      <c r="Z7" s="104"/>
+      <c r="C7" s="86"/>
+      <c r="D7" s="86"/>
+      <c r="E7" s="86"/>
+      <c r="F7" s="86"/>
+      <c r="G7" s="86"/>
+      <c r="H7" s="86"/>
+      <c r="I7" s="86"/>
+      <c r="J7" s="86"/>
+      <c r="K7" s="86"/>
+      <c r="L7" s="86"/>
+      <c r="M7" s="86"/>
+      <c r="N7" s="86"/>
+      <c r="O7" s="86"/>
+      <c r="P7" s="86"/>
+      <c r="Q7" s="86"/>
+      <c r="R7" s="86"/>
+      <c r="S7" s="86"/>
+      <c r="T7" s="86"/>
+      <c r="U7" s="86"/>
+      <c r="V7" s="86"/>
+      <c r="W7" s="86"/>
+      <c r="X7" s="86"/>
+      <c r="Y7" s="86"/>
+      <c r="Z7" s="86"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4405,12 +4414,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C7:C8">
-    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="33" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C7))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6">
-    <cfRule type="containsText" dxfId="4" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="32" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C6))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4427,7 +4436,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2">
-    <cfRule type="containsText" dxfId="3" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="31" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C2))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4444,7 +4453,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4">
-    <cfRule type="containsText" dxfId="2" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="30" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C4))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4461,7 +4470,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C5">
-    <cfRule type="containsText" dxfId="1" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="29" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C5))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4478,7 +4487,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3">
-    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="28" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C3))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -4543,10 +4552,10 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" s="91">
+      <c r="A2" s="93">
         <v>1</v>
       </c>
-      <c r="B2" s="99">
+      <c r="B2" s="101">
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
@@ -4563,8 +4572,8 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" s="92"/>
-      <c r="B3" s="99"/>
+      <c r="A3" s="94"/>
+      <c r="B3" s="101"/>
       <c r="C3" s="4" t="s">
         <v>65</v>
       </c>
@@ -4579,8 +4588,8 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" s="93"/>
-      <c r="B4" s="100">
+      <c r="A4" s="95"/>
+      <c r="B4" s="102">
         <v>2</v>
       </c>
       <c r="C4" s="4" t="s">
@@ -4597,14 +4606,14 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" s="93"/>
-      <c r="B5" s="100"/>
+      <c r="A5" s="95"/>
+      <c r="B5" s="102"/>
       <c r="C5" s="4" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6" s="93"/>
+      <c r="A6" s="95"/>
       <c r="B6" s="15">
         <v>3</v>
       </c>
@@ -4613,7 +4622,7 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" s="93"/>
+      <c r="A7" s="95"/>
       <c r="B7" s="16" t="s">
         <v>90</v>
       </c>
@@ -4622,8 +4631,8 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" s="93"/>
-      <c r="B8" s="101">
+      <c r="A8" s="95"/>
+      <c r="B8" s="103">
         <v>6</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -4631,14 +4640,14 @@
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="93"/>
-      <c r="B9" s="102"/>
+      <c r="A9" s="95"/>
+      <c r="B9" s="104"/>
       <c r="C9" s="4" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A10" s="93"/>
+      <c r="A10" s="95"/>
       <c r="B10" s="17">
         <v>7</v>
       </c>
@@ -4647,14 +4656,14 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="93"/>
+      <c r="A11" s="95"/>
       <c r="B11" s="24"/>
       <c r="C11" s="4" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="93"/>
+      <c r="A12" s="95"/>
       <c r="B12" s="18">
         <v>8</v>
       </c>
@@ -4663,7 +4672,7 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" s="94"/>
+      <c r="A13" s="96"/>
       <c r="B13" s="25" t="s">
         <v>78</v>
       </c>
@@ -4672,7 +4681,7 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="95"/>
+      <c r="A14" s="97"/>
       <c r="B14" s="26" t="s">
         <v>91</v>
       </c>
@@ -4681,7 +4690,7 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="14.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="96">
+      <c r="A15" s="98">
         <v>2</v>
       </c>
       <c r="B15" s="19" t="s">
@@ -4692,7 +4701,7 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="97"/>
+      <c r="A16" s="99"/>
       <c r="B16" s="20" t="s">
         <v>365</v>
       </c>
@@ -4701,7 +4710,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="97"/>
+      <c r="A17" s="99"/>
       <c r="B17" s="21" t="s">
         <v>366</v>
       </c>
@@ -4710,7 +4719,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="98"/>
+      <c r="A18" s="100"/>
       <c r="B18" s="22" t="s">
         <v>92</v>
       </c>
@@ -4719,7 +4728,7 @@
       </c>
     </row>
     <row r="19" spans="1:3" ht="14.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="85">
+      <c r="A19" s="87">
         <v>3</v>
       </c>
       <c r="B19" s="23" t="s">
@@ -4730,7 +4739,7 @@
       </c>
     </row>
     <row r="20" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="86"/>
+      <c r="A20" s="88"/>
       <c r="B20" s="27" t="s">
         <v>93</v>
       </c>
@@ -4739,7 +4748,7 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="87"/>
+      <c r="A21" s="89"/>
       <c r="B21" s="28" t="s">
         <v>95</v>
       </c>
@@ -4748,7 +4757,7 @@
       </c>
     </row>
     <row r="22" spans="1:3" ht="14.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="88">
+      <c r="A22" s="90">
         <v>4</v>
       </c>
       <c r="B22" s="19" t="s">
@@ -4759,7 +4768,7 @@
       </c>
     </row>
     <row r="23" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="89"/>
+      <c r="A23" s="91"/>
       <c r="B23" s="20" t="s">
         <v>98</v>
       </c>
@@ -4768,7 +4777,7 @@
       </c>
     </row>
     <row r="24" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="89"/>
+      <c r="A24" s="91"/>
       <c r="B24" s="21" t="s">
         <v>100</v>
       </c>
@@ -4777,7 +4786,7 @@
       </c>
     </row>
     <row r="25" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="89"/>
+      <c r="A25" s="91"/>
       <c r="B25" s="16" t="s">
         <v>102</v>
       </c>
@@ -4786,7 +4795,7 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" s="89"/>
+      <c r="A26" s="91"/>
       <c r="B26" s="29" t="s">
         <v>104</v>
       </c>
@@ -4795,7 +4804,7 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" s="89"/>
+      <c r="A27" s="91"/>
       <c r="B27" s="30" t="s">
         <v>106</v>
       </c>
@@ -4804,7 +4813,7 @@
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" s="89"/>
+      <c r="A28" s="91"/>
       <c r="B28" s="18">
         <v>8</v>
       </c>
@@ -4813,7 +4822,7 @@
       </c>
     </row>
     <row r="29" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="90"/>
+      <c r="A29" s="92"/>
       <c r="B29" s="31" t="s">
         <v>78</v>
       </c>
@@ -5394,11 +5403,11 @@
       <c r="D1" s="72" t="s">
         <v>395</v>
       </c>
-      <c r="W1" s="103" t="s">
+      <c r="W1" s="105" t="s">
         <v>405</v>
       </c>
-      <c r="X1" s="103"/>
-      <c r="Y1" s="103"/>
+      <c r="X1" s="105"/>
+      <c r="Y1" s="105"/>
     </row>
     <row r="2" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="77" t="s">
@@ -5458,6 +5467,12 @@
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A5" s="106" t="s">
+        <v>611</v>
+      </c>
+      <c r="B5" t="s">
+        <v>610</v>
+      </c>
       <c r="C5" s="73" t="s">
         <v>142</v>
       </c>
@@ -5581,6 +5596,12 @@
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="C14" s="106" t="s">
+        <v>611</v>
+      </c>
+      <c r="D14" t="s">
+        <v>610</v>
+      </c>
       <c r="X14" s="79" t="s">
         <v>416</v>
       </c>

--- a/Info/Additional_information.xlsx
+++ b/Info/Additional_information.xlsx
@@ -8,28 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D32B09DE-0775-4C6B-968A-C2F38F7561FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6C3954E-7927-4B29-BE7B-A3AC528C7A3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Library_Link" sheetId="13" r:id="rId1"/>
-    <sheet name="Colours_specifications" sheetId="1" r:id="rId2"/>
-    <sheet name="EURO albums content" sheetId="4" r:id="rId3"/>
-    <sheet name="albums_ID" sheetId="11" r:id="rId4"/>
-    <sheet name="albums ID naming" sheetId="9" r:id="rId5"/>
-    <sheet name="Лист1" sheetId="12" r:id="rId6"/>
-    <sheet name="Mint_Alias" sheetId="5" r:id="rId7"/>
-    <sheet name="Coin_Shops" sheetId="8" r:id="rId8"/>
-    <sheet name="Mint_work_years" sheetId="6" r:id="rId9"/>
-    <sheet name="File_Naming" sheetId="2" r:id="rId10"/>
-    <sheet name="Existing_subtypes" sheetId="3" r:id="rId11"/>
-    <sheet name="Links_to_Data" sheetId="7" r:id="rId12"/>
+    <sheet name="Colours_specifications" sheetId="1" r:id="rId1"/>
+    <sheet name="EURO albums content" sheetId="4" r:id="rId2"/>
+    <sheet name="albums_ID" sheetId="11" r:id="rId3"/>
+    <sheet name="albums ID naming" sheetId="9" r:id="rId4"/>
+    <sheet name="Лист1" sheetId="12" r:id="rId5"/>
+    <sheet name="Mint_Alias" sheetId="5" r:id="rId6"/>
+    <sheet name="Coin_Shops" sheetId="8" r:id="rId7"/>
+    <sheet name="Mint_work_years" sheetId="6" r:id="rId8"/>
+    <sheet name="File_Naming" sheetId="2" r:id="rId9"/>
+    <sheet name="Existing_subtypes" sheetId="3" r:id="rId10"/>
+    <sheet name="Links_to_Data" sheetId="7" r:id="rId11"/>
+    <sheet name="Library_Link" sheetId="13" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">albums_ID!$B$1:$E$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Colours_specifications!$A$1:$D$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'EURO albums content'!$A$1:$C$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">albums_ID!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Colours_specifications!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'EURO albums content'!$A$1:$C$15</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="615">
   <si>
     <t>good quality (UNC for UNC collection; UNC and XF for XF collection)</t>
   </si>
@@ -1915,6 +1915,15 @@
   </si>
   <si>
     <t>00'</t>
+  </si>
+  <si>
+    <t>Keywords</t>
+  </si>
+  <si>
+    <t>Юбилейные,2 евро,Монако,Monaco,дубли,монеты мира</t>
+  </si>
+  <si>
+    <t>Юбилейные,2 евро,Австрия,Бельгия,Кипр,Эстония,Франция,Италия,Латвия,Ирландия,Литва,Нидерланды,Португалия,Austria,Belgium,Cyprus,Estonia,France,Italy,Latvia,Ireland,Lithuania,Netherlands,Portugal</t>
   </si>
 </sst>
 </file>
@@ -2742,6 +2751,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="12" fillId="20" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2794,9 +2806,6 @@
     <xf numFmtId="49" fontId="9" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3725,572 +3734,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D5AF97D-14BA-4E23-B5FF-856D52BDA29A}">
-  <dimension ref="B7:Z7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="2" width="9.453125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="7" spans="2:26" ht="61.5" x14ac:dyDescent="1.35">
-      <c r="B7" s="85" t="s">
-        <v>609</v>
-      </c>
-      <c r="C7" s="86"/>
-      <c r="D7" s="86"/>
-      <c r="E7" s="86"/>
-      <c r="F7" s="86"/>
-      <c r="G7" s="86"/>
-      <c r="H7" s="86"/>
-      <c r="I7" s="86"/>
-      <c r="J7" s="86"/>
-      <c r="K7" s="86"/>
-      <c r="L7" s="86"/>
-      <c r="M7" s="86"/>
-      <c r="N7" s="86"/>
-      <c r="O7" s="86"/>
-      <c r="P7" s="86"/>
-      <c r="Q7" s="86"/>
-      <c r="R7" s="86"/>
-      <c r="S7" s="86"/>
-      <c r="T7" s="86"/>
-      <c r="U7" s="86"/>
-      <c r="V7" s="86"/>
-      <c r="W7" s="86"/>
-      <c r="X7" s="86"/>
-      <c r="Y7" s="86"/>
-      <c r="Z7" s="86"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B7:Z7"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="B7" r:id="rId1" xr:uid="{1B51AF5A-9579-4E45-802C-86E0D9768BAB}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0041FEF0-BF6F-4667-AFBD-1C23A1866795}">
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="10.7265625" customWidth="1"/>
-    <col min="2" max="2" width="17.453125" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="37.90625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="9">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="9">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="9">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="9">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="9">
-        <v>5</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="9">
-        <v>6</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8265AFD9-D9EB-4B75-B60D-6B7F7204230D}">
-  <dimension ref="A1:B29"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="26.36328125" customWidth="1"/>
-    <col min="2" max="2" width="31.36328125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" s="4"/>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" s="4"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="4"/>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" s="4"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="4"/>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="4"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="4"/>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" s="4"/>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="4"/>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" s="4"/>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B12" s="4"/>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B13" s="4"/>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" s="4"/>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B15" s="4"/>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B16" s="4"/>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B17" s="4"/>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B18" s="4"/>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B19" s="4"/>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B20" s="4"/>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B21" s="4"/>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B22" s="4"/>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B23" s="4"/>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A24" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B24" s="4"/>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B25" s="4"/>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A26" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B26" s="4"/>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A27" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B27" s="4"/>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A28" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B28" s="4"/>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A29" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="B29" s="4"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{729F7C06-1AE8-4162-8F40-6E9A64E311D7}">
-  <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="4.81640625" customWidth="1"/>
-    <col min="2" max="2" width="57.1796875" customWidth="1"/>
-    <col min="3" max="3" width="104.453125" customWidth="1"/>
-    <col min="4" max="4" width="15.453125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>303</v>
-      </c>
-      <c r="B1" s="45" t="s">
-        <v>304</v>
-      </c>
-      <c r="C1" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="41">
-        <v>1</v>
-      </c>
-      <c r="B2" s="46" t="s">
-        <v>306</v>
-      </c>
-      <c r="C2" s="47" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="41">
-        <v>2</v>
-      </c>
-      <c r="B3" s="46" t="s">
-        <v>308</v>
-      </c>
-      <c r="C3" s="47" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="41">
-        <v>3</v>
-      </c>
-      <c r="B4" s="46" t="s">
-        <v>310</v>
-      </c>
-      <c r="C4" s="47" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="41">
-        <v>4</v>
-      </c>
-      <c r="B5" s="46" t="s">
-        <v>312</v>
-      </c>
-      <c r="C5" s="47" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="41">
-        <v>5</v>
-      </c>
-      <c r="B6" s="46" t="s">
-        <v>314</v>
-      </c>
-      <c r="C6" s="47" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="41">
-        <v>6</v>
-      </c>
-      <c r="B7" s="46" t="s">
-        <v>316</v>
-      </c>
-      <c r="C7" s="47" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A8" s="41">
-        <v>7</v>
-      </c>
-      <c r="B8" s="46" t="s">
-        <v>318</v>
-      </c>
-      <c r="C8" s="47" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="41">
-        <v>8</v>
-      </c>
-      <c r="B9" s="46" t="s">
-        <v>320</v>
-      </c>
-      <c r="C9" s="47" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A10" s="41">
-        <v>9</v>
-      </c>
-      <c r="B10" s="46" t="s">
-        <v>322</v>
-      </c>
-      <c r="C10" s="47" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="41">
-        <v>10</v>
-      </c>
-      <c r="B11" s="46" t="s">
-        <v>324</v>
-      </c>
-      <c r="C11" s="47" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="41">
-        <v>11</v>
-      </c>
-      <c r="B12" s="46" t="s">
-        <v>324</v>
-      </c>
-      <c r="C12" s="47" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" s="41">
-        <v>12</v>
-      </c>
-      <c r="B13" s="46" t="s">
-        <v>327</v>
-      </c>
-      <c r="C13" s="47" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" s="41">
-        <v>13</v>
-      </c>
-      <c r="B14" s="48" t="s">
-        <v>329</v>
-      </c>
-      <c r="C14" s="49" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" s="50">
-        <v>14</v>
-      </c>
-      <c r="B15" s="48" t="s">
-        <v>331</v>
-      </c>
-      <c r="C15" s="49" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" s="50">
-        <v>15</v>
-      </c>
-      <c r="B16" s="48" t="s">
-        <v>333</v>
-      </c>
-      <c r="C16" s="49" t="s">
-        <v>332</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" location="p75892" xr:uid="{2004A8F5-EEA3-401A-8147-DCBE2B32B8A8}"/>
-    <hyperlink ref="B9" r:id="rId2" xr:uid="{3753811B-46E0-40E4-A28F-CA6D25194D0F}"/>
-    <hyperlink ref="B3" r:id="rId3" xr:uid="{ABC31D49-3E50-4123-A5E8-5A9AD3B5E23A}"/>
-    <hyperlink ref="B4" r:id="rId4" xr:uid="{9BB030EB-2475-45E8-8729-CB926565C2F2}"/>
-    <hyperlink ref="B5" r:id="rId5" xr:uid="{7321AD3B-4F9A-4715-8E78-C68C70C3ED3B}"/>
-    <hyperlink ref="B6" r:id="rId6" xr:uid="{548D83D1-6D3D-4818-ADA3-FE0E9231956A}"/>
-    <hyperlink ref="B7" r:id="rId7" xr:uid="{472B0F29-A646-4E1D-889A-066C1E7B1A15}"/>
-    <hyperlink ref="B8" r:id="rId8" xr:uid="{AC393C1F-E1F7-4A34-BAB9-9A5547AA9097}"/>
-    <hyperlink ref="B10" r:id="rId9" xr:uid="{03660F06-E14B-4321-BA0A-8107D65FCB9A}"/>
-    <hyperlink ref="B11" r:id="rId10" xr:uid="{4C30CEFE-89AC-45A8-B194-BA95B0264245}"/>
-    <hyperlink ref="B12" r:id="rId11" xr:uid="{6B68188A-ED23-4BA9-84BA-0548CD8D3167}"/>
-    <hyperlink ref="B13" r:id="rId12" xr:uid="{3F6B392C-913E-4879-8C3F-C8EDE5C0C628}"/>
-    <hyperlink ref="B14" r:id="rId13" xr:uid="{C5D03E4D-384E-4F2E-B584-EB754AA1EC51}"/>
-    <hyperlink ref="B15" r:id="rId14" xr:uid="{4438EF86-C632-4762-BA87-39D3DF57E123}"/>
-    <hyperlink ref="B16" r:id="rId15" xr:uid="{953D4D13-1E13-4CD6-AAB4-804DCEA3E92F}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId16"/>
-  <legacyDrawing r:id="rId17"/>
-  <tableParts count="1">
-    <tablePart r:id="rId18"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -4518,7 +3961,459 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8265AFD9-D9EB-4B75-B60D-6B7F7204230D}">
+  <dimension ref="A1:B29"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="26.36328125" customWidth="1"/>
+    <col min="2" max="2" width="31.36328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="4"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="4"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="4"/>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="4"/>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="4"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="4"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="4"/>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="4"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="4"/>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="4"/>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="4"/>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="4"/>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="4"/>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="4"/>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" s="4"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" s="4"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="4"/>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="4"/>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" s="4"/>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" s="4"/>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="4"/>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="4"/>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24" s="4"/>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" s="4"/>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" s="4"/>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" s="4"/>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B28" s="4"/>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="B29" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{729F7C06-1AE8-4162-8F40-6E9A64E311D7}">
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="4.81640625" customWidth="1"/>
+    <col min="2" max="2" width="57.1796875" customWidth="1"/>
+    <col min="3" max="3" width="104.453125" customWidth="1"/>
+    <col min="4" max="4" width="15.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B1" s="45" t="s">
+        <v>304</v>
+      </c>
+      <c r="C1" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="41">
+        <v>1</v>
+      </c>
+      <c r="B2" s="46" t="s">
+        <v>306</v>
+      </c>
+      <c r="C2" s="47" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" s="41">
+        <v>2</v>
+      </c>
+      <c r="B3" s="46" t="s">
+        <v>308</v>
+      </c>
+      <c r="C3" s="47" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="41">
+        <v>3</v>
+      </c>
+      <c r="B4" s="46" t="s">
+        <v>310</v>
+      </c>
+      <c r="C4" s="47" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="41">
+        <v>4</v>
+      </c>
+      <c r="B5" s="46" t="s">
+        <v>312</v>
+      </c>
+      <c r="C5" s="47" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="41">
+        <v>5</v>
+      </c>
+      <c r="B6" s="46" t="s">
+        <v>314</v>
+      </c>
+      <c r="C6" s="47" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="41">
+        <v>6</v>
+      </c>
+      <c r="B7" s="46" t="s">
+        <v>316</v>
+      </c>
+      <c r="C7" s="47" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A8" s="41">
+        <v>7</v>
+      </c>
+      <c r="B8" s="46" t="s">
+        <v>318</v>
+      </c>
+      <c r="C8" s="47" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="41">
+        <v>8</v>
+      </c>
+      <c r="B9" s="46" t="s">
+        <v>320</v>
+      </c>
+      <c r="C9" s="47" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A10" s="41">
+        <v>9</v>
+      </c>
+      <c r="B10" s="46" t="s">
+        <v>322</v>
+      </c>
+      <c r="C10" s="47" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="41">
+        <v>10</v>
+      </c>
+      <c r="B11" s="46" t="s">
+        <v>324</v>
+      </c>
+      <c r="C11" s="47" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" s="41">
+        <v>11</v>
+      </c>
+      <c r="B12" s="46" t="s">
+        <v>324</v>
+      </c>
+      <c r="C12" s="47" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" s="41">
+        <v>12</v>
+      </c>
+      <c r="B13" s="46" t="s">
+        <v>327</v>
+      </c>
+      <c r="C13" s="47" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" s="41">
+        <v>13</v>
+      </c>
+      <c r="B14" s="48" t="s">
+        <v>329</v>
+      </c>
+      <c r="C14" s="49" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="50">
+        <v>14</v>
+      </c>
+      <c r="B15" s="48" t="s">
+        <v>331</v>
+      </c>
+      <c r="C15" s="49" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" s="50">
+        <v>15</v>
+      </c>
+      <c r="B16" s="48" t="s">
+        <v>333</v>
+      </c>
+      <c r="C16" s="49" t="s">
+        <v>332</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" location="p75892" xr:uid="{2004A8F5-EEA3-401A-8147-DCBE2B32B8A8}"/>
+    <hyperlink ref="B9" r:id="rId2" xr:uid="{3753811B-46E0-40E4-A28F-CA6D25194D0F}"/>
+    <hyperlink ref="B3" r:id="rId3" xr:uid="{ABC31D49-3E50-4123-A5E8-5A9AD3B5E23A}"/>
+    <hyperlink ref="B4" r:id="rId4" xr:uid="{9BB030EB-2475-45E8-8729-CB926565C2F2}"/>
+    <hyperlink ref="B5" r:id="rId5" xr:uid="{7321AD3B-4F9A-4715-8E78-C68C70C3ED3B}"/>
+    <hyperlink ref="B6" r:id="rId6" xr:uid="{548D83D1-6D3D-4818-ADA3-FE0E9231956A}"/>
+    <hyperlink ref="B7" r:id="rId7" xr:uid="{472B0F29-A646-4E1D-889A-066C1E7B1A15}"/>
+    <hyperlink ref="B8" r:id="rId8" xr:uid="{AC393C1F-E1F7-4A34-BAB9-9A5547AA9097}"/>
+    <hyperlink ref="B10" r:id="rId9" xr:uid="{03660F06-E14B-4321-BA0A-8107D65FCB9A}"/>
+    <hyperlink ref="B11" r:id="rId10" xr:uid="{4C30CEFE-89AC-45A8-B194-BA95B0264245}"/>
+    <hyperlink ref="B12" r:id="rId11" xr:uid="{6B68188A-ED23-4BA9-84BA-0548CD8D3167}"/>
+    <hyperlink ref="B13" r:id="rId12" xr:uid="{3F6B392C-913E-4879-8C3F-C8EDE5C0C628}"/>
+    <hyperlink ref="B14" r:id="rId13" xr:uid="{C5D03E4D-384E-4F2E-B584-EB754AA1EC51}"/>
+    <hyperlink ref="B15" r:id="rId14" xr:uid="{4438EF86-C632-4762-BA87-39D3DF57E123}"/>
+    <hyperlink ref="B16" r:id="rId15" xr:uid="{953D4D13-1E13-4CD6-AAB4-804DCEA3E92F}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId16"/>
+  <legacyDrawing r:id="rId17"/>
+  <tableParts count="1">
+    <tablePart r:id="rId18"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D5AF97D-14BA-4E23-B5FF-856D52BDA29A}">
+  <dimension ref="B7:Z7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="9.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="7" spans="2:26" ht="61.5" x14ac:dyDescent="1.35">
+      <c r="B7" s="86" t="s">
+        <v>609</v>
+      </c>
+      <c r="C7" s="87"/>
+      <c r="D7" s="87"/>
+      <c r="E7" s="87"/>
+      <c r="F7" s="87"/>
+      <c r="G7" s="87"/>
+      <c r="H7" s="87"/>
+      <c r="I7" s="87"/>
+      <c r="J7" s="87"/>
+      <c r="K7" s="87"/>
+      <c r="L7" s="87"/>
+      <c r="M7" s="87"/>
+      <c r="N7" s="87"/>
+      <c r="O7" s="87"/>
+      <c r="P7" s="87"/>
+      <c r="Q7" s="87"/>
+      <c r="R7" s="87"/>
+      <c r="S7" s="87"/>
+      <c r="T7" s="87"/>
+      <c r="U7" s="87"/>
+      <c r="V7" s="87"/>
+      <c r="W7" s="87"/>
+      <c r="X7" s="87"/>
+      <c r="Y7" s="87"/>
+      <c r="Z7" s="87"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B7:Z7"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="B7" r:id="rId1" xr:uid="{1B51AF5A-9579-4E45-802C-86E0D9768BAB}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57D9DE6C-583F-4F0B-9E0F-CDE5965E194A}">
   <dimension ref="A1:I30"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -4552,10 +4447,10 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" s="93">
+      <c r="A2" s="94">
         <v>1</v>
       </c>
-      <c r="B2" s="101">
+      <c r="B2" s="102">
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
@@ -4572,8 +4467,8 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" s="94"/>
-      <c r="B3" s="101"/>
+      <c r="A3" s="95"/>
+      <c r="B3" s="102"/>
       <c r="C3" s="4" t="s">
         <v>65</v>
       </c>
@@ -4588,8 +4483,8 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" s="95"/>
-      <c r="B4" s="102">
+      <c r="A4" s="96"/>
+      <c r="B4" s="103">
         <v>2</v>
       </c>
       <c r="C4" s="4" t="s">
@@ -4606,14 +4501,14 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" s="95"/>
-      <c r="B5" s="102"/>
+      <c r="A5" s="96"/>
+      <c r="B5" s="103"/>
       <c r="C5" s="4" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6" s="95"/>
+      <c r="A6" s="96"/>
       <c r="B6" s="15">
         <v>3</v>
       </c>
@@ -4622,7 +4517,7 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" s="95"/>
+      <c r="A7" s="96"/>
       <c r="B7" s="16" t="s">
         <v>90</v>
       </c>
@@ -4631,8 +4526,8 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" s="95"/>
-      <c r="B8" s="103">
+      <c r="A8" s="96"/>
+      <c r="B8" s="104">
         <v>6</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -4640,14 +4535,14 @@
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="95"/>
-      <c r="B9" s="104"/>
+      <c r="A9" s="96"/>
+      <c r="B9" s="105"/>
       <c r="C9" s="4" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A10" s="95"/>
+      <c r="A10" s="96"/>
       <c r="B10" s="17">
         <v>7</v>
       </c>
@@ -4656,14 +4551,14 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="95"/>
+      <c r="A11" s="96"/>
       <c r="B11" s="24"/>
       <c r="C11" s="4" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="95"/>
+      <c r="A12" s="96"/>
       <c r="B12" s="18">
         <v>8</v>
       </c>
@@ -4672,7 +4567,7 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" s="96"/>
+      <c r="A13" s="97"/>
       <c r="B13" s="25" t="s">
         <v>78</v>
       </c>
@@ -4681,7 +4576,7 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="97"/>
+      <c r="A14" s="98"/>
       <c r="B14" s="26" t="s">
         <v>91</v>
       </c>
@@ -4690,7 +4585,7 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="14.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="98">
+      <c r="A15" s="99">
         <v>2</v>
       </c>
       <c r="B15" s="19" t="s">
@@ -4701,7 +4596,7 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="99"/>
+      <c r="A16" s="100"/>
       <c r="B16" s="20" t="s">
         <v>365</v>
       </c>
@@ -4710,7 +4605,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="99"/>
+      <c r="A17" s="100"/>
       <c r="B17" s="21" t="s">
         <v>366</v>
       </c>
@@ -4719,7 +4614,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="100"/>
+      <c r="A18" s="101"/>
       <c r="B18" s="22" t="s">
         <v>92</v>
       </c>
@@ -4728,7 +4623,7 @@
       </c>
     </row>
     <row r="19" spans="1:3" ht="14.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="87">
+      <c r="A19" s="88">
         <v>3</v>
       </c>
       <c r="B19" s="23" t="s">
@@ -4739,7 +4634,7 @@
       </c>
     </row>
     <row r="20" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="88"/>
+      <c r="A20" s="89"/>
       <c r="B20" s="27" t="s">
         <v>93</v>
       </c>
@@ -4748,7 +4643,7 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="89"/>
+      <c r="A21" s="90"/>
       <c r="B21" s="28" t="s">
         <v>95</v>
       </c>
@@ -4757,7 +4652,7 @@
       </c>
     </row>
     <row r="22" spans="1:3" ht="14.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="90">
+      <c r="A22" s="91">
         <v>4</v>
       </c>
       <c r="B22" s="19" t="s">
@@ -4768,7 +4663,7 @@
       </c>
     </row>
     <row r="23" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="91"/>
+      <c r="A23" s="92"/>
       <c r="B23" s="20" t="s">
         <v>98</v>
       </c>
@@ -4777,7 +4672,7 @@
       </c>
     </row>
     <row r="24" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="91"/>
+      <c r="A24" s="92"/>
       <c r="B24" s="21" t="s">
         <v>100</v>
       </c>
@@ -4786,7 +4681,7 @@
       </c>
     </row>
     <row r="25" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="91"/>
+      <c r="A25" s="92"/>
       <c r="B25" s="16" t="s">
         <v>102</v>
       </c>
@@ -4795,7 +4690,7 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" s="91"/>
+      <c r="A26" s="92"/>
       <c r="B26" s="29" t="s">
         <v>104</v>
       </c>
@@ -4804,7 +4699,7 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" s="91"/>
+      <c r="A27" s="92"/>
       <c r="B27" s="30" t="s">
         <v>106</v>
       </c>
@@ -4813,7 +4708,7 @@
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" s="91"/>
+      <c r="A28" s="92"/>
       <c r="B28" s="18">
         <v>8</v>
       </c>
@@ -4822,7 +4717,7 @@
       </c>
     </row>
     <row r="29" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="92"/>
+      <c r="A29" s="93"/>
       <c r="B29" s="31" t="s">
         <v>78</v>
       </c>
@@ -4850,9 +4745,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DC835FD-69FE-4DBC-957F-9A46CA05517E}">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.453125" customWidth="1"/>
@@ -4860,10 +4755,10 @@
     <col min="3" max="3" width="70" customWidth="1"/>
     <col min="4" max="4" width="89.08984375" customWidth="1"/>
     <col min="5" max="5" width="84.6328125" customWidth="1"/>
-    <col min="6" max="6" width="8.453125" customWidth="1"/>
+    <col min="6" max="6" width="72" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="78" t="s">
         <v>536</v>
       </c>
@@ -4879,8 +4774,11 @@
       <c r="E1" s="78" t="s">
         <v>397</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F1" s="78" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
@@ -4896,8 +4794,11 @@
       <c r="E2" s="83" t="s">
         <v>527</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F2" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -4913,8 +4814,11 @@
       <c r="E3" s="83" t="s">
         <v>532</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F3" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2</v>
       </c>
@@ -4931,7 +4835,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>3</v>
       </c>
@@ -4948,7 +4852,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>4</v>
       </c>
@@ -4965,7 +4869,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>5</v>
       </c>
@@ -4982,7 +4886,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>6</v>
       </c>
@@ -4999,7 +4903,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>7</v>
       </c>
@@ -5016,7 +4920,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>8</v>
       </c>
@@ -5033,7 +4937,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>9</v>
       </c>
@@ -5050,7 +4954,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>10</v>
       </c>
@@ -5067,7 +4971,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>11</v>
       </c>
@@ -5084,7 +4988,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>12</v>
       </c>
@@ -5101,7 +5005,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>13</v>
       </c>
@@ -5118,7 +5022,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>14</v>
       </c>
@@ -5340,7 +5244,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:E1" xr:uid="{1DC835FD-69FE-4DBC-957F-9A46CA05517E}"/>
+  <autoFilter ref="A1:F1" xr:uid="{1DC835FD-69FE-4DBC-957F-9A46CA05517E}"/>
   <phoneticPr fontId="18" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" xr:uid="{A9DAC5E2-B569-49C7-B7C7-5FB2F0F45121}"/>
@@ -5376,7 +5280,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{866E9A5E-386D-439E-AA25-CB46A31C625C}">
   <dimension ref="A1:Z50"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -5403,11 +5307,11 @@
       <c r="D1" s="72" t="s">
         <v>395</v>
       </c>
-      <c r="W1" s="105" t="s">
+      <c r="W1" s="106" t="s">
         <v>405</v>
       </c>
-      <c r="X1" s="105"/>
-      <c r="Y1" s="105"/>
+      <c r="X1" s="106"/>
+      <c r="Y1" s="106"/>
     </row>
     <row r="2" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="77" t="s">
@@ -5467,7 +5371,7 @@
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A5" s="106" t="s">
+      <c r="A5" s="85" t="s">
         <v>611</v>
       </c>
       <c r="B5" t="s">
@@ -5596,7 +5500,7 @@
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="C14" s="106" t="s">
+      <c r="C14" s="85" t="s">
         <v>611</v>
       </c>
       <c r="D14" t="s">
@@ -5905,7 +5809,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7B3F3C9-87AF-45FC-9E9F-2A256D1F4917}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -5914,7 +5818,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4C14141-45DA-4C30-845C-3E630B347F10}">
   <dimension ref="A1:F51"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -6954,7 +6858,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8049D8E-7482-48AF-95C9-7F1B728B0DDE}">
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -7152,7 +7056,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF1BA8E2-9FD2-4C47-B5D3-EF9907B8F692}">
   <dimension ref="A1:D52"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -7826,4 +7730,118 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0041FEF0-BF6F-4667-AFBD-1C23A1866795}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.7265625" customWidth="1"/>
+    <col min="2" max="2" width="17.453125" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="37.90625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="9">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="9">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="9">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="9">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="9">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="9">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Info/Additional_information.xlsx
+++ b/Info/Additional_information.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6C3954E-7927-4B29-BE7B-A3AC528C7A3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47837715-4139-4BDD-B455-B3CC3DAB14DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="616">
   <si>
     <t>good quality (UNC for UNC collection; UNC and XF for XF collection)</t>
   </si>
@@ -1924,6 +1924,9 @@
   </si>
   <si>
     <t>Юбилейные,2 евро,Австрия,Бельгия,Кипр,Эстония,Франция,Италия,Латвия,Ирландия,Литва,Нидерланды,Португалия,Austria,Belgium,Cyprus,Estonia,France,Italy,Latvia,Ireland,Lithuania,Netherlands,Portugal</t>
+  </si>
+  <si>
+    <t>Юбилейные,2 евро,Германия,Люксембург,Мальта,Germany,Luxembourg,Malta</t>
   </si>
 </sst>
 </file>
@@ -2754,8 +2757,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="12" fillId="20" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2807,6 +2808,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -4374,33 +4377,33 @@
   </cols>
   <sheetData>
     <row r="7" spans="2:26" ht="61.5" x14ac:dyDescent="1.35">
-      <c r="B7" s="86" t="s">
+      <c r="B7" s="105" t="s">
         <v>609</v>
       </c>
-      <c r="C7" s="87"/>
-      <c r="D7" s="87"/>
-      <c r="E7" s="87"/>
-      <c r="F7" s="87"/>
-      <c r="G7" s="87"/>
-      <c r="H7" s="87"/>
-      <c r="I7" s="87"/>
-      <c r="J7" s="87"/>
-      <c r="K7" s="87"/>
-      <c r="L7" s="87"/>
-      <c r="M7" s="87"/>
-      <c r="N7" s="87"/>
-      <c r="O7" s="87"/>
-      <c r="P7" s="87"/>
-      <c r="Q7" s="87"/>
-      <c r="R7" s="87"/>
-      <c r="S7" s="87"/>
-      <c r="T7" s="87"/>
-      <c r="U7" s="87"/>
-      <c r="V7" s="87"/>
-      <c r="W7" s="87"/>
-      <c r="X7" s="87"/>
-      <c r="Y7" s="87"/>
-      <c r="Z7" s="87"/>
+      <c r="C7" s="106"/>
+      <c r="D7" s="106"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="106"/>
+      <c r="G7" s="106"/>
+      <c r="H7" s="106"/>
+      <c r="I7" s="106"/>
+      <c r="J7" s="106"/>
+      <c r="K7" s="106"/>
+      <c r="L7" s="106"/>
+      <c r="M7" s="106"/>
+      <c r="N7" s="106"/>
+      <c r="O7" s="106"/>
+      <c r="P7" s="106"/>
+      <c r="Q7" s="106"/>
+      <c r="R7" s="106"/>
+      <c r="S7" s="106"/>
+      <c r="T7" s="106"/>
+      <c r="U7" s="106"/>
+      <c r="V7" s="106"/>
+      <c r="W7" s="106"/>
+      <c r="X7" s="106"/>
+      <c r="Y7" s="106"/>
+      <c r="Z7" s="106"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4447,10 +4450,10 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" s="94">
+      <c r="A2" s="92">
         <v>1</v>
       </c>
-      <c r="B2" s="102">
+      <c r="B2" s="100">
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
@@ -4467,8 +4470,8 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" s="95"/>
-      <c r="B3" s="102"/>
+      <c r="A3" s="93"/>
+      <c r="B3" s="100"/>
       <c r="C3" s="4" t="s">
         <v>65</v>
       </c>
@@ -4483,8 +4486,8 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" s="96"/>
-      <c r="B4" s="103">
+      <c r="A4" s="94"/>
+      <c r="B4" s="101">
         <v>2</v>
       </c>
       <c r="C4" s="4" t="s">
@@ -4501,14 +4504,14 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" s="96"/>
-      <c r="B5" s="103"/>
+      <c r="A5" s="94"/>
+      <c r="B5" s="101"/>
       <c r="C5" s="4" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6" s="96"/>
+      <c r="A6" s="94"/>
       <c r="B6" s="15">
         <v>3</v>
       </c>
@@ -4517,7 +4520,7 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" s="96"/>
+      <c r="A7" s="94"/>
       <c r="B7" s="16" t="s">
         <v>90</v>
       </c>
@@ -4526,8 +4529,8 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" s="96"/>
-      <c r="B8" s="104">
+      <c r="A8" s="94"/>
+      <c r="B8" s="102">
         <v>6</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -4535,14 +4538,14 @@
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="96"/>
-      <c r="B9" s="105"/>
+      <c r="A9" s="94"/>
+      <c r="B9" s="103"/>
       <c r="C9" s="4" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A10" s="96"/>
+      <c r="A10" s="94"/>
       <c r="B10" s="17">
         <v>7</v>
       </c>
@@ -4551,14 +4554,14 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="96"/>
+      <c r="A11" s="94"/>
       <c r="B11" s="24"/>
       <c r="C11" s="4" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="96"/>
+      <c r="A12" s="94"/>
       <c r="B12" s="18">
         <v>8</v>
       </c>
@@ -4567,7 +4570,7 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" s="97"/>
+      <c r="A13" s="95"/>
       <c r="B13" s="25" t="s">
         <v>78</v>
       </c>
@@ -4576,7 +4579,7 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="98"/>
+      <c r="A14" s="96"/>
       <c r="B14" s="26" t="s">
         <v>91</v>
       </c>
@@ -4585,7 +4588,7 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="14.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="99">
+      <c r="A15" s="97">
         <v>2</v>
       </c>
       <c r="B15" s="19" t="s">
@@ -4596,7 +4599,7 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="100"/>
+      <c r="A16" s="98"/>
       <c r="B16" s="20" t="s">
         <v>365</v>
       </c>
@@ -4605,7 +4608,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="100"/>
+      <c r="A17" s="98"/>
       <c r="B17" s="21" t="s">
         <v>366</v>
       </c>
@@ -4614,7 +4617,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="101"/>
+      <c r="A18" s="99"/>
       <c r="B18" s="22" t="s">
         <v>92</v>
       </c>
@@ -4623,7 +4626,7 @@
       </c>
     </row>
     <row r="19" spans="1:3" ht="14.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="88">
+      <c r="A19" s="86">
         <v>3</v>
       </c>
       <c r="B19" s="23" t="s">
@@ -4634,7 +4637,7 @@
       </c>
     </row>
     <row r="20" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="89"/>
+      <c r="A20" s="87"/>
       <c r="B20" s="27" t="s">
         <v>93</v>
       </c>
@@ -4643,7 +4646,7 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="90"/>
+      <c r="A21" s="88"/>
       <c r="B21" s="28" t="s">
         <v>95</v>
       </c>
@@ -4652,7 +4655,7 @@
       </c>
     </row>
     <row r="22" spans="1:3" ht="14.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="91">
+      <c r="A22" s="89">
         <v>4</v>
       </c>
       <c r="B22" s="19" t="s">
@@ -4663,7 +4666,7 @@
       </c>
     </row>
     <row r="23" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="92"/>
+      <c r="A23" s="90"/>
       <c r="B23" s="20" t="s">
         <v>98</v>
       </c>
@@ -4672,7 +4675,7 @@
       </c>
     </row>
     <row r="24" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="92"/>
+      <c r="A24" s="90"/>
       <c r="B24" s="21" t="s">
         <v>100</v>
       </c>
@@ -4681,7 +4684,7 @@
       </c>
     </row>
     <row r="25" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="92"/>
+      <c r="A25" s="90"/>
       <c r="B25" s="16" t="s">
         <v>102</v>
       </c>
@@ -4690,7 +4693,7 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" s="92"/>
+      <c r="A26" s="90"/>
       <c r="B26" s="29" t="s">
         <v>104</v>
       </c>
@@ -4699,7 +4702,7 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" s="92"/>
+      <c r="A27" s="90"/>
       <c r="B27" s="30" t="s">
         <v>106</v>
       </c>
@@ -4708,7 +4711,7 @@
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" s="92"/>
+      <c r="A28" s="90"/>
       <c r="B28" s="18">
         <v>8</v>
       </c>
@@ -4717,7 +4720,7 @@
       </c>
     </row>
     <row r="29" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="93"/>
+      <c r="A29" s="91"/>
       <c r="B29" s="31" t="s">
         <v>78</v>
       </c>
@@ -4833,6 +4836,9 @@
       </c>
       <c r="E4" s="83" t="s">
         <v>533</v>
+      </c>
+      <c r="F4" t="s">
+        <v>615</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -5307,11 +5313,11 @@
       <c r="D1" s="72" t="s">
         <v>395</v>
       </c>
-      <c r="W1" s="106" t="s">
+      <c r="W1" s="104" t="s">
         <v>405</v>
       </c>
-      <c r="X1" s="106"/>
-      <c r="Y1" s="106"/>
+      <c r="X1" s="104"/>
+      <c r="Y1" s="104"/>
     </row>
     <row r="2" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="77" t="s">

--- a/Info/Additional_information.xlsx
+++ b/Info/Additional_information.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47837715-4139-4BDD-B455-B3CC3DAB14DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCBB1B73-04C2-4517-A1C2-D11AED08894B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="616">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="628">
   <si>
     <t>good quality (UNC for UNC collection; UNC and XF for XF collection)</t>
   </si>
@@ -1920,13 +1920,49 @@
     <t>Keywords</t>
   </si>
   <si>
-    <t>Юбилейные,2 евро,Монако,Monaco,дубли,монеты мира</t>
-  </si>
-  <si>
-    <t>Юбилейные,2 евро,Австрия,Бельгия,Кипр,Эстония,Франция,Италия,Латвия,Ирландия,Литва,Нидерланды,Португалия,Austria,Belgium,Cyprus,Estonia,France,Italy,Latvia,Ireland,Lithuania,Netherlands,Portugal</t>
-  </si>
-  <si>
-    <t>Юбилейные,2 евро,Германия,Люксембург,Мальта,Germany,Luxembourg,Malta</t>
+    <t>Null,Пусто,пустой</t>
+  </si>
+  <si>
+    <t>Юбилейные,США,$,двор D,доллар,USA</t>
+  </si>
+  <si>
+    <t>Юбилейные,США,$,двор P,двор S,Дворы P и S,доллар,USA</t>
+  </si>
+  <si>
+    <t>Юбилейные,Россия,РФ,Рубль,рубли,Russian Federation</t>
+  </si>
+  <si>
+    <t>Юбилейные,2 евро,Монако,Monaco,дубли,монеты мира,еврозона</t>
+  </si>
+  <si>
+    <t>Юбилейные,2 евро,Австрия,Austria,Бельгия,Belgium,Кипр,Cyprus,Эстония,Estonia,Франция,France,Италия,Italy,Латвия,Latvia,Ирландия,Ireland,Литва,Lithuania,Нидерланды,Netherlands,Португалия,Portugal,еврозона</t>
+  </si>
+  <si>
+    <t>Юбилейные,2 евро,Германия,Germany,Люксембург,Luxembourg,Мальта,Malta,еврозона</t>
+  </si>
+  <si>
+    <t>Юбилейные,2 евро,Андорра,Andorra,Сан-Марино,San Marino,San-Marino,Ватикан,Vatican City,еврозона</t>
+  </si>
+  <si>
+    <t>Юбилейные,2 евро,Финляндия,Finland,Испания,Spain,Словения,Slovenia,Словакия,Slovakia,Хорватия,Croatia,Греция,Greece,еврозона</t>
+  </si>
+  <si>
+    <t>Регулярка,Регулярные,евро,евроцент,Австрия,Austria,Бельгия,Belgium,Болгария,Bulgaria,Хорватия,Croatia,Кипр,Cyprus,Эстония,Estonia,Финляндия,Finland,Франция,France,Германия,GermanyГреция,Greece,Ирландия,Ireland,Италия,Italy,Латвия,Latvia,Люксембург,Luxembourg,Мальта,Malta,еврозона</t>
+  </si>
+  <si>
+    <t>Регулярка,Регулярные,евро,евроцент,еврозона,Монако,Monaco,Нидерланды,Netherlands,Португалия,Portugal,Сан-Марино,San Marino,San-Marino,Словакия,Slovakia,Испания,Spain</t>
+  </si>
+  <si>
+    <t>Регулярка,Регулярные,США,$,двор P,двор S,Дворы P и S,доллар,USA</t>
+  </si>
+  <si>
+    <t>Регулярка,Регулярные,США,$,двор D,доллар,USA</t>
+  </si>
+  <si>
+    <t>Регулярка,Регулярные,Россия,РФ,Рубль,рубли,Russian Federation</t>
+  </si>
+  <si>
+    <t>Регулярка,Регулярные,СССР,Россия,Рубль,рубли,USSR,Советский союз, Soviet Union</t>
   </si>
 </sst>
 </file>
@@ -4758,7 +4794,7 @@
     <col min="3" max="3" width="70" customWidth="1"/>
     <col min="4" max="4" width="89.08984375" customWidth="1"/>
     <col min="5" max="5" width="84.6328125" customWidth="1"/>
-    <col min="6" max="6" width="72" customWidth="1"/>
+    <col min="6" max="6" width="182.36328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
@@ -4798,7 +4834,7 @@
         <v>527</v>
       </c>
       <c r="F2" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -4818,7 +4854,7 @@
         <v>532</v>
       </c>
       <c r="F3" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -4838,7 +4874,7 @@
         <v>533</v>
       </c>
       <c r="F4" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -4857,6 +4893,9 @@
       <c r="E5" s="83" t="s">
         <v>534</v>
       </c>
+      <c r="F5" t="s">
+        <v>620</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6">
@@ -4874,6 +4913,9 @@
       <c r="E6" s="83" t="s">
         <v>535</v>
       </c>
+      <c r="F6" t="s">
+        <v>621</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7">
@@ -4891,6 +4933,9 @@
       <c r="E7" s="83" t="s">
         <v>607</v>
       </c>
+      <c r="F7" t="s">
+        <v>613</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8">
@@ -4908,6 +4953,9 @@
       <c r="E8" s="83" t="s">
         <v>608</v>
       </c>
+      <c r="F8" t="s">
+        <v>613</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9">
@@ -4925,6 +4973,9 @@
       <c r="E9" s="83" t="s">
         <v>539</v>
       </c>
+      <c r="F9" t="s">
+        <v>615</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10">
@@ -4942,6 +4993,9 @@
       <c r="E10" s="83" t="s">
         <v>540</v>
       </c>
+      <c r="F10" t="s">
+        <v>614</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11">
@@ -4959,6 +5013,9 @@
       <c r="E11" s="83" t="s">
         <v>543</v>
       </c>
+      <c r="F11" t="s">
+        <v>616</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12">
@@ -4976,6 +5033,9 @@
       <c r="E12" s="83" t="s">
         <v>544</v>
       </c>
+      <c r="F12" t="s">
+        <v>616</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13">
@@ -4993,6 +5053,9 @@
       <c r="E13" s="83" t="s">
         <v>547</v>
       </c>
+      <c r="F13" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14">
@@ -5010,6 +5073,9 @@
       <c r="E14" s="83" t="s">
         <v>548</v>
       </c>
+      <c r="F14" t="s">
+        <v>623</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15">
@@ -5027,6 +5093,9 @@
       <c r="E15" s="83" t="s">
         <v>551</v>
       </c>
+      <c r="F15" t="s">
+        <v>624</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16">
@@ -5044,8 +5113,11 @@
       <c r="E16" s="83" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F16" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>15</v>
       </c>
@@ -5061,8 +5133,11 @@
       <c r="E17" s="83" t="s">
         <v>558</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F17" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>16</v>
       </c>
@@ -5078,8 +5153,11 @@
       <c r="E18" s="83" t="s">
         <v>562</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F18" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>17</v>
       </c>
@@ -5096,7 +5174,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>18</v>
       </c>
@@ -5113,7 +5191,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>19</v>
       </c>
@@ -5130,7 +5208,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>20</v>
       </c>
@@ -5147,7 +5225,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>21</v>
       </c>
@@ -5164,7 +5242,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>22</v>
       </c>
@@ -5181,7 +5259,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>23</v>
       </c>
@@ -5198,7 +5276,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>24</v>
       </c>
@@ -5215,7 +5293,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>25</v>
       </c>
@@ -5232,7 +5310,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>26</v>
       </c>

--- a/Info/Additional_information.xlsx
+++ b/Info/Additional_information.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCBB1B73-04C2-4517-A1C2-D11AED08894B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{472FF70B-05F9-4DEB-B758-8EB77759CCAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,14 +17,13 @@
     <sheet name="EURO albums content" sheetId="4" r:id="rId2"/>
     <sheet name="albums_ID" sheetId="11" r:id="rId3"/>
     <sheet name="albums ID naming" sheetId="9" r:id="rId4"/>
-    <sheet name="Лист1" sheetId="12" r:id="rId5"/>
-    <sheet name="Mint_Alias" sheetId="5" r:id="rId6"/>
-    <sheet name="Coin_Shops" sheetId="8" r:id="rId7"/>
-    <sheet name="Mint_work_years" sheetId="6" r:id="rId8"/>
-    <sheet name="File_Naming" sheetId="2" r:id="rId9"/>
-    <sheet name="Existing_subtypes" sheetId="3" r:id="rId10"/>
-    <sheet name="Links_to_Data" sheetId="7" r:id="rId11"/>
-    <sheet name="Library_Link" sheetId="13" r:id="rId12"/>
+    <sheet name="Mint_Alias" sheetId="5" r:id="rId5"/>
+    <sheet name="Coin_Shops" sheetId="8" r:id="rId6"/>
+    <sheet name="Mint_work_years" sheetId="6" r:id="rId7"/>
+    <sheet name="File_Naming" sheetId="2" r:id="rId8"/>
+    <sheet name="Existing_subtypes" sheetId="3" r:id="rId9"/>
+    <sheet name="Links_to_Data" sheetId="7" r:id="rId10"/>
+    <sheet name="Library_Link" sheetId="13" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">albums_ID!$A$1:$F$1</definedName>
@@ -78,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="628">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="637">
   <si>
     <t>good quality (UNC for UNC collection; UNC and XF for XF collection)</t>
   </si>
@@ -1803,21 +1802,12 @@
     <t>Spain and Canada regular and commemorative coins</t>
   </si>
   <si>
-    <t>Регулярные и юбилейныеонеты Испании и Канады</t>
-  </si>
-  <si>
     <t>A009-03-FB-BN</t>
   </si>
   <si>
     <t>A009-04-FB-DN</t>
   </si>
   <si>
-    <t>Монеты мира (Азия)</t>
-  </si>
-  <si>
-    <t>Монеты мира (Европа, Америка, Африка, Австралия и Океания)</t>
-  </si>
-  <si>
     <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A009-03-FB-BN.html</t>
   </si>
   <si>
@@ -1830,12 +1820,6 @@
     <t>World banknotes</t>
   </si>
   <si>
-    <t>World coins (Asia)</t>
-  </si>
-  <si>
-    <t>World coins (Europe, America, Africa, Australia and Oceania)</t>
-  </si>
-  <si>
     <t>A010-01-OA-DB</t>
   </si>
   <si>
@@ -1860,21 +1844,12 @@
     <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A011-02-OA-GR.html</t>
   </si>
   <si>
-    <t>Билеты (часть 2) в паркии, кино, на особые события, на поезда, на самолёты. Различные жетоны</t>
-  </si>
-  <si>
     <t>Tickets (part 2) for parks, cinemas, special events, trains, and planes. Various tokens</t>
   </si>
   <si>
-    <t>Билеты на метро, проездные трамвайные билеты. Жетоны метро</t>
-  </si>
-  <si>
     <t>A012-01-OA-BU</t>
   </si>
   <si>
-    <t>Tickets for metro, tram passes. Metro tokens</t>
-  </si>
-  <si>
     <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A012-01-OA-BU.html</t>
   </si>
   <si>
@@ -1962,7 +1937,58 @@
     <t>Регулярка,Регулярные,Россия,РФ,Рубль,рубли,Russian Federation</t>
   </si>
   <si>
-    <t>Регулярка,Регулярные,СССР,Россия,Рубль,рубли,USSR,Советский союз, Soviet Union</t>
+    <t>Регулярные и юбилейны монеты Испании и Канады</t>
+  </si>
+  <si>
+    <t>Регулярка,Регулярные,Юбилейные,СССР,Россия,Рубль,рубли,USSR,Советский союз, Soviet Union</t>
+  </si>
+  <si>
+    <t>Регулярка,Регулярные,Юбилейные,Канада,Испания,Canada,Spain</t>
+  </si>
+  <si>
+    <t>Регулярка,Регулярные,Юбилейные,Казахстан,Kazakhstan,Британская Индия,Великобритания,Great Britain,British India,Индия,India,Российская Империя,Россия,Russian Empire</t>
+  </si>
+  <si>
+    <t>Регулярка,Регулярные,Юбилейные,Великобритания,Great Britain,Украина,Ukraine,Германия,Germany,Германская империя,German Empire,Веймарская республика,Weimar Republic,Третий Рейх,Third Reich,Nazi Germany,ГДР,GDR,ФРГ,BRD</t>
+  </si>
+  <si>
+    <t>Монеты мира (часть 2) Азия</t>
+  </si>
+  <si>
+    <t>Монеты мира (часть 1) Европа, Америка, Африка, Австралия и Океания</t>
+  </si>
+  <si>
+    <t>World coins (part 1) Europe, America, Africa, Australia and Oceania</t>
+  </si>
+  <si>
+    <t>World coins (part 2) Asia</t>
+  </si>
+  <si>
+    <t>монеты мира,Регулярка,Регулярные</t>
+  </si>
+  <si>
+    <t>Билеты,театры, музей,музеи,концерты,спектакли</t>
+  </si>
+  <si>
+    <t>Банкноты мира,Боны</t>
+  </si>
+  <si>
+    <t>Билеты (часть 2) в парки, кино, на особые события, на поезда, на самолёты. Различные жетоны</t>
+  </si>
+  <si>
+    <t>Билеты,аквапарки,парки,кино,поезда,самолёты,жетоны</t>
+  </si>
+  <si>
+    <t>Билеты метро, проездные трамвайные билеты. Жетоны метро</t>
+  </si>
+  <si>
+    <t>Metro tickets, tram passes. Metro tokens</t>
+  </si>
+  <si>
+    <t>Билеты метро, проездные трамвайные билеты,жетоны метро</t>
+  </si>
+  <si>
+    <t>Пластиковые карты,Plastic cards</t>
   </si>
 </sst>
 </file>
@@ -2853,6 +2879,54 @@
   </cellStyles>
   <dxfs count="34">
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3336,54 +3410,6 @@
         </horizontal>
       </border>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -3452,44 +3478,44 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{973D7237-72C7-453E-A0E1-526C93326B28}" name="Таблица3" displayName="Таблица3" ref="A1:F51" totalsRowShown="0" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{973D7237-72C7-453E-A0E1-526C93326B28}" name="Таблица3" displayName="Таблица3" ref="A1:F51" totalsRowShown="0" headerRowDxfId="33" dataDxfId="31" headerRowBorderDxfId="32" tableBorderDxfId="30" totalsRowBorderDxfId="29">
   <autoFilter ref="A1:F51" xr:uid="{A2D8FA3D-4024-4365-BE1D-F93D0AF2D426}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{12C2DF0B-47FA-46A4-8424-55A1488EF88B}" name="ID" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{EB0B36CE-168D-429E-896D-DBA54794224F}" name="Name_Eng" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{6C3A2CE8-252E-4C52-985B-8CDDFD9FA0C7}" name="OfficialMintName_Native" dataDxfId="20"/>
-    <tableColumn id="8" xr3:uid="{DA5871DC-2EDB-49C0-953E-EC0F70288E21}" name="Country" dataDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{FCD85F85-A94E-4BBE-9D3B-2B7494638375}" name="Mint_City" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{E5141978-CA91-4DE9-86F1-8A8AFA716534}" name="Alias" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{12C2DF0B-47FA-46A4-8424-55A1488EF88B}" name="ID" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{EB0B36CE-168D-429E-896D-DBA54794224F}" name="Name_Eng" dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{6C3A2CE8-252E-4C52-985B-8CDDFD9FA0C7}" name="OfficialMintName_Native" dataDxfId="26"/>
+    <tableColumn id="8" xr3:uid="{DA5871DC-2EDB-49C0-953E-EC0F70288E21}" name="Country" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{FCD85F85-A94E-4BBE-9D3B-2B7494638375}" name="Mint_City" dataDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{E5141978-CA91-4DE9-86F1-8A8AFA716534}" name="Alias" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D0DCC88A-2D36-4004-A694-FC0C0F0C3396}" name="Таблица2" displayName="Таблица2" ref="A1:C16" totalsRowShown="0" headerRowBorderDxfId="16" tableBorderDxfId="15" totalsRowBorderDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D0DCC88A-2D36-4004-A694-FC0C0F0C3396}" name="Таблица2" displayName="Таблица2" ref="A1:C16" totalsRowShown="0" headerRowBorderDxfId="22" tableBorderDxfId="21" totalsRowBorderDxfId="20">
   <autoFilter ref="A1:C16" xr:uid="{00000000-0009-0000-0100-000002000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{28358E6A-6F3A-468C-9E1C-880A34D9BECE}" name="№" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{28358E6A-6F3A-468C-9E1C-880A34D9BECE}" name="№" dataDxfId="19"/>
     <tableColumn id="2" xr3:uid="{DD0AD5C8-324B-4DA7-B39F-B2DB3EF91222}" name="Links:"/>
-    <tableColumn id="3" xr3:uid="{FC8A6018-CA7E-4C73-9B21-B272B55FA8C1}" name="Description:" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{FC8A6018-CA7E-4C73-9B21-B272B55FA8C1}" name="Description:" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9D0F8E3D-96B1-4DB8-B1A6-8DD6B84F3693}" name="Таблица35" displayName="Таблица35" ref="A1:D52" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10" tableBorderDxfId="8" totalsRowBorderDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9D0F8E3D-96B1-4DB8-B1A6-8DD6B84F3693}" name="Таблица35" displayName="Таблица35" ref="A1:D52" totalsRowShown="0" headerRowDxfId="17" dataDxfId="15" headerRowBorderDxfId="16" tableBorderDxfId="14" totalsRowBorderDxfId="13">
   <autoFilter ref="A1:D52" xr:uid="{A2D8FA3D-4024-4365-BE1D-F93D0AF2D426}"/>
   <tableColumns count="4">
-    <tableColumn id="4" xr3:uid="{74AFB32D-7AAA-46BE-8174-ED698BB4613E}" name="Mint_id" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{523D65CD-0F56-441F-90B5-E46A9B14F0D0}" name="Ekaterinburg Mint" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{1AAB7352-E935-4EC6-A0D1-3EDC5D0BC93C}" name="Year_of_start" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{5FF15381-476A-4F88-B93A-6452F2830A0A}" name="Year_of_end" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{74AFB32D-7AAA-46BE-8174-ED698BB4613E}" name="Mint_id" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{523D65CD-0F56-441F-90B5-E46A9B14F0D0}" name="Ekaterinburg Mint" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{1AAB7352-E935-4EC6-A0D1-3EDC5D0BC93C}" name="Year_of_start" dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{5FF15381-476A-4F88-B93A-6452F2830A0A}" name="Year_of_end" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3503,9 +3529,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{8354E581-3B48-4762-81A7-EA76E36C4BB5}" name="№" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{1F45DC85-8ECA-45FE-BF45-E528619CEE0E}" name="Links:" dataDxfId="1" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{3FAE616B-3296-4770-9E56-8A824991EECA}" name="Description:" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{8354E581-3B48-4762-81A7-EA76E36C4BB5}" name="№" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{1F45DC85-8ECA-45FE-BF45-E528619CEE0E}" name="Links:" dataDxfId="7" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{3FAE616B-3296-4770-9E56-8A824991EECA}" name="Description:" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -3896,12 +3922,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C7:C8">
-    <cfRule type="containsText" dxfId="33" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C7))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6">
-    <cfRule type="containsText" dxfId="32" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="4" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C6))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3918,7 +3944,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2">
-    <cfRule type="containsText" dxfId="31" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="3" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C2))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3935,7 +3961,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4">
-    <cfRule type="containsText" dxfId="30" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="2" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C4))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3952,7 +3978,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C5">
-    <cfRule type="containsText" dxfId="29" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="1" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C5))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3969,7 +3995,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3">
-    <cfRule type="containsText" dxfId="28" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C3))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -4001,196 +4027,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8265AFD9-D9EB-4B75-B60D-6B7F7204230D}">
-  <dimension ref="A1:B29"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="26.36328125" customWidth="1"/>
-    <col min="2" max="2" width="31.36328125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" s="4"/>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" s="4"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="4"/>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" s="4"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="4"/>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="4"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="4"/>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" s="4"/>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="4"/>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" s="4"/>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B12" s="4"/>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B13" s="4"/>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" s="4"/>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B15" s="4"/>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B16" s="4"/>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B17" s="4"/>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B18" s="4"/>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B19" s="4"/>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B20" s="4"/>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B21" s="4"/>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B22" s="4"/>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B23" s="4"/>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A24" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B24" s="4"/>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B25" s="4"/>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A26" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B26" s="4"/>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A27" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B27" s="4"/>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A28" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B28" s="4"/>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A29" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="B29" s="4"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{729F7C06-1AE8-4162-8F40-6E9A64E311D7}">
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -4404,7 +4240,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D5AF97D-14BA-4E23-B5FF-856D52BDA29A}">
   <dimension ref="B7:Z7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -4414,7 +4250,7 @@
   <sheetData>
     <row r="7" spans="2:26" ht="61.5" x14ac:dyDescent="1.35">
       <c r="B7" s="105" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="C7" s="106"/>
       <c r="D7" s="106"/>
@@ -4814,7 +4650,7 @@
         <v>397</v>
       </c>
       <c r="F1" s="78" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -4834,7 +4670,7 @@
         <v>527</v>
       </c>
       <c r="F2" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -4854,7 +4690,7 @@
         <v>532</v>
       </c>
       <c r="F3" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -4874,7 +4710,7 @@
         <v>533</v>
       </c>
       <c r="F4" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -4894,7 +4730,7 @@
         <v>534</v>
       </c>
       <c r="F5" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -4914,7 +4750,7 @@
         <v>535</v>
       </c>
       <c r="F6" t="s">
-        <v>621</v>
+        <v>613</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -4931,10 +4767,10 @@
         <v>499</v>
       </c>
       <c r="E7" s="83" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="F7" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -4951,10 +4787,10 @@
         <v>498</v>
       </c>
       <c r="E8" s="83" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="F8" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -4974,7 +4810,7 @@
         <v>539</v>
       </c>
       <c r="F9" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -4994,7 +4830,7 @@
         <v>540</v>
       </c>
       <c r="F10" t="s">
-        <v>614</v>
+        <v>606</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -5014,7 +4850,7 @@
         <v>543</v>
       </c>
       <c r="F11" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
@@ -5034,7 +4870,7 @@
         <v>544</v>
       </c>
       <c r="F12" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
@@ -5054,7 +4890,7 @@
         <v>547</v>
       </c>
       <c r="F13" t="s">
-        <v>622</v>
+        <v>614</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
@@ -5074,7 +4910,7 @@
         <v>548</v>
       </c>
       <c r="F14" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
@@ -5094,7 +4930,7 @@
         <v>551</v>
       </c>
       <c r="F15" t="s">
-        <v>624</v>
+        <v>616</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
@@ -5114,7 +4950,7 @@
         <v>552</v>
       </c>
       <c r="F16" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
@@ -5134,7 +4970,7 @@
         <v>558</v>
       </c>
       <c r="F17" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
@@ -5154,7 +4990,7 @@
         <v>562</v>
       </c>
       <c r="F18" t="s">
-        <v>627</v>
+        <v>620</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
@@ -5168,10 +5004,13 @@
         <v>573</v>
       </c>
       <c r="D19" t="s">
-        <v>574</v>
+        <v>619</v>
       </c>
       <c r="E19" s="83" t="s">
         <v>564</v>
+      </c>
+      <c r="F19" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
@@ -5179,7 +5018,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="C20" t="s">
         <v>569</v>
@@ -5188,7 +5027,10 @@
         <v>570</v>
       </c>
       <c r="E20" s="83" t="s">
-        <v>605</v>
+        <v>597</v>
+      </c>
+      <c r="F20" t="s">
+        <v>622</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
@@ -5196,7 +5038,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="C21" t="s">
         <v>571</v>
@@ -5205,7 +5047,10 @@
         <v>572</v>
       </c>
       <c r="E21" s="83" t="s">
-        <v>606</v>
+        <v>598</v>
+      </c>
+      <c r="F21" t="s">
+        <v>623</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
@@ -5213,16 +5058,19 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C22" t="s">
-        <v>584</v>
+        <v>626</v>
       </c>
       <c r="D22" t="s">
-        <v>578</v>
+        <v>625</v>
       </c>
       <c r="E22" s="83" t="s">
-        <v>579</v>
+        <v>576</v>
+      </c>
+      <c r="F22" t="s">
+        <v>628</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
@@ -5230,16 +5078,19 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C23" t="s">
-        <v>583</v>
+        <v>627</v>
       </c>
       <c r="D23" t="s">
+        <v>624</v>
+      </c>
+      <c r="E23" s="83" t="s">
         <v>577</v>
       </c>
-      <c r="E23" s="83" t="s">
-        <v>580</v>
+      <c r="F23" t="s">
+        <v>628</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
@@ -5247,16 +5098,19 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="C24" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="D24" t="s">
+        <v>578</v>
+      </c>
+      <c r="E24" s="83" t="s">
         <v>581</v>
       </c>
-      <c r="E24" s="83" t="s">
-        <v>586</v>
+      <c r="F24" t="s">
+        <v>630</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
@@ -5264,16 +5118,19 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="C25" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="D25" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="E25" s="83" t="s">
-        <v>589</v>
+        <v>584</v>
+      </c>
+      <c r="F25" t="s">
+        <v>629</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
@@ -5281,16 +5138,19 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="C26" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="D26" t="s">
-        <v>593</v>
+        <v>631</v>
       </c>
       <c r="E26" s="83" t="s">
-        <v>592</v>
+        <v>587</v>
+      </c>
+      <c r="F26" t="s">
+        <v>632</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
@@ -5298,16 +5158,19 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>596</v>
+        <v>589</v>
       </c>
       <c r="C27" t="s">
-        <v>597</v>
+        <v>634</v>
       </c>
       <c r="D27" t="s">
-        <v>595</v>
+        <v>633</v>
       </c>
       <c r="E27" s="83" t="s">
-        <v>598</v>
+        <v>590</v>
+      </c>
+      <c r="F27" t="s">
+        <v>635</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
@@ -5315,16 +5178,19 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="C28" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="D28" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="E28" s="83" t="s">
-        <v>600</v>
+        <v>592</v>
+      </c>
+      <c r="F28" t="s">
+        <v>636</v>
       </c>
     </row>
   </sheetData>
@@ -5456,10 +5322,10 @@
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5" s="85" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="B5" t="s">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="C5" s="73" t="s">
         <v>142</v>
@@ -5585,10 +5451,10 @@
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.35">
       <c r="C14" s="85" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="D14" t="s">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="X14" s="79" t="s">
         <v>416</v>
@@ -5894,15 +5760,6 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7B3F3C9-87AF-45FC-9E9F-2A256D1F4917}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4C14141-45DA-4C30-845C-3E630B347F10}">
   <dimension ref="A1:F51"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -6942,7 +6799,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8049D8E-7482-48AF-95C9-7F1B728B0DDE}">
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -7140,7 +6997,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF1BA8E2-9FD2-4C47-B5D3-EF9907B8F692}">
   <dimension ref="A1:D52"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -7816,7 +7673,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0041FEF0-BF6F-4667-AFBD-1C23A1866795}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -7928,4 +7785,194 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8265AFD9-D9EB-4B75-B60D-6B7F7204230D}">
+  <dimension ref="A1:B29"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="26.36328125" customWidth="1"/>
+    <col min="2" max="2" width="31.36328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="4"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="4"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="4"/>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="4"/>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="4"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="4"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="4"/>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="4"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="4"/>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="4"/>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="4"/>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="4"/>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="4"/>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="4"/>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" s="4"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" s="4"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="4"/>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="4"/>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" s="4"/>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" s="4"/>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="4"/>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="4"/>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24" s="4"/>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" s="4"/>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" s="4"/>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" s="4"/>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B28" s="4"/>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="B29" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Info/Additional_information.xlsx
+++ b/Info/Additional_information.xlsx
@@ -8,22 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{472FF70B-05F9-4DEB-B758-8EB77759CCAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E71DF8E1-957B-4FAE-9D42-4C8BD8B31A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Colours_specifications" sheetId="1" r:id="rId1"/>
     <sheet name="EURO albums content" sheetId="4" r:id="rId2"/>
     <sheet name="albums_ID" sheetId="11" r:id="rId3"/>
-    <sheet name="albums ID naming" sheetId="9" r:id="rId4"/>
-    <sheet name="Mint_Alias" sheetId="5" r:id="rId5"/>
-    <sheet name="Coin_Shops" sheetId="8" r:id="rId6"/>
-    <sheet name="Mint_work_years" sheetId="6" r:id="rId7"/>
-    <sheet name="File_Naming" sheetId="2" r:id="rId8"/>
-    <sheet name="Existing_subtypes" sheetId="3" r:id="rId9"/>
-    <sheet name="Links_to_Data" sheetId="7" r:id="rId10"/>
-    <sheet name="Library_Link" sheetId="13" r:id="rId11"/>
+    <sheet name="albums_buttons" sheetId="14" r:id="rId4"/>
+    <sheet name="albums ID naming" sheetId="9" r:id="rId5"/>
+    <sheet name="Mint_Alias" sheetId="5" r:id="rId6"/>
+    <sheet name="Coin_Shops" sheetId="8" r:id="rId7"/>
+    <sheet name="Mint_work_years" sheetId="6" r:id="rId8"/>
+    <sheet name="File_Naming" sheetId="2" r:id="rId9"/>
+    <sheet name="Existing_subtypes" sheetId="3" r:id="rId10"/>
+    <sheet name="Links_to_Data" sheetId="7" r:id="rId11"/>
+    <sheet name="Library_Link" sheetId="13" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">albums_ID!$A$1:$F$1</definedName>
@@ -77,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="676">
   <si>
     <t>good quality (UNC for UNC collection; UNC and XF for XF collection)</t>
   </si>
@@ -1989,13 +1990,130 @@
   </si>
   <si>
     <t>Пластиковые карты,Plastic cards</t>
+  </si>
+  <si>
+    <t>Album_ID</t>
+  </si>
+  <si>
+    <t>Icon </t>
+  </si>
+  <si>
+    <t>Name </t>
+  </si>
+  <si>
+    <t>Excel_Link</t>
+  </si>
+  <si>
+    <t>Folder_Link</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Austria/%23EURO%23Austria%23Commemorative%23%5B2005-present%5D%23UNC.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Austria/</t>
+  </si>
+  <si>
+    <t>Австрия / Austria</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Belgium/%23EURO%23Belgium%23Commemorative%23%5B2005-present%5D%23UNC.xlsx</t>
+  </si>
+  <si>
+    <t>Бельгия / Belgium</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Belgium/</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Cyprus/%23EURO%23Cyprus%23Commemorative%23%5B2009-present%5D%23UNC.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Cyprus/</t>
+  </si>
+  <si>
+    <t>Кипр / Cyprus</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Estonia/%23EURO%23Estonia%23Commemorative%23%5B2012-present%5D%23UNC.xlsx</t>
+  </si>
+  <si>
+    <t>Эстония / Estonia</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Estonia/</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/France/%23EURO%23France%23Commemorative%23%5B2007-present%5D%23UNC.xlsx</t>
+  </si>
+  <si>
+    <t>Франция / France</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/France/</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Italy/%23EURO%23Italy%23Commemorative%23%5B2004-present%5D%23UNC.xlsx</t>
+  </si>
+  <si>
+    <t>Италия / Italy</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Italy/</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Latvia/%23EURO%23Latvia%23Commemorative%23%5B2014-present%5D%23UNC.xlsx</t>
+  </si>
+  <si>
+    <t>Латвия / Latvia</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Latvia/</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Ireland/%23EURO%23Ireland%23Commemorative%23%5B2007-present%5D%23UNC.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Ireland/</t>
+  </si>
+  <si>
+    <t>Ирландия / Ireland</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Lithuania/%23EURO%23Lithuania%23Commemorative%23%5B2015-present%5D%23UNC.xlsx</t>
+  </si>
+  <si>
+    <t>Литва / Lithuania</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Lithuania/</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Netherlands/%23EURO%23Netherlands%23Commemorative%23%5B2007-present%5D%23UNC.xlsx</t>
+  </si>
+  <si>
+    <t>Нидерланды / Netherlands</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Netherlands/</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Portugal/%23EURO%23Portugal%23Commemorative%23%5B2007-present%5D%23UNC.xlsx</t>
+  </si>
+  <si>
+    <t>Португалия / Portugal</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Portugal/</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/2/20/Flag_of_the_Netherlands.svg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2151,6 +2269,11 @@
       <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF0A0A0A"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="22">
@@ -2590,7 +2713,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2872,6 +2995,10 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -3801,14 +3928,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="3.08984375" customWidth="1"/>
     <col min="3" max="3" width="5" customWidth="1"/>
     <col min="4" max="4" width="81" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" ht="18.5">
       <c r="A1" s="64" t="s">
         <v>7</v>
       </c>
@@ -3822,7 +3949,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -3836,7 +3963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -3850,7 +3977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -3864,7 +3991,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -3878,7 +4005,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -3892,7 +4019,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -3906,7 +4033,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -4027,9 +4154,199 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8265AFD9-D9EB-4B75-B60D-6B7F7204230D}">
+  <dimension ref="A1:B29"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="26.36328125" customWidth="1"/>
+    <col min="2" max="2" width="31.36328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="18.5">
+      <c r="A1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="4"/>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="4"/>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="4"/>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="4"/>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="4"/>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="4"/>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="4"/>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="4"/>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="4"/>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="4"/>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="4"/>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="4"/>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="4"/>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="4"/>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" s="4"/>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" s="4"/>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="4"/>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="4"/>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" s="4"/>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" s="4"/>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="4"/>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="4"/>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24" s="4"/>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B25" s="4"/>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" s="4"/>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" s="4"/>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B28" s="4"/>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="B29" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{729F7C06-1AE8-4162-8F40-6E9A64E311D7}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="4.81640625" customWidth="1"/>
     <col min="2" max="2" width="57.1796875" customWidth="1"/>
@@ -4037,7 +4354,7 @@
     <col min="4" max="4" width="15.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>303</v>
       </c>
@@ -4048,7 +4365,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3">
       <c r="A2" s="41">
         <v>1</v>
       </c>
@@ -4059,7 +4376,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3">
       <c r="A3" s="41">
         <v>2</v>
       </c>
@@ -4070,7 +4387,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3">
       <c r="A4" s="41">
         <v>3</v>
       </c>
@@ -4081,7 +4398,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3">
       <c r="A5" s="41">
         <v>4</v>
       </c>
@@ -4092,7 +4409,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3">
       <c r="A6" s="41">
         <v>5</v>
       </c>
@@ -4103,7 +4420,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3">
       <c r="A7" s="41">
         <v>6</v>
       </c>
@@ -4114,7 +4431,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" ht="29">
       <c r="A8" s="41">
         <v>7</v>
       </c>
@@ -4125,7 +4442,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3">
       <c r="A9" s="41">
         <v>8</v>
       </c>
@@ -4136,7 +4453,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" ht="29">
       <c r="A10" s="41">
         <v>9</v>
       </c>
@@ -4147,7 +4464,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3">
       <c r="A11" s="41">
         <v>10</v>
       </c>
@@ -4158,7 +4475,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3">
       <c r="A12" s="41">
         <v>11</v>
       </c>
@@ -4169,7 +4486,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3">
       <c r="A13" s="41">
         <v>12</v>
       </c>
@@ -4180,7 +4497,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3">
       <c r="A14" s="41">
         <v>13</v>
       </c>
@@ -4191,7 +4508,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3">
       <c r="A15" s="50">
         <v>14</v>
       </c>
@@ -4202,7 +4519,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3">
       <c r="A16" s="50">
         <v>15</v>
       </c>
@@ -4240,15 +4557,15 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D5AF97D-14BA-4E23-B5FF-856D52BDA29A}">
   <dimension ref="B7:Z7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="9.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="7" spans="2:26" ht="61.5" x14ac:dyDescent="1.35">
+    <row r="7" spans="2:26" ht="61.5">
       <c r="B7" s="105" t="s">
         <v>601</v>
       </c>
@@ -4291,7 +4608,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57D9DE6C-583F-4F0B-9E0F-CDE5965E194A}">
   <dimension ref="A1:I30"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="9.90625" customWidth="1"/>
     <col min="2" max="2" width="18.7265625" customWidth="1"/>
@@ -4301,7 +4618,7 @@
     <col min="9" max="9" width="26.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" ht="18.5">
       <c r="A1" s="66" t="s">
         <v>62</v>
       </c>
@@ -4321,7 +4638,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9">
       <c r="A2" s="92">
         <v>1</v>
       </c>
@@ -4341,7 +4658,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9">
       <c r="A3" s="93"/>
       <c r="B3" s="100"/>
       <c r="C3" s="4" t="s">
@@ -4357,7 +4674,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9">
       <c r="A4" s="94"/>
       <c r="B4" s="101">
         <v>2</v>
@@ -4375,14 +4692,14 @@
         <v>81</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9">
       <c r="A5" s="94"/>
       <c r="B5" s="101"/>
       <c r="C5" s="4" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9">
       <c r="A6" s="94"/>
       <c r="B6" s="15">
         <v>3</v>
@@ -4391,7 +4708,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9">
       <c r="A7" s="94"/>
       <c r="B7" s="16" t="s">
         <v>90</v>
@@ -4400,7 +4717,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9">
       <c r="A8" s="94"/>
       <c r="B8" s="102">
         <v>6</v>
@@ -4409,14 +4726,14 @@
         <v>70</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9">
       <c r="A9" s="94"/>
       <c r="B9" s="103"/>
       <c r="C9" s="4" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9">
       <c r="A10" s="94"/>
       <c r="B10" s="17">
         <v>7</v>
@@ -4425,14 +4742,14 @@
         <v>72</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9">
       <c r="A11" s="94"/>
       <c r="B11" s="24"/>
       <c r="C11" s="4" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9">
       <c r="A12" s="94"/>
       <c r="B12" s="18">
         <v>8</v>
@@ -4441,7 +4758,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9">
       <c r="A13" s="95"/>
       <c r="B13" s="25" t="s">
         <v>78</v>
@@ -4450,7 +4767,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:9" ht="15" thickBot="1">
       <c r="A14" s="96"/>
       <c r="B14" s="26" t="s">
         <v>91</v>
@@ -4459,7 +4776,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="14.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" ht="14.5" customHeight="1" thickTop="1">
       <c r="A15" s="97">
         <v>2</v>
       </c>
@@ -4470,7 +4787,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" ht="14.5" customHeight="1">
       <c r="A16" s="98"/>
       <c r="B16" s="20" t="s">
         <v>365</v>
@@ -4479,7 +4796,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" ht="14.5" customHeight="1">
       <c r="A17" s="98"/>
       <c r="B17" s="21" t="s">
         <v>366</v>
@@ -4488,7 +4805,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" ht="14.5" customHeight="1" thickBot="1">
       <c r="A18" s="99"/>
       <c r="B18" s="22" t="s">
         <v>92</v>
@@ -4497,7 +4814,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="14.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" ht="14.5" customHeight="1" thickTop="1">
       <c r="A19" s="86">
         <v>3</v>
       </c>
@@ -4508,7 +4825,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" ht="14.5" customHeight="1">
       <c r="A20" s="87"/>
       <c r="B20" s="27" t="s">
         <v>93</v>
@@ -4517,7 +4834,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" ht="14.5" customHeight="1" thickBot="1">
       <c r="A21" s="88"/>
       <c r="B21" s="28" t="s">
         <v>95</v>
@@ -4526,7 +4843,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="14.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" ht="14.5" customHeight="1" thickTop="1">
       <c r="A22" s="89">
         <v>4</v>
       </c>
@@ -4537,7 +4854,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" ht="14.5" customHeight="1">
       <c r="A23" s="90"/>
       <c r="B23" s="20" t="s">
         <v>98</v>
@@ -4546,7 +4863,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" ht="14.5" customHeight="1">
       <c r="A24" s="90"/>
       <c r="B24" s="21" t="s">
         <v>100</v>
@@ -4555,7 +4872,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" ht="14.5" customHeight="1">
       <c r="A25" s="90"/>
       <c r="B25" s="16" t="s">
         <v>102</v>
@@ -4564,7 +4881,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3">
       <c r="A26" s="90"/>
       <c r="B26" s="29" t="s">
         <v>104</v>
@@ -4573,7 +4890,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3">
       <c r="A27" s="90"/>
       <c r="B27" s="30" t="s">
         <v>106</v>
@@ -4582,7 +4899,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3">
       <c r="A28" s="90"/>
       <c r="B28" s="18">
         <v>8</v>
@@ -4591,7 +4908,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:3" ht="15" thickBot="1">
       <c r="A29" s="91"/>
       <c r="B29" s="31" t="s">
         <v>78</v>
@@ -4600,7 +4917,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
+    <row r="30" spans="1:3" ht="15" thickTop="1"/>
   </sheetData>
   <autoFilter ref="A1:C15" xr:uid="{57D9DE6C-583F-4F0B-9E0F-CDE5965E194A}"/>
   <mergeCells count="7">
@@ -4623,7 +4940,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DC835FD-69FE-4DBC-957F-9A46CA05517E}">
   <dimension ref="A1:F28"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="3.453125" customWidth="1"/>
     <col min="2" max="2" width="15.54296875" customWidth="1"/>
@@ -4633,7 +4950,7 @@
     <col min="6" max="6" width="182.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" ht="18.5">
       <c r="A1" s="78" t="s">
         <v>536</v>
       </c>
@@ -4653,7 +4970,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" ht="14.5" customHeight="1">
       <c r="A2">
         <v>0</v>
       </c>
@@ -4673,7 +4990,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>1</v>
       </c>
@@ -4693,7 +5010,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>2</v>
       </c>
@@ -4713,7 +5030,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>3</v>
       </c>
@@ -4733,7 +5050,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>4</v>
       </c>
@@ -4753,7 +5070,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>5</v>
       </c>
@@ -4773,7 +5090,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>6</v>
       </c>
@@ -4793,7 +5110,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>7</v>
       </c>
@@ -4813,7 +5130,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>8</v>
       </c>
@@ -4833,7 +5150,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>9</v>
       </c>
@@ -4853,7 +5170,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>10</v>
       </c>
@@ -4873,7 +5190,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>11</v>
       </c>
@@ -4893,7 +5210,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>12</v>
       </c>
@@ -4913,7 +5230,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>13</v>
       </c>
@@ -4933,7 +5250,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>14</v>
       </c>
@@ -4953,7 +5270,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6">
       <c r="A17">
         <v>15</v>
       </c>
@@ -4973,7 +5290,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6">
       <c r="A18">
         <v>16</v>
       </c>
@@ -4993,7 +5310,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6">
       <c r="A19">
         <v>17</v>
       </c>
@@ -5013,7 +5330,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6">
       <c r="A20">
         <v>18</v>
       </c>
@@ -5033,7 +5350,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6">
       <c r="A21">
         <v>19</v>
       </c>
@@ -5053,7 +5370,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6">
       <c r="A22">
         <v>20</v>
       </c>
@@ -5073,7 +5390,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6">
       <c r="A23">
         <v>21</v>
       </c>
@@ -5093,7 +5410,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6">
       <c r="A24">
         <v>22</v>
       </c>
@@ -5113,7 +5430,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6">
       <c r="A25">
         <v>23</v>
       </c>
@@ -5133,7 +5450,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6">
       <c r="A26">
         <v>24</v>
       </c>
@@ -5153,7 +5470,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6">
       <c r="A27">
         <v>25</v>
       </c>
@@ -5173,7 +5490,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6">
       <c r="A28">
         <v>26</v>
       </c>
@@ -5231,9 +5548,269 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C94A307-2E39-40B9-B204-C92675C0AF71}">
+  <dimension ref="A1:E43"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="15.36328125" customWidth="1"/>
+    <col min="2" max="2" width="54.7265625" customWidth="1"/>
+    <col min="3" max="3" width="27.36328125" customWidth="1"/>
+    <col min="4" max="4" width="151" customWidth="1"/>
+    <col min="5" max="5" width="79.54296875" customWidth="1"/>
+    <col min="6" max="6" width="62" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>637</v>
+      </c>
+      <c r="B1" t="s">
+        <v>638</v>
+      </c>
+      <c r="C1" t="s">
+        <v>639</v>
+      </c>
+      <c r="D1" t="s">
+        <v>640</v>
+      </c>
+      <c r="E1" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>525</v>
+      </c>
+      <c r="B2" t="s">
+        <v>413</v>
+      </c>
+      <c r="C2" t="s">
+        <v>644</v>
+      </c>
+      <c r="D2" s="108" t="s">
+        <v>642</v>
+      </c>
+      <c r="E2" s="108" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>525</v>
+      </c>
+      <c r="B3" t="s">
+        <v>414</v>
+      </c>
+      <c r="C3" t="s">
+        <v>646</v>
+      </c>
+      <c r="D3" s="108" t="s">
+        <v>645</v>
+      </c>
+      <c r="E3" s="108" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>525</v>
+      </c>
+      <c r="B4" t="s">
+        <v>420</v>
+      </c>
+      <c r="C4" t="s">
+        <v>650</v>
+      </c>
+      <c r="D4" s="108" t="s">
+        <v>648</v>
+      </c>
+      <c r="E4" s="108" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>525</v>
+      </c>
+      <c r="B5" t="s">
+        <v>432</v>
+      </c>
+      <c r="C5" t="s">
+        <v>652</v>
+      </c>
+      <c r="D5" s="108" t="s">
+        <v>651</v>
+      </c>
+      <c r="E5" s="108" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>525</v>
+      </c>
+      <c r="B6" t="s">
+        <v>430</v>
+      </c>
+      <c r="C6" t="s">
+        <v>655</v>
+      </c>
+      <c r="D6" s="108" t="s">
+        <v>654</v>
+      </c>
+      <c r="E6" s="108" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>525</v>
+      </c>
+      <c r="B7" t="s">
+        <v>419</v>
+      </c>
+      <c r="C7" t="s">
+        <v>658</v>
+      </c>
+      <c r="D7" s="108" t="s">
+        <v>657</v>
+      </c>
+      <c r="E7" s="108" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>525</v>
+      </c>
+      <c r="B8" t="s">
+        <v>421</v>
+      </c>
+      <c r="C8" t="s">
+        <v>661</v>
+      </c>
+      <c r="D8" s="108" t="s">
+        <v>660</v>
+      </c>
+      <c r="E8" s="108" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>525</v>
+      </c>
+      <c r="B9" t="s">
+        <v>417</v>
+      </c>
+      <c r="C9" t="s">
+        <v>665</v>
+      </c>
+      <c r="D9" s="108" t="s">
+        <v>663</v>
+      </c>
+      <c r="E9" s="108" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>525</v>
+      </c>
+      <c r="B10" t="s">
+        <v>422</v>
+      </c>
+      <c r="C10" t="s">
+        <v>667</v>
+      </c>
+      <c r="D10" s="108" t="s">
+        <v>666</v>
+      </c>
+      <c r="E10" s="108" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>525</v>
+      </c>
+      <c r="B11" s="108" t="s">
+        <v>675</v>
+      </c>
+      <c r="C11" t="s">
+        <v>670</v>
+      </c>
+      <c r="D11" s="108" t="s">
+        <v>669</v>
+      </c>
+      <c r="E11" s="108" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>525</v>
+      </c>
+      <c r="C12" t="s">
+        <v>673</v>
+      </c>
+      <c r="D12" s="108" t="s">
+        <v>672</v>
+      </c>
+      <c r="E12" s="108" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="39" spans="3:3">
+      <c r="C39" s="107"/>
+    </row>
+    <row r="40" spans="3:3">
+      <c r="C40" s="107"/>
+    </row>
+    <row r="41" spans="3:3">
+      <c r="C41" s="107"/>
+    </row>
+    <row r="42" spans="3:3">
+      <c r="C42" s="107"/>
+    </row>
+    <row r="43" spans="3:3">
+      <c r="C43" s="107"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{F43C89B6-D718-4498-AEF4-6F42227C5856}"/>
+    <hyperlink ref="E2" r:id="rId2" xr:uid="{76242B5D-84A5-47A1-B07F-4BA0D50A8014}"/>
+    <hyperlink ref="D3" r:id="rId3" xr:uid="{58B70BA2-33AC-4FA7-9AFF-DFD0B73ADEF0}"/>
+    <hyperlink ref="E3" r:id="rId4" xr:uid="{49C7B78D-C192-410D-8898-89F7BA109F8D}"/>
+    <hyperlink ref="D4" r:id="rId5" xr:uid="{321D7864-3399-4EAA-B153-B3813E5AA455}"/>
+    <hyperlink ref="E4" r:id="rId6" xr:uid="{D93B84B2-EEC6-458D-9CE2-C592A19A1A49}"/>
+    <hyperlink ref="D5" r:id="rId7" xr:uid="{51E99284-24FE-4D67-B556-AA834A9D4DCF}"/>
+    <hyperlink ref="E5" r:id="rId8" xr:uid="{66FF5A68-761C-4AF5-8980-4DECCA869DDC}"/>
+    <hyperlink ref="D6" r:id="rId9" xr:uid="{C74848F1-E164-4114-9460-C82CF448F63E}"/>
+    <hyperlink ref="E6" r:id="rId10" xr:uid="{B713E859-CCEE-4F0A-BCDC-262577CD73B5}"/>
+    <hyperlink ref="D7" r:id="rId11" xr:uid="{30733141-7CE7-4A95-B89E-F180DAB80B9A}"/>
+    <hyperlink ref="E7" r:id="rId12" xr:uid="{B81EC275-111B-4225-A923-336C142B9117}"/>
+    <hyperlink ref="D8" r:id="rId13" xr:uid="{08083F06-4B9D-4FED-B15C-C45FB551303A}"/>
+    <hyperlink ref="E8" r:id="rId14" xr:uid="{866928B3-9E7C-4F3E-81C5-092A1E1B038C}"/>
+    <hyperlink ref="D9" r:id="rId15" xr:uid="{FB102BAF-1980-4145-AD3E-283F0D9DAF4D}"/>
+    <hyperlink ref="E9" r:id="rId16" xr:uid="{164C3D23-0287-4BB9-B30F-5F2742E658C4}"/>
+    <hyperlink ref="D10" r:id="rId17" xr:uid="{71F06BE1-DC2D-4771-BD1B-C298E74743A7}"/>
+    <hyperlink ref="E10" r:id="rId18" xr:uid="{3BDBC051-CDF7-4AFA-9E0B-8CCC76D76447}"/>
+    <hyperlink ref="D11" r:id="rId19" xr:uid="{DB5268F6-A4BF-44FF-B0B7-F027CC14C4A7}"/>
+    <hyperlink ref="E11" r:id="rId20" xr:uid="{66913E9C-2B0E-4C62-B98A-E8AF58BA6DC1}"/>
+    <hyperlink ref="D12" r:id="rId21" xr:uid="{C3BCEC62-1D50-4E96-8B88-F958C554A1CA}"/>
+    <hyperlink ref="E12" r:id="rId22" xr:uid="{0767262B-1C7A-4CB5-9F51-0BE6DEA46404}"/>
+    <hyperlink ref="B11" r:id="rId23" xr:uid="{D9DCBBB1-C4D4-4F20-9427-B0D2AF112CD3}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId24"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{866E9A5E-386D-439E-AA25-CB46A31C625C}">
   <dimension ref="A1:Z50"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="15.453125" style="77" customWidth="1"/>
     <col min="2" max="2" width="24.7265625" customWidth="1"/>
@@ -5244,7 +5821,7 @@
     <col min="25" max="25" width="26.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="36.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:25" ht="36.5" customHeight="1">
       <c r="A1" s="76" t="s">
         <v>392</v>
       </c>
@@ -5263,7 +5840,7 @@
       <c r="X1" s="104"/>
       <c r="Y1" s="104"/>
     </row>
-    <row r="2" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:25" ht="15.5">
       <c r="A2" s="77" t="s">
         <v>404</v>
       </c>
@@ -5280,7 +5857,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:25">
       <c r="A3" s="77" t="s">
         <v>383</v>
       </c>
@@ -5300,7 +5877,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:25">
       <c r="A4" s="77" t="s">
         <v>398</v>
       </c>
@@ -5320,7 +5897,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:25">
       <c r="A5" s="85" t="s">
         <v>603</v>
       </c>
@@ -5340,7 +5917,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:25">
       <c r="C6" s="73" t="s">
         <v>379</v>
       </c>
@@ -5354,7 +5931,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:25">
       <c r="C7" s="73" t="s">
         <v>380</v>
       </c>
@@ -5368,7 +5945,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:25">
       <c r="C8" s="73" t="s">
         <v>381</v>
       </c>
@@ -5382,7 +5959,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:25">
       <c r="C9" s="73" t="s">
         <v>382</v>
       </c>
@@ -5396,7 +5973,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:25" ht="15.5">
       <c r="C10" s="84" t="s">
         <v>555</v>
       </c>
@@ -5407,7 +5984,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:25">
       <c r="C11" s="73" t="s">
         <v>378</v>
       </c>
@@ -5421,7 +5998,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:25">
       <c r="C12" s="73" t="s">
         <v>565</v>
       </c>
@@ -5435,7 +6012,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:25">
       <c r="C13" s="84" t="s">
         <v>567</v>
       </c>
@@ -5449,7 +6026,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:25">
       <c r="C14" s="85" t="s">
         <v>603</v>
       </c>
@@ -5463,7 +6040,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:25">
       <c r="X15" s="79" t="s">
         <v>417</v>
       </c>
@@ -5471,7 +6048,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:25">
       <c r="X16" s="79" t="s">
         <v>418</v>
       </c>
@@ -5479,7 +6056,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="17" spans="24:25" x14ac:dyDescent="0.35">
+    <row r="17" spans="24:25">
       <c r="X17" s="79" t="s">
         <v>419</v>
       </c>
@@ -5487,7 +6064,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="18" spans="24:25" x14ac:dyDescent="0.35">
+    <row r="18" spans="24:25">
       <c r="X18" s="79" t="s">
         <v>420</v>
       </c>
@@ -5495,7 +6072,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="19" spans="24:25" x14ac:dyDescent="0.35">
+    <row r="19" spans="24:25">
       <c r="X19" s="79" t="s">
         <v>421</v>
       </c>
@@ -5503,7 +6080,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="20" spans="24:25" x14ac:dyDescent="0.35">
+    <row r="20" spans="24:25">
       <c r="X20" s="79" t="s">
         <v>422</v>
       </c>
@@ -5511,7 +6088,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="21" spans="24:25" x14ac:dyDescent="0.35">
+    <row r="21" spans="24:25">
       <c r="X21" s="79" t="s">
         <v>423</v>
       </c>
@@ -5519,7 +6096,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="22" spans="24:25" x14ac:dyDescent="0.35">
+    <row r="22" spans="24:25">
       <c r="X22" s="79" t="s">
         <v>424</v>
       </c>
@@ -5527,7 +6104,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="23" spans="24:25" x14ac:dyDescent="0.35">
+    <row r="23" spans="24:25">
       <c r="X23" s="79" t="s">
         <v>425</v>
       </c>
@@ -5535,7 +6112,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="24" spans="24:25" x14ac:dyDescent="0.35">
+    <row r="24" spans="24:25">
       <c r="X24" s="79" t="s">
         <v>426</v>
       </c>
@@ -5543,7 +6120,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="25" spans="24:25" x14ac:dyDescent="0.35">
+    <row r="25" spans="24:25">
       <c r="X25" s="79" t="s">
         <v>427</v>
       </c>
@@ -5551,7 +6128,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="26" spans="24:25" x14ac:dyDescent="0.35">
+    <row r="26" spans="24:25">
       <c r="X26" s="79" t="s">
         <v>428</v>
       </c>
@@ -5559,7 +6136,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="27" spans="24:25" x14ac:dyDescent="0.35">
+    <row r="27" spans="24:25">
       <c r="X27" s="79" t="s">
         <v>429</v>
       </c>
@@ -5567,7 +6144,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="28" spans="24:25" x14ac:dyDescent="0.35">
+    <row r="28" spans="24:25">
       <c r="X28" s="79" t="s">
         <v>430</v>
       </c>
@@ -5575,7 +6152,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="29" spans="24:25" x14ac:dyDescent="0.35">
+    <row r="29" spans="24:25">
       <c r="X29" s="79" t="s">
         <v>431</v>
       </c>
@@ -5583,7 +6160,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="30" spans="24:25" x14ac:dyDescent="0.35">
+    <row r="30" spans="24:25">
       <c r="X30" s="79" t="s">
         <v>432</v>
       </c>
@@ -5591,7 +6168,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="31" spans="24:25" x14ac:dyDescent="0.35">
+    <row r="31" spans="24:25">
       <c r="X31" s="79" t="s">
         <v>433</v>
       </c>
@@ -5599,7 +6176,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="32" spans="24:25" x14ac:dyDescent="0.35">
+    <row r="32" spans="24:25">
       <c r="X32" s="79" t="s">
         <v>484</v>
       </c>
@@ -5607,7 +6184,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="33" spans="23:26" x14ac:dyDescent="0.35">
+    <row r="33" spans="23:26">
       <c r="X33" s="79" t="s">
         <v>485</v>
       </c>
@@ -5615,7 +6192,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="34" spans="23:26" x14ac:dyDescent="0.35">
+    <row r="34" spans="23:26">
       <c r="X34" s="79" t="s">
         <v>486</v>
       </c>
@@ -5623,7 +6200,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="35" spans="23:26" x14ac:dyDescent="0.35">
+    <row r="35" spans="23:26">
       <c r="X35" s="79" t="s">
         <v>487</v>
       </c>
@@ -5631,7 +6208,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="36" spans="23:26" x14ac:dyDescent="0.35">
+    <row r="36" spans="23:26">
       <c r="X36" s="79" t="s">
         <v>516</v>
       </c>
@@ -5639,12 +6216,12 @@
         <v>517</v>
       </c>
     </row>
-    <row r="38" spans="23:26" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="23:26" ht="15.5">
       <c r="W38" s="81" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="39" spans="23:26" x14ac:dyDescent="0.35">
+    <row r="39" spans="23:26">
       <c r="X39" s="79" t="s">
         <v>434</v>
       </c>
@@ -5652,7 +6229,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="40" spans="23:26" x14ac:dyDescent="0.35">
+    <row r="40" spans="23:26">
       <c r="X40" s="79" t="s">
         <v>435</v>
       </c>
@@ -5661,7 +6238,7 @@
       </c>
       <c r="Z40" s="79"/>
     </row>
-    <row r="41" spans="23:26" x14ac:dyDescent="0.35">
+    <row r="41" spans="23:26">
       <c r="X41" s="79" t="s">
         <v>436</v>
       </c>
@@ -5670,7 +6247,7 @@
       </c>
       <c r="Z41" s="79"/>
     </row>
-    <row r="42" spans="23:26" x14ac:dyDescent="0.35">
+    <row r="42" spans="23:26">
       <c r="X42" s="79" t="s">
         <v>437</v>
       </c>
@@ -5679,7 +6256,7 @@
       </c>
       <c r="Z42" s="79"/>
     </row>
-    <row r="43" spans="23:26" x14ac:dyDescent="0.35">
+    <row r="43" spans="23:26">
       <c r="X43" s="79" t="s">
         <v>438</v>
       </c>
@@ -5688,14 +6265,14 @@
       </c>
       <c r="Z43" s="79"/>
     </row>
-    <row r="44" spans="23:26" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="23:26" ht="15.5">
       <c r="W44" s="81" t="s">
         <v>402</v>
       </c>
       <c r="X44" s="80"/>
       <c r="Z44" s="79"/>
     </row>
-    <row r="45" spans="23:26" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="45" spans="23:26" ht="15.5">
       <c r="X45" s="79" t="s">
         <v>439</v>
       </c>
@@ -5704,7 +6281,7 @@
       </c>
       <c r="Z45" s="80"/>
     </row>
-    <row r="46" spans="23:26" x14ac:dyDescent="0.35">
+    <row r="46" spans="23:26">
       <c r="X46" s="79" t="s">
         <v>440</v>
       </c>
@@ -5713,7 +6290,7 @@
       </c>
       <c r="Z46" s="79"/>
     </row>
-    <row r="47" spans="23:26" x14ac:dyDescent="0.35">
+    <row r="47" spans="23:26">
       <c r="X47" s="79" t="s">
         <v>441</v>
       </c>
@@ -5722,7 +6299,7 @@
       </c>
       <c r="Z47" s="79"/>
     </row>
-    <row r="48" spans="23:26" x14ac:dyDescent="0.35">
+    <row r="48" spans="23:26">
       <c r="X48" s="79" t="s">
         <v>442</v>
       </c>
@@ -5731,7 +6308,7 @@
       </c>
       <c r="Z48" s="79"/>
     </row>
-    <row r="49" spans="15:25" x14ac:dyDescent="0.35">
+    <row r="49" spans="15:25">
       <c r="O49" s="79"/>
       <c r="X49" s="79" t="s">
         <v>443</v>
@@ -5740,7 +6317,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="50" spans="15:25" x14ac:dyDescent="0.35">
+    <row r="50" spans="15:25">
       <c r="O50" s="79"/>
       <c r="X50" s="79" t="s">
         <v>441</v>
@@ -5759,10 +6336,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4C14141-45DA-4C30-845C-3E630B347F10}">
   <dimension ref="A1:F51"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="6.54296875" style="41" customWidth="1"/>
     <col min="2" max="2" width="38.26953125" customWidth="1"/>
@@ -5771,7 +6348,7 @@
     <col min="6" max="6" width="6.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6">
       <c r="A1" s="32" t="s">
         <v>7</v>
       </c>
@@ -5791,7 +6368,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6">
       <c r="A2" s="35">
         <v>1</v>
       </c>
@@ -5811,7 +6388,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6">
       <c r="A3" s="38">
         <v>2</v>
       </c>
@@ -5831,7 +6408,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6">
       <c r="A4" s="35">
         <v>3</v>
       </c>
@@ -5851,7 +6428,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6">
       <c r="A5" s="38">
         <v>4</v>
       </c>
@@ -5871,7 +6448,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6">
       <c r="A6" s="35">
         <v>5</v>
       </c>
@@ -5891,7 +6468,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6">
       <c r="A7" s="38">
         <v>6</v>
       </c>
@@ -5911,7 +6488,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6">
       <c r="A8" s="35">
         <v>7</v>
       </c>
@@ -5931,7 +6508,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6">
       <c r="A9" s="38">
         <v>8</v>
       </c>
@@ -5951,7 +6528,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6">
       <c r="A10" s="35">
         <v>9</v>
       </c>
@@ -5971,7 +6548,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6">
       <c r="A11" s="38">
         <v>10</v>
       </c>
@@ -5991,7 +6568,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6">
       <c r="A12" s="35">
         <v>11</v>
       </c>
@@ -6011,7 +6588,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6">
       <c r="A13" s="38">
         <v>12</v>
       </c>
@@ -6031,7 +6608,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6">
       <c r="A14" s="35">
         <v>13</v>
       </c>
@@ -6051,7 +6628,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6">
       <c r="A15" s="38">
         <v>14</v>
       </c>
@@ -6071,7 +6648,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6">
       <c r="A16" s="35">
         <v>15</v>
       </c>
@@ -6091,7 +6668,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6">
       <c r="A17" s="38">
         <v>16</v>
       </c>
@@ -6111,7 +6688,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6">
       <c r="A18" s="35">
         <v>17</v>
       </c>
@@ -6131,7 +6708,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6">
       <c r="A19" s="38">
         <v>18</v>
       </c>
@@ -6151,7 +6728,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6">
       <c r="A20" s="35">
         <v>19</v>
       </c>
@@ -6171,7 +6748,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6">
       <c r="A21" s="38">
         <v>20</v>
       </c>
@@ -6191,7 +6768,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6">
       <c r="A22" s="35">
         <v>21</v>
       </c>
@@ -6211,7 +6788,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6">
       <c r="A23" s="38">
         <v>22</v>
       </c>
@@ -6231,7 +6808,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6">
       <c r="A24" s="35">
         <v>23</v>
       </c>
@@ -6251,7 +6828,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6">
       <c r="A25" s="38">
         <v>24</v>
       </c>
@@ -6271,7 +6848,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6">
       <c r="A26" s="35">
         <v>25</v>
       </c>
@@ -6291,7 +6868,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6">
       <c r="A27" s="38">
         <v>26</v>
       </c>
@@ -6311,7 +6888,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6">
       <c r="A28" s="35">
         <v>27</v>
       </c>
@@ -6331,7 +6908,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6">
       <c r="A29" s="38">
         <v>28</v>
       </c>
@@ -6351,7 +6928,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6">
       <c r="A30" s="35">
         <v>29</v>
       </c>
@@ -6371,7 +6948,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6">
       <c r="A31" s="38">
         <v>30</v>
       </c>
@@ -6391,7 +6968,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6">
       <c r="A32" s="35">
         <v>31</v>
       </c>
@@ -6411,7 +6988,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6">
       <c r="A33" s="38">
         <v>32</v>
       </c>
@@ -6431,7 +7008,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6">
       <c r="A34" s="38">
         <v>33</v>
       </c>
@@ -6451,7 +7028,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6">
       <c r="A35" s="35">
         <v>34</v>
       </c>
@@ -6471,7 +7048,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6">
       <c r="A36" s="35">
         <v>35</v>
       </c>
@@ -6491,7 +7068,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6">
       <c r="A37" s="35">
         <v>36</v>
       </c>
@@ -6511,7 +7088,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6">
       <c r="A38" s="35">
         <v>37</v>
       </c>
@@ -6531,7 +7108,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6">
       <c r="A39" s="35">
         <v>38</v>
       </c>
@@ -6551,7 +7128,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6">
       <c r="A40" s="35">
         <v>39</v>
       </c>
@@ -6571,7 +7148,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6">
       <c r="A41" s="35">
         <v>40</v>
       </c>
@@ -6591,7 +7168,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6">
       <c r="A42" s="35">
         <v>41</v>
       </c>
@@ -6611,7 +7188,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6">
       <c r="A43" s="35">
         <v>42</v>
       </c>
@@ -6631,7 +7208,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6">
       <c r="A44" s="38">
         <v>43</v>
       </c>
@@ -6651,7 +7228,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6">
       <c r="A45" s="38">
         <v>44</v>
       </c>
@@ -6671,7 +7248,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6">
       <c r="A46" s="35">
         <v>45</v>
       </c>
@@ -6691,7 +7268,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6">
       <c r="A47" s="35">
         <v>46</v>
       </c>
@@ -6711,7 +7288,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6">
       <c r="A48" s="35">
         <v>47</v>
       </c>
@@ -6731,7 +7308,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6">
       <c r="A49" s="35">
         <v>48</v>
       </c>
@@ -6751,7 +7328,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6">
       <c r="A50" s="35">
         <v>49</v>
       </c>
@@ -6771,7 +7348,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6">
       <c r="A51" s="70">
         <v>50</v>
       </c>
@@ -6799,17 +7376,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8049D8E-7482-48AF-95C9-7F1B728B0DDE}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="4.90625" customWidth="1"/>
     <col min="2" max="2" width="57.1796875" customWidth="1"/>
     <col min="3" max="3" width="60.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="15" thickBot="1">
       <c r="A1" s="51" t="s">
         <v>303</v>
       </c>
@@ -6820,7 +7397,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" ht="15" thickTop="1">
       <c r="A2" s="54">
         <v>1</v>
       </c>
@@ -6831,7 +7408,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3">
       <c r="A3" s="54">
         <v>2</v>
       </c>
@@ -6842,7 +7419,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3">
       <c r="A4" s="58">
         <v>3</v>
       </c>
@@ -6853,7 +7430,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3">
       <c r="A5" s="58">
         <v>4</v>
       </c>
@@ -6864,7 +7441,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3">
       <c r="A6" s="58">
         <v>5</v>
       </c>
@@ -6875,7 +7452,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3">
       <c r="A7" s="58">
         <v>6</v>
       </c>
@@ -6886,7 +7463,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3">
       <c r="A8" s="58">
         <v>7</v>
       </c>
@@ -6897,7 +7474,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3">
       <c r="A9" s="58">
         <v>8</v>
       </c>
@@ -6908,7 +7485,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3">
       <c r="A10" s="58">
         <v>9</v>
       </c>
@@ -6919,7 +7496,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" ht="29">
       <c r="A11" s="58">
         <v>10</v>
       </c>
@@ -6930,7 +7507,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3">
       <c r="A12" s="50">
         <v>11</v>
       </c>
@@ -6941,7 +7518,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3">
       <c r="A13" s="58">
         <v>12</v>
       </c>
@@ -6952,7 +7529,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3">
       <c r="A14" s="50">
         <v>13</v>
       </c>
@@ -6963,12 +7540,12 @@
         <v>359</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3">
       <c r="A15" s="50"/>
       <c r="B15" s="62"/>
       <c r="C15" s="61"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3">
       <c r="A16" s="50"/>
       <c r="B16" s="63"/>
       <c r="C16" s="61"/>
@@ -6997,10 +7574,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF1BA8E2-9FD2-4C47-B5D3-EF9907B8F692}">
   <dimension ref="A1:D52"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="10.54296875" style="41" customWidth="1"/>
     <col min="2" max="2" width="38.26953125" customWidth="1"/>
@@ -7008,7 +7585,7 @@
     <col min="4" max="4" width="13.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4">
       <c r="A1" s="32" t="s">
         <v>299</v>
       </c>
@@ -7022,7 +7599,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4">
       <c r="A2" s="35">
         <v>1</v>
       </c>
@@ -7034,7 +7611,7 @@
       </c>
       <c r="D2" s="43"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4">
       <c r="A3" s="38">
         <v>2</v>
       </c>
@@ -7048,7 +7625,7 @@
         <v>1944</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4">
       <c r="A4" s="35">
         <v>3</v>
       </c>
@@ -7060,7 +7637,7 @@
       </c>
       <c r="D4" s="43"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4">
       <c r="A5" s="38">
         <v>4</v>
       </c>
@@ -7072,7 +7649,7 @@
       </c>
       <c r="D5" s="43"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4">
       <c r="A6" s="35">
         <v>5</v>
       </c>
@@ -7086,7 +7663,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4">
       <c r="A7" s="38">
         <v>6</v>
       </c>
@@ -7098,7 +7675,7 @@
       </c>
       <c r="D7" s="43"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4">
       <c r="A8" s="35">
         <v>7</v>
       </c>
@@ -7110,7 +7687,7 @@
       </c>
       <c r="D8" s="43"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4">
       <c r="A9" s="38">
         <v>8</v>
       </c>
@@ -7122,7 +7699,7 @@
       </c>
       <c r="D9" s="43"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4">
       <c r="A10" s="35">
         <v>9</v>
       </c>
@@ -7136,7 +7713,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4">
       <c r="A11" s="38">
         <v>10</v>
       </c>
@@ -7148,7 +7725,7 @@
       </c>
       <c r="D11" s="43"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4">
       <c r="A12" s="35">
         <v>11</v>
       </c>
@@ -7162,7 +7739,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4">
       <c r="A13" s="38">
         <v>12</v>
       </c>
@@ -7176,7 +7753,7 @@
         <v>1879</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4">
       <c r="A14" s="35">
         <v>13</v>
       </c>
@@ -7188,7 +7765,7 @@
       </c>
       <c r="D14" s="44"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4">
       <c r="A15" s="38">
         <v>14</v>
       </c>
@@ -7202,7 +7779,7 @@
         <v>1887</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4">
       <c r="A16" s="35">
         <v>15</v>
       </c>
@@ -7216,7 +7793,7 @@
         <v>1953</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4">
       <c r="A17" s="38">
         <v>16</v>
       </c>
@@ -7228,7 +7805,7 @@
       </c>
       <c r="D17" s="44"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4">
       <c r="A18" s="35">
         <v>17</v>
       </c>
@@ -7240,7 +7817,7 @@
       </c>
       <c r="D18" s="44"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4">
       <c r="A19" s="38">
         <v>18</v>
       </c>
@@ -7254,7 +7831,7 @@
         <v>1882</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4">
       <c r="A20" s="35">
         <v>19</v>
       </c>
@@ -7266,7 +7843,7 @@
       </c>
       <c r="D20" s="43"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4">
       <c r="A21" s="38">
         <v>20</v>
       </c>
@@ -7278,7 +7855,7 @@
       </c>
       <c r="D21" s="43"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4">
       <c r="A22" s="35">
         <v>21</v>
       </c>
@@ -7290,7 +7867,7 @@
       </c>
       <c r="D22" s="43"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4">
       <c r="A23" s="38">
         <v>22</v>
       </c>
@@ -7302,7 +7879,7 @@
       </c>
       <c r="D23" s="43"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4">
       <c r="A24" s="35">
         <v>23</v>
       </c>
@@ -7314,7 +7891,7 @@
       </c>
       <c r="D24" s="43"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4">
       <c r="A25" s="38">
         <v>24</v>
       </c>
@@ -7326,7 +7903,7 @@
       </c>
       <c r="D25" s="43"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4">
       <c r="A26" s="35">
         <v>25</v>
       </c>
@@ -7338,7 +7915,7 @@
       </c>
       <c r="D26" s="44"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4">
       <c r="A27" s="38">
         <v>26</v>
       </c>
@@ -7350,7 +7927,7 @@
       </c>
       <c r="D27" s="43"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4">
       <c r="A28" s="35">
         <v>27</v>
       </c>
@@ -7364,7 +7941,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4">
       <c r="A29" s="38">
         <v>28</v>
       </c>
@@ -7376,7 +7953,7 @@
       </c>
       <c r="D29" s="43"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4">
       <c r="A30" s="35">
         <v>29</v>
       </c>
@@ -7388,7 +7965,7 @@
       </c>
       <c r="D30" s="43"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4">
       <c r="A31" s="38">
         <v>30</v>
       </c>
@@ -7400,7 +7977,7 @@
       </c>
       <c r="D31" s="44"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4">
       <c r="A32" s="35">
         <v>31</v>
       </c>
@@ -7412,7 +7989,7 @@
       </c>
       <c r="D32" s="44"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4">
       <c r="A33" s="38">
         <v>32</v>
       </c>
@@ -7424,7 +8001,7 @@
       </c>
       <c r="D33" s="43"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4">
       <c r="A34" s="38">
         <v>33</v>
       </c>
@@ -7438,7 +8015,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4">
       <c r="A35" s="35">
         <v>34</v>
       </c>
@@ -7450,7 +8027,7 @@
       </c>
       <c r="D35" s="44"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4">
       <c r="A36" s="35">
         <v>35</v>
       </c>
@@ -7462,7 +8039,7 @@
       </c>
       <c r="D36" s="43"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4">
       <c r="A37" s="35">
         <v>36</v>
       </c>
@@ -7474,7 +8051,7 @@
       </c>
       <c r="D37" s="43"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4">
       <c r="A38" s="35">
         <v>37</v>
       </c>
@@ -7486,7 +8063,7 @@
       </c>
       <c r="D38" s="44"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4">
       <c r="A39" s="35">
         <v>38</v>
       </c>
@@ -7498,7 +8075,7 @@
       </c>
       <c r="D39" s="44"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4">
       <c r="A40" s="35">
         <v>39</v>
       </c>
@@ -7510,7 +8087,7 @@
       </c>
       <c r="D40" s="43"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4">
       <c r="A41" s="35">
         <v>40</v>
       </c>
@@ -7524,7 +8101,7 @@
         <v>1869</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4">
       <c r="A42" s="35">
         <v>41</v>
       </c>
@@ -7536,7 +8113,7 @@
       </c>
       <c r="D42" s="43"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4">
       <c r="A43" s="35">
         <v>42</v>
       </c>
@@ -7550,7 +8127,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4">
       <c r="A44" s="38">
         <v>43</v>
       </c>
@@ -7564,7 +8141,7 @@
         <v>1895</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4">
       <c r="A45" s="38">
         <v>44</v>
       </c>
@@ -7578,7 +8155,7 @@
         <v>1902</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4">
       <c r="A46" s="38">
         <v>44</v>
       </c>
@@ -7590,7 +8167,7 @@
       </c>
       <c r="D46" s="43"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4">
       <c r="A47" s="35">
         <v>45</v>
       </c>
@@ -7602,7 +8179,7 @@
       </c>
       <c r="D47" s="43"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4">
       <c r="A48" s="35">
         <v>46</v>
       </c>
@@ -7614,7 +8191,7 @@
       </c>
       <c r="D48" s="43"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:4">
       <c r="A49" s="35">
         <v>47</v>
       </c>
@@ -7626,7 +8203,7 @@
       </c>
       <c r="D49" s="43"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:4">
       <c r="A50" s="38">
         <v>48</v>
       </c>
@@ -7638,7 +8215,7 @@
       </c>
       <c r="D50" s="43"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:4">
       <c r="A51" s="35">
         <v>49</v>
       </c>
@@ -7652,7 +8229,7 @@
         <v>1876</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:4">
       <c r="A52" s="38">
         <v>50</v>
       </c>
@@ -7673,10 +8250,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0041FEF0-BF6F-4667-AFBD-1C23A1866795}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="10.7265625" customWidth="1"/>
     <col min="2" max="2" width="17.453125" customWidth="1"/>
@@ -7684,7 +8261,7 @@
     <col min="4" max="4" width="37.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" ht="18.5">
       <c r="A1" s="3" t="s">
         <v>26</v>
       </c>
@@ -7698,7 +8275,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4">
       <c r="A2" s="9">
         <v>1</v>
       </c>
@@ -7712,7 +8289,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4">
       <c r="A3" s="9">
         <v>2</v>
       </c>
@@ -7726,7 +8303,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4">
       <c r="A4" s="9">
         <v>3</v>
       </c>
@@ -7740,7 +8317,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4">
       <c r="A5" s="9">
         <v>4</v>
       </c>
@@ -7754,7 +8331,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4">
       <c r="A6" s="9">
         <v>5</v>
       </c>
@@ -7768,7 +8345,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4">
       <c r="A7" s="9">
         <v>6</v>
       </c>
@@ -7781,196 +8358,6 @@
       <c r="D7" s="4" t="s">
         <v>32</v>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8265AFD9-D9EB-4B75-B60D-6B7F7204230D}">
-  <dimension ref="A1:B29"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="26.36328125" customWidth="1"/>
-    <col min="2" max="2" width="31.36328125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A1" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" s="4"/>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" s="4"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="4"/>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" s="4"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="4"/>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="4"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="4"/>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" s="4"/>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="4"/>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" s="4"/>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B12" s="4"/>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B13" s="4"/>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" s="4"/>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B15" s="4"/>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B16" s="4"/>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B17" s="4"/>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B18" s="4"/>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B19" s="4"/>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B20" s="4"/>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B21" s="4"/>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B22" s="4"/>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B23" s="4"/>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A24" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B24" s="4"/>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B25" s="4"/>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A26" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B26" s="4"/>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A27" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B27" s="4"/>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A28" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B28" s="4"/>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A29" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="B29" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Info/Additional_information.xlsx
+++ b/Info/Additional_information.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E71DF8E1-957B-4FAE-9D42-4C8BD8B31A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D074E7B7-19EA-4AD0-A25D-B42283A78632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="676">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="686">
   <si>
     <t>good quality (UNC for UNC collection; UNC and XF for XF collection)</t>
   </si>
@@ -2107,13 +2107,43 @@
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/2/20/Flag_of_the_Netherlands.svg</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/5/5c/Flag_of_Portugal.svg</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/1/11/Flag_of_Lithuania.svg</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/4/45/Flag_of_Ireland.svg</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/8/84/Flag_of_Latvia.svg</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/0/03/Flag_of_Italy.svg</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/c/c3/Flag_of_France.svg</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/8/8f/Flag_of_Estonia.svg</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/d/d4/Flag_of_Cyprus.svg</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/6/65/Flag_of_Belgium.svg</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/4/41/Flag_of_Austria.svg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2269,11 +2299,6 @@
       <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="7"/>
-      <color rgb="FF0A0A0A"/>
-      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="22">
@@ -2713,7 +2738,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2942,6 +2967,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="12" fillId="20" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2995,10 +3021,6 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -3928,14 +3950,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.08984375" customWidth="1"/>
     <col min="3" max="3" width="5" customWidth="1"/>
     <col min="4" max="4" width="81" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.5">
+    <row r="1" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="64" t="s">
         <v>7</v>
       </c>
@@ -3949,7 +3971,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -3963,7 +3985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -3977,7 +3999,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -3991,7 +4013,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -4005,7 +4027,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -4019,7 +4041,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -4033,7 +4055,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -4156,13 +4178,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8265AFD9-D9EB-4B75-B60D-6B7F7204230D}">
   <dimension ref="A1:B29"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="26.36328125" customWidth="1"/>
     <col min="2" max="2" width="31.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.5">
+    <row r="1" spans="1:2" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>34</v>
       </c>
@@ -4170,169 +4192,169 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>35</v>
       </c>
       <c r="B2" s="4"/>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>36</v>
       </c>
       <c r="B3" s="4"/>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="4"/>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>38</v>
       </c>
       <c r="B5" s="4"/>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>39</v>
       </c>
       <c r="B6" s="4"/>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>40</v>
       </c>
       <c r="B7" s="4"/>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>41</v>
       </c>
       <c r="B8" s="4"/>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>42</v>
       </c>
       <c r="B9" s="4"/>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>43</v>
       </c>
       <c r="B10" s="4"/>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>44</v>
       </c>
       <c r="B11" s="4"/>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>45</v>
       </c>
       <c r="B12" s="4"/>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>46</v>
       </c>
       <c r="B13" s="4"/>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>47</v>
       </c>
       <c r="B14" s="4"/>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>48</v>
       </c>
       <c r="B15" s="4"/>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>49</v>
       </c>
       <c r="B16" s="4"/>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>50</v>
       </c>
       <c r="B17" s="4"/>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>51</v>
       </c>
       <c r="B18" s="4"/>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>52</v>
       </c>
       <c r="B19" s="4"/>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>53</v>
       </c>
       <c r="B20" s="4"/>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>54</v>
       </c>
       <c r="B21" s="4"/>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
         <v>55</v>
       </c>
       <c r="B22" s="4"/>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>56</v>
       </c>
       <c r="B23" s="4"/>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>57</v>
       </c>
       <c r="B24" s="4"/>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>58</v>
       </c>
       <c r="B25" s="4"/>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>59</v>
       </c>
       <c r="B26" s="4"/>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>60</v>
       </c>
       <c r="B27" s="4"/>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
         <v>61</v>
       </c>
       <c r="B28" s="4"/>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>367</v>
       </c>
@@ -4346,7 +4368,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{729F7C06-1AE8-4162-8F40-6E9A64E311D7}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.81640625" customWidth="1"/>
     <col min="2" max="2" width="57.1796875" customWidth="1"/>
@@ -4354,7 +4376,7 @@
     <col min="4" max="4" width="15.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>303</v>
       </c>
@@ -4365,7 +4387,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="41">
         <v>1</v>
       </c>
@@ -4376,7 +4398,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="41">
         <v>2</v>
       </c>
@@ -4387,7 +4409,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="41">
         <v>3</v>
       </c>
@@ -4398,7 +4420,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="41">
         <v>4</v>
       </c>
@@ -4409,7 +4431,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="41">
         <v>5</v>
       </c>
@@ -4420,7 +4442,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="41">
         <v>6</v>
       </c>
@@ -4431,7 +4453,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="29">
+    <row r="8" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="41">
         <v>7</v>
       </c>
@@ -4442,7 +4464,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="41">
         <v>8</v>
       </c>
@@ -4453,7 +4475,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="29">
+    <row r="10" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="41">
         <v>9</v>
       </c>
@@ -4464,7 +4486,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="41">
         <v>10</v>
       </c>
@@ -4475,7 +4497,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="41">
         <v>11</v>
       </c>
@@ -4486,7 +4508,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="41">
         <v>12</v>
       </c>
@@ -4497,7 +4519,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="41">
         <v>13</v>
       </c>
@@ -4508,7 +4530,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="50">
         <v>14</v>
       </c>
@@ -4519,7 +4541,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="50">
         <v>15</v>
       </c>
@@ -4560,39 +4582,39 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D5AF97D-14BA-4E23-B5FF-856D52BDA29A}">
   <dimension ref="B7:Z7"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="9.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="7" spans="2:26" ht="61.5">
-      <c r="B7" s="105" t="s">
+    <row r="7" spans="2:26" ht="61.5" x14ac:dyDescent="1.35">
+      <c r="B7" s="106" t="s">
         <v>601</v>
       </c>
-      <c r="C7" s="106"/>
-      <c r="D7" s="106"/>
-      <c r="E7" s="106"/>
-      <c r="F7" s="106"/>
-      <c r="G7" s="106"/>
-      <c r="H7" s="106"/>
-      <c r="I7" s="106"/>
-      <c r="J7" s="106"/>
-      <c r="K7" s="106"/>
-      <c r="L7" s="106"/>
-      <c r="M7" s="106"/>
-      <c r="N7" s="106"/>
-      <c r="O7" s="106"/>
-      <c r="P7" s="106"/>
-      <c r="Q7" s="106"/>
-      <c r="R7" s="106"/>
-      <c r="S7" s="106"/>
-      <c r="T7" s="106"/>
-      <c r="U7" s="106"/>
-      <c r="V7" s="106"/>
-      <c r="W7" s="106"/>
-      <c r="X7" s="106"/>
-      <c r="Y7" s="106"/>
-      <c r="Z7" s="106"/>
+      <c r="C7" s="107"/>
+      <c r="D7" s="107"/>
+      <c r="E7" s="107"/>
+      <c r="F7" s="107"/>
+      <c r="G7" s="107"/>
+      <c r="H7" s="107"/>
+      <c r="I7" s="107"/>
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
+      <c r="N7" s="107"/>
+      <c r="O7" s="107"/>
+      <c r="P7" s="107"/>
+      <c r="Q7" s="107"/>
+      <c r="R7" s="107"/>
+      <c r="S7" s="107"/>
+      <c r="T7" s="107"/>
+      <c r="U7" s="107"/>
+      <c r="V7" s="107"/>
+      <c r="W7" s="107"/>
+      <c r="X7" s="107"/>
+      <c r="Y7" s="107"/>
+      <c r="Z7" s="107"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4608,7 +4630,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57D9DE6C-583F-4F0B-9E0F-CDE5965E194A}">
   <dimension ref="A1:I30"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.90625" customWidth="1"/>
     <col min="2" max="2" width="18.7265625" customWidth="1"/>
@@ -4618,7 +4640,7 @@
     <col min="9" max="9" width="26.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18.5">
+    <row r="1" spans="1:9" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="66" t="s">
         <v>62</v>
       </c>
@@ -4638,11 +4660,11 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="92">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" s="93">
         <v>1</v>
       </c>
-      <c r="B2" s="100">
+      <c r="B2" s="101">
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
@@ -4658,9 +4680,9 @@
         <v>76</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="93"/>
-      <c r="B3" s="100"/>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" s="94"/>
+      <c r="B3" s="101"/>
       <c r="C3" s="4" t="s">
         <v>65</v>
       </c>
@@ -4674,9 +4696,9 @@
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="94"/>
-      <c r="B4" s="101">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="95"/>
+      <c r="B4" s="102">
         <v>2</v>
       </c>
       <c r="C4" s="4" t="s">
@@ -4692,15 +4714,15 @@
         <v>81</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="94"/>
-      <c r="B5" s="101"/>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="95"/>
+      <c r="B5" s="102"/>
       <c r="C5" s="4" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="94"/>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" s="95"/>
       <c r="B6" s="15">
         <v>3</v>
       </c>
@@ -4708,8 +4730,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="94"/>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" s="95"/>
       <c r="B7" s="16" t="s">
         <v>90</v>
       </c>
@@ -4717,24 +4739,24 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="94"/>
-      <c r="B8" s="102">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" s="95"/>
+      <c r="B8" s="103">
         <v>6</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="94"/>
-      <c r="B9" s="103"/>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" s="95"/>
+      <c r="B9" s="104"/>
       <c r="C9" s="4" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="94"/>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" s="95"/>
       <c r="B10" s="17">
         <v>7</v>
       </c>
@@ -4742,15 +4764,15 @@
         <v>72</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="94"/>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" s="95"/>
       <c r="B11" s="24"/>
       <c r="C11" s="4" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="94"/>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12" s="95"/>
       <c r="B12" s="18">
         <v>8</v>
       </c>
@@ -4758,8 +4780,8 @@
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="95"/>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13" s="96"/>
       <c r="B13" s="25" t="s">
         <v>78</v>
       </c>
@@ -4767,8 +4789,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15" thickBot="1">
-      <c r="A14" s="96"/>
+    <row r="14" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="97"/>
       <c r="B14" s="26" t="s">
         <v>91</v>
       </c>
@@ -4776,8 +4798,8 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="14.5" customHeight="1" thickTop="1">
-      <c r="A15" s="97">
+    <row r="15" spans="1:9" ht="14.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="98">
         <v>2</v>
       </c>
       <c r="B15" s="19" t="s">
@@ -4787,8 +4809,8 @@
         <v>84</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="14.5" customHeight="1">
-      <c r="A16" s="98"/>
+    <row r="16" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="99"/>
       <c r="B16" s="20" t="s">
         <v>365</v>
       </c>
@@ -4796,8 +4818,8 @@
         <v>85</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="14.5" customHeight="1">
-      <c r="A17" s="98"/>
+    <row r="17" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="99"/>
       <c r="B17" s="21" t="s">
         <v>366</v>
       </c>
@@ -4805,8 +4827,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="14.5" customHeight="1" thickBot="1">
-      <c r="A18" s="99"/>
+    <row r="18" spans="1:3" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="100"/>
       <c r="B18" s="22" t="s">
         <v>92</v>
       </c>
@@ -4814,8 +4836,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="14.5" customHeight="1" thickTop="1">
-      <c r="A19" s="86">
+    <row r="19" spans="1:3" ht="14.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="87">
         <v>3</v>
       </c>
       <c r="B19" s="23" t="s">
@@ -4825,8 +4847,8 @@
         <v>87</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="14.5" customHeight="1">
-      <c r="A20" s="87"/>
+    <row r="20" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="88"/>
       <c r="B20" s="27" t="s">
         <v>93</v>
       </c>
@@ -4834,8 +4856,8 @@
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="14.5" customHeight="1" thickBot="1">
-      <c r="A21" s="88"/>
+    <row r="21" spans="1:3" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="89"/>
       <c r="B21" s="28" t="s">
         <v>95</v>
       </c>
@@ -4843,8 +4865,8 @@
         <v>94</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="14.5" customHeight="1" thickTop="1">
-      <c r="A22" s="89">
+    <row r="22" spans="1:3" ht="14.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="90">
         <v>4</v>
       </c>
       <c r="B22" s="19" t="s">
@@ -4854,8 +4876,8 @@
         <v>97</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="14.5" customHeight="1">
-      <c r="A23" s="90"/>
+    <row r="23" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="91"/>
       <c r="B23" s="20" t="s">
         <v>98</v>
       </c>
@@ -4863,8 +4885,8 @@
         <v>99</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="14.5" customHeight="1">
-      <c r="A24" s="90"/>
+    <row r="24" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="91"/>
       <c r="B24" s="21" t="s">
         <v>100</v>
       </c>
@@ -4872,8 +4894,8 @@
         <v>101</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="14.5" customHeight="1">
-      <c r="A25" s="90"/>
+    <row r="25" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="91"/>
       <c r="B25" s="16" t="s">
         <v>102</v>
       </c>
@@ -4881,8 +4903,8 @@
         <v>103</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="90"/>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" s="91"/>
       <c r="B26" s="29" t="s">
         <v>104</v>
       </c>
@@ -4890,8 +4912,8 @@
         <v>105</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="90"/>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="91"/>
       <c r="B27" s="30" t="s">
         <v>106</v>
       </c>
@@ -4899,8 +4921,8 @@
         <v>107</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="90"/>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" s="91"/>
       <c r="B28" s="18">
         <v>8</v>
       </c>
@@ -4908,8 +4930,8 @@
         <v>108</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15" thickBot="1">
-      <c r="A29" s="91"/>
+    <row r="29" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="92"/>
       <c r="B29" s="31" t="s">
         <v>78</v>
       </c>
@@ -4917,7 +4939,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15" thickTop="1"/>
+    <row r="30" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <autoFilter ref="A1:C15" xr:uid="{57D9DE6C-583F-4F0B-9E0F-CDE5965E194A}"/>
   <mergeCells count="7">
@@ -4940,7 +4962,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DC835FD-69FE-4DBC-957F-9A46CA05517E}">
   <dimension ref="A1:F28"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.453125" customWidth="1"/>
     <col min="2" max="2" width="15.54296875" customWidth="1"/>
@@ -4950,7 +4972,7 @@
     <col min="6" max="6" width="182.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18.5">
+    <row r="1" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="78" t="s">
         <v>536</v>
       </c>
@@ -4970,7 +4992,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="14.5" customHeight="1">
+    <row r="2" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
@@ -4990,7 +5012,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -5010,7 +5032,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2</v>
       </c>
@@ -5030,7 +5052,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>3</v>
       </c>
@@ -5050,7 +5072,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>4</v>
       </c>
@@ -5070,7 +5092,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>5</v>
       </c>
@@ -5090,7 +5112,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>6</v>
       </c>
@@ -5110,7 +5132,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>7</v>
       </c>
@@ -5130,7 +5152,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>8</v>
       </c>
@@ -5150,7 +5172,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>9</v>
       </c>
@@ -5170,7 +5192,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>10</v>
       </c>
@@ -5190,7 +5212,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>11</v>
       </c>
@@ -5210,7 +5232,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>12</v>
       </c>
@@ -5230,7 +5252,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>13</v>
       </c>
@@ -5250,7 +5272,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>14</v>
       </c>
@@ -5270,7 +5292,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>15</v>
       </c>
@@ -5290,7 +5312,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>16</v>
       </c>
@@ -5310,7 +5332,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>17</v>
       </c>
@@ -5330,7 +5352,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>18</v>
       </c>
@@ -5350,7 +5372,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>19</v>
       </c>
@@ -5370,7 +5392,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>20</v>
       </c>
@@ -5390,7 +5412,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>21</v>
       </c>
@@ -5410,7 +5432,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>22</v>
       </c>
@@ -5430,7 +5452,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>23</v>
       </c>
@@ -5450,7 +5472,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>24</v>
       </c>
@@ -5470,7 +5492,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>25</v>
       </c>
@@ -5490,7 +5512,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>26</v>
       </c>
@@ -5549,8 +5571,8 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C94A307-2E39-40B9-B204-C92675C0AF71}">
-  <dimension ref="A1:E43"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.36328125" customWidth="1"/>
     <col min="2" max="2" width="54.7265625" customWidth="1"/>
@@ -5560,7 +5582,7 @@
     <col min="6" max="6" width="62" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>637</v>
       </c>
@@ -5577,204 +5599,192 @@
         <v>641</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>525</v>
       </c>
-      <c r="B2" t="s">
-        <v>413</v>
+      <c r="B2" s="86" t="s">
+        <v>685</v>
       </c>
       <c r="C2" t="s">
         <v>644</v>
       </c>
-      <c r="D2" s="108" t="s">
+      <c r="D2" s="86" t="s">
         <v>642</v>
       </c>
-      <c r="E2" s="108" t="s">
+      <c r="E2" s="86" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>525</v>
       </c>
-      <c r="B3" t="s">
-        <v>414</v>
+      <c r="B3" s="86" t="s">
+        <v>684</v>
       </c>
       <c r="C3" t="s">
         <v>646</v>
       </c>
-      <c r="D3" s="108" t="s">
+      <c r="D3" s="86" t="s">
         <v>645</v>
       </c>
-      <c r="E3" s="108" t="s">
+      <c r="E3" s="86" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>525</v>
       </c>
-      <c r="B4" t="s">
-        <v>420</v>
+      <c r="B4" s="86" t="s">
+        <v>683</v>
       </c>
       <c r="C4" t="s">
         <v>650</v>
       </c>
-      <c r="D4" s="108" t="s">
+      <c r="D4" s="86" t="s">
         <v>648</v>
       </c>
-      <c r="E4" s="108" t="s">
+      <c r="E4" s="86" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>525</v>
       </c>
-      <c r="B5" t="s">
-        <v>432</v>
+      <c r="B5" s="86" t="s">
+        <v>682</v>
       </c>
       <c r="C5" t="s">
         <v>652</v>
       </c>
-      <c r="D5" s="108" t="s">
+      <c r="D5" s="86" t="s">
         <v>651</v>
       </c>
-      <c r="E5" s="108" t="s">
+      <c r="E5" s="86" t="s">
         <v>653</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>525</v>
       </c>
-      <c r="B6" t="s">
-        <v>430</v>
+      <c r="B6" s="86" t="s">
+        <v>681</v>
       </c>
       <c r="C6" t="s">
         <v>655</v>
       </c>
-      <c r="D6" s="108" t="s">
+      <c r="D6" s="86" t="s">
         <v>654</v>
       </c>
-      <c r="E6" s="108" t="s">
+      <c r="E6" s="86" t="s">
         <v>656</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>525</v>
       </c>
-      <c r="B7" t="s">
-        <v>419</v>
+      <c r="B7" s="86" t="s">
+        <v>680</v>
       </c>
       <c r="C7" t="s">
         <v>658</v>
       </c>
-      <c r="D7" s="108" t="s">
+      <c r="D7" s="86" t="s">
         <v>657</v>
       </c>
-      <c r="E7" s="108" t="s">
+      <c r="E7" s="86" t="s">
         <v>659</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>525</v>
       </c>
-      <c r="B8" t="s">
-        <v>421</v>
+      <c r="B8" s="86" t="s">
+        <v>679</v>
       </c>
       <c r="C8" t="s">
         <v>661</v>
       </c>
-      <c r="D8" s="108" t="s">
+      <c r="D8" s="86" t="s">
         <v>660</v>
       </c>
-      <c r="E8" s="108" t="s">
+      <c r="E8" s="86" t="s">
         <v>662</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>525</v>
       </c>
-      <c r="B9" t="s">
-        <v>417</v>
+      <c r="B9" s="86" t="s">
+        <v>678</v>
       </c>
       <c r="C9" t="s">
         <v>665</v>
       </c>
-      <c r="D9" s="108" t="s">
+      <c r="D9" s="86" t="s">
         <v>663</v>
       </c>
-      <c r="E9" s="108" t="s">
+      <c r="E9" s="86" t="s">
         <v>664</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>525</v>
       </c>
-      <c r="B10" t="s">
-        <v>422</v>
+      <c r="B10" s="86" t="s">
+        <v>677</v>
       </c>
       <c r="C10" t="s">
         <v>667</v>
       </c>
-      <c r="D10" s="108" t="s">
+      <c r="D10" s="86" t="s">
         <v>666</v>
       </c>
-      <c r="E10" s="108" t="s">
+      <c r="E10" s="86" t="s">
         <v>668</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>525</v>
       </c>
-      <c r="B11" s="108" t="s">
+      <c r="B11" s="86" t="s">
         <v>675</v>
       </c>
       <c r="C11" t="s">
         <v>670</v>
       </c>
-      <c r="D11" s="108" t="s">
+      <c r="D11" s="86" t="s">
         <v>669</v>
       </c>
-      <c r="E11" s="108" t="s">
+      <c r="E11" s="86" t="s">
         <v>671</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>525</v>
       </c>
+      <c r="B12" s="86" t="s">
+        <v>676</v>
+      </c>
       <c r="C12" t="s">
         <v>673</v>
       </c>
-      <c r="D12" s="108" t="s">
+      <c r="D12" s="86" t="s">
         <v>672</v>
       </c>
-      <c r="E12" s="108" t="s">
+      <c r="E12" s="86" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="39" spans="3:3">
-      <c r="C39" s="107"/>
-    </row>
-    <row r="40" spans="3:3">
-      <c r="C40" s="107"/>
-    </row>
-    <row r="41" spans="3:3">
-      <c r="C41" s="107"/>
-    </row>
-    <row r="42" spans="3:3">
-      <c r="C42" s="107"/>
-    </row>
-    <row r="43" spans="3:3">
-      <c r="C43" s="107"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -5801,16 +5811,26 @@
     <hyperlink ref="D12" r:id="rId21" xr:uid="{C3BCEC62-1D50-4E96-8B88-F958C554A1CA}"/>
     <hyperlink ref="E12" r:id="rId22" xr:uid="{0767262B-1C7A-4CB5-9F51-0BE6DEA46404}"/>
     <hyperlink ref="B11" r:id="rId23" xr:uid="{D9DCBBB1-C4D4-4F20-9427-B0D2AF112CD3}"/>
+    <hyperlink ref="B12" r:id="rId24" xr:uid="{FC46B876-DFFD-4E53-A957-3D2BC8815FA3}"/>
+    <hyperlink ref="B10" r:id="rId25" xr:uid="{926C3E00-DCD6-4310-9B50-91AE34BCCA6C}"/>
+    <hyperlink ref="B9" r:id="rId26" xr:uid="{486130FA-C5B7-413F-8938-0DBB26405C6E}"/>
+    <hyperlink ref="B8" r:id="rId27" xr:uid="{705B0842-49E5-4954-8D20-562430076B56}"/>
+    <hyperlink ref="B7" r:id="rId28" xr:uid="{FA68651C-31D4-4BFB-9BF3-531BF1B82EB0}"/>
+    <hyperlink ref="B6" r:id="rId29" xr:uid="{A524D317-9A0F-499E-8A97-BF4270B8E034}"/>
+    <hyperlink ref="B5" r:id="rId30" xr:uid="{224835A2-87B9-484B-8C86-0648F793FEB9}"/>
+    <hyperlink ref="B4" r:id="rId31" xr:uid="{1EE65E01-F51A-4442-B856-39E408288117}"/>
+    <hyperlink ref="B3" r:id="rId32" xr:uid="{572E5994-4E82-45C2-8C57-C227E8278590}"/>
+    <hyperlink ref="B2" r:id="rId33" xr:uid="{E21B452D-72F9-4ECE-B18B-D5EB5E3AE775}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId24"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId34"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{866E9A5E-386D-439E-AA25-CB46A31C625C}">
   <dimension ref="A1:Z50"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.453125" style="77" customWidth="1"/>
     <col min="2" max="2" width="24.7265625" customWidth="1"/>
@@ -5821,7 +5841,7 @@
     <col min="25" max="25" width="26.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="36.5" customHeight="1">
+    <row r="1" spans="1:25" ht="36.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="76" t="s">
         <v>392</v>
       </c>
@@ -5834,13 +5854,13 @@
       <c r="D1" s="72" t="s">
         <v>395</v>
       </c>
-      <c r="W1" s="104" t="s">
+      <c r="W1" s="105" t="s">
         <v>405</v>
       </c>
-      <c r="X1" s="104"/>
-      <c r="Y1" s="104"/>
-    </row>
-    <row r="2" spans="1:25" ht="15.5">
+      <c r="X1" s="105"/>
+      <c r="Y1" s="105"/>
+    </row>
+    <row r="2" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="77" t="s">
         <v>404</v>
       </c>
@@ -5857,7 +5877,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3" s="77" t="s">
         <v>383</v>
       </c>
@@ -5877,7 +5897,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4" s="77" t="s">
         <v>398</v>
       </c>
@@ -5897,7 +5917,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5" s="85" t="s">
         <v>603</v>
       </c>
@@ -5917,7 +5937,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
       <c r="C6" s="73" t="s">
         <v>379</v>
       </c>
@@ -5931,7 +5951,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
       <c r="C7" s="73" t="s">
         <v>380</v>
       </c>
@@ -5945,7 +5965,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
       <c r="C8" s="73" t="s">
         <v>381</v>
       </c>
@@ -5959,7 +5979,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
       <c r="C9" s="73" t="s">
         <v>382</v>
       </c>
@@ -5973,7 +5993,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="15.5">
+    <row r="10" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C10" s="84" t="s">
         <v>555</v>
       </c>
@@ -5984,7 +6004,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
       <c r="C11" s="73" t="s">
         <v>378</v>
       </c>
@@ -5998,7 +6018,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
       <c r="C12" s="73" t="s">
         <v>565</v>
       </c>
@@ -6012,7 +6032,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
       <c r="C13" s="84" t="s">
         <v>567</v>
       </c>
@@ -6026,7 +6046,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="14" spans="1:25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
       <c r="C14" s="85" t="s">
         <v>603</v>
       </c>
@@ -6040,7 +6060,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="15" spans="1:25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
       <c r="X15" s="79" t="s">
         <v>417</v>
       </c>
@@ -6048,7 +6068,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="16" spans="1:25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
       <c r="X16" s="79" t="s">
         <v>418</v>
       </c>
@@ -6056,7 +6076,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="17" spans="24:25">
+    <row r="17" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X17" s="79" t="s">
         <v>419</v>
       </c>
@@ -6064,7 +6084,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="18" spans="24:25">
+    <row r="18" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X18" s="79" t="s">
         <v>420</v>
       </c>
@@ -6072,7 +6092,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="19" spans="24:25">
+    <row r="19" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X19" s="79" t="s">
         <v>421</v>
       </c>
@@ -6080,7 +6100,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="20" spans="24:25">
+    <row r="20" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X20" s="79" t="s">
         <v>422</v>
       </c>
@@ -6088,7 +6108,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="21" spans="24:25">
+    <row r="21" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X21" s="79" t="s">
         <v>423</v>
       </c>
@@ -6096,7 +6116,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="22" spans="24:25">
+    <row r="22" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X22" s="79" t="s">
         <v>424</v>
       </c>
@@ -6104,7 +6124,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="23" spans="24:25">
+    <row r="23" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X23" s="79" t="s">
         <v>425</v>
       </c>
@@ -6112,7 +6132,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="24" spans="24:25">
+    <row r="24" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X24" s="79" t="s">
         <v>426</v>
       </c>
@@ -6120,7 +6140,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="25" spans="24:25">
+    <row r="25" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X25" s="79" t="s">
         <v>427</v>
       </c>
@@ -6128,7 +6148,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="26" spans="24:25">
+    <row r="26" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X26" s="79" t="s">
         <v>428</v>
       </c>
@@ -6136,7 +6156,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="27" spans="24:25">
+    <row r="27" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X27" s="79" t="s">
         <v>429</v>
       </c>
@@ -6144,7 +6164,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="28" spans="24:25">
+    <row r="28" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X28" s="79" t="s">
         <v>430</v>
       </c>
@@ -6152,7 +6172,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="29" spans="24:25">
+    <row r="29" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X29" s="79" t="s">
         <v>431</v>
       </c>
@@ -6160,7 +6180,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="30" spans="24:25">
+    <row r="30" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X30" s="79" t="s">
         <v>432</v>
       </c>
@@ -6168,7 +6188,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="31" spans="24:25">
+    <row r="31" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X31" s="79" t="s">
         <v>433</v>
       </c>
@@ -6176,7 +6196,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="32" spans="24:25">
+    <row r="32" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X32" s="79" t="s">
         <v>484</v>
       </c>
@@ -6184,7 +6204,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="33" spans="23:26">
+    <row r="33" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X33" s="79" t="s">
         <v>485</v>
       </c>
@@ -6192,7 +6212,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="34" spans="23:26">
+    <row r="34" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X34" s="79" t="s">
         <v>486</v>
       </c>
@@ -6200,7 +6220,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="35" spans="23:26">
+    <row r="35" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X35" s="79" t="s">
         <v>487</v>
       </c>
@@ -6208,7 +6228,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="36" spans="23:26">
+    <row r="36" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X36" s="79" t="s">
         <v>516</v>
       </c>
@@ -6216,12 +6236,12 @@
         <v>517</v>
       </c>
     </row>
-    <row r="38" spans="23:26" ht="15.5">
+    <row r="38" spans="23:26" ht="15.5" x14ac:dyDescent="0.35">
       <c r="W38" s="81" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="39" spans="23:26">
+    <row r="39" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X39" s="79" t="s">
         <v>434</v>
       </c>
@@ -6229,7 +6249,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="40" spans="23:26">
+    <row r="40" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X40" s="79" t="s">
         <v>435</v>
       </c>
@@ -6238,7 +6258,7 @@
       </c>
       <c r="Z40" s="79"/>
     </row>
-    <row r="41" spans="23:26">
+    <row r="41" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X41" s="79" t="s">
         <v>436</v>
       </c>
@@ -6247,7 +6267,7 @@
       </c>
       <c r="Z41" s="79"/>
     </row>
-    <row r="42" spans="23:26">
+    <row r="42" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X42" s="79" t="s">
         <v>437</v>
       </c>
@@ -6256,7 +6276,7 @@
       </c>
       <c r="Z42" s="79"/>
     </row>
-    <row r="43" spans="23:26">
+    <row r="43" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X43" s="79" t="s">
         <v>438</v>
       </c>
@@ -6265,14 +6285,14 @@
       </c>
       <c r="Z43" s="79"/>
     </row>
-    <row r="44" spans="23:26" ht="15.5">
+    <row r="44" spans="23:26" ht="15.5" x14ac:dyDescent="0.35">
       <c r="W44" s="81" t="s">
         <v>402</v>
       </c>
       <c r="X44" s="80"/>
       <c r="Z44" s="79"/>
     </row>
-    <row r="45" spans="23:26" ht="15.5">
+    <row r="45" spans="23:26" ht="15.5" x14ac:dyDescent="0.35">
       <c r="X45" s="79" t="s">
         <v>439</v>
       </c>
@@ -6281,7 +6301,7 @@
       </c>
       <c r="Z45" s="80"/>
     </row>
-    <row r="46" spans="23:26">
+    <row r="46" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X46" s="79" t="s">
         <v>440</v>
       </c>
@@ -6290,7 +6310,7 @@
       </c>
       <c r="Z46" s="79"/>
     </row>
-    <row r="47" spans="23:26">
+    <row r="47" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X47" s="79" t="s">
         <v>441</v>
       </c>
@@ -6299,7 +6319,7 @@
       </c>
       <c r="Z47" s="79"/>
     </row>
-    <row r="48" spans="23:26">
+    <row r="48" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X48" s="79" t="s">
         <v>442</v>
       </c>
@@ -6308,7 +6328,7 @@
       </c>
       <c r="Z48" s="79"/>
     </row>
-    <row r="49" spans="15:25">
+    <row r="49" spans="15:25" x14ac:dyDescent="0.35">
       <c r="O49" s="79"/>
       <c r="X49" s="79" t="s">
         <v>443</v>
@@ -6317,7 +6337,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="50" spans="15:25">
+    <row r="50" spans="15:25" x14ac:dyDescent="0.35">
       <c r="O50" s="79"/>
       <c r="X50" s="79" t="s">
         <v>441</v>
@@ -6339,7 +6359,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4C14141-45DA-4C30-845C-3E630B347F10}">
   <dimension ref="A1:F51"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.54296875" style="41" customWidth="1"/>
     <col min="2" max="2" width="38.26953125" customWidth="1"/>
@@ -6348,7 +6368,7 @@
     <col min="6" max="6" width="6.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="32" t="s">
         <v>7</v>
       </c>
@@ -6368,7 +6388,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="35">
         <v>1</v>
       </c>
@@ -6388,7 +6408,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="38">
         <v>2</v>
       </c>
@@ -6408,7 +6428,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="35">
         <v>3</v>
       </c>
@@ -6428,7 +6448,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="38">
         <v>4</v>
       </c>
@@ -6448,7 +6468,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="35">
         <v>5</v>
       </c>
@@ -6468,7 +6488,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="38">
         <v>6</v>
       </c>
@@ -6488,7 +6508,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="35">
         <v>7</v>
       </c>
@@ -6508,7 +6528,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="38">
         <v>8</v>
       </c>
@@ -6528,7 +6548,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="35">
         <v>9</v>
       </c>
@@ -6548,7 +6568,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="38">
         <v>10</v>
       </c>
@@ -6568,7 +6588,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="35">
         <v>11</v>
       </c>
@@ -6588,7 +6608,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="38">
         <v>12</v>
       </c>
@@ -6608,7 +6628,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="35">
         <v>13</v>
       </c>
@@ -6628,7 +6648,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="38">
         <v>14</v>
       </c>
@@ -6648,7 +6668,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="35">
         <v>15</v>
       </c>
@@ -6668,7 +6688,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="38">
         <v>16</v>
       </c>
@@ -6688,7 +6708,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="35">
         <v>17</v>
       </c>
@@ -6708,7 +6728,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="38">
         <v>18</v>
       </c>
@@ -6728,7 +6748,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="35">
         <v>19</v>
       </c>
@@ -6748,7 +6768,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="38">
         <v>20</v>
       </c>
@@ -6768,7 +6788,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="35">
         <v>21</v>
       </c>
@@ -6788,7 +6808,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="38">
         <v>22</v>
       </c>
@@ -6808,7 +6828,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="35">
         <v>23</v>
       </c>
@@ -6828,7 +6848,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="38">
         <v>24</v>
       </c>
@@ -6848,7 +6868,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="35">
         <v>25</v>
       </c>
@@ -6868,7 +6888,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="38">
         <v>26</v>
       </c>
@@ -6888,7 +6908,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="35">
         <v>27</v>
       </c>
@@ -6908,7 +6928,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="38">
         <v>28</v>
       </c>
@@ -6928,7 +6948,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="35">
         <v>29</v>
       </c>
@@ -6948,7 +6968,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="38">
         <v>30</v>
       </c>
@@ -6968,7 +6988,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="35">
         <v>31</v>
       </c>
@@ -6988,7 +7008,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="38">
         <v>32</v>
       </c>
@@ -7008,7 +7028,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="38">
         <v>33</v>
       </c>
@@ -7028,7 +7048,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="35">
         <v>34</v>
       </c>
@@ -7048,7 +7068,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="35">
         <v>35</v>
       </c>
@@ -7068,7 +7088,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="35">
         <v>36</v>
       </c>
@@ -7088,7 +7108,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="35">
         <v>37</v>
       </c>
@@ -7108,7 +7128,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="35">
         <v>38</v>
       </c>
@@ -7128,7 +7148,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="35">
         <v>39</v>
       </c>
@@ -7148,7 +7168,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="35">
         <v>40</v>
       </c>
@@ -7168,7 +7188,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="35">
         <v>41</v>
       </c>
@@ -7188,7 +7208,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="35">
         <v>42</v>
       </c>
@@ -7208,7 +7228,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="38">
         <v>43</v>
       </c>
@@ -7228,7 +7248,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="38">
         <v>44</v>
       </c>
@@ -7248,7 +7268,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="35">
         <v>45</v>
       </c>
@@ -7268,7 +7288,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="35">
         <v>46</v>
       </c>
@@ -7288,7 +7308,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="35">
         <v>47</v>
       </c>
@@ -7308,7 +7328,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="35">
         <v>48</v>
       </c>
@@ -7328,7 +7348,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="35">
         <v>49</v>
       </c>
@@ -7348,7 +7368,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="70">
         <v>50</v>
       </c>
@@ -7379,14 +7399,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8049D8E-7482-48AF-95C9-7F1B728B0DDE}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.90625" customWidth="1"/>
     <col min="2" max="2" width="57.1796875" customWidth="1"/>
     <col min="3" max="3" width="60.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" thickBot="1">
+    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="51" t="s">
         <v>303</v>
       </c>
@@ -7397,7 +7417,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15" thickTop="1">
+    <row r="2" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="A2" s="54">
         <v>1</v>
       </c>
@@ -7408,7 +7428,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="54">
         <v>2</v>
       </c>
@@ -7419,7 +7439,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="58">
         <v>3</v>
       </c>
@@ -7430,7 +7450,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="58">
         <v>4</v>
       </c>
@@ -7441,7 +7461,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="58">
         <v>5</v>
       </c>
@@ -7452,7 +7472,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="58">
         <v>6</v>
       </c>
@@ -7463,7 +7483,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="58">
         <v>7</v>
       </c>
@@ -7474,7 +7494,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="58">
         <v>8</v>
       </c>
@@ -7485,7 +7505,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="58">
         <v>9</v>
       </c>
@@ -7496,7 +7516,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="29">
+    <row r="11" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="58">
         <v>10</v>
       </c>
@@ -7507,7 +7527,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="50">
         <v>11</v>
       </c>
@@ -7518,7 +7538,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="58">
         <v>12</v>
       </c>
@@ -7529,7 +7549,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="50">
         <v>13</v>
       </c>
@@ -7540,12 +7560,12 @@
         <v>359</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="50"/>
       <c r="B15" s="62"/>
       <c r="C15" s="61"/>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="50"/>
       <c r="B16" s="63"/>
       <c r="C16" s="61"/>
@@ -7577,7 +7597,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF1BA8E2-9FD2-4C47-B5D3-EF9907B8F692}">
   <dimension ref="A1:D52"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.54296875" style="41" customWidth="1"/>
     <col min="2" max="2" width="38.26953125" customWidth="1"/>
@@ -7585,7 +7605,7 @@
     <col min="4" max="4" width="13.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="32" t="s">
         <v>299</v>
       </c>
@@ -7599,7 +7619,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="35">
         <v>1</v>
       </c>
@@ -7611,7 +7631,7 @@
       </c>
       <c r="D2" s="43"/>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="38">
         <v>2</v>
       </c>
@@ -7625,7 +7645,7 @@
         <v>1944</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="35">
         <v>3</v>
       </c>
@@ -7637,7 +7657,7 @@
       </c>
       <c r="D4" s="43"/>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="38">
         <v>4</v>
       </c>
@@ -7649,7 +7669,7 @@
       </c>
       <c r="D5" s="43"/>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="35">
         <v>5</v>
       </c>
@@ -7663,7 +7683,7 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="38">
         <v>6</v>
       </c>
@@ -7675,7 +7695,7 @@
       </c>
       <c r="D7" s="43"/>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="35">
         <v>7</v>
       </c>
@@ -7687,7 +7707,7 @@
       </c>
       <c r="D8" s="43"/>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="38">
         <v>8</v>
       </c>
@@ -7699,7 +7719,7 @@
       </c>
       <c r="D9" s="43"/>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="35">
         <v>9</v>
       </c>
@@ -7713,7 +7733,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="38">
         <v>10</v>
       </c>
@@ -7725,7 +7745,7 @@
       </c>
       <c r="D11" s="43"/>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="35">
         <v>11</v>
       </c>
@@ -7739,7 +7759,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="38">
         <v>12</v>
       </c>
@@ -7753,7 +7773,7 @@
         <v>1879</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="35">
         <v>13</v>
       </c>
@@ -7765,7 +7785,7 @@
       </c>
       <c r="D14" s="44"/>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="38">
         <v>14</v>
       </c>
@@ -7779,7 +7799,7 @@
         <v>1887</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="35">
         <v>15</v>
       </c>
@@ -7793,7 +7813,7 @@
         <v>1953</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="38">
         <v>16</v>
       </c>
@@ -7805,7 +7825,7 @@
       </c>
       <c r="D17" s="44"/>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="35">
         <v>17</v>
       </c>
@@ -7817,7 +7837,7 @@
       </c>
       <c r="D18" s="44"/>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="38">
         <v>18</v>
       </c>
@@ -7831,7 +7851,7 @@
         <v>1882</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="35">
         <v>19</v>
       </c>
@@ -7843,7 +7863,7 @@
       </c>
       <c r="D20" s="43"/>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="38">
         <v>20</v>
       </c>
@@ -7855,7 +7875,7 @@
       </c>
       <c r="D21" s="43"/>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" s="35">
         <v>21</v>
       </c>
@@ -7867,7 +7887,7 @@
       </c>
       <c r="D22" s="43"/>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="38">
         <v>22</v>
       </c>
@@ -7879,7 +7899,7 @@
       </c>
       <c r="D23" s="43"/>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="35">
         <v>23</v>
       </c>
@@ -7891,7 +7911,7 @@
       </c>
       <c r="D24" s="43"/>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" s="38">
         <v>24</v>
       </c>
@@ -7903,7 +7923,7 @@
       </c>
       <c r="D25" s="43"/>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" s="35">
         <v>25</v>
       </c>
@@ -7915,7 +7935,7 @@
       </c>
       <c r="D26" s="44"/>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" s="38">
         <v>26</v>
       </c>
@@ -7927,7 +7947,7 @@
       </c>
       <c r="D27" s="43"/>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" s="35">
         <v>27</v>
       </c>
@@ -7941,7 +7961,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" s="38">
         <v>28</v>
       </c>
@@ -7953,7 +7973,7 @@
       </c>
       <c r="D29" s="43"/>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" s="35">
         <v>29</v>
       </c>
@@ -7965,7 +7985,7 @@
       </c>
       <c r="D30" s="43"/>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" s="38">
         <v>30</v>
       </c>
@@ -7977,7 +7997,7 @@
       </c>
       <c r="D31" s="44"/>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" s="35">
         <v>31</v>
       </c>
@@ -7989,7 +8009,7 @@
       </c>
       <c r="D32" s="44"/>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" s="38">
         <v>32</v>
       </c>
@@ -8001,7 +8021,7 @@
       </c>
       <c r="D33" s="43"/>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="38">
         <v>33</v>
       </c>
@@ -8015,7 +8035,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" s="35">
         <v>34</v>
       </c>
@@ -8027,7 +8047,7 @@
       </c>
       <c r="D35" s="44"/>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="35">
         <v>35</v>
       </c>
@@ -8039,7 +8059,7 @@
       </c>
       <c r="D36" s="43"/>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="35">
         <v>36</v>
       </c>
@@ -8051,7 +8071,7 @@
       </c>
       <c r="D37" s="43"/>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="35">
         <v>37</v>
       </c>
@@ -8063,7 +8083,7 @@
       </c>
       <c r="D38" s="44"/>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" s="35">
         <v>38</v>
       </c>
@@ -8075,7 +8095,7 @@
       </c>
       <c r="D39" s="44"/>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" s="35">
         <v>39</v>
       </c>
@@ -8087,7 +8107,7 @@
       </c>
       <c r="D40" s="43"/>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" s="35">
         <v>40</v>
       </c>
@@ -8101,7 +8121,7 @@
         <v>1869</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" s="35">
         <v>41</v>
       </c>
@@ -8113,7 +8133,7 @@
       </c>
       <c r="D42" s="43"/>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" s="35">
         <v>42</v>
       </c>
@@ -8127,7 +8147,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" s="38">
         <v>43</v>
       </c>
@@ -8141,7 +8161,7 @@
         <v>1895</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" s="38">
         <v>44</v>
       </c>
@@ -8155,7 +8175,7 @@
         <v>1902</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" s="38">
         <v>44</v>
       </c>
@@ -8167,7 +8187,7 @@
       </c>
       <c r="D46" s="43"/>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" s="35">
         <v>45</v>
       </c>
@@ -8179,7 +8199,7 @@
       </c>
       <c r="D47" s="43"/>
     </row>
-    <row r="48" spans="1:4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" s="35">
         <v>46</v>
       </c>
@@ -8191,7 +8211,7 @@
       </c>
       <c r="D48" s="43"/>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" s="35">
         <v>47</v>
       </c>
@@ -8203,7 +8223,7 @@
       </c>
       <c r="D49" s="43"/>
     </row>
-    <row r="50" spans="1:4">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" s="38">
         <v>48</v>
       </c>
@@ -8215,7 +8235,7 @@
       </c>
       <c r="D50" s="43"/>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" s="35">
         <v>49</v>
       </c>
@@ -8229,7 +8249,7 @@
         <v>1876</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" s="38">
         <v>50</v>
       </c>
@@ -8253,7 +8273,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0041FEF0-BF6F-4667-AFBD-1C23A1866795}">
   <dimension ref="A1:D7"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.7265625" customWidth="1"/>
     <col min="2" max="2" width="17.453125" customWidth="1"/>
@@ -8261,7 +8281,7 @@
     <col min="4" max="4" width="37.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.5">
+    <row r="1" spans="1:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>26</v>
       </c>
@@ -8275,7 +8295,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="9">
         <v>1</v>
       </c>
@@ -8289,7 +8309,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="9">
         <v>2</v>
       </c>
@@ -8303,7 +8323,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="9">
         <v>3</v>
       </c>
@@ -8317,7 +8337,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="9">
         <v>4</v>
       </c>
@@ -8331,7 +8351,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="9">
         <v>5</v>
       </c>
@@ -8345,7 +8365,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="9">
         <v>6</v>
       </c>

--- a/Info/Additional_information.xlsx
+++ b/Info/Additional_information.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D074E7B7-19EA-4AD0-A25D-B42283A78632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFD6B733-983E-4BAA-A817-285C0CCC8ADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,6 +27,7 @@
     <sheet name="Library_Link" sheetId="13" r:id="rId12"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">albums_buttons!$A$1:$E$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">albums_ID!$A$1:$F$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Colours_specifications!$A$1:$D$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'EURO albums content'!$A$1:$C$15</definedName>
@@ -78,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="686">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="742">
   <si>
     <t>good quality (UNC for UNC collection; UNC and XF for XF collection)</t>
   </si>
@@ -2137,6 +2138,174 @@
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/4/41/Flag_of_Austria.svg</t>
+  </si>
+  <si>
+    <t>Юбилейные 2 ЕВРО Монако / Monaco</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Monaco/%23EURO%23Monaco%23Commemorative%23%5B2007-present%5D%23UNC.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Monaco/</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/e/ea/Flag_of_Monaco.svg</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/2/2f/Flag_of_the_United_Nations.svg</t>
+  </si>
+  <si>
+    <t>Дубли монет мира (вне конкретной коллеции)</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/Foreign_various/Foreighn_duplicates.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/Foreign_various/</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Germany/%23EURO%23Germany%23Commemorative%23%5B2006-present%5D%23UNC.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Germany/</t>
+  </si>
+  <si>
+    <t>Германия / Germany</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/b/ba/Flag_of_Germany.svg</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Luxembourg/%23EURO%23Luxembourg%23Commemorative%23%5B2004-present%5D%23UNC.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Luxembourg/</t>
+  </si>
+  <si>
+    <t>Люксембург / Luxembourg</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/d/da/Flag_of_Luxembourg.svg</t>
+  </si>
+  <si>
+    <t>Мальта / Malta</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Malta/%23EURO%23Malta%23Commemorative%23%5B2009-present%5D%23UNC.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Malta/</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/7/73/Flag_of_Malta.svg</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/1/19/Flag_of_Andorra.svg</t>
+  </si>
+  <si>
+    <t>Андорра / Andorra</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Andorra/%23EURO%23Andorra%23Commemorative%23%5B2014-present%5D%23UNC.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Andorra/</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/San_Marino/%23EURO%23San_Marino%23Commemorative%23%5B2004-present%5D%23UNC.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/San_Marino/</t>
+  </si>
+  <si>
+    <t>Сан-Марино / San Marino</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/b/b1/Flag_of_San_Marino.svg</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/b/b3/Flag_of_Vatican_City_%282023%E2%80%93present%29.svg</t>
+  </si>
+  <si>
+    <t>Ватикан / Vatican City</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Vatican_city/%23EURO%23Vatican_city%23Commemorative%23%5B2004-present%5D%23UNC.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Vatican_city/</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Finland/%23EURO%23Finland%23Commemorative%23%5B2004-present%5D%23UNC.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Finland/</t>
+  </si>
+  <si>
+    <t>Финляндия / Finland</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/b/bc/Flag_of_Finland.svg</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Spain/%23EURO%23Spain%23Commemorative%23%5B2005-present%5D%23UNC.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Spain/</t>
+  </si>
+  <si>
+    <t>Испания / Spain</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/9/9a/Flag_of_Spain.svg</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Slovenia/%23EURO%23Slovenia%23Commemorative%23%5B2007-present%5D%23UNC.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Slovenia/</t>
+  </si>
+  <si>
+    <t>Словения / Slovenia</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/f/f0/Flag_of_Slovenia.svg</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Slovakia/%23EURO%23Slovakia%23Commemorative%23%5B2009-present%5D%23UNC.xlsx</t>
+  </si>
+  <si>
+    <t>Словакия / Slovakia</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Slovakia/</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/e/e6/Flag_of_Slovakia.svg</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Croatia/%23EURO%23Croatia%23Commemorative%23%5B2023-present%5D%23UNC.xlsx</t>
+  </si>
+  <si>
+    <t>Хорватия / Croatia</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Croatia/</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/1/1b/Flag_of_Croatia.svg</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Greece/%23EURO%23Greece%23Commemorative%23%5B2004-present%5D%23UNC.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Greece/</t>
+  </si>
+  <si>
+    <t>Греция / Greece</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/5/5c/Flag_of_Greece.svg</t>
   </si>
 </sst>
 </file>
@@ -5571,12 +5740,12 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C94A307-2E39-40B9-B204-C92675C0AF71}">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.36328125" customWidth="1"/>
-    <col min="2" max="2" width="54.7265625" customWidth="1"/>
-    <col min="3" max="3" width="27.36328125" customWidth="1"/>
+    <col min="2" max="2" width="57.54296875" customWidth="1"/>
+    <col min="3" max="3" width="34.81640625" customWidth="1"/>
     <col min="4" max="4" width="151" customWidth="1"/>
     <col min="5" max="5" width="79.54296875" customWidth="1"/>
     <col min="6" max="6" width="62" customWidth="1"/>
@@ -5601,36 +5770,36 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B2" s="86" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="C2" t="s">
-        <v>644</v>
+        <v>686</v>
       </c>
       <c r="D2" s="86" t="s">
-        <v>642</v>
+        <v>687</v>
       </c>
       <c r="E2" s="86" t="s">
-        <v>643</v>
+        <v>688</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B3" s="86" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="C3" t="s">
-        <v>646</v>
+        <v>691</v>
       </c>
       <c r="D3" s="86" t="s">
-        <v>645</v>
+        <v>692</v>
       </c>
       <c r="E3" s="86" t="s">
-        <v>647</v>
+        <v>693</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -5638,16 +5807,16 @@
         <v>525</v>
       </c>
       <c r="B4" s="86" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="C4" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="D4" s="86" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="E4" s="86" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -5655,16 +5824,16 @@
         <v>525</v>
       </c>
       <c r="B5" s="86" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C5" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="D5" s="86" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="E5" s="86" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -5672,16 +5841,16 @@
         <v>525</v>
       </c>
       <c r="B6" s="86" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="C6" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="D6" s="86" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="E6" s="86" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -5689,16 +5858,16 @@
         <v>525</v>
       </c>
       <c r="B7" s="86" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="C7" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="D7" s="86" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="E7" s="86" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -5706,16 +5875,16 @@
         <v>525</v>
       </c>
       <c r="B8" s="86" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="C8" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="D8" s="86" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="E8" s="86" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -5723,16 +5892,16 @@
         <v>525</v>
       </c>
       <c r="B9" s="86" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="C9" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="D9" s="86" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="E9" s="86" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -5740,16 +5909,16 @@
         <v>525</v>
       </c>
       <c r="B10" s="86" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="C10" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
       <c r="D10" s="86" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="E10" s="86" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -5757,16 +5926,16 @@
         <v>525</v>
       </c>
       <c r="B11" s="86" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="C11" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="D11" s="86" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="E11" s="86" t="s">
-        <v>671</v>
+        <v>664</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -5774,56 +5943,337 @@
         <v>525</v>
       </c>
       <c r="B12" s="86" t="s">
+        <v>677</v>
+      </c>
+      <c r="C12" t="s">
+        <v>667</v>
+      </c>
+      <c r="D12" s="86" t="s">
+        <v>666</v>
+      </c>
+      <c r="E12" s="86" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>525</v>
+      </c>
+      <c r="B13" s="86" t="s">
+        <v>675</v>
+      </c>
+      <c r="C13" t="s">
+        <v>670</v>
+      </c>
+      <c r="D13" s="86" t="s">
+        <v>669</v>
+      </c>
+      <c r="E13" s="86" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>525</v>
+      </c>
+      <c r="B14" s="86" t="s">
         <v>676</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C14" t="s">
         <v>673</v>
       </c>
-      <c r="D12" s="86" t="s">
+      <c r="D14" s="86" t="s">
         <v>672</v>
       </c>
-      <c r="E12" s="86" t="s">
+      <c r="E14" s="86" t="s">
         <v>674</v>
       </c>
     </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>531</v>
+      </c>
+      <c r="B15" s="86" t="s">
+        <v>697</v>
+      </c>
+      <c r="C15" t="s">
+        <v>696</v>
+      </c>
+      <c r="D15" s="86" t="s">
+        <v>694</v>
+      </c>
+      <c r="E15" s="86" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>531</v>
+      </c>
+      <c r="B16" s="86" t="s">
+        <v>701</v>
+      </c>
+      <c r="C16" t="s">
+        <v>700</v>
+      </c>
+      <c r="D16" s="86" t="s">
+        <v>698</v>
+      </c>
+      <c r="E16" s="86" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>531</v>
+      </c>
+      <c r="B17" s="86" t="s">
+        <v>705</v>
+      </c>
+      <c r="C17" t="s">
+        <v>702</v>
+      </c>
+      <c r="D17" s="86" t="s">
+        <v>703</v>
+      </c>
+      <c r="E17" s="86" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>522</v>
+      </c>
+      <c r="B18" s="86" t="s">
+        <v>706</v>
+      </c>
+      <c r="C18" t="s">
+        <v>707</v>
+      </c>
+      <c r="D18" s="86" t="s">
+        <v>708</v>
+      </c>
+      <c r="E18" s="86" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>522</v>
+      </c>
+      <c r="B19" s="86" t="s">
+        <v>713</v>
+      </c>
+      <c r="C19" t="s">
+        <v>712</v>
+      </c>
+      <c r="D19" s="86" t="s">
+        <v>710</v>
+      </c>
+      <c r="E19" s="86" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>522</v>
+      </c>
+      <c r="B20" s="86" t="s">
+        <v>714</v>
+      </c>
+      <c r="C20" t="s">
+        <v>715</v>
+      </c>
+      <c r="D20" s="86" t="s">
+        <v>716</v>
+      </c>
+      <c r="E20" s="86" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>530</v>
+      </c>
+      <c r="B21" s="86" t="s">
+        <v>721</v>
+      </c>
+      <c r="C21" t="s">
+        <v>720</v>
+      </c>
+      <c r="D21" s="86" t="s">
+        <v>718</v>
+      </c>
+      <c r="E21" s="86" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>530</v>
+      </c>
+      <c r="B22" s="86" t="s">
+        <v>725</v>
+      </c>
+      <c r="C22" t="s">
+        <v>724</v>
+      </c>
+      <c r="D22" s="86" t="s">
+        <v>722</v>
+      </c>
+      <c r="E22" s="86" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>530</v>
+      </c>
+      <c r="B23" s="86" t="s">
+        <v>729</v>
+      </c>
+      <c r="C23" t="s">
+        <v>728</v>
+      </c>
+      <c r="D23" s="86" t="s">
+        <v>726</v>
+      </c>
+      <c r="E23" s="86" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>530</v>
+      </c>
+      <c r="B24" s="86" t="s">
+        <v>733</v>
+      </c>
+      <c r="C24" t="s">
+        <v>731</v>
+      </c>
+      <c r="D24" s="86" t="s">
+        <v>730</v>
+      </c>
+      <c r="E24" s="86" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>530</v>
+      </c>
+      <c r="B25" s="86" t="s">
+        <v>737</v>
+      </c>
+      <c r="C25" t="s">
+        <v>735</v>
+      </c>
+      <c r="D25" s="86" t="s">
+        <v>734</v>
+      </c>
+      <c r="E25" s="86" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>530</v>
+      </c>
+      <c r="B26" s="86" t="s">
+        <v>741</v>
+      </c>
+      <c r="C26" t="s">
+        <v>740</v>
+      </c>
+      <c r="D26" s="86" t="s">
+        <v>738</v>
+      </c>
+      <c r="E26" s="86" t="s">
+        <v>739</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:E1" xr:uid="{9C94A307-2E39-40B9-B204-C92675C0AF71}"/>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{F43C89B6-D718-4498-AEF4-6F42227C5856}"/>
-    <hyperlink ref="E2" r:id="rId2" xr:uid="{76242B5D-84A5-47A1-B07F-4BA0D50A8014}"/>
-    <hyperlink ref="D3" r:id="rId3" xr:uid="{58B70BA2-33AC-4FA7-9AFF-DFD0B73ADEF0}"/>
-    <hyperlink ref="E3" r:id="rId4" xr:uid="{49C7B78D-C192-410D-8898-89F7BA109F8D}"/>
-    <hyperlink ref="D4" r:id="rId5" xr:uid="{321D7864-3399-4EAA-B153-B3813E5AA455}"/>
-    <hyperlink ref="E4" r:id="rId6" xr:uid="{D93B84B2-EEC6-458D-9CE2-C592A19A1A49}"/>
-    <hyperlink ref="D5" r:id="rId7" xr:uid="{51E99284-24FE-4D67-B556-AA834A9D4DCF}"/>
-    <hyperlink ref="E5" r:id="rId8" xr:uid="{66FF5A68-761C-4AF5-8980-4DECCA869DDC}"/>
-    <hyperlink ref="D6" r:id="rId9" xr:uid="{C74848F1-E164-4114-9460-C82CF448F63E}"/>
-    <hyperlink ref="E6" r:id="rId10" xr:uid="{B713E859-CCEE-4F0A-BCDC-262577CD73B5}"/>
-    <hyperlink ref="D7" r:id="rId11" xr:uid="{30733141-7CE7-4A95-B89E-F180DAB80B9A}"/>
-    <hyperlink ref="E7" r:id="rId12" xr:uid="{B81EC275-111B-4225-A923-336C142B9117}"/>
-    <hyperlink ref="D8" r:id="rId13" xr:uid="{08083F06-4B9D-4FED-B15C-C45FB551303A}"/>
-    <hyperlink ref="E8" r:id="rId14" xr:uid="{866928B3-9E7C-4F3E-81C5-092A1E1B038C}"/>
-    <hyperlink ref="D9" r:id="rId15" xr:uid="{FB102BAF-1980-4145-AD3E-283F0D9DAF4D}"/>
-    <hyperlink ref="E9" r:id="rId16" xr:uid="{164C3D23-0287-4BB9-B30F-5F2742E658C4}"/>
-    <hyperlink ref="D10" r:id="rId17" xr:uid="{71F06BE1-DC2D-4771-BD1B-C298E74743A7}"/>
-    <hyperlink ref="E10" r:id="rId18" xr:uid="{3BDBC051-CDF7-4AFA-9E0B-8CCC76D76447}"/>
-    <hyperlink ref="D11" r:id="rId19" xr:uid="{DB5268F6-A4BF-44FF-B0B7-F027CC14C4A7}"/>
-    <hyperlink ref="E11" r:id="rId20" xr:uid="{66913E9C-2B0E-4C62-B98A-E8AF58BA6DC1}"/>
-    <hyperlink ref="D12" r:id="rId21" xr:uid="{C3BCEC62-1D50-4E96-8B88-F958C554A1CA}"/>
-    <hyperlink ref="E12" r:id="rId22" xr:uid="{0767262B-1C7A-4CB5-9F51-0BE6DEA46404}"/>
-    <hyperlink ref="B11" r:id="rId23" xr:uid="{D9DCBBB1-C4D4-4F20-9427-B0D2AF112CD3}"/>
-    <hyperlink ref="B12" r:id="rId24" xr:uid="{FC46B876-DFFD-4E53-A957-3D2BC8815FA3}"/>
-    <hyperlink ref="B10" r:id="rId25" xr:uid="{926C3E00-DCD6-4310-9B50-91AE34BCCA6C}"/>
-    <hyperlink ref="B9" r:id="rId26" xr:uid="{486130FA-C5B7-413F-8938-0DBB26405C6E}"/>
-    <hyperlink ref="B8" r:id="rId27" xr:uid="{705B0842-49E5-4954-8D20-562430076B56}"/>
-    <hyperlink ref="B7" r:id="rId28" xr:uid="{FA68651C-31D4-4BFB-9BF3-531BF1B82EB0}"/>
-    <hyperlink ref="B6" r:id="rId29" xr:uid="{A524D317-9A0F-499E-8A97-BF4270B8E034}"/>
-    <hyperlink ref="B5" r:id="rId30" xr:uid="{224835A2-87B9-484B-8C86-0648F793FEB9}"/>
-    <hyperlink ref="B4" r:id="rId31" xr:uid="{1EE65E01-F51A-4442-B856-39E408288117}"/>
-    <hyperlink ref="B3" r:id="rId32" xr:uid="{572E5994-4E82-45C2-8C57-C227E8278590}"/>
-    <hyperlink ref="B2" r:id="rId33" xr:uid="{E21B452D-72F9-4ECE-B18B-D5EB5E3AE775}"/>
+    <hyperlink ref="D4" r:id="rId1" xr:uid="{F43C89B6-D718-4498-AEF4-6F42227C5856}"/>
+    <hyperlink ref="E4" r:id="rId2" xr:uid="{76242B5D-84A5-47A1-B07F-4BA0D50A8014}"/>
+    <hyperlink ref="D5" r:id="rId3" xr:uid="{58B70BA2-33AC-4FA7-9AFF-DFD0B73ADEF0}"/>
+    <hyperlink ref="E5" r:id="rId4" xr:uid="{49C7B78D-C192-410D-8898-89F7BA109F8D}"/>
+    <hyperlink ref="D6" r:id="rId5" xr:uid="{321D7864-3399-4EAA-B153-B3813E5AA455}"/>
+    <hyperlink ref="E6" r:id="rId6" xr:uid="{D93B84B2-EEC6-458D-9CE2-C592A19A1A49}"/>
+    <hyperlink ref="D7" r:id="rId7" xr:uid="{51E99284-24FE-4D67-B556-AA834A9D4DCF}"/>
+    <hyperlink ref="E7" r:id="rId8" xr:uid="{66FF5A68-761C-4AF5-8980-4DECCA869DDC}"/>
+    <hyperlink ref="D8" r:id="rId9" xr:uid="{C74848F1-E164-4114-9460-C82CF448F63E}"/>
+    <hyperlink ref="E8" r:id="rId10" xr:uid="{B713E859-CCEE-4F0A-BCDC-262577CD73B5}"/>
+    <hyperlink ref="D9" r:id="rId11" xr:uid="{30733141-7CE7-4A95-B89E-F180DAB80B9A}"/>
+    <hyperlink ref="E9" r:id="rId12" xr:uid="{B81EC275-111B-4225-A923-336C142B9117}"/>
+    <hyperlink ref="D10" r:id="rId13" xr:uid="{08083F06-4B9D-4FED-B15C-C45FB551303A}"/>
+    <hyperlink ref="E10" r:id="rId14" xr:uid="{866928B3-9E7C-4F3E-81C5-092A1E1B038C}"/>
+    <hyperlink ref="D11" r:id="rId15" xr:uid="{FB102BAF-1980-4145-AD3E-283F0D9DAF4D}"/>
+    <hyperlink ref="E11" r:id="rId16" xr:uid="{164C3D23-0287-4BB9-B30F-5F2742E658C4}"/>
+    <hyperlink ref="D12" r:id="rId17" xr:uid="{71F06BE1-DC2D-4771-BD1B-C298E74743A7}"/>
+    <hyperlink ref="E12" r:id="rId18" xr:uid="{3BDBC051-CDF7-4AFA-9E0B-8CCC76D76447}"/>
+    <hyperlink ref="D13" r:id="rId19" xr:uid="{DB5268F6-A4BF-44FF-B0B7-F027CC14C4A7}"/>
+    <hyperlink ref="E13" r:id="rId20" xr:uid="{66913E9C-2B0E-4C62-B98A-E8AF58BA6DC1}"/>
+    <hyperlink ref="D14" r:id="rId21" xr:uid="{C3BCEC62-1D50-4E96-8B88-F958C554A1CA}"/>
+    <hyperlink ref="E14" r:id="rId22" xr:uid="{0767262B-1C7A-4CB5-9F51-0BE6DEA46404}"/>
+    <hyperlink ref="B13" r:id="rId23" xr:uid="{D9DCBBB1-C4D4-4F20-9427-B0D2AF112CD3}"/>
+    <hyperlink ref="B14" r:id="rId24" xr:uid="{FC46B876-DFFD-4E53-A957-3D2BC8815FA3}"/>
+    <hyperlink ref="B12" r:id="rId25" xr:uid="{926C3E00-DCD6-4310-9B50-91AE34BCCA6C}"/>
+    <hyperlink ref="B11" r:id="rId26" xr:uid="{486130FA-C5B7-413F-8938-0DBB26405C6E}"/>
+    <hyperlink ref="B10" r:id="rId27" xr:uid="{705B0842-49E5-4954-8D20-562430076B56}"/>
+    <hyperlink ref="B9" r:id="rId28" xr:uid="{FA68651C-31D4-4BFB-9BF3-531BF1B82EB0}"/>
+    <hyperlink ref="B8" r:id="rId29" xr:uid="{A524D317-9A0F-499E-8A97-BF4270B8E034}"/>
+    <hyperlink ref="B7" r:id="rId30" xr:uid="{224835A2-87B9-484B-8C86-0648F793FEB9}"/>
+    <hyperlink ref="B6" r:id="rId31" xr:uid="{1EE65E01-F51A-4442-B856-39E408288117}"/>
+    <hyperlink ref="B5" r:id="rId32" xr:uid="{572E5994-4E82-45C2-8C57-C227E8278590}"/>
+    <hyperlink ref="B4" r:id="rId33" xr:uid="{E21B452D-72F9-4ECE-B18B-D5EB5E3AE775}"/>
+    <hyperlink ref="D2" r:id="rId34" xr:uid="{C122B09A-BC90-4334-B233-A677FB722C6B}"/>
+    <hyperlink ref="E2" r:id="rId35" xr:uid="{7C10BA6B-B595-474C-AB0F-4C7325F76E2E}"/>
+    <hyperlink ref="B2" r:id="rId36" xr:uid="{E5B4B3D0-0580-40C1-A82E-EEF5DB4FA3D3}"/>
+    <hyperlink ref="B3" r:id="rId37" xr:uid="{6F288D9E-9A84-4149-BF6D-81B9C56482B9}"/>
+    <hyperlink ref="D3" r:id="rId38" xr:uid="{CD9BA36B-6257-4275-B29F-9820B9E0FAAD}"/>
+    <hyperlink ref="E3" r:id="rId39" xr:uid="{22160837-5BF7-4C02-AA75-5A4DDED7483B}"/>
+    <hyperlink ref="D15" r:id="rId40" xr:uid="{08D86FCC-DC99-468B-AF88-2F35BA4CEE4E}"/>
+    <hyperlink ref="E15" r:id="rId41" xr:uid="{A3E5EEB3-E332-4D63-8644-0D8EAC0618EB}"/>
+    <hyperlink ref="B15" r:id="rId42" xr:uid="{6D3177AF-7385-43C2-8F89-C5C60DA30F33}"/>
+    <hyperlink ref="D16" r:id="rId43" xr:uid="{DAAB8CD5-2B92-4477-BFCD-855BF38B4D4C}"/>
+    <hyperlink ref="E16" r:id="rId44" xr:uid="{5CCFC139-B39A-45CE-8B4A-FE22CCA3F0C4}"/>
+    <hyperlink ref="B16" r:id="rId45" xr:uid="{4FBAE51B-635A-4CEA-8C2A-D6B78271AE81}"/>
+    <hyperlink ref="D17" r:id="rId46" xr:uid="{B5941483-D115-46A6-A7CF-2DA1234577E8}"/>
+    <hyperlink ref="E17" r:id="rId47" xr:uid="{5CD7624C-6026-4B43-8A7A-94B9E36BBE3A}"/>
+    <hyperlink ref="B17" r:id="rId48" xr:uid="{8C8DC446-9A22-4A1E-A9F4-62C22459C74D}"/>
+    <hyperlink ref="B18" r:id="rId49" xr:uid="{2654B1C8-B9CD-4908-922D-88197075D9E5}"/>
+    <hyperlink ref="D18" r:id="rId50" xr:uid="{F63F49B7-1B9B-4E8A-8292-443092CE0318}"/>
+    <hyperlink ref="E18" r:id="rId51" xr:uid="{14EBC11F-4EC8-4BE8-BDAB-66AA6AFC5030}"/>
+    <hyperlink ref="D19" r:id="rId52" xr:uid="{370EBFC6-32C9-4BF2-8CCF-13D3B5959FE8}"/>
+    <hyperlink ref="E19" r:id="rId53" xr:uid="{3846D806-F68A-4F1F-BA9C-A6C54B6755CF}"/>
+    <hyperlink ref="B19" r:id="rId54" xr:uid="{34670EEF-FEA5-4D65-9AF1-5155E84B688F}"/>
+    <hyperlink ref="B20" r:id="rId55" xr:uid="{C935F8A6-68AB-4109-B907-A4FD44D8404F}"/>
+    <hyperlink ref="D20" r:id="rId56" xr:uid="{4F1E9AF9-BD4A-4249-82A6-8A7423BF8E31}"/>
+    <hyperlink ref="E20" r:id="rId57" xr:uid="{B195B90E-E6DC-4AF8-95C6-5CD4B8C4D633}"/>
+    <hyperlink ref="D21" r:id="rId58" xr:uid="{1FCC0BD6-CBE6-454F-B322-434F13714237}"/>
+    <hyperlink ref="E21" r:id="rId59" xr:uid="{7C238BAC-DA66-4EB9-8C60-CD252B1D37C4}"/>
+    <hyperlink ref="B21" r:id="rId60" xr:uid="{4C338E4E-6192-4A54-90CC-8798C56C61F5}"/>
+    <hyperlink ref="D22" r:id="rId61" xr:uid="{81AA71FF-776E-4ABD-8420-5DC15128330B}"/>
+    <hyperlink ref="E22" r:id="rId62" xr:uid="{88F693B0-24C7-48C7-9EA1-429F1263AA37}"/>
+    <hyperlink ref="B22" r:id="rId63" xr:uid="{F1C87633-9360-4B16-A294-557B6642482F}"/>
+    <hyperlink ref="D23" r:id="rId64" xr:uid="{02BC1E53-E32F-4E76-A6DD-03BCC4FB6EAB}"/>
+    <hyperlink ref="E23" r:id="rId65" xr:uid="{A7AB4DAE-8A68-411C-9C6D-EC63EE7602E0}"/>
+    <hyperlink ref="B23" r:id="rId66" xr:uid="{DA3E4B95-1A7E-471C-B19A-F63D28ED4A73}"/>
+    <hyperlink ref="D24" r:id="rId67" xr:uid="{6F54E97E-F954-42B1-871B-FC1E502B3A9E}"/>
+    <hyperlink ref="E24" r:id="rId68" xr:uid="{D6597889-CEFD-4EFF-9F1D-19B27A0DF2C6}"/>
+    <hyperlink ref="B24" r:id="rId69" xr:uid="{4633297F-0119-419D-9AC9-84FD21BEE9A5}"/>
+    <hyperlink ref="D25" r:id="rId70" xr:uid="{95D9FD25-765E-47B4-8EF8-418062420EC8}"/>
+    <hyperlink ref="E25" r:id="rId71" xr:uid="{A1C19FF3-6152-47ED-94C0-A8F061988BD8}"/>
+    <hyperlink ref="B25" r:id="rId72" xr:uid="{0ADCC7F1-2D19-481A-81C8-884DDAC971B9}"/>
+    <hyperlink ref="D26" r:id="rId73" xr:uid="{CC2C793F-46E6-4490-8587-7080976DB526}"/>
+    <hyperlink ref="E26" r:id="rId74" xr:uid="{53C6B407-F6E4-459C-A5B9-55B888457584}"/>
+    <hyperlink ref="B26" r:id="rId75" xr:uid="{F09D25B3-78C0-4BD5-B806-7546F8B4EF54}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId34"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId76"/>
 </worksheet>
 </file>
 

--- a/Info/Additional_information.xlsx
+++ b/Info/Additional_information.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFD6B733-983E-4BAA-A817-285C0CCC8ADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4778BFE4-7488-4F79-91C1-D222976A7BDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="742">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="743">
   <si>
     <t>good quality (UNC for UNC collection; UNC and XF for XF collection)</t>
   </si>
@@ -2306,6 +2306,9 @@
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/5/5c/Flag_of_Greece.svg</t>
+  </si>
+  <si>
+    <t>На текущий момент альбом не заполнен</t>
   </si>
 </sst>
 </file>
@@ -3197,54 +3200,6 @@
   </cellStyles>
   <dxfs count="34">
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3728,6 +3683,54 @@
         </horizontal>
       </border>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -3796,44 +3799,44 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{973D7237-72C7-453E-A0E1-526C93326B28}" name="Таблица3" displayName="Таблица3" ref="A1:F51" totalsRowShown="0" headerRowDxfId="33" dataDxfId="31" headerRowBorderDxfId="32" tableBorderDxfId="30" totalsRowBorderDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{973D7237-72C7-453E-A0E1-526C93326B28}" name="Таблица3" displayName="Таблица3" ref="A1:F51" totalsRowShown="0" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
   <autoFilter ref="A1:F51" xr:uid="{A2D8FA3D-4024-4365-BE1D-F93D0AF2D426}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{12C2DF0B-47FA-46A4-8424-55A1488EF88B}" name="ID" dataDxfId="28"/>
-    <tableColumn id="2" xr3:uid="{EB0B36CE-168D-429E-896D-DBA54794224F}" name="Name_Eng" dataDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{6C3A2CE8-252E-4C52-985B-8CDDFD9FA0C7}" name="OfficialMintName_Native" dataDxfId="26"/>
-    <tableColumn id="8" xr3:uid="{DA5871DC-2EDB-49C0-953E-EC0F70288E21}" name="Country" dataDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{FCD85F85-A94E-4BBE-9D3B-2B7494638375}" name="Mint_City" dataDxfId="24"/>
-    <tableColumn id="6" xr3:uid="{E5141978-CA91-4DE9-86F1-8A8AFA716534}" name="Alias" dataDxfId="23"/>
+    <tableColumn id="1" xr3:uid="{12C2DF0B-47FA-46A4-8424-55A1488EF88B}" name="ID" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{EB0B36CE-168D-429E-896D-DBA54794224F}" name="Name_Eng" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{6C3A2CE8-252E-4C52-985B-8CDDFD9FA0C7}" name="OfficialMintName_Native" dataDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{DA5871DC-2EDB-49C0-953E-EC0F70288E21}" name="Country" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{FCD85F85-A94E-4BBE-9D3B-2B7494638375}" name="Mint_City" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{E5141978-CA91-4DE9-86F1-8A8AFA716534}" name="Alias" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D0DCC88A-2D36-4004-A694-FC0C0F0C3396}" name="Таблица2" displayName="Таблица2" ref="A1:C16" totalsRowShown="0" headerRowBorderDxfId="22" tableBorderDxfId="21" totalsRowBorderDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D0DCC88A-2D36-4004-A694-FC0C0F0C3396}" name="Таблица2" displayName="Таблица2" ref="A1:C16" totalsRowShown="0" headerRowBorderDxfId="16" tableBorderDxfId="15" totalsRowBorderDxfId="14">
   <autoFilter ref="A1:C16" xr:uid="{00000000-0009-0000-0100-000002000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{28358E6A-6F3A-468C-9E1C-880A34D9BECE}" name="№" dataDxfId="19"/>
+    <tableColumn id="1" xr3:uid="{28358E6A-6F3A-468C-9E1C-880A34D9BECE}" name="№" dataDxfId="13"/>
     <tableColumn id="2" xr3:uid="{DD0AD5C8-324B-4DA7-B39F-B2DB3EF91222}" name="Links:"/>
-    <tableColumn id="3" xr3:uid="{FC8A6018-CA7E-4C73-9B21-B272B55FA8C1}" name="Description:" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{FC8A6018-CA7E-4C73-9B21-B272B55FA8C1}" name="Description:" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9D0F8E3D-96B1-4DB8-B1A6-8DD6B84F3693}" name="Таблица35" displayName="Таблица35" ref="A1:D52" totalsRowShown="0" headerRowDxfId="17" dataDxfId="15" headerRowBorderDxfId="16" tableBorderDxfId="14" totalsRowBorderDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9D0F8E3D-96B1-4DB8-B1A6-8DD6B84F3693}" name="Таблица35" displayName="Таблица35" ref="A1:D52" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10" tableBorderDxfId="8" totalsRowBorderDxfId="7">
   <autoFilter ref="A1:D52" xr:uid="{A2D8FA3D-4024-4365-BE1D-F93D0AF2D426}"/>
   <tableColumns count="4">
-    <tableColumn id="4" xr3:uid="{74AFB32D-7AAA-46BE-8174-ED698BB4613E}" name="Mint_id" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{523D65CD-0F56-441F-90B5-E46A9B14F0D0}" name="Ekaterinburg Mint" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{1AAB7352-E935-4EC6-A0D1-3EDC5D0BC93C}" name="Year_of_start" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{5FF15381-476A-4F88-B93A-6452F2830A0A}" name="Year_of_end" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{74AFB32D-7AAA-46BE-8174-ED698BB4613E}" name="Mint_id" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{523D65CD-0F56-441F-90B5-E46A9B14F0D0}" name="Ekaterinburg Mint" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{1AAB7352-E935-4EC6-A0D1-3EDC5D0BC93C}" name="Year_of_start" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{5FF15381-476A-4F88-B93A-6452F2830A0A}" name="Year_of_end" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3847,9 +3850,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{8354E581-3B48-4762-81A7-EA76E36C4BB5}" name="№" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{1F45DC85-8ECA-45FE-BF45-E528619CEE0E}" name="Links:" dataDxfId="7" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{3FAE616B-3296-4770-9E56-8A824991EECA}" name="Description:" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{8354E581-3B48-4762-81A7-EA76E36C4BB5}" name="№" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{1F45DC85-8ECA-45FE-BF45-E528619CEE0E}" name="Links:" dataDxfId="1" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{3FAE616B-3296-4770-9E56-8A824991EECA}" name="Description:" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -4240,12 +4243,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C7:C8">
-    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="33" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C7))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6">
-    <cfRule type="containsText" dxfId="4" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="32" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C6))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4262,7 +4265,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2">
-    <cfRule type="containsText" dxfId="3" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="31" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C2))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4279,7 +4282,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4">
-    <cfRule type="containsText" dxfId="2" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="30" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C4))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4296,7 +4299,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C5">
-    <cfRule type="containsText" dxfId="1" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="29" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C5))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4313,7 +4316,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3">
-    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="28" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C3))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -5740,12 +5743,12 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C94A307-2E39-40B9-B204-C92675C0AF71}">
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.36328125" customWidth="1"/>
     <col min="2" max="2" width="57.54296875" customWidth="1"/>
-    <col min="3" max="3" width="34.81640625" customWidth="1"/>
+    <col min="3" max="3" width="36.453125" customWidth="1"/>
     <col min="4" max="4" width="151" customWidth="1"/>
     <col min="5" max="5" width="79.54296875" customWidth="1"/>
     <col min="6" max="6" width="62" customWidth="1"/>
@@ -6191,6 +6194,22 @@
       </c>
       <c r="E26" s="86" t="s">
         <v>739</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>529</v>
+      </c>
+      <c r="C27" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>528</v>
+      </c>
+      <c r="C28" t="s">
+        <v>742</v>
       </c>
     </row>
   </sheetData>

--- a/Info/Additional_information.xlsx
+++ b/Info/Additional_information.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4778BFE4-7488-4F79-91C1-D222976A7BDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{034E2343-17F9-4569-9033-511EDAB51CD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="743">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1188" uniqueCount="855">
   <si>
     <t>good quality (UNC for UNC collection; UNC and XF for XF collection)</t>
   </si>
@@ -1804,12 +1804,6 @@
     <t>Spain and Canada regular and commemorative coins</t>
   </si>
   <si>
-    <t>A009-03-FB-BN</t>
-  </si>
-  <si>
-    <t>A009-04-FB-DN</t>
-  </si>
-  <si>
     <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A009-03-FB-BN.html</t>
   </si>
   <si>
@@ -1822,24 +1816,15 @@
     <t>World banknotes</t>
   </si>
   <si>
-    <t>A010-01-OA-DB</t>
-  </si>
-  <si>
     <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A010-01-OA-DB.html</t>
   </si>
   <si>
-    <t>A011-01-OA-GR</t>
-  </si>
-  <si>
     <t>Tickets (part 1) to the theater, museums, concerts and performances</t>
   </si>
   <si>
     <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A011-01-OA-GR.html</t>
   </si>
   <si>
-    <t>A011-02-OA-GR</t>
-  </si>
-  <si>
     <t>Билеты (часть 1) в театры, музеи, на концерты и спектакли</t>
   </si>
   <si>
@@ -1849,15 +1834,9 @@
     <t>Tickets (part 2) for parks, cinemas, special events, trains, and planes. Various tokens</t>
   </si>
   <si>
-    <t>A012-01-OA-BU</t>
-  </si>
-  <si>
     <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A012-01-OA-BU.html</t>
   </si>
   <si>
-    <t>A013-01-OA-LN</t>
-  </si>
-  <si>
     <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A013-01-OA-LN.html</t>
   </si>
   <si>
@@ -1870,9 +1849,6 @@
     <t>A009-01-FB-LN</t>
   </si>
   <si>
-    <t>A009-02-FB-LN</t>
-  </si>
-  <si>
     <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A009-01-FB-LN.html</t>
   </si>
   <si>
@@ -2309,6 +2285,366 @@
   </si>
   <si>
     <t>На текущий момент альбом не заполнен</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/USA/%23USA%23Commemorative%23%5B1999-present%5D%23circulation_quality.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/USA/</t>
+  </si>
+  <si>
+    <t>Юбилейные монеты США (дворы P и S)</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/a/a4/Flag_of_the_United_States.svg</t>
+  </si>
+  <si>
+    <t>Юбилейные монеты США (двор D)</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/Russia/%23Russia%23USSR%23Commemorative%23%5B1965-1991%5D%23circulation_quality.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/Russia/</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/f/f3/Flag_of_Russia.svg</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Austria/%23EURO%23Austria%23Regular%23%5B2002-present%5D%23circulation_quality.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Belgium/%23EURO%23Belgium%23Regular%23%5B1999-present%5D%23circulation_quality.xlsx</t>
+  </si>
+  <si>
+    <t>Болгария / Bulgaria</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Bulgaria/%23EURO%23Bulgaria%23Regular%23%5B2026-present%5D%23circulation_quality.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Bulgaria/</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/9/9a/Flag_of_Bulgaria.svg</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Croatia/%23EURO%23Croatia%23Regular%23%5B2008-present%5D%23circulation_quality.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Cyprus/%23EURO%23Cyprus%23Regular%23%5B2008-present%5D%23circulation_qualitys.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Estonia/%23EURO%23Estonia%23Regular%23%5B2011-present%5D%23circulation_quality.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Finland/%23EURO%23Finland%23Regular%23%5B1999-present%5D%23circulation_quality.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/France/%23EURO%23France%23Regular%23%5B1999-present%5D%23circulation_quality.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Germany/%23EURO%23Germany%23Regular%23%5B2002-present%5D%23circulation_quality.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Greece/%23EURO%23Greece%23Regular%23%5B2002-present%5D%23circulation_quality.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Ireland/%23EURO%23Ireland%23Regular%23%5B2002-present%5D%23circulation_quality.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Italy/%23EURO%23Italy%23Regular%23%5B2002-present%5D%23circulation_quality.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Latvia/%23EURO%23Latvia%23Regular%23%5B2014-present%5D%23circulation_quality.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Luxembourg/%23EURO%23Luxembourg%23Regular%23%5B2002-present%5D%23circulation_quality.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/blob/master/Collections/EURO/Malta/</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Malta/%23EURO%23Malta%23Regular%23%5B2008-present%5D%23circulation_quality.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Monaco/%23EURO%23Monaco%23Regular%23%5B2001-present%5D%23circulation_quality.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Netherlands/%23EURO%23Netherlands%23Regular%23%5B1999-present%5D%23circulation_quality.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Portugal/%23EURO%23Portugal%23Regular%23%5B2002-present%5D%23circulation_quality.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/San_Marino/%23EURO%23San_Marino%23Regular%23%5B2002-present%5D%23circulation_quality.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Slovakia/%23EURO%23Slovakia%23Regular%23%5B2009-present%5D%23circulation_quality.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/EURO/Spain/%23EURO%23Spain%23Regular%23%5B1999-present%5D%23circulation_quality.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/USA/%23USA%23Regular%23%5B1900-present%5D%23circulation_quality.xlsx</t>
+  </si>
+  <si>
+    <t>Регулярные монеты США (дворы P и S)</t>
+  </si>
+  <si>
+    <t>Регулярные монеты США (двор D)</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/Russia/%23Russia%23Russian_Federation%23Regular%23%5B1992-present%5D%23circulation_quality.xlsx</t>
+  </si>
+  <si>
+    <t>Регулярные монеты РФ</t>
+  </si>
+  <si>
+    <t>Юбилейные монеты СССР</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/a/a9/Flag_of_the_Soviet_Union.svg</t>
+  </si>
+  <si>
+    <t>Регулярные монеты СССР</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/Russia/%23Russia%23USSR%23Regular%23%5B1921-1991%5D%23circulation_quality.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/Spain/%23Spain%23Regular%23%5B1934-2001%5D%23circulation_quality.xlsx</t>
+  </si>
+  <si>
+    <t>Регулярные монеты Испании</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/Spain/</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/Canada/%23Canada%23Regular%23%5B1953-present%5D%23circulation_quality.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/Canada/</t>
+  </si>
+  <si>
+    <t>Регулярные монеты Канады</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/c/cf/Flag_of_Canada.svg</t>
+  </si>
+  <si>
+    <t>Юбилейные монеты Канады</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/Canada/%23Canada%23Commemorative%23%5B1953-present%5D%23circulation_quality.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/Kazakhstan/%23Kazakhstan%23Regular%23%5B1995-present%5D%23circulation_quality.xlsx</t>
+  </si>
+  <si>
+    <t>Регулярные монеты Казахстана</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/Kazakhstan/</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/d/d3/Flag_of_Kazakhstan.svg</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/Kazakhstan/%23Kazakhstan%23Commercial%23%5B2004-present%5D%23circulation_quality.xlsx</t>
+  </si>
+  <si>
+    <t>Юбилейные монеты Казахстана</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/United_Kingdom/%23British_India%23Regular%23%5B1834-1947%5D%23circulation_quality.xlsx</t>
+  </si>
+  <si>
+    <t>Регулярные монеты Британской Индии</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/United_Kingdom/</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/b/be/British_Raj_Red_Ensign.svg</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/India/%23Republic_of_India%23Regular%23%5B1950-1956%5D%23circulation_quality.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/India/</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/4/41/Flag_of_India.svg</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/India/%23Republic_of_India%23Regular%23%5B1957-present%5D%23circulation_quality.xlsx</t>
+  </si>
+  <si>
+    <t>Регулярные монеты Индии [1950-1956]</t>
+  </si>
+  <si>
+    <t>Регулярные монеты Индии [1957-present]</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/Russia/%23Russia%23Russian_Empire%23Regular%23%5B1867-1917%5D%23circulation_quality.xlsx</t>
+  </si>
+  <si>
+    <t>Регулярные монеты Российской империи</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/6/64/Flag_of_Russia_%281858%E2%80%931896%29.svg</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/United_Kingdom/%23United_Kingdom%23Before_DecimalDay%23Regular%23%5B1953-1970%5D%23circulation_quality.xlsx</t>
+  </si>
+  <si>
+    <t>Регулярные монеты Великобритании до Десятичного дня [1953-1970]</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/8/83/Flag_of_the_United_Kingdom_%283-5%29.svg</t>
+  </si>
+  <si>
+    <t>Регулярные монеты Великобритании после Десятичного дня [1968-present]</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/United_Kingdom/%23United_Kingdom%23After_DecimalDay%23Regular%23%5B1968-present%5D%23circulation_quality.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/Ukraine/%23Ukraine%23Regular%23%5B1992-present%5D%23circulation_quality.xlsx</t>
+  </si>
+  <si>
+    <t>Регулярные монеты Украины</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/Ukraine/</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/4/49/Flag_of_Ukraine.svg</t>
+  </si>
+  <si>
+    <t>Юбилейные монеты Украины</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/Ukraine/%23Ukraine%23Commercial%23%5B2004-present%5D%23circulation_quality.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/Germany/%23Germany%23German%20Empire%23Regular%23%5B1871-1922%5D%23circulation_quality.xlsx</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/Germany/</t>
+  </si>
+  <si>
+    <t>Регулярные монеты Германской империи [1871-1922]</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/1/1f/Flag_of_Germany_%281867%E2%80%931918%29.svg</t>
+  </si>
+  <si>
+    <t>Инфляционные монеты Веймарской республики [1919-1925]</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/9/93/Flag_of_Weimar_Republic_%28jack%29.svg</t>
+  </si>
+  <si>
+    <t>Рентная марка Веймарской республики [1923-1929]</t>
+  </si>
+  <si>
+    <t>Регулярные монеты Третьего Рейха [1933-1948]</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/Germany/%23Germany%23Third_Reich%23Regular%23%5B1933-1948%5D%23circulation_quality.xlsx</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/7/77/Flag_of_Germany_%281935%E2%80%931945%29.svg</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/Germany/%23Germany%23GDR%23Regular%23%5B1950-1990%5D%23circulation_quality.xlsx</t>
+  </si>
+  <si>
+    <t>Регулярные монеты ГДР [1950-1990]</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/9/97/Flag_of_the_German_Democratic_Republic.svg</t>
+  </si>
+  <si>
+    <t>Регулярные монеты ФРГ [1948-2001]</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/Germany/%23Germany%23FRG%23Regular%23%5B1948-2001%5D%23circulation_quality.xlsx</t>
+  </si>
+  <si>
+    <t>Монеты мира (часть 1) Европа, Америка, Африка, Австралия и Океания(вне конкретной коллеции)</t>
+  </si>
+  <si>
+    <t>A010-01-FB-LN</t>
+  </si>
+  <si>
+    <t>A011-01-FB-BN</t>
+  </si>
+  <si>
+    <t>A011-02-FB-DN</t>
+  </si>
+  <si>
+    <t>A012-01-OA-DB</t>
+  </si>
+  <si>
+    <t>A013-01-OA-GR</t>
+  </si>
+  <si>
+    <t>A013-02-OA-GR</t>
+  </si>
+  <si>
+    <t>A014-01-OA-BU</t>
+  </si>
+  <si>
+    <t>A015-01-OA-LN</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/Foreign_various/Foreighn_originals.xlsx</t>
+  </si>
+  <si>
+    <t>Монеты мира (часть 2) Азия (вне конкретной коллеции)</t>
+  </si>
+  <si>
+    <t>💵</t>
+  </si>
+  <si>
+    <t>🎟</t>
+  </si>
+  <si>
+    <t>🎫</t>
+  </si>
+  <si>
+    <t>Различные жетоны</t>
+  </si>
+  <si>
+    <t>🔘</t>
+  </si>
+  <si>
+    <t>Билеты (часть 2) в паркии, кино, на особые события, на поезда, на самолёты</t>
+  </si>
+  <si>
+    <t>Билеты на метро</t>
+  </si>
+  <si>
+    <t>🚇</t>
+  </si>
+  <si>
+    <t>Проездные трамвайные билеты</t>
+  </si>
+  <si>
+    <t>🚋</t>
+  </si>
+  <si>
+    <t>Ⓜ️</t>
+  </si>
+  <si>
+    <t>Жетоны метро</t>
+  </si>
+  <si>
+    <t>💳</t>
   </si>
 </sst>
 </file>
@@ -4761,7 +5097,7 @@
   <sheetData>
     <row r="7" spans="2:26" ht="61.5" x14ac:dyDescent="1.35">
       <c r="B7" s="106" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="C7" s="107"/>
       <c r="D7" s="107"/>
@@ -5161,7 +5497,7 @@
         <v>397</v>
       </c>
       <c r="F1" s="78" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5181,7 +5517,7 @@
         <v>527</v>
       </c>
       <c r="F2" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -5201,7 +5537,7 @@
         <v>532</v>
       </c>
       <c r="F3" t="s">
-        <v>610</v>
+        <v>602</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -5221,7 +5557,7 @@
         <v>533</v>
       </c>
       <c r="F4" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -5241,7 +5577,7 @@
         <v>534</v>
       </c>
       <c r="F5" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -5261,7 +5597,7 @@
         <v>535</v>
       </c>
       <c r="F6" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -5278,10 +5614,10 @@
         <v>499</v>
       </c>
       <c r="E7" s="83" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="F7" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -5298,10 +5634,10 @@
         <v>498</v>
       </c>
       <c r="E8" s="83" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="F8" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -5321,7 +5657,7 @@
         <v>539</v>
       </c>
       <c r="F9" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -5341,7 +5677,7 @@
         <v>540</v>
       </c>
       <c r="F10" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -5361,7 +5697,7 @@
         <v>543</v>
       </c>
       <c r="F11" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
@@ -5381,7 +5717,7 @@
         <v>544</v>
       </c>
       <c r="F12" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
@@ -5401,7 +5737,7 @@
         <v>547</v>
       </c>
       <c r="F13" t="s">
-        <v>614</v>
+        <v>606</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
@@ -5421,7 +5757,7 @@
         <v>548</v>
       </c>
       <c r="F14" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
@@ -5441,7 +5777,7 @@
         <v>551</v>
       </c>
       <c r="F15" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
@@ -5461,7 +5797,7 @@
         <v>552</v>
       </c>
       <c r="F16" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
@@ -5481,7 +5817,7 @@
         <v>558</v>
       </c>
       <c r="F17" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
@@ -5501,7 +5837,7 @@
         <v>562</v>
       </c>
       <c r="F18" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
@@ -5515,13 +5851,13 @@
         <v>573</v>
       </c>
       <c r="D19" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
       <c r="E19" s="83" t="s">
         <v>564</v>
       </c>
       <c r="F19" t="s">
-        <v>621</v>
+        <v>613</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
@@ -5529,7 +5865,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="C20" t="s">
         <v>569</v>
@@ -5538,10 +5874,10 @@
         <v>570</v>
       </c>
       <c r="E20" s="83" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="F20" t="s">
-        <v>622</v>
+        <v>614</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
@@ -5549,7 +5885,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>596</v>
+        <v>832</v>
       </c>
       <c r="C21" t="s">
         <v>571</v>
@@ -5558,10 +5894,10 @@
         <v>572</v>
       </c>
       <c r="E21" s="83" t="s">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="F21" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
@@ -5569,19 +5905,19 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
+        <v>833</v>
+      </c>
+      <c r="C22" t="s">
+        <v>618</v>
+      </c>
+      <c r="D22" t="s">
+        <v>617</v>
+      </c>
+      <c r="E22" s="83" t="s">
         <v>574</v>
       </c>
-      <c r="C22" t="s">
-        <v>626</v>
-      </c>
-      <c r="D22" t="s">
-        <v>625</v>
-      </c>
-      <c r="E22" s="83" t="s">
-        <v>576</v>
-      </c>
       <c r="F22" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
@@ -5589,19 +5925,19 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
+        <v>834</v>
+      </c>
+      <c r="C23" t="s">
+        <v>619</v>
+      </c>
+      <c r="D23" t="s">
+        <v>616</v>
+      </c>
+      <c r="E23" s="83" t="s">
         <v>575</v>
       </c>
-      <c r="C23" t="s">
-        <v>627</v>
-      </c>
-      <c r="D23" t="s">
-        <v>624</v>
-      </c>
-      <c r="E23" s="83" t="s">
-        <v>577</v>
-      </c>
       <c r="F23" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
@@ -5609,19 +5945,19 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>580</v>
+        <v>835</v>
       </c>
       <c r="C24" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="D24" t="s">
+        <v>576</v>
+      </c>
+      <c r="E24" s="83" t="s">
         <v>578</v>
       </c>
-      <c r="E24" s="83" t="s">
-        <v>581</v>
-      </c>
       <c r="F24" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
@@ -5629,19 +5965,19 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>582</v>
+        <v>836</v>
       </c>
       <c r="C25" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="D25" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="E25" s="83" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="F25" t="s">
-        <v>629</v>
+        <v>621</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
@@ -5649,19 +5985,19 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>585</v>
+        <v>837</v>
       </c>
       <c r="C26" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="D26" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="E26" s="83" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="F26" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
@@ -5669,19 +6005,19 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>589</v>
+        <v>838</v>
       </c>
       <c r="C27" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="D27" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="E27" s="83" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="F27" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
@@ -5689,19 +6025,19 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>591</v>
+        <v>839</v>
       </c>
       <c r="C28" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="D28" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="E28" s="83" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="F28" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
     </row>
   </sheetData>
@@ -5743,12 +6079,12 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C94A307-2E39-40B9-B204-C92675C0AF71}">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E87"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.36328125" customWidth="1"/>
     <col min="2" max="2" width="57.54296875" customWidth="1"/>
-    <col min="3" max="3" width="36.453125" customWidth="1"/>
+    <col min="3" max="3" width="39.1796875" customWidth="1"/>
     <col min="4" max="4" width="151" customWidth="1"/>
     <col min="5" max="5" width="79.54296875" customWidth="1"/>
     <col min="6" max="6" width="62" customWidth="1"/>
@@ -5756,19 +6092,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="B1" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="C1" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="D1" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="E1" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -5776,16 +6112,16 @@
         <v>526</v>
       </c>
       <c r="B2" s="86" t="s">
-        <v>689</v>
+        <v>681</v>
       </c>
       <c r="C2" t="s">
-        <v>686</v>
+        <v>678</v>
       </c>
       <c r="D2" s="86" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="E2" s="86" t="s">
-        <v>688</v>
+        <v>680</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -5793,16 +6129,16 @@
         <v>526</v>
       </c>
       <c r="B3" s="86" t="s">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="C3" t="s">
-        <v>691</v>
+        <v>683</v>
       </c>
       <c r="D3" s="86" t="s">
-        <v>692</v>
+        <v>684</v>
       </c>
       <c r="E3" s="86" t="s">
-        <v>693</v>
+        <v>685</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -5810,16 +6146,16 @@
         <v>525</v>
       </c>
       <c r="B4" s="86" t="s">
-        <v>685</v>
+        <v>677</v>
       </c>
       <c r="C4" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="D4" s="86" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="E4" s="86" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -5827,16 +6163,16 @@
         <v>525</v>
       </c>
       <c r="B5" s="86" t="s">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="C5" t="s">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="D5" s="86" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="E5" s="86" t="s">
-        <v>647</v>
+        <v>639</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -5844,16 +6180,16 @@
         <v>525</v>
       </c>
       <c r="B6" s="86" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="C6" t="s">
-        <v>650</v>
+        <v>642</v>
       </c>
       <c r="D6" s="86" t="s">
-        <v>648</v>
+        <v>640</v>
       </c>
       <c r="E6" s="86" t="s">
-        <v>649</v>
+        <v>641</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -5861,16 +6197,16 @@
         <v>525</v>
       </c>
       <c r="B7" s="86" t="s">
-        <v>682</v>
+        <v>674</v>
       </c>
       <c r="C7" t="s">
-        <v>652</v>
+        <v>644</v>
       </c>
       <c r="D7" s="86" t="s">
-        <v>651</v>
+        <v>643</v>
       </c>
       <c r="E7" s="86" t="s">
-        <v>653</v>
+        <v>645</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -5878,16 +6214,16 @@
         <v>525</v>
       </c>
       <c r="B8" s="86" t="s">
-        <v>681</v>
+        <v>673</v>
       </c>
       <c r="C8" t="s">
-        <v>655</v>
+        <v>647</v>
       </c>
       <c r="D8" s="86" t="s">
-        <v>654</v>
+        <v>646</v>
       </c>
       <c r="E8" s="86" t="s">
-        <v>656</v>
+        <v>648</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -5895,16 +6231,16 @@
         <v>525</v>
       </c>
       <c r="B9" s="86" t="s">
-        <v>680</v>
+        <v>672</v>
       </c>
       <c r="C9" t="s">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="D9" s="86" t="s">
-        <v>657</v>
+        <v>649</v>
       </c>
       <c r="E9" s="86" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -5912,16 +6248,16 @@
         <v>525</v>
       </c>
       <c r="B10" s="86" t="s">
-        <v>679</v>
+        <v>671</v>
       </c>
       <c r="C10" t="s">
-        <v>661</v>
+        <v>653</v>
       </c>
       <c r="D10" s="86" t="s">
-        <v>660</v>
+        <v>652</v>
       </c>
       <c r="E10" s="86" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -5929,16 +6265,16 @@
         <v>525</v>
       </c>
       <c r="B11" s="86" t="s">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="C11" t="s">
-        <v>665</v>
+        <v>657</v>
       </c>
       <c r="D11" s="86" t="s">
-        <v>663</v>
+        <v>655</v>
       </c>
       <c r="E11" s="86" t="s">
-        <v>664</v>
+        <v>656</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -5946,16 +6282,16 @@
         <v>525</v>
       </c>
       <c r="B12" s="86" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
       <c r="C12" t="s">
-        <v>667</v>
+        <v>659</v>
       </c>
       <c r="D12" s="86" t="s">
-        <v>666</v>
+        <v>658</v>
       </c>
       <c r="E12" s="86" t="s">
-        <v>668</v>
+        <v>660</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -5963,16 +6299,16 @@
         <v>525</v>
       </c>
       <c r="B13" s="86" t="s">
-        <v>675</v>
+        <v>667</v>
       </c>
       <c r="C13" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="D13" s="86" t="s">
-        <v>669</v>
+        <v>661</v>
       </c>
       <c r="E13" s="86" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
@@ -5980,16 +6316,16 @@
         <v>525</v>
       </c>
       <c r="B14" s="86" t="s">
-        <v>676</v>
+        <v>668</v>
       </c>
       <c r="C14" t="s">
-        <v>673</v>
+        <v>665</v>
       </c>
       <c r="D14" s="86" t="s">
-        <v>672</v>
+        <v>664</v>
       </c>
       <c r="E14" s="86" t="s">
-        <v>674</v>
+        <v>666</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
@@ -5997,16 +6333,16 @@
         <v>531</v>
       </c>
       <c r="B15" s="86" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="C15" t="s">
-        <v>696</v>
+        <v>688</v>
       </c>
       <c r="D15" s="86" t="s">
-        <v>694</v>
+        <v>686</v>
       </c>
       <c r="E15" s="86" t="s">
-        <v>695</v>
+        <v>687</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
@@ -6014,16 +6350,16 @@
         <v>531</v>
       </c>
       <c r="B16" s="86" t="s">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="C16" t="s">
-        <v>700</v>
+        <v>692</v>
       </c>
       <c r="D16" s="86" t="s">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="E16" s="86" t="s">
-        <v>699</v>
+        <v>691</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
@@ -6031,16 +6367,16 @@
         <v>531</v>
       </c>
       <c r="B17" s="86" t="s">
-        <v>705</v>
+        <v>697</v>
       </c>
       <c r="C17" t="s">
-        <v>702</v>
+        <v>694</v>
       </c>
       <c r="D17" s="86" t="s">
-        <v>703</v>
+        <v>695</v>
       </c>
       <c r="E17" s="86" t="s">
-        <v>704</v>
+        <v>696</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
@@ -6048,16 +6384,16 @@
         <v>522</v>
       </c>
       <c r="B18" s="86" t="s">
-        <v>706</v>
+        <v>698</v>
       </c>
       <c r="C18" t="s">
-        <v>707</v>
+        <v>699</v>
       </c>
       <c r="D18" s="86" t="s">
-        <v>708</v>
+        <v>700</v>
       </c>
       <c r="E18" s="86" t="s">
-        <v>709</v>
+        <v>701</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
@@ -6065,16 +6401,16 @@
         <v>522</v>
       </c>
       <c r="B19" s="86" t="s">
-        <v>713</v>
+        <v>705</v>
       </c>
       <c r="C19" t="s">
-        <v>712</v>
+        <v>704</v>
       </c>
       <c r="D19" s="86" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="E19" s="86" t="s">
-        <v>711</v>
+        <v>703</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
@@ -6082,16 +6418,16 @@
         <v>522</v>
       </c>
       <c r="B20" s="86" t="s">
-        <v>714</v>
+        <v>706</v>
       </c>
       <c r="C20" t="s">
-        <v>715</v>
+        <v>707</v>
       </c>
       <c r="D20" s="86" t="s">
-        <v>716</v>
+        <v>708</v>
       </c>
       <c r="E20" s="86" t="s">
-        <v>717</v>
+        <v>709</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
@@ -6099,16 +6435,16 @@
         <v>530</v>
       </c>
       <c r="B21" s="86" t="s">
-        <v>721</v>
+        <v>713</v>
       </c>
       <c r="C21" t="s">
-        <v>720</v>
+        <v>712</v>
       </c>
       <c r="D21" s="86" t="s">
-        <v>718</v>
+        <v>710</v>
       </c>
       <c r="E21" s="86" t="s">
-        <v>719</v>
+        <v>711</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
@@ -6116,16 +6452,16 @@
         <v>530</v>
       </c>
       <c r="B22" s="86" t="s">
-        <v>725</v>
+        <v>717</v>
       </c>
       <c r="C22" t="s">
-        <v>724</v>
+        <v>716</v>
       </c>
       <c r="D22" s="86" t="s">
-        <v>722</v>
+        <v>714</v>
       </c>
       <c r="E22" s="86" t="s">
-        <v>723</v>
+        <v>715</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
@@ -6133,16 +6469,16 @@
         <v>530</v>
       </c>
       <c r="B23" s="86" t="s">
-        <v>729</v>
+        <v>721</v>
       </c>
       <c r="C23" t="s">
-        <v>728</v>
+        <v>720</v>
       </c>
       <c r="D23" s="86" t="s">
-        <v>726</v>
+        <v>718</v>
       </c>
       <c r="E23" s="86" t="s">
-        <v>727</v>
+        <v>719</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
@@ -6150,16 +6486,16 @@
         <v>530</v>
       </c>
       <c r="B24" s="86" t="s">
-        <v>733</v>
+        <v>725</v>
       </c>
       <c r="C24" t="s">
-        <v>731</v>
+        <v>723</v>
       </c>
       <c r="D24" s="86" t="s">
-        <v>730</v>
+        <v>722</v>
       </c>
       <c r="E24" s="86" t="s">
-        <v>732</v>
+        <v>724</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
@@ -6167,16 +6503,16 @@
         <v>530</v>
       </c>
       <c r="B25" s="86" t="s">
-        <v>737</v>
+        <v>729</v>
       </c>
       <c r="C25" t="s">
-        <v>735</v>
+        <v>727</v>
       </c>
       <c r="D25" s="86" t="s">
-        <v>734</v>
+        <v>726</v>
       </c>
       <c r="E25" s="86" t="s">
-        <v>736</v>
+        <v>728</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
@@ -6184,16 +6520,16 @@
         <v>530</v>
       </c>
       <c r="B26" s="86" t="s">
-        <v>741</v>
+        <v>733</v>
       </c>
       <c r="C26" t="s">
-        <v>740</v>
+        <v>732</v>
       </c>
       <c r="D26" s="86" t="s">
-        <v>738</v>
+        <v>730</v>
       </c>
       <c r="E26" s="86" t="s">
-        <v>739</v>
+        <v>731</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
@@ -6201,7 +6537,7 @@
         <v>529</v>
       </c>
       <c r="C27" t="s">
-        <v>742</v>
+        <v>734</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
@@ -6209,7 +6545,962 @@
         <v>528</v>
       </c>
       <c r="C28" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>538</v>
+      </c>
+      <c r="B29" s="86" t="s">
+        <v>738</v>
+      </c>
+      <c r="C29" t="s">
+        <v>737</v>
+      </c>
+      <c r="D29" s="86" t="s">
+        <v>735</v>
+      </c>
+      <c r="E29" s="86" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>537</v>
+      </c>
+      <c r="B30" s="86" t="s">
+        <v>738</v>
+      </c>
+      <c r="C30" t="s">
+        <v>739</v>
+      </c>
+      <c r="D30" s="86" t="s">
+        <v>735</v>
+      </c>
+      <c r="E30" s="86" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>541</v>
+      </c>
+      <c r="B31" s="86" t="s">
         <v>742</v>
+      </c>
+      <c r="C31" t="s">
+        <v>510</v>
+      </c>
+      <c r="D31" s="86" t="s">
+        <v>740</v>
+      </c>
+      <c r="E31" s="86" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>542</v>
+      </c>
+      <c r="B32" s="86" t="s">
+        <v>742</v>
+      </c>
+      <c r="C32" t="s">
+        <v>511</v>
+      </c>
+      <c r="D32" s="86" t="s">
+        <v>740</v>
+      </c>
+      <c r="E32" s="86" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>545</v>
+      </c>
+      <c r="B33" s="86" t="s">
+        <v>677</v>
+      </c>
+      <c r="C33" t="s">
+        <v>636</v>
+      </c>
+      <c r="D33" s="86" t="s">
+        <v>743</v>
+      </c>
+      <c r="E33" s="86" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>545</v>
+      </c>
+      <c r="B34" s="86" t="s">
+        <v>676</v>
+      </c>
+      <c r="C34" t="s">
+        <v>638</v>
+      </c>
+      <c r="D34" s="86" t="s">
+        <v>744</v>
+      </c>
+      <c r="E34" s="86" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>545</v>
+      </c>
+      <c r="B35" s="86" t="s">
+        <v>748</v>
+      </c>
+      <c r="C35" t="s">
+        <v>745</v>
+      </c>
+      <c r="D35" s="86" t="s">
+        <v>746</v>
+      </c>
+      <c r="E35" s="86" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>545</v>
+      </c>
+      <c r="B36" s="86" t="s">
+        <v>729</v>
+      </c>
+      <c r="C36" t="s">
+        <v>727</v>
+      </c>
+      <c r="D36" s="86" t="s">
+        <v>749</v>
+      </c>
+      <c r="E36" s="86" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>545</v>
+      </c>
+      <c r="B37" s="86" t="s">
+        <v>675</v>
+      </c>
+      <c r="C37" t="s">
+        <v>642</v>
+      </c>
+      <c r="D37" s="86" t="s">
+        <v>750</v>
+      </c>
+      <c r="E37" s="86" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>545</v>
+      </c>
+      <c r="B38" s="86" t="s">
+        <v>674</v>
+      </c>
+      <c r="C38" t="s">
+        <v>644</v>
+      </c>
+      <c r="D38" s="86" t="s">
+        <v>751</v>
+      </c>
+      <c r="E38" s="86" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>545</v>
+      </c>
+      <c r="B39" s="86" t="s">
+        <v>713</v>
+      </c>
+      <c r="C39" t="s">
+        <v>712</v>
+      </c>
+      <c r="D39" s="86" t="s">
+        <v>752</v>
+      </c>
+      <c r="E39" s="86" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>545</v>
+      </c>
+      <c r="B40" s="86" t="s">
+        <v>673</v>
+      </c>
+      <c r="C40" t="s">
+        <v>647</v>
+      </c>
+      <c r="D40" s="86" t="s">
+        <v>753</v>
+      </c>
+      <c r="E40" s="86" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>545</v>
+      </c>
+      <c r="B41" s="86" t="s">
+        <v>689</v>
+      </c>
+      <c r="C41" t="s">
+        <v>688</v>
+      </c>
+      <c r="D41" s="86" t="s">
+        <v>754</v>
+      </c>
+      <c r="E41" s="86" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>545</v>
+      </c>
+      <c r="B42" s="86" t="s">
+        <v>733</v>
+      </c>
+      <c r="C42" t="s">
+        <v>732</v>
+      </c>
+      <c r="D42" s="86" t="s">
+        <v>755</v>
+      </c>
+      <c r="E42" s="86" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>545</v>
+      </c>
+      <c r="B43" s="86" t="s">
+        <v>670</v>
+      </c>
+      <c r="C43" t="s">
+        <v>657</v>
+      </c>
+      <c r="D43" s="86" t="s">
+        <v>756</v>
+      </c>
+      <c r="E43" s="86" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>545</v>
+      </c>
+      <c r="B44" s="86" t="s">
+        <v>672</v>
+      </c>
+      <c r="C44" t="s">
+        <v>650</v>
+      </c>
+      <c r="D44" s="86" t="s">
+        <v>757</v>
+      </c>
+      <c r="E44" s="86" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>545</v>
+      </c>
+      <c r="B45" s="86" t="s">
+        <v>671</v>
+      </c>
+      <c r="C45" t="s">
+        <v>653</v>
+      </c>
+      <c r="D45" s="86" t="s">
+        <v>758</v>
+      </c>
+      <c r="E45" s="86" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>545</v>
+      </c>
+      <c r="B46" s="86" t="s">
+        <v>693</v>
+      </c>
+      <c r="C46" t="s">
+        <v>692</v>
+      </c>
+      <c r="D46" s="86" t="s">
+        <v>759</v>
+      </c>
+      <c r="E46" s="86" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>545</v>
+      </c>
+      <c r="B47" s="86" t="s">
+        <v>697</v>
+      </c>
+      <c r="C47" t="s">
+        <v>694</v>
+      </c>
+      <c r="D47" s="83" t="s">
+        <v>761</v>
+      </c>
+      <c r="E47" s="86" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>546</v>
+      </c>
+      <c r="B48" s="86" t="s">
+        <v>681</v>
+      </c>
+      <c r="C48" t="s">
+        <v>678</v>
+      </c>
+      <c r="D48" s="86" t="s">
+        <v>762</v>
+      </c>
+      <c r="E48" s="86" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>546</v>
+      </c>
+      <c r="B49" s="86" t="s">
+        <v>667</v>
+      </c>
+      <c r="C49" t="s">
+        <v>662</v>
+      </c>
+      <c r="D49" s="86" t="s">
+        <v>763</v>
+      </c>
+      <c r="E49" s="86" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>546</v>
+      </c>
+      <c r="B50" s="86" t="s">
+        <v>668</v>
+      </c>
+      <c r="C50" t="s">
+        <v>665</v>
+      </c>
+      <c r="D50" s="86" t="s">
+        <v>764</v>
+      </c>
+      <c r="E50" s="86" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>546</v>
+      </c>
+      <c r="B51" s="86" t="s">
+        <v>705</v>
+      </c>
+      <c r="C51" t="s">
+        <v>704</v>
+      </c>
+      <c r="D51" s="86" t="s">
+        <v>765</v>
+      </c>
+      <c r="E51" s="86" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>546</v>
+      </c>
+      <c r="B52" s="86" t="s">
+        <v>725</v>
+      </c>
+      <c r="C52" t="s">
+        <v>723</v>
+      </c>
+      <c r="D52" s="86" t="s">
+        <v>766</v>
+      </c>
+      <c r="E52" s="86" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>546</v>
+      </c>
+      <c r="B53" s="86" t="s">
+        <v>717</v>
+      </c>
+      <c r="C53" t="s">
+        <v>716</v>
+      </c>
+      <c r="D53" s="86" t="s">
+        <v>767</v>
+      </c>
+      <c r="E53" s="86" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>549</v>
+      </c>
+      <c r="B54" s="86" t="s">
+        <v>742</v>
+      </c>
+      <c r="C54" t="s">
+        <v>769</v>
+      </c>
+      <c r="D54" s="86" t="s">
+        <v>768</v>
+      </c>
+      <c r="E54" s="86" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>550</v>
+      </c>
+      <c r="B55" s="86" t="s">
+        <v>742</v>
+      </c>
+      <c r="C55" t="s">
+        <v>770</v>
+      </c>
+      <c r="D55" s="86" t="s">
+        <v>768</v>
+      </c>
+      <c r="E55" s="86" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>557</v>
+      </c>
+      <c r="B56" s="86" t="s">
+        <v>742</v>
+      </c>
+      <c r="C56" t="s">
+        <v>772</v>
+      </c>
+      <c r="D56" s="86" t="s">
+        <v>771</v>
+      </c>
+      <c r="E56" s="86" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>561</v>
+      </c>
+      <c r="B57" s="86" t="s">
+        <v>774</v>
+      </c>
+      <c r="C57" t="s">
+        <v>773</v>
+      </c>
+      <c r="D57" s="86" t="s">
+        <v>740</v>
+      </c>
+      <c r="E57" s="86" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>561</v>
+      </c>
+      <c r="B58" s="86" t="s">
+        <v>774</v>
+      </c>
+      <c r="C58" t="s">
+        <v>775</v>
+      </c>
+      <c r="D58" s="86" t="s">
+        <v>776</v>
+      </c>
+      <c r="E58" s="86" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>563</v>
+      </c>
+      <c r="B59" s="86" t="s">
+        <v>717</v>
+      </c>
+      <c r="C59" t="s">
+        <v>778</v>
+      </c>
+      <c r="D59" s="86" t="s">
+        <v>777</v>
+      </c>
+      <c r="E59" s="86" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>563</v>
+      </c>
+      <c r="B60" s="86" t="s">
+        <v>783</v>
+      </c>
+      <c r="C60" t="s">
+        <v>782</v>
+      </c>
+      <c r="D60" s="86" t="s">
+        <v>780</v>
+      </c>
+      <c r="E60" s="86" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>563</v>
+      </c>
+      <c r="B61" s="86" t="s">
+        <v>783</v>
+      </c>
+      <c r="C61" t="s">
+        <v>784</v>
+      </c>
+      <c r="D61" s="86" t="s">
+        <v>785</v>
+      </c>
+      <c r="E61" s="86" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>588</v>
+      </c>
+      <c r="B62" s="86" t="s">
+        <v>789</v>
+      </c>
+      <c r="C62" t="s">
+        <v>787</v>
+      </c>
+      <c r="D62" s="86" t="s">
+        <v>786</v>
+      </c>
+      <c r="E62" s="86" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>588</v>
+      </c>
+      <c r="B63" s="86" t="s">
+        <v>789</v>
+      </c>
+      <c r="C63" t="s">
+        <v>791</v>
+      </c>
+      <c r="D63" s="86" t="s">
+        <v>790</v>
+      </c>
+      <c r="E63" s="86" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>588</v>
+      </c>
+      <c r="B64" s="86" t="s">
+        <v>795</v>
+      </c>
+      <c r="C64" t="s">
+        <v>793</v>
+      </c>
+      <c r="D64" s="86" t="s">
+        <v>792</v>
+      </c>
+      <c r="E64" s="86" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>588</v>
+      </c>
+      <c r="B65" s="86" t="s">
+        <v>798</v>
+      </c>
+      <c r="C65" t="s">
+        <v>800</v>
+      </c>
+      <c r="D65" s="86" t="s">
+        <v>796</v>
+      </c>
+      <c r="E65" s="86" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>588</v>
+      </c>
+      <c r="B66" s="86" t="s">
+        <v>798</v>
+      </c>
+      <c r="C66" t="s">
+        <v>801</v>
+      </c>
+      <c r="D66" s="86" t="s">
+        <v>799</v>
+      </c>
+      <c r="E66" s="86" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>588</v>
+      </c>
+      <c r="B67" s="86" t="s">
+        <v>804</v>
+      </c>
+      <c r="C67" t="s">
+        <v>803</v>
+      </c>
+      <c r="D67" s="86" t="s">
+        <v>802</v>
+      </c>
+      <c r="E67" s="86" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>832</v>
+      </c>
+      <c r="B68" s="86" t="s">
+        <v>807</v>
+      </c>
+      <c r="C68" t="s">
+        <v>806</v>
+      </c>
+      <c r="D68" s="86" t="s">
+        <v>805</v>
+      </c>
+      <c r="E68" s="86" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>832</v>
+      </c>
+      <c r="B69" s="86" t="s">
+        <v>807</v>
+      </c>
+      <c r="C69" t="s">
+        <v>808</v>
+      </c>
+      <c r="D69" s="86" t="s">
+        <v>809</v>
+      </c>
+      <c r="E69" s="86" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>832</v>
+      </c>
+      <c r="B70" s="86" t="s">
+        <v>813</v>
+      </c>
+      <c r="C70" t="s">
+        <v>811</v>
+      </c>
+      <c r="D70" s="86" t="s">
+        <v>810</v>
+      </c>
+      <c r="E70" s="86" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>832</v>
+      </c>
+      <c r="B71" s="86" t="s">
+        <v>813</v>
+      </c>
+      <c r="C71" t="s">
+        <v>814</v>
+      </c>
+      <c r="D71" s="86" t="s">
+        <v>815</v>
+      </c>
+      <c r="E71" s="86" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>832</v>
+      </c>
+      <c r="B72" s="86" t="s">
+        <v>819</v>
+      </c>
+      <c r="C72" t="s">
+        <v>818</v>
+      </c>
+      <c r="D72" s="86" t="s">
+        <v>816</v>
+      </c>
+      <c r="E72" s="86" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>832</v>
+      </c>
+      <c r="B73" s="86" t="s">
+        <v>821</v>
+      </c>
+      <c r="C73" t="s">
+        <v>820</v>
+      </c>
+      <c r="D73" s="86" t="s">
+        <v>816</v>
+      </c>
+      <c r="E73" s="86" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>832</v>
+      </c>
+      <c r="B74" s="86" t="s">
+        <v>821</v>
+      </c>
+      <c r="C74" t="s">
+        <v>822</v>
+      </c>
+      <c r="D74" s="86" t="s">
+        <v>816</v>
+      </c>
+      <c r="E74" s="86" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>832</v>
+      </c>
+      <c r="B75" s="86" t="s">
+        <v>825</v>
+      </c>
+      <c r="C75" t="s">
+        <v>823</v>
+      </c>
+      <c r="D75" s="86" t="s">
+        <v>824</v>
+      </c>
+      <c r="E75" s="86" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>832</v>
+      </c>
+      <c r="B76" s="86" t="s">
+        <v>828</v>
+      </c>
+      <c r="C76" t="s">
+        <v>827</v>
+      </c>
+      <c r="D76" s="86" t="s">
+        <v>826</v>
+      </c>
+      <c r="E76" s="86" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>832</v>
+      </c>
+      <c r="B77" s="86" t="s">
+        <v>689</v>
+      </c>
+      <c r="C77" t="s">
+        <v>829</v>
+      </c>
+      <c r="D77" s="86" t="s">
+        <v>830</v>
+      </c>
+      <c r="E77" s="86" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>833</v>
+      </c>
+      <c r="B78" s="86" t="s">
+        <v>682</v>
+      </c>
+      <c r="C78" t="s">
+        <v>831</v>
+      </c>
+      <c r="D78" s="86" t="s">
+        <v>840</v>
+      </c>
+      <c r="E78" s="86" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>834</v>
+      </c>
+      <c r="B79" s="86" t="s">
+        <v>682</v>
+      </c>
+      <c r="C79" t="s">
+        <v>841</v>
+      </c>
+      <c r="D79" s="86" t="s">
+        <v>840</v>
+      </c>
+      <c r="E79" s="86" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>835</v>
+      </c>
+      <c r="B80" t="s">
+        <v>842</v>
+      </c>
+      <c r="C80" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>836</v>
+      </c>
+      <c r="B81" t="s">
+        <v>843</v>
+      </c>
+      <c r="C81" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>837</v>
+      </c>
+      <c r="B82" t="s">
+        <v>844</v>
+      </c>
+      <c r="C82" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>837</v>
+      </c>
+      <c r="B83" t="s">
+        <v>846</v>
+      </c>
+      <c r="C83" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>838</v>
+      </c>
+      <c r="B84" t="s">
+        <v>849</v>
+      </c>
+      <c r="C84" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>838</v>
+      </c>
+      <c r="B85" t="s">
+        <v>851</v>
+      </c>
+      <c r="C85" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>838</v>
+      </c>
+      <c r="B86" t="s">
+        <v>852</v>
+      </c>
+      <c r="C86" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>839</v>
+      </c>
+      <c r="B87" t="s">
+        <v>854</v>
+      </c>
+      <c r="C87" t="s">
+        <v>586</v>
       </c>
     </row>
   </sheetData>
@@ -6290,9 +7581,161 @@
     <hyperlink ref="D26" r:id="rId73" xr:uid="{CC2C793F-46E6-4490-8587-7080976DB526}"/>
     <hyperlink ref="E26" r:id="rId74" xr:uid="{53C6B407-F6E4-459C-A5B9-55B888457584}"/>
     <hyperlink ref="B26" r:id="rId75" xr:uid="{F09D25B3-78C0-4BD5-B806-7546F8B4EF54}"/>
+    <hyperlink ref="D29" r:id="rId76" xr:uid="{C09A55D4-F8C1-4BFE-9053-2A26156CEC11}"/>
+    <hyperlink ref="E29" r:id="rId77" xr:uid="{6CECFB2C-F1F3-4533-932C-4C621394B204}"/>
+    <hyperlink ref="B29" r:id="rId78" xr:uid="{13444664-1DB7-4DFF-819D-9CE401F529C8}"/>
+    <hyperlink ref="B30" r:id="rId79" xr:uid="{DE71BB17-7CF5-4B7E-ACAD-B902D63D4425}"/>
+    <hyperlink ref="D30" r:id="rId80" xr:uid="{E680186B-8E0C-4537-B17E-F024183FFC2E}"/>
+    <hyperlink ref="E30" r:id="rId81" xr:uid="{47F4380A-F029-4435-A9E0-91A9BB1488E9}"/>
+    <hyperlink ref="D31" r:id="rId82" xr:uid="{03A72534-E2AE-4082-BBAF-BD100F47261F}"/>
+    <hyperlink ref="E31" r:id="rId83" xr:uid="{9D87F1C9-561F-4A12-9664-CD9C2C1B2502}"/>
+    <hyperlink ref="B31" r:id="rId84" xr:uid="{62391A74-CD76-44EF-BDD9-F5B8DB56EC1A}"/>
+    <hyperlink ref="B32" r:id="rId85" xr:uid="{764A4666-16C8-4646-B8B8-2A4057E941DF}"/>
+    <hyperlink ref="D32" r:id="rId86" xr:uid="{2D15A23B-28F2-4A89-9956-A5C3557A118E}"/>
+    <hyperlink ref="E32" r:id="rId87" xr:uid="{5C647187-D2F8-43C0-B67B-E1E97AD133CE}"/>
+    <hyperlink ref="B33" r:id="rId88" xr:uid="{6589D223-52E6-4323-905B-95FE15BA27A5}"/>
+    <hyperlink ref="D33" r:id="rId89" xr:uid="{1BE2D3C8-EF16-413A-8477-CB97D47FDF8B}"/>
+    <hyperlink ref="E33" r:id="rId90" xr:uid="{C8449556-9E88-4BD4-80EB-56B4E04237BA}"/>
+    <hyperlink ref="B34" r:id="rId91" xr:uid="{A394C1A0-D73E-4D14-BE8F-3A3544ABABE8}"/>
+    <hyperlink ref="D34" r:id="rId92" xr:uid="{ADFF6004-0E43-49A9-BCEF-CB95AC47C403}"/>
+    <hyperlink ref="E34" r:id="rId93" xr:uid="{274493AE-B2B0-41EC-8F58-8620CD6AF4E6}"/>
+    <hyperlink ref="D35" r:id="rId94" xr:uid="{E7EDA7AE-0C25-46AE-9FC4-737E15B8CF8B}"/>
+    <hyperlink ref="E35" r:id="rId95" xr:uid="{0540CFF2-652B-4C5C-8E8F-697E1B2FD4A6}"/>
+    <hyperlink ref="B35" r:id="rId96" xr:uid="{FFE96848-A418-4F5F-9786-229A113AAF9D}"/>
+    <hyperlink ref="D36" r:id="rId97" xr:uid="{2D1E9057-EA4D-4CF4-8826-EDDF02F8FEFC}"/>
+    <hyperlink ref="B36" r:id="rId98" xr:uid="{BD8E924A-3188-47DE-A627-C9EF7725EFB8}"/>
+    <hyperlink ref="E36" r:id="rId99" xr:uid="{9EE7F16B-5801-44E4-8CF0-F871FF540186}"/>
+    <hyperlink ref="D37" r:id="rId100" xr:uid="{CEAF79D5-66E4-4EEE-864C-2AC2DF0C917A}"/>
+    <hyperlink ref="B37" r:id="rId101" xr:uid="{68819B00-5C9C-48CE-9E4E-F7236A281ABB}"/>
+    <hyperlink ref="E37" r:id="rId102" xr:uid="{0B896BF6-D27D-4641-A829-E2485B5E1BEB}"/>
+    <hyperlink ref="D38" r:id="rId103" xr:uid="{A83E777F-5B8F-48A4-A591-A37B3CBC254E}"/>
+    <hyperlink ref="B38" r:id="rId104" xr:uid="{AF6F9D9C-FE67-4BBD-867D-F5FDC21C5C1E}"/>
+    <hyperlink ref="E38" r:id="rId105" xr:uid="{0A0CCFF9-2752-412B-9DCA-5FA6C35C72DF}"/>
+    <hyperlink ref="D39" r:id="rId106" xr:uid="{5428D053-EA0E-4FDA-8064-2C0152B565C4}"/>
+    <hyperlink ref="B39" r:id="rId107" xr:uid="{A2AFCA4E-B288-4B11-A262-6C9441F19856}"/>
+    <hyperlink ref="E39" r:id="rId108" xr:uid="{9750A024-0FC6-45D8-A842-2ADF5815D038}"/>
+    <hyperlink ref="D40" r:id="rId109" xr:uid="{40052E9F-E510-4992-B9DC-6D44A7F4D686}"/>
+    <hyperlink ref="B40" r:id="rId110" xr:uid="{066BCFF0-E45B-45A9-B58B-7B23A48B7F71}"/>
+    <hyperlink ref="E40" r:id="rId111" xr:uid="{87027703-9446-455B-960A-7B9B1B9E89F5}"/>
+    <hyperlink ref="D41" r:id="rId112" xr:uid="{1D98FB4F-9653-4B8A-A706-25CDA836DD68}"/>
+    <hyperlink ref="B41" r:id="rId113" xr:uid="{792C7678-86FC-4BC9-B12E-472F732020C0}"/>
+    <hyperlink ref="E41" r:id="rId114" xr:uid="{171CD734-D869-4CCD-BA30-B81D39416309}"/>
+    <hyperlink ref="D42" r:id="rId115" xr:uid="{5BADDB78-17A1-437E-ACE0-4C4DEE4E9E05}"/>
+    <hyperlink ref="B42" r:id="rId116" xr:uid="{D06657F8-6F99-42F6-B9F3-49A684742B24}"/>
+    <hyperlink ref="E42" r:id="rId117" xr:uid="{3180C4EE-9C5E-4DCA-9B05-BF0166CFA5FA}"/>
+    <hyperlink ref="D43" r:id="rId118" xr:uid="{E3D1E8E1-F0D3-4485-A27F-136EC19F41EB}"/>
+    <hyperlink ref="B43" r:id="rId119" xr:uid="{168ECAC8-5CA4-4AB4-BA86-2343EFAB274F}"/>
+    <hyperlink ref="E43" r:id="rId120" xr:uid="{2289E2C4-E1C3-4E9B-9397-CF97B89D8FB5}"/>
+    <hyperlink ref="D44" r:id="rId121" xr:uid="{92148C7D-1FCA-4938-9D60-35FD42A5C6F8}"/>
+    <hyperlink ref="B44" r:id="rId122" xr:uid="{58258E80-4B9F-4049-AB45-6CC8F8FEB9D5}"/>
+    <hyperlink ref="E44" r:id="rId123" xr:uid="{FF6B9C9C-4764-4DFF-AAC9-FD0B25459B43}"/>
+    <hyperlink ref="D45" r:id="rId124" xr:uid="{6DC01287-948E-48D7-91D5-610CA890D935}"/>
+    <hyperlink ref="B45" r:id="rId125" xr:uid="{54C0780A-C7AB-4D26-80B4-CA39CD4E8B59}"/>
+    <hyperlink ref="E45" r:id="rId126" xr:uid="{240C1B21-070F-460A-8AFD-5ECFFEF3D78F}"/>
+    <hyperlink ref="D46" r:id="rId127" xr:uid="{71391FBA-F9B4-4260-AE55-6741BC4B6421}"/>
+    <hyperlink ref="B46" r:id="rId128" xr:uid="{A1035F26-F72D-41F5-AD06-5E47389DABEC}"/>
+    <hyperlink ref="E46" r:id="rId129" xr:uid="{24AF3411-416E-40F4-B811-8A0F266BFA2F}"/>
+    <hyperlink ref="E47" r:id="rId130" xr:uid="{6C5FCF83-955D-4BAB-B4EE-53D48053D82E}"/>
+    <hyperlink ref="B47" r:id="rId131" xr:uid="{6CE3FE8B-C469-4330-9B65-A31331CF4F5E}"/>
+    <hyperlink ref="D47" r:id="rId132" xr:uid="{9DF17FE5-078D-4443-B44D-DE912ADED581}"/>
+    <hyperlink ref="D48" r:id="rId133" xr:uid="{0CC94319-6542-416C-9E2C-B8516708D0C3}"/>
+    <hyperlink ref="B48" r:id="rId134" xr:uid="{86E09BDE-2C54-4A58-8AFA-FB34D4879912}"/>
+    <hyperlink ref="E48" r:id="rId135" xr:uid="{E679A9C3-E712-4983-8EE0-896C892C3CA6}"/>
+    <hyperlink ref="D49" r:id="rId136" xr:uid="{4D8CF836-2B11-4203-ABF4-B8901B2A2A10}"/>
+    <hyperlink ref="B49" r:id="rId137" xr:uid="{FC37C663-5517-48B1-BEE4-48F12CFDB482}"/>
+    <hyperlink ref="E49" r:id="rId138" xr:uid="{4592A7C3-8F3E-47FE-B8C0-B6136CA2701B}"/>
+    <hyperlink ref="D50" r:id="rId139" xr:uid="{E409413C-086C-4F0E-B39C-7C800F67D341}"/>
+    <hyperlink ref="B50" r:id="rId140" xr:uid="{CBB7FA2B-F0FD-49C7-B12C-EF486D939FC6}"/>
+    <hyperlink ref="E50" r:id="rId141" xr:uid="{23466661-EF48-41D4-9331-14EAEFFC8E40}"/>
+    <hyperlink ref="D51" r:id="rId142" xr:uid="{42A2E9D5-32BC-4E1E-8165-4ED4EA93C4ED}"/>
+    <hyperlink ref="E51" r:id="rId143" xr:uid="{A3B15FA1-4EF2-45A9-8FD5-6486DA00399F}"/>
+    <hyperlink ref="B51" r:id="rId144" xr:uid="{AD80AFC5-4978-4D96-976B-BF77DE86EDE5}"/>
+    <hyperlink ref="B52" r:id="rId145" xr:uid="{1AE24143-EFD8-46F1-9FEB-C05E8EA319B2}"/>
+    <hyperlink ref="E52" r:id="rId146" xr:uid="{B7C1D7D2-01ED-4DB0-9ACB-E71844B6391F}"/>
+    <hyperlink ref="D52" r:id="rId147" xr:uid="{7C84555B-72D0-4E7E-8120-FFEF538F6482}"/>
+    <hyperlink ref="D53" r:id="rId148" xr:uid="{DBB88F75-BAA7-4417-B751-9F6B398F20D6}"/>
+    <hyperlink ref="E53" r:id="rId149" xr:uid="{C4B2FB7C-D751-4BE4-B80D-1D19FB599067}"/>
+    <hyperlink ref="B53" r:id="rId150" xr:uid="{C0A87CF5-0CDC-43C5-AD74-D08EADAD4ECE}"/>
+    <hyperlink ref="D54" r:id="rId151" xr:uid="{321A9243-4B72-4C19-9CD1-9199FDFCF2E6}"/>
+    <hyperlink ref="B54" r:id="rId152" xr:uid="{26D7EF60-C714-4FD5-AC80-9248C6C665B5}"/>
+    <hyperlink ref="B55" r:id="rId153" xr:uid="{A57736B4-6732-46D4-8BC8-7C32525F98D6}"/>
+    <hyperlink ref="D55" r:id="rId154" xr:uid="{1B3BEB40-1EE5-404E-8CDC-AA9B3E1B0947}"/>
+    <hyperlink ref="E54" r:id="rId155" xr:uid="{EE68E9AD-2777-4231-AEE5-D934B4B626AB}"/>
+    <hyperlink ref="E55" r:id="rId156" xr:uid="{53BCCA0C-6DBE-4C35-8C04-CFBF70FA60F2}"/>
+    <hyperlink ref="D56" r:id="rId157" xr:uid="{9AA71A7E-44B8-470A-B313-862336B7F5A5}"/>
+    <hyperlink ref="E56" r:id="rId158" xr:uid="{585DECC9-3251-4499-892F-F9240A7EE776}"/>
+    <hyperlink ref="B56" r:id="rId159" xr:uid="{A373CF1C-3A6E-486F-B517-2C8792E95129}"/>
+    <hyperlink ref="D57" r:id="rId160" xr:uid="{F9CF8130-800A-487B-BFCE-4909473DADC4}"/>
+    <hyperlink ref="E57" r:id="rId161" xr:uid="{958AAFCE-E6FF-49DB-85E6-FEE7FAC835F5}"/>
+    <hyperlink ref="B57" r:id="rId162" xr:uid="{DCDF3C10-E8F4-45FB-B43E-916B3077418F}"/>
+    <hyperlink ref="B58" r:id="rId163" xr:uid="{9660E1B0-262B-4C02-B474-D0382995C450}"/>
+    <hyperlink ref="D58" r:id="rId164" xr:uid="{919F2C2C-62F0-4C8A-9785-233396A60613}"/>
+    <hyperlink ref="E58" r:id="rId165" xr:uid="{1E52A1A8-4704-4A25-8CEC-F89177A70432}"/>
+    <hyperlink ref="D59" r:id="rId166" xr:uid="{707A19C4-4FA3-438C-B15B-93A62BA351CF}"/>
+    <hyperlink ref="E59" r:id="rId167" xr:uid="{2443E35E-BC71-4101-8147-FA7277B1A04D}"/>
+    <hyperlink ref="B59" r:id="rId168" xr:uid="{597780D5-57AF-44E3-BC1D-DF5DF0B564E3}"/>
+    <hyperlink ref="D60" r:id="rId169" xr:uid="{9957E43F-25F9-4AD6-AF02-3042376D2CBC}"/>
+    <hyperlink ref="E60" r:id="rId170" xr:uid="{0A83859D-98FA-4037-A2BE-FA8F7CBE6E46}"/>
+    <hyperlink ref="B60" r:id="rId171" xr:uid="{2A7D74A8-8B5D-46CE-9350-0FAC4655511B}"/>
+    <hyperlink ref="D61" r:id="rId172" xr:uid="{0E22EB11-B3F4-4B3D-9949-5BB47BE472FF}"/>
+    <hyperlink ref="E61" r:id="rId173" xr:uid="{203E2512-19F8-444F-B5FE-FCEFA21380D9}"/>
+    <hyperlink ref="B61" r:id="rId174" xr:uid="{D42B148C-2E41-45DC-9406-03F899255054}"/>
+    <hyperlink ref="D62" r:id="rId175" xr:uid="{E8A08F00-2B07-41D3-BECA-92E437337767}"/>
+    <hyperlink ref="E62" r:id="rId176" xr:uid="{CC57E1D3-F163-4C30-A8C6-CA03AA34248D}"/>
+    <hyperlink ref="B62" r:id="rId177" xr:uid="{758C4E99-7187-45B3-B96E-4E1A344950BB}"/>
+    <hyperlink ref="D63" r:id="rId178" xr:uid="{8D6FE8C4-9089-409E-AC71-07A6BA994DD8}"/>
+    <hyperlink ref="E63" r:id="rId179" xr:uid="{C0915D43-2F9A-44CA-AA9B-2D6F571A6531}"/>
+    <hyperlink ref="B63" r:id="rId180" xr:uid="{BD35CE35-8B49-4F57-A541-E8AB4942E01C}"/>
+    <hyperlink ref="D64" r:id="rId181" xr:uid="{AD3B2EB4-61E6-4EC2-B841-C66ABAF57A8D}"/>
+    <hyperlink ref="E64" r:id="rId182" xr:uid="{CA19CD5B-D261-46F6-A06C-A6DD329847C8}"/>
+    <hyperlink ref="B64" r:id="rId183" xr:uid="{902A512C-7DB9-483B-922E-9EC9EB0A5727}"/>
+    <hyperlink ref="D65" r:id="rId184" xr:uid="{D37A5DB7-6170-4DB3-A6C4-6B7C3536BB6A}"/>
+    <hyperlink ref="E65" r:id="rId185" xr:uid="{5BE49E4F-CE72-4598-A298-9EA3583C9BB4}"/>
+    <hyperlink ref="B65" r:id="rId186" xr:uid="{218FE68B-E3EA-48FD-B04F-F05EC4D04342}"/>
+    <hyperlink ref="D66" r:id="rId187" xr:uid="{55D0245C-636D-41C8-8BEA-F7465FDF2FC1}"/>
+    <hyperlink ref="E66" r:id="rId188" xr:uid="{745BE301-751B-44AD-BB23-64393F55A01A}"/>
+    <hyperlink ref="B66" r:id="rId189" xr:uid="{72E099E5-D9E8-43F6-BA7B-AD0788C8ACDF}"/>
+    <hyperlink ref="D67" r:id="rId190" xr:uid="{670FA2F5-7537-44F0-A891-BC8F9FB0FDA1}"/>
+    <hyperlink ref="E67" r:id="rId191" xr:uid="{C44FBCC9-F7D2-411F-B321-7ACCA7BDB113}"/>
+    <hyperlink ref="B67" r:id="rId192" xr:uid="{7AAC8125-2903-4BEF-861C-0652EB8A1EBA}"/>
+    <hyperlink ref="D68" r:id="rId193" xr:uid="{4247E04D-3AB7-4CE4-8D6E-225BEB05B2EC}"/>
+    <hyperlink ref="E68" r:id="rId194" xr:uid="{3F6A67C6-2350-4E0B-855A-7A0CA546CADA}"/>
+    <hyperlink ref="B68" r:id="rId195" xr:uid="{EDAF1894-D1E3-4CB7-A453-D26D0CE785FC}"/>
+    <hyperlink ref="B69" r:id="rId196" xr:uid="{60D8C8EA-A2CC-4EC4-93CF-D8C6F9145025}"/>
+    <hyperlink ref="D69" r:id="rId197" xr:uid="{F6B676D4-F9FF-4FAC-BF4F-6B297B8E4386}"/>
+    <hyperlink ref="E69" r:id="rId198" xr:uid="{AD04D2E5-748B-41B8-A77F-6FE55DE52558}"/>
+    <hyperlink ref="D70" r:id="rId199" xr:uid="{2919C844-F24C-4EBC-BBC0-393934ACE57D}"/>
+    <hyperlink ref="E70" r:id="rId200" xr:uid="{16E264FE-A51B-4307-BAC2-77D48753B271}"/>
+    <hyperlink ref="D71" r:id="rId201" xr:uid="{923213AD-4D4E-456F-B24C-29D5EE8D2DC5}"/>
+    <hyperlink ref="E71" r:id="rId202" xr:uid="{0FB2A237-55E7-482E-BFDD-773D6CA63339}"/>
+    <hyperlink ref="D72" r:id="rId203" xr:uid="{0FB5C72B-F07D-4BAE-8F9A-333776CD5938}"/>
+    <hyperlink ref="E72" r:id="rId204" xr:uid="{1E54D0E6-426F-4655-B12E-6919FDCF820A}"/>
+    <hyperlink ref="B71" r:id="rId205" xr:uid="{6F4BDAA6-1768-40E1-BA7A-3A7B8F3E9DDF}"/>
+    <hyperlink ref="B72" r:id="rId206" xr:uid="{EBBCEFF8-5BDF-4051-A5A6-449AB5359B3C}"/>
+    <hyperlink ref="E73" r:id="rId207" xr:uid="{BE30CFAC-63AD-4E25-9DE4-2BF7C9B898E5}"/>
+    <hyperlink ref="D73" r:id="rId208" xr:uid="{3A9183DE-FD11-4043-B1A6-6E9E780E188A}"/>
+    <hyperlink ref="B73" r:id="rId209" xr:uid="{39C6DCAA-BE89-4B4F-BAB3-B01A8C5FED4E}"/>
+    <hyperlink ref="B74" r:id="rId210" xr:uid="{BD8ABE7B-7146-4F9C-B38C-CE77AC97911C}"/>
+    <hyperlink ref="D74" r:id="rId211" xr:uid="{575F04ED-6CE7-4807-8B13-F326EF7B2C8E}"/>
+    <hyperlink ref="E74" r:id="rId212" xr:uid="{681838FB-70EA-419D-BCE3-E08F5364A2E0}"/>
+    <hyperlink ref="D75" r:id="rId213" xr:uid="{4BFFDDEF-9B37-49D7-8898-707DFDE3F5A2}"/>
+    <hyperlink ref="E75" r:id="rId214" xr:uid="{9B9DFAF3-C1E1-423C-B6F9-E51D877DDB12}"/>
+    <hyperlink ref="B75" r:id="rId215" xr:uid="{59F2747A-CC65-4ED5-A56B-786A043CE67B}"/>
+    <hyperlink ref="D76" r:id="rId216" xr:uid="{ECC3D6DF-5B1B-4DC1-B19F-8886FD8EB116}"/>
+    <hyperlink ref="E76" r:id="rId217" xr:uid="{12F9552E-0BC3-4624-9123-B55AFBCCB562}"/>
+    <hyperlink ref="E77" r:id="rId218" xr:uid="{75179926-30E5-4350-921B-A5B14E1B232D}"/>
+    <hyperlink ref="B76" r:id="rId219" xr:uid="{EA078301-086A-4811-A4E1-A4C2AAE42D90}"/>
+    <hyperlink ref="D77" r:id="rId220" xr:uid="{C965BAE7-26E3-47CA-A128-1A1426B08287}"/>
+    <hyperlink ref="B77" r:id="rId221" xr:uid="{08F176CD-1942-484A-B91A-5E7D7BE2E642}"/>
+    <hyperlink ref="D78" r:id="rId222" xr:uid="{61B038FC-067A-4428-85A1-623DE325F1ED}"/>
+    <hyperlink ref="E78" r:id="rId223" xr:uid="{BB3648F4-8B0F-4A80-8F41-403E4053E2DA}"/>
+    <hyperlink ref="B78" r:id="rId224" xr:uid="{B824C2FD-2669-4F5E-A3AB-CBE4E6052B0C}"/>
+    <hyperlink ref="B79" r:id="rId225" xr:uid="{4654EB0D-7573-4009-B0CF-95DC2A913755}"/>
+    <hyperlink ref="D79" r:id="rId226" xr:uid="{8D237BAA-60AB-4BA0-B2C0-B05074E53B92}"/>
+    <hyperlink ref="E79" r:id="rId227" xr:uid="{C1E57DEC-20E0-487A-A1F8-F2C132F19122}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId76"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId228"/>
 </worksheet>
 </file>
 
@@ -6388,10 +7831,10 @@
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5" s="85" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="B5" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="C5" s="73" t="s">
         <v>142</v>
@@ -6517,10 +7960,10 @@
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.35">
       <c r="C14" s="85" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="D14" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="X14" s="79" t="s">
         <v>416</v>

--- a/Info/Additional_information.xlsx
+++ b/Info/Additional_information.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{034E2343-17F9-4569-9033-511EDAB51CD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{307CE2A6-F4AC-4756-B7A5-E82FDDC593C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Colours_specifications" sheetId="1" r:id="rId1"/>
@@ -24,11 +24,11 @@
     <sheet name="File_Naming" sheetId="2" r:id="rId9"/>
     <sheet name="Existing_subtypes" sheetId="3" r:id="rId10"/>
     <sheet name="Links_to_Data" sheetId="7" r:id="rId11"/>
-    <sheet name="Library_Link" sheetId="13" r:id="rId12"/>
+    <sheet name="Library_Links" sheetId="13" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">albums_buttons!$A$1:$E$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">albums_ID!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">albums_ID!$A$1:$E$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Colours_specifications!$A$1:$D$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'EURO albums content'!$A$1:$C$15</definedName>
   </definedNames>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1188" uniqueCount="855">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1217" uniqueCount="855">
   <si>
     <t>good quality (UNC for UNC collection; UNC and XF for XF collection)</t>
   </si>
@@ -1273,9 +1273,6 @@
     <t>Album ID</t>
   </si>
   <si>
-    <t>Album hardcoded link</t>
-  </si>
-  <si>
     <t>FB</t>
   </si>
   <si>
@@ -1663,9 +1660,6 @@
     <t>A000-00-00-00</t>
   </si>
   <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A000-00-00-00.html</t>
-  </si>
-  <si>
     <t>A001-06-GD-BK</t>
   </si>
   <si>
@@ -1678,18 +1672,6 @@
     <t>A001-02-GD-BK</t>
   </si>
   <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A001-01-GD-BK.html</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A001-02-GD-BK.html</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A001-03-GD-BK.html</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A001-04-GD-BK.html</t>
-  </si>
-  <si>
     <t>#</t>
   </si>
   <si>
@@ -1699,48 +1681,24 @@
     <t>A002-01-OA-BK</t>
   </si>
   <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A002-01-OA-BK.html</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A002-02-OA-BK.html</t>
-  </si>
-  <si>
     <t>A003-01-OA-DB</t>
   </si>
   <si>
     <t>A003-02-OA-DB</t>
   </si>
   <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A003-01-OA-DB.html</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A003-02-OA-DB.html</t>
-  </si>
-  <si>
     <t>A004-01-OA-BK</t>
   </si>
   <si>
     <t>A004-02-OA-BK</t>
   </si>
   <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A004-01-OA-BK.html</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A004-02-OA-BK.html</t>
-  </si>
-  <si>
     <t>A005-01-OA-BK</t>
   </si>
   <si>
     <t>A005-02-OA-BK</t>
   </si>
   <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A005-01-OA-BK.html</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A005-02-OA-BK.html</t>
-  </si>
-  <si>
     <t xml:space="preserve">Регулярные монеты РФ </t>
   </si>
   <si>
@@ -1756,9 +1714,6 @@
     <t>A006-01-OA-BU</t>
   </si>
   <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A006-01-OA-BU.html</t>
-  </si>
-  <si>
     <t>USSR commemorative and regular coins</t>
   </si>
   <si>
@@ -1768,15 +1723,9 @@
     <t>A007-01-OA-BK</t>
   </si>
   <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A007-01-OA-BK.html</t>
-  </si>
-  <si>
     <t>A008-01-OA-BK</t>
   </si>
   <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A008-01-OA-BK.html</t>
-  </si>
-  <si>
     <t>DN</t>
   </si>
   <si>
@@ -1804,42 +1753,21 @@
     <t>Spain and Canada regular and commemorative coins</t>
   </si>
   <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A009-03-FB-BN.html</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A009-04-FB-DN.html</t>
-  </si>
-  <si>
     <t>Банкноты мира</t>
   </si>
   <si>
     <t>World banknotes</t>
   </si>
   <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A010-01-OA-DB.html</t>
-  </si>
-  <si>
     <t>Tickets (part 1) to the theater, museums, concerts and performances</t>
   </si>
   <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A011-01-OA-GR.html</t>
-  </si>
-  <si>
     <t>Билеты (часть 1) в театры, музеи, на концерты и спектакли</t>
   </si>
   <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A011-02-OA-GR.html</t>
-  </si>
-  <si>
     <t>Tickets (part 2) for parks, cinemas, special events, trains, and planes. Various tokens</t>
   </si>
   <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A012-01-OA-BU.html</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A013-01-OA-LN.html</t>
-  </si>
-  <si>
     <t>Пластиковые карты</t>
   </si>
   <si>
@@ -1849,18 +1777,6 @@
     <t>A009-01-FB-LN</t>
   </si>
   <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A009-01-FB-LN.html</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A009-02-FB-LN.html</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A001-05-GD-BK.html</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A001-06-GD-BK.html</t>
-  </si>
-  <si>
     <t>https://dartalexator.github.io/CoinCollection/index.html</t>
   </si>
   <si>
@@ -2645,6 +2561,90 @@
   </si>
   <si>
     <t>💳</t>
+  </si>
+  <si>
+    <t>Hard Link</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A000-00-00-00</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A001-01-GD-BK</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A001-02-GD-BK</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A001-03-GD-BK</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A001-04-GD-BK</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A001-05-GD-BK</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A001-06-GD-BK</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A002-01-OA-BK</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A002-02-OA-BK</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A003-01-OA-DB</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A003-02-OA-DB</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A004-01-OA-BK</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A004-02-OA-BK</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A005-01-OA-BK</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A005-02-OA-BK</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A006-01-OA-BU</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A007-01-OA-BK</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A008-01-OA-BK</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A009-01-FB-LN</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A010-01-FB-LN</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A011-01-FB-BN</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A011-02-FB-DN</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A012-01-OA-DB</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A013-01-OA-GR</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A013-02-OA-GR</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A014-01-OA-BU</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A015-01-OA-LN</t>
   </si>
 </sst>
 </file>
@@ -3246,7 +3246,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3476,6 +3476,8 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="12" fillId="20" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3527,14 +3529,63 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="34">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -4019,54 +4070,6 @@
         </horizontal>
       </border>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -4135,44 +4138,44 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{973D7237-72C7-453E-A0E1-526C93326B28}" name="Таблица3" displayName="Таблица3" ref="A1:F51" totalsRowShown="0" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{973D7237-72C7-453E-A0E1-526C93326B28}" name="Таблица3" displayName="Таблица3" ref="A1:F51" totalsRowShown="0" headerRowDxfId="33" dataDxfId="31" headerRowBorderDxfId="32" tableBorderDxfId="30" totalsRowBorderDxfId="29">
   <autoFilter ref="A1:F51" xr:uid="{A2D8FA3D-4024-4365-BE1D-F93D0AF2D426}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{12C2DF0B-47FA-46A4-8424-55A1488EF88B}" name="ID" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{EB0B36CE-168D-429E-896D-DBA54794224F}" name="Name_Eng" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{6C3A2CE8-252E-4C52-985B-8CDDFD9FA0C7}" name="OfficialMintName_Native" dataDxfId="20"/>
-    <tableColumn id="8" xr3:uid="{DA5871DC-2EDB-49C0-953E-EC0F70288E21}" name="Country" dataDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{FCD85F85-A94E-4BBE-9D3B-2B7494638375}" name="Mint_City" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{E5141978-CA91-4DE9-86F1-8A8AFA716534}" name="Alias" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{12C2DF0B-47FA-46A4-8424-55A1488EF88B}" name="ID" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{EB0B36CE-168D-429E-896D-DBA54794224F}" name="Name_Eng" dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{6C3A2CE8-252E-4C52-985B-8CDDFD9FA0C7}" name="OfficialMintName_Native" dataDxfId="26"/>
+    <tableColumn id="8" xr3:uid="{DA5871DC-2EDB-49C0-953E-EC0F70288E21}" name="Country" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{FCD85F85-A94E-4BBE-9D3B-2B7494638375}" name="Mint_City" dataDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{E5141978-CA91-4DE9-86F1-8A8AFA716534}" name="Alias" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D0DCC88A-2D36-4004-A694-FC0C0F0C3396}" name="Таблица2" displayName="Таблица2" ref="A1:C16" totalsRowShown="0" headerRowBorderDxfId="16" tableBorderDxfId="15" totalsRowBorderDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D0DCC88A-2D36-4004-A694-FC0C0F0C3396}" name="Таблица2" displayName="Таблица2" ref="A1:C16" totalsRowShown="0" headerRowBorderDxfId="22" tableBorderDxfId="21" totalsRowBorderDxfId="20">
   <autoFilter ref="A1:C16" xr:uid="{00000000-0009-0000-0100-000002000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{28358E6A-6F3A-468C-9E1C-880A34D9BECE}" name="№" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{28358E6A-6F3A-468C-9E1C-880A34D9BECE}" name="№" dataDxfId="19"/>
     <tableColumn id="2" xr3:uid="{DD0AD5C8-324B-4DA7-B39F-B2DB3EF91222}" name="Links:"/>
-    <tableColumn id="3" xr3:uid="{FC8A6018-CA7E-4C73-9B21-B272B55FA8C1}" name="Description:" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{FC8A6018-CA7E-4C73-9B21-B272B55FA8C1}" name="Description:" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9D0F8E3D-96B1-4DB8-B1A6-8DD6B84F3693}" name="Таблица35" displayName="Таблица35" ref="A1:D52" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10" tableBorderDxfId="8" totalsRowBorderDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9D0F8E3D-96B1-4DB8-B1A6-8DD6B84F3693}" name="Таблица35" displayName="Таблица35" ref="A1:D52" totalsRowShown="0" headerRowDxfId="17" dataDxfId="15" headerRowBorderDxfId="16" tableBorderDxfId="14" totalsRowBorderDxfId="13">
   <autoFilter ref="A1:D52" xr:uid="{A2D8FA3D-4024-4365-BE1D-F93D0AF2D426}"/>
   <tableColumns count="4">
-    <tableColumn id="4" xr3:uid="{74AFB32D-7AAA-46BE-8174-ED698BB4613E}" name="Mint_id" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{523D65CD-0F56-441F-90B5-E46A9B14F0D0}" name="Ekaterinburg Mint" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{1AAB7352-E935-4EC6-A0D1-3EDC5D0BC93C}" name="Year_of_start" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{5FF15381-476A-4F88-B93A-6452F2830A0A}" name="Year_of_end" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{74AFB32D-7AAA-46BE-8174-ED698BB4613E}" name="Mint_id" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{523D65CD-0F56-441F-90B5-E46A9B14F0D0}" name="Ekaterinburg Mint" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{1AAB7352-E935-4EC6-A0D1-3EDC5D0BC93C}" name="Year_of_start" dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{5FF15381-476A-4F88-B93A-6452F2830A0A}" name="Year_of_end" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4186,9 +4189,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{8354E581-3B48-4762-81A7-EA76E36C4BB5}" name="№" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{1F45DC85-8ECA-45FE-BF45-E528619CEE0E}" name="Links:" dataDxfId="1" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{3FAE616B-3296-4770-9E56-8A824991EECA}" name="Description:" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{8354E581-3B48-4762-81A7-EA76E36C4BB5}" name="№" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{1F45DC85-8ECA-45FE-BF45-E528619CEE0E}" name="Links:" dataDxfId="7" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{3FAE616B-3296-4770-9E56-8A824991EECA}" name="Description:" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -4579,12 +4582,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C7:C8">
-    <cfRule type="containsText" dxfId="33" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C7))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6">
-    <cfRule type="containsText" dxfId="32" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="4" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C6))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4601,7 +4604,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2">
-    <cfRule type="containsText" dxfId="31" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="3" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C2))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4618,7 +4621,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4">
-    <cfRule type="containsText" dxfId="30" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="2" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C4))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4635,7 +4638,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C5">
-    <cfRule type="containsText" dxfId="29" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="1" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C5))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4652,7 +4655,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3">
-    <cfRule type="containsText" dxfId="28" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C3))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -5089,47 +5092,355 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D5AF97D-14BA-4E23-B5FF-856D52BDA29A}">
-  <dimension ref="B7:Z7"/>
+  <dimension ref="A1:Y30"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="9.453125" customWidth="1"/>
+    <col min="1" max="1" width="4.08984375" customWidth="1"/>
+    <col min="2" max="2" width="17.1796875" customWidth="1"/>
+    <col min="3" max="3" width="81.08984375" customWidth="1"/>
+    <col min="4" max="5" width="8.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="7" spans="2:26" ht="61.5" x14ac:dyDescent="1.35">
-      <c r="B7" s="106" t="s">
-        <v>593</v>
-      </c>
-      <c r="C7" s="107"/>
-      <c r="D7" s="107"/>
-      <c r="E7" s="107"/>
-      <c r="F7" s="107"/>
-      <c r="G7" s="107"/>
-      <c r="H7" s="107"/>
-      <c r="I7" s="107"/>
-      <c r="J7" s="107"/>
-      <c r="K7" s="107"/>
-      <c r="L7" s="107"/>
-      <c r="M7" s="107"/>
-      <c r="N7" s="107"/>
-      <c r="O7" s="107"/>
-      <c r="P7" s="107"/>
-      <c r="Q7" s="107"/>
-      <c r="R7" s="107"/>
-      <c r="S7" s="107"/>
-      <c r="T7" s="107"/>
-      <c r="U7" s="107"/>
-      <c r="V7" s="107"/>
-      <c r="W7" s="107"/>
-      <c r="X7" s="107"/>
-      <c r="Y7" s="107"/>
-      <c r="Z7" s="107"/>
+    <row r="1" spans="1:25" ht="61.5" x14ac:dyDescent="1.35">
+      <c r="A1" s="87" t="s">
+        <v>565</v>
+      </c>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="88"/>
+      <c r="M1" s="88"/>
+      <c r="N1" s="88"/>
+      <c r="O1" s="88"/>
+      <c r="P1" s="88"/>
+      <c r="Q1" s="88"/>
+      <c r="R1" s="88"/>
+      <c r="S1" s="88"/>
+      <c r="T1" s="88"/>
+      <c r="U1" s="88"/>
+      <c r="V1" s="88"/>
+      <c r="W1" s="88"/>
+      <c r="X1" s="88"/>
+      <c r="Y1" s="88"/>
+    </row>
+    <row r="3" spans="1:25" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="A3" s="108" t="s">
+        <v>530</v>
+      </c>
+      <c r="B3" s="78" t="s">
+        <v>396</v>
+      </c>
+      <c r="C3" s="78" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>525</v>
+      </c>
+      <c r="C4" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
+        <v>524</v>
+      </c>
+      <c r="C5" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6" t="s">
+        <v>529</v>
+      </c>
+      <c r="C6" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>521</v>
+      </c>
+      <c r="C7" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>528</v>
+      </c>
+      <c r="C8" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>5</v>
+      </c>
+      <c r="B9" t="s">
+        <v>527</v>
+      </c>
+      <c r="C9" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>6</v>
+      </c>
+      <c r="B10" t="s">
+        <v>526</v>
+      </c>
+      <c r="C10" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
+        <v>532</v>
+      </c>
+      <c r="C11" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>8</v>
+      </c>
+      <c r="B12" t="s">
+        <v>531</v>
+      </c>
+      <c r="C12" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>9</v>
+      </c>
+      <c r="B13" t="s">
+        <v>533</v>
+      </c>
+      <c r="C13" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>10</v>
+      </c>
+      <c r="B14" t="s">
+        <v>534</v>
+      </c>
+      <c r="C14" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>11</v>
+      </c>
+      <c r="B15" t="s">
+        <v>535</v>
+      </c>
+      <c r="C15" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>12</v>
+      </c>
+      <c r="B16" t="s">
+        <v>536</v>
+      </c>
+      <c r="C16" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>13</v>
+      </c>
+      <c r="B17" t="s">
+        <v>537</v>
+      </c>
+      <c r="C17" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>14</v>
+      </c>
+      <c r="B18" t="s">
+        <v>538</v>
+      </c>
+      <c r="C18" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>543</v>
+      </c>
+      <c r="C19" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>16</v>
+      </c>
+      <c r="B20" t="s">
+        <v>546</v>
+      </c>
+      <c r="C20" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>17</v>
+      </c>
+      <c r="B21" t="s">
+        <v>547</v>
+      </c>
+      <c r="C21" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>18</v>
+      </c>
+      <c r="B22" t="s">
+        <v>564</v>
+      </c>
+      <c r="C22" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>19</v>
+      </c>
+      <c r="B23" t="s">
+        <v>804</v>
+      </c>
+      <c r="C23" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>20</v>
+      </c>
+      <c r="B24" t="s">
+        <v>805</v>
+      </c>
+      <c r="C24" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>21</v>
+      </c>
+      <c r="B25" t="s">
+        <v>806</v>
+      </c>
+      <c r="C25" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>22</v>
+      </c>
+      <c r="B26" t="s">
+        <v>807</v>
+      </c>
+      <c r="C26" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>23</v>
+      </c>
+      <c r="B27" t="s">
+        <v>808</v>
+      </c>
+      <c r="C27" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>24</v>
+      </c>
+      <c r="B28" t="s">
+        <v>809</v>
+      </c>
+      <c r="C28" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>25</v>
+      </c>
+      <c r="B29" t="s">
+        <v>810</v>
+      </c>
+      <c r="C29" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>26</v>
+      </c>
+      <c r="B30" t="s">
+        <v>811</v>
+      </c>
+      <c r="C30" t="s">
+        <v>854</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B7:Z7"/>
-  </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B7" r:id="rId1" xr:uid="{1B51AF5A-9579-4E45-802C-86E0D9768BAB}"/>
+    <hyperlink ref="A1" r:id="rId1" xr:uid="{1B51AF5A-9579-4E45-802C-86E0D9768BAB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5169,10 +5480,10 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" s="93">
+      <c r="A2" s="95">
         <v>1</v>
       </c>
-      <c r="B2" s="101">
+      <c r="B2" s="103">
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
@@ -5189,8 +5500,8 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" s="94"/>
-      <c r="B3" s="101"/>
+      <c r="A3" s="96"/>
+      <c r="B3" s="103"/>
       <c r="C3" s="4" t="s">
         <v>65</v>
       </c>
@@ -5205,8 +5516,8 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" s="95"/>
-      <c r="B4" s="102">
+      <c r="A4" s="97"/>
+      <c r="B4" s="104">
         <v>2</v>
       </c>
       <c r="C4" s="4" t="s">
@@ -5223,14 +5534,14 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" s="95"/>
-      <c r="B5" s="102"/>
+      <c r="A5" s="97"/>
+      <c r="B5" s="104"/>
       <c r="C5" s="4" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6" s="95"/>
+      <c r="A6" s="97"/>
       <c r="B6" s="15">
         <v>3</v>
       </c>
@@ -5239,7 +5550,7 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" s="95"/>
+      <c r="A7" s="97"/>
       <c r="B7" s="16" t="s">
         <v>90</v>
       </c>
@@ -5248,8 +5559,8 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" s="95"/>
-      <c r="B8" s="103">
+      <c r="A8" s="97"/>
+      <c r="B8" s="105">
         <v>6</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -5257,14 +5568,14 @@
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="95"/>
-      <c r="B9" s="104"/>
+      <c r="A9" s="97"/>
+      <c r="B9" s="106"/>
       <c r="C9" s="4" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A10" s="95"/>
+      <c r="A10" s="97"/>
       <c r="B10" s="17">
         <v>7</v>
       </c>
@@ -5273,14 +5584,14 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="95"/>
+      <c r="A11" s="97"/>
       <c r="B11" s="24"/>
       <c r="C11" s="4" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="95"/>
+      <c r="A12" s="97"/>
       <c r="B12" s="18">
         <v>8</v>
       </c>
@@ -5289,7 +5600,7 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" s="96"/>
+      <c r="A13" s="98"/>
       <c r="B13" s="25" t="s">
         <v>78</v>
       </c>
@@ -5298,7 +5609,7 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="97"/>
+      <c r="A14" s="99"/>
       <c r="B14" s="26" t="s">
         <v>91</v>
       </c>
@@ -5307,7 +5618,7 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="14.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="98">
+      <c r="A15" s="100">
         <v>2</v>
       </c>
       <c r="B15" s="19" t="s">
@@ -5318,7 +5629,7 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="99"/>
+      <c r="A16" s="101"/>
       <c r="B16" s="20" t="s">
         <v>365</v>
       </c>
@@ -5327,7 +5638,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="99"/>
+      <c r="A17" s="101"/>
       <c r="B17" s="21" t="s">
         <v>366</v>
       </c>
@@ -5336,7 +5647,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="100"/>
+      <c r="A18" s="102"/>
       <c r="B18" s="22" t="s">
         <v>92</v>
       </c>
@@ -5345,7 +5656,7 @@
       </c>
     </row>
     <row r="19" spans="1:3" ht="14.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="87">
+      <c r="A19" s="89">
         <v>3</v>
       </c>
       <c r="B19" s="23" t="s">
@@ -5356,7 +5667,7 @@
       </c>
     </row>
     <row r="20" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="88"/>
+      <c r="A20" s="90"/>
       <c r="B20" s="27" t="s">
         <v>93</v>
       </c>
@@ -5365,7 +5676,7 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="89"/>
+      <c r="A21" s="91"/>
       <c r="B21" s="28" t="s">
         <v>95</v>
       </c>
@@ -5374,7 +5685,7 @@
       </c>
     </row>
     <row r="22" spans="1:3" ht="14.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="90">
+      <c r="A22" s="92">
         <v>4</v>
       </c>
       <c r="B22" s="19" t="s">
@@ -5385,7 +5696,7 @@
       </c>
     </row>
     <row r="23" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="91"/>
+      <c r="A23" s="93"/>
       <c r="B23" s="20" t="s">
         <v>98</v>
       </c>
@@ -5394,7 +5705,7 @@
       </c>
     </row>
     <row r="24" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="91"/>
+      <c r="A24" s="93"/>
       <c r="B24" s="21" t="s">
         <v>100</v>
       </c>
@@ -5403,7 +5714,7 @@
       </c>
     </row>
     <row r="25" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="91"/>
+      <c r="A25" s="93"/>
       <c r="B25" s="16" t="s">
         <v>102</v>
       </c>
@@ -5412,7 +5723,7 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" s="91"/>
+      <c r="A26" s="93"/>
       <c r="B26" s="29" t="s">
         <v>104</v>
       </c>
@@ -5421,7 +5732,7 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" s="91"/>
+      <c r="A27" s="93"/>
       <c r="B27" s="30" t="s">
         <v>106</v>
       </c>
@@ -5430,7 +5741,7 @@
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" s="91"/>
+      <c r="A28" s="93"/>
       <c r="B28" s="18">
         <v>8</v>
       </c>
@@ -5439,7 +5750,7 @@
       </c>
     </row>
     <row r="29" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="92"/>
+      <c r="A29" s="94"/>
       <c r="B29" s="31" t="s">
         <v>78</v>
       </c>
@@ -5469,611 +5780,497 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DC835FD-69FE-4DBC-957F-9A46CA05517E}">
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.453125" customWidth="1"/>
     <col min="2" max="2" width="15.54296875" customWidth="1"/>
     <col min="3" max="3" width="70" customWidth="1"/>
     <col min="4" max="4" width="89.08984375" customWidth="1"/>
-    <col min="5" max="5" width="84.6328125" customWidth="1"/>
-    <col min="6" max="6" width="182.36328125" customWidth="1"/>
+    <col min="5" max="5" width="182.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="78" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="B1" s="78" t="s">
         <v>396</v>
       </c>
       <c r="C1" s="78" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D1" s="78" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E1" s="78" t="s">
-        <v>397</v>
-      </c>
-      <c r="F1" s="78" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D2" t="s">
-        <v>523</v>
-      </c>
-      <c r="E2" s="83" t="s">
-        <v>527</v>
-      </c>
-      <c r="F2" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+        <v>522</v>
+      </c>
+      <c r="E2" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C3" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D3" t="s">
-        <v>503</v>
-      </c>
-      <c r="E3" s="83" t="s">
-        <v>532</v>
-      </c>
-      <c r="F3" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+        <v>502</v>
+      </c>
+      <c r="E3" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C4" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D4" t="s">
-        <v>504</v>
-      </c>
-      <c r="E4" s="83" t="s">
-        <v>533</v>
-      </c>
-      <c r="F4" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+        <v>503</v>
+      </c>
+      <c r="E4" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C5" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D5" t="s">
-        <v>505</v>
-      </c>
-      <c r="E5" s="83" t="s">
-        <v>534</v>
-      </c>
-      <c r="F5" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+        <v>504</v>
+      </c>
+      <c r="E5" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C6" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D6" t="s">
-        <v>500</v>
-      </c>
-      <c r="E6" s="83" t="s">
-        <v>535</v>
-      </c>
-      <c r="F6" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+        <v>499</v>
+      </c>
+      <c r="E6" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C7" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D7" t="s">
-        <v>499</v>
-      </c>
-      <c r="E7" s="83" t="s">
-        <v>591</v>
-      </c>
-      <c r="F7" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+        <v>498</v>
+      </c>
+      <c r="E7" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C8" t="s">
+        <v>496</v>
+      </c>
+      <c r="D8" t="s">
         <v>497</v>
       </c>
-      <c r="D8" t="s">
-        <v>498</v>
-      </c>
-      <c r="E8" s="83" t="s">
-        <v>592</v>
-      </c>
-      <c r="F8" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="E8" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="C9" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D9" t="s">
-        <v>509</v>
-      </c>
-      <c r="E9" s="83" t="s">
-        <v>539</v>
-      </c>
-      <c r="F9" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+        <v>508</v>
+      </c>
+      <c r="E9" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="C10" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D10" t="s">
-        <v>508</v>
-      </c>
-      <c r="E10" s="83" t="s">
-        <v>540</v>
-      </c>
-      <c r="F10" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+        <v>507</v>
+      </c>
+      <c r="E10" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="C11" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D11" t="s">
-        <v>510</v>
-      </c>
-      <c r="E11" s="83" t="s">
-        <v>543</v>
-      </c>
-      <c r="F11" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+        <v>509</v>
+      </c>
+      <c r="E11" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="C12" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D12" t="s">
-        <v>511</v>
-      </c>
-      <c r="E12" s="83" t="s">
-        <v>544</v>
-      </c>
-      <c r="F12" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+        <v>510</v>
+      </c>
+      <c r="E12" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="C13" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D13" t="s">
-        <v>512</v>
-      </c>
-      <c r="E13" s="83" t="s">
-        <v>547</v>
-      </c>
-      <c r="F13" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+        <v>511</v>
+      </c>
+      <c r="E13" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="C14" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D14" t="s">
-        <v>513</v>
-      </c>
-      <c r="E14" s="83" t="s">
-        <v>548</v>
-      </c>
-      <c r="F14" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+        <v>512</v>
+      </c>
+      <c r="E14" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="C15" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D15" t="s">
-        <v>520</v>
-      </c>
-      <c r="E15" s="83" t="s">
-        <v>551</v>
-      </c>
-      <c r="F15" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+        <v>519</v>
+      </c>
+      <c r="E15" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>550</v>
+        <v>538</v>
       </c>
       <c r="C16" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D16" t="s">
-        <v>521</v>
-      </c>
-      <c r="E16" s="83" t="s">
-        <v>552</v>
-      </c>
-      <c r="F16" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+        <v>520</v>
+      </c>
+      <c r="E16" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>557</v>
+        <v>543</v>
       </c>
       <c r="C17" t="s">
-        <v>554</v>
+        <v>540</v>
       </c>
       <c r="D17" t="s">
-        <v>553</v>
-      </c>
-      <c r="E17" s="83" t="s">
-        <v>558</v>
-      </c>
-      <c r="F17" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+        <v>539</v>
+      </c>
+      <c r="E17" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>561</v>
+        <v>546</v>
       </c>
       <c r="C18" t="s">
-        <v>559</v>
+        <v>544</v>
       </c>
       <c r="D18" t="s">
-        <v>560</v>
-      </c>
-      <c r="E18" s="83" t="s">
-        <v>562</v>
-      </c>
-      <c r="F18" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+        <v>545</v>
+      </c>
+      <c r="E18" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>563</v>
+        <v>547</v>
       </c>
       <c r="C19" t="s">
-        <v>573</v>
+        <v>556</v>
       </c>
       <c r="D19" t="s">
-        <v>611</v>
-      </c>
-      <c r="E19" s="83" t="s">
-        <v>564</v>
-      </c>
-      <c r="F19" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+        <v>583</v>
+      </c>
+      <c r="E19" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>588</v>
+        <v>564</v>
       </c>
       <c r="C20" t="s">
-        <v>569</v>
+        <v>552</v>
       </c>
       <c r="D20" t="s">
-        <v>570</v>
-      </c>
-      <c r="E20" s="83" t="s">
-        <v>589</v>
-      </c>
-      <c r="F20" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+        <v>553</v>
+      </c>
+      <c r="E20" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>832</v>
+        <v>804</v>
       </c>
       <c r="C21" t="s">
-        <v>571</v>
+        <v>554</v>
       </c>
       <c r="D21" t="s">
-        <v>572</v>
-      </c>
-      <c r="E21" s="83" t="s">
-        <v>590</v>
-      </c>
-      <c r="F21" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+        <v>555</v>
+      </c>
+      <c r="E21" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>833</v>
+        <v>805</v>
       </c>
       <c r="C22" t="s">
-        <v>618</v>
+        <v>590</v>
       </c>
       <c r="D22" t="s">
-        <v>617</v>
-      </c>
-      <c r="E22" s="83" t="s">
-        <v>574</v>
-      </c>
-      <c r="F22" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+        <v>589</v>
+      </c>
+      <c r="E22" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>834</v>
+        <v>806</v>
       </c>
       <c r="C23" t="s">
-        <v>619</v>
+        <v>591</v>
       </c>
       <c r="D23" t="s">
-        <v>616</v>
-      </c>
-      <c r="E23" s="83" t="s">
-        <v>575</v>
-      </c>
-      <c r="F23" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+        <v>588</v>
+      </c>
+      <c r="E23" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>835</v>
+        <v>807</v>
       </c>
       <c r="C24" t="s">
-        <v>577</v>
+        <v>558</v>
       </c>
       <c r="D24" t="s">
-        <v>576</v>
-      </c>
-      <c r="E24" s="83" t="s">
-        <v>578</v>
-      </c>
-      <c r="F24" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+        <v>557</v>
+      </c>
+      <c r="E24" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>836</v>
+        <v>808</v>
       </c>
       <c r="C25" t="s">
-        <v>579</v>
+        <v>559</v>
       </c>
       <c r="D25" t="s">
-        <v>581</v>
-      </c>
-      <c r="E25" s="83" t="s">
-        <v>580</v>
-      </c>
-      <c r="F25" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+        <v>560</v>
+      </c>
+      <c r="E25" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>837</v>
+        <v>809</v>
       </c>
       <c r="C26" t="s">
-        <v>583</v>
+        <v>561</v>
       </c>
       <c r="D26" t="s">
-        <v>623</v>
-      </c>
-      <c r="E26" s="83" t="s">
-        <v>582</v>
-      </c>
-      <c r="F26" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+        <v>595</v>
+      </c>
+      <c r="E26" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>838</v>
+        <v>810</v>
       </c>
       <c r="C27" t="s">
-        <v>626</v>
+        <v>598</v>
       </c>
       <c r="D27" t="s">
-        <v>625</v>
-      </c>
-      <c r="E27" s="83" t="s">
-        <v>584</v>
-      </c>
-      <c r="F27" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+        <v>597</v>
+      </c>
+      <c r="E27" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>839</v>
+        <v>811</v>
       </c>
       <c r="C28" t="s">
-        <v>587</v>
+        <v>563</v>
       </c>
       <c r="D28" t="s">
-        <v>586</v>
-      </c>
-      <c r="E28" s="83" t="s">
-        <v>585</v>
-      </c>
-      <c r="F28" t="s">
-        <v>628</v>
+        <v>562</v>
+      </c>
+      <c r="E28" t="s">
+        <v>600</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1" xr:uid="{1DC835FD-69FE-4DBC-957F-9A46CA05517E}"/>
+  <autoFilter ref="A1:E1" xr:uid="{1DC835FD-69FE-4DBC-957F-9A46CA05517E}"/>
   <phoneticPr fontId="18" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" xr:uid="{A9DAC5E2-B569-49C7-B7C7-5FB2F0F45121}"/>
-    <hyperlink ref="E3" r:id="rId2" xr:uid="{33229A5C-B9EF-446E-B26C-5E9B3367FC6A}"/>
-    <hyperlink ref="E4" r:id="rId3" xr:uid="{E92AA73C-477D-491C-B552-06044006752C}"/>
-    <hyperlink ref="E5" r:id="rId4" xr:uid="{46F4B82E-CA81-4179-8D28-AC8C124F710A}"/>
-    <hyperlink ref="E6" r:id="rId5" xr:uid="{C6A03004-EF3C-49D6-8ACE-BE0675BA0CCC}"/>
-    <hyperlink ref="E9" r:id="rId6" xr:uid="{6FD5A6C1-19A0-4B26-8171-7C4526375D06}"/>
-    <hyperlink ref="E10" r:id="rId7" xr:uid="{055F54FF-C230-49E3-8AD3-39B18FF220A9}"/>
-    <hyperlink ref="E11" r:id="rId8" xr:uid="{9F0940F2-1A8A-4E23-95C1-A7D4AE8ED2FC}"/>
-    <hyperlink ref="E12" r:id="rId9" xr:uid="{5E911F10-CBF5-4238-ADB1-11E959F15120}"/>
-    <hyperlink ref="E13" r:id="rId10" xr:uid="{8862EA93-397B-43EB-950D-E7CA51E64B3F}"/>
-    <hyperlink ref="E14" r:id="rId11" xr:uid="{8200010C-9C93-4E8D-8296-12B7EC7B60F9}"/>
-    <hyperlink ref="E15" r:id="rId12" xr:uid="{37ED73B8-7E15-4DEB-825D-F64E0DFBF76A}"/>
-    <hyperlink ref="E16" r:id="rId13" xr:uid="{5232A4EB-1465-4673-AA0F-DE4AFAAFFFF6}"/>
-    <hyperlink ref="E17" r:id="rId14" xr:uid="{BB9C39F4-10B9-4609-B013-760BBB7F8EFB}"/>
-    <hyperlink ref="E18" r:id="rId15" xr:uid="{D6DAB22F-8554-40C2-BC8F-DB4FE657DEE9}"/>
-    <hyperlink ref="E19" r:id="rId16" xr:uid="{64EBF9BB-DC33-40A2-9BE8-3F6E300B72B4}"/>
-    <hyperlink ref="E22" r:id="rId17" xr:uid="{84B2B169-2119-45C3-BD04-4482D7704951}"/>
-    <hyperlink ref="E23" r:id="rId18" xr:uid="{50B15920-8FF5-4A31-A3B6-630BFE6B7256}"/>
-    <hyperlink ref="E24" r:id="rId19" xr:uid="{CEF53131-34F9-40EB-8CC6-385E2C745B2A}"/>
-    <hyperlink ref="E25" r:id="rId20" xr:uid="{59E99A6F-25C8-4D24-898D-69FF859E9ADC}"/>
-    <hyperlink ref="E26" r:id="rId21" xr:uid="{99417517-FEFC-4B15-8968-043D037E8B12}"/>
-    <hyperlink ref="E27" r:id="rId22" xr:uid="{26F0F77D-076A-435A-A497-02AC8B18D716}"/>
-    <hyperlink ref="E28" r:id="rId23" xr:uid="{4275CB21-59E8-4194-8A88-6E70460DDA71}"/>
-    <hyperlink ref="E20" r:id="rId24" xr:uid="{A654E291-8976-4CCF-906F-52619F8C1947}"/>
-    <hyperlink ref="E21" r:id="rId25" xr:uid="{E871A1FA-77B9-4C91-B5CC-BBA3F76C259E}"/>
-    <hyperlink ref="E7" r:id="rId26" xr:uid="{E1253D1D-3D30-4B68-939D-54031E7A4705}"/>
-    <hyperlink ref="E8" r:id="rId27" xr:uid="{72D72E9D-ABBE-43E4-8111-C052FCD7B2CF}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId28"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6092,1415 +6289,1415 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>629</v>
+        <v>601</v>
       </c>
       <c r="B1" t="s">
-        <v>630</v>
+        <v>602</v>
       </c>
       <c r="C1" t="s">
-        <v>631</v>
+        <v>603</v>
       </c>
       <c r="D1" t="s">
-        <v>632</v>
+        <v>604</v>
       </c>
       <c r="E1" t="s">
-        <v>633</v>
+        <v>605</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B2" s="86" t="s">
-        <v>681</v>
+        <v>653</v>
       </c>
       <c r="C2" t="s">
-        <v>678</v>
+        <v>650</v>
       </c>
       <c r="D2" s="86" t="s">
-        <v>679</v>
+        <v>651</v>
       </c>
       <c r="E2" s="86" t="s">
-        <v>680</v>
+        <v>652</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B3" s="86" t="s">
-        <v>682</v>
+        <v>654</v>
       </c>
       <c r="C3" t="s">
-        <v>683</v>
+        <v>655</v>
       </c>
       <c r="D3" s="86" t="s">
-        <v>684</v>
+        <v>656</v>
       </c>
       <c r="E3" s="86" t="s">
-        <v>685</v>
+        <v>657</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B4" s="86" t="s">
-        <v>677</v>
+        <v>649</v>
       </c>
       <c r="C4" t="s">
-        <v>636</v>
+        <v>608</v>
       </c>
       <c r="D4" s="86" t="s">
-        <v>634</v>
+        <v>606</v>
       </c>
       <c r="E4" s="86" t="s">
-        <v>635</v>
+        <v>607</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B5" s="86" t="s">
-        <v>676</v>
+        <v>648</v>
       </c>
       <c r="C5" t="s">
-        <v>638</v>
+        <v>610</v>
       </c>
       <c r="D5" s="86" t="s">
-        <v>637</v>
+        <v>609</v>
       </c>
       <c r="E5" s="86" t="s">
-        <v>639</v>
+        <v>611</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B6" s="86" t="s">
-        <v>675</v>
+        <v>647</v>
       </c>
       <c r="C6" t="s">
-        <v>642</v>
+        <v>614</v>
       </c>
       <c r="D6" s="86" t="s">
-        <v>640</v>
+        <v>612</v>
       </c>
       <c r="E6" s="86" t="s">
-        <v>641</v>
+        <v>613</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B7" s="86" t="s">
-        <v>674</v>
+        <v>646</v>
       </c>
       <c r="C7" t="s">
-        <v>644</v>
+        <v>616</v>
       </c>
       <c r="D7" s="86" t="s">
-        <v>643</v>
+        <v>615</v>
       </c>
       <c r="E7" s="86" t="s">
-        <v>645</v>
+        <v>617</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B8" s="86" t="s">
-        <v>673</v>
+        <v>645</v>
       </c>
       <c r="C8" t="s">
-        <v>647</v>
+        <v>619</v>
       </c>
       <c r="D8" s="86" t="s">
-        <v>646</v>
+        <v>618</v>
       </c>
       <c r="E8" s="86" t="s">
-        <v>648</v>
+        <v>620</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B9" s="86" t="s">
-        <v>672</v>
+        <v>644</v>
       </c>
       <c r="C9" t="s">
-        <v>650</v>
+        <v>622</v>
       </c>
       <c r="D9" s="86" t="s">
-        <v>649</v>
+        <v>621</v>
       </c>
       <c r="E9" s="86" t="s">
-        <v>651</v>
+        <v>623</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B10" s="86" t="s">
-        <v>671</v>
+        <v>643</v>
       </c>
       <c r="C10" t="s">
-        <v>653</v>
+        <v>625</v>
       </c>
       <c r="D10" s="86" t="s">
-        <v>652</v>
+        <v>624</v>
       </c>
       <c r="E10" s="86" t="s">
-        <v>654</v>
+        <v>626</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B11" s="86" t="s">
-        <v>670</v>
+        <v>642</v>
       </c>
       <c r="C11" t="s">
-        <v>657</v>
+        <v>629</v>
       </c>
       <c r="D11" s="86" t="s">
-        <v>655</v>
+        <v>627</v>
       </c>
       <c r="E11" s="86" t="s">
-        <v>656</v>
+        <v>628</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B12" s="86" t="s">
-        <v>669</v>
+        <v>641</v>
       </c>
       <c r="C12" t="s">
-        <v>659</v>
+        <v>631</v>
       </c>
       <c r="D12" s="86" t="s">
-        <v>658</v>
+        <v>630</v>
       </c>
       <c r="E12" s="86" t="s">
-        <v>660</v>
+        <v>632</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B13" s="86" t="s">
-        <v>667</v>
+        <v>639</v>
       </c>
       <c r="C13" t="s">
-        <v>662</v>
+        <v>634</v>
       </c>
       <c r="D13" s="86" t="s">
-        <v>661</v>
+        <v>633</v>
       </c>
       <c r="E13" s="86" t="s">
-        <v>663</v>
+        <v>635</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B14" s="86" t="s">
-        <v>668</v>
+        <v>640</v>
       </c>
       <c r="C14" t="s">
-        <v>665</v>
+        <v>637</v>
       </c>
       <c r="D14" s="86" t="s">
-        <v>664</v>
+        <v>636</v>
       </c>
       <c r="E14" s="86" t="s">
-        <v>666</v>
+        <v>638</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B15" s="86" t="s">
-        <v>689</v>
+        <v>661</v>
       </c>
       <c r="C15" t="s">
-        <v>688</v>
+        <v>660</v>
       </c>
       <c r="D15" s="86" t="s">
-        <v>686</v>
+        <v>658</v>
       </c>
       <c r="E15" s="86" t="s">
-        <v>687</v>
+        <v>659</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B16" s="86" t="s">
-        <v>693</v>
+        <v>665</v>
       </c>
       <c r="C16" t="s">
-        <v>692</v>
+        <v>664</v>
       </c>
       <c r="D16" s="86" t="s">
-        <v>690</v>
+        <v>662</v>
       </c>
       <c r="E16" s="86" t="s">
-        <v>691</v>
+        <v>663</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B17" s="86" t="s">
-        <v>697</v>
+        <v>669</v>
       </c>
       <c r="C17" t="s">
-        <v>694</v>
+        <v>666</v>
       </c>
       <c r="D17" s="86" t="s">
-        <v>695</v>
+        <v>667</v>
       </c>
       <c r="E17" s="86" t="s">
-        <v>696</v>
+        <v>668</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B18" s="86" t="s">
-        <v>698</v>
+        <v>670</v>
       </c>
       <c r="C18" t="s">
-        <v>699</v>
+        <v>671</v>
       </c>
       <c r="D18" s="86" t="s">
-        <v>700</v>
+        <v>672</v>
       </c>
       <c r="E18" s="86" t="s">
-        <v>701</v>
+        <v>673</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B19" s="86" t="s">
-        <v>705</v>
+        <v>677</v>
       </c>
       <c r="C19" t="s">
-        <v>704</v>
+        <v>676</v>
       </c>
       <c r="D19" s="86" t="s">
-        <v>702</v>
+        <v>674</v>
       </c>
       <c r="E19" s="86" t="s">
-        <v>703</v>
+        <v>675</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B20" s="86" t="s">
-        <v>706</v>
+        <v>678</v>
       </c>
       <c r="C20" t="s">
-        <v>707</v>
+        <v>679</v>
       </c>
       <c r="D20" s="86" t="s">
-        <v>708</v>
+        <v>680</v>
       </c>
       <c r="E20" s="86" t="s">
-        <v>709</v>
+        <v>681</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B21" s="86" t="s">
-        <v>713</v>
+        <v>685</v>
       </c>
       <c r="C21" t="s">
-        <v>712</v>
+        <v>684</v>
       </c>
       <c r="D21" s="86" t="s">
-        <v>710</v>
+        <v>682</v>
       </c>
       <c r="E21" s="86" t="s">
-        <v>711</v>
+        <v>683</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B22" s="86" t="s">
-        <v>717</v>
+        <v>689</v>
       </c>
       <c r="C22" t="s">
-        <v>716</v>
+        <v>688</v>
       </c>
       <c r="D22" s="86" t="s">
-        <v>714</v>
+        <v>686</v>
       </c>
       <c r="E22" s="86" t="s">
-        <v>715</v>
+        <v>687</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B23" s="86" t="s">
-        <v>721</v>
+        <v>693</v>
       </c>
       <c r="C23" t="s">
-        <v>720</v>
+        <v>692</v>
       </c>
       <c r="D23" s="86" t="s">
-        <v>718</v>
+        <v>690</v>
       </c>
       <c r="E23" s="86" t="s">
-        <v>719</v>
+        <v>691</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B24" s="86" t="s">
-        <v>725</v>
+        <v>697</v>
       </c>
       <c r="C24" t="s">
-        <v>723</v>
+        <v>695</v>
       </c>
       <c r="D24" s="86" t="s">
-        <v>722</v>
+        <v>694</v>
       </c>
       <c r="E24" s="86" t="s">
-        <v>724</v>
+        <v>696</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B25" s="86" t="s">
-        <v>729</v>
+        <v>701</v>
       </c>
       <c r="C25" t="s">
-        <v>727</v>
+        <v>699</v>
       </c>
       <c r="D25" s="86" t="s">
-        <v>726</v>
+        <v>698</v>
       </c>
       <c r="E25" s="86" t="s">
-        <v>728</v>
+        <v>700</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B26" s="86" t="s">
-        <v>733</v>
+        <v>705</v>
       </c>
       <c r="C26" t="s">
-        <v>732</v>
+        <v>704</v>
       </c>
       <c r="D26" s="86" t="s">
-        <v>730</v>
+        <v>702</v>
       </c>
       <c r="E26" s="86" t="s">
-        <v>731</v>
+        <v>703</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C27" t="s">
-        <v>734</v>
+        <v>706</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C28" t="s">
-        <v>734</v>
+        <v>706</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="B29" s="86" t="s">
-        <v>738</v>
+        <v>710</v>
       </c>
       <c r="C29" t="s">
-        <v>737</v>
+        <v>709</v>
       </c>
       <c r="D29" s="86" t="s">
-        <v>735</v>
+        <v>707</v>
       </c>
       <c r="E29" s="86" t="s">
-        <v>736</v>
+        <v>708</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="B30" s="86" t="s">
-        <v>738</v>
+        <v>710</v>
       </c>
       <c r="C30" t="s">
-        <v>739</v>
+        <v>711</v>
       </c>
       <c r="D30" s="86" t="s">
-        <v>735</v>
+        <v>707</v>
       </c>
       <c r="E30" s="86" t="s">
-        <v>736</v>
+        <v>708</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="B31" s="86" t="s">
-        <v>742</v>
+        <v>714</v>
       </c>
       <c r="C31" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D31" s="86" t="s">
-        <v>740</v>
+        <v>712</v>
       </c>
       <c r="E31" s="86" t="s">
-        <v>741</v>
+        <v>713</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="B32" s="86" t="s">
-        <v>742</v>
+        <v>714</v>
       </c>
       <c r="C32" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D32" s="86" t="s">
-        <v>740</v>
+        <v>712</v>
       </c>
       <c r="E32" s="86" t="s">
-        <v>741</v>
+        <v>713</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="B33" s="86" t="s">
-        <v>677</v>
+        <v>649</v>
       </c>
       <c r="C33" t="s">
-        <v>636</v>
+        <v>608</v>
       </c>
       <c r="D33" s="86" t="s">
-        <v>743</v>
+        <v>715</v>
       </c>
       <c r="E33" s="86" t="s">
-        <v>635</v>
+        <v>607</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="B34" s="86" t="s">
-        <v>676</v>
+        <v>648</v>
       </c>
       <c r="C34" t="s">
-        <v>638</v>
+        <v>610</v>
       </c>
       <c r="D34" s="86" t="s">
-        <v>744</v>
+        <v>716</v>
       </c>
       <c r="E34" s="86" t="s">
-        <v>639</v>
+        <v>611</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="B35" s="86" t="s">
-        <v>748</v>
+        <v>720</v>
       </c>
       <c r="C35" t="s">
-        <v>745</v>
+        <v>717</v>
       </c>
       <c r="D35" s="86" t="s">
-        <v>746</v>
+        <v>718</v>
       </c>
       <c r="E35" s="86" t="s">
-        <v>747</v>
+        <v>719</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="B36" s="86" t="s">
-        <v>729</v>
+        <v>701</v>
       </c>
       <c r="C36" t="s">
-        <v>727</v>
+        <v>699</v>
       </c>
       <c r="D36" s="86" t="s">
-        <v>749</v>
+        <v>721</v>
       </c>
       <c r="E36" s="86" t="s">
-        <v>728</v>
+        <v>700</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="B37" s="86" t="s">
-        <v>675</v>
+        <v>647</v>
       </c>
       <c r="C37" t="s">
-        <v>642</v>
+        <v>614</v>
       </c>
       <c r="D37" s="86" t="s">
-        <v>750</v>
+        <v>722</v>
       </c>
       <c r="E37" s="86" t="s">
-        <v>641</v>
+        <v>613</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="B38" s="86" t="s">
-        <v>674</v>
+        <v>646</v>
       </c>
       <c r="C38" t="s">
-        <v>644</v>
+        <v>616</v>
       </c>
       <c r="D38" s="86" t="s">
-        <v>751</v>
+        <v>723</v>
       </c>
       <c r="E38" s="86" t="s">
-        <v>645</v>
+        <v>617</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="B39" s="86" t="s">
-        <v>713</v>
+        <v>685</v>
       </c>
       <c r="C39" t="s">
-        <v>712</v>
+        <v>684</v>
       </c>
       <c r="D39" s="86" t="s">
-        <v>752</v>
+        <v>724</v>
       </c>
       <c r="E39" s="86" t="s">
-        <v>711</v>
+        <v>683</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="B40" s="86" t="s">
-        <v>673</v>
+        <v>645</v>
       </c>
       <c r="C40" t="s">
-        <v>647</v>
+        <v>619</v>
       </c>
       <c r="D40" s="86" t="s">
-        <v>753</v>
+        <v>725</v>
       </c>
       <c r="E40" s="86" t="s">
-        <v>648</v>
+        <v>620</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="B41" s="86" t="s">
-        <v>689</v>
+        <v>661</v>
       </c>
       <c r="C41" t="s">
-        <v>688</v>
+        <v>660</v>
       </c>
       <c r="D41" s="86" t="s">
-        <v>754</v>
+        <v>726</v>
       </c>
       <c r="E41" s="86" t="s">
-        <v>687</v>
+        <v>659</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="B42" s="86" t="s">
-        <v>733</v>
+        <v>705</v>
       </c>
       <c r="C42" t="s">
-        <v>732</v>
+        <v>704</v>
       </c>
       <c r="D42" s="86" t="s">
-        <v>755</v>
+        <v>727</v>
       </c>
       <c r="E42" s="86" t="s">
-        <v>731</v>
+        <v>703</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="B43" s="86" t="s">
-        <v>670</v>
+        <v>642</v>
       </c>
       <c r="C43" t="s">
-        <v>657</v>
+        <v>629</v>
       </c>
       <c r="D43" s="86" t="s">
-        <v>756</v>
+        <v>728</v>
       </c>
       <c r="E43" s="86" t="s">
-        <v>656</v>
+        <v>628</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="B44" s="86" t="s">
-        <v>672</v>
+        <v>644</v>
       </c>
       <c r="C44" t="s">
-        <v>650</v>
+        <v>622</v>
       </c>
       <c r="D44" s="86" t="s">
-        <v>757</v>
+        <v>729</v>
       </c>
       <c r="E44" s="86" t="s">
-        <v>651</v>
+        <v>623</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="B45" s="86" t="s">
-        <v>671</v>
+        <v>643</v>
       </c>
       <c r="C45" t="s">
-        <v>653</v>
+        <v>625</v>
       </c>
       <c r="D45" s="86" t="s">
-        <v>758</v>
+        <v>730</v>
       </c>
       <c r="E45" s="86" t="s">
-        <v>654</v>
+        <v>626</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="B46" s="86" t="s">
-        <v>693</v>
+        <v>665</v>
       </c>
       <c r="C46" t="s">
-        <v>692</v>
+        <v>664</v>
       </c>
       <c r="D46" s="86" t="s">
-        <v>759</v>
+        <v>731</v>
       </c>
       <c r="E46" s="86" t="s">
-        <v>691</v>
+        <v>663</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="B47" s="86" t="s">
-        <v>697</v>
+        <v>669</v>
       </c>
       <c r="C47" t="s">
-        <v>694</v>
+        <v>666</v>
       </c>
       <c r="D47" s="83" t="s">
-        <v>761</v>
+        <v>733</v>
       </c>
       <c r="E47" s="86" t="s">
-        <v>760</v>
+        <v>732</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="B48" s="86" t="s">
-        <v>681</v>
+        <v>653</v>
       </c>
       <c r="C48" t="s">
-        <v>678</v>
+        <v>650</v>
       </c>
       <c r="D48" s="86" t="s">
-        <v>762</v>
+        <v>734</v>
       </c>
       <c r="E48" s="86" t="s">
-        <v>680</v>
+        <v>652</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="B49" s="86" t="s">
-        <v>667</v>
+        <v>639</v>
       </c>
       <c r="C49" t="s">
-        <v>662</v>
+        <v>634</v>
       </c>
       <c r="D49" s="86" t="s">
-        <v>763</v>
+        <v>735</v>
       </c>
       <c r="E49" s="86" t="s">
-        <v>663</v>
+        <v>635</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="B50" s="86" t="s">
-        <v>668</v>
+        <v>640</v>
       </c>
       <c r="C50" t="s">
-        <v>665</v>
+        <v>637</v>
       </c>
       <c r="D50" s="86" t="s">
-        <v>764</v>
+        <v>736</v>
       </c>
       <c r="E50" s="86" t="s">
-        <v>666</v>
+        <v>638</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="B51" s="86" t="s">
-        <v>705</v>
+        <v>677</v>
       </c>
       <c r="C51" t="s">
-        <v>704</v>
+        <v>676</v>
       </c>
       <c r="D51" s="86" t="s">
-        <v>765</v>
+        <v>737</v>
       </c>
       <c r="E51" s="86" t="s">
-        <v>703</v>
+        <v>675</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="B52" s="86" t="s">
-        <v>725</v>
+        <v>697</v>
       </c>
       <c r="C52" t="s">
-        <v>723</v>
+        <v>695</v>
       </c>
       <c r="D52" s="86" t="s">
-        <v>766</v>
+        <v>738</v>
       </c>
       <c r="E52" s="86" t="s">
-        <v>724</v>
+        <v>696</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="B53" s="86" t="s">
-        <v>717</v>
+        <v>689</v>
       </c>
       <c r="C53" t="s">
-        <v>716</v>
+        <v>688</v>
       </c>
       <c r="D53" s="86" t="s">
-        <v>767</v>
+        <v>739</v>
       </c>
       <c r="E53" s="86" t="s">
-        <v>715</v>
+        <v>687</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="B54" s="86" t="s">
-        <v>742</v>
+        <v>714</v>
       </c>
       <c r="C54" t="s">
-        <v>769</v>
+        <v>741</v>
       </c>
       <c r="D54" s="86" t="s">
-        <v>768</v>
+        <v>740</v>
       </c>
       <c r="E54" s="86" t="s">
-        <v>736</v>
+        <v>708</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>550</v>
+        <v>538</v>
       </c>
       <c r="B55" s="86" t="s">
+        <v>714</v>
+      </c>
+      <c r="C55" t="s">
         <v>742</v>
       </c>
-      <c r="C55" t="s">
-        <v>770</v>
-      </c>
       <c r="D55" s="86" t="s">
-        <v>768</v>
+        <v>740</v>
       </c>
       <c r="E55" s="86" t="s">
-        <v>736</v>
+        <v>708</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>557</v>
+        <v>543</v>
       </c>
       <c r="B56" s="86" t="s">
-        <v>742</v>
+        <v>714</v>
       </c>
       <c r="C56" t="s">
-        <v>772</v>
+        <v>744</v>
       </c>
       <c r="D56" s="86" t="s">
-        <v>771</v>
+        <v>743</v>
       </c>
       <c r="E56" s="86" t="s">
-        <v>741</v>
+        <v>713</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>561</v>
+        <v>546</v>
       </c>
       <c r="B57" s="86" t="s">
-        <v>774</v>
+        <v>746</v>
       </c>
       <c r="C57" t="s">
-        <v>773</v>
+        <v>745</v>
       </c>
       <c r="D57" s="86" t="s">
-        <v>740</v>
+        <v>712</v>
       </c>
       <c r="E57" s="86" t="s">
-        <v>741</v>
+        <v>713</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>561</v>
+        <v>546</v>
       </c>
       <c r="B58" s="86" t="s">
-        <v>774</v>
+        <v>746</v>
       </c>
       <c r="C58" t="s">
-        <v>775</v>
+        <v>747</v>
       </c>
       <c r="D58" s="86" t="s">
-        <v>776</v>
+        <v>748</v>
       </c>
       <c r="E58" s="86" t="s">
-        <v>741</v>
+        <v>713</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>563</v>
+        <v>547</v>
       </c>
       <c r="B59" s="86" t="s">
-        <v>717</v>
+        <v>689</v>
       </c>
       <c r="C59" t="s">
-        <v>778</v>
+        <v>750</v>
       </c>
       <c r="D59" s="86" t="s">
-        <v>777</v>
+        <v>749</v>
       </c>
       <c r="E59" s="86" t="s">
-        <v>779</v>
+        <v>751</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>563</v>
+        <v>547</v>
       </c>
       <c r="B60" s="86" t="s">
-        <v>783</v>
+        <v>755</v>
       </c>
       <c r="C60" t="s">
-        <v>782</v>
+        <v>754</v>
       </c>
       <c r="D60" s="86" t="s">
-        <v>780</v>
+        <v>752</v>
       </c>
       <c r="E60" s="86" t="s">
-        <v>781</v>
+        <v>753</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>563</v>
+        <v>547</v>
       </c>
       <c r="B61" s="86" t="s">
-        <v>783</v>
+        <v>755</v>
       </c>
       <c r="C61" t="s">
-        <v>784</v>
+        <v>756</v>
       </c>
       <c r="D61" s="86" t="s">
-        <v>785</v>
+        <v>757</v>
       </c>
       <c r="E61" s="86" t="s">
-        <v>781</v>
+        <v>753</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>588</v>
+        <v>564</v>
       </c>
       <c r="B62" s="86" t="s">
-        <v>789</v>
+        <v>761</v>
       </c>
       <c r="C62" t="s">
-        <v>787</v>
+        <v>759</v>
       </c>
       <c r="D62" s="86" t="s">
-        <v>786</v>
+        <v>758</v>
       </c>
       <c r="E62" s="86" t="s">
-        <v>788</v>
+        <v>760</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>588</v>
+        <v>564</v>
       </c>
       <c r="B63" s="86" t="s">
-        <v>789</v>
+        <v>761</v>
       </c>
       <c r="C63" t="s">
-        <v>791</v>
+        <v>763</v>
       </c>
       <c r="D63" s="86" t="s">
-        <v>790</v>
+        <v>762</v>
       </c>
       <c r="E63" s="86" t="s">
-        <v>788</v>
+        <v>760</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>588</v>
+        <v>564</v>
       </c>
       <c r="B64" s="86" t="s">
-        <v>795</v>
+        <v>767</v>
       </c>
       <c r="C64" t="s">
-        <v>793</v>
+        <v>765</v>
       </c>
       <c r="D64" s="86" t="s">
-        <v>792</v>
+        <v>764</v>
       </c>
       <c r="E64" s="86" t="s">
-        <v>794</v>
+        <v>766</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>588</v>
+        <v>564</v>
       </c>
       <c r="B65" s="86" t="s">
-        <v>798</v>
+        <v>770</v>
       </c>
       <c r="C65" t="s">
-        <v>800</v>
+        <v>772</v>
       </c>
       <c r="D65" s="86" t="s">
-        <v>796</v>
+        <v>768</v>
       </c>
       <c r="E65" s="86" t="s">
-        <v>797</v>
+        <v>769</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>588</v>
+        <v>564</v>
       </c>
       <c r="B66" s="86" t="s">
-        <v>798</v>
+        <v>770</v>
       </c>
       <c r="C66" t="s">
-        <v>801</v>
+        <v>773</v>
       </c>
       <c r="D66" s="86" t="s">
-        <v>799</v>
+        <v>771</v>
       </c>
       <c r="E66" s="86" t="s">
-        <v>797</v>
+        <v>769</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>588</v>
+        <v>564</v>
       </c>
       <c r="B67" s="86" t="s">
-        <v>804</v>
+        <v>776</v>
       </c>
       <c r="C67" t="s">
-        <v>803</v>
+        <v>775</v>
       </c>
       <c r="D67" s="86" t="s">
-        <v>802</v>
+        <v>774</v>
       </c>
       <c r="E67" s="86" t="s">
-        <v>741</v>
+        <v>713</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>832</v>
+        <v>804</v>
       </c>
       <c r="B68" s="86" t="s">
-        <v>807</v>
+        <v>779</v>
       </c>
       <c r="C68" t="s">
-        <v>806</v>
+        <v>778</v>
       </c>
       <c r="D68" s="86" t="s">
-        <v>805</v>
+        <v>777</v>
       </c>
       <c r="E68" s="86" t="s">
-        <v>794</v>
+        <v>766</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>832</v>
+        <v>804</v>
       </c>
       <c r="B69" s="86" t="s">
-        <v>807</v>
+        <v>779</v>
       </c>
       <c r="C69" t="s">
-        <v>808</v>
+        <v>780</v>
       </c>
       <c r="D69" s="86" t="s">
-        <v>809</v>
+        <v>781</v>
       </c>
       <c r="E69" s="86" t="s">
-        <v>794</v>
+        <v>766</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>832</v>
+        <v>804</v>
       </c>
       <c r="B70" s="86" t="s">
-        <v>813</v>
+        <v>785</v>
       </c>
       <c r="C70" t="s">
-        <v>811</v>
+        <v>783</v>
       </c>
       <c r="D70" s="86" t="s">
-        <v>810</v>
+        <v>782</v>
       </c>
       <c r="E70" s="86" t="s">
-        <v>812</v>
+        <v>784</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>832</v>
+        <v>804</v>
       </c>
       <c r="B71" s="86" t="s">
-        <v>813</v>
+        <v>785</v>
       </c>
       <c r="C71" t="s">
-        <v>814</v>
+        <v>786</v>
       </c>
       <c r="D71" s="86" t="s">
-        <v>815</v>
+        <v>787</v>
       </c>
       <c r="E71" s="86" t="s">
-        <v>812</v>
+        <v>784</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>832</v>
+        <v>804</v>
       </c>
       <c r="B72" s="86" t="s">
-        <v>819</v>
+        <v>791</v>
       </c>
       <c r="C72" t="s">
-        <v>818</v>
+        <v>790</v>
       </c>
       <c r="D72" s="86" t="s">
-        <v>816</v>
+        <v>788</v>
       </c>
       <c r="E72" s="86" t="s">
-        <v>817</v>
+        <v>789</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>832</v>
+        <v>804</v>
       </c>
       <c r="B73" s="86" t="s">
-        <v>821</v>
+        <v>793</v>
       </c>
       <c r="C73" t="s">
-        <v>820</v>
+        <v>792</v>
       </c>
       <c r="D73" s="86" t="s">
-        <v>816</v>
+        <v>788</v>
       </c>
       <c r="E73" s="86" t="s">
-        <v>817</v>
+        <v>789</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>832</v>
+        <v>804</v>
       </c>
       <c r="B74" s="86" t="s">
-        <v>821</v>
+        <v>793</v>
       </c>
       <c r="C74" t="s">
-        <v>822</v>
+        <v>794</v>
       </c>
       <c r="D74" s="86" t="s">
-        <v>816</v>
+        <v>788</v>
       </c>
       <c r="E74" s="86" t="s">
-        <v>817</v>
+        <v>789</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>832</v>
+        <v>804</v>
       </c>
       <c r="B75" s="86" t="s">
-        <v>825</v>
+        <v>797</v>
       </c>
       <c r="C75" t="s">
-        <v>823</v>
+        <v>795</v>
       </c>
       <c r="D75" s="86" t="s">
-        <v>824</v>
+        <v>796</v>
       </c>
       <c r="E75" s="86" t="s">
-        <v>817</v>
+        <v>789</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>832</v>
+        <v>804</v>
       </c>
       <c r="B76" s="86" t="s">
-        <v>828</v>
+        <v>800</v>
       </c>
       <c r="C76" t="s">
-        <v>827</v>
+        <v>799</v>
       </c>
       <c r="D76" s="86" t="s">
-        <v>826</v>
+        <v>798</v>
       </c>
       <c r="E76" s="86" t="s">
-        <v>817</v>
+        <v>789</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>832</v>
+        <v>804</v>
       </c>
       <c r="B77" s="86" t="s">
-        <v>689</v>
+        <v>661</v>
       </c>
       <c r="C77" t="s">
-        <v>829</v>
+        <v>801</v>
       </c>
       <c r="D77" s="86" t="s">
-        <v>830</v>
+        <v>802</v>
       </c>
       <c r="E77" s="86" t="s">
-        <v>817</v>
+        <v>789</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>833</v>
+        <v>805</v>
       </c>
       <c r="B78" s="86" t="s">
-        <v>682</v>
+        <v>654</v>
       </c>
       <c r="C78" t="s">
-        <v>831</v>
+        <v>803</v>
       </c>
       <c r="D78" s="86" t="s">
-        <v>840</v>
+        <v>812</v>
       </c>
       <c r="E78" s="86" t="s">
-        <v>685</v>
+        <v>657</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>834</v>
+        <v>806</v>
       </c>
       <c r="B79" s="86" t="s">
-        <v>682</v>
+        <v>654</v>
       </c>
       <c r="C79" t="s">
-        <v>841</v>
+        <v>813</v>
       </c>
       <c r="D79" s="86" t="s">
-        <v>840</v>
+        <v>812</v>
       </c>
       <c r="E79" s="86" t="s">
-        <v>685</v>
+        <v>657</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>835</v>
+        <v>807</v>
       </c>
       <c r="B80" t="s">
-        <v>842</v>
+        <v>814</v>
       </c>
       <c r="C80" t="s">
-        <v>576</v>
+        <v>557</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>836</v>
+        <v>808</v>
       </c>
       <c r="B81" t="s">
-        <v>843</v>
+        <v>815</v>
       </c>
       <c r="C81" t="s">
-        <v>581</v>
+        <v>560</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>837</v>
+        <v>809</v>
       </c>
       <c r="B82" t="s">
-        <v>844</v>
+        <v>816</v>
       </c>
       <c r="C82" t="s">
-        <v>847</v>
+        <v>819</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>837</v>
+        <v>809</v>
       </c>
       <c r="B83" t="s">
-        <v>846</v>
+        <v>818</v>
       </c>
       <c r="C83" t="s">
-        <v>845</v>
+        <v>817</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>838</v>
+        <v>810</v>
       </c>
       <c r="B84" t="s">
-        <v>849</v>
+        <v>821</v>
       </c>
       <c r="C84" t="s">
-        <v>848</v>
+        <v>820</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>838</v>
+        <v>810</v>
       </c>
       <c r="B85" t="s">
-        <v>851</v>
+        <v>823</v>
       </c>
       <c r="C85" t="s">
-        <v>850</v>
+        <v>822</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>838</v>
+        <v>810</v>
       </c>
       <c r="B86" t="s">
-        <v>852</v>
+        <v>824</v>
       </c>
       <c r="C86" t="s">
-        <v>853</v>
+        <v>825</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>839</v>
+        <v>811</v>
       </c>
       <c r="B87" t="s">
-        <v>854</v>
+        <v>826</v>
       </c>
       <c r="C87" t="s">
-        <v>586</v>
+        <v>562</v>
       </c>
     </row>
   </sheetData>
@@ -7766,15 +7963,15 @@
       <c r="D1" s="72" t="s">
         <v>395</v>
       </c>
-      <c r="W1" s="105" t="s">
-        <v>405</v>
-      </c>
-      <c r="X1" s="105"/>
-      <c r="Y1" s="105"/>
+      <c r="W1" s="107" t="s">
+        <v>404</v>
+      </c>
+      <c r="X1" s="107"/>
+      <c r="Y1" s="107"/>
     </row>
     <row r="2" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="77" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B2" s="75" t="s">
         <v>390</v>
@@ -7786,7 +7983,7 @@
         <v>384</v>
       </c>
       <c r="W2" s="82" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.35">
@@ -7803,18 +8000,18 @@
         <v>385</v>
       </c>
       <c r="X3" s="79" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="Y3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4" s="77" t="s">
+        <v>397</v>
+      </c>
+      <c r="B4" t="s">
         <v>398</v>
-      </c>
-      <c r="B4" t="s">
-        <v>399</v>
       </c>
       <c r="C4" s="73" t="s">
         <v>377</v>
@@ -7823,18 +8020,18 @@
         <v>9</v>
       </c>
       <c r="X4" s="79" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="Y4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5" s="85" t="s">
-        <v>595</v>
+        <v>567</v>
       </c>
       <c r="B5" t="s">
-        <v>594</v>
+        <v>566</v>
       </c>
       <c r="C5" s="73" t="s">
         <v>142</v>
@@ -7843,10 +8040,10 @@
         <v>10</v>
       </c>
       <c r="X5" s="79" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="Y5" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.35">
@@ -7857,10 +8054,10 @@
         <v>387</v>
       </c>
       <c r="X6" s="79" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="Y6" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.35">
@@ -7871,10 +8068,10 @@
         <v>11</v>
       </c>
       <c r="X7" s="79" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="Y7" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.35">
@@ -7885,10 +8082,10 @@
         <v>388</v>
       </c>
       <c r="X8" s="79" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="Y8" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.35">
@@ -7899,21 +8096,21 @@
         <v>389</v>
       </c>
       <c r="X9" s="79" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Y9" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="10" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C10" s="84" t="s">
-        <v>555</v>
+        <v>541</v>
       </c>
       <c r="D10" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="W10" s="81" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.35">
@@ -7924,338 +8121,338 @@
         <v>386</v>
       </c>
       <c r="X11" s="79" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Y11" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.35">
       <c r="C12" s="73" t="s">
-        <v>565</v>
+        <v>548</v>
       </c>
       <c r="D12" t="s">
-        <v>566</v>
+        <v>549</v>
       </c>
       <c r="X12" s="79" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="Y12" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.35">
       <c r="C13" s="84" t="s">
-        <v>567</v>
+        <v>550</v>
       </c>
       <c r="D13" t="s">
-        <v>568</v>
+        <v>551</v>
       </c>
       <c r="X13" s="79" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="Y13" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.35">
       <c r="C14" s="85" t="s">
-        <v>595</v>
+        <v>567</v>
       </c>
       <c r="D14" t="s">
-        <v>594</v>
+        <v>566</v>
       </c>
       <c r="X14" s="79" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Y14" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.35">
       <c r="X15" s="79" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="Y15" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.35">
       <c r="X16" s="79" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="Y16" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="17" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X17" s="79" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="Y17" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="18" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X18" s="79" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="Y18" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="19" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X19" s="79" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="Y19" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="20" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X20" s="79" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="Y20" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="21" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X21" s="79" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="Y21" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="22" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X22" s="79" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="Y22" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="23" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X23" s="79" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="Y23" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="24" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X24" s="79" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="Y24" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="25" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X25" s="79" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="Y25" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="26" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X26" s="79" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="Y26" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="27" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X27" s="79" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="Y27" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="28" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X28" s="79" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="Y28" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="29" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X29" s="79" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="Y29" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="30" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X30" s="79" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="Y30" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="31" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X31" s="79" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="Y31" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="32" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X32" s="79" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="Y32" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="33" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X33" s="79" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Y33" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="34" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X34" s="79" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="Y34" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="35" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X35" s="79" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="Y35" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="36" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X36" s="79" t="s">
+        <v>515</v>
+      </c>
+      <c r="Y36" t="s">
         <v>516</v>
-      </c>
-      <c r="Y36" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="38" spans="23:26" ht="15.5" x14ac:dyDescent="0.35">
       <c r="W38" s="81" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="39" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X39" s="79" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="Y39" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="40" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X40" s="79" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Y40" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="Z40" s="79"/>
     </row>
     <row r="41" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X41" s="79" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="Y41" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="Z41" s="79"/>
     </row>
     <row r="42" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X42" s="79" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="Y42" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="Z42" s="79"/>
     </row>
     <row r="43" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X43" s="79" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="Y43" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="Z43" s="79"/>
     </row>
     <row r="44" spans="23:26" ht="15.5" x14ac:dyDescent="0.35">
       <c r="W44" s="81" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="X44" s="80"/>
       <c r="Z44" s="79"/>
     </row>
     <row r="45" spans="23:26" ht="15.5" x14ac:dyDescent="0.35">
       <c r="X45" s="79" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Y45" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="Z45" s="80"/>
     </row>
     <row r="46" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X46" s="79" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="Y46" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="Z46" s="79"/>
     </row>
     <row r="47" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X47" s="79" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Y47" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="Z47" s="79"/>
     </row>
     <row r="48" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X48" s="79" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Y48" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="Z48" s="79"/>
     </row>
     <row r="49" spans="15:25" x14ac:dyDescent="0.35">
       <c r="O49" s="79"/>
       <c r="X49" s="79" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="Y49" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="50" spans="15:25" x14ac:dyDescent="0.35">
       <c r="O50" s="79"/>
       <c r="X50" s="79" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Y50" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
   </sheetData>

--- a/Info/Additional_information.xlsx
+++ b/Info/Additional_information.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{307CE2A6-F4AC-4756-B7A5-E82FDDC593C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F049E0BF-8338-4C2C-B18A-E5FEB5B5BE2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3246,7 +3246,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3476,8 +3476,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="20" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3529,63 +3531,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="34">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -4070,6 +4023,54 @@
         </horizontal>
       </border>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -4138,44 +4139,44 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{973D7237-72C7-453E-A0E1-526C93326B28}" name="Таблица3" displayName="Таблица3" ref="A1:F51" totalsRowShown="0" headerRowDxfId="33" dataDxfId="31" headerRowBorderDxfId="32" tableBorderDxfId="30" totalsRowBorderDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{973D7237-72C7-453E-A0E1-526C93326B28}" name="Таблица3" displayName="Таблица3" ref="A1:F51" totalsRowShown="0" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
   <autoFilter ref="A1:F51" xr:uid="{A2D8FA3D-4024-4365-BE1D-F93D0AF2D426}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{12C2DF0B-47FA-46A4-8424-55A1488EF88B}" name="ID" dataDxfId="28"/>
-    <tableColumn id="2" xr3:uid="{EB0B36CE-168D-429E-896D-DBA54794224F}" name="Name_Eng" dataDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{6C3A2CE8-252E-4C52-985B-8CDDFD9FA0C7}" name="OfficialMintName_Native" dataDxfId="26"/>
-    <tableColumn id="8" xr3:uid="{DA5871DC-2EDB-49C0-953E-EC0F70288E21}" name="Country" dataDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{FCD85F85-A94E-4BBE-9D3B-2B7494638375}" name="Mint_City" dataDxfId="24"/>
-    <tableColumn id="6" xr3:uid="{E5141978-CA91-4DE9-86F1-8A8AFA716534}" name="Alias" dataDxfId="23"/>
+    <tableColumn id="1" xr3:uid="{12C2DF0B-47FA-46A4-8424-55A1488EF88B}" name="ID" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{EB0B36CE-168D-429E-896D-DBA54794224F}" name="Name_Eng" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{6C3A2CE8-252E-4C52-985B-8CDDFD9FA0C7}" name="OfficialMintName_Native" dataDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{DA5871DC-2EDB-49C0-953E-EC0F70288E21}" name="Country" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{FCD85F85-A94E-4BBE-9D3B-2B7494638375}" name="Mint_City" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{E5141978-CA91-4DE9-86F1-8A8AFA716534}" name="Alias" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D0DCC88A-2D36-4004-A694-FC0C0F0C3396}" name="Таблица2" displayName="Таблица2" ref="A1:C16" totalsRowShown="0" headerRowBorderDxfId="22" tableBorderDxfId="21" totalsRowBorderDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D0DCC88A-2D36-4004-A694-FC0C0F0C3396}" name="Таблица2" displayName="Таблица2" ref="A1:C16" totalsRowShown="0" headerRowBorderDxfId="16" tableBorderDxfId="15" totalsRowBorderDxfId="14">
   <autoFilter ref="A1:C16" xr:uid="{00000000-0009-0000-0100-000002000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{28358E6A-6F3A-468C-9E1C-880A34D9BECE}" name="№" dataDxfId="19"/>
+    <tableColumn id="1" xr3:uid="{28358E6A-6F3A-468C-9E1C-880A34D9BECE}" name="№" dataDxfId="13"/>
     <tableColumn id="2" xr3:uid="{DD0AD5C8-324B-4DA7-B39F-B2DB3EF91222}" name="Links:"/>
-    <tableColumn id="3" xr3:uid="{FC8A6018-CA7E-4C73-9B21-B272B55FA8C1}" name="Description:" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{FC8A6018-CA7E-4C73-9B21-B272B55FA8C1}" name="Description:" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9D0F8E3D-96B1-4DB8-B1A6-8DD6B84F3693}" name="Таблица35" displayName="Таблица35" ref="A1:D52" totalsRowShown="0" headerRowDxfId="17" dataDxfId="15" headerRowBorderDxfId="16" tableBorderDxfId="14" totalsRowBorderDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9D0F8E3D-96B1-4DB8-B1A6-8DD6B84F3693}" name="Таблица35" displayName="Таблица35" ref="A1:D52" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10" tableBorderDxfId="8" totalsRowBorderDxfId="7">
   <autoFilter ref="A1:D52" xr:uid="{A2D8FA3D-4024-4365-BE1D-F93D0AF2D426}"/>
   <tableColumns count="4">
-    <tableColumn id="4" xr3:uid="{74AFB32D-7AAA-46BE-8174-ED698BB4613E}" name="Mint_id" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{523D65CD-0F56-441F-90B5-E46A9B14F0D0}" name="Ekaterinburg Mint" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{1AAB7352-E935-4EC6-A0D1-3EDC5D0BC93C}" name="Year_of_start" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{5FF15381-476A-4F88-B93A-6452F2830A0A}" name="Year_of_end" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{74AFB32D-7AAA-46BE-8174-ED698BB4613E}" name="Mint_id" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{523D65CD-0F56-441F-90B5-E46A9B14F0D0}" name="Ekaterinburg Mint" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{1AAB7352-E935-4EC6-A0D1-3EDC5D0BC93C}" name="Year_of_start" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{5FF15381-476A-4F88-B93A-6452F2830A0A}" name="Year_of_end" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4189,9 +4190,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{8354E581-3B48-4762-81A7-EA76E36C4BB5}" name="№" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{1F45DC85-8ECA-45FE-BF45-E528619CEE0E}" name="Links:" dataDxfId="7" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{3FAE616B-3296-4770-9E56-8A824991EECA}" name="Description:" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{8354E581-3B48-4762-81A7-EA76E36C4BB5}" name="№" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{1F45DC85-8ECA-45FE-BF45-E528619CEE0E}" name="Links:" dataDxfId="1" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{3FAE616B-3296-4770-9E56-8A824991EECA}" name="Description:" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -4582,12 +4583,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C7:C8">
-    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="33" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C7))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6">
-    <cfRule type="containsText" dxfId="4" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="32" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C6))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4604,7 +4605,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2">
-    <cfRule type="containsText" dxfId="3" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="31" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C2))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4621,7 +4622,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4">
-    <cfRule type="containsText" dxfId="2" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="30" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C4))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4638,7 +4639,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C5">
-    <cfRule type="containsText" dxfId="1" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="29" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C5))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4655,7 +4656,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3">
-    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="28" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C3))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -5102,36 +5103,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="61.5" x14ac:dyDescent="1.35">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="108" t="s">
         <v>565</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
-      <c r="L1" s="88"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="88"/>
-      <c r="O1" s="88"/>
-      <c r="P1" s="88"/>
-      <c r="Q1" s="88"/>
-      <c r="R1" s="88"/>
-      <c r="S1" s="88"/>
-      <c r="T1" s="88"/>
-      <c r="U1" s="88"/>
-      <c r="V1" s="88"/>
-      <c r="W1" s="88"/>
-      <c r="X1" s="88"/>
-      <c r="Y1" s="88"/>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
+      <c r="J1" s="109"/>
+      <c r="K1" s="109"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="87"/>
+      <c r="U1" s="87"/>
+      <c r="V1" s="87"/>
+      <c r="W1" s="87"/>
+      <c r="X1" s="87"/>
+      <c r="Y1" s="87"/>
     </row>
     <row r="3" spans="1:25" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="A3" s="108" t="s">
+      <c r="A3" s="88" t="s">
         <v>530</v>
       </c>
       <c r="B3" s="78" t="s">
@@ -5439,10 +5440,14 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:S1"/>
+  </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" r:id="rId1" xr:uid="{1B51AF5A-9579-4E45-802C-86E0D9768BAB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/Info/Additional_information.xlsx
+++ b/Info/Additional_information.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F049E0BF-8338-4C2C-B18A-E5FEB5B5BE2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{811409A7-A766-45EF-BD38-3D1B5B9A2605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Colours_specifications" sheetId="1" r:id="rId1"/>
@@ -19,8 +19,8 @@
     <sheet name="albums_buttons" sheetId="14" r:id="rId4"/>
     <sheet name="albums ID naming" sheetId="9" r:id="rId5"/>
     <sheet name="Mint_Alias" sheetId="5" r:id="rId6"/>
-    <sheet name="Coin_Shops" sheetId="8" r:id="rId7"/>
-    <sheet name="Mint_work_years" sheetId="6" r:id="rId8"/>
+    <sheet name="Mint_work_years" sheetId="6" r:id="rId7"/>
+    <sheet name="Coin_Shops" sheetId="8" r:id="rId8"/>
     <sheet name="File_Naming" sheetId="2" r:id="rId9"/>
     <sheet name="Existing_subtypes" sheetId="3" r:id="rId10"/>
     <sheet name="Links_to_Data" sheetId="7" r:id="rId11"/>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1217" uniqueCount="855">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1226" uniqueCount="869">
   <si>
     <t>good quality (UNC for UNC collection; UNC and XF for XF collection)</t>
   </si>
@@ -1204,9 +1204,6 @@
     <t>Orange</t>
   </si>
   <si>
-    <t>Annual Sets</t>
-  </si>
-  <si>
     <t>BK</t>
   </si>
   <si>
@@ -1738,18 +1735,6 @@
     <t xml:space="preserve">	Light Brown</t>
   </si>
   <si>
-    <t>Kazachstan, Indian, Russian Empire coins</t>
-  </si>
-  <si>
-    <t>Монеты Казахстана, Индии, Российской империи</t>
-  </si>
-  <si>
-    <t>Great Britain, Ukrainian and German coins</t>
-  </si>
-  <si>
-    <t>Монеты Великобритании, Украины и Германии</t>
-  </si>
-  <si>
     <t>Spain and Canada regular and commemorative coins</t>
   </si>
   <si>
@@ -1840,12 +1825,6 @@
     <t>Регулярка,Регулярные,Юбилейные,Канада,Испания,Canada,Spain</t>
   </si>
   <si>
-    <t>Регулярка,Регулярные,Юбилейные,Казахстан,Kazakhstan,Британская Индия,Великобритания,Great Britain,British India,Индия,India,Российская Империя,Россия,Russian Empire</t>
-  </si>
-  <si>
-    <t>Регулярка,Регулярные,Юбилейные,Великобритания,Great Britain,Украина,Ukraine,Германия,Germany,Германская империя,German Empire,Веймарская республика,Weimar Republic,Третий Рейх,Third Reich,Nazi Germany,ГДР,GDR,ФРГ,BRD</t>
-  </si>
-  <si>
     <t>Монеты мира (часть 2) Азия</t>
   </si>
   <si>
@@ -2332,9 +2311,6 @@
     <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/Spain/%23Spain%23Regular%23%5B1934-2001%5D%23circulation_quality.xlsx</t>
   </si>
   <si>
-    <t>Регулярные монеты Испании</t>
-  </si>
-  <si>
     <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/Spain/</t>
   </si>
   <si>
@@ -2645,6 +2621,72 @@
   </si>
   <si>
     <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A015-01-OA-LN</t>
+  </si>
+  <si>
+    <t>Annual Sets or special Sets</t>
+  </si>
+  <si>
+    <t>Юбилейные монеты Индии [1964-present]</t>
+  </si>
+  <si>
+    <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/India/%23Republic_of_India%23Commemorativer%23%5B1964-present%5D%23circulation_quality.xlsx</t>
+  </si>
+  <si>
+    <t>Регулярка,Регулярные,Юбилейные,Казахстан,Kazakhstan</t>
+  </si>
+  <si>
+    <t>Регулярные и юбилейны монеты Казахстана</t>
+  </si>
+  <si>
+    <t>Kazachstan regular and commemorative coins</t>
+  </si>
+  <si>
+    <t>Монеты Украины, Индии, Великобритании</t>
+  </si>
+  <si>
+    <t>Great Britain, Ukrainian, Indian coins</t>
+  </si>
+  <si>
+    <t>Регулярка,Регулярные,Юбилейные,Украина,Ukraine,Британская Индия,Великобритания,Great Britain,British India,Индия,India,United Kingdom,Соединённое королевство</t>
+  </si>
+  <si>
+    <t>Russian Empire and German coins</t>
+  </si>
+  <si>
+    <t>Монеты Российской империи и Германии</t>
+  </si>
+  <si>
+    <t>Российская Империя,Россия,Russian Empire,Германия,Germany,Германская империя,German Empire,Веймарская республика,Weimar Republic,Третий Рейх,Third Reich,Nazi Germany,ГДР,GDR,ФРГ,BRD</t>
+  </si>
+  <si>
+    <t>A009-01-FB-BN</t>
+  </si>
+  <si>
+    <t>A009-02-FB-DN</t>
+  </si>
+  <si>
+    <t>A010-01-OA-DB</t>
+  </si>
+  <si>
+    <t>A011-01-OA-GR</t>
+  </si>
+  <si>
+    <t>A011-02-OA-GR</t>
+  </si>
+  <si>
+    <t>A012-01-OA-BU</t>
+  </si>
+  <si>
+    <t>A013-01-OA-LN</t>
+  </si>
+  <si>
+    <t>A014-01-OA-DN</t>
+  </si>
+  <si>
+    <t>A015-01-OA-BK</t>
+  </si>
+  <si>
+    <t>A016-01-OA-BK</t>
   </si>
 </sst>
 </file>
@@ -3540,6 +3582,54 @@
   </cellStyles>
   <dxfs count="34">
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -4023,54 +4113,6 @@
         </horizontal>
       </border>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -4139,46 +4181,46 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{973D7237-72C7-453E-A0E1-526C93326B28}" name="Таблица3" displayName="Таблица3" ref="A1:F51" totalsRowShown="0" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{973D7237-72C7-453E-A0E1-526C93326B28}" name="Таблица3" displayName="Таблица3" ref="A1:F51" totalsRowShown="0" headerRowDxfId="33" dataDxfId="31" headerRowBorderDxfId="32" tableBorderDxfId="30" totalsRowBorderDxfId="29">
   <autoFilter ref="A1:F51" xr:uid="{A2D8FA3D-4024-4365-BE1D-F93D0AF2D426}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{12C2DF0B-47FA-46A4-8424-55A1488EF88B}" name="ID" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{EB0B36CE-168D-429E-896D-DBA54794224F}" name="Name_Eng" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{6C3A2CE8-252E-4C52-985B-8CDDFD9FA0C7}" name="OfficialMintName_Native" dataDxfId="20"/>
-    <tableColumn id="8" xr3:uid="{DA5871DC-2EDB-49C0-953E-EC0F70288E21}" name="Country" dataDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{FCD85F85-A94E-4BBE-9D3B-2B7494638375}" name="Mint_City" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{E5141978-CA91-4DE9-86F1-8A8AFA716534}" name="Alias" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{12C2DF0B-47FA-46A4-8424-55A1488EF88B}" name="ID" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{EB0B36CE-168D-429E-896D-DBA54794224F}" name="Name_Eng" dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{6C3A2CE8-252E-4C52-985B-8CDDFD9FA0C7}" name="OfficialMintName_Native" dataDxfId="26"/>
+    <tableColumn id="8" xr3:uid="{DA5871DC-2EDB-49C0-953E-EC0F70288E21}" name="Country" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{FCD85F85-A94E-4BBE-9D3B-2B7494638375}" name="Mint_City" dataDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{E5141978-CA91-4DE9-86F1-8A8AFA716534}" name="Alias" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D0DCC88A-2D36-4004-A694-FC0C0F0C3396}" name="Таблица2" displayName="Таблица2" ref="A1:C16" totalsRowShown="0" headerRowBorderDxfId="16" tableBorderDxfId="15" totalsRowBorderDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9D0F8E3D-96B1-4DB8-B1A6-8DD6B84F3693}" name="Таблица35" displayName="Таблица35" ref="A1:D52" totalsRowShown="0" headerRowDxfId="17" dataDxfId="15" headerRowBorderDxfId="16" tableBorderDxfId="14" totalsRowBorderDxfId="13">
+  <autoFilter ref="A1:D52" xr:uid="{A2D8FA3D-4024-4365-BE1D-F93D0AF2D426}"/>
+  <tableColumns count="4">
+    <tableColumn id="4" xr3:uid="{74AFB32D-7AAA-46BE-8174-ED698BB4613E}" name="Mint_id" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{523D65CD-0F56-441F-90B5-E46A9B14F0D0}" name="Ekaterinburg Mint" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{1AAB7352-E935-4EC6-A0D1-3EDC5D0BC93C}" name="Year_of_start" dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{5FF15381-476A-4F88-B93A-6452F2830A0A}" name="Year_of_end" dataDxfId="9"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D0DCC88A-2D36-4004-A694-FC0C0F0C3396}" name="Таблица2" displayName="Таблица2" ref="A1:C16" totalsRowShown="0" headerRowBorderDxfId="22" tableBorderDxfId="21" totalsRowBorderDxfId="20">
   <autoFilter ref="A1:C16" xr:uid="{00000000-0009-0000-0100-000002000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{28358E6A-6F3A-468C-9E1C-880A34D9BECE}" name="№" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{28358E6A-6F3A-468C-9E1C-880A34D9BECE}" name="№" dataDxfId="19"/>
     <tableColumn id="2" xr3:uid="{DD0AD5C8-324B-4DA7-B39F-B2DB3EF91222}" name="Links:"/>
-    <tableColumn id="3" xr3:uid="{FC8A6018-CA7E-4C73-9B21-B272B55FA8C1}" name="Description:" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{FC8A6018-CA7E-4C73-9B21-B272B55FA8C1}" name="Description:" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9D0F8E3D-96B1-4DB8-B1A6-8DD6B84F3693}" name="Таблица35" displayName="Таблица35" ref="A1:D52" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10" tableBorderDxfId="8" totalsRowBorderDxfId="7">
-  <autoFilter ref="A1:D52" xr:uid="{A2D8FA3D-4024-4365-BE1D-F93D0AF2D426}"/>
-  <tableColumns count="4">
-    <tableColumn id="4" xr3:uid="{74AFB32D-7AAA-46BE-8174-ED698BB4613E}" name="Mint_id" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{523D65CD-0F56-441F-90B5-E46A9B14F0D0}" name="Ekaterinburg Mint" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{1AAB7352-E935-4EC6-A0D1-3EDC5D0BC93C}" name="Year_of_start" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{5FF15381-476A-4F88-B93A-6452F2830A0A}" name="Year_of_end" dataDxfId="3"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -4190,9 +4232,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{8354E581-3B48-4762-81A7-EA76E36C4BB5}" name="№" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{1F45DC85-8ECA-45FE-BF45-E528619CEE0E}" name="Links:" dataDxfId="1" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{3FAE616B-3296-4770-9E56-8A824991EECA}" name="Description:" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{8354E581-3B48-4762-81A7-EA76E36C4BB5}" name="№" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{1F45DC85-8ECA-45FE-BF45-E528619CEE0E}" name="Links:" dataDxfId="7" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{3FAE616B-3296-4770-9E56-8A824991EECA}" name="Description:" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -4578,17 +4620,17 @@
         <v>1</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>374</v>
+        <v>847</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C7:C8">
-    <cfRule type="containsText" dxfId="33" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C7))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6">
-    <cfRule type="containsText" dxfId="32" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="4" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C6))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4605,7 +4647,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2">
-    <cfRule type="containsText" dxfId="31" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="3" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C2))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4622,7 +4664,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4">
-    <cfRule type="containsText" dxfId="30" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="2" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C4))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4639,7 +4681,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C5">
-    <cfRule type="containsText" dxfId="29" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="1" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C5))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4656,7 +4698,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3">
-    <cfRule type="containsText" dxfId="28" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C3))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -5104,7 +5146,7 @@
   <sheetData>
     <row r="1" spans="1:25" ht="61.5" x14ac:dyDescent="1.35">
       <c r="A1" s="108" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="B1" s="109"/>
       <c r="C1" s="109"/>
@@ -5133,13 +5175,13 @@
     </row>
     <row r="3" spans="1:25" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A3" s="88" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B3" s="78" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C3" s="78" t="s">
-        <v>827</v>
+        <v>819</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.35">
@@ -5147,10 +5189,10 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C4" t="s">
-        <v>828</v>
+        <v>820</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.35">
@@ -5158,10 +5200,10 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C5" t="s">
-        <v>829</v>
+        <v>821</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.35">
@@ -5169,10 +5211,10 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C6" t="s">
-        <v>830</v>
+        <v>822</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.35">
@@ -5180,10 +5222,10 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C7" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.35">
@@ -5191,10 +5233,10 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C8" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.35">
@@ -5202,10 +5244,10 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C9" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.35">
@@ -5213,10 +5255,10 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C10" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.35">
@@ -5224,10 +5266,10 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C11" t="s">
-        <v>835</v>
+        <v>827</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.35">
@@ -5235,10 +5277,10 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C12" t="s">
-        <v>836</v>
+        <v>828</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.35">
@@ -5246,10 +5288,10 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C13" t="s">
-        <v>837</v>
+        <v>829</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.35">
@@ -5257,10 +5299,10 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C14" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.35">
@@ -5268,10 +5310,10 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C15" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.35">
@@ -5279,10 +5321,10 @@
         <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C16" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
@@ -5290,10 +5332,10 @@
         <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C17" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
@@ -5301,10 +5343,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C18" t="s">
-        <v>842</v>
+        <v>834</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
@@ -5312,10 +5354,10 @@
         <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C19" t="s">
-        <v>843</v>
+        <v>835</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
@@ -5323,10 +5365,10 @@
         <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C20" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
@@ -5334,10 +5376,10 @@
         <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C21" t="s">
-        <v>845</v>
+        <v>837</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
@@ -5345,10 +5387,10 @@
         <v>18</v>
       </c>
       <c r="B22" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="C22" t="s">
-        <v>846</v>
+        <v>838</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
@@ -5356,10 +5398,10 @@
         <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>804</v>
+        <v>796</v>
       </c>
       <c r="C23" t="s">
-        <v>847</v>
+        <v>839</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
@@ -5367,10 +5409,10 @@
         <v>20</v>
       </c>
       <c r="B24" t="s">
-        <v>805</v>
+        <v>797</v>
       </c>
       <c r="C24" t="s">
-        <v>848</v>
+        <v>840</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
@@ -5378,10 +5420,10 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>806</v>
+        <v>798</v>
       </c>
       <c r="C25" t="s">
-        <v>849</v>
+        <v>841</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
@@ -5389,10 +5431,10 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>807</v>
+        <v>799</v>
       </c>
       <c r="C26" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
@@ -5400,10 +5442,10 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>808</v>
+        <v>800</v>
       </c>
       <c r="C27" t="s">
-        <v>851</v>
+        <v>843</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
@@ -5411,10 +5453,10 @@
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>809</v>
+        <v>801</v>
       </c>
       <c r="C28" t="s">
-        <v>852</v>
+        <v>844</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
@@ -5422,10 +5464,10 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>810</v>
+        <v>802</v>
       </c>
       <c r="C29" t="s">
-        <v>853</v>
+        <v>845</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
@@ -5433,10 +5475,10 @@
         <v>26</v>
       </c>
       <c r="B30" t="s">
-        <v>811</v>
+        <v>803</v>
       </c>
       <c r="C30" t="s">
-        <v>854</v>
+        <v>846</v>
       </c>
     </row>
   </sheetData>
@@ -5785,7 +5827,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DC835FD-69FE-4DBC-957F-9A46CA05517E}">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.453125" customWidth="1"/>
@@ -5797,19 +5839,19 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="78" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B1" s="78" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C1" s="78" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D1" s="78" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E1" s="78" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5817,16 +5859,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E2" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -5834,16 +5876,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C3" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D3" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E3" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -5851,16 +5893,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C4" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D4" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E4" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -5868,16 +5910,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C5" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D5" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E5" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -5885,16 +5927,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C6" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D6" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E6" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -5902,16 +5944,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C7" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D7" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E7" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -5919,16 +5961,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C8" t="s">
+        <v>495</v>
+      </c>
+      <c r="D8" t="s">
         <v>496</v>
       </c>
-      <c r="D8" t="s">
-        <v>497</v>
-      </c>
       <c r="E8" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -5936,16 +5978,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C9" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D9" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="E9" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -5953,16 +5995,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C10" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D10" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E10" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -5970,16 +6012,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C11" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D11" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E11" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -5987,16 +6029,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C12" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E12" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -6004,16 +6046,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C13" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D13" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="E13" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
@@ -6021,16 +6063,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C14" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D14" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E14" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
@@ -6038,16 +6080,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C15" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D15" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E15" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
@@ -6055,16 +6097,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C16" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="D16" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E16" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
@@ -6072,16 +6114,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C17" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D17" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E17" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
@@ -6089,16 +6131,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C18" t="s">
+        <v>543</v>
+      </c>
+      <c r="D18" t="s">
         <v>544</v>
       </c>
-      <c r="D18" t="s">
-        <v>545</v>
-      </c>
       <c r="E18" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
@@ -6106,169 +6148,186 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C19" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="D19" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="E19" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>564</v>
+        <v>859</v>
       </c>
       <c r="C20" t="s">
-        <v>552</v>
+        <v>583</v>
       </c>
       <c r="D20" t="s">
-        <v>553</v>
+        <v>582</v>
       </c>
       <c r="E20" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>804</v>
+        <v>860</v>
       </c>
       <c r="C21" t="s">
-        <v>554</v>
+        <v>584</v>
       </c>
       <c r="D21" t="s">
-        <v>555</v>
+        <v>581</v>
       </c>
       <c r="E21" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>805</v>
+        <v>861</v>
       </c>
       <c r="C22" t="s">
-        <v>590</v>
+        <v>553</v>
       </c>
       <c r="D22" t="s">
-        <v>589</v>
+        <v>552</v>
       </c>
       <c r="E22" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>806</v>
+        <v>862</v>
       </c>
       <c r="C23" t="s">
-        <v>591</v>
+        <v>554</v>
       </c>
       <c r="D23" t="s">
-        <v>588</v>
+        <v>555</v>
       </c>
       <c r="E23" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B24" t="s">
-        <v>807</v>
+        <v>863</v>
       </c>
       <c r="C24" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="D24" t="s">
-        <v>557</v>
+        <v>588</v>
       </c>
       <c r="E24" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>808</v>
+        <v>864</v>
       </c>
       <c r="C25" t="s">
-        <v>559</v>
+        <v>591</v>
       </c>
       <c r="D25" t="s">
-        <v>560</v>
+        <v>590</v>
       </c>
       <c r="E25" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>809</v>
+        <v>865</v>
       </c>
       <c r="C26" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="D26" t="s">
-        <v>595</v>
+        <v>557</v>
       </c>
       <c r="E26" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>810</v>
+        <v>866</v>
       </c>
       <c r="C27" t="s">
-        <v>598</v>
+        <v>852</v>
       </c>
       <c r="D27" t="s">
-        <v>597</v>
+        <v>851</v>
       </c>
       <c r="E27" t="s">
-        <v>599</v>
+        <v>850</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>811</v>
+        <v>867</v>
       </c>
       <c r="C28" t="s">
-        <v>563</v>
+        <v>854</v>
       </c>
       <c r="D28" t="s">
-        <v>562</v>
+        <v>853</v>
       </c>
       <c r="E28" t="s">
-        <v>600</v>
+        <v>855</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>29</v>
+      </c>
+      <c r="B29" t="s">
+        <v>868</v>
+      </c>
+      <c r="C29" t="s">
+        <v>856</v>
+      </c>
+      <c r="D29" t="s">
+        <v>857</v>
+      </c>
+      <c r="E29" t="s">
+        <v>858</v>
       </c>
     </row>
   </sheetData>
@@ -6281,12 +6340,12 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C94A307-2E39-40B9-B204-C92675C0AF71}">
-  <dimension ref="A1:E87"/>
+  <dimension ref="A1:E88"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.36328125" customWidth="1"/>
     <col min="2" max="2" width="57.54296875" customWidth="1"/>
-    <col min="3" max="3" width="39.1796875" customWidth="1"/>
+    <col min="3" max="3" width="62.26953125" customWidth="1"/>
     <col min="4" max="4" width="151" customWidth="1"/>
     <col min="5" max="5" width="79.54296875" customWidth="1"/>
     <col min="6" max="6" width="62" customWidth="1"/>
@@ -6294,1415 +6353,1432 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>601</v>
+        <v>594</v>
       </c>
       <c r="B1" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
       <c r="C1" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="D1" t="s">
-        <v>604</v>
+        <v>597</v>
       </c>
       <c r="E1" t="s">
-        <v>605</v>
+        <v>598</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B2" s="86" t="s">
-        <v>653</v>
+        <v>646</v>
       </c>
       <c r="C2" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="D2" s="86" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="E2" s="86" t="s">
-        <v>652</v>
+        <v>645</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B3" s="86" t="s">
-        <v>654</v>
+        <v>647</v>
       </c>
       <c r="C3" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="D3" s="86" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="E3" s="86" t="s">
-        <v>657</v>
+        <v>650</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B4" s="86" t="s">
-        <v>649</v>
+        <v>642</v>
       </c>
       <c r="C4" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="D4" s="86" t="s">
-        <v>606</v>
+        <v>599</v>
       </c>
       <c r="E4" s="86" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B5" s="86" t="s">
-        <v>648</v>
+        <v>641</v>
       </c>
       <c r="C5" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="D5" s="86" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="E5" s="86" t="s">
-        <v>611</v>
+        <v>604</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B6" s="86" t="s">
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="C6" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
       <c r="D6" s="86" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
       <c r="E6" s="86" t="s">
-        <v>613</v>
+        <v>606</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B7" s="86" t="s">
-        <v>646</v>
+        <v>639</v>
       </c>
       <c r="C7" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="D7" s="86" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
       <c r="E7" s="86" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B8" s="86" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="C8" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="D8" s="86" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
       <c r="E8" s="86" t="s">
-        <v>620</v>
+        <v>613</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B9" s="86" t="s">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="C9" t="s">
-        <v>622</v>
+        <v>615</v>
       </c>
       <c r="D9" s="86" t="s">
-        <v>621</v>
+        <v>614</v>
       </c>
       <c r="E9" s="86" t="s">
-        <v>623</v>
+        <v>616</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B10" s="86" t="s">
-        <v>643</v>
+        <v>636</v>
       </c>
       <c r="C10" t="s">
-        <v>625</v>
+        <v>618</v>
       </c>
       <c r="D10" s="86" t="s">
-        <v>624</v>
+        <v>617</v>
       </c>
       <c r="E10" s="86" t="s">
-        <v>626</v>
+        <v>619</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B11" s="86" t="s">
-        <v>642</v>
+        <v>635</v>
       </c>
       <c r="C11" t="s">
-        <v>629</v>
+        <v>622</v>
       </c>
       <c r="D11" s="86" t="s">
-        <v>627</v>
+        <v>620</v>
       </c>
       <c r="E11" s="86" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B12" s="86" t="s">
-        <v>641</v>
+        <v>634</v>
       </c>
       <c r="C12" t="s">
-        <v>631</v>
+        <v>624</v>
       </c>
       <c r="D12" s="86" t="s">
-        <v>630</v>
+        <v>623</v>
       </c>
       <c r="E12" s="86" t="s">
-        <v>632</v>
+        <v>625</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B13" s="86" t="s">
-        <v>639</v>
+        <v>632</v>
       </c>
       <c r="C13" t="s">
-        <v>634</v>
+        <v>627</v>
       </c>
       <c r="D13" s="86" t="s">
-        <v>633</v>
+        <v>626</v>
       </c>
       <c r="E13" s="86" t="s">
-        <v>635</v>
+        <v>628</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B14" s="86" t="s">
-        <v>640</v>
+        <v>633</v>
       </c>
       <c r="C14" t="s">
-        <v>637</v>
+        <v>630</v>
       </c>
       <c r="D14" s="86" t="s">
-        <v>636</v>
+        <v>629</v>
       </c>
       <c r="E14" s="86" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B15" s="86" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="C15" t="s">
-        <v>660</v>
+        <v>653</v>
       </c>
       <c r="D15" s="86" t="s">
-        <v>658</v>
+        <v>651</v>
       </c>
       <c r="E15" s="86" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B16" s="86" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="C16" t="s">
-        <v>664</v>
+        <v>657</v>
       </c>
       <c r="D16" s="86" t="s">
-        <v>662</v>
+        <v>655</v>
       </c>
       <c r="E16" s="86" t="s">
-        <v>663</v>
+        <v>656</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B17" s="86" t="s">
-        <v>669</v>
+        <v>662</v>
       </c>
       <c r="C17" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="D17" s="86" t="s">
-        <v>667</v>
+        <v>660</v>
       </c>
       <c r="E17" s="86" t="s">
-        <v>668</v>
+        <v>661</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B18" s="86" t="s">
-        <v>670</v>
+        <v>663</v>
       </c>
       <c r="C18" t="s">
-        <v>671</v>
+        <v>664</v>
       </c>
       <c r="D18" s="86" t="s">
-        <v>672</v>
+        <v>665</v>
       </c>
       <c r="E18" s="86" t="s">
-        <v>673</v>
+        <v>666</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B19" s="86" t="s">
-        <v>677</v>
+        <v>670</v>
       </c>
       <c r="C19" t="s">
-        <v>676</v>
+        <v>669</v>
       </c>
       <c r="D19" s="86" t="s">
-        <v>674</v>
+        <v>667</v>
       </c>
       <c r="E19" s="86" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B20" s="86" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="C20" t="s">
-        <v>679</v>
+        <v>672</v>
       </c>
       <c r="D20" s="86" t="s">
-        <v>680</v>
+        <v>673</v>
       </c>
       <c r="E20" s="86" t="s">
-        <v>681</v>
+        <v>674</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B21" s="86" t="s">
-        <v>685</v>
+        <v>678</v>
       </c>
       <c r="C21" t="s">
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="D21" s="86" t="s">
-        <v>682</v>
+        <v>675</v>
       </c>
       <c r="E21" s="86" t="s">
-        <v>683</v>
+        <v>676</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B22" s="86" t="s">
-        <v>689</v>
+        <v>682</v>
       </c>
       <c r="C22" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="D22" s="86" t="s">
-        <v>686</v>
+        <v>679</v>
       </c>
       <c r="E22" s="86" t="s">
-        <v>687</v>
+        <v>680</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B23" s="86" t="s">
-        <v>693</v>
+        <v>686</v>
       </c>
       <c r="C23" t="s">
-        <v>692</v>
+        <v>685</v>
       </c>
       <c r="D23" s="86" t="s">
-        <v>690</v>
+        <v>683</v>
       </c>
       <c r="E23" s="86" t="s">
-        <v>691</v>
+        <v>684</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B24" s="86" t="s">
-        <v>697</v>
+        <v>690</v>
       </c>
       <c r="C24" t="s">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="D24" s="86" t="s">
-        <v>694</v>
+        <v>687</v>
       </c>
       <c r="E24" s="86" t="s">
-        <v>696</v>
+        <v>689</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B25" s="86" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="C25" t="s">
-        <v>699</v>
+        <v>692</v>
       </c>
       <c r="D25" s="86" t="s">
-        <v>698</v>
+        <v>691</v>
       </c>
       <c r="E25" s="86" t="s">
-        <v>700</v>
+        <v>693</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B26" s="86" t="s">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="C26" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="D26" s="86" t="s">
-        <v>702</v>
+        <v>695</v>
       </c>
       <c r="E26" s="86" t="s">
-        <v>703</v>
+        <v>696</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C27" t="s">
-        <v>706</v>
+        <v>699</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C28" t="s">
-        <v>706</v>
+        <v>699</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B29" s="86" t="s">
-        <v>710</v>
+        <v>703</v>
       </c>
       <c r="C29" t="s">
-        <v>709</v>
+        <v>702</v>
       </c>
       <c r="D29" s="86" t="s">
-        <v>707</v>
+        <v>700</v>
       </c>
       <c r="E29" s="86" t="s">
-        <v>708</v>
+        <v>701</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B30" s="86" t="s">
-        <v>710</v>
+        <v>703</v>
       </c>
       <c r="C30" t="s">
-        <v>711</v>
+        <v>704</v>
       </c>
       <c r="D30" s="86" t="s">
-        <v>707</v>
+        <v>700</v>
       </c>
       <c r="E30" s="86" t="s">
-        <v>708</v>
+        <v>701</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B31" s="86" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="C31" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D31" s="86" t="s">
-        <v>712</v>
+        <v>705</v>
       </c>
       <c r="E31" s="86" t="s">
-        <v>713</v>
+        <v>706</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B32" s="86" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="C32" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D32" s="86" t="s">
-        <v>712</v>
+        <v>705</v>
       </c>
       <c r="E32" s="86" t="s">
-        <v>713</v>
+        <v>706</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B33" s="86" t="s">
-        <v>649</v>
+        <v>642</v>
       </c>
       <c r="C33" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="D33" s="86" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="E33" s="86" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B34" s="86" t="s">
-        <v>648</v>
+        <v>641</v>
       </c>
       <c r="C34" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="D34" s="86" t="s">
-        <v>716</v>
+        <v>709</v>
       </c>
       <c r="E34" s="86" t="s">
-        <v>611</v>
+        <v>604</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B35" s="86" t="s">
-        <v>720</v>
+        <v>713</v>
       </c>
       <c r="C35" t="s">
-        <v>717</v>
+        <v>710</v>
       </c>
       <c r="D35" s="86" t="s">
-        <v>718</v>
+        <v>711</v>
       </c>
       <c r="E35" s="86" t="s">
-        <v>719</v>
+        <v>712</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B36" s="86" t="s">
-        <v>701</v>
+        <v>694</v>
       </c>
       <c r="C36" t="s">
-        <v>699</v>
+        <v>692</v>
       </c>
       <c r="D36" s="86" t="s">
-        <v>721</v>
+        <v>714</v>
       </c>
       <c r="E36" s="86" t="s">
-        <v>700</v>
+        <v>693</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B37" s="86" t="s">
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="C37" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
       <c r="D37" s="86" t="s">
-        <v>722</v>
+        <v>715</v>
       </c>
       <c r="E37" s="86" t="s">
-        <v>613</v>
+        <v>606</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B38" s="86" t="s">
-        <v>646</v>
+        <v>639</v>
       </c>
       <c r="C38" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="D38" s="86" t="s">
-        <v>723</v>
+        <v>716</v>
       </c>
       <c r="E38" s="86" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B39" s="86" t="s">
-        <v>685</v>
+        <v>678</v>
       </c>
       <c r="C39" t="s">
-        <v>684</v>
+        <v>677</v>
       </c>
       <c r="D39" s="86" t="s">
-        <v>724</v>
+        <v>717</v>
       </c>
       <c r="E39" s="86" t="s">
-        <v>683</v>
+        <v>676</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B40" s="86" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="C40" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="D40" s="86" t="s">
-        <v>725</v>
+        <v>718</v>
       </c>
       <c r="E40" s="86" t="s">
-        <v>620</v>
+        <v>613</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B41" s="86" t="s">
-        <v>661</v>
+        <v>654</v>
       </c>
       <c r="C41" t="s">
-        <v>660</v>
+        <v>653</v>
       </c>
       <c r="D41" s="86" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
       <c r="E41" s="86" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B42" s="86" t="s">
-        <v>705</v>
+        <v>698</v>
       </c>
       <c r="C42" t="s">
-        <v>704</v>
+        <v>697</v>
       </c>
       <c r="D42" s="86" t="s">
-        <v>727</v>
+        <v>720</v>
       </c>
       <c r="E42" s="86" t="s">
-        <v>703</v>
+        <v>696</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B43" s="86" t="s">
-        <v>642</v>
+        <v>635</v>
       </c>
       <c r="C43" t="s">
-        <v>629</v>
+        <v>622</v>
       </c>
       <c r="D43" s="86" t="s">
-        <v>728</v>
+        <v>721</v>
       </c>
       <c r="E43" s="86" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B44" s="86" t="s">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="C44" t="s">
-        <v>622</v>
+        <v>615</v>
       </c>
       <c r="D44" s="86" t="s">
-        <v>729</v>
+        <v>722</v>
       </c>
       <c r="E44" s="86" t="s">
-        <v>623</v>
+        <v>616</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B45" s="86" t="s">
-        <v>643</v>
+        <v>636</v>
       </c>
       <c r="C45" t="s">
-        <v>625</v>
+        <v>618</v>
       </c>
       <c r="D45" s="86" t="s">
-        <v>730</v>
+        <v>723</v>
       </c>
       <c r="E45" s="86" t="s">
-        <v>626</v>
+        <v>619</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B46" s="86" t="s">
-        <v>665</v>
+        <v>658</v>
       </c>
       <c r="C46" t="s">
-        <v>664</v>
+        <v>657</v>
       </c>
       <c r="D46" s="86" t="s">
-        <v>731</v>
+        <v>724</v>
       </c>
       <c r="E46" s="86" t="s">
-        <v>663</v>
+        <v>656</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B47" s="86" t="s">
-        <v>669</v>
+        <v>662</v>
       </c>
       <c r="C47" t="s">
-        <v>666</v>
+        <v>659</v>
       </c>
       <c r="D47" s="83" t="s">
-        <v>733</v>
+        <v>726</v>
       </c>
       <c r="E47" s="86" t="s">
-        <v>732</v>
+        <v>725</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B48" s="86" t="s">
-        <v>653</v>
+        <v>646</v>
       </c>
       <c r="C48" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="D48" s="86" t="s">
-        <v>734</v>
+        <v>727</v>
       </c>
       <c r="E48" s="86" t="s">
-        <v>652</v>
+        <v>645</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B49" s="86" t="s">
-        <v>639</v>
+        <v>632</v>
       </c>
       <c r="C49" t="s">
-        <v>634</v>
+        <v>627</v>
       </c>
       <c r="D49" s="86" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="E49" s="86" t="s">
-        <v>635</v>
+        <v>628</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B50" s="86" t="s">
-        <v>640</v>
+        <v>633</v>
       </c>
       <c r="C50" t="s">
-        <v>637</v>
+        <v>630</v>
       </c>
       <c r="D50" s="86" t="s">
-        <v>736</v>
+        <v>729</v>
       </c>
       <c r="E50" s="86" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B51" s="86" t="s">
-        <v>677</v>
+        <v>670</v>
       </c>
       <c r="C51" t="s">
-        <v>676</v>
+        <v>669</v>
       </c>
       <c r="D51" s="86" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="E51" s="86" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B52" s="86" t="s">
-        <v>697</v>
+        <v>690</v>
       </c>
       <c r="C52" t="s">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="D52" s="86" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="E52" s="86" t="s">
-        <v>696</v>
+        <v>689</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B53" s="86" t="s">
-        <v>689</v>
+        <v>682</v>
       </c>
       <c r="C53" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="D53" s="86" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="E53" s="86" t="s">
-        <v>687</v>
+        <v>680</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B54" s="86" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="C54" t="s">
-        <v>741</v>
+        <v>734</v>
       </c>
       <c r="D54" s="86" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="E54" s="86" t="s">
-        <v>708</v>
+        <v>701</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B55" s="86" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="C55" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="D55" s="86" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="E55" s="86" t="s">
-        <v>708</v>
+        <v>701</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B56" s="86" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="C56" t="s">
-        <v>744</v>
+        <v>737</v>
       </c>
       <c r="D56" s="86" t="s">
-        <v>743</v>
+        <v>736</v>
       </c>
       <c r="E56" s="86" t="s">
-        <v>713</v>
+        <v>706</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B57" s="86" t="s">
-        <v>746</v>
+        <v>739</v>
       </c>
       <c r="C57" t="s">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="D57" s="86" t="s">
-        <v>712</v>
+        <v>705</v>
       </c>
       <c r="E57" s="86" t="s">
-        <v>713</v>
+        <v>706</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B58" s="86" t="s">
-        <v>746</v>
+        <v>739</v>
       </c>
       <c r="C58" t="s">
-        <v>747</v>
+        <v>740</v>
       </c>
       <c r="D58" s="86" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="E58" s="86" t="s">
-        <v>713</v>
+        <v>706</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B59" s="86" t="s">
-        <v>689</v>
+        <v>682</v>
       </c>
       <c r="C59" t="s">
-        <v>750</v>
+        <v>740</v>
       </c>
       <c r="D59" s="86" t="s">
-        <v>749</v>
+        <v>742</v>
       </c>
       <c r="E59" s="86" t="s">
-        <v>751</v>
+        <v>743</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B60" s="86" t="s">
-        <v>755</v>
+        <v>747</v>
       </c>
       <c r="C60" t="s">
-        <v>754</v>
+        <v>746</v>
       </c>
       <c r="D60" s="86" t="s">
-        <v>752</v>
+        <v>744</v>
       </c>
       <c r="E60" s="86" t="s">
-        <v>753</v>
+        <v>745</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B61" s="86" t="s">
-        <v>755</v>
+        <v>747</v>
       </c>
       <c r="C61" t="s">
-        <v>756</v>
+        <v>748</v>
       </c>
       <c r="D61" s="86" t="s">
-        <v>757</v>
+        <v>749</v>
       </c>
       <c r="E61" s="86" t="s">
-        <v>753</v>
+        <v>745</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>564</v>
+        <v>859</v>
       </c>
       <c r="B62" s="86" t="s">
-        <v>761</v>
+        <v>647</v>
       </c>
       <c r="C62" t="s">
-        <v>759</v>
+        <v>795</v>
       </c>
       <c r="D62" s="86" t="s">
-        <v>758</v>
+        <v>804</v>
       </c>
       <c r="E62" s="86" t="s">
-        <v>760</v>
+        <v>650</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>564</v>
+        <v>860</v>
       </c>
       <c r="B63" s="86" t="s">
-        <v>761</v>
+        <v>647</v>
       </c>
       <c r="C63" t="s">
-        <v>763</v>
+        <v>805</v>
       </c>
       <c r="D63" s="86" t="s">
-        <v>762</v>
+        <v>804</v>
       </c>
       <c r="E63" s="86" t="s">
-        <v>760</v>
+        <v>650</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>564</v>
-      </c>
-      <c r="B64" s="86" t="s">
-        <v>767</v>
+        <v>862</v>
+      </c>
+      <c r="B64" t="s">
+        <v>806</v>
       </c>
       <c r="C64" t="s">
-        <v>765</v>
-      </c>
-      <c r="D64" s="86" t="s">
-        <v>764</v>
-      </c>
-      <c r="E64" s="86" t="s">
-        <v>766</v>
+        <v>552</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>564</v>
-      </c>
-      <c r="B65" s="86" t="s">
-        <v>770</v>
+        <v>862</v>
+      </c>
+      <c r="B65" t="s">
+        <v>807</v>
       </c>
       <c r="C65" t="s">
-        <v>772</v>
-      </c>
-      <c r="D65" s="86" t="s">
-        <v>768</v>
-      </c>
-      <c r="E65" s="86" t="s">
-        <v>769</v>
+        <v>555</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>564</v>
-      </c>
-      <c r="B66" s="86" t="s">
-        <v>770</v>
+        <v>863</v>
+      </c>
+      <c r="B66" t="s">
+        <v>808</v>
       </c>
       <c r="C66" t="s">
-        <v>773</v>
-      </c>
-      <c r="D66" s="86" t="s">
-        <v>771</v>
-      </c>
-      <c r="E66" s="86" t="s">
-        <v>769</v>
+        <v>811</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>564</v>
-      </c>
-      <c r="B67" s="86" t="s">
-        <v>776</v>
+        <v>863</v>
+      </c>
+      <c r="B67" t="s">
+        <v>810</v>
       </c>
       <c r="C67" t="s">
-        <v>775</v>
-      </c>
-      <c r="D67" s="86" t="s">
-        <v>774</v>
-      </c>
-      <c r="E67" s="86" t="s">
-        <v>713</v>
+        <v>809</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>804</v>
-      </c>
-      <c r="B68" s="86" t="s">
-        <v>779</v>
+        <v>864</v>
+      </c>
+      <c r="B68" t="s">
+        <v>813</v>
       </c>
       <c r="C68" t="s">
-        <v>778</v>
-      </c>
-      <c r="D68" s="86" t="s">
-        <v>777</v>
-      </c>
-      <c r="E68" s="86" t="s">
-        <v>766</v>
+        <v>812</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>804</v>
-      </c>
-      <c r="B69" s="86" t="s">
-        <v>779</v>
+        <v>864</v>
+      </c>
+      <c r="B69" t="s">
+        <v>815</v>
       </c>
       <c r="C69" t="s">
-        <v>780</v>
-      </c>
-      <c r="D69" s="86" t="s">
-        <v>781</v>
-      </c>
-      <c r="E69" s="86" t="s">
-        <v>766</v>
+        <v>814</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>804</v>
-      </c>
-      <c r="B70" s="86" t="s">
-        <v>785</v>
+        <v>864</v>
+      </c>
+      <c r="B70" t="s">
+        <v>816</v>
       </c>
       <c r="C70" t="s">
-        <v>783</v>
-      </c>
-      <c r="D70" s="86" t="s">
-        <v>782</v>
-      </c>
-      <c r="E70" s="86" t="s">
-        <v>784</v>
+        <v>817</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>804</v>
-      </c>
-      <c r="B71" s="86" t="s">
-        <v>785</v>
+        <v>865</v>
+      </c>
+      <c r="B71" t="s">
+        <v>818</v>
       </c>
       <c r="C71" t="s">
-        <v>786</v>
-      </c>
-      <c r="D71" s="86" t="s">
-        <v>787</v>
-      </c>
-      <c r="E71" s="86" t="s">
-        <v>784</v>
+        <v>557</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>804</v>
+        <v>866</v>
       </c>
       <c r="B72" s="86" t="s">
-        <v>791</v>
+        <v>753</v>
       </c>
       <c r="C72" t="s">
-        <v>790</v>
+        <v>751</v>
       </c>
       <c r="D72" s="86" t="s">
-        <v>788</v>
+        <v>750</v>
       </c>
       <c r="E72" s="86" t="s">
-        <v>789</v>
+        <v>752</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>804</v>
+        <v>866</v>
       </c>
       <c r="B73" s="86" t="s">
-        <v>793</v>
+        <v>753</v>
       </c>
       <c r="C73" t="s">
-        <v>792</v>
+        <v>755</v>
       </c>
       <c r="D73" s="86" t="s">
-        <v>788</v>
+        <v>754</v>
       </c>
       <c r="E73" s="86" t="s">
-        <v>789</v>
+        <v>752</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>804</v>
+        <v>867</v>
       </c>
       <c r="B74" s="86" t="s">
-        <v>793</v>
+        <v>777</v>
       </c>
       <c r="C74" t="s">
-        <v>794</v>
+        <v>775</v>
       </c>
       <c r="D74" s="86" t="s">
-        <v>788</v>
+        <v>774</v>
       </c>
       <c r="E74" s="86" t="s">
-        <v>789</v>
+        <v>776</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>804</v>
+        <v>867</v>
       </c>
       <c r="B75" s="86" t="s">
-        <v>797</v>
+        <v>777</v>
       </c>
       <c r="C75" t="s">
-        <v>795</v>
+        <v>778</v>
       </c>
       <c r="D75" s="86" t="s">
-        <v>796</v>
+        <v>779</v>
       </c>
       <c r="E75" s="86" t="s">
-        <v>789</v>
+        <v>776</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>804</v>
+        <v>867</v>
       </c>
       <c r="B76" s="86" t="s">
-        <v>800</v>
+        <v>759</v>
       </c>
       <c r="C76" t="s">
-        <v>799</v>
+        <v>757</v>
       </c>
       <c r="D76" s="86" t="s">
-        <v>798</v>
+        <v>756</v>
       </c>
       <c r="E76" s="86" t="s">
-        <v>789</v>
+        <v>758</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>804</v>
+        <v>867</v>
       </c>
       <c r="B77" s="86" t="s">
-        <v>661</v>
+        <v>762</v>
       </c>
       <c r="C77" t="s">
-        <v>801</v>
+        <v>764</v>
       </c>
       <c r="D77" s="86" t="s">
-        <v>802</v>
+        <v>760</v>
       </c>
       <c r="E77" s="86" t="s">
-        <v>789</v>
+        <v>761</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>805</v>
+        <v>867</v>
       </c>
       <c r="B78" s="86" t="s">
-        <v>654</v>
+        <v>762</v>
       </c>
       <c r="C78" t="s">
-        <v>803</v>
+        <v>765</v>
       </c>
       <c r="D78" s="86" t="s">
-        <v>812</v>
+        <v>763</v>
       </c>
       <c r="E78" s="86" t="s">
-        <v>657</v>
+        <v>761</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>806</v>
+        <v>867</v>
       </c>
       <c r="B79" s="86" t="s">
-        <v>654</v>
+        <v>762</v>
       </c>
       <c r="C79" t="s">
-        <v>813</v>
+        <v>848</v>
       </c>
       <c r="D79" s="86" t="s">
-        <v>812</v>
+        <v>849</v>
       </c>
       <c r="E79" s="86" t="s">
-        <v>657</v>
+        <v>761</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>807</v>
-      </c>
-      <c r="B80" t="s">
-        <v>814</v>
+        <v>867</v>
+      </c>
+      <c r="B80" s="86" t="s">
+        <v>771</v>
       </c>
       <c r="C80" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+        <v>770</v>
+      </c>
+      <c r="D80" s="86" t="s">
+        <v>769</v>
+      </c>
+      <c r="E80" s="86" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>808</v>
-      </c>
-      <c r="B81" t="s">
-        <v>815</v>
+        <v>867</v>
+      </c>
+      <c r="B81" s="86" t="s">
+        <v>771</v>
       </c>
       <c r="C81" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+        <v>772</v>
+      </c>
+      <c r="D81" s="86" t="s">
+        <v>773</v>
+      </c>
+      <c r="E81" s="86" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>809</v>
-      </c>
-      <c r="B82" t="s">
-        <v>816</v>
+        <v>868</v>
+      </c>
+      <c r="B82" s="86" t="s">
+        <v>768</v>
       </c>
       <c r="C82" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+        <v>767</v>
+      </c>
+      <c r="D82" s="86" t="s">
+        <v>766</v>
+      </c>
+      <c r="E82" s="86" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>809</v>
-      </c>
-      <c r="B83" t="s">
-        <v>818</v>
+        <v>868</v>
+      </c>
+      <c r="B83" s="86" t="s">
+        <v>783</v>
       </c>
       <c r="C83" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+        <v>782</v>
+      </c>
+      <c r="D83" s="86" t="s">
+        <v>780</v>
+      </c>
+      <c r="E83" s="86" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>810</v>
-      </c>
-      <c r="B84" t="s">
-        <v>821</v>
+        <v>868</v>
+      </c>
+      <c r="B84" s="86" t="s">
+        <v>785</v>
       </c>
       <c r="C84" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+        <v>784</v>
+      </c>
+      <c r="D84" s="86" t="s">
+        <v>780</v>
+      </c>
+      <c r="E84" s="86" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>810</v>
-      </c>
-      <c r="B85" t="s">
-        <v>823</v>
+        <v>868</v>
+      </c>
+      <c r="B85" s="86" t="s">
+        <v>785</v>
       </c>
       <c r="C85" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+        <v>786</v>
+      </c>
+      <c r="D85" s="86" t="s">
+        <v>780</v>
+      </c>
+      <c r="E85" s="86" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>810</v>
-      </c>
-      <c r="B86" t="s">
-        <v>824</v>
+        <v>868</v>
+      </c>
+      <c r="B86" s="86" t="s">
+        <v>789</v>
       </c>
       <c r="C86" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+        <v>787</v>
+      </c>
+      <c r="D86" s="86" t="s">
+        <v>788</v>
+      </c>
+      <c r="E86" s="86" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>811</v>
-      </c>
-      <c r="B87" t="s">
-        <v>826</v>
+        <v>868</v>
+      </c>
+      <c r="B87" s="86" t="s">
+        <v>792</v>
       </c>
       <c r="C87" t="s">
-        <v>562</v>
+        <v>791</v>
+      </c>
+      <c r="D87" s="86" t="s">
+        <v>790</v>
+      </c>
+      <c r="E87" s="86" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>868</v>
+      </c>
+      <c r="B88" s="86" t="s">
+        <v>654</v>
+      </c>
+      <c r="C88" t="s">
+        <v>793</v>
+      </c>
+      <c r="D88" s="86" t="s">
+        <v>794</v>
+      </c>
+      <c r="E88" s="86" t="s">
+        <v>781</v>
       </c>
     </row>
   </sheetData>
@@ -7882,62 +7958,65 @@
     <hyperlink ref="D61" r:id="rId172" xr:uid="{0E22EB11-B3F4-4B3D-9949-5BB47BE472FF}"/>
     <hyperlink ref="E61" r:id="rId173" xr:uid="{203E2512-19F8-444F-B5FE-FCEFA21380D9}"/>
     <hyperlink ref="B61" r:id="rId174" xr:uid="{D42B148C-2E41-45DC-9406-03F899255054}"/>
-    <hyperlink ref="D62" r:id="rId175" xr:uid="{E8A08F00-2B07-41D3-BECA-92E437337767}"/>
-    <hyperlink ref="E62" r:id="rId176" xr:uid="{CC57E1D3-F163-4C30-A8C6-CA03AA34248D}"/>
-    <hyperlink ref="B62" r:id="rId177" xr:uid="{758C4E99-7187-45B3-B96E-4E1A344950BB}"/>
-    <hyperlink ref="D63" r:id="rId178" xr:uid="{8D6FE8C4-9089-409E-AC71-07A6BA994DD8}"/>
-    <hyperlink ref="E63" r:id="rId179" xr:uid="{C0915D43-2F9A-44CA-AA9B-2D6F571A6531}"/>
-    <hyperlink ref="B63" r:id="rId180" xr:uid="{BD35CE35-8B49-4F57-A541-E8AB4942E01C}"/>
-    <hyperlink ref="D64" r:id="rId181" xr:uid="{AD3B2EB4-61E6-4EC2-B841-C66ABAF57A8D}"/>
-    <hyperlink ref="E64" r:id="rId182" xr:uid="{CA19CD5B-D261-46F6-A06C-A6DD329847C8}"/>
-    <hyperlink ref="B64" r:id="rId183" xr:uid="{902A512C-7DB9-483B-922E-9EC9EB0A5727}"/>
-    <hyperlink ref="D65" r:id="rId184" xr:uid="{D37A5DB7-6170-4DB3-A6C4-6B7C3536BB6A}"/>
-    <hyperlink ref="E65" r:id="rId185" xr:uid="{5BE49E4F-CE72-4598-A298-9EA3583C9BB4}"/>
-    <hyperlink ref="B65" r:id="rId186" xr:uid="{218FE68B-E3EA-48FD-B04F-F05EC4D04342}"/>
-    <hyperlink ref="D66" r:id="rId187" xr:uid="{55D0245C-636D-41C8-8BEA-F7465FDF2FC1}"/>
-    <hyperlink ref="E66" r:id="rId188" xr:uid="{745BE301-751B-44AD-BB23-64393F55A01A}"/>
-    <hyperlink ref="B66" r:id="rId189" xr:uid="{72E099E5-D9E8-43F6-BA7B-AD0788C8ACDF}"/>
-    <hyperlink ref="D67" r:id="rId190" xr:uid="{670FA2F5-7537-44F0-A891-BC8F9FB0FDA1}"/>
-    <hyperlink ref="E67" r:id="rId191" xr:uid="{C44FBCC9-F7D2-411F-B321-7ACCA7BDB113}"/>
-    <hyperlink ref="B67" r:id="rId192" xr:uid="{7AAC8125-2903-4BEF-861C-0652EB8A1EBA}"/>
-    <hyperlink ref="D68" r:id="rId193" xr:uid="{4247E04D-3AB7-4CE4-8D6E-225BEB05B2EC}"/>
-    <hyperlink ref="E68" r:id="rId194" xr:uid="{3F6A67C6-2350-4E0B-855A-7A0CA546CADA}"/>
-    <hyperlink ref="B68" r:id="rId195" xr:uid="{EDAF1894-D1E3-4CB7-A453-D26D0CE785FC}"/>
-    <hyperlink ref="B69" r:id="rId196" xr:uid="{60D8C8EA-A2CC-4EC4-93CF-D8C6F9145025}"/>
-    <hyperlink ref="D69" r:id="rId197" xr:uid="{F6B676D4-F9FF-4FAC-BF4F-6B297B8E4386}"/>
-    <hyperlink ref="E69" r:id="rId198" xr:uid="{AD04D2E5-748B-41B8-A77F-6FE55DE52558}"/>
-    <hyperlink ref="D70" r:id="rId199" xr:uid="{2919C844-F24C-4EBC-BBC0-393934ACE57D}"/>
-    <hyperlink ref="E70" r:id="rId200" xr:uid="{16E264FE-A51B-4307-BAC2-77D48753B271}"/>
-    <hyperlink ref="D71" r:id="rId201" xr:uid="{923213AD-4D4E-456F-B24C-29D5EE8D2DC5}"/>
-    <hyperlink ref="E71" r:id="rId202" xr:uid="{0FB2A237-55E7-482E-BFDD-773D6CA63339}"/>
-    <hyperlink ref="D72" r:id="rId203" xr:uid="{0FB5C72B-F07D-4BAE-8F9A-333776CD5938}"/>
-    <hyperlink ref="E72" r:id="rId204" xr:uid="{1E54D0E6-426F-4655-B12E-6919FDCF820A}"/>
-    <hyperlink ref="B71" r:id="rId205" xr:uid="{6F4BDAA6-1768-40E1-BA7A-3A7B8F3E9DDF}"/>
-    <hyperlink ref="B72" r:id="rId206" xr:uid="{EBBCEFF8-5BDF-4051-A5A6-449AB5359B3C}"/>
-    <hyperlink ref="E73" r:id="rId207" xr:uid="{BE30CFAC-63AD-4E25-9DE4-2BF7C9B898E5}"/>
-    <hyperlink ref="D73" r:id="rId208" xr:uid="{3A9183DE-FD11-4043-B1A6-6E9E780E188A}"/>
-    <hyperlink ref="B73" r:id="rId209" xr:uid="{39C6DCAA-BE89-4B4F-BAB3-B01A8C5FED4E}"/>
-    <hyperlink ref="B74" r:id="rId210" xr:uid="{BD8ABE7B-7146-4F9C-B38C-CE77AC97911C}"/>
-    <hyperlink ref="D74" r:id="rId211" xr:uid="{575F04ED-6CE7-4807-8B13-F326EF7B2C8E}"/>
-    <hyperlink ref="E74" r:id="rId212" xr:uid="{681838FB-70EA-419D-BCE3-E08F5364A2E0}"/>
-    <hyperlink ref="D75" r:id="rId213" xr:uid="{4BFFDDEF-9B37-49D7-8898-707DFDE3F5A2}"/>
-    <hyperlink ref="E75" r:id="rId214" xr:uid="{9B9DFAF3-C1E1-423C-B6F9-E51D877DDB12}"/>
-    <hyperlink ref="B75" r:id="rId215" xr:uid="{59F2747A-CC65-4ED5-A56B-786A043CE67B}"/>
-    <hyperlink ref="D76" r:id="rId216" xr:uid="{ECC3D6DF-5B1B-4DC1-B19F-8886FD8EB116}"/>
-    <hyperlink ref="E76" r:id="rId217" xr:uid="{12F9552E-0BC3-4624-9123-B55AFBCCB562}"/>
-    <hyperlink ref="E77" r:id="rId218" xr:uid="{75179926-30E5-4350-921B-A5B14E1B232D}"/>
-    <hyperlink ref="B76" r:id="rId219" xr:uid="{EA078301-086A-4811-A4E1-A4C2AAE42D90}"/>
-    <hyperlink ref="D77" r:id="rId220" xr:uid="{C965BAE7-26E3-47CA-A128-1A1426B08287}"/>
-    <hyperlink ref="B77" r:id="rId221" xr:uid="{08F176CD-1942-484A-B91A-5E7D7BE2E642}"/>
-    <hyperlink ref="D78" r:id="rId222" xr:uid="{61B038FC-067A-4428-85A1-623DE325F1ED}"/>
-    <hyperlink ref="E78" r:id="rId223" xr:uid="{BB3648F4-8B0F-4A80-8F41-403E4053E2DA}"/>
-    <hyperlink ref="B78" r:id="rId224" xr:uid="{B824C2FD-2669-4F5E-A3AB-CBE4E6052B0C}"/>
-    <hyperlink ref="B79" r:id="rId225" xr:uid="{4654EB0D-7573-4009-B0CF-95DC2A913755}"/>
-    <hyperlink ref="D79" r:id="rId226" xr:uid="{8D237BAA-60AB-4BA0-B2C0-B05074E53B92}"/>
-    <hyperlink ref="E79" r:id="rId227" xr:uid="{C1E57DEC-20E0-487A-A1F8-F2C132F19122}"/>
+    <hyperlink ref="D72" r:id="rId175" xr:uid="{E8A08F00-2B07-41D3-BECA-92E437337767}"/>
+    <hyperlink ref="E72" r:id="rId176" xr:uid="{CC57E1D3-F163-4C30-A8C6-CA03AA34248D}"/>
+    <hyperlink ref="B72" r:id="rId177" xr:uid="{758C4E99-7187-45B3-B96E-4E1A344950BB}"/>
+    <hyperlink ref="D73" r:id="rId178" xr:uid="{8D6FE8C4-9089-409E-AC71-07A6BA994DD8}"/>
+    <hyperlink ref="E73" r:id="rId179" xr:uid="{C0915D43-2F9A-44CA-AA9B-2D6F571A6531}"/>
+    <hyperlink ref="B73" r:id="rId180" xr:uid="{BD35CE35-8B49-4F57-A541-E8AB4942E01C}"/>
+    <hyperlink ref="D76" r:id="rId181" xr:uid="{AD3B2EB4-61E6-4EC2-B841-C66ABAF57A8D}"/>
+    <hyperlink ref="E76" r:id="rId182" xr:uid="{CA19CD5B-D261-46F6-A06C-A6DD329847C8}"/>
+    <hyperlink ref="B76" r:id="rId183" xr:uid="{902A512C-7DB9-483B-922E-9EC9EB0A5727}"/>
+    <hyperlink ref="D77" r:id="rId184" xr:uid="{D37A5DB7-6170-4DB3-A6C4-6B7C3536BB6A}"/>
+    <hyperlink ref="E77" r:id="rId185" xr:uid="{5BE49E4F-CE72-4598-A298-9EA3583C9BB4}"/>
+    <hyperlink ref="B77" r:id="rId186" xr:uid="{218FE68B-E3EA-48FD-B04F-F05EC4D04342}"/>
+    <hyperlink ref="D78" r:id="rId187" xr:uid="{55D0245C-636D-41C8-8BEA-F7465FDF2FC1}"/>
+    <hyperlink ref="E78" r:id="rId188" xr:uid="{745BE301-751B-44AD-BB23-64393F55A01A}"/>
+    <hyperlink ref="B78" r:id="rId189" xr:uid="{72E099E5-D9E8-43F6-BA7B-AD0788C8ACDF}"/>
+    <hyperlink ref="D82" r:id="rId190" xr:uid="{670FA2F5-7537-44F0-A891-BC8F9FB0FDA1}"/>
+    <hyperlink ref="E82" r:id="rId191" xr:uid="{C44FBCC9-F7D2-411F-B321-7ACCA7BDB113}"/>
+    <hyperlink ref="B82" r:id="rId192" xr:uid="{7AAC8125-2903-4BEF-861C-0652EB8A1EBA}"/>
+    <hyperlink ref="D80" r:id="rId193" xr:uid="{4247E04D-3AB7-4CE4-8D6E-225BEB05B2EC}"/>
+    <hyperlink ref="E80" r:id="rId194" xr:uid="{3F6A67C6-2350-4E0B-855A-7A0CA546CADA}"/>
+    <hyperlink ref="B80" r:id="rId195" xr:uid="{EDAF1894-D1E3-4CB7-A453-D26D0CE785FC}"/>
+    <hyperlink ref="B81" r:id="rId196" xr:uid="{60D8C8EA-A2CC-4EC4-93CF-D8C6F9145025}"/>
+    <hyperlink ref="D81" r:id="rId197" xr:uid="{F6B676D4-F9FF-4FAC-BF4F-6B297B8E4386}"/>
+    <hyperlink ref="E81" r:id="rId198" xr:uid="{AD04D2E5-748B-41B8-A77F-6FE55DE52558}"/>
+    <hyperlink ref="D74" r:id="rId199" xr:uid="{2919C844-F24C-4EBC-BBC0-393934ACE57D}"/>
+    <hyperlink ref="E74" r:id="rId200" xr:uid="{16E264FE-A51B-4307-BAC2-77D48753B271}"/>
+    <hyperlink ref="D75" r:id="rId201" xr:uid="{923213AD-4D4E-456F-B24C-29D5EE8D2DC5}"/>
+    <hyperlink ref="E75" r:id="rId202" xr:uid="{0FB2A237-55E7-482E-BFDD-773D6CA63339}"/>
+    <hyperlink ref="D83" r:id="rId203" xr:uid="{0FB5C72B-F07D-4BAE-8F9A-333776CD5938}"/>
+    <hyperlink ref="E83" r:id="rId204" xr:uid="{1E54D0E6-426F-4655-B12E-6919FDCF820A}"/>
+    <hyperlink ref="B75" r:id="rId205" xr:uid="{6F4BDAA6-1768-40E1-BA7A-3A7B8F3E9DDF}"/>
+    <hyperlink ref="B83" r:id="rId206" xr:uid="{EBBCEFF8-5BDF-4051-A5A6-449AB5359B3C}"/>
+    <hyperlink ref="E84" r:id="rId207" xr:uid="{BE30CFAC-63AD-4E25-9DE4-2BF7C9B898E5}"/>
+    <hyperlink ref="D84" r:id="rId208" xr:uid="{3A9183DE-FD11-4043-B1A6-6E9E780E188A}"/>
+    <hyperlink ref="B84" r:id="rId209" xr:uid="{39C6DCAA-BE89-4B4F-BAB3-B01A8C5FED4E}"/>
+    <hyperlink ref="B85" r:id="rId210" xr:uid="{BD8ABE7B-7146-4F9C-B38C-CE77AC97911C}"/>
+    <hyperlink ref="D85" r:id="rId211" xr:uid="{575F04ED-6CE7-4807-8B13-F326EF7B2C8E}"/>
+    <hyperlink ref="E85" r:id="rId212" xr:uid="{681838FB-70EA-419D-BCE3-E08F5364A2E0}"/>
+    <hyperlink ref="D86" r:id="rId213" xr:uid="{4BFFDDEF-9B37-49D7-8898-707DFDE3F5A2}"/>
+    <hyperlink ref="E86" r:id="rId214" xr:uid="{9B9DFAF3-C1E1-423C-B6F9-E51D877DDB12}"/>
+    <hyperlink ref="B86" r:id="rId215" xr:uid="{59F2747A-CC65-4ED5-A56B-786A043CE67B}"/>
+    <hyperlink ref="D87" r:id="rId216" xr:uid="{ECC3D6DF-5B1B-4DC1-B19F-8886FD8EB116}"/>
+    <hyperlink ref="E87" r:id="rId217" xr:uid="{12F9552E-0BC3-4624-9123-B55AFBCCB562}"/>
+    <hyperlink ref="E88" r:id="rId218" xr:uid="{75179926-30E5-4350-921B-A5B14E1B232D}"/>
+    <hyperlink ref="B87" r:id="rId219" xr:uid="{EA078301-086A-4811-A4E1-A4C2AAE42D90}"/>
+    <hyperlink ref="D88" r:id="rId220" xr:uid="{C965BAE7-26E3-47CA-A128-1A1426B08287}"/>
+    <hyperlink ref="B88" r:id="rId221" xr:uid="{08F176CD-1942-484A-B91A-5E7D7BE2E642}"/>
+    <hyperlink ref="D62" r:id="rId222" xr:uid="{61B038FC-067A-4428-85A1-623DE325F1ED}"/>
+    <hyperlink ref="E62" r:id="rId223" xr:uid="{BB3648F4-8B0F-4A80-8F41-403E4053E2DA}"/>
+    <hyperlink ref="B62" r:id="rId224" xr:uid="{B824C2FD-2669-4F5E-A3AB-CBE4E6052B0C}"/>
+    <hyperlink ref="B63" r:id="rId225" xr:uid="{4654EB0D-7573-4009-B0CF-95DC2A913755}"/>
+    <hyperlink ref="D63" r:id="rId226" xr:uid="{8D237BAA-60AB-4BA0-B2C0-B05074E53B92}"/>
+    <hyperlink ref="E63" r:id="rId227" xr:uid="{C1E57DEC-20E0-487A-A1F8-F2C132F19122}"/>
+    <hyperlink ref="B79" r:id="rId228" xr:uid="{7578032B-1F3A-4539-8690-8C437B785A34}"/>
+    <hyperlink ref="E79" r:id="rId229" xr:uid="{F09459B5-03BF-4EB8-A810-ADCB843144F0}"/>
+    <hyperlink ref="D79" r:id="rId230" xr:uid="{CE2026CE-7571-4E0A-A6D8-C5CC51EE426C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId228"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId231"/>
 </worksheet>
 </file>
 
@@ -7957,86 +8036,86 @@
   <sheetData>
     <row r="1" spans="1:25" ht="36.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="76" t="s">
+        <v>391</v>
+      </c>
+      <c r="B1" s="76" t="s">
         <v>392</v>
       </c>
-      <c r="B1" s="76" t="s">
+      <c r="C1" s="74" t="s">
         <v>393</v>
       </c>
-      <c r="C1" s="74" t="s">
+      <c r="D1" s="72" t="s">
         <v>394</v>
       </c>
-      <c r="D1" s="72" t="s">
-        <v>395</v>
-      </c>
       <c r="W1" s="107" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="X1" s="107"/>
       <c r="Y1" s="107"/>
     </row>
     <row r="2" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="77" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B2" s="75" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C2" s="73" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="W2" s="82" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3" s="77" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B3" s="75" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C3" s="73" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="X3" s="79" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="Y3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4" s="77" t="s">
+        <v>396</v>
+      </c>
+      <c r="B4" t="s">
         <v>397</v>
       </c>
-      <c r="B4" t="s">
-        <v>398</v>
-      </c>
       <c r="C4" s="73" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D4" t="s">
         <v>9</v>
       </c>
       <c r="X4" s="79" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="Y4" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5" s="85" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="B5" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="C5" s="73" t="s">
         <v>142</v>
@@ -8045,419 +8124,419 @@
         <v>10</v>
       </c>
       <c r="X5" s="79" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="Y5" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.35">
       <c r="C6" s="73" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="X6" s="79" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="Y6" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.35">
       <c r="C7" s="73" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
       </c>
       <c r="X7" s="79" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="Y7" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.35">
       <c r="C8" s="73" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D8" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="X8" s="79" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="Y8" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.35">
       <c r="C9" s="73" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D9" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="X9" s="79" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="Y9" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="10" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C10" s="84" t="s">
+        <v>540</v>
+      </c>
+      <c r="D10" t="s">
         <v>541</v>
       </c>
-      <c r="D10" t="s">
-        <v>542</v>
-      </c>
       <c r="W10" s="81" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.35">
       <c r="C11" s="73" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D11" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="X11" s="79" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Y11" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.35">
       <c r="C12" s="73" t="s">
+        <v>547</v>
+      </c>
+      <c r="D12" t="s">
         <v>548</v>
       </c>
-      <c r="D12" t="s">
-        <v>549</v>
-      </c>
       <c r="X12" s="79" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Y12" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.35">
       <c r="C13" s="84" t="s">
+        <v>549</v>
+      </c>
+      <c r="D13" t="s">
         <v>550</v>
       </c>
-      <c r="D13" t="s">
-        <v>551</v>
-      </c>
       <c r="X13" s="79" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="Y13" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.35">
       <c r="C14" s="85" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="D14" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="X14" s="79" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="Y14" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.35">
       <c r="X15" s="79" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Y15" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.35">
       <c r="X16" s="79" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="Y16" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="17" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X17" s="79" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="Y17" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="18" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X18" s="79" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="Y18" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="19" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X19" s="79" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="Y19" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="20" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X20" s="79" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="Y20" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="21" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X21" s="79" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="Y21" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="22" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X22" s="79" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="Y22" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="23" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X23" s="79" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="Y23" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="24" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X24" s="79" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="Y24" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="25" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X25" s="79" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="Y25" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="26" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X26" s="79" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="Y26" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="27" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X27" s="79" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="Y27" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="28" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X28" s="79" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="Y28" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="29" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X29" s="79" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="Y29" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="30" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X30" s="79" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="Y30" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="31" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X31" s="79" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="Y31" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="32" spans="24:25" x14ac:dyDescent="0.35">
       <c r="X32" s="79" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="Y32" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="33" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X33" s="79" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="Y33" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="34" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X34" s="79" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Y34" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="35" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X35" s="79" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="Y35" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="36" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X36" s="79" t="s">
+        <v>514</v>
+      </c>
+      <c r="Y36" t="s">
         <v>515</v>
-      </c>
-      <c r="Y36" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="38" spans="23:26" ht="15.5" x14ac:dyDescent="0.35">
       <c r="W38" s="81" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="39" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X39" s="79" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="Y39" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="40" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X40" s="79" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="Y40" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="Z40" s="79"/>
     </row>
     <row r="41" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X41" s="79" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Y41" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="Z41" s="79"/>
     </row>
     <row r="42" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X42" s="79" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="Y42" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="Z42" s="79"/>
     </row>
     <row r="43" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X43" s="79" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="Y43" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="Z43" s="79"/>
     </row>
     <row r="44" spans="23:26" ht="15.5" x14ac:dyDescent="0.35">
       <c r="W44" s="81" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="X44" s="80"/>
       <c r="Z44" s="79"/>
     </row>
     <row r="45" spans="23:26" ht="15.5" x14ac:dyDescent="0.35">
       <c r="X45" s="79" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="Y45" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="Z45" s="80"/>
     </row>
     <row r="46" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X46" s="79" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Y46" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="Z46" s="79"/>
     </row>
     <row r="47" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X47" s="79" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="Y47" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="Z47" s="79"/>
     </row>
     <row r="48" spans="23:26" x14ac:dyDescent="0.35">
       <c r="X48" s="79" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Y48" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="Z48" s="79"/>
     </row>
     <row r="49" spans="15:25" x14ac:dyDescent="0.35">
       <c r="O49" s="79"/>
       <c r="X49" s="79" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Y49" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="50" spans="15:25" x14ac:dyDescent="0.35">
       <c r="O50" s="79"/>
       <c r="X50" s="79" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="Y50" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
   </sheetData>
@@ -9511,6 +9590,682 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF1BA8E2-9FD2-4C47-B5D3-EF9907B8F692}">
+  <dimension ref="A1:D52"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.54296875" style="41" customWidth="1"/>
+    <col min="2" max="2" width="38.26953125" customWidth="1"/>
+    <col min="3" max="3" width="14.6328125" customWidth="1"/>
+    <col min="4" max="4" width="13.36328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="32" t="s">
+        <v>299</v>
+      </c>
+      <c r="B1" s="68" t="s">
+        <v>360</v>
+      </c>
+      <c r="C1" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="D1" s="33" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="35">
+        <v>1</v>
+      </c>
+      <c r="B2" s="36" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2" s="42">
+        <v>1194</v>
+      </c>
+      <c r="D2" s="43"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="38">
+        <v>2</v>
+      </c>
+      <c r="B3" s="39" t="s">
+        <v>117</v>
+      </c>
+      <c r="C3" s="43">
+        <v>1938</v>
+      </c>
+      <c r="D3" s="44">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="35">
+        <v>3</v>
+      </c>
+      <c r="B4" s="36" t="s">
+        <v>119</v>
+      </c>
+      <c r="C4" s="42">
+        <v>1591</v>
+      </c>
+      <c r="D4" s="43"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="38">
+        <v>4</v>
+      </c>
+      <c r="B5" s="36" t="s">
+        <v>123</v>
+      </c>
+      <c r="C5" s="42">
+        <v>864</v>
+      </c>
+      <c r="D5" s="43"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="35">
+        <v>5</v>
+      </c>
+      <c r="B6" s="36" t="s">
+        <v>127</v>
+      </c>
+      <c r="C6" s="42">
+        <v>1832</v>
+      </c>
+      <c r="D6" s="43">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="38">
+        <v>6</v>
+      </c>
+      <c r="B7" s="36" t="s">
+        <v>131</v>
+      </c>
+      <c r="C7" s="42">
+        <v>1010</v>
+      </c>
+      <c r="D7" s="43"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="35">
+        <v>7</v>
+      </c>
+      <c r="B8" s="36" t="s">
+        <v>135</v>
+      </c>
+      <c r="C8" s="42">
+        <v>1994</v>
+      </c>
+      <c r="D8" s="43"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="38">
+        <v>8</v>
+      </c>
+      <c r="B9" s="36" t="s">
+        <v>139</v>
+      </c>
+      <c r="C9" s="43">
+        <v>1972</v>
+      </c>
+      <c r="D9" s="43"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="35">
+        <v>9</v>
+      </c>
+      <c r="B10" s="36" t="s">
+        <v>143</v>
+      </c>
+      <c r="C10" s="43">
+        <v>1988</v>
+      </c>
+      <c r="D10" s="43">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="38">
+        <v>10</v>
+      </c>
+      <c r="B11" s="36" t="s">
+        <v>147</v>
+      </c>
+      <c r="C11" s="43">
+        <v>1280</v>
+      </c>
+      <c r="D11" s="43"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="35">
+        <v>11</v>
+      </c>
+      <c r="B12" s="39" t="s">
+        <v>151</v>
+      </c>
+      <c r="C12" s="43">
+        <v>1872</v>
+      </c>
+      <c r="D12" s="44">
+        <v>1878</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="38">
+        <v>12</v>
+      </c>
+      <c r="B13" s="39" t="s">
+        <v>154</v>
+      </c>
+      <c r="C13" s="43">
+        <v>1872</v>
+      </c>
+      <c r="D13" s="44">
+        <v>1879</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="35">
+        <v>13</v>
+      </c>
+      <c r="B14" s="39" t="s">
+        <v>158</v>
+      </c>
+      <c r="C14" s="43">
+        <v>1871</v>
+      </c>
+      <c r="D14" s="44"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="38">
+        <v>14</v>
+      </c>
+      <c r="B15" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="C15" s="43">
+        <v>1872</v>
+      </c>
+      <c r="D15" s="44">
+        <v>1887</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="35">
+        <v>15</v>
+      </c>
+      <c r="B16" s="39" t="s">
+        <v>166</v>
+      </c>
+      <c r="C16" s="43">
+        <v>1888</v>
+      </c>
+      <c r="D16" s="44">
+        <v>1953</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="38">
+        <v>16</v>
+      </c>
+      <c r="B17" s="39" t="s">
+        <v>169</v>
+      </c>
+      <c r="C17" s="43">
+        <v>1374</v>
+      </c>
+      <c r="D17" s="44"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="35">
+        <v>17</v>
+      </c>
+      <c r="B18" s="39" t="s">
+        <v>173</v>
+      </c>
+      <c r="C18" s="43">
+        <v>1827</v>
+      </c>
+      <c r="D18" s="44"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="38">
+        <v>18</v>
+      </c>
+      <c r="B19" s="39" t="s">
+        <v>177</v>
+      </c>
+      <c r="C19" s="43">
+        <v>1872</v>
+      </c>
+      <c r="D19" s="44">
+        <v>1882</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="35">
+        <v>19</v>
+      </c>
+      <c r="B20" s="36" t="s">
+        <v>181</v>
+      </c>
+      <c r="C20" s="43">
+        <v>801</v>
+      </c>
+      <c r="D20" s="43"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="38">
+        <v>20</v>
+      </c>
+      <c r="B21" s="39" t="s">
+        <v>185</v>
+      </c>
+      <c r="C21" s="43">
+        <v>1990</v>
+      </c>
+      <c r="D21" s="43"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="35">
+        <v>21</v>
+      </c>
+      <c r="B22" s="36" t="s">
+        <v>189</v>
+      </c>
+      <c r="C22" s="43">
+        <v>1328</v>
+      </c>
+      <c r="D22" s="43"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="38">
+        <v>22</v>
+      </c>
+      <c r="B23" s="36" t="s">
+        <v>193</v>
+      </c>
+      <c r="C23" s="43">
+        <v>1976</v>
+      </c>
+      <c r="D23" s="43"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="35">
+        <v>23</v>
+      </c>
+      <c r="B24" s="36" t="s">
+        <v>197</v>
+      </c>
+      <c r="C24" s="43">
+        <v>1928</v>
+      </c>
+      <c r="D24" s="43"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="38">
+        <v>24</v>
+      </c>
+      <c r="B25" s="36" t="s">
+        <v>201</v>
+      </c>
+      <c r="C25" s="43">
+        <v>1972</v>
+      </c>
+      <c r="D25" s="43"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" s="35">
+        <v>25</v>
+      </c>
+      <c r="B26" s="39" t="s">
+        <v>205</v>
+      </c>
+      <c r="C26" s="43">
+        <v>1942</v>
+      </c>
+      <c r="D26" s="44"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" s="38">
+        <v>26</v>
+      </c>
+      <c r="B27" s="36" t="s">
+        <v>210</v>
+      </c>
+      <c r="C27" s="43">
+        <v>1724</v>
+      </c>
+      <c r="D27" s="43"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" s="35">
+        <v>27</v>
+      </c>
+      <c r="B28" s="39" t="s">
+        <v>214</v>
+      </c>
+      <c r="C28" s="43">
+        <v>1992</v>
+      </c>
+      <c r="D28" s="44">
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" s="38">
+        <v>28</v>
+      </c>
+      <c r="B29" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="C29" s="43">
+        <v>1998</v>
+      </c>
+      <c r="D29" s="43"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" s="35">
+        <v>29</v>
+      </c>
+      <c r="B30" s="36" t="s">
+        <v>223</v>
+      </c>
+      <c r="C30" s="43">
+        <v>1968</v>
+      </c>
+      <c r="D30" s="43"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" s="38">
+        <v>30</v>
+      </c>
+      <c r="B31" s="39" t="s">
+        <v>227</v>
+      </c>
+      <c r="C31" s="43">
+        <v>1792</v>
+      </c>
+      <c r="D31" s="44"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" s="35">
+        <v>31</v>
+      </c>
+      <c r="B32" s="36" t="s">
+        <v>231</v>
+      </c>
+      <c r="C32" s="43">
+        <v>1906</v>
+      </c>
+      <c r="D32" s="44"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" s="38">
+        <v>32</v>
+      </c>
+      <c r="B33" s="36" t="s">
+        <v>233</v>
+      </c>
+      <c r="C33" s="43">
+        <v>1854</v>
+      </c>
+      <c r="D33" s="43"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" s="38">
+        <v>33</v>
+      </c>
+      <c r="B34" s="39" t="s">
+        <v>236</v>
+      </c>
+      <c r="C34" s="43">
+        <v>1835</v>
+      </c>
+      <c r="D34" s="44">
+        <v>1942</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" s="35">
+        <v>34</v>
+      </c>
+      <c r="B35" s="39" t="s">
+        <v>239</v>
+      </c>
+      <c r="C35" s="43">
+        <v>1973</v>
+      </c>
+      <c r="D35" s="44"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" s="35">
+        <v>35</v>
+      </c>
+      <c r="B36" s="36" t="s">
+        <v>242</v>
+      </c>
+      <c r="C36" s="43">
+        <v>1908</v>
+      </c>
+      <c r="D36" s="43"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" s="35">
+        <v>36</v>
+      </c>
+      <c r="B37" s="36" t="s">
+        <v>245</v>
+      </c>
+      <c r="C37" s="43">
+        <v>1976</v>
+      </c>
+      <c r="D37" s="43"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" s="35">
+        <v>37</v>
+      </c>
+      <c r="B38" s="39" t="s">
+        <v>247</v>
+      </c>
+      <c r="C38" s="43">
+        <v>1803</v>
+      </c>
+      <c r="D38" s="44"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" s="35">
+        <v>38</v>
+      </c>
+      <c r="B39" s="39" t="s">
+        <v>252</v>
+      </c>
+      <c r="C39" s="43">
+        <v>1829</v>
+      </c>
+      <c r="D39" s="44"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" s="35">
+        <v>39</v>
+      </c>
+      <c r="B40" s="36" t="s">
+        <v>256</v>
+      </c>
+      <c r="C40" s="43">
+        <v>1757</v>
+      </c>
+      <c r="D40" s="43"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" s="35">
+        <v>40</v>
+      </c>
+      <c r="B41" s="36" t="s">
+        <v>260</v>
+      </c>
+      <c r="C41" s="43">
+        <v>1640</v>
+      </c>
+      <c r="D41" s="43">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" s="35">
+        <v>41</v>
+      </c>
+      <c r="B42" s="36" t="s">
+        <v>263</v>
+      </c>
+      <c r="C42" s="43">
+        <v>1992</v>
+      </c>
+      <c r="D42" s="43"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" s="35">
+        <v>42</v>
+      </c>
+      <c r="B43" s="36" t="s">
+        <v>268</v>
+      </c>
+      <c r="C43" s="43">
+        <v>1850</v>
+      </c>
+      <c r="D43" s="43">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" s="38">
+        <v>43</v>
+      </c>
+      <c r="B44" s="39" t="s">
+        <v>272</v>
+      </c>
+      <c r="C44" s="43">
+        <v>1860</v>
+      </c>
+      <c r="D44" s="43">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" s="38">
+        <v>44</v>
+      </c>
+      <c r="B45" s="39" t="s">
+        <v>275</v>
+      </c>
+      <c r="C45" s="43">
+        <v>1890</v>
+      </c>
+      <c r="D45" s="44">
+        <v>1902</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" s="38">
+        <v>44</v>
+      </c>
+      <c r="B46" s="39" t="s">
+        <v>275</v>
+      </c>
+      <c r="C46" s="43">
+        <v>1923</v>
+      </c>
+      <c r="D46" s="43"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" s="35">
+        <v>45</v>
+      </c>
+      <c r="B47" s="36" t="s">
+        <v>280</v>
+      </c>
+      <c r="C47" s="43">
+        <v>1943</v>
+      </c>
+      <c r="D47" s="43"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48" s="35">
+        <v>46</v>
+      </c>
+      <c r="B48" s="36" t="s">
+        <v>302</v>
+      </c>
+      <c r="C48" s="43">
+        <v>1988</v>
+      </c>
+      <c r="D48" s="43"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" s="35">
+        <v>47</v>
+      </c>
+      <c r="B49" s="36" t="s">
+        <v>289</v>
+      </c>
+      <c r="C49" s="43">
+        <v>1951</v>
+      </c>
+      <c r="D49" s="43"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" s="38">
+        <v>48</v>
+      </c>
+      <c r="B50" s="36" t="s">
+        <v>294</v>
+      </c>
+      <c r="C50" s="43">
+        <v>1535</v>
+      </c>
+      <c r="D50" s="43"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" s="35">
+        <v>49</v>
+      </c>
+      <c r="B51" s="68" t="s">
+        <v>360</v>
+      </c>
+      <c r="C51" s="69">
+        <v>1725</v>
+      </c>
+      <c r="D51" s="69">
+        <v>1876</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" s="38">
+        <v>50</v>
+      </c>
+      <c r="B52" s="68" t="s">
+        <v>368</v>
+      </c>
+      <c r="C52" s="69">
+        <v>1952</v>
+      </c>
+      <c r="D52" s="69"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8049D8E-7482-48AF-95C9-7F1B728B0DDE}">
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -9708,682 +10463,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF1BA8E2-9FD2-4C47-B5D3-EF9907B8F692}">
-  <dimension ref="A1:D52"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="10.54296875" style="41" customWidth="1"/>
-    <col min="2" max="2" width="38.26953125" customWidth="1"/>
-    <col min="3" max="3" width="14.6328125" customWidth="1"/>
-    <col min="4" max="4" width="13.36328125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="32" t="s">
-        <v>299</v>
-      </c>
-      <c r="B1" s="68" t="s">
-        <v>360</v>
-      </c>
-      <c r="C1" s="34" t="s">
-        <v>300</v>
-      </c>
-      <c r="D1" s="33" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="35">
-        <v>1</v>
-      </c>
-      <c r="B2" s="36" t="s">
-        <v>113</v>
-      </c>
-      <c r="C2" s="42">
-        <v>1194</v>
-      </c>
-      <c r="D2" s="43"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="38">
-        <v>2</v>
-      </c>
-      <c r="B3" s="39" t="s">
-        <v>117</v>
-      </c>
-      <c r="C3" s="43">
-        <v>1938</v>
-      </c>
-      <c r="D3" s="44">
-        <v>1944</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="35">
-        <v>3</v>
-      </c>
-      <c r="B4" s="36" t="s">
-        <v>119</v>
-      </c>
-      <c r="C4" s="42">
-        <v>1591</v>
-      </c>
-      <c r="D4" s="43"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="38">
-        <v>4</v>
-      </c>
-      <c r="B5" s="36" t="s">
-        <v>123</v>
-      </c>
-      <c r="C5" s="42">
-        <v>1973</v>
-      </c>
-      <c r="D5" s="43"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="35">
-        <v>5</v>
-      </c>
-      <c r="B6" s="36" t="s">
-        <v>127</v>
-      </c>
-      <c r="C6" s="42">
-        <v>989</v>
-      </c>
-      <c r="D6" s="43">
-        <v>2017</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="38">
-        <v>6</v>
-      </c>
-      <c r="B7" s="36" t="s">
-        <v>131</v>
-      </c>
-      <c r="C7" s="42">
-        <v>1010</v>
-      </c>
-      <c r="D7" s="43"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="35">
-        <v>7</v>
-      </c>
-      <c r="B8" s="36" t="s">
-        <v>135</v>
-      </c>
-      <c r="C8" s="42">
-        <v>1994</v>
-      </c>
-      <c r="D8" s="43"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="38">
-        <v>8</v>
-      </c>
-      <c r="B9" s="36" t="s">
-        <v>139</v>
-      </c>
-      <c r="C9" s="43">
-        <v>1972</v>
-      </c>
-      <c r="D9" s="43"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="35">
-        <v>9</v>
-      </c>
-      <c r="B10" s="36" t="s">
-        <v>143</v>
-      </c>
-      <c r="C10" s="43">
-        <v>1988</v>
-      </c>
-      <c r="D10" s="43">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="38">
-        <v>10</v>
-      </c>
-      <c r="B11" s="36" t="s">
-        <v>147</v>
-      </c>
-      <c r="C11" s="43">
-        <v>1280</v>
-      </c>
-      <c r="D11" s="43"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="35">
-        <v>11</v>
-      </c>
-      <c r="B12" s="39" t="s">
-        <v>151</v>
-      </c>
-      <c r="C12" s="43">
-        <v>1872</v>
-      </c>
-      <c r="D12" s="44">
-        <v>1878</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="38">
-        <v>12</v>
-      </c>
-      <c r="B13" s="39" t="s">
-        <v>154</v>
-      </c>
-      <c r="C13" s="43">
-        <v>1872</v>
-      </c>
-      <c r="D13" s="44">
-        <v>1879</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="35">
-        <v>13</v>
-      </c>
-      <c r="B14" s="39" t="s">
-        <v>158</v>
-      </c>
-      <c r="C14" s="43">
-        <v>1871</v>
-      </c>
-      <c r="D14" s="44"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="38">
-        <v>14</v>
-      </c>
-      <c r="B15" s="39" t="s">
-        <v>162</v>
-      </c>
-      <c r="C15" s="43">
-        <v>1872</v>
-      </c>
-      <c r="D15" s="44">
-        <v>1887</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="35">
-        <v>15</v>
-      </c>
-      <c r="B16" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="C16" s="43">
-        <v>1888</v>
-      </c>
-      <c r="D16" s="44">
-        <v>1953</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="38">
-        <v>16</v>
-      </c>
-      <c r="B17" s="39" t="s">
-        <v>169</v>
-      </c>
-      <c r="C17" s="43">
-        <v>1374</v>
-      </c>
-      <c r="D17" s="44"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="35">
-        <v>17</v>
-      </c>
-      <c r="B18" s="39" t="s">
-        <v>173</v>
-      </c>
-      <c r="C18" s="43">
-        <v>1827</v>
-      </c>
-      <c r="D18" s="44"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="38">
-        <v>18</v>
-      </c>
-      <c r="B19" s="39" t="s">
-        <v>177</v>
-      </c>
-      <c r="C19" s="43">
-        <v>1872</v>
-      </c>
-      <c r="D19" s="44">
-        <v>1882</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="35">
-        <v>19</v>
-      </c>
-      <c r="B20" s="36" t="s">
-        <v>181</v>
-      </c>
-      <c r="C20" s="43">
-        <v>801</v>
-      </c>
-      <c r="D20" s="43"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="38">
-        <v>20</v>
-      </c>
-      <c r="B21" s="39" t="s">
-        <v>185</v>
-      </c>
-      <c r="C21" s="43">
-        <v>1990</v>
-      </c>
-      <c r="D21" s="43"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="35">
-        <v>21</v>
-      </c>
-      <c r="B22" s="36" t="s">
-        <v>189</v>
-      </c>
-      <c r="C22" s="43">
-        <v>1328</v>
-      </c>
-      <c r="D22" s="43"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="38">
-        <v>22</v>
-      </c>
-      <c r="B23" s="36" t="s">
-        <v>193</v>
-      </c>
-      <c r="C23" s="43">
-        <v>1976</v>
-      </c>
-      <c r="D23" s="43"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="35">
-        <v>23</v>
-      </c>
-      <c r="B24" s="36" t="s">
-        <v>197</v>
-      </c>
-      <c r="C24" s="43">
-        <v>1928</v>
-      </c>
-      <c r="D24" s="43"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="38">
-        <v>24</v>
-      </c>
-      <c r="B25" s="36" t="s">
-        <v>201</v>
-      </c>
-      <c r="C25" s="43">
-        <v>1972</v>
-      </c>
-      <c r="D25" s="43"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="35">
-        <v>25</v>
-      </c>
-      <c r="B26" s="39" t="s">
-        <v>205</v>
-      </c>
-      <c r="C26" s="43">
-        <v>1942</v>
-      </c>
-      <c r="D26" s="44"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="38">
-        <v>26</v>
-      </c>
-      <c r="B27" s="36" t="s">
-        <v>210</v>
-      </c>
-      <c r="C27" s="43">
-        <v>1724</v>
-      </c>
-      <c r="D27" s="43"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" s="35">
-        <v>27</v>
-      </c>
-      <c r="B28" s="39" t="s">
-        <v>214</v>
-      </c>
-      <c r="C28" s="43">
-        <v>1992</v>
-      </c>
-      <c r="D28" s="44">
-        <v>1996</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="38">
-        <v>28</v>
-      </c>
-      <c r="B29" s="36" t="s">
-        <v>219</v>
-      </c>
-      <c r="C29" s="43">
-        <v>1998</v>
-      </c>
-      <c r="D29" s="43"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="35">
-        <v>29</v>
-      </c>
-      <c r="B30" s="36" t="s">
-        <v>223</v>
-      </c>
-      <c r="C30" s="43">
-        <v>1968</v>
-      </c>
-      <c r="D30" s="43"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" s="38">
-        <v>30</v>
-      </c>
-      <c r="B31" s="39" t="s">
-        <v>227</v>
-      </c>
-      <c r="C31" s="43">
-        <v>1792</v>
-      </c>
-      <c r="D31" s="44"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" s="35">
-        <v>31</v>
-      </c>
-      <c r="B32" s="36" t="s">
-        <v>231</v>
-      </c>
-      <c r="C32" s="43">
-        <v>1906</v>
-      </c>
-      <c r="D32" s="44"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="38">
-        <v>32</v>
-      </c>
-      <c r="B33" s="36" t="s">
-        <v>233</v>
-      </c>
-      <c r="C33" s="43">
-        <v>1854</v>
-      </c>
-      <c r="D33" s="43"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" s="38">
-        <v>33</v>
-      </c>
-      <c r="B34" s="39" t="s">
-        <v>236</v>
-      </c>
-      <c r="C34" s="43">
-        <v>1835</v>
-      </c>
-      <c r="D34" s="44">
-        <v>1942</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" s="35">
-        <v>34</v>
-      </c>
-      <c r="B35" s="39" t="s">
-        <v>239</v>
-      </c>
-      <c r="C35" s="43">
-        <v>1973</v>
-      </c>
-      <c r="D35" s="44"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" s="35">
-        <v>35</v>
-      </c>
-      <c r="B36" s="36" t="s">
-        <v>242</v>
-      </c>
-      <c r="C36" s="43">
-        <v>1908</v>
-      </c>
-      <c r="D36" s="43"/>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" s="35">
-        <v>36</v>
-      </c>
-      <c r="B37" s="36" t="s">
-        <v>245</v>
-      </c>
-      <c r="C37" s="43">
-        <v>1976</v>
-      </c>
-      <c r="D37" s="43"/>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" s="35">
-        <v>37</v>
-      </c>
-      <c r="B38" s="39" t="s">
-        <v>247</v>
-      </c>
-      <c r="C38" s="43">
-        <v>1803</v>
-      </c>
-      <c r="D38" s="44"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" s="35">
-        <v>38</v>
-      </c>
-      <c r="B39" s="39" t="s">
-        <v>252</v>
-      </c>
-      <c r="C39" s="43">
-        <v>1829</v>
-      </c>
-      <c r="D39" s="44"/>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" s="35">
-        <v>39</v>
-      </c>
-      <c r="B40" s="36" t="s">
-        <v>256</v>
-      </c>
-      <c r="C40" s="43">
-        <v>1757</v>
-      </c>
-      <c r="D40" s="43"/>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="35">
-        <v>40</v>
-      </c>
-      <c r="B41" s="36" t="s">
-        <v>260</v>
-      </c>
-      <c r="C41" s="43">
-        <v>1640</v>
-      </c>
-      <c r="D41" s="43">
-        <v>1869</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" s="35">
-        <v>41</v>
-      </c>
-      <c r="B42" s="36" t="s">
-        <v>263</v>
-      </c>
-      <c r="C42" s="43">
-        <v>1992</v>
-      </c>
-      <c r="D42" s="43"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" s="35">
-        <v>42</v>
-      </c>
-      <c r="B43" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="C43" s="43">
-        <v>1850</v>
-      </c>
-      <c r="D43" s="43">
-        <v>2003</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" s="38">
-        <v>43</v>
-      </c>
-      <c r="B44" s="39" t="s">
-        <v>272</v>
-      </c>
-      <c r="C44" s="43">
-        <v>1860</v>
-      </c>
-      <c r="D44" s="43">
-        <v>1895</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" s="38">
-        <v>44</v>
-      </c>
-      <c r="B45" s="39" t="s">
-        <v>275</v>
-      </c>
-      <c r="C45" s="43">
-        <v>1890</v>
-      </c>
-      <c r="D45" s="44">
-        <v>1902</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" s="38">
-        <v>44</v>
-      </c>
-      <c r="B46" s="39" t="s">
-        <v>275</v>
-      </c>
-      <c r="C46" s="43">
-        <v>1923</v>
-      </c>
-      <c r="D46" s="43"/>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" s="35">
-        <v>45</v>
-      </c>
-      <c r="B47" s="36" t="s">
-        <v>280</v>
-      </c>
-      <c r="C47" s="43">
-        <v>1943</v>
-      </c>
-      <c r="D47" s="43"/>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" s="35">
-        <v>46</v>
-      </c>
-      <c r="B48" s="36" t="s">
-        <v>302</v>
-      </c>
-      <c r="C48" s="43">
-        <v>1988</v>
-      </c>
-      <c r="D48" s="43"/>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" s="35">
-        <v>47</v>
-      </c>
-      <c r="B49" s="36" t="s">
-        <v>289</v>
-      </c>
-      <c r="C49" s="43">
-        <v>1951</v>
-      </c>
-      <c r="D49" s="43"/>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" s="38">
-        <v>48</v>
-      </c>
-      <c r="B50" s="36" t="s">
-        <v>294</v>
-      </c>
-      <c r="C50" s="43">
-        <v>1535</v>
-      </c>
-      <c r="D50" s="43"/>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" s="35">
-        <v>49</v>
-      </c>
-      <c r="B51" s="68" t="s">
-        <v>360</v>
-      </c>
-      <c r="C51" s="69">
-        <v>1725</v>
-      </c>
-      <c r="D51" s="69">
-        <v>1876</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" s="38">
-        <v>50</v>
-      </c>
-      <c r="B52" s="68" t="s">
-        <v>368</v>
-      </c>
-      <c r="C52" s="69">
-        <v>1952</v>
-      </c>
-      <c r="D52" s="69"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId2"/>
-  </tableParts>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0041FEF0-BF6F-4667-AFBD-1C23A1866795}">
   <dimension ref="A1:D7"/>

--- a/Info/Additional_information.xlsx
+++ b/Info/Additional_information.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{811409A7-A766-45EF-BD38-3D1B5B9A2605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{868399DC-251A-4026-9205-AE472E550FA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Colours_specifications" sheetId="1" r:id="rId1"/>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1226" uniqueCount="869">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1284" uniqueCount="889">
   <si>
     <t>good quality (UNC for UNC collection; UNC and XF for XF collection)</t>
   </si>
@@ -1759,9 +1759,6 @@
     <t>Plastic cards</t>
   </si>
   <si>
-    <t>A009-01-FB-LN</t>
-  </si>
-  <si>
     <t>https://dartalexator.github.io/CoinCollection/index.html</t>
   </si>
   <si>
@@ -2470,30 +2467,6 @@
     <t>Монеты мира (часть 1) Европа, Америка, Африка, Австралия и Океания(вне конкретной коллеции)</t>
   </si>
   <si>
-    <t>A010-01-FB-LN</t>
-  </si>
-  <si>
-    <t>A011-01-FB-BN</t>
-  </si>
-  <si>
-    <t>A011-02-FB-DN</t>
-  </si>
-  <si>
-    <t>A012-01-OA-DB</t>
-  </si>
-  <si>
-    <t>A013-01-OA-GR</t>
-  </si>
-  <si>
-    <t>A013-02-OA-GR</t>
-  </si>
-  <si>
-    <t>A014-01-OA-BU</t>
-  </si>
-  <si>
-    <t>A015-01-OA-LN</t>
-  </si>
-  <si>
     <t>https://github.com/DartAlexator/CoinCollection/raw/master/Collections/Foreign_various/Foreighn_originals.xlsx</t>
   </si>
   <si>
@@ -2542,87 +2515,6 @@
     <t>Hard Link</t>
   </si>
   <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A000-00-00-00</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A001-01-GD-BK</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A001-02-GD-BK</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A001-03-GD-BK</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A001-04-GD-BK</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A001-05-GD-BK</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A001-06-GD-BK</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A002-01-OA-BK</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A002-02-OA-BK</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A003-01-OA-DB</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A003-02-OA-DB</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A004-01-OA-BK</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A004-02-OA-BK</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A005-01-OA-BK</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A005-02-OA-BK</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A006-01-OA-BU</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A007-01-OA-BK</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A008-01-OA-BK</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A009-01-FB-LN</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A010-01-FB-LN</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A011-01-FB-BN</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A011-02-FB-DN</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A012-01-OA-DB</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A013-01-OA-GR</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A013-02-OA-GR</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A014-01-OA-BU</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Info/Hardcoded_album_links/A015-01-OA-LN</t>
-  </si>
-  <si>
     <t>Annual Sets or special Sets</t>
   </si>
   <si>
@@ -2687,6 +2579,174 @@
   </si>
   <si>
     <t>A016-01-OA-BK</t>
+  </si>
+  <si>
+    <t>#000</t>
+  </si>
+  <si>
+    <t>#001</t>
+  </si>
+  <si>
+    <t>#002</t>
+  </si>
+  <si>
+    <t>#003</t>
+  </si>
+  <si>
+    <t>#004</t>
+  </si>
+  <si>
+    <t>#005</t>
+  </si>
+  <si>
+    <t>#006</t>
+  </si>
+  <si>
+    <t>#007</t>
+  </si>
+  <si>
+    <t>#008</t>
+  </si>
+  <si>
+    <t>#009</t>
+  </si>
+  <si>
+    <t>#010</t>
+  </si>
+  <si>
+    <t>#011</t>
+  </si>
+  <si>
+    <t>#012</t>
+  </si>
+  <si>
+    <t>#013</t>
+  </si>
+  <si>
+    <t>#014</t>
+  </si>
+  <si>
+    <t>#015</t>
+  </si>
+  <si>
+    <t>#016</t>
+  </si>
+  <si>
+    <t>#017</t>
+  </si>
+  <si>
+    <t>#020</t>
+  </si>
+  <si>
+    <t>#021</t>
+  </si>
+  <si>
+    <t>#022</t>
+  </si>
+  <si>
+    <t>#023</t>
+  </si>
+  <si>
+    <t>#024</t>
+  </si>
+  <si>
+    <t>#025</t>
+  </si>
+  <si>
+    <t>#026</t>
+  </si>
+  <si>
+    <t>#027</t>
+  </si>
+  <si>
+    <t>#018</t>
+  </si>
+  <si>
+    <t>#019</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/#000</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/#001</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/#002</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/#003</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/#004</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/#005</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/#006</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/#007</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/#008</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/#009</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/#010</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/#011</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/#012</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/#013</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/#014</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/#015</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/#016</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/#017</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/#018</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/#019</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/#020</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/#021</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/#022</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/#023</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/#024</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/#025</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/#026</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/#027</t>
   </si>
 </sst>
 </file>
@@ -3288,7 +3348,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3522,6 +3582,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="20" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3637,6 +3700,103 @@
     </dxf>
     <dxf>
       <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="0"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color theme="0"/>
+        </right>
+        <top style="thin">
+          <color theme="0"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="0"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thick">
+          <color theme="0"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <fill>
@@ -3789,103 +3949,6 @@
         <horizontal style="thin">
           <color auto="1"/>
         </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color theme="0"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color theme="0"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color theme="0"/>
-        </right>
-        <top style="thin">
-          <color theme="0"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="0"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thick">
-          <color theme="0"/>
-        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -4196,29 +4259,29 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9D0F8E3D-96B1-4DB8-B1A6-8DD6B84F3693}" name="Таблица35" displayName="Таблица35" ref="A1:D52" totalsRowShown="0" headerRowDxfId="17" dataDxfId="15" headerRowBorderDxfId="16" tableBorderDxfId="14" totalsRowBorderDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9D0F8E3D-96B1-4DB8-B1A6-8DD6B84F3693}" name="Таблица35" displayName="Таблица35" ref="A1:D52" totalsRowShown="0" headerRowDxfId="22" dataDxfId="20" headerRowBorderDxfId="21" tableBorderDxfId="19" totalsRowBorderDxfId="18">
   <autoFilter ref="A1:D52" xr:uid="{A2D8FA3D-4024-4365-BE1D-F93D0AF2D426}"/>
   <tableColumns count="4">
-    <tableColumn id="4" xr3:uid="{74AFB32D-7AAA-46BE-8174-ED698BB4613E}" name="Mint_id" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{523D65CD-0F56-441F-90B5-E46A9B14F0D0}" name="Ekaterinburg Mint" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{1AAB7352-E935-4EC6-A0D1-3EDC5D0BC93C}" name="Year_of_start" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{5FF15381-476A-4F88-B93A-6452F2830A0A}" name="Year_of_end" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{74AFB32D-7AAA-46BE-8174-ED698BB4613E}" name="Mint_id" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{523D65CD-0F56-441F-90B5-E46A9B14F0D0}" name="Ekaterinburg Mint" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{1AAB7352-E935-4EC6-A0D1-3EDC5D0BC93C}" name="Year_of_start" dataDxfId="15"/>
+    <tableColumn id="7" xr3:uid="{5FF15381-476A-4F88-B93A-6452F2830A0A}" name="Year_of_end" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D0DCC88A-2D36-4004-A694-FC0C0F0C3396}" name="Таблица2" displayName="Таблица2" ref="A1:C16" totalsRowShown="0" headerRowBorderDxfId="22" tableBorderDxfId="21" totalsRowBorderDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D0DCC88A-2D36-4004-A694-FC0C0F0C3396}" name="Таблица2" displayName="Таблица2" ref="A1:C16" totalsRowShown="0" headerRowBorderDxfId="13" tableBorderDxfId="12" totalsRowBorderDxfId="11">
   <autoFilter ref="A1:C16" xr:uid="{00000000-0009-0000-0100-000002000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{28358E6A-6F3A-468C-9E1C-880A34D9BECE}" name="№" dataDxfId="19"/>
+    <tableColumn id="1" xr3:uid="{28358E6A-6F3A-468C-9E1C-880A34D9BECE}" name="№" dataDxfId="10"/>
     <tableColumn id="2" xr3:uid="{DD0AD5C8-324B-4DA7-B39F-B2DB3EF91222}" name="Links:"/>
-    <tableColumn id="3" xr3:uid="{FC8A6018-CA7E-4C73-9B21-B272B55FA8C1}" name="Description:" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{FC8A6018-CA7E-4C73-9B21-B272B55FA8C1}" name="Description:" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -4620,7 +4683,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>847</v>
+        <v>811</v>
       </c>
     </row>
   </sheetData>
@@ -5135,7 +5198,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D5AF97D-14BA-4E23-B5FF-856D52BDA29A}">
-  <dimension ref="A1:Y30"/>
+  <dimension ref="A1:W31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.08984375" customWidth="1"/>
@@ -5144,36 +5207,34 @@
     <col min="4" max="5" width="8.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="61.5" x14ac:dyDescent="1.35">
-      <c r="A1" s="108" t="s">
-        <v>560</v>
-      </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="109"/>
-      <c r="F1" s="109"/>
-      <c r="G1" s="109"/>
-      <c r="H1" s="109"/>
-      <c r="I1" s="109"/>
-      <c r="J1" s="109"/>
-      <c r="K1" s="109"/>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
+    <row r="1" spans="1:23" ht="61.5" x14ac:dyDescent="1.35">
+      <c r="A1" s="109" t="s">
+        <v>559</v>
+      </c>
+      <c r="B1" s="110"/>
+      <c r="C1" s="110"/>
+      <c r="D1" s="110"/>
+      <c r="E1" s="110"/>
+      <c r="F1" s="110"/>
+      <c r="G1" s="110"/>
+      <c r="H1" s="110"/>
+      <c r="I1" s="110"/>
+      <c r="J1" s="110"/>
+      <c r="K1" s="110"/>
+      <c r="L1" s="110"/>
+      <c r="M1" s="110"/>
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="87"/>
+      <c r="S1" s="87"/>
       <c r="T1" s="87"/>
       <c r="U1" s="87"/>
       <c r="V1" s="87"/>
       <c r="W1" s="87"/>
-      <c r="X1" s="87"/>
-      <c r="Y1" s="87"/>
-    </row>
-    <row r="3" spans="1:25" ht="18.5" x14ac:dyDescent="0.45">
+    </row>
+    <row r="3" spans="1:23" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A3" s="88" t="s">
         <v>529</v>
       </c>
@@ -5181,310 +5242,322 @@
         <v>395</v>
       </c>
       <c r="C3" s="78" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A4">
-        <v>0</v>
+        <v>810</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A4" s="89" t="s">
+        <v>833</v>
       </c>
       <c r="B4" t="s">
         <v>524</v>
       </c>
       <c r="C4" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>1</v>
+        <v>861</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A5" s="89" t="s">
+        <v>834</v>
       </c>
       <c r="B5" t="s">
         <v>523</v>
       </c>
       <c r="C5" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A6">
-        <v>2</v>
+        <v>862</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A6" s="89" t="s">
+        <v>835</v>
       </c>
       <c r="B6" t="s">
         <v>528</v>
       </c>
       <c r="C6" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A7">
-        <v>3</v>
+        <v>863</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A7" s="89" t="s">
+        <v>836</v>
       </c>
       <c r="B7" t="s">
         <v>520</v>
       </c>
       <c r="C7" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A8">
-        <v>4</v>
+        <v>864</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A8" s="89" t="s">
+        <v>837</v>
       </c>
       <c r="B8" t="s">
         <v>527</v>
       </c>
       <c r="C8" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A9">
-        <v>5</v>
+        <v>865</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A9" s="89" t="s">
+        <v>838</v>
       </c>
       <c r="B9" t="s">
         <v>526</v>
       </c>
       <c r="C9" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A10">
-        <v>6</v>
+        <v>866</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A10" s="89" t="s">
+        <v>839</v>
       </c>
       <c r="B10" t="s">
         <v>525</v>
       </c>
       <c r="C10" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A11">
-        <v>7</v>
+        <v>867</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A11" s="89" t="s">
+        <v>840</v>
       </c>
       <c r="B11" t="s">
         <v>531</v>
       </c>
       <c r="C11" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A12">
-        <v>8</v>
+        <v>868</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A12" s="89" t="s">
+        <v>841</v>
       </c>
       <c r="B12" t="s">
         <v>530</v>
       </c>
       <c r="C12" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A13">
-        <v>9</v>
+        <v>869</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A13" s="89" t="s">
+        <v>842</v>
       </c>
       <c r="B13" t="s">
         <v>532</v>
       </c>
       <c r="C13" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A14">
-        <v>10</v>
+        <v>870</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A14" s="89" t="s">
+        <v>843</v>
       </c>
       <c r="B14" t="s">
         <v>533</v>
       </c>
       <c r="C14" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A15">
-        <v>11</v>
+        <v>871</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A15" s="89" t="s">
+        <v>844</v>
       </c>
       <c r="B15" t="s">
         <v>534</v>
       </c>
       <c r="C15" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A16">
-        <v>12</v>
+        <v>872</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A16" s="89" t="s">
+        <v>845</v>
       </c>
       <c r="B16" t="s">
         <v>535</v>
       </c>
       <c r="C16" t="s">
-        <v>832</v>
+        <v>873</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17">
-        <v>13</v>
+      <c r="A17" s="89" t="s">
+        <v>846</v>
       </c>
       <c r="B17" t="s">
         <v>536</v>
       </c>
       <c r="C17" t="s">
-        <v>833</v>
+        <v>874</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18">
-        <v>14</v>
+      <c r="A18" s="89" t="s">
+        <v>847</v>
       </c>
       <c r="B18" t="s">
         <v>537</v>
       </c>
       <c r="C18" t="s">
-        <v>834</v>
+        <v>875</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19">
-        <v>15</v>
+      <c r="A19" s="89" t="s">
+        <v>848</v>
       </c>
       <c r="B19" t="s">
         <v>542</v>
       </c>
       <c r="C19" t="s">
-        <v>835</v>
+        <v>876</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20">
-        <v>16</v>
+      <c r="A20" s="89" t="s">
+        <v>849</v>
       </c>
       <c r="B20" t="s">
         <v>545</v>
       </c>
       <c r="C20" t="s">
-        <v>836</v>
+        <v>877</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21">
-        <v>17</v>
+      <c r="A21" s="89" t="s">
+        <v>850</v>
       </c>
       <c r="B21" t="s">
         <v>546</v>
       </c>
       <c r="C21" t="s">
-        <v>837</v>
+        <v>878</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22">
-        <v>18</v>
+      <c r="A22" s="89" t="s">
+        <v>859</v>
       </c>
       <c r="B22" t="s">
-        <v>559</v>
+        <v>823</v>
       </c>
       <c r="C22" t="s">
-        <v>838</v>
+        <v>879</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23">
-        <v>19</v>
+      <c r="A23" s="89" t="s">
+        <v>860</v>
       </c>
       <c r="B23" t="s">
-        <v>796</v>
+        <v>824</v>
       </c>
       <c r="C23" t="s">
-        <v>839</v>
+        <v>880</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24">
-        <v>20</v>
+      <c r="A24" s="89" t="s">
+        <v>851</v>
       </c>
       <c r="B24" t="s">
-        <v>797</v>
+        <v>825</v>
       </c>
       <c r="C24" t="s">
-        <v>840</v>
+        <v>881</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25">
-        <v>21</v>
+      <c r="A25" s="89" t="s">
+        <v>852</v>
       </c>
       <c r="B25" t="s">
-        <v>798</v>
+        <v>826</v>
       </c>
       <c r="C25" t="s">
-        <v>841</v>
+        <v>882</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26">
-        <v>22</v>
+      <c r="A26" s="89" t="s">
+        <v>853</v>
       </c>
       <c r="B26" t="s">
-        <v>799</v>
+        <v>827</v>
       </c>
       <c r="C26" t="s">
-        <v>842</v>
+        <v>883</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27">
-        <v>23</v>
+      <c r="A27" s="89" t="s">
+        <v>854</v>
       </c>
       <c r="B27" t="s">
-        <v>800</v>
+        <v>828</v>
       </c>
       <c r="C27" t="s">
-        <v>843</v>
+        <v>884</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28">
-        <v>24</v>
+      <c r="A28" s="89" t="s">
+        <v>855</v>
       </c>
       <c r="B28" t="s">
-        <v>801</v>
+        <v>829</v>
       </c>
       <c r="C28" t="s">
-        <v>844</v>
+        <v>885</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29">
-        <v>25</v>
+      <c r="A29" s="89" t="s">
+        <v>856</v>
       </c>
       <c r="B29" t="s">
-        <v>802</v>
+        <v>830</v>
       </c>
       <c r="C29" t="s">
-        <v>845</v>
+        <v>886</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30">
-        <v>26</v>
+      <c r="A30" s="89" t="s">
+        <v>857</v>
       </c>
       <c r="B30" t="s">
-        <v>803</v>
+        <v>831</v>
       </c>
       <c r="C30" t="s">
-        <v>846</v>
+        <v>887</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" s="89" t="s">
+        <v>858</v>
+      </c>
+      <c r="B31" t="s">
+        <v>832</v>
+      </c>
+      <c r="C31" t="s">
+        <v>888</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A1:Q1"/>
   </mergeCells>
+  <phoneticPr fontId="18" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="A1" r:id="rId1" xr:uid="{1B51AF5A-9579-4E45-802C-86E0D9768BAB}"/>
   </hyperlinks>
@@ -5527,10 +5600,10 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" s="95">
+      <c r="A2" s="96">
         <v>1</v>
       </c>
-      <c r="B2" s="103">
+      <c r="B2" s="104">
         <v>1</v>
       </c>
       <c r="C2" s="4" t="s">
@@ -5547,8 +5620,8 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" s="96"/>
-      <c r="B3" s="103"/>
+      <c r="A3" s="97"/>
+      <c r="B3" s="104"/>
       <c r="C3" s="4" t="s">
         <v>65</v>
       </c>
@@ -5563,8 +5636,8 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" s="97"/>
-      <c r="B4" s="104">
+      <c r="A4" s="98"/>
+      <c r="B4" s="105">
         <v>2</v>
       </c>
       <c r="C4" s="4" t="s">
@@ -5581,14 +5654,14 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" s="97"/>
-      <c r="B5" s="104"/>
+      <c r="A5" s="98"/>
+      <c r="B5" s="105"/>
       <c r="C5" s="4" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6" s="97"/>
+      <c r="A6" s="98"/>
       <c r="B6" s="15">
         <v>3</v>
       </c>
@@ -5597,7 +5670,7 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" s="97"/>
+      <c r="A7" s="98"/>
       <c r="B7" s="16" t="s">
         <v>90</v>
       </c>
@@ -5606,8 +5679,8 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" s="97"/>
-      <c r="B8" s="105">
+      <c r="A8" s="98"/>
+      <c r="B8" s="106">
         <v>6</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -5615,14 +5688,14 @@
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="97"/>
-      <c r="B9" s="106"/>
+      <c r="A9" s="98"/>
+      <c r="B9" s="107"/>
       <c r="C9" s="4" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A10" s="97"/>
+      <c r="A10" s="98"/>
       <c r="B10" s="17">
         <v>7</v>
       </c>
@@ -5631,14 +5704,14 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="97"/>
+      <c r="A11" s="98"/>
       <c r="B11" s="24"/>
       <c r="C11" s="4" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="97"/>
+      <c r="A12" s="98"/>
       <c r="B12" s="18">
         <v>8</v>
       </c>
@@ -5647,7 +5720,7 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" s="98"/>
+      <c r="A13" s="99"/>
       <c r="B13" s="25" t="s">
         <v>78</v>
       </c>
@@ -5656,7 +5729,7 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="99"/>
+      <c r="A14" s="100"/>
       <c r="B14" s="26" t="s">
         <v>91</v>
       </c>
@@ -5665,7 +5738,7 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="14.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="100">
+      <c r="A15" s="101">
         <v>2</v>
       </c>
       <c r="B15" s="19" t="s">
@@ -5676,7 +5749,7 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="101"/>
+      <c r="A16" s="102"/>
       <c r="B16" s="20" t="s">
         <v>365</v>
       </c>
@@ -5685,7 +5758,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="101"/>
+      <c r="A17" s="102"/>
       <c r="B17" s="21" t="s">
         <v>366</v>
       </c>
@@ -5694,7 +5767,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="102"/>
+      <c r="A18" s="103"/>
       <c r="B18" s="22" t="s">
         <v>92</v>
       </c>
@@ -5703,7 +5776,7 @@
       </c>
     </row>
     <row r="19" spans="1:3" ht="14.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="89">
+      <c r="A19" s="90">
         <v>3</v>
       </c>
       <c r="B19" s="23" t="s">
@@ -5714,7 +5787,7 @@
       </c>
     </row>
     <row r="20" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="90"/>
+      <c r="A20" s="91"/>
       <c r="B20" s="27" t="s">
         <v>93</v>
       </c>
@@ -5723,7 +5796,7 @@
       </c>
     </row>
     <row r="21" spans="1:3" ht="14.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="91"/>
+      <c r="A21" s="92"/>
       <c r="B21" s="28" t="s">
         <v>95</v>
       </c>
@@ -5732,7 +5805,7 @@
       </c>
     </row>
     <row r="22" spans="1:3" ht="14.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="92">
+      <c r="A22" s="93">
         <v>4</v>
       </c>
       <c r="B22" s="19" t="s">
@@ -5743,7 +5816,7 @@
       </c>
     </row>
     <row r="23" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="93"/>
+      <c r="A23" s="94"/>
       <c r="B23" s="20" t="s">
         <v>98</v>
       </c>
@@ -5752,7 +5825,7 @@
       </c>
     </row>
     <row r="24" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="93"/>
+      <c r="A24" s="94"/>
       <c r="B24" s="21" t="s">
         <v>100</v>
       </c>
@@ -5761,7 +5834,7 @@
       </c>
     </row>
     <row r="25" spans="1:3" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="93"/>
+      <c r="A25" s="94"/>
       <c r="B25" s="16" t="s">
         <v>102</v>
       </c>
@@ -5770,7 +5843,7 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" s="93"/>
+      <c r="A26" s="94"/>
       <c r="B26" s="29" t="s">
         <v>104</v>
       </c>
@@ -5779,7 +5852,7 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" s="93"/>
+      <c r="A27" s="94"/>
       <c r="B27" s="30" t="s">
         <v>106</v>
       </c>
@@ -5788,7 +5861,7 @@
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" s="93"/>
+      <c r="A28" s="94"/>
       <c r="B28" s="18">
         <v>8</v>
       </c>
@@ -5797,7 +5870,7 @@
       </c>
     </row>
     <row r="29" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="94"/>
+      <c r="A29" s="95"/>
       <c r="B29" s="31" t="s">
         <v>78</v>
       </c>
@@ -5830,7 +5903,7 @@
   <dimension ref="A1:E29"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="3.453125" customWidth="1"/>
+    <col min="1" max="1" width="5.26953125" customWidth="1"/>
     <col min="2" max="2" width="15.54296875" customWidth="1"/>
     <col min="3" max="3" width="70" customWidth="1"/>
     <col min="4" max="4" width="89.08984375" customWidth="1"/>
@@ -5851,12 +5924,12 @@
         <v>481</v>
       </c>
       <c r="E1" s="78" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>0</v>
+      <c r="A2" s="89" t="s">
+        <v>833</v>
       </c>
       <c r="B2" t="s">
         <v>524</v>
@@ -5868,12 +5941,12 @@
         <v>521</v>
       </c>
       <c r="E2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3">
-        <v>1</v>
+      <c r="A3" s="89" t="s">
+        <v>834</v>
       </c>
       <c r="B3" t="s">
         <v>523</v>
@@ -5885,12 +5958,12 @@
         <v>501</v>
       </c>
       <c r="E3" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4">
-        <v>2</v>
+      <c r="A4" s="89" t="s">
+        <v>835</v>
       </c>
       <c r="B4" t="s">
         <v>528</v>
@@ -5902,12 +5975,12 @@
         <v>502</v>
       </c>
       <c r="E4" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>3</v>
+      <c r="A5" s="89" t="s">
+        <v>836</v>
       </c>
       <c r="B5" t="s">
         <v>520</v>
@@ -5919,12 +5992,12 @@
         <v>503</v>
       </c>
       <c r="E5" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6">
-        <v>4</v>
+      <c r="A6" s="89" t="s">
+        <v>837</v>
       </c>
       <c r="B6" t="s">
         <v>527</v>
@@ -5936,12 +6009,12 @@
         <v>498</v>
       </c>
       <c r="E6" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7">
-        <v>5</v>
+      <c r="A7" s="89" t="s">
+        <v>838</v>
       </c>
       <c r="B7" t="s">
         <v>526</v>
@@ -5953,12 +6026,12 @@
         <v>497</v>
       </c>
       <c r="E7" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8">
-        <v>6</v>
+      <c r="A8" s="89" t="s">
+        <v>839</v>
       </c>
       <c r="B8" t="s">
         <v>525</v>
@@ -5970,12 +6043,12 @@
         <v>496</v>
       </c>
       <c r="E8" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9">
-        <v>7</v>
+      <c r="A9" s="89" t="s">
+        <v>840</v>
       </c>
       <c r="B9" t="s">
         <v>531</v>
@@ -5987,12 +6060,12 @@
         <v>507</v>
       </c>
       <c r="E9" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10">
-        <v>8</v>
+      <c r="A10" s="89" t="s">
+        <v>841</v>
       </c>
       <c r="B10" t="s">
         <v>530</v>
@@ -6004,12 +6077,12 @@
         <v>506</v>
       </c>
       <c r="E10" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11">
-        <v>9</v>
+      <c r="A11" s="89" t="s">
+        <v>842</v>
       </c>
       <c r="B11" t="s">
         <v>532</v>
@@ -6021,12 +6094,12 @@
         <v>508</v>
       </c>
       <c r="E11" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12">
-        <v>10</v>
+      <c r="A12" s="89" t="s">
+        <v>843</v>
       </c>
       <c r="B12" t="s">
         <v>533</v>
@@ -6038,12 +6111,12 @@
         <v>509</v>
       </c>
       <c r="E12" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13">
-        <v>11</v>
+      <c r="A13" s="89" t="s">
+        <v>844</v>
       </c>
       <c r="B13" t="s">
         <v>534</v>
@@ -6055,12 +6128,12 @@
         <v>510</v>
       </c>
       <c r="E13" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14">
-        <v>12</v>
+      <c r="A14" s="89" t="s">
+        <v>845</v>
       </c>
       <c r="B14" t="s">
         <v>535</v>
@@ -6072,12 +6145,12 @@
         <v>511</v>
       </c>
       <c r="E14" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15">
-        <v>13</v>
+      <c r="A15" s="89" t="s">
+        <v>846</v>
       </c>
       <c r="B15" t="s">
         <v>536</v>
@@ -6089,12 +6162,12 @@
         <v>518</v>
       </c>
       <c r="E15" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16">
-        <v>14</v>
+      <c r="A16" s="89" t="s">
+        <v>847</v>
       </c>
       <c r="B16" t="s">
         <v>537</v>
@@ -6106,12 +6179,12 @@
         <v>519</v>
       </c>
       <c r="E16" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17">
-        <v>15</v>
+      <c r="A17" s="89" t="s">
+        <v>848</v>
       </c>
       <c r="B17" t="s">
         <v>542</v>
@@ -6123,12 +6196,12 @@
         <v>538</v>
       </c>
       <c r="E17" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18">
-        <v>16</v>
+      <c r="A18" s="89" t="s">
+        <v>849</v>
       </c>
       <c r="B18" t="s">
         <v>545</v>
@@ -6140,12 +6213,12 @@
         <v>544</v>
       </c>
       <c r="E18" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19">
-        <v>17</v>
+      <c r="A19" s="89" t="s">
+        <v>850</v>
       </c>
       <c r="B19" t="s">
         <v>546</v>
@@ -6154,52 +6227,52 @@
         <v>551</v>
       </c>
       <c r="D19" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E19" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" s="89" t="s">
+        <v>859</v>
+      </c>
+      <c r="B20" t="s">
+        <v>823</v>
+      </c>
+      <c r="C20" t="s">
+        <v>582</v>
+      </c>
+      <c r="D20" t="s">
+        <v>581</v>
+      </c>
+      <c r="E20" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" s="89" t="s">
+        <v>860</v>
+      </c>
+      <c r="B21" t="s">
+        <v>824</v>
+      </c>
+      <c r="C21" t="s">
+        <v>583</v>
+      </c>
+      <c r="D21" t="s">
         <v>580</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20">
-        <v>20</v>
-      </c>
-      <c r="B20" t="s">
-        <v>859</v>
-      </c>
-      <c r="C20" t="s">
-        <v>583</v>
-      </c>
-      <c r="D20" t="s">
-        <v>582</v>
-      </c>
-      <c r="E20" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21">
-        <v>21</v>
-      </c>
-      <c r="B21" t="s">
-        <v>860</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="E21" t="s">
         <v>584</v>
       </c>
-      <c r="D21" t="s">
-        <v>581</v>
-      </c>
-      <c r="E21" t="s">
-        <v>585</v>
-      </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22">
-        <v>22</v>
+      <c r="A22" s="89" t="s">
+        <v>851</v>
       </c>
       <c r="B22" t="s">
-        <v>861</v>
+        <v>825</v>
       </c>
       <c r="C22" t="s">
         <v>553</v>
@@ -6208,15 +6281,15 @@
         <v>552</v>
       </c>
       <c r="E22" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23">
-        <v>23</v>
+      <c r="A23" s="89" t="s">
+        <v>852</v>
       </c>
       <c r="B23" t="s">
-        <v>862</v>
+        <v>826</v>
       </c>
       <c r="C23" t="s">
         <v>554</v>
@@ -6225,49 +6298,49 @@
         <v>555</v>
       </c>
       <c r="E23" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24">
-        <v>24</v>
+      <c r="A24" s="89" t="s">
+        <v>853</v>
       </c>
       <c r="B24" t="s">
-        <v>863</v>
+        <v>827</v>
       </c>
       <c r="C24" t="s">
         <v>556</v>
       </c>
       <c r="D24" t="s">
+        <v>587</v>
+      </c>
+      <c r="E24" t="s">
         <v>588</v>
       </c>
-      <c r="E24" t="s">
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" s="89" t="s">
+        <v>854</v>
+      </c>
+      <c r="B25" t="s">
+        <v>828</v>
+      </c>
+      <c r="C25" t="s">
+        <v>590</v>
+      </c>
+      <c r="D25" t="s">
         <v>589</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A25">
-        <v>25</v>
-      </c>
-      <c r="B25" t="s">
-        <v>864</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="E25" t="s">
         <v>591</v>
       </c>
-      <c r="D25" t="s">
-        <v>590</v>
-      </c>
-      <c r="E25" t="s">
-        <v>592</v>
-      </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26">
-        <v>26</v>
+      <c r="A26" s="89" t="s">
+        <v>855</v>
       </c>
       <c r="B26" t="s">
-        <v>865</v>
+        <v>829</v>
       </c>
       <c r="C26" t="s">
         <v>558</v>
@@ -6276,58 +6349,58 @@
         <v>557</v>
       </c>
       <c r="E26" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A27">
-        <v>27</v>
+      <c r="A27" s="89" t="s">
+        <v>856</v>
       </c>
       <c r="B27" t="s">
-        <v>866</v>
+        <v>830</v>
       </c>
       <c r="C27" t="s">
-        <v>852</v>
+        <v>816</v>
       </c>
       <c r="D27" t="s">
-        <v>851</v>
+        <v>815</v>
       </c>
       <c r="E27" t="s">
-        <v>850</v>
+        <v>814</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A28">
-        <v>28</v>
+      <c r="A28" s="89" t="s">
+        <v>857</v>
       </c>
       <c r="B28" t="s">
-        <v>867</v>
+        <v>831</v>
       </c>
       <c r="C28" t="s">
-        <v>854</v>
+        <v>818</v>
       </c>
       <c r="D28" t="s">
-        <v>853</v>
+        <v>817</v>
       </c>
       <c r="E28" t="s">
-        <v>855</v>
+        <v>819</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A29">
-        <v>29</v>
+      <c r="A29" s="89" t="s">
+        <v>858</v>
       </c>
       <c r="B29" t="s">
-        <v>868</v>
+        <v>832</v>
       </c>
       <c r="C29" t="s">
-        <v>856</v>
+        <v>820</v>
       </c>
       <c r="D29" t="s">
-        <v>857</v>
+        <v>821</v>
       </c>
       <c r="E29" t="s">
-        <v>858</v>
+        <v>822</v>
       </c>
     </row>
   </sheetData>
@@ -6353,19 +6426,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>593</v>
+      </c>
+      <c r="B1" t="s">
         <v>594</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>595</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>596</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>597</v>
-      </c>
-      <c r="E1" t="s">
-        <v>598</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -6373,16 +6446,16 @@
         <v>524</v>
       </c>
       <c r="B2" s="86" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C2" t="s">
+        <v>642</v>
+      </c>
+      <c r="D2" s="86" t="s">
         <v>643</v>
       </c>
-      <c r="D2" s="86" t="s">
+      <c r="E2" s="86" t="s">
         <v>644</v>
-      </c>
-      <c r="E2" s="86" t="s">
-        <v>645</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -6390,16 +6463,16 @@
         <v>524</v>
       </c>
       <c r="B3" s="86" t="s">
+        <v>646</v>
+      </c>
+      <c r="C3" t="s">
         <v>647</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" s="86" t="s">
         <v>648</v>
       </c>
-      <c r="D3" s="86" t="s">
+      <c r="E3" s="86" t="s">
         <v>649</v>
-      </c>
-      <c r="E3" s="86" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -6407,16 +6480,16 @@
         <v>523</v>
       </c>
       <c r="B4" s="86" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C4" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D4" s="86" t="s">
+        <v>598</v>
+      </c>
+      <c r="E4" s="86" t="s">
         <v>599</v>
-      </c>
-      <c r="E4" s="86" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -6424,16 +6497,16 @@
         <v>523</v>
       </c>
       <c r="B5" s="86" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C5" t="s">
+        <v>602</v>
+      </c>
+      <c r="D5" s="86" t="s">
+        <v>601</v>
+      </c>
+      <c r="E5" s="86" t="s">
         <v>603</v>
-      </c>
-      <c r="D5" s="86" t="s">
-        <v>602</v>
-      </c>
-      <c r="E5" s="86" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -6441,16 +6514,16 @@
         <v>523</v>
       </c>
       <c r="B6" s="86" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C6" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D6" s="86" t="s">
+        <v>604</v>
+      </c>
+      <c r="E6" s="86" t="s">
         <v>605</v>
-      </c>
-      <c r="E6" s="86" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -6458,16 +6531,16 @@
         <v>523</v>
       </c>
       <c r="B7" s="86" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C7" t="s">
+        <v>608</v>
+      </c>
+      <c r="D7" s="86" t="s">
+        <v>607</v>
+      </c>
+      <c r="E7" s="86" t="s">
         <v>609</v>
-      </c>
-      <c r="D7" s="86" t="s">
-        <v>608</v>
-      </c>
-      <c r="E7" s="86" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -6475,16 +6548,16 @@
         <v>523</v>
       </c>
       <c r="B8" s="86" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C8" t="s">
+        <v>611</v>
+      </c>
+      <c r="D8" s="86" t="s">
+        <v>610</v>
+      </c>
+      <c r="E8" s="86" t="s">
         <v>612</v>
-      </c>
-      <c r="D8" s="86" t="s">
-        <v>611</v>
-      </c>
-      <c r="E8" s="86" t="s">
-        <v>613</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -6492,16 +6565,16 @@
         <v>523</v>
       </c>
       <c r="B9" s="86" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C9" t="s">
+        <v>614</v>
+      </c>
+      <c r="D9" s="86" t="s">
+        <v>613</v>
+      </c>
+      <c r="E9" s="86" t="s">
         <v>615</v>
-      </c>
-      <c r="D9" s="86" t="s">
-        <v>614</v>
-      </c>
-      <c r="E9" s="86" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -6509,16 +6582,16 @@
         <v>523</v>
       </c>
       <c r="B10" s="86" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C10" t="s">
+        <v>617</v>
+      </c>
+      <c r="D10" s="86" t="s">
+        <v>616</v>
+      </c>
+      <c r="E10" s="86" t="s">
         <v>618</v>
-      </c>
-      <c r="D10" s="86" t="s">
-        <v>617</v>
-      </c>
-      <c r="E10" s="86" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -6526,16 +6599,16 @@
         <v>523</v>
       </c>
       <c r="B11" s="86" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C11" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="D11" s="86" t="s">
+        <v>619</v>
+      </c>
+      <c r="E11" s="86" t="s">
         <v>620</v>
-      </c>
-      <c r="E11" s="86" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -6543,16 +6616,16 @@
         <v>523</v>
       </c>
       <c r="B12" s="86" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C12" t="s">
+        <v>623</v>
+      </c>
+      <c r="D12" s="86" t="s">
+        <v>622</v>
+      </c>
+      <c r="E12" s="86" t="s">
         <v>624</v>
-      </c>
-      <c r="D12" s="86" t="s">
-        <v>623</v>
-      </c>
-      <c r="E12" s="86" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -6560,16 +6633,16 @@
         <v>523</v>
       </c>
       <c r="B13" s="86" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C13" t="s">
+        <v>626</v>
+      </c>
+      <c r="D13" s="86" t="s">
+        <v>625</v>
+      </c>
+      <c r="E13" s="86" t="s">
         <v>627</v>
-      </c>
-      <c r="D13" s="86" t="s">
-        <v>626</v>
-      </c>
-      <c r="E13" s="86" t="s">
-        <v>628</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
@@ -6577,16 +6650,16 @@
         <v>523</v>
       </c>
       <c r="B14" s="86" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C14" t="s">
+        <v>629</v>
+      </c>
+      <c r="D14" s="86" t="s">
+        <v>628</v>
+      </c>
+      <c r="E14" s="86" t="s">
         <v>630</v>
-      </c>
-      <c r="D14" s="86" t="s">
-        <v>629</v>
-      </c>
-      <c r="E14" s="86" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
@@ -6594,16 +6667,16 @@
         <v>528</v>
       </c>
       <c r="B15" s="86" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C15" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D15" s="86" t="s">
+        <v>650</v>
+      </c>
+      <c r="E15" s="86" t="s">
         <v>651</v>
-      </c>
-      <c r="E15" s="86" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
@@ -6611,16 +6684,16 @@
         <v>528</v>
       </c>
       <c r="B16" s="86" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C16" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D16" s="86" t="s">
+        <v>654</v>
+      </c>
+      <c r="E16" s="86" t="s">
         <v>655</v>
-      </c>
-      <c r="E16" s="86" t="s">
-        <v>656</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
@@ -6628,16 +6701,16 @@
         <v>528</v>
       </c>
       <c r="B17" s="86" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C17" t="s">
+        <v>658</v>
+      </c>
+      <c r="D17" s="86" t="s">
         <v>659</v>
       </c>
-      <c r="D17" s="86" t="s">
+      <c r="E17" s="86" t="s">
         <v>660</v>
-      </c>
-      <c r="E17" s="86" t="s">
-        <v>661</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
@@ -6645,16 +6718,16 @@
         <v>520</v>
       </c>
       <c r="B18" s="86" t="s">
+        <v>662</v>
+      </c>
+      <c r="C18" t="s">
         <v>663</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" s="86" t="s">
         <v>664</v>
       </c>
-      <c r="D18" s="86" t="s">
+      <c r="E18" s="86" t="s">
         <v>665</v>
-      </c>
-      <c r="E18" s="86" t="s">
-        <v>666</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
@@ -6662,16 +6735,16 @@
         <v>520</v>
       </c>
       <c r="B19" s="86" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C19" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D19" s="86" t="s">
+        <v>666</v>
+      </c>
+      <c r="E19" s="86" t="s">
         <v>667</v>
-      </c>
-      <c r="E19" s="86" t="s">
-        <v>668</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
@@ -6679,16 +6752,16 @@
         <v>520</v>
       </c>
       <c r="B20" s="86" t="s">
+        <v>670</v>
+      </c>
+      <c r="C20" t="s">
         <v>671</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" s="86" t="s">
         <v>672</v>
       </c>
-      <c r="D20" s="86" t="s">
+      <c r="E20" s="86" t="s">
         <v>673</v>
-      </c>
-      <c r="E20" s="86" t="s">
-        <v>674</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
@@ -6696,16 +6769,16 @@
         <v>527</v>
       </c>
       <c r="B21" s="86" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C21" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="D21" s="86" t="s">
+        <v>674</v>
+      </c>
+      <c r="E21" s="86" t="s">
         <v>675</v>
-      </c>
-      <c r="E21" s="86" t="s">
-        <v>676</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
@@ -6713,16 +6786,16 @@
         <v>527</v>
       </c>
       <c r="B22" s="86" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C22" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="D22" s="86" t="s">
+        <v>678</v>
+      </c>
+      <c r="E22" s="86" t="s">
         <v>679</v>
-      </c>
-      <c r="E22" s="86" t="s">
-        <v>680</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
@@ -6730,16 +6803,16 @@
         <v>527</v>
       </c>
       <c r="B23" s="86" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C23" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D23" s="86" t="s">
+        <v>682</v>
+      </c>
+      <c r="E23" s="86" t="s">
         <v>683</v>
-      </c>
-      <c r="E23" s="86" t="s">
-        <v>684</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
@@ -6747,16 +6820,16 @@
         <v>527</v>
       </c>
       <c r="B24" s="86" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C24" t="s">
+        <v>687</v>
+      </c>
+      <c r="D24" s="86" t="s">
+        <v>686</v>
+      </c>
+      <c r="E24" s="86" t="s">
         <v>688</v>
-      </c>
-      <c r="D24" s="86" t="s">
-        <v>687</v>
-      </c>
-      <c r="E24" s="86" t="s">
-        <v>689</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
@@ -6764,16 +6837,16 @@
         <v>527</v>
       </c>
       <c r="B25" s="86" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C25" t="s">
+        <v>691</v>
+      </c>
+      <c r="D25" s="86" t="s">
+        <v>690</v>
+      </c>
+      <c r="E25" s="86" t="s">
         <v>692</v>
-      </c>
-      <c r="D25" s="86" t="s">
-        <v>691</v>
-      </c>
-      <c r="E25" s="86" t="s">
-        <v>693</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
@@ -6781,16 +6854,16 @@
         <v>527</v>
       </c>
       <c r="B26" s="86" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C26" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D26" s="86" t="s">
+        <v>694</v>
+      </c>
+      <c r="E26" s="86" t="s">
         <v>695</v>
-      </c>
-      <c r="E26" s="86" t="s">
-        <v>696</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
@@ -6798,7 +6871,7 @@
         <v>526</v>
       </c>
       <c r="C27" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
@@ -6806,7 +6879,7 @@
         <v>525</v>
       </c>
       <c r="C28" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
@@ -6814,16 +6887,16 @@
         <v>531</v>
       </c>
       <c r="B29" s="86" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C29" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="D29" s="86" t="s">
+        <v>699</v>
+      </c>
+      <c r="E29" s="86" t="s">
         <v>700</v>
-      </c>
-      <c r="E29" s="86" t="s">
-        <v>701</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
@@ -6831,16 +6904,16 @@
         <v>530</v>
       </c>
       <c r="B30" s="86" t="s">
+        <v>702</v>
+      </c>
+      <c r="C30" t="s">
         <v>703</v>
       </c>
-      <c r="C30" t="s">
-        <v>704</v>
-      </c>
       <c r="D30" s="86" t="s">
+        <v>699</v>
+      </c>
+      <c r="E30" s="86" t="s">
         <v>700</v>
-      </c>
-      <c r="E30" s="86" t="s">
-        <v>701</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
@@ -6848,16 +6921,16 @@
         <v>532</v>
       </c>
       <c r="B31" s="86" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C31" t="s">
         <v>508</v>
       </c>
       <c r="D31" s="86" t="s">
+        <v>704</v>
+      </c>
+      <c r="E31" s="86" t="s">
         <v>705</v>
-      </c>
-      <c r="E31" s="86" t="s">
-        <v>706</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
@@ -6865,16 +6938,16 @@
         <v>533</v>
       </c>
       <c r="B32" s="86" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C32" t="s">
         <v>509</v>
       </c>
       <c r="D32" s="86" t="s">
+        <v>704</v>
+      </c>
+      <c r="E32" s="86" t="s">
         <v>705</v>
-      </c>
-      <c r="E32" s="86" t="s">
-        <v>706</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
@@ -6882,16 +6955,16 @@
         <v>534</v>
       </c>
       <c r="B33" s="86" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C33" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D33" s="86" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="E33" s="86" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
@@ -6899,16 +6972,16 @@
         <v>534</v>
       </c>
       <c r="B34" s="86" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C34" t="s">
+        <v>602</v>
+      </c>
+      <c r="D34" s="86" t="s">
+        <v>708</v>
+      </c>
+      <c r="E34" s="86" t="s">
         <v>603</v>
-      </c>
-      <c r="D34" s="86" t="s">
-        <v>709</v>
-      </c>
-      <c r="E34" s="86" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
@@ -6916,16 +6989,16 @@
         <v>534</v>
       </c>
       <c r="B35" s="86" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C35" t="s">
+        <v>709</v>
+      </c>
+      <c r="D35" s="86" t="s">
         <v>710</v>
       </c>
-      <c r="D35" s="86" t="s">
+      <c r="E35" s="86" t="s">
         <v>711</v>
-      </c>
-      <c r="E35" s="86" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
@@ -6933,16 +7006,16 @@
         <v>534</v>
       </c>
       <c r="B36" s="86" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C36" t="s">
+        <v>691</v>
+      </c>
+      <c r="D36" s="86" t="s">
+        <v>713</v>
+      </c>
+      <c r="E36" s="86" t="s">
         <v>692</v>
-      </c>
-      <c r="D36" s="86" t="s">
-        <v>714</v>
-      </c>
-      <c r="E36" s="86" t="s">
-        <v>693</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
@@ -6950,16 +7023,16 @@
         <v>534</v>
       </c>
       <c r="B37" s="86" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C37" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D37" s="86" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E37" s="86" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
@@ -6967,16 +7040,16 @@
         <v>534</v>
       </c>
       <c r="B38" s="86" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C38" t="s">
+        <v>608</v>
+      </c>
+      <c r="D38" s="86" t="s">
+        <v>715</v>
+      </c>
+      <c r="E38" s="86" t="s">
         <v>609</v>
-      </c>
-      <c r="D38" s="86" t="s">
-        <v>716</v>
-      </c>
-      <c r="E38" s="86" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
@@ -6984,16 +7057,16 @@
         <v>534</v>
       </c>
       <c r="B39" s="86" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C39" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="D39" s="86" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="E39" s="86" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
@@ -7001,16 +7074,16 @@
         <v>534</v>
       </c>
       <c r="B40" s="86" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C40" t="s">
+        <v>611</v>
+      </c>
+      <c r="D40" s="86" t="s">
+        <v>717</v>
+      </c>
+      <c r="E40" s="86" t="s">
         <v>612</v>
-      </c>
-      <c r="D40" s="86" t="s">
-        <v>718</v>
-      </c>
-      <c r="E40" s="86" t="s">
-        <v>613</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
@@ -7018,16 +7091,16 @@
         <v>534</v>
       </c>
       <c r="B41" s="86" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C41" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D41" s="86" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="E41" s="86" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
@@ -7035,16 +7108,16 @@
         <v>534</v>
       </c>
       <c r="B42" s="86" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C42" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D42" s="86" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E42" s="86" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
@@ -7052,16 +7125,16 @@
         <v>534</v>
       </c>
       <c r="B43" s="86" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C43" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="D43" s="86" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="E43" s="86" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
@@ -7069,16 +7142,16 @@
         <v>534</v>
       </c>
       <c r="B44" s="86" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C44" t="s">
+        <v>614</v>
+      </c>
+      <c r="D44" s="86" t="s">
+        <v>721</v>
+      </c>
+      <c r="E44" s="86" t="s">
         <v>615</v>
-      </c>
-      <c r="D44" s="86" t="s">
-        <v>722</v>
-      </c>
-      <c r="E44" s="86" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
@@ -7086,16 +7159,16 @@
         <v>534</v>
       </c>
       <c r="B45" s="86" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C45" t="s">
+        <v>617</v>
+      </c>
+      <c r="D45" s="86" t="s">
+        <v>722</v>
+      </c>
+      <c r="E45" s="86" t="s">
         <v>618</v>
-      </c>
-      <c r="D45" s="86" t="s">
-        <v>723</v>
-      </c>
-      <c r="E45" s="86" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
@@ -7103,16 +7176,16 @@
         <v>534</v>
       </c>
       <c r="B46" s="86" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C46" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D46" s="86" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="E46" s="86" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
@@ -7120,16 +7193,16 @@
         <v>534</v>
       </c>
       <c r="B47" s="86" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C47" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D47" s="83" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E47" s="86" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
@@ -7137,16 +7210,16 @@
         <v>535</v>
       </c>
       <c r="B48" s="86" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C48" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="D48" s="86" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="E48" s="86" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
@@ -7154,16 +7227,16 @@
         <v>535</v>
       </c>
       <c r="B49" s="86" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C49" t="s">
+        <v>626</v>
+      </c>
+      <c r="D49" s="86" t="s">
+        <v>727</v>
+      </c>
+      <c r="E49" s="86" t="s">
         <v>627</v>
-      </c>
-      <c r="D49" s="86" t="s">
-        <v>728</v>
-      </c>
-      <c r="E49" s="86" t="s">
-        <v>628</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
@@ -7171,16 +7244,16 @@
         <v>535</v>
       </c>
       <c r="B50" s="86" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C50" t="s">
+        <v>629</v>
+      </c>
+      <c r="D50" s="86" t="s">
+        <v>728</v>
+      </c>
+      <c r="E50" s="86" t="s">
         <v>630</v>
-      </c>
-      <c r="D50" s="86" t="s">
-        <v>729</v>
-      </c>
-      <c r="E50" s="86" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
@@ -7188,16 +7261,16 @@
         <v>535</v>
       </c>
       <c r="B51" s="86" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C51" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D51" s="86" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E51" s="86" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
@@ -7205,16 +7278,16 @@
         <v>535</v>
       </c>
       <c r="B52" s="86" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C52" t="s">
+        <v>687</v>
+      </c>
+      <c r="D52" s="86" t="s">
+        <v>730</v>
+      </c>
+      <c r="E52" s="86" t="s">
         <v>688</v>
-      </c>
-      <c r="D52" s="86" t="s">
-        <v>731</v>
-      </c>
-      <c r="E52" s="86" t="s">
-        <v>689</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
@@ -7222,16 +7295,16 @@
         <v>535</v>
       </c>
       <c r="B53" s="86" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C53" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="D53" s="86" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="E53" s="86" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
@@ -7239,16 +7312,16 @@
         <v>536</v>
       </c>
       <c r="B54" s="86" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C54" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D54" s="86" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E54" s="86" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
@@ -7256,16 +7329,16 @@
         <v>537</v>
       </c>
       <c r="B55" s="86" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C55" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="D55" s="86" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E55" s="86" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
@@ -7273,16 +7346,16 @@
         <v>542</v>
       </c>
       <c r="B56" s="86" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C56" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="D56" s="86" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="E56" s="86" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
@@ -7290,16 +7363,16 @@
         <v>545</v>
       </c>
       <c r="B57" s="86" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C57" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D57" s="86" t="s">
+        <v>704</v>
+      </c>
+      <c r="E57" s="86" t="s">
         <v>705</v>
-      </c>
-      <c r="E57" s="86" t="s">
-        <v>706</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
@@ -7307,16 +7380,16 @@
         <v>545</v>
       </c>
       <c r="B58" s="86" t="s">
+        <v>738</v>
+      </c>
+      <c r="C58" t="s">
         <v>739</v>
       </c>
-      <c r="C58" t="s">
+      <c r="D58" s="86" t="s">
         <v>740</v>
       </c>
-      <c r="D58" s="86" t="s">
-        <v>741</v>
-      </c>
       <c r="E58" s="86" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
@@ -7324,16 +7397,16 @@
         <v>546</v>
       </c>
       <c r="B59" s="86" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C59" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D59" s="86" t="s">
+        <v>741</v>
+      </c>
+      <c r="E59" s="86" t="s">
         <v>742</v>
-      </c>
-      <c r="E59" s="86" t="s">
-        <v>743</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
@@ -7341,16 +7414,16 @@
         <v>546</v>
       </c>
       <c r="B60" s="86" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="C60" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D60" s="86" t="s">
+        <v>743</v>
+      </c>
+      <c r="E60" s="86" t="s">
         <v>744</v>
-      </c>
-      <c r="E60" s="86" t="s">
-        <v>745</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
@@ -7358,58 +7431,58 @@
         <v>546</v>
       </c>
       <c r="B61" s="86" t="s">
+        <v>746</v>
+      </c>
+      <c r="C61" t="s">
         <v>747</v>
       </c>
-      <c r="C61" t="s">
+      <c r="D61" s="86" t="s">
         <v>748</v>
       </c>
-      <c r="D61" s="86" t="s">
-        <v>749</v>
-      </c>
       <c r="E61" s="86" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>859</v>
+        <v>823</v>
       </c>
       <c r="B62" s="86" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C62" t="s">
+        <v>794</v>
+      </c>
+      <c r="D62" s="86" t="s">
         <v>795</v>
       </c>
-      <c r="D62" s="86" t="s">
-        <v>804</v>
-      </c>
       <c r="E62" s="86" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>860</v>
+        <v>824</v>
       </c>
       <c r="B63" s="86" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C63" t="s">
-        <v>805</v>
+        <v>796</v>
       </c>
       <c r="D63" s="86" t="s">
-        <v>804</v>
+        <v>795</v>
       </c>
       <c r="E63" s="86" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>862</v>
+        <v>826</v>
       </c>
       <c r="B64" t="s">
-        <v>806</v>
+        <v>797</v>
       </c>
       <c r="C64" t="s">
         <v>552</v>
@@ -7417,10 +7490,10 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>862</v>
+        <v>826</v>
       </c>
       <c r="B65" t="s">
-        <v>807</v>
+        <v>798</v>
       </c>
       <c r="C65" t="s">
         <v>555</v>
@@ -7428,65 +7501,65 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>863</v>
+        <v>827</v>
       </c>
       <c r="B66" t="s">
-        <v>808</v>
+        <v>799</v>
       </c>
       <c r="C66" t="s">
-        <v>811</v>
+        <v>802</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>863</v>
+        <v>827</v>
       </c>
       <c r="B67" t="s">
-        <v>810</v>
+        <v>801</v>
       </c>
       <c r="C67" t="s">
-        <v>809</v>
+        <v>800</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>864</v>
+        <v>828</v>
       </c>
       <c r="B68" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C68" t="s">
-        <v>812</v>
+        <v>803</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>864</v>
+        <v>828</v>
       </c>
       <c r="B69" t="s">
-        <v>815</v>
+        <v>806</v>
       </c>
       <c r="C69" t="s">
-        <v>814</v>
+        <v>805</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>864</v>
+        <v>828</v>
       </c>
       <c r="B70" t="s">
-        <v>816</v>
+        <v>807</v>
       </c>
       <c r="C70" t="s">
-        <v>817</v>
+        <v>808</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>865</v>
+        <v>829</v>
       </c>
       <c r="B71" t="s">
-        <v>818</v>
+        <v>809</v>
       </c>
       <c r="C71" t="s">
         <v>557</v>
@@ -7494,291 +7567,291 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>866</v>
+        <v>830</v>
       </c>
       <c r="B72" s="86" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C72" t="s">
+        <v>750</v>
+      </c>
+      <c r="D72" s="86" t="s">
+        <v>749</v>
+      </c>
+      <c r="E72" s="86" t="s">
         <v>751</v>
-      </c>
-      <c r="D72" s="86" t="s">
-        <v>750</v>
-      </c>
-      <c r="E72" s="86" t="s">
-        <v>752</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>866</v>
+        <v>830</v>
       </c>
       <c r="B73" s="86" t="s">
+        <v>752</v>
+      </c>
+      <c r="C73" t="s">
+        <v>754</v>
+      </c>
+      <c r="D73" s="86" t="s">
         <v>753</v>
       </c>
-      <c r="C73" t="s">
-        <v>755</v>
-      </c>
-      <c r="D73" s="86" t="s">
-        <v>754</v>
-      </c>
       <c r="E73" s="86" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>867</v>
+        <v>831</v>
       </c>
       <c r="B74" s="86" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="C74" t="s">
+        <v>774</v>
+      </c>
+      <c r="D74" s="86" t="s">
+        <v>773</v>
+      </c>
+      <c r="E74" s="86" t="s">
         <v>775</v>
-      </c>
-      <c r="D74" s="86" t="s">
-        <v>774</v>
-      </c>
-      <c r="E74" s="86" t="s">
-        <v>776</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>867</v>
+        <v>831</v>
       </c>
       <c r="B75" s="86" t="s">
+        <v>776</v>
+      </c>
+      <c r="C75" t="s">
         <v>777</v>
       </c>
-      <c r="C75" t="s">
+      <c r="D75" s="86" t="s">
         <v>778</v>
       </c>
-      <c r="D75" s="86" t="s">
-        <v>779</v>
-      </c>
       <c r="E75" s="86" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>867</v>
+        <v>831</v>
       </c>
       <c r="B76" s="86" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="C76" t="s">
+        <v>756</v>
+      </c>
+      <c r="D76" s="86" t="s">
+        <v>755</v>
+      </c>
+      <c r="E76" s="86" t="s">
         <v>757</v>
-      </c>
-      <c r="D76" s="86" t="s">
-        <v>756</v>
-      </c>
-      <c r="E76" s="86" t="s">
-        <v>758</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>867</v>
+        <v>831</v>
       </c>
       <c r="B77" s="86" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C77" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D77" s="86" t="s">
+        <v>759</v>
+      </c>
+      <c r="E77" s="86" t="s">
         <v>760</v>
-      </c>
-      <c r="E77" s="86" t="s">
-        <v>761</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>867</v>
+        <v>831</v>
       </c>
       <c r="B78" s="86" t="s">
+        <v>761</v>
+      </c>
+      <c r="C78" t="s">
+        <v>764</v>
+      </c>
+      <c r="D78" s="86" t="s">
         <v>762</v>
       </c>
-      <c r="C78" t="s">
-        <v>765</v>
-      </c>
-      <c r="D78" s="86" t="s">
-        <v>763</v>
-      </c>
       <c r="E78" s="86" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>867</v>
+        <v>831</v>
       </c>
       <c r="B79" s="86" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C79" t="s">
-        <v>848</v>
+        <v>812</v>
       </c>
       <c r="D79" s="86" t="s">
-        <v>849</v>
+        <v>813</v>
       </c>
       <c r="E79" s="86" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>867</v>
+        <v>831</v>
       </c>
       <c r="B80" s="86" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="C80" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="D80" s="86" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="E80" s="86" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>867</v>
+        <v>831</v>
       </c>
       <c r="B81" s="86" t="s">
+        <v>770</v>
+      </c>
+      <c r="C81" t="s">
         <v>771</v>
       </c>
-      <c r="C81" t="s">
+      <c r="D81" s="86" t="s">
         <v>772</v>
       </c>
-      <c r="D81" s="86" t="s">
-        <v>773</v>
-      </c>
       <c r="E81" s="86" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>868</v>
+        <v>832</v>
       </c>
       <c r="B82" s="86" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C82" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="D82" s="86" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E82" s="86" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>868</v>
+        <v>832</v>
       </c>
       <c r="B83" s="86" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="C83" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="D83" s="86" t="s">
+        <v>779</v>
+      </c>
+      <c r="E83" s="86" t="s">
         <v>780</v>
-      </c>
-      <c r="E83" s="86" t="s">
-        <v>781</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>868</v>
+        <v>832</v>
       </c>
       <c r="B84" s="86" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="C84" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="D84" s="86" t="s">
+        <v>779</v>
+      </c>
+      <c r="E84" s="86" t="s">
         <v>780</v>
-      </c>
-      <c r="E84" s="86" t="s">
-        <v>781</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>868</v>
+        <v>832</v>
       </c>
       <c r="B85" s="86" t="s">
+        <v>784</v>
+      </c>
+      <c r="C85" t="s">
         <v>785</v>
       </c>
-      <c r="C85" t="s">
-        <v>786</v>
-      </c>
       <c r="D85" s="86" t="s">
+        <v>779</v>
+      </c>
+      <c r="E85" s="86" t="s">
         <v>780</v>
-      </c>
-      <c r="E85" s="86" t="s">
-        <v>781</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>868</v>
+        <v>832</v>
       </c>
       <c r="B86" s="86" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C86" t="s">
+        <v>786</v>
+      </c>
+      <c r="D86" s="86" t="s">
         <v>787</v>
       </c>
-      <c r="D86" s="86" t="s">
-        <v>788</v>
-      </c>
       <c r="E86" s="86" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>868</v>
+        <v>832</v>
       </c>
       <c r="B87" s="86" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="C87" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="D87" s="86" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="E87" s="86" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>868</v>
+        <v>832</v>
       </c>
       <c r="B88" s="86" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C88" t="s">
+        <v>792</v>
+      </c>
+      <c r="D88" s="86" t="s">
         <v>793</v>
       </c>
-      <c r="D88" s="86" t="s">
-        <v>794</v>
-      </c>
       <c r="E88" s="86" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
   </sheetData>
@@ -8047,11 +8120,11 @@
       <c r="D1" s="72" t="s">
         <v>394</v>
       </c>
-      <c r="W1" s="107" t="s">
+      <c r="W1" s="108" t="s">
         <v>403</v>
       </c>
-      <c r="X1" s="107"/>
-      <c r="Y1" s="107"/>
+      <c r="X1" s="108"/>
+      <c r="Y1" s="108"/>
     </row>
     <row r="2" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="77" t="s">
@@ -8112,10 +8185,10 @@
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5" s="85" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B5" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C5" s="73" t="s">
         <v>142</v>
@@ -8241,10 +8314,10 @@
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.35">
       <c r="C14" s="85" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D14" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="X14" s="79" t="s">
         <v>414</v>

--- a/Info/Additional_information.xlsx
+++ b/Info/Additional_information.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{868399DC-251A-4026-9205-AE472E550FA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D995C7D-5206-4A69-AA69-5CA952D3B75F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Colours_specifications" sheetId="1" r:id="rId1"/>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1284" uniqueCount="889">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1284" uniqueCount="890">
   <si>
     <t>good quality (UNC for UNC collection; UNC and XF for XF collection)</t>
   </si>
@@ -1669,9 +1669,6 @@
     <t>A001-02-GD-BK</t>
   </si>
   <si>
-    <t>#</t>
-  </si>
-  <si>
     <t>A002-02-OA-BK</t>
   </si>
   <si>
@@ -2581,172 +2578,178 @@
     <t>A016-01-OA-BK</t>
   </si>
   <si>
-    <t>#000</t>
-  </si>
-  <si>
-    <t>#001</t>
-  </si>
-  <si>
-    <t>#002</t>
-  </si>
-  <si>
-    <t>#003</t>
-  </si>
-  <si>
-    <t>#004</t>
-  </si>
-  <si>
-    <t>#005</t>
-  </si>
-  <si>
-    <t>#006</t>
-  </si>
-  <si>
-    <t>#007</t>
-  </si>
-  <si>
-    <t>#008</t>
-  </si>
-  <si>
-    <t>#009</t>
-  </si>
-  <si>
-    <t>#010</t>
-  </si>
-  <si>
-    <t>#011</t>
-  </si>
-  <si>
-    <t>#012</t>
-  </si>
-  <si>
-    <t>#013</t>
-  </si>
-  <si>
-    <t>#014</t>
-  </si>
-  <si>
-    <t>#015</t>
-  </si>
-  <si>
-    <t>#016</t>
-  </si>
-  <si>
-    <t>#017</t>
-  </si>
-  <si>
-    <t>#020</t>
-  </si>
-  <si>
-    <t>#021</t>
-  </si>
-  <si>
-    <t>#022</t>
-  </si>
-  <si>
-    <t>#023</t>
-  </si>
-  <si>
-    <t>#024</t>
-  </si>
-  <si>
-    <t>#025</t>
-  </si>
-  <si>
-    <t>#026</t>
-  </si>
-  <si>
-    <t>#027</t>
-  </si>
-  <si>
-    <t>#018</t>
-  </si>
-  <si>
-    <t>#019</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Links/#000</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Links/#001</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Links/#002</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Links/#003</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Links/#004</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Links/#005</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Links/#006</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Links/#007</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Links/#008</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Links/#009</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Links/#010</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Links/#011</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Links/#012</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Links/#013</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Links/#014</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Links/#015</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Links/#016</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Links/#017</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Links/#018</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Links/#019</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Links/#020</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Links/#021</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Links/#022</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Links/#023</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Links/#024</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Links/#025</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Links/#026</t>
-  </si>
-  <si>
-    <t>https://dartalexator.github.io/CoinCollection/Links/#027</t>
+    <t>n000</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/n000</t>
+  </si>
+  <si>
+    <t>n001</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/n001</t>
+  </si>
+  <si>
+    <t>n002</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/n002</t>
+  </si>
+  <si>
+    <t>n003</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/n003</t>
+  </si>
+  <si>
+    <t>n004</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/n004</t>
+  </si>
+  <si>
+    <t>n005</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/n005</t>
+  </si>
+  <si>
+    <t>n006</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/n006</t>
+  </si>
+  <si>
+    <t>n007</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/n007</t>
+  </si>
+  <si>
+    <t>n008</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/n008</t>
+  </si>
+  <si>
+    <t>n009</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/n009</t>
+  </si>
+  <si>
+    <t>n010</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/n010</t>
+  </si>
+  <si>
+    <t>n011</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/n011</t>
+  </si>
+  <si>
+    <t>n012</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/n012</t>
+  </si>
+  <si>
+    <t>n013</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/n013</t>
+  </si>
+  <si>
+    <t>n014</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/n014</t>
+  </si>
+  <si>
+    <t>n015</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/n015</t>
+  </si>
+  <si>
+    <t>n016</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/n016</t>
+  </si>
+  <si>
+    <t>n017</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/n017</t>
+  </si>
+  <si>
+    <t>n018</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/n018</t>
+  </si>
+  <si>
+    <t>n019</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/n019</t>
+  </si>
+  <si>
+    <t>n020</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/n020</t>
+  </si>
+  <si>
+    <t>n021</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/n021</t>
+  </si>
+  <si>
+    <t>n022</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/n022</t>
+  </si>
+  <si>
+    <t>n023</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/n023</t>
+  </si>
+  <si>
+    <t>n024</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/n024</t>
+  </si>
+  <si>
+    <t>n025</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/n025</t>
+  </si>
+  <si>
+    <t>n026</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/n026</t>
+  </si>
+  <si>
+    <t>n027</t>
+  </si>
+  <si>
+    <t>https://dartalexator.github.io/CoinCollection/Links/n027</t>
+  </si>
+  <si>
+    <t>Short ID</t>
+  </si>
+  <si>
+    <t>Num</t>
   </si>
 </sst>
 </file>
@@ -3645,54 +3648,6 @@
   </cellStyles>
   <dxfs count="34">
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -4176,6 +4131,54 @@
         </horizontal>
       </border>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -4244,44 +4247,44 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{973D7237-72C7-453E-A0E1-526C93326B28}" name="Таблица3" displayName="Таблица3" ref="A1:F51" totalsRowShown="0" headerRowDxfId="33" dataDxfId="31" headerRowBorderDxfId="32" tableBorderDxfId="30" totalsRowBorderDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{973D7237-72C7-453E-A0E1-526C93326B28}" name="Таблица3" displayName="Таблица3" ref="A1:F51" totalsRowShown="0" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
   <autoFilter ref="A1:F51" xr:uid="{A2D8FA3D-4024-4365-BE1D-F93D0AF2D426}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{12C2DF0B-47FA-46A4-8424-55A1488EF88B}" name="ID" dataDxfId="28"/>
-    <tableColumn id="2" xr3:uid="{EB0B36CE-168D-429E-896D-DBA54794224F}" name="Name_Eng" dataDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{6C3A2CE8-252E-4C52-985B-8CDDFD9FA0C7}" name="OfficialMintName_Native" dataDxfId="26"/>
-    <tableColumn id="8" xr3:uid="{DA5871DC-2EDB-49C0-953E-EC0F70288E21}" name="Country" dataDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{FCD85F85-A94E-4BBE-9D3B-2B7494638375}" name="Mint_City" dataDxfId="24"/>
-    <tableColumn id="6" xr3:uid="{E5141978-CA91-4DE9-86F1-8A8AFA716534}" name="Alias" dataDxfId="23"/>
+    <tableColumn id="1" xr3:uid="{12C2DF0B-47FA-46A4-8424-55A1488EF88B}" name="ID" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{EB0B36CE-168D-429E-896D-DBA54794224F}" name="Name_Eng" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{6C3A2CE8-252E-4C52-985B-8CDDFD9FA0C7}" name="OfficialMintName_Native" dataDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{DA5871DC-2EDB-49C0-953E-EC0F70288E21}" name="Country" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{FCD85F85-A94E-4BBE-9D3B-2B7494638375}" name="Mint_City" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{E5141978-CA91-4DE9-86F1-8A8AFA716534}" name="Alias" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9D0F8E3D-96B1-4DB8-B1A6-8DD6B84F3693}" name="Таблица35" displayName="Таблица35" ref="A1:D52" totalsRowShown="0" headerRowDxfId="22" dataDxfId="20" headerRowBorderDxfId="21" tableBorderDxfId="19" totalsRowBorderDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9D0F8E3D-96B1-4DB8-B1A6-8DD6B84F3693}" name="Таблица35" displayName="Таблица35" ref="A1:D52" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13" totalsRowBorderDxfId="12">
   <autoFilter ref="A1:D52" xr:uid="{A2D8FA3D-4024-4365-BE1D-F93D0AF2D426}"/>
   <tableColumns count="4">
-    <tableColumn id="4" xr3:uid="{74AFB32D-7AAA-46BE-8174-ED698BB4613E}" name="Mint_id" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{523D65CD-0F56-441F-90B5-E46A9B14F0D0}" name="Ekaterinburg Mint" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{1AAB7352-E935-4EC6-A0D1-3EDC5D0BC93C}" name="Year_of_start" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{5FF15381-476A-4F88-B93A-6452F2830A0A}" name="Year_of_end" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{74AFB32D-7AAA-46BE-8174-ED698BB4613E}" name="Mint_id" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{523D65CD-0F56-441F-90B5-E46A9B14F0D0}" name="Ekaterinburg Mint" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{1AAB7352-E935-4EC6-A0D1-3EDC5D0BC93C}" name="Year_of_start" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{5FF15381-476A-4F88-B93A-6452F2830A0A}" name="Year_of_end" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D0DCC88A-2D36-4004-A694-FC0C0F0C3396}" name="Таблица2" displayName="Таблица2" ref="A1:C16" totalsRowShown="0" headerRowBorderDxfId="13" tableBorderDxfId="12" totalsRowBorderDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D0DCC88A-2D36-4004-A694-FC0C0F0C3396}" name="Таблица2" displayName="Таблица2" ref="A1:C16" totalsRowShown="0" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
   <autoFilter ref="A1:C16" xr:uid="{00000000-0009-0000-0100-000002000000}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{28358E6A-6F3A-468C-9E1C-880A34D9BECE}" name="№" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{28358E6A-6F3A-468C-9E1C-880A34D9BECE}" name="№" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{DD0AD5C8-324B-4DA7-B39F-B2DB3EF91222}" name="Links:"/>
-    <tableColumn id="3" xr3:uid="{FC8A6018-CA7E-4C73-9B21-B272B55FA8C1}" name="Description:" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{FC8A6018-CA7E-4C73-9B21-B272B55FA8C1}" name="Description:" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -4295,9 +4298,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{8354E581-3B48-4762-81A7-EA76E36C4BB5}" name="№" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{1F45DC85-8ECA-45FE-BF45-E528619CEE0E}" name="Links:" dataDxfId="7" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{3FAE616B-3296-4770-9E56-8A824991EECA}" name="Description:" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{8354E581-3B48-4762-81A7-EA76E36C4BB5}" name="№" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{1F45DC85-8ECA-45FE-BF45-E528619CEE0E}" name="Links:" dataDxfId="1" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{3FAE616B-3296-4770-9E56-8A824991EECA}" name="Description:" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -4683,17 +4686,17 @@
         <v>1</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C7:C8">
-    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="33" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C7))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C6">
-    <cfRule type="containsText" dxfId="4" priority="11" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="32" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C6))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4710,7 +4713,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2">
-    <cfRule type="containsText" dxfId="3" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="31" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C2))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4727,7 +4730,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C4">
-    <cfRule type="containsText" dxfId="2" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="30" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C4))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4744,7 +4747,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C5">
-    <cfRule type="containsText" dxfId="1" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="29" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C5))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4761,7 +4764,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3">
-    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="28" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(C3))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -5201,7 +5204,7 @@
   <dimension ref="A1:W31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="4.08984375" customWidth="1"/>
+    <col min="1" max="1" width="9.26953125" customWidth="1"/>
     <col min="2" max="2" width="17.1796875" customWidth="1"/>
     <col min="3" max="3" width="81.08984375" customWidth="1"/>
     <col min="4" max="5" width="8.26953125" customWidth="1"/>
@@ -5209,7 +5212,7 @@
   <sheetData>
     <row r="1" spans="1:23" ht="61.5" x14ac:dyDescent="1.35">
       <c r="A1" s="109" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B1" s="110"/>
       <c r="C1" s="110"/>
@@ -5236,24 +5239,24 @@
     </row>
     <row r="3" spans="1:23" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A3" s="88" t="s">
-        <v>529</v>
+        <v>888</v>
       </c>
       <c r="B3" s="78" t="s">
         <v>395</v>
       </c>
       <c r="C3" s="78" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A4" s="89" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B4" t="s">
         <v>524</v>
       </c>
-      <c r="C4" t="s">
-        <v>861</v>
+      <c r="C4" s="86" t="s">
+        <v>833</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.35">
@@ -5264,293 +5267,293 @@
         <v>523</v>
       </c>
       <c r="C5" t="s">
-        <v>862</v>
+        <v>835</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A6" s="89" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B6" t="s">
         <v>528</v>
       </c>
       <c r="C6" t="s">
-        <v>863</v>
+        <v>837</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A7" s="89" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="B7" t="s">
         <v>520</v>
       </c>
       <c r="C7" t="s">
-        <v>864</v>
+        <v>839</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A8" s="89" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="B8" t="s">
         <v>527</v>
       </c>
       <c r="C8" t="s">
-        <v>865</v>
+        <v>841</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A9" s="89" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="B9" t="s">
         <v>526</v>
       </c>
       <c r="C9" t="s">
-        <v>866</v>
+        <v>843</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A10" s="89" t="s">
-        <v>839</v>
+        <v>844</v>
       </c>
       <c r="B10" t="s">
         <v>525</v>
       </c>
       <c r="C10" t="s">
-        <v>867</v>
+        <v>845</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A11" s="89" t="s">
-        <v>840</v>
+        <v>846</v>
       </c>
       <c r="B11" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C11" t="s">
-        <v>868</v>
+        <v>847</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A12" s="89" t="s">
-        <v>841</v>
+        <v>848</v>
       </c>
       <c r="B12" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C12" t="s">
-        <v>869</v>
+        <v>849</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A13" s="89" t="s">
-        <v>842</v>
+        <v>850</v>
       </c>
       <c r="B13" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C13" t="s">
-        <v>870</v>
+        <v>851</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A14" s="89" t="s">
-        <v>843</v>
+        <v>852</v>
       </c>
       <c r="B14" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C14" t="s">
-        <v>871</v>
+        <v>853</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A15" s="89" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="B15" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C15" t="s">
-        <v>872</v>
+        <v>855</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A16" s="89" t="s">
-        <v>845</v>
+        <v>856</v>
       </c>
       <c r="B16" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C16" t="s">
-        <v>873</v>
+        <v>857</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="89" t="s">
-        <v>846</v>
+        <v>858</v>
       </c>
       <c r="B17" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C17" t="s">
-        <v>874</v>
+        <v>859</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="89" t="s">
-        <v>847</v>
+        <v>860</v>
       </c>
       <c r="B18" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C18" t="s">
-        <v>875</v>
+        <v>861</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="89" t="s">
-        <v>848</v>
+        <v>862</v>
       </c>
       <c r="B19" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C19" t="s">
-        <v>876</v>
+        <v>863</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="89" t="s">
-        <v>849</v>
+        <v>864</v>
       </c>
       <c r="B20" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C20" t="s">
-        <v>877</v>
+        <v>865</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="89" t="s">
-        <v>850</v>
+        <v>866</v>
       </c>
       <c r="B21" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C21" t="s">
-        <v>878</v>
+        <v>867</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="89" t="s">
-        <v>859</v>
+        <v>868</v>
       </c>
       <c r="B22" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C22" t="s">
-        <v>879</v>
+        <v>869</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="89" t="s">
-        <v>860</v>
+        <v>870</v>
       </c>
       <c r="B23" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C23" t="s">
-        <v>880</v>
+        <v>871</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="89" t="s">
-        <v>851</v>
+        <v>872</v>
       </c>
       <c r="B24" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C24" t="s">
-        <v>881</v>
+        <v>873</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="89" t="s">
-        <v>852</v>
+        <v>874</v>
       </c>
       <c r="B25" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="C25" t="s">
-        <v>882</v>
+        <v>875</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="89" t="s">
-        <v>853</v>
+        <v>876</v>
       </c>
       <c r="B26" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="C26" t="s">
-        <v>883</v>
+        <v>877</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="89" t="s">
-        <v>854</v>
+        <v>878</v>
       </c>
       <c r="B27" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="C27" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="89" t="s">
-        <v>855</v>
+        <v>880</v>
       </c>
       <c r="B28" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="C28" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="89" t="s">
-        <v>856</v>
+        <v>882</v>
       </c>
       <c r="B29" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="C29" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="89" t="s">
-        <v>857</v>
+        <v>884</v>
       </c>
       <c r="B30" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="C30" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="89" t="s">
-        <v>858</v>
+        <v>886</v>
       </c>
       <c r="B31" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C31" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
   </sheetData>
@@ -5560,9 +5563,10 @@
   <phoneticPr fontId="18" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="A1" r:id="rId1" xr:uid="{1B51AF5A-9579-4E45-802C-86E0D9768BAB}"/>
+    <hyperlink ref="C4" r:id="rId2" location="000" display="https://dartalexator.github.io/CoinCollection/Links/#000" xr:uid="{31617FEB-1274-4FE6-BFED-687BBBBEEB99}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -5903,7 +5907,7 @@
   <dimension ref="A1:E29"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.26953125" customWidth="1"/>
+    <col min="1" max="1" width="8.90625" customWidth="1"/>
     <col min="2" max="2" width="15.54296875" customWidth="1"/>
     <col min="3" max="3" width="70" customWidth="1"/>
     <col min="4" max="4" width="89.08984375" customWidth="1"/>
@@ -5912,7 +5916,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="78" t="s">
-        <v>529</v>
+        <v>889</v>
       </c>
       <c r="B1" s="78" t="s">
         <v>395</v>
@@ -5924,12 +5928,12 @@
         <v>481</v>
       </c>
       <c r="E1" s="78" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="89" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B2" t="s">
         <v>524</v>
@@ -5941,7 +5945,7 @@
         <v>521</v>
       </c>
       <c r="E2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -5958,12 +5962,12 @@
         <v>501</v>
       </c>
       <c r="E3" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="89" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B4" t="s">
         <v>528</v>
@@ -5975,12 +5979,12 @@
         <v>502</v>
       </c>
       <c r="E4" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="89" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="B5" t="s">
         <v>520</v>
@@ -5992,12 +5996,12 @@
         <v>503</v>
       </c>
       <c r="E5" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="89" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="B6" t="s">
         <v>527</v>
@@ -6009,12 +6013,12 @@
         <v>498</v>
       </c>
       <c r="E6" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="89" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="B7" t="s">
         <v>526</v>
@@ -6026,12 +6030,12 @@
         <v>497</v>
       </c>
       <c r="E7" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="89" t="s">
-        <v>839</v>
+        <v>844</v>
       </c>
       <c r="B8" t="s">
         <v>525</v>
@@ -6043,15 +6047,15 @@
         <v>496</v>
       </c>
       <c r="E8" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="89" t="s">
-        <v>840</v>
+        <v>846</v>
       </c>
       <c r="B9" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C9" t="s">
         <v>499</v>
@@ -6060,15 +6064,15 @@
         <v>507</v>
       </c>
       <c r="E9" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="89" t="s">
-        <v>841</v>
+        <v>848</v>
       </c>
       <c r="B10" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C10" t="s">
         <v>500</v>
@@ -6077,15 +6081,15 @@
         <v>506</v>
       </c>
       <c r="E10" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="89" t="s">
-        <v>842</v>
+        <v>850</v>
       </c>
       <c r="B11" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C11" t="s">
         <v>504</v>
@@ -6094,15 +6098,15 @@
         <v>508</v>
       </c>
       <c r="E11" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="89" t="s">
-        <v>843</v>
+        <v>852</v>
       </c>
       <c r="B12" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C12" t="s">
         <v>505</v>
@@ -6111,15 +6115,15 @@
         <v>509</v>
       </c>
       <c r="E12" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="89" t="s">
-        <v>844</v>
+        <v>854</v>
       </c>
       <c r="B13" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C13" t="s">
         <v>512</v>
@@ -6128,15 +6132,15 @@
         <v>510</v>
       </c>
       <c r="E13" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="89" t="s">
-        <v>845</v>
+        <v>856</v>
       </c>
       <c r="B14" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C14" t="s">
         <v>513</v>
@@ -6145,15 +6149,15 @@
         <v>511</v>
       </c>
       <c r="E14" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="89" t="s">
-        <v>846</v>
+        <v>858</v>
       </c>
       <c r="B15" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C15" t="s">
         <v>516</v>
@@ -6162,15 +6166,15 @@
         <v>518</v>
       </c>
       <c r="E15" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="89" t="s">
-        <v>847</v>
+        <v>860</v>
       </c>
       <c r="B16" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C16" t="s">
         <v>517</v>
@@ -6179,228 +6183,228 @@
         <v>519</v>
       </c>
       <c r="E16" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="89" t="s">
-        <v>848</v>
+        <v>862</v>
       </c>
       <c r="B17" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C17" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D17" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="E17" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="89" t="s">
-        <v>849</v>
+        <v>864</v>
       </c>
       <c r="B18" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C18" t="s">
+        <v>542</v>
+      </c>
+      <c r="D18" t="s">
         <v>543</v>
       </c>
-      <c r="D18" t="s">
-        <v>544</v>
-      </c>
       <c r="E18" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="89" t="s">
-        <v>850</v>
+        <v>866</v>
       </c>
       <c r="B19" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C19" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D19" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E19" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="89" t="s">
-        <v>859</v>
+        <v>868</v>
       </c>
       <c r="B20" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C20" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D20" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E20" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="89" t="s">
-        <v>860</v>
+        <v>870</v>
       </c>
       <c r="B21" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C21" t="s">
+        <v>582</v>
+      </c>
+      <c r="D21" t="s">
+        <v>579</v>
+      </c>
+      <c r="E21" t="s">
         <v>583</v>
-      </c>
-      <c r="D21" t="s">
-        <v>580</v>
-      </c>
-      <c r="E21" t="s">
-        <v>584</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="89" t="s">
-        <v>851</v>
+        <v>872</v>
       </c>
       <c r="B22" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C22" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D22" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E22" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="89" t="s">
-        <v>852</v>
+        <v>874</v>
       </c>
       <c r="B23" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="C23" t="s">
+        <v>553</v>
+      </c>
+      <c r="D23" t="s">
         <v>554</v>
       </c>
-      <c r="D23" t="s">
-        <v>555</v>
-      </c>
       <c r="E23" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="89" t="s">
-        <v>853</v>
+        <v>876</v>
       </c>
       <c r="B24" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="C24" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D24" t="s">
+        <v>586</v>
+      </c>
+      <c r="E24" t="s">
         <v>587</v>
-      </c>
-      <c r="E24" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="89" t="s">
-        <v>854</v>
+        <v>878</v>
       </c>
       <c r="B25" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="C25" t="s">
+        <v>589</v>
+      </c>
+      <c r="D25" t="s">
+        <v>588</v>
+      </c>
+      <c r="E25" t="s">
         <v>590</v>
-      </c>
-      <c r="D25" t="s">
-        <v>589</v>
-      </c>
-      <c r="E25" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="89" t="s">
-        <v>855</v>
+        <v>880</v>
       </c>
       <c r="B26" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="C26" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="D26" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="E26" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="89" t="s">
-        <v>856</v>
+        <v>882</v>
       </c>
       <c r="B27" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="C27" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="D27" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="E27" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="89" t="s">
-        <v>857</v>
+        <v>884</v>
       </c>
       <c r="B28" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="C28" t="s">
+        <v>817</v>
+      </c>
+      <c r="D28" t="s">
+        <v>816</v>
+      </c>
+      <c r="E28" t="s">
         <v>818</v>
-      </c>
-      <c r="D28" t="s">
-        <v>817</v>
-      </c>
-      <c r="E28" t="s">
-        <v>819</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="89" t="s">
-        <v>858</v>
+        <v>886</v>
       </c>
       <c r="B29" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C29" t="s">
+        <v>819</v>
+      </c>
+      <c r="D29" t="s">
         <v>820</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>821</v>
-      </c>
-      <c r="E29" t="s">
-        <v>822</v>
       </c>
     </row>
   </sheetData>
@@ -6426,19 +6430,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>592</v>
+      </c>
+      <c r="B1" t="s">
         <v>593</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>594</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>595</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>596</v>
-      </c>
-      <c r="E1" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -6446,16 +6450,16 @@
         <v>524</v>
       </c>
       <c r="B2" s="86" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D2" s="86" t="s">
         <v>642</v>
       </c>
-      <c r="D2" s="86" t="s">
+      <c r="E2" s="86" t="s">
         <v>643</v>
-      </c>
-      <c r="E2" s="86" t="s">
-        <v>644</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -6463,16 +6467,16 @@
         <v>524</v>
       </c>
       <c r="B3" s="86" t="s">
+        <v>645</v>
+      </c>
+      <c r="C3" t="s">
         <v>646</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" s="86" t="s">
         <v>647</v>
       </c>
-      <c r="D3" s="86" t="s">
+      <c r="E3" s="86" t="s">
         <v>648</v>
-      </c>
-      <c r="E3" s="86" t="s">
-        <v>649</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -6480,16 +6484,16 @@
         <v>523</v>
       </c>
       <c r="B4" s="86" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C4" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="D4" s="86" t="s">
+        <v>597</v>
+      </c>
+      <c r="E4" s="86" t="s">
         <v>598</v>
-      </c>
-      <c r="E4" s="86" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -6497,16 +6501,16 @@
         <v>523</v>
       </c>
       <c r="B5" s="86" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C5" t="s">
+        <v>601</v>
+      </c>
+      <c r="D5" s="86" t="s">
+        <v>600</v>
+      </c>
+      <c r="E5" s="86" t="s">
         <v>602</v>
-      </c>
-      <c r="D5" s="86" t="s">
-        <v>601</v>
-      </c>
-      <c r="E5" s="86" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
@@ -6514,16 +6518,16 @@
         <v>523</v>
       </c>
       <c r="B6" s="86" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C6" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="D6" s="86" t="s">
+        <v>603</v>
+      </c>
+      <c r="E6" s="86" t="s">
         <v>604</v>
-      </c>
-      <c r="E6" s="86" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
@@ -6531,16 +6535,16 @@
         <v>523</v>
       </c>
       <c r="B7" s="86" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C7" t="s">
+        <v>607</v>
+      </c>
+      <c r="D7" s="86" t="s">
+        <v>606</v>
+      </c>
+      <c r="E7" s="86" t="s">
         <v>608</v>
-      </c>
-      <c r="D7" s="86" t="s">
-        <v>607</v>
-      </c>
-      <c r="E7" s="86" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -6548,16 +6552,16 @@
         <v>523</v>
       </c>
       <c r="B8" s="86" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C8" t="s">
+        <v>610</v>
+      </c>
+      <c r="D8" s="86" t="s">
+        <v>609</v>
+      </c>
+      <c r="E8" s="86" t="s">
         <v>611</v>
-      </c>
-      <c r="D8" s="86" t="s">
-        <v>610</v>
-      </c>
-      <c r="E8" s="86" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -6565,16 +6569,16 @@
         <v>523</v>
       </c>
       <c r="B9" s="86" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C9" t="s">
+        <v>613</v>
+      </c>
+      <c r="D9" s="86" t="s">
+        <v>612</v>
+      </c>
+      <c r="E9" s="86" t="s">
         <v>614</v>
-      </c>
-      <c r="D9" s="86" t="s">
-        <v>613</v>
-      </c>
-      <c r="E9" s="86" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -6582,16 +6586,16 @@
         <v>523</v>
       </c>
       <c r="B10" s="86" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C10" t="s">
+        <v>616</v>
+      </c>
+      <c r="D10" s="86" t="s">
+        <v>615</v>
+      </c>
+      <c r="E10" s="86" t="s">
         <v>617</v>
-      </c>
-      <c r="D10" s="86" t="s">
-        <v>616</v>
-      </c>
-      <c r="E10" s="86" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -6599,16 +6603,16 @@
         <v>523</v>
       </c>
       <c r="B11" s="86" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C11" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="D11" s="86" t="s">
+        <v>618</v>
+      </c>
+      <c r="E11" s="86" t="s">
         <v>619</v>
-      </c>
-      <c r="E11" s="86" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -6616,16 +6620,16 @@
         <v>523</v>
       </c>
       <c r="B12" s="86" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C12" t="s">
+        <v>622</v>
+      </c>
+      <c r="D12" s="86" t="s">
+        <v>621</v>
+      </c>
+      <c r="E12" s="86" t="s">
         <v>623</v>
-      </c>
-      <c r="D12" s="86" t="s">
-        <v>622</v>
-      </c>
-      <c r="E12" s="86" t="s">
-        <v>624</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -6633,16 +6637,16 @@
         <v>523</v>
       </c>
       <c r="B13" s="86" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C13" t="s">
+        <v>625</v>
+      </c>
+      <c r="D13" s="86" t="s">
+        <v>624</v>
+      </c>
+      <c r="E13" s="86" t="s">
         <v>626</v>
-      </c>
-      <c r="D13" s="86" t="s">
-        <v>625</v>
-      </c>
-      <c r="E13" s="86" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
@@ -6650,16 +6654,16 @@
         <v>523</v>
       </c>
       <c r="B14" s="86" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C14" t="s">
+        <v>628</v>
+      </c>
+      <c r="D14" s="86" t="s">
+        <v>627</v>
+      </c>
+      <c r="E14" s="86" t="s">
         <v>629</v>
-      </c>
-      <c r="D14" s="86" t="s">
-        <v>628</v>
-      </c>
-      <c r="E14" s="86" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
@@ -6667,16 +6671,16 @@
         <v>528</v>
       </c>
       <c r="B15" s="86" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C15" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D15" s="86" t="s">
+        <v>649</v>
+      </c>
+      <c r="E15" s="86" t="s">
         <v>650</v>
-      </c>
-      <c r="E15" s="86" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
@@ -6684,16 +6688,16 @@
         <v>528</v>
       </c>
       <c r="B16" s="86" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C16" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D16" s="86" t="s">
+        <v>653</v>
+      </c>
+      <c r="E16" s="86" t="s">
         <v>654</v>
-      </c>
-      <c r="E16" s="86" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
@@ -6701,16 +6705,16 @@
         <v>528</v>
       </c>
       <c r="B17" s="86" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C17" t="s">
+        <v>657</v>
+      </c>
+      <c r="D17" s="86" t="s">
         <v>658</v>
       </c>
-      <c r="D17" s="86" t="s">
+      <c r="E17" s="86" t="s">
         <v>659</v>
-      </c>
-      <c r="E17" s="86" t="s">
-        <v>660</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
@@ -6718,16 +6722,16 @@
         <v>520</v>
       </c>
       <c r="B18" s="86" t="s">
+        <v>661</v>
+      </c>
+      <c r="C18" t="s">
         <v>662</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" s="86" t="s">
         <v>663</v>
       </c>
-      <c r="D18" s="86" t="s">
+      <c r="E18" s="86" t="s">
         <v>664</v>
-      </c>
-      <c r="E18" s="86" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
@@ -6735,16 +6739,16 @@
         <v>520</v>
       </c>
       <c r="B19" s="86" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C19" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D19" s="86" t="s">
+        <v>665</v>
+      </c>
+      <c r="E19" s="86" t="s">
         <v>666</v>
-      </c>
-      <c r="E19" s="86" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
@@ -6752,16 +6756,16 @@
         <v>520</v>
       </c>
       <c r="B20" s="86" t="s">
+        <v>669</v>
+      </c>
+      <c r="C20" t="s">
         <v>670</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" s="86" t="s">
         <v>671</v>
       </c>
-      <c r="D20" s="86" t="s">
+      <c r="E20" s="86" t="s">
         <v>672</v>
-      </c>
-      <c r="E20" s="86" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
@@ -6769,16 +6773,16 @@
         <v>527</v>
       </c>
       <c r="B21" s="86" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C21" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="D21" s="86" t="s">
+        <v>673</v>
+      </c>
+      <c r="E21" s="86" t="s">
         <v>674</v>
-      </c>
-      <c r="E21" s="86" t="s">
-        <v>675</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
@@ -6786,16 +6790,16 @@
         <v>527</v>
       </c>
       <c r="B22" s="86" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C22" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D22" s="86" t="s">
+        <v>677</v>
+      </c>
+      <c r="E22" s="86" t="s">
         <v>678</v>
-      </c>
-      <c r="E22" s="86" t="s">
-        <v>679</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
@@ -6803,16 +6807,16 @@
         <v>527</v>
       </c>
       <c r="B23" s="86" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C23" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="D23" s="86" t="s">
+        <v>681</v>
+      </c>
+      <c r="E23" s="86" t="s">
         <v>682</v>
-      </c>
-      <c r="E23" s="86" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
@@ -6820,16 +6824,16 @@
         <v>527</v>
       </c>
       <c r="B24" s="86" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C24" t="s">
+        <v>686</v>
+      </c>
+      <c r="D24" s="86" t="s">
+        <v>685</v>
+      </c>
+      <c r="E24" s="86" t="s">
         <v>687</v>
-      </c>
-      <c r="D24" s="86" t="s">
-        <v>686</v>
-      </c>
-      <c r="E24" s="86" t="s">
-        <v>688</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
@@ -6837,16 +6841,16 @@
         <v>527</v>
       </c>
       <c r="B25" s="86" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C25" t="s">
+        <v>690</v>
+      </c>
+      <c r="D25" s="86" t="s">
+        <v>689</v>
+      </c>
+      <c r="E25" s="86" t="s">
         <v>691</v>
-      </c>
-      <c r="D25" s="86" t="s">
-        <v>690</v>
-      </c>
-      <c r="E25" s="86" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
@@ -6854,16 +6858,16 @@
         <v>527</v>
       </c>
       <c r="B26" s="86" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C26" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="D26" s="86" t="s">
+        <v>693</v>
+      </c>
+      <c r="E26" s="86" t="s">
         <v>694</v>
-      </c>
-      <c r="E26" s="86" t="s">
-        <v>695</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
@@ -6871,7 +6875,7 @@
         <v>526</v>
       </c>
       <c r="C27" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
@@ -6879,979 +6883,979 @@
         <v>525</v>
       </c>
       <c r="C28" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B29" s="86" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="C29" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D29" s="86" t="s">
+        <v>698</v>
+      </c>
+      <c r="E29" s="86" t="s">
         <v>699</v>
-      </c>
-      <c r="E29" s="86" t="s">
-        <v>700</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B30" s="86" t="s">
+        <v>701</v>
+      </c>
+      <c r="C30" t="s">
         <v>702</v>
       </c>
-      <c r="C30" t="s">
-        <v>703</v>
-      </c>
       <c r="D30" s="86" t="s">
+        <v>698</v>
+      </c>
+      <c r="E30" s="86" t="s">
         <v>699</v>
-      </c>
-      <c r="E30" s="86" t="s">
-        <v>700</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B31" s="86" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C31" t="s">
         <v>508</v>
       </c>
       <c r="D31" s="86" t="s">
+        <v>703</v>
+      </c>
+      <c r="E31" s="86" t="s">
         <v>704</v>
-      </c>
-      <c r="E31" s="86" t="s">
-        <v>705</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B32" s="86" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C32" t="s">
         <v>509</v>
       </c>
       <c r="D32" s="86" t="s">
+        <v>703</v>
+      </c>
+      <c r="E32" s="86" t="s">
         <v>704</v>
-      </c>
-      <c r="E32" s="86" t="s">
-        <v>705</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B33" s="86" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C33" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="D33" s="86" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="E33" s="86" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B34" s="86" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C34" t="s">
+        <v>601</v>
+      </c>
+      <c r="D34" s="86" t="s">
+        <v>707</v>
+      </c>
+      <c r="E34" s="86" t="s">
         <v>602</v>
-      </c>
-      <c r="D34" s="86" t="s">
-        <v>708</v>
-      </c>
-      <c r="E34" s="86" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B35" s="86" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="C35" t="s">
+        <v>708</v>
+      </c>
+      <c r="D35" s="86" t="s">
         <v>709</v>
       </c>
-      <c r="D35" s="86" t="s">
+      <c r="E35" s="86" t="s">
         <v>710</v>
-      </c>
-      <c r="E35" s="86" t="s">
-        <v>711</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B36" s="86" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C36" t="s">
+        <v>690</v>
+      </c>
+      <c r="D36" s="86" t="s">
+        <v>712</v>
+      </c>
+      <c r="E36" s="86" t="s">
         <v>691</v>
-      </c>
-      <c r="D36" s="86" t="s">
-        <v>713</v>
-      </c>
-      <c r="E36" s="86" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B37" s="86" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C37" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="D37" s="86" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E37" s="86" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B38" s="86" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C38" t="s">
+        <v>607</v>
+      </c>
+      <c r="D38" s="86" t="s">
+        <v>714</v>
+      </c>
+      <c r="E38" s="86" t="s">
         <v>608</v>
-      </c>
-      <c r="D38" s="86" t="s">
-        <v>715</v>
-      </c>
-      <c r="E38" s="86" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B39" s="86" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C39" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="D39" s="86" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="E39" s="86" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B40" s="86" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C40" t="s">
+        <v>610</v>
+      </c>
+      <c r="D40" s="86" t="s">
+        <v>716</v>
+      </c>
+      <c r="E40" s="86" t="s">
         <v>611</v>
-      </c>
-      <c r="D40" s="86" t="s">
-        <v>717</v>
-      </c>
-      <c r="E40" s="86" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B41" s="86" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C41" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D41" s="86" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="E41" s="86" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B42" s="86" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C42" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="D42" s="86" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="E42" s="86" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B43" s="86" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C43" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="D43" s="86" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E43" s="86" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B44" s="86" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C44" t="s">
+        <v>613</v>
+      </c>
+      <c r="D44" s="86" t="s">
+        <v>720</v>
+      </c>
+      <c r="E44" s="86" t="s">
         <v>614</v>
-      </c>
-      <c r="D44" s="86" t="s">
-        <v>721</v>
-      </c>
-      <c r="E44" s="86" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B45" s="86" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C45" t="s">
+        <v>616</v>
+      </c>
+      <c r="D45" s="86" t="s">
+        <v>721</v>
+      </c>
+      <c r="E45" s="86" t="s">
         <v>617</v>
-      </c>
-      <c r="D45" s="86" t="s">
-        <v>722</v>
-      </c>
-      <c r="E45" s="86" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B46" s="86" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C46" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D46" s="86" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="E46" s="86" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B47" s="86" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C47" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="D47" s="83" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E47" s="86" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B48" s="86" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C48" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D48" s="86" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E48" s="86" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B49" s="86" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C49" t="s">
+        <v>625</v>
+      </c>
+      <c r="D49" s="86" t="s">
+        <v>726</v>
+      </c>
+      <c r="E49" s="86" t="s">
         <v>626</v>
-      </c>
-      <c r="D49" s="86" t="s">
-        <v>727</v>
-      </c>
-      <c r="E49" s="86" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B50" s="86" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C50" t="s">
+        <v>628</v>
+      </c>
+      <c r="D50" s="86" t="s">
+        <v>727</v>
+      </c>
+      <c r="E50" s="86" t="s">
         <v>629</v>
-      </c>
-      <c r="D50" s="86" t="s">
-        <v>728</v>
-      </c>
-      <c r="E50" s="86" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B51" s="86" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C51" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D51" s="86" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E51" s="86" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B52" s="86" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C52" t="s">
+        <v>686</v>
+      </c>
+      <c r="D52" s="86" t="s">
+        <v>729</v>
+      </c>
+      <c r="E52" s="86" t="s">
         <v>687</v>
-      </c>
-      <c r="D52" s="86" t="s">
-        <v>730</v>
-      </c>
-      <c r="E52" s="86" t="s">
-        <v>688</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B53" s="86" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C53" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D53" s="86" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E53" s="86" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B54" s="86" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C54" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D54" s="86" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="E54" s="86" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B55" s="86" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C55" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D55" s="86" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="E55" s="86" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B56" s="86" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C56" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="D56" s="86" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="E56" s="86" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B57" s="86" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C57" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="D57" s="86" t="s">
+        <v>703</v>
+      </c>
+      <c r="E57" s="86" t="s">
         <v>704</v>
-      </c>
-      <c r="E57" s="86" t="s">
-        <v>705</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B58" s="86" t="s">
+        <v>737</v>
+      </c>
+      <c r="C58" t="s">
         <v>738</v>
       </c>
-      <c r="C58" t="s">
+      <c r="D58" s="86" t="s">
         <v>739</v>
       </c>
-      <c r="D58" s="86" t="s">
-        <v>740</v>
-      </c>
       <c r="E58" s="86" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B59" s="86" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C59" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D59" s="86" t="s">
+        <v>740</v>
+      </c>
+      <c r="E59" s="86" t="s">
         <v>741</v>
-      </c>
-      <c r="E59" s="86" t="s">
-        <v>742</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B60" s="86" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C60" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="D60" s="86" t="s">
+        <v>742</v>
+      </c>
+      <c r="E60" s="86" t="s">
         <v>743</v>
-      </c>
-      <c r="E60" s="86" t="s">
-        <v>744</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B61" s="86" t="s">
+        <v>745</v>
+      </c>
+      <c r="C61" t="s">
         <v>746</v>
       </c>
-      <c r="C61" t="s">
+      <c r="D61" s="86" t="s">
         <v>747</v>
       </c>
-      <c r="D61" s="86" t="s">
-        <v>748</v>
-      </c>
       <c r="E61" s="86" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B62" s="86" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C62" t="s">
+        <v>793</v>
+      </c>
+      <c r="D62" s="86" t="s">
         <v>794</v>
       </c>
-      <c r="D62" s="86" t="s">
-        <v>795</v>
-      </c>
       <c r="E62" s="86" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B63" s="86" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C63" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D63" s="86" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="E63" s="86" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B64" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C64" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B65" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="C65" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B66" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="C66" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B67" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="C67" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B68" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="C68" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B69" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="C69" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B70" t="s">
+        <v>806</v>
+      </c>
+      <c r="C70" t="s">
         <v>807</v>
-      </c>
-      <c r="C70" t="s">
-        <v>808</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B71" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="C71" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B72" s="86" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C72" t="s">
+        <v>749</v>
+      </c>
+      <c r="D72" s="86" t="s">
+        <v>748</v>
+      </c>
+      <c r="E72" s="86" t="s">
         <v>750</v>
-      </c>
-      <c r="D72" s="86" t="s">
-        <v>749</v>
-      </c>
-      <c r="E72" s="86" t="s">
-        <v>751</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B73" s="86" t="s">
+        <v>751</v>
+      </c>
+      <c r="C73" t="s">
+        <v>753</v>
+      </c>
+      <c r="D73" s="86" t="s">
         <v>752</v>
       </c>
-      <c r="C73" t="s">
-        <v>754</v>
-      </c>
-      <c r="D73" s="86" t="s">
-        <v>753</v>
-      </c>
       <c r="E73" s="86" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B74" s="86" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C74" t="s">
+        <v>773</v>
+      </c>
+      <c r="D74" s="86" t="s">
+        <v>772</v>
+      </c>
+      <c r="E74" s="86" t="s">
         <v>774</v>
-      </c>
-      <c r="D74" s="86" t="s">
-        <v>773</v>
-      </c>
-      <c r="E74" s="86" t="s">
-        <v>775</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B75" s="86" t="s">
+        <v>775</v>
+      </c>
+      <c r="C75" t="s">
         <v>776</v>
       </c>
-      <c r="C75" t="s">
+      <c r="D75" s="86" t="s">
         <v>777</v>
       </c>
-      <c r="D75" s="86" t="s">
-        <v>778</v>
-      </c>
       <c r="E75" s="86" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B76" s="86" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C76" t="s">
+        <v>755</v>
+      </c>
+      <c r="D76" s="86" t="s">
+        <v>754</v>
+      </c>
+      <c r="E76" s="86" t="s">
         <v>756</v>
-      </c>
-      <c r="D76" s="86" t="s">
-        <v>755</v>
-      </c>
-      <c r="E76" s="86" t="s">
-        <v>757</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B77" s="86" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C77" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D77" s="86" t="s">
+        <v>758</v>
+      </c>
+      <c r="E77" s="86" t="s">
         <v>759</v>
-      </c>
-      <c r="E77" s="86" t="s">
-        <v>760</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B78" s="86" t="s">
+        <v>760</v>
+      </c>
+      <c r="C78" t="s">
+        <v>763</v>
+      </c>
+      <c r="D78" s="86" t="s">
         <v>761</v>
       </c>
-      <c r="C78" t="s">
-        <v>764</v>
-      </c>
-      <c r="D78" s="86" t="s">
-        <v>762</v>
-      </c>
       <c r="E78" s="86" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B79" s="86" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C79" t="s">
+        <v>811</v>
+      </c>
+      <c r="D79" s="86" t="s">
         <v>812</v>
       </c>
-      <c r="D79" s="86" t="s">
-        <v>813</v>
-      </c>
       <c r="E79" s="86" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B80" s="86" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C80" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="D80" s="86" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="E80" s="86" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B81" s="86" t="s">
+        <v>769</v>
+      </c>
+      <c r="C81" t="s">
         <v>770</v>
       </c>
-      <c r="C81" t="s">
+      <c r="D81" s="86" t="s">
         <v>771</v>
       </c>
-      <c r="D81" s="86" t="s">
-        <v>772</v>
-      </c>
       <c r="E81" s="86" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B82" s="86" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C82" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D82" s="86" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="E82" s="86" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B83" s="86" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C83" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="D83" s="86" t="s">
+        <v>778</v>
+      </c>
+      <c r="E83" s="86" t="s">
         <v>779</v>
-      </c>
-      <c r="E83" s="86" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B84" s="86" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="C84" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="D84" s="86" t="s">
+        <v>778</v>
+      </c>
+      <c r="E84" s="86" t="s">
         <v>779</v>
-      </c>
-      <c r="E84" s="86" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B85" s="86" t="s">
+        <v>783</v>
+      </c>
+      <c r="C85" t="s">
         <v>784</v>
       </c>
-      <c r="C85" t="s">
-        <v>785</v>
-      </c>
       <c r="D85" s="86" t="s">
+        <v>778</v>
+      </c>
+      <c r="E85" s="86" t="s">
         <v>779</v>
-      </c>
-      <c r="E85" s="86" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B86" s="86" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C86" t="s">
+        <v>785</v>
+      </c>
+      <c r="D86" s="86" t="s">
         <v>786</v>
       </c>
-      <c r="D86" s="86" t="s">
-        <v>787</v>
-      </c>
       <c r="E86" s="86" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B87" s="86" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="C87" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D87" s="86" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="E87" s="86" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B88" s="86" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C88" t="s">
+        <v>791</v>
+      </c>
+      <c r="D88" s="86" t="s">
         <v>792</v>
       </c>
-      <c r="D88" s="86" t="s">
-        <v>793</v>
-      </c>
       <c r="E88" s="86" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
   </sheetData>
@@ -8185,10 +8189,10 @@
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5" s="85" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B5" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C5" s="73" t="s">
         <v>142</v>
@@ -8261,10 +8265,10 @@
     </row>
     <row r="10" spans="1:25" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C10" s="84" t="s">
+        <v>539</v>
+      </c>
+      <c r="D10" t="s">
         <v>540</v>
-      </c>
-      <c r="D10" t="s">
-        <v>541</v>
       </c>
       <c r="W10" s="81" t="s">
         <v>480</v>
@@ -8286,10 +8290,10 @@
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.35">
       <c r="C12" s="73" t="s">
+        <v>546</v>
+      </c>
+      <c r="D12" t="s">
         <v>547</v>
-      </c>
-      <c r="D12" t="s">
-        <v>548</v>
       </c>
       <c r="X12" s="79" t="s">
         <v>412</v>
@@ -8300,10 +8304,10 @@
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.35">
       <c r="C13" s="84" t="s">
+        <v>548</v>
+      </c>
+      <c r="D13" t="s">
         <v>549</v>
-      </c>
-      <c r="D13" t="s">
-        <v>550</v>
       </c>
       <c r="X13" s="79" t="s">
         <v>413</v>
@@ -8314,10 +8318,10 @@
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.35">
       <c r="C14" s="85" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D14" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="X14" s="79" t="s">
         <v>414</v>

--- a/Info/Additional_information.xlsx
+++ b/Info/Additional_information.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D995C7D-5206-4A69-AA69-5CA952D3B75F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4512A1A4-9655-40A7-8AB9-6F0BA12A83C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Colours_specifications" sheetId="1" r:id="rId1"/>
@@ -6421,7 +6421,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.36328125" customWidth="1"/>
-    <col min="2" max="2" width="57.54296875" customWidth="1"/>
+    <col min="2" max="2" width="80" customWidth="1"/>
     <col min="3" max="3" width="62.26953125" customWidth="1"/>
     <col min="4" max="4" width="151" customWidth="1"/>
     <col min="5" max="5" width="79.54296875" customWidth="1"/>
@@ -7316,7 +7316,7 @@
         <v>535</v>
       </c>
       <c r="B54" s="86" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="C54" t="s">
         <v>732</v>
@@ -7333,7 +7333,7 @@
         <v>536</v>
       </c>
       <c r="B55" s="86" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="C55" t="s">
         <v>733</v>
@@ -8012,85 +8012,85 @@
     <hyperlink ref="E53" r:id="rId149" xr:uid="{C4B2FB7C-D751-4BE4-B80D-1D19FB599067}"/>
     <hyperlink ref="B53" r:id="rId150" xr:uid="{C0A87CF5-0CDC-43C5-AD74-D08EADAD4ECE}"/>
     <hyperlink ref="D54" r:id="rId151" xr:uid="{321A9243-4B72-4C19-9CD1-9199FDFCF2E6}"/>
-    <hyperlink ref="B54" r:id="rId152" xr:uid="{26D7EF60-C714-4FD5-AC80-9248C6C665B5}"/>
-    <hyperlink ref="B55" r:id="rId153" xr:uid="{A57736B4-6732-46D4-8BC8-7C32525F98D6}"/>
-    <hyperlink ref="D55" r:id="rId154" xr:uid="{1B3BEB40-1EE5-404E-8CDC-AA9B3E1B0947}"/>
-    <hyperlink ref="E54" r:id="rId155" xr:uid="{EE68E9AD-2777-4231-AEE5-D934B4B626AB}"/>
-    <hyperlink ref="E55" r:id="rId156" xr:uid="{53BCCA0C-6DBE-4C35-8C04-CFBF70FA60F2}"/>
-    <hyperlink ref="D56" r:id="rId157" xr:uid="{9AA71A7E-44B8-470A-B313-862336B7F5A5}"/>
-    <hyperlink ref="E56" r:id="rId158" xr:uid="{585DECC9-3251-4499-892F-F9240A7EE776}"/>
-    <hyperlink ref="B56" r:id="rId159" xr:uid="{A373CF1C-3A6E-486F-B517-2C8792E95129}"/>
-    <hyperlink ref="D57" r:id="rId160" xr:uid="{F9CF8130-800A-487B-BFCE-4909473DADC4}"/>
-    <hyperlink ref="E57" r:id="rId161" xr:uid="{958AAFCE-E6FF-49DB-85E6-FEE7FAC835F5}"/>
-    <hyperlink ref="B57" r:id="rId162" xr:uid="{DCDF3C10-E8F4-45FB-B43E-916B3077418F}"/>
-    <hyperlink ref="B58" r:id="rId163" xr:uid="{9660E1B0-262B-4C02-B474-D0382995C450}"/>
-    <hyperlink ref="D58" r:id="rId164" xr:uid="{919F2C2C-62F0-4C8A-9785-233396A60613}"/>
-    <hyperlink ref="E58" r:id="rId165" xr:uid="{1E52A1A8-4704-4A25-8CEC-F89177A70432}"/>
-    <hyperlink ref="D59" r:id="rId166" xr:uid="{707A19C4-4FA3-438C-B15B-93A62BA351CF}"/>
-    <hyperlink ref="E59" r:id="rId167" xr:uid="{2443E35E-BC71-4101-8147-FA7277B1A04D}"/>
-    <hyperlink ref="B59" r:id="rId168" xr:uid="{597780D5-57AF-44E3-BC1D-DF5DF0B564E3}"/>
-    <hyperlink ref="D60" r:id="rId169" xr:uid="{9957E43F-25F9-4AD6-AF02-3042376D2CBC}"/>
-    <hyperlink ref="E60" r:id="rId170" xr:uid="{0A83859D-98FA-4037-A2BE-FA8F7CBE6E46}"/>
-    <hyperlink ref="B60" r:id="rId171" xr:uid="{2A7D74A8-8B5D-46CE-9350-0FAC4655511B}"/>
-    <hyperlink ref="D61" r:id="rId172" xr:uid="{0E22EB11-B3F4-4B3D-9949-5BB47BE472FF}"/>
-    <hyperlink ref="E61" r:id="rId173" xr:uid="{203E2512-19F8-444F-B5FE-FCEFA21380D9}"/>
-    <hyperlink ref="B61" r:id="rId174" xr:uid="{D42B148C-2E41-45DC-9406-03F899255054}"/>
-    <hyperlink ref="D72" r:id="rId175" xr:uid="{E8A08F00-2B07-41D3-BECA-92E437337767}"/>
-    <hyperlink ref="E72" r:id="rId176" xr:uid="{CC57E1D3-F163-4C30-A8C6-CA03AA34248D}"/>
-    <hyperlink ref="B72" r:id="rId177" xr:uid="{758C4E99-7187-45B3-B96E-4E1A344950BB}"/>
-    <hyperlink ref="D73" r:id="rId178" xr:uid="{8D6FE8C4-9089-409E-AC71-07A6BA994DD8}"/>
-    <hyperlink ref="E73" r:id="rId179" xr:uid="{C0915D43-2F9A-44CA-AA9B-2D6F571A6531}"/>
-    <hyperlink ref="B73" r:id="rId180" xr:uid="{BD35CE35-8B49-4F57-A541-E8AB4942E01C}"/>
-    <hyperlink ref="D76" r:id="rId181" xr:uid="{AD3B2EB4-61E6-4EC2-B841-C66ABAF57A8D}"/>
-    <hyperlink ref="E76" r:id="rId182" xr:uid="{CA19CD5B-D261-46F6-A06C-A6DD329847C8}"/>
-    <hyperlink ref="B76" r:id="rId183" xr:uid="{902A512C-7DB9-483B-922E-9EC9EB0A5727}"/>
-    <hyperlink ref="D77" r:id="rId184" xr:uid="{D37A5DB7-6170-4DB3-A6C4-6B7C3536BB6A}"/>
-    <hyperlink ref="E77" r:id="rId185" xr:uid="{5BE49E4F-CE72-4598-A298-9EA3583C9BB4}"/>
-    <hyperlink ref="B77" r:id="rId186" xr:uid="{218FE68B-E3EA-48FD-B04F-F05EC4D04342}"/>
-    <hyperlink ref="D78" r:id="rId187" xr:uid="{55D0245C-636D-41C8-8BEA-F7465FDF2FC1}"/>
-    <hyperlink ref="E78" r:id="rId188" xr:uid="{745BE301-751B-44AD-BB23-64393F55A01A}"/>
-    <hyperlink ref="B78" r:id="rId189" xr:uid="{72E099E5-D9E8-43F6-BA7B-AD0788C8ACDF}"/>
-    <hyperlink ref="D82" r:id="rId190" xr:uid="{670FA2F5-7537-44F0-A891-BC8F9FB0FDA1}"/>
-    <hyperlink ref="E82" r:id="rId191" xr:uid="{C44FBCC9-F7D2-411F-B321-7ACCA7BDB113}"/>
-    <hyperlink ref="B82" r:id="rId192" xr:uid="{7AAC8125-2903-4BEF-861C-0652EB8A1EBA}"/>
-    <hyperlink ref="D80" r:id="rId193" xr:uid="{4247E04D-3AB7-4CE4-8D6E-225BEB05B2EC}"/>
-    <hyperlink ref="E80" r:id="rId194" xr:uid="{3F6A67C6-2350-4E0B-855A-7A0CA546CADA}"/>
-    <hyperlink ref="B80" r:id="rId195" xr:uid="{EDAF1894-D1E3-4CB7-A453-D26D0CE785FC}"/>
-    <hyperlink ref="B81" r:id="rId196" xr:uid="{60D8C8EA-A2CC-4EC4-93CF-D8C6F9145025}"/>
-    <hyperlink ref="D81" r:id="rId197" xr:uid="{F6B676D4-F9FF-4FAC-BF4F-6B297B8E4386}"/>
-    <hyperlink ref="E81" r:id="rId198" xr:uid="{AD04D2E5-748B-41B8-A77F-6FE55DE52558}"/>
-    <hyperlink ref="D74" r:id="rId199" xr:uid="{2919C844-F24C-4EBC-BBC0-393934ACE57D}"/>
-    <hyperlink ref="E74" r:id="rId200" xr:uid="{16E264FE-A51B-4307-BAC2-77D48753B271}"/>
-    <hyperlink ref="D75" r:id="rId201" xr:uid="{923213AD-4D4E-456F-B24C-29D5EE8D2DC5}"/>
-    <hyperlink ref="E75" r:id="rId202" xr:uid="{0FB2A237-55E7-482E-BFDD-773D6CA63339}"/>
-    <hyperlink ref="D83" r:id="rId203" xr:uid="{0FB5C72B-F07D-4BAE-8F9A-333776CD5938}"/>
-    <hyperlink ref="E83" r:id="rId204" xr:uid="{1E54D0E6-426F-4655-B12E-6919FDCF820A}"/>
-    <hyperlink ref="B75" r:id="rId205" xr:uid="{6F4BDAA6-1768-40E1-BA7A-3A7B8F3E9DDF}"/>
-    <hyperlink ref="B83" r:id="rId206" xr:uid="{EBBCEFF8-5BDF-4051-A5A6-449AB5359B3C}"/>
-    <hyperlink ref="E84" r:id="rId207" xr:uid="{BE30CFAC-63AD-4E25-9DE4-2BF7C9B898E5}"/>
-    <hyperlink ref="D84" r:id="rId208" xr:uid="{3A9183DE-FD11-4043-B1A6-6E9E780E188A}"/>
-    <hyperlink ref="B84" r:id="rId209" xr:uid="{39C6DCAA-BE89-4B4F-BAB3-B01A8C5FED4E}"/>
-    <hyperlink ref="B85" r:id="rId210" xr:uid="{BD8ABE7B-7146-4F9C-B38C-CE77AC97911C}"/>
-    <hyperlink ref="D85" r:id="rId211" xr:uid="{575F04ED-6CE7-4807-8B13-F326EF7B2C8E}"/>
-    <hyperlink ref="E85" r:id="rId212" xr:uid="{681838FB-70EA-419D-BCE3-E08F5364A2E0}"/>
-    <hyperlink ref="D86" r:id="rId213" xr:uid="{4BFFDDEF-9B37-49D7-8898-707DFDE3F5A2}"/>
-    <hyperlink ref="E86" r:id="rId214" xr:uid="{9B9DFAF3-C1E1-423C-B6F9-E51D877DDB12}"/>
-    <hyperlink ref="B86" r:id="rId215" xr:uid="{59F2747A-CC65-4ED5-A56B-786A043CE67B}"/>
-    <hyperlink ref="D87" r:id="rId216" xr:uid="{ECC3D6DF-5B1B-4DC1-B19F-8886FD8EB116}"/>
-    <hyperlink ref="E87" r:id="rId217" xr:uid="{12F9552E-0BC3-4624-9123-B55AFBCCB562}"/>
-    <hyperlink ref="E88" r:id="rId218" xr:uid="{75179926-30E5-4350-921B-A5B14E1B232D}"/>
-    <hyperlink ref="B87" r:id="rId219" xr:uid="{EA078301-086A-4811-A4E1-A4C2AAE42D90}"/>
-    <hyperlink ref="D88" r:id="rId220" xr:uid="{C965BAE7-26E3-47CA-A128-1A1426B08287}"/>
-    <hyperlink ref="B88" r:id="rId221" xr:uid="{08F176CD-1942-484A-B91A-5E7D7BE2E642}"/>
-    <hyperlink ref="D62" r:id="rId222" xr:uid="{61B038FC-067A-4428-85A1-623DE325F1ED}"/>
-    <hyperlink ref="E62" r:id="rId223" xr:uid="{BB3648F4-8B0F-4A80-8F41-403E4053E2DA}"/>
-    <hyperlink ref="B62" r:id="rId224" xr:uid="{B824C2FD-2669-4F5E-A3AB-CBE4E6052B0C}"/>
-    <hyperlink ref="B63" r:id="rId225" xr:uid="{4654EB0D-7573-4009-B0CF-95DC2A913755}"/>
-    <hyperlink ref="D63" r:id="rId226" xr:uid="{8D237BAA-60AB-4BA0-B2C0-B05074E53B92}"/>
-    <hyperlink ref="E63" r:id="rId227" xr:uid="{C1E57DEC-20E0-487A-A1F8-F2C132F19122}"/>
-    <hyperlink ref="B79" r:id="rId228" xr:uid="{7578032B-1F3A-4539-8690-8C437B785A34}"/>
-    <hyperlink ref="E79" r:id="rId229" xr:uid="{F09459B5-03BF-4EB8-A810-ADCB843144F0}"/>
-    <hyperlink ref="D79" r:id="rId230" xr:uid="{CE2026CE-7571-4E0A-A6D8-C5CC51EE426C}"/>
+    <hyperlink ref="D55" r:id="rId152" xr:uid="{1B3BEB40-1EE5-404E-8CDC-AA9B3E1B0947}"/>
+    <hyperlink ref="E54" r:id="rId153" xr:uid="{EE68E9AD-2777-4231-AEE5-D934B4B626AB}"/>
+    <hyperlink ref="E55" r:id="rId154" xr:uid="{53BCCA0C-6DBE-4C35-8C04-CFBF70FA60F2}"/>
+    <hyperlink ref="D56" r:id="rId155" xr:uid="{9AA71A7E-44B8-470A-B313-862336B7F5A5}"/>
+    <hyperlink ref="E56" r:id="rId156" xr:uid="{585DECC9-3251-4499-892F-F9240A7EE776}"/>
+    <hyperlink ref="B56" r:id="rId157" xr:uid="{A373CF1C-3A6E-486F-B517-2C8792E95129}"/>
+    <hyperlink ref="D57" r:id="rId158" xr:uid="{F9CF8130-800A-487B-BFCE-4909473DADC4}"/>
+    <hyperlink ref="E57" r:id="rId159" xr:uid="{958AAFCE-E6FF-49DB-85E6-FEE7FAC835F5}"/>
+    <hyperlink ref="B57" r:id="rId160" xr:uid="{DCDF3C10-E8F4-45FB-B43E-916B3077418F}"/>
+    <hyperlink ref="B58" r:id="rId161" xr:uid="{9660E1B0-262B-4C02-B474-D0382995C450}"/>
+    <hyperlink ref="D58" r:id="rId162" xr:uid="{919F2C2C-62F0-4C8A-9785-233396A60613}"/>
+    <hyperlink ref="E58" r:id="rId163" xr:uid="{1E52A1A8-4704-4A25-8CEC-F89177A70432}"/>
+    <hyperlink ref="D59" r:id="rId164" xr:uid="{707A19C4-4FA3-438C-B15B-93A62BA351CF}"/>
+    <hyperlink ref="E59" r:id="rId165" xr:uid="{2443E35E-BC71-4101-8147-FA7277B1A04D}"/>
+    <hyperlink ref="B59" r:id="rId166" xr:uid="{597780D5-57AF-44E3-BC1D-DF5DF0B564E3}"/>
+    <hyperlink ref="D60" r:id="rId167" xr:uid="{9957E43F-25F9-4AD6-AF02-3042376D2CBC}"/>
+    <hyperlink ref="E60" r:id="rId168" xr:uid="{0A83859D-98FA-4037-A2BE-FA8F7CBE6E46}"/>
+    <hyperlink ref="B60" r:id="rId169" xr:uid="{2A7D74A8-8B5D-46CE-9350-0FAC4655511B}"/>
+    <hyperlink ref="D61" r:id="rId170" xr:uid="{0E22EB11-B3F4-4B3D-9949-5BB47BE472FF}"/>
+    <hyperlink ref="E61" r:id="rId171" xr:uid="{203E2512-19F8-444F-B5FE-FCEFA21380D9}"/>
+    <hyperlink ref="B61" r:id="rId172" xr:uid="{D42B148C-2E41-45DC-9406-03F899255054}"/>
+    <hyperlink ref="D72" r:id="rId173" xr:uid="{E8A08F00-2B07-41D3-BECA-92E437337767}"/>
+    <hyperlink ref="E72" r:id="rId174" xr:uid="{CC57E1D3-F163-4C30-A8C6-CA03AA34248D}"/>
+    <hyperlink ref="B72" r:id="rId175" xr:uid="{758C4E99-7187-45B3-B96E-4E1A344950BB}"/>
+    <hyperlink ref="D73" r:id="rId176" xr:uid="{8D6FE8C4-9089-409E-AC71-07A6BA994DD8}"/>
+    <hyperlink ref="E73" r:id="rId177" xr:uid="{C0915D43-2F9A-44CA-AA9B-2D6F571A6531}"/>
+    <hyperlink ref="B73" r:id="rId178" xr:uid="{BD35CE35-8B49-4F57-A541-E8AB4942E01C}"/>
+    <hyperlink ref="D76" r:id="rId179" xr:uid="{AD3B2EB4-61E6-4EC2-B841-C66ABAF57A8D}"/>
+    <hyperlink ref="E76" r:id="rId180" xr:uid="{CA19CD5B-D261-46F6-A06C-A6DD329847C8}"/>
+    <hyperlink ref="B76" r:id="rId181" xr:uid="{902A512C-7DB9-483B-922E-9EC9EB0A5727}"/>
+    <hyperlink ref="D77" r:id="rId182" xr:uid="{D37A5DB7-6170-4DB3-A6C4-6B7C3536BB6A}"/>
+    <hyperlink ref="E77" r:id="rId183" xr:uid="{5BE49E4F-CE72-4598-A298-9EA3583C9BB4}"/>
+    <hyperlink ref="B77" r:id="rId184" xr:uid="{218FE68B-E3EA-48FD-B04F-F05EC4D04342}"/>
+    <hyperlink ref="D78" r:id="rId185" xr:uid="{55D0245C-636D-41C8-8BEA-F7465FDF2FC1}"/>
+    <hyperlink ref="E78" r:id="rId186" xr:uid="{745BE301-751B-44AD-BB23-64393F55A01A}"/>
+    <hyperlink ref="B78" r:id="rId187" xr:uid="{72E099E5-D9E8-43F6-BA7B-AD0788C8ACDF}"/>
+    <hyperlink ref="D82" r:id="rId188" xr:uid="{670FA2F5-7537-44F0-A891-BC8F9FB0FDA1}"/>
+    <hyperlink ref="E82" r:id="rId189" xr:uid="{C44FBCC9-F7D2-411F-B321-7ACCA7BDB113}"/>
+    <hyperlink ref="B82" r:id="rId190" xr:uid="{7AAC8125-2903-4BEF-861C-0652EB8A1EBA}"/>
+    <hyperlink ref="D80" r:id="rId191" xr:uid="{4247E04D-3AB7-4CE4-8D6E-225BEB05B2EC}"/>
+    <hyperlink ref="E80" r:id="rId192" xr:uid="{3F6A67C6-2350-4E0B-855A-7A0CA546CADA}"/>
+    <hyperlink ref="B80" r:id="rId193" xr:uid="{EDAF1894-D1E3-4CB7-A453-D26D0CE785FC}"/>
+    <hyperlink ref="B81" r:id="rId194" xr:uid="{60D8C8EA-A2CC-4EC4-93CF-D8C6F9145025}"/>
+    <hyperlink ref="D81" r:id="rId195" xr:uid="{F6B676D4-F9FF-4FAC-BF4F-6B297B8E4386}"/>
+    <hyperlink ref="E81" r:id="rId196" xr:uid="{AD04D2E5-748B-41B8-A77F-6FE55DE52558}"/>
+    <hyperlink ref="D74" r:id="rId197" xr:uid="{2919C844-F24C-4EBC-BBC0-393934ACE57D}"/>
+    <hyperlink ref="E74" r:id="rId198" xr:uid="{16E264FE-A51B-4307-BAC2-77D48753B271}"/>
+    <hyperlink ref="D75" r:id="rId199" xr:uid="{923213AD-4D4E-456F-B24C-29D5EE8D2DC5}"/>
+    <hyperlink ref="E75" r:id="rId200" xr:uid="{0FB2A237-55E7-482E-BFDD-773D6CA63339}"/>
+    <hyperlink ref="D83" r:id="rId201" xr:uid="{0FB5C72B-F07D-4BAE-8F9A-333776CD5938}"/>
+    <hyperlink ref="E83" r:id="rId202" xr:uid="{1E54D0E6-426F-4655-B12E-6919FDCF820A}"/>
+    <hyperlink ref="B75" r:id="rId203" xr:uid="{6F4BDAA6-1768-40E1-BA7A-3A7B8F3E9DDF}"/>
+    <hyperlink ref="B83" r:id="rId204" xr:uid="{EBBCEFF8-5BDF-4051-A5A6-449AB5359B3C}"/>
+    <hyperlink ref="E84" r:id="rId205" xr:uid="{BE30CFAC-63AD-4E25-9DE4-2BF7C9B898E5}"/>
+    <hyperlink ref="D84" r:id="rId206" xr:uid="{3A9183DE-FD11-4043-B1A6-6E9E780E188A}"/>
+    <hyperlink ref="B84" r:id="rId207" xr:uid="{39C6DCAA-BE89-4B4F-BAB3-B01A8C5FED4E}"/>
+    <hyperlink ref="B85" r:id="rId208" xr:uid="{BD8ABE7B-7146-4F9C-B38C-CE77AC97911C}"/>
+    <hyperlink ref="D85" r:id="rId209" xr:uid="{575F04ED-6CE7-4807-8B13-F326EF7B2C8E}"/>
+    <hyperlink ref="E85" r:id="rId210" xr:uid="{681838FB-70EA-419D-BCE3-E08F5364A2E0}"/>
+    <hyperlink ref="D86" r:id="rId211" xr:uid="{4BFFDDEF-9B37-49D7-8898-707DFDE3F5A2}"/>
+    <hyperlink ref="E86" r:id="rId212" xr:uid="{9B9DFAF3-C1E1-423C-B6F9-E51D877DDB12}"/>
+    <hyperlink ref="B86" r:id="rId213" xr:uid="{59F2747A-CC65-4ED5-A56B-786A043CE67B}"/>
+    <hyperlink ref="D87" r:id="rId214" xr:uid="{ECC3D6DF-5B1B-4DC1-B19F-8886FD8EB116}"/>
+    <hyperlink ref="E87" r:id="rId215" xr:uid="{12F9552E-0BC3-4624-9123-B55AFBCCB562}"/>
+    <hyperlink ref="E88" r:id="rId216" xr:uid="{75179926-30E5-4350-921B-A5B14E1B232D}"/>
+    <hyperlink ref="B87" r:id="rId217" xr:uid="{EA078301-086A-4811-A4E1-A4C2AAE42D90}"/>
+    <hyperlink ref="D88" r:id="rId218" xr:uid="{C965BAE7-26E3-47CA-A128-1A1426B08287}"/>
+    <hyperlink ref="B88" r:id="rId219" xr:uid="{08F176CD-1942-484A-B91A-5E7D7BE2E642}"/>
+    <hyperlink ref="D62" r:id="rId220" xr:uid="{61B038FC-067A-4428-85A1-623DE325F1ED}"/>
+    <hyperlink ref="E62" r:id="rId221" xr:uid="{BB3648F4-8B0F-4A80-8F41-403E4053E2DA}"/>
+    <hyperlink ref="B62" r:id="rId222" xr:uid="{B824C2FD-2669-4F5E-A3AB-CBE4E6052B0C}"/>
+    <hyperlink ref="B63" r:id="rId223" xr:uid="{4654EB0D-7573-4009-B0CF-95DC2A913755}"/>
+    <hyperlink ref="D63" r:id="rId224" xr:uid="{8D237BAA-60AB-4BA0-B2C0-B05074E53B92}"/>
+    <hyperlink ref="E63" r:id="rId225" xr:uid="{C1E57DEC-20E0-487A-A1F8-F2C132F19122}"/>
+    <hyperlink ref="B79" r:id="rId226" xr:uid="{7578032B-1F3A-4539-8690-8C437B785A34}"/>
+    <hyperlink ref="E79" r:id="rId227" xr:uid="{F09459B5-03BF-4EB8-A810-ADCB843144F0}"/>
+    <hyperlink ref="D79" r:id="rId228" xr:uid="{CE2026CE-7571-4E0A-A6D8-C5CC51EE426C}"/>
+    <hyperlink ref="B54" r:id="rId229" xr:uid="{0B7CCEC9-99F8-480C-A814-A4B0A2739401}"/>
+    <hyperlink ref="B55" r:id="rId230" xr:uid="{F73EF657-8EB5-45AC-8396-34C949807F6C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId231"/>

--- a/Info/Additional_information.xlsx
+++ b/Info/Additional_information.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4512A1A4-9655-40A7-8AB9-6F0BA12A83C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A5E8BDA-4F5C-4C95-8CD4-18F35FED4E07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1284" uniqueCount="890">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1284" uniqueCount="891">
   <si>
     <t>good quality (UNC for UNC collection; UNC and XF for XF collection)</t>
   </si>
@@ -2750,6 +2750,9 @@
   </si>
   <si>
     <t>Num</t>
+  </si>
+  <si>
+    <t>A010-01-OA-GR</t>
   </si>
 </sst>
 </file>
@@ -7483,7 +7486,7 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>825</v>
+        <v>890</v>
       </c>
       <c r="B64" t="s">
         <v>796</v>

--- a/Info/Additional_information.xlsx
+++ b/Info/Additional_information.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A5E8BDA-4F5C-4C95-8CD4-18F35FED4E07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{071E7A64-7DE3-4C46-807E-55DB128E89F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1284" uniqueCount="891">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1284" uniqueCount="890">
   <si>
     <t>good quality (UNC for UNC collection; UNC and XF for XF collection)</t>
   </si>
@@ -2750,9 +2750,6 @@
   </si>
   <si>
     <t>Num</t>
-  </si>
-  <si>
-    <t>A010-01-OA-GR</t>
   </si>
 </sst>
 </file>
@@ -7486,7 +7483,7 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>890</v>
+        <v>824</v>
       </c>
       <c r="B64" t="s">
         <v>796</v>
